--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5919137-F823-48CC-B00B-48005600A117}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80CE465A-0C5E-458E-9CC8-D0AE9D6875F8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="367">
   <si>
     <t>UTK</t>
   </si>
@@ -384,7 +384,751 @@
     <t>304487344</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>SZ-860</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-829</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-827</t>
+  </si>
+  <si>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-840</t>
+  </si>
+  <si>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>NFD6-03-05-XR64</t>
+  </si>
+  <si>
+    <t>NFD6-03-06-ZR9C</t>
+  </si>
+  <si>
+    <t>NFD6-03-08-3J6T</t>
+  </si>
+  <si>
+    <t>NFD6-03-11-55HQ</t>
+  </si>
+  <si>
+    <t>NFD6-03-11-TYNX</t>
+  </si>
+  <si>
+    <t>NFD6-03-11-XC2P</t>
+  </si>
+  <si>
+    <t>NFD6-03-11-YCU9</t>
+  </si>
+  <si>
+    <t>NFD6-03-11-ZSWT</t>
+  </si>
+  <si>
+    <t>NFD6-03-12-5PZS</t>
+  </si>
+  <si>
+    <t>NFD6-03-12-5ZXB</t>
+  </si>
+  <si>
+    <t>NFD6-03-12-PSV3</t>
+  </si>
+  <si>
+    <t>NFD6-03-12-YMZA</t>
+  </si>
+  <si>
+    <t>NFD6-03-12-ZNGU</t>
+  </si>
+  <si>
+    <t>NFD6-03-13-6ASC</t>
+  </si>
+  <si>
+    <t>NFD6-03-13-8PPP</t>
+  </si>
+  <si>
+    <t>NFD6-03-13-AQKV</t>
+  </si>
+  <si>
+    <t>NFD6-03-13-JMD3</t>
+  </si>
+  <si>
+    <t>NFD6-03-13-LM4Z</t>
+  </si>
+  <si>
+    <t>NFD6-03-13-VJAC</t>
+  </si>
+  <si>
+    <t>NFD6-03-13-YGUN</t>
+  </si>
+  <si>
+    <t>NFD6-03-14-2LZF</t>
+  </si>
+  <si>
+    <t>NFD6-03-14-2WGD</t>
+  </si>
+  <si>
+    <t>NFD6-03-14-4BTZ/XD</t>
+  </si>
+  <si>
+    <t>NFD6-03-14-B3WN/XD</t>
+  </si>
+  <si>
+    <t>NFD6-03-14-D7V3</t>
+  </si>
+  <si>
+    <t>NFE6-03-05-VV5A</t>
+  </si>
+  <si>
+    <t>NFE6-03-11-4APB</t>
+  </si>
+  <si>
+    <t>NFE6-03-11-LACH</t>
+  </si>
+  <si>
+    <t>NFE6-03-13-3D8U</t>
+  </si>
+  <si>
+    <t>NFE6-03-13-76MJ</t>
+  </si>
+  <si>
+    <t>NFE6-03-13-8PGU</t>
+  </si>
+  <si>
+    <t>NFE6-03-13-AGA5</t>
+  </si>
+  <si>
+    <t>NFE6-03-13-DXRF</t>
+  </si>
+  <si>
+    <t>NFE6-03-14-6CCC</t>
+  </si>
+  <si>
+    <t>NFE6-03-14-8KAL</t>
+  </si>
+  <si>
+    <t>NFE6-03-14-EZDD</t>
+  </si>
+  <si>
+    <t>NFE6-03-14-HZMS</t>
+  </si>
+  <si>
+    <t>NFE6-03-14-L2CR</t>
+  </si>
+  <si>
+    <t>NFE6-03-15-Q2KT</t>
+  </si>
+  <si>
+    <t>R412480</t>
+  </si>
+  <si>
+    <t>SA26/H001101</t>
+  </si>
+  <si>
+    <t>SA26/H001148</t>
+  </si>
+  <si>
+    <t>267004042</t>
+  </si>
+  <si>
+    <t>267004040</t>
+  </si>
+  <si>
+    <t>2025-04-17-9CXK/CS</t>
+  </si>
+  <si>
+    <t>69b3d65b6967eb2a8b5cd169</t>
+  </si>
+  <si>
+    <t>69a560e451e7020fc80bf519</t>
+  </si>
+  <si>
+    <t>69b3e3656967eb2a8b5cd342</t>
+  </si>
+  <si>
+    <t>69b50e826967eb2a8b5ce26e</t>
+  </si>
+  <si>
+    <t>69b51c186967eb2a8b5ce304</t>
+  </si>
+  <si>
+    <t>69b12a5951e7020fc80cc98a</t>
+  </si>
+  <si>
+    <t>69b3e3286967eb2a8b5cd33f</t>
+  </si>
+  <si>
+    <t>69b400556967eb2a8b5cd7c3</t>
+  </si>
+  <si>
+    <t>69aee66151e7020fc80ca14e</t>
+  </si>
+  <si>
+    <t>69aee66151e7020fc80ca151</t>
+  </si>
+  <si>
+    <t>69b538f86967eb2a8b5ce608</t>
+  </si>
+  <si>
+    <t>69b7bfa36967eb2a8b5cf6b1</t>
+  </si>
+  <si>
+    <t>69b2bf2e6967eb2a8b5cc43b</t>
+  </si>
+  <si>
+    <t>69b3ecae6967eb2a8b5cd4c5</t>
+  </si>
+  <si>
+    <t>69b7d4d86967eb2a8b5cfab4</t>
+  </si>
+  <si>
+    <t>69b436ef6967eb2a8b5cde8f</t>
+  </si>
+  <si>
+    <t>69b436ef6967eb2a8b5cde92</t>
+  </si>
+  <si>
+    <t>69b16e8851e7020fc80cd78d</t>
+  </si>
+  <si>
+    <t>69b407bd6967eb2a8b5cd8d1</t>
+  </si>
+  <si>
+    <t>69b2ba0e6967eb2a8b5cc388</t>
+  </si>
+  <si>
+    <t>69b2ba0e6967eb2a8b5cc389</t>
+  </si>
+  <si>
+    <t>69b402bc6967eb2a8b5cd81c</t>
+  </si>
+  <si>
+    <t>69b2dc0b6967eb2a8b5cc80e</t>
+  </si>
+  <si>
+    <t>69b314476967eb2a8b5cccd8</t>
+  </si>
+  <si>
+    <t>69b3d2286967eb2a8b5cd0a1</t>
+  </si>
+  <si>
+    <t>69b3ed1f6967eb2a8b5cd4f0</t>
+  </si>
+  <si>
+    <t>69b3ee436967eb2a8b5cd506</t>
+  </si>
+  <si>
+    <t>69b402316967eb2a8b5cd80c</t>
+  </si>
+  <si>
+    <t>69b420ad6967eb2a8b5cdc1a</t>
+  </si>
+  <si>
+    <t>69b3c55b6967eb2a8b5ccf22</t>
+  </si>
+  <si>
+    <t>69b3d5a66967eb2a8b5cd147</t>
+  </si>
+  <si>
+    <t>69b408116967eb2a8b5cd8e8</t>
+  </si>
+  <si>
+    <t>69b438186967eb2a8b5cdeb3</t>
+  </si>
+  <si>
+    <t>69b45b436967eb2a8b5ce0aa</t>
+  </si>
+  <si>
+    <t>69b45ec56967eb2a8b5ce0d9</t>
+  </si>
+  <si>
+    <t>69b539166967eb2a8b5ce60f</t>
+  </si>
+  <si>
+    <t>69b539166967eb2a8b5ce610</t>
+  </si>
+  <si>
+    <t>69b55be86967eb2a8b5ce84c</t>
+  </si>
+  <si>
+    <t>69b5679d6967eb2a8b5ce915</t>
+  </si>
+  <si>
+    <t>69b538bc6967eb2a8b5ce5ea</t>
+  </si>
+  <si>
+    <t>69b538bc6967eb2a8b5ce5eb</t>
+  </si>
+  <si>
+    <t>69b5679d6967eb2a8b5ce912</t>
+  </si>
+  <si>
+    <t>69b570fb6967eb2a8b5ce9bb</t>
+  </si>
+  <si>
+    <t>69b5e5026967eb2a8b5ced7e</t>
+  </si>
+  <si>
+    <t>69b7f6b4d96b4f4a2437b6e0</t>
+  </si>
+  <si>
+    <t>303328609/1</t>
+  </si>
+  <si>
+    <t>303480735/1</t>
+  </si>
+  <si>
+    <t>303480735/2</t>
+  </si>
+  <si>
+    <t>303622400/1</t>
+  </si>
+  <si>
+    <t>303622400/2</t>
+  </si>
+  <si>
+    <t>303622400/3</t>
+  </si>
+  <si>
+    <t>303622412/1</t>
+  </si>
+  <si>
+    <t>303795368/1</t>
+  </si>
+  <si>
+    <t>303795664/1</t>
+  </si>
+  <si>
+    <t>303971373/1</t>
+  </si>
+  <si>
+    <t>303971373/2</t>
+  </si>
+  <si>
+    <t>303971373/3</t>
+  </si>
+  <si>
+    <t>304013150/1</t>
+  </si>
+  <si>
+    <t>304013150/2</t>
+  </si>
+  <si>
+    <t>304013150/3</t>
+  </si>
+  <si>
+    <t>304013257/1</t>
+  </si>
+  <si>
+    <t>304064433/1</t>
+  </si>
+  <si>
+    <t>304064475/1</t>
+  </si>
+  <si>
+    <t>304065375/1</t>
+  </si>
+  <si>
+    <t>304104837/1</t>
+  </si>
+  <si>
+    <t>304105182/1</t>
+  </si>
+  <si>
+    <t>304105283/1</t>
+  </si>
+  <si>
+    <t>304105312/1</t>
+  </si>
+  <si>
+    <t>304105312/2</t>
+  </si>
+  <si>
+    <t>304148879/1</t>
+  </si>
+  <si>
+    <t>304149201/1</t>
+  </si>
+  <si>
+    <t>304149235/1</t>
+  </si>
+  <si>
+    <t>304149312/1</t>
+  </si>
+  <si>
+    <t>304149395/1</t>
+  </si>
+  <si>
+    <t>304149470/1</t>
+  </si>
+  <si>
+    <t>304149556/1</t>
+  </si>
+  <si>
+    <t>304149556/2</t>
+  </si>
+  <si>
+    <t>304149556/3</t>
+  </si>
+  <si>
+    <t>304149602/1</t>
+  </si>
+  <si>
+    <t>304149705/1</t>
+  </si>
+  <si>
+    <t>304198423/1</t>
+  </si>
+  <si>
+    <t>304198423/2</t>
+  </si>
+  <si>
+    <t>304198451/1</t>
+  </si>
+  <si>
+    <t>304198673/1</t>
+  </si>
+  <si>
+    <t>304198722/1</t>
+  </si>
+  <si>
+    <t>304198847/1</t>
+  </si>
+  <si>
+    <t>304198975/1</t>
+  </si>
+  <si>
+    <t>304199224/1</t>
+  </si>
+  <si>
+    <t>304199306/1</t>
+  </si>
+  <si>
+    <t>304248127/1</t>
+  </si>
+  <si>
+    <t>304248184/1</t>
+  </si>
+  <si>
+    <t>304248184/2</t>
+  </si>
+  <si>
+    <t>304248259/1</t>
+  </si>
+  <si>
+    <t>304248375/1</t>
+  </si>
+  <si>
+    <t>304248471/1</t>
+  </si>
+  <si>
+    <t>304248525/1</t>
+  </si>
+  <si>
+    <t>304248563/1</t>
+  </si>
+  <si>
+    <t>304248703/1</t>
+  </si>
+  <si>
+    <t>304248846/1</t>
+  </si>
+  <si>
+    <t>304248944/1</t>
+  </si>
+  <si>
+    <t>304248996/1</t>
+  </si>
+  <si>
+    <t>304249020/1</t>
+  </si>
+  <si>
+    <t>304249101/1</t>
+  </si>
+  <si>
+    <t>304308923/1</t>
+  </si>
+  <si>
+    <t>304309237/1</t>
+  </si>
+  <si>
+    <t>304309260/1</t>
+  </si>
+  <si>
+    <t>304309339/1</t>
+  </si>
+  <si>
+    <t>304309452/1</t>
+  </si>
+  <si>
+    <t>304309507/1</t>
+  </si>
+  <si>
+    <t>304309534/1</t>
+  </si>
+  <si>
+    <t>304309762/1</t>
+  </si>
+  <si>
+    <t>304362291/1</t>
+  </si>
+  <si>
+    <t>304362458/1</t>
+  </si>
+  <si>
+    <t>304362479/1</t>
+  </si>
+  <si>
+    <t>304362479/2</t>
+  </si>
+  <si>
+    <t>304362511/1</t>
+  </si>
+  <si>
+    <t>304362625/1</t>
+  </si>
+  <si>
+    <t>304362738/1</t>
+  </si>
+  <si>
+    <t>304362883/1</t>
+  </si>
+  <si>
+    <t>304362906/1</t>
+  </si>
+  <si>
+    <t>304362906/2</t>
+  </si>
+  <si>
+    <t>304362906/3</t>
+  </si>
+  <si>
+    <t>304362952/1</t>
+  </si>
+  <si>
+    <t>304362992/1</t>
+  </si>
+  <si>
+    <t>304363211/1</t>
+  </si>
+  <si>
+    <t>304429556/1</t>
+  </si>
+  <si>
+    <t>304429684/1</t>
+  </si>
+  <si>
+    <t>304429764/1</t>
+  </si>
+  <si>
+    <t>304429878/1</t>
+  </si>
+  <si>
+    <t>304429974/1</t>
+  </si>
+  <si>
+    <t>304430145/1</t>
+  </si>
+  <si>
+    <t>304430343/1</t>
+  </si>
+  <si>
+    <t>304487077/1</t>
+  </si>
+  <si>
+    <t>304487312/1</t>
+  </si>
+  <si>
+    <t>304487344/1</t>
+  </si>
+  <si>
+    <t>202603162600550101</t>
+  </si>
+  <si>
+    <t>202603162600550102</t>
+  </si>
+  <si>
+    <t>202603162600559901</t>
+  </si>
+  <si>
+    <t>202603162600571601</t>
+  </si>
+  <si>
+    <t>202603162600592601</t>
+  </si>
+  <si>
+    <t>202603162600595201</t>
+  </si>
+  <si>
+    <t>202603162600607801</t>
+  </si>
+  <si>
+    <t>202603162600593101</t>
+  </si>
+  <si>
+    <t>202603162600590601</t>
+  </si>
+  <si>
+    <t>202603162600601101</t>
+  </si>
+  <si>
+    <t>202603162600600301</t>
+  </si>
+  <si>
+    <t>202603162600596701</t>
+  </si>
+  <si>
+    <t>202603162600597701</t>
+  </si>
+  <si>
+    <t>202603162600598301</t>
+  </si>
+  <si>
+    <t>202603162600610501</t>
+  </si>
+  <si>
+    <t>202603162600605801</t>
+  </si>
+  <si>
+    <t>202603162600605401</t>
+  </si>
+  <si>
+    <t>202603162600609001</t>
+  </si>
+  <si>
+    <t>202603162600605501</t>
+  </si>
+  <si>
+    <t>202603162600612901</t>
+  </si>
+  <si>
+    <t>202603162600610301</t>
+  </si>
+  <si>
+    <t>202603162600621801</t>
+  </si>
+  <si>
+    <t>202603162600617901</t>
+  </si>
+  <si>
+    <t>202603162600622101</t>
+  </si>
+  <si>
+    <t>202603162600556101</t>
+  </si>
+  <si>
+    <t>202603162600595901</t>
+  </si>
+  <si>
+    <t>202603162600594201</t>
+  </si>
+  <si>
+    <t>202603162600611901</t>
+  </si>
+  <si>
+    <t>202603162600613601</t>
+  </si>
+  <si>
+    <t>202603162600614001</t>
+  </si>
+  <si>
+    <t>202603162600610901</t>
+  </si>
+  <si>
+    <t>202603162600613901</t>
+  </si>
+  <si>
+    <t>202603162600619701</t>
+  </si>
+  <si>
+    <t>202603162600621601</t>
+  </si>
+  <si>
+    <t>202603162600620301</t>
+  </si>
+  <si>
+    <t>202603162600620302</t>
+  </si>
+  <si>
+    <t>202603162600624001</t>
+  </si>
+  <si>
+    <t>202603162600625101</t>
+  </si>
+  <si>
+    <t>202603162600625801</t>
+  </si>
+  <si>
+    <t>202603162600625802</t>
+  </si>
+  <si>
+    <t>159995579538047732</t>
+  </si>
+  <si>
+    <t>159995579538047749</t>
+  </si>
+  <si>
+    <t>159995579538217098</t>
+  </si>
+  <si>
+    <t>159995579538217104</t>
+  </si>
+  <si>
+    <t>159995579538231292</t>
+  </si>
+  <si>
+    <t>159995579538231308</t>
+  </si>
+  <si>
+    <t>NFD6-03-14-4BTZ/XD1</t>
   </si>
 </sst>
 </file>
@@ -420,10 +1164,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -705,12 +1448,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D116"/>
+  <dimension ref="A1:D190"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" style="1"/>
+    <col min="1" max="1" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
@@ -726,923 +1469,2082 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>186</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B4" s="1" t="s">
+        <v>187</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B5" s="1" t="s">
+        <v>188</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="B6" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B7" s="1" t="s">
+        <v>190</v>
+      </c>
       <c r="C7" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="B8" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="C8" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B9" s="1" t="s">
+        <v>192</v>
+      </c>
       <c r="C9" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>12</v>
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B14" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="B15" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="B16" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="B17" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="B19" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="B20" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="B21" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>24</v>
+      <c r="B23" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="B27" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="B28" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="B29" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="B30" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="B31" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="B32" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="B33" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="B34" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="B35" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="B36" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="B37" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+      <c r="B39" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+      <c r="B40" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="B41" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="B43" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="B44" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="B45" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+      <c r="B46" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+      <c r="B47" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+      <c r="B48" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+      <c r="B50" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+      <c r="B53" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+      <c r="B54" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+      <c r="B55" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+      <c r="B56" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+      <c r="B59" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
+      <c r="B62" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+      <c r="B63" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
+      <c r="B64" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>66</v>
+      <c r="B65" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
+      <c r="B81" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
+      <c r="B82" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>85</v>
+      <c r="B84" s="1" t="s">
+        <v>267</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>86</v>
+      <c r="A85" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>87</v>
+      <c r="A86" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>269</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
+      <c r="A87" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
+      <c r="B104" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
+      <c r="B105" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
+      <c r="B106" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
+      <c r="B107" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
+      <c r="B108" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
+      <c r="B109" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" s="2" t="s">
-        <v>111</v>
+      <c r="B110" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
-        <v>112</v>
+      <c r="A111" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" s="2" t="s">
-        <v>113</v>
+      <c r="A112" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>295</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" s="2" t="s">
-        <v>114</v>
+      <c r="A113" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>296</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114" s="2" t="s">
-        <v>115</v>
+      <c r="A114" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>297</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
-        <v>116</v>
+      <c r="A115" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>298</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" s="2" t="s">
-        <v>117</v>
+      <c r="A116" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>118</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C566192-2600-46E1-9DF3-601FFF1EDC57}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{288C945F-D63E-4F3E-8F22-8FB69ED17C6C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="321">
   <si>
     <t>UTK</t>
   </si>
@@ -342,7 +342,655 @@
     <t>99002215</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>SZ-827</t>
+  </si>
+  <si>
+    <t>SZ-829</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-860</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-840</t>
+  </si>
+  <si>
+    <t>1-2230/2026</t>
+  </si>
+  <si>
+    <t>1001822123 árukereső</t>
+  </si>
+  <si>
+    <t>267004149</t>
+  </si>
+  <si>
+    <t>26MPE0003027</t>
+  </si>
+  <si>
+    <t>NFD6-03-06-JW48</t>
+  </si>
+  <si>
+    <t>NFD6-03-08-5T23/XD</t>
+  </si>
+  <si>
+    <t>NFD6-03-09-Z4RJ</t>
+  </si>
+  <si>
+    <t>NFD6-03-11-BMYG</t>
+  </si>
+  <si>
+    <t>NFD6-03-12-W9CB</t>
+  </si>
+  <si>
+    <t>NFD6-03-13-APKE</t>
+  </si>
+  <si>
+    <t>NFD6-03-14-877R</t>
+  </si>
+  <si>
+    <t>NFD6-03-14-8PSM</t>
+  </si>
+  <si>
+    <t>NFD6-03-14-RE4Z</t>
+  </si>
+  <si>
+    <t>NFD6-03-16-3VEY</t>
+  </si>
+  <si>
+    <t>NFD6-03-16-8C2M</t>
+  </si>
+  <si>
+    <t>NFD6-03-16-9PSK</t>
+  </si>
+  <si>
+    <t>NFD6-03-16-C9JA</t>
+  </si>
+  <si>
+    <t>NFD6-03-16-ECAG</t>
+  </si>
+  <si>
+    <t>NFD6-03-16-GYWA</t>
+  </si>
+  <si>
+    <t>NFD6-03-16-JVWS</t>
+  </si>
+  <si>
+    <t>NFD6-03-16-L63L</t>
+  </si>
+  <si>
+    <t>NFD6-03-16-Y6M6</t>
+  </si>
+  <si>
+    <t>NFD6-03-16-ZHNK</t>
+  </si>
+  <si>
+    <t>NFE6-03-09-EEYZ</t>
+  </si>
+  <si>
+    <t>NFE6-03-15-QRLT</t>
+  </si>
+  <si>
+    <t>NFE6-03-16-28D6</t>
+  </si>
+  <si>
+    <t>NFE6-03-16-6K3E</t>
+  </si>
+  <si>
+    <t>NFE6-03-16-UT6R</t>
+  </si>
+  <si>
+    <t>SA26/H000996</t>
+  </si>
+  <si>
+    <t>267004091</t>
+  </si>
+  <si>
+    <t>267004116</t>
+  </si>
+  <si>
+    <t>267004055</t>
+  </si>
+  <si>
+    <t>267004038</t>
+  </si>
+  <si>
+    <t>267004103</t>
+  </si>
+  <si>
+    <t>267004092</t>
+  </si>
+  <si>
+    <t>159995579538264658</t>
+  </si>
+  <si>
+    <t>159995579538236723</t>
+  </si>
+  <si>
+    <t>248743260/1</t>
+  </si>
+  <si>
+    <t>248743260/2</t>
+  </si>
+  <si>
+    <t>248744005/1</t>
+  </si>
+  <si>
+    <t>69b4261c6967eb2a8b5cdce6</t>
+  </si>
+  <si>
+    <t>69b7e2616967eb2a8b5cfd02</t>
+  </si>
+  <si>
+    <t>69b457856967eb2a8b5ce07b</t>
+  </si>
+  <si>
+    <t>69b51c186967eb2a8b5ce304</t>
+  </si>
+  <si>
+    <t>69afc2ea51e7020fc80ca938</t>
+  </si>
+  <si>
+    <t>69b40a186967eb2a8b5cd933</t>
+  </si>
+  <si>
+    <t>69b90df4d96b4f4a2437c591</t>
+  </si>
+  <si>
+    <t>69b806fad96b4f4a2437b967</t>
+  </si>
+  <si>
+    <t>69b914a8d96b4f4a2437c6b9</t>
+  </si>
+  <si>
+    <t>69b547866967eb2a8b5ce70e</t>
+  </si>
+  <si>
+    <t>69b92325d96b4f4a2437c8ef</t>
+  </si>
+  <si>
+    <t>69b838a4d96b4f4a2437c075</t>
+  </si>
+  <si>
+    <t>69b2d7596967eb2a8b5cc782</t>
+  </si>
+  <si>
+    <t>69b314476967eb2a8b5cccd8</t>
+  </si>
+  <si>
+    <t>69b40f176967eb2a8b5cd9d4</t>
+  </si>
+  <si>
+    <t>69b421f96967eb2a8b5cdc5f</t>
+  </si>
+  <si>
+    <t>69b42eba6967eb2a8b5cddbc</t>
+  </si>
+  <si>
+    <t>69b42eba6967eb2a8b5cddbd</t>
+  </si>
+  <si>
+    <t>69b4336a6967eb2a8b5cde4a</t>
+  </si>
+  <si>
+    <t>69b458ec6967eb2a8b5ce09d</t>
+  </si>
+  <si>
+    <t>69b483136967eb2a8b5ce1c2</t>
+  </si>
+  <si>
+    <t>69b47c126967eb2a8b5ce18e</t>
+  </si>
+  <si>
+    <t>69b538bd6967eb2a8b5ce5fc</t>
+  </si>
+  <si>
+    <t>69b538bd6967eb2a8b5ce5fd</t>
+  </si>
+  <si>
+    <t>69b5679d6967eb2a8b5ce915</t>
+  </si>
+  <si>
+    <t>69b56c4c6967eb2a8b5ce964</t>
+  </si>
+  <si>
+    <t>69b580396967eb2a8b5cea90</t>
+  </si>
+  <si>
+    <t>69b50e896967eb2a8b5ce271</t>
+  </si>
+  <si>
+    <t>69b524286967eb2a8b5ce3d6</t>
+  </si>
+  <si>
+    <t>69b582976967eb2a8b5cead5</t>
+  </si>
+  <si>
+    <t>69b5cc666967eb2a8b5ced24</t>
+  </si>
+  <si>
+    <t>69b5dbbc6967eb2a8b5ced60</t>
+  </si>
+  <si>
+    <t>69b6a7876967eb2a8b5cf04a</t>
+  </si>
+  <si>
+    <t>69b646476967eb2a8b5ced9f</t>
+  </si>
+  <si>
+    <t>69b7066f6967eb2a8b5cf35f</t>
+  </si>
+  <si>
+    <t>69b70a346967eb2a8b5cf393</t>
+  </si>
+  <si>
+    <t>69b718056967eb2a8b5cf3ed</t>
+  </si>
+  <si>
+    <t>69b7d4c36967eb2a8b5cfaac</t>
+  </si>
+  <si>
+    <t>69b7d4c36967eb2a8b5cfaad</t>
+  </si>
+  <si>
+    <t>69b7fc90d96b4f4a2437b79c</t>
+  </si>
+  <si>
+    <t>69b80714d96b4f4a2437b972</t>
+  </si>
+  <si>
+    <t>69b80977d96b4f4a2437b9f2</t>
+  </si>
+  <si>
+    <t>69b849e3d96b4f4a2437c197</t>
+  </si>
+  <si>
+    <t>69b849e3d96b4f4a2437c198</t>
+  </si>
+  <si>
+    <t>69b85b98d96b4f4a2437c256</t>
+  </si>
+  <si>
+    <t>69b7c0c86967eb2a8b5cf6e2</t>
+  </si>
+  <si>
+    <t>69b93d97d96b4f4a2437cd08</t>
+  </si>
+  <si>
+    <t>69b849e3d96b4f4a2437c19b</t>
+  </si>
+  <si>
+    <t>69b8779dd96b4f4a2437c318</t>
+  </si>
+  <si>
+    <t>69b863b0d96b4f4a2437c290</t>
+  </si>
+  <si>
+    <t>69b856c9d96b4f4a2437c22b</t>
+  </si>
+  <si>
+    <t>FIZZ-1000825747_2</t>
+  </si>
+  <si>
+    <t>26MPE0003027/1</t>
+  </si>
+  <si>
+    <t>303536248/1</t>
+  </si>
+  <si>
+    <t>303710089/1</t>
+  </si>
+  <si>
+    <t>303710089/2</t>
+  </si>
+  <si>
+    <t>303710089/3</t>
+  </si>
+  <si>
+    <t>303795481/1</t>
+  </si>
+  <si>
+    <t>303795481/2</t>
+  </si>
+  <si>
+    <t>303838529/1</t>
+  </si>
+  <si>
+    <t>303838529/2</t>
+  </si>
+  <si>
+    <t>303838529/3</t>
+  </si>
+  <si>
+    <t>304012943/1</t>
+  </si>
+  <si>
+    <t>304105423/1</t>
+  </si>
+  <si>
+    <t>304149784/1</t>
+  </si>
+  <si>
+    <t>304149784/2</t>
+  </si>
+  <si>
+    <t>304149784/3</t>
+  </si>
+  <si>
+    <t>304198600/1</t>
+  </si>
+  <si>
+    <t>304198600/2</t>
+  </si>
+  <si>
+    <t>304198600/3</t>
+  </si>
+  <si>
+    <t>304198657/1</t>
+  </si>
+  <si>
+    <t>304198774/1</t>
+  </si>
+  <si>
+    <t>304198801/1</t>
+  </si>
+  <si>
+    <t>304198801/2</t>
+  </si>
+  <si>
+    <t>304248184/1</t>
+  </si>
+  <si>
+    <t>304248184/2</t>
+  </si>
+  <si>
+    <t>304248693/1</t>
+  </si>
+  <si>
+    <t>304309583/1</t>
+  </si>
+  <si>
+    <t>304309706/1</t>
+  </si>
+  <si>
+    <t>304309706/2</t>
+  </si>
+  <si>
+    <t>304309706/3</t>
+  </si>
+  <si>
+    <t>304309794/1</t>
+  </si>
+  <si>
+    <t>304309904/1</t>
+  </si>
+  <si>
+    <t>304309911/1</t>
+  </si>
+  <si>
+    <t>304429580/1</t>
+  </si>
+  <si>
+    <t>304429580/2</t>
+  </si>
+  <si>
+    <t>304429684/1</t>
+  </si>
+  <si>
+    <t>304429700/1</t>
+  </si>
+  <si>
+    <t>304430496/1</t>
+  </si>
+  <si>
+    <t>304430496/2</t>
+  </si>
+  <si>
+    <t>304487030/1</t>
+  </si>
+  <si>
+    <t>304487174/1</t>
+  </si>
+  <si>
+    <t>304487263/1</t>
+  </si>
+  <si>
+    <t>304487527/1</t>
+  </si>
+  <si>
+    <t>304487531/1</t>
+  </si>
+  <si>
+    <t>304487531/2</t>
+  </si>
+  <si>
+    <t>304487531/3</t>
+  </si>
+  <si>
+    <t>304487557/1</t>
+  </si>
+  <si>
+    <t>304487596/1</t>
+  </si>
+  <si>
+    <t>304487622/1</t>
+  </si>
+  <si>
+    <t>304487693/1</t>
+  </si>
+  <si>
+    <t>304487754/1</t>
+  </si>
+  <si>
+    <t>304487842/1</t>
+  </si>
+  <si>
+    <t>304487946/1</t>
+  </si>
+  <si>
+    <t>304487984/1</t>
+  </si>
+  <si>
+    <t>304488013/1</t>
+  </si>
+  <si>
+    <t>304543850/1</t>
+  </si>
+  <si>
+    <t>304544037/1</t>
+  </si>
+  <si>
+    <t>304544088/1</t>
+  </si>
+  <si>
+    <t>304544088/2</t>
+  </si>
+  <si>
+    <t>304544148/1</t>
+  </si>
+  <si>
+    <t>304544221/1</t>
+  </si>
+  <si>
+    <t>304544432/1</t>
+  </si>
+  <si>
+    <t>304544500/1</t>
+  </si>
+  <si>
+    <t>304544529/1</t>
+  </si>
+  <si>
+    <t>304544573/1</t>
+  </si>
+  <si>
+    <t>304544655/1</t>
+  </si>
+  <si>
+    <t>304544655/2</t>
+  </si>
+  <si>
+    <t>304544726/1</t>
+  </si>
+  <si>
+    <t>304577138/1</t>
+  </si>
+  <si>
+    <t>304577138/2</t>
+  </si>
+  <si>
+    <t>304577375/1</t>
+  </si>
+  <si>
+    <t>304618750/1</t>
+  </si>
+  <si>
+    <t>304618762/1</t>
+  </si>
+  <si>
+    <t>99002215/1</t>
+  </si>
+  <si>
+    <t>202603162600560501</t>
+  </si>
+  <si>
+    <t>202603162600560502</t>
+  </si>
+  <si>
+    <t>159995579537972639</t>
+  </si>
+  <si>
+    <t>159995579537972707</t>
+  </si>
+  <si>
+    <t>202603172600581901</t>
+  </si>
+  <si>
+    <t>202603172600581902</t>
+  </si>
+  <si>
+    <t>202603172600581903</t>
+  </si>
+  <si>
+    <t>202603162600591501</t>
+  </si>
+  <si>
+    <t>202603162600600001</t>
+  </si>
+  <si>
+    <t>202603162600605201</t>
+  </si>
+  <si>
+    <t>202603172600624301</t>
+  </si>
+  <si>
+    <t>202603162600614301</t>
+  </si>
+  <si>
+    <t>202603172600614601</t>
+  </si>
+  <si>
+    <t>202603172600640101</t>
+  </si>
+  <si>
+    <t>202603172600640701</t>
+  </si>
+  <si>
+    <t>202603172600632001</t>
+  </si>
+  <si>
+    <t>202603172600635501</t>
+  </si>
+  <si>
+    <t>202603172600633001</t>
+  </si>
+  <si>
+    <t>202603172600633002</t>
+  </si>
+  <si>
+    <t>202603172600633003</t>
+  </si>
+  <si>
+    <t>202603172600635001</t>
+  </si>
+  <si>
+    <t>202603172600637801</t>
+  </si>
+  <si>
+    <t>202603172600639201</t>
+  </si>
+  <si>
+    <t>202603172600638001</t>
+  </si>
+  <si>
+    <t>202603172600636901</t>
+  </si>
+  <si>
+    <t>202603172600577001</t>
+  </si>
+  <si>
+    <t>202603162600629901</t>
+  </si>
+  <si>
+    <t>202603172600632601</t>
+  </si>
+  <si>
+    <t>202603172600634801</t>
+  </si>
+  <si>
+    <t>202603172600636701</t>
+  </si>
+  <si>
+    <t>159995579537957827</t>
+  </si>
+  <si>
+    <t>159995579537957834</t>
   </si>
 </sst>
 </file>
@@ -378,10 +1026,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -663,10 +1310,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D169"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="1"/>
@@ -684,811 +1331,1851 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
+      <c r="A2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="B6" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="B7" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B8" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="B9" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="B11" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B12" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="B13" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="B14" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B15" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B16" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="B17" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="B18" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="B19" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="B20" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="B21" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="B22" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="B23" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="B25" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="B26" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="B27" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="B28" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="B29" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="B31" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="B32" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="B33" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="B34" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="B35" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="B36" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="B37" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="B38" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="B39" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+      <c r="B40" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+      <c r="B41" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="B42" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="B43" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="B44" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="B46" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+      <c r="B47" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+      <c r="B48" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+      <c r="B49" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+      <c r="B51" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+      <c r="B52" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+      <c r="B53" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+      <c r="B54" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+      <c r="B55" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+      <c r="B56" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
+      <c r="B57" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+      <c r="B60" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
+      <c r="B61" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
+      <c r="B64" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>68</v>
+      <c r="B66" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>69</v>
+      <c r="A67" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>70</v>
+      <c r="A68" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
+      <c r="B91" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
+      <c r="B93" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
+      <c r="B94" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
+      <c r="B95" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
+      <c r="B97" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
+      <c r="B98" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
+      <c r="B99" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>101</v>
+      <c r="B100" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
+      <c r="A101" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="B130" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C162" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C102" s="1" t="s">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C163" s="1" t="s">
         <v>104</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2E8B8C-8C03-42DD-9C01-27D4EFE56E93}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FFEF9EC-C371-4F3D-9020-D56BBBEED1A0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="331">
   <si>
     <t>UTK</t>
   </si>
@@ -363,7 +363,664 @@
     <t>304727116</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>SZ-829</t>
+  </si>
+  <si>
+    <t>SZ-840</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>1001822123 árukereső</t>
+  </si>
+  <si>
+    <t>267003822</t>
+  </si>
+  <si>
+    <t>267004130</t>
+  </si>
+  <si>
+    <t>267004139</t>
+  </si>
+  <si>
+    <t>267004163</t>
+  </si>
+  <si>
+    <t>267004169</t>
+  </si>
+  <si>
+    <t>267004175</t>
+  </si>
+  <si>
+    <t>267004177</t>
+  </si>
+  <si>
+    <t>26MPE0002981</t>
+  </si>
+  <si>
+    <t>ID4993_XD</t>
+  </si>
+  <si>
+    <t>NFD6-03-01-CD3V/CSXD</t>
+  </si>
+  <si>
+    <t>NFD6-03-14-ARE6</t>
+  </si>
+  <si>
+    <t>NFD6-03-14-EXMJ</t>
+  </si>
+  <si>
+    <t>NFD6-03-14-XK5S</t>
+  </si>
+  <si>
+    <t>NFD6-03-16-SHJH</t>
+  </si>
+  <si>
+    <t>NFD6-03-16-ZZNQ</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-545T</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-8NSY</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-9ALH</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-ALAA</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-AR33</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-KEES</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-KW5E</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-LMM5</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-TQMA</t>
+  </si>
+  <si>
+    <t>NFE6-03-16-QMH5</t>
+  </si>
+  <si>
+    <t>NFE6-03-17-C2S3</t>
+  </si>
+  <si>
+    <t>NFE6-03-17-GVR7</t>
+  </si>
+  <si>
+    <t>NFE6-03-17-JC4T</t>
+  </si>
+  <si>
+    <t>NFE6-03-17-SH2T</t>
+  </si>
+  <si>
+    <t>NFD6-03-07-KVGL</t>
+  </si>
+  <si>
+    <t>267004104</t>
+  </si>
+  <si>
+    <t>267003977</t>
+  </si>
+  <si>
+    <t>159995579538236723</t>
+  </si>
+  <si>
+    <t>69b3d65b6967eb2a8b5cd169</t>
+  </si>
+  <si>
+    <t>69a6d6b851e7020fc80c1786</t>
+  </si>
+  <si>
+    <t>69aa854851e7020fc80c5adc</t>
+  </si>
+  <si>
+    <t>69b7e2616967eb2a8b5cfd02</t>
+  </si>
+  <si>
+    <t>69b3d6d36967eb2a8b5cd16c</t>
+  </si>
+  <si>
+    <t>69b0414851e7020fc80cc057</t>
+  </si>
+  <si>
+    <t>69b0414851e7020fc80cc058</t>
+  </si>
+  <si>
+    <t>69b93b68d96b4f4a2437cce0</t>
+  </si>
+  <si>
+    <t>69ba371ad96b4f4a2437db56</t>
+  </si>
+  <si>
+    <t>69b05e8951e7020fc80cc390</t>
+  </si>
+  <si>
+    <t>69b29d536967eb2a8b5cbf82</t>
+  </si>
+  <si>
+    <t>69b95688d96b4f4a2437d0bb</t>
+  </si>
+  <si>
+    <t>69b1469551e7020fc80ccffc</t>
+  </si>
+  <si>
+    <t>69b1469551e7020fc80ccffe</t>
+  </si>
+  <si>
+    <t>69b1aa6751e7020fc80ce0f4</t>
+  </si>
+  <si>
+    <t>69b96685d96b4f4a2437d364</t>
+  </si>
+  <si>
+    <t>69b405ba6967eb2a8b5cd895</t>
+  </si>
+  <si>
+    <t>69b423056967eb2a8b5cdc74</t>
+  </si>
+  <si>
+    <t>69b51efd6967eb2a8b5ce356</t>
+  </si>
+  <si>
+    <t>69b538bd6967eb2a8b5ce5fc</t>
+  </si>
+  <si>
+    <t>69b538bd6967eb2a8b5ce5fd</t>
+  </si>
+  <si>
+    <t>69b53d6b6967eb2a8b5ce670</t>
+  </si>
+  <si>
+    <t>69b926a9d96b4f4a2437c995</t>
+  </si>
+  <si>
+    <t>69b65c8c6967eb2a8b5cee01</t>
+  </si>
+  <si>
+    <t>69b90922d96b4f4a2437c50f</t>
+  </si>
+  <si>
+    <t>69b7f327d96b4f4a2437b648</t>
+  </si>
+  <si>
+    <t>69b7fb69d96b4f4a2437b76d</t>
+  </si>
+  <si>
+    <t>69b80cffd96b4f4a2437ba9f</t>
+  </si>
+  <si>
+    <t>69b812e5d96b4f4a2437bb88</t>
+  </si>
+  <si>
+    <t>69ba5edad96b4f4a2437dcee</t>
+  </si>
+  <si>
+    <t>69b840a7d96b4f4a2437c10c</t>
+  </si>
+  <si>
+    <t>69b840a7d96b4f4a2437c10d</t>
+  </si>
+  <si>
+    <t>69b99012d96b4f4a2437d86c</t>
+  </si>
+  <si>
+    <t>69b7b6396967eb2a8b5cf59a</t>
+  </si>
+  <si>
+    <t>69b8152cd96b4f4a2437bbe0</t>
+  </si>
+  <si>
+    <t>69b8152cd96b4f4a2437bbe4</t>
+  </si>
+  <si>
+    <t>69b85920d96b4f4a2437c238</t>
+  </si>
+  <si>
+    <t>69b85920d96b4f4a2437c239</t>
+  </si>
+  <si>
+    <t>69b85a52d96b4f4a2437c23f</t>
+  </si>
+  <si>
+    <t>69b85a52d96b4f4a2437c240</t>
+  </si>
+  <si>
+    <t>69b97292d96b4f4a2437d51c</t>
+  </si>
+  <si>
+    <t>69b9aaa1d96b4f4a2437d9fe</t>
+  </si>
+  <si>
+    <t>69b95198d96b4f4a2437cfdd</t>
+  </si>
+  <si>
+    <t>69b97290d96b4f4a2437d4f9</t>
+  </si>
+  <si>
+    <t>69b98523d96b4f4a2437d74c</t>
+  </si>
+  <si>
+    <t>69b9b429d96b4f4a2437da5b</t>
+  </si>
+  <si>
+    <t>69b9b429d96b4f4a2437da5d</t>
+  </si>
+  <si>
+    <t>69b9c594d96b4f4a2437daca</t>
+  </si>
+  <si>
+    <t>69ba5366d96b4f4a2437dbee</t>
+  </si>
+  <si>
+    <t>69ba77bbd96b4f4a2437e12b</t>
+  </si>
+  <si>
+    <t>FIZZ-1000826603</t>
+  </si>
+  <si>
+    <t>1449-135794</t>
+  </si>
+  <si>
+    <t>FIZZ-1000838075</t>
+  </si>
+  <si>
+    <t>FIZZ-1000838632</t>
+  </si>
+  <si>
+    <t>FIZZ-1000838792</t>
+  </si>
+  <si>
+    <t>FIZZ-1000839110</t>
+  </si>
+  <si>
+    <t>FIZZ-1000839256</t>
+  </si>
+  <si>
+    <t>26MPE0002981/1</t>
+  </si>
+  <si>
+    <t>303277688/1</t>
+  </si>
+  <si>
+    <t>303753487/1</t>
+  </si>
+  <si>
+    <t>303753487/2</t>
+  </si>
+  <si>
+    <t>303753487/3</t>
+  </si>
+  <si>
+    <t>303838421/1</t>
+  </si>
+  <si>
+    <t>303838421/2</t>
+  </si>
+  <si>
+    <t>304104709/1</t>
+  </si>
+  <si>
+    <t>304149239/1</t>
+  </si>
+  <si>
+    <t>304149445/1</t>
+  </si>
+  <si>
+    <t>304248355/1</t>
+  </si>
+  <si>
+    <t>304248670/1</t>
+  </si>
+  <si>
+    <t>304309284/1</t>
+  </si>
+  <si>
+    <t>304309284/2</t>
+  </si>
+  <si>
+    <t>304309359/1</t>
+  </si>
+  <si>
+    <t>304309626/2/1</t>
+  </si>
+  <si>
+    <t>304362446/1</t>
+  </si>
+  <si>
+    <t>304362446/2</t>
+  </si>
+  <si>
+    <t>304362446/3</t>
+  </si>
+  <si>
+    <t>304362553/1</t>
+  </si>
+  <si>
+    <t>304362553/2</t>
+  </si>
+  <si>
+    <t>304362553/3</t>
+  </si>
+  <si>
+    <t>304362648/1</t>
+  </si>
+  <si>
+    <t>304362715/1</t>
+  </si>
+  <si>
+    <t>304429908/1</t>
+  </si>
+  <si>
+    <t>304430114/1</t>
+  </si>
+  <si>
+    <t>304430270/1</t>
+  </si>
+  <si>
+    <t>304430270/2</t>
+  </si>
+  <si>
+    <t>304487425/1</t>
+  </si>
+  <si>
+    <t>304487643/1</t>
+  </si>
+  <si>
+    <t>304487829/1</t>
+  </si>
+  <si>
+    <t>304487980/1</t>
+  </si>
+  <si>
+    <t>304487980/2</t>
+  </si>
+  <si>
+    <t>304543914/1</t>
+  </si>
+  <si>
+    <t>304544031/1</t>
+  </si>
+  <si>
+    <t>304544210/1</t>
+  </si>
+  <si>
+    <t>304544278/1</t>
+  </si>
+  <si>
+    <t>304544293/1</t>
+  </si>
+  <si>
+    <t>304544578/1</t>
+  </si>
+  <si>
+    <t>304576505/1</t>
+  </si>
+  <si>
+    <t>304577027/1</t>
+  </si>
+  <si>
+    <t>304577027/2</t>
+  </si>
+  <si>
+    <t>304577027/3</t>
+  </si>
+  <si>
+    <t>304577084/1</t>
+  </si>
+  <si>
+    <t>304577105/1</t>
+  </si>
+  <si>
+    <t>304577256/1</t>
+  </si>
+  <si>
+    <t>304577393/1</t>
+  </si>
+  <si>
+    <t>304618651/1</t>
+  </si>
+  <si>
+    <t>304618854/1</t>
+  </si>
+  <si>
+    <t>304618872/1</t>
+  </si>
+  <si>
+    <t>304619007/1</t>
+  </si>
+  <si>
+    <t>304619126/1</t>
+  </si>
+  <si>
+    <t>304619200/1</t>
+  </si>
+  <si>
+    <t>304619203/1</t>
+  </si>
+  <si>
+    <t>304619224/1</t>
+  </si>
+  <si>
+    <t>304619291/1</t>
+  </si>
+  <si>
+    <t>304619390/1</t>
+  </si>
+  <si>
+    <t>304619429/1</t>
+  </si>
+  <si>
+    <t>304619536/1</t>
+  </si>
+  <si>
+    <t>304619625/1</t>
+  </si>
+  <si>
+    <t>304675694/1</t>
+  </si>
+  <si>
+    <t>304675801/1</t>
+  </si>
+  <si>
+    <t>304675844/1</t>
+  </si>
+  <si>
+    <t>304675872/1</t>
+  </si>
+  <si>
+    <t>304675954/1</t>
+  </si>
+  <si>
+    <t>304675981/1</t>
+  </si>
+  <si>
+    <t>304675981/2</t>
+  </si>
+  <si>
+    <t>304675981/3</t>
+  </si>
+  <si>
+    <t>304675997/1</t>
+  </si>
+  <si>
+    <t>304676140/1</t>
+  </si>
+  <si>
+    <t>304676159/1</t>
+  </si>
+  <si>
+    <t>304676205/1</t>
+  </si>
+  <si>
+    <t>304676304/1</t>
+  </si>
+  <si>
+    <t>304676401/1</t>
+  </si>
+  <si>
+    <t>304676417/1</t>
+  </si>
+  <si>
+    <t>304676454/1</t>
+  </si>
+  <si>
+    <t>304726779/1</t>
+  </si>
+  <si>
+    <t>304726908/1</t>
+  </si>
+  <si>
+    <t>304726908/2</t>
+  </si>
+  <si>
+    <t>304726908/3</t>
+  </si>
+  <si>
+    <t>304726958/1</t>
+  </si>
+  <si>
+    <t>304727007/1</t>
+  </si>
+  <si>
+    <t>304727116/1</t>
+  </si>
+  <si>
+    <t>304727116/2</t>
+  </si>
+  <si>
+    <t>159995579538324383</t>
+  </si>
+  <si>
+    <t>159995579538311185</t>
+  </si>
+  <si>
+    <t>202603162600618501</t>
+  </si>
+  <si>
+    <t>202603162600619301</t>
+  </si>
+  <si>
+    <t>202603162600615501</t>
+  </si>
+  <si>
+    <t>202603172600638801</t>
+  </si>
+  <si>
+    <t>202603172600637101</t>
+  </si>
+  <si>
+    <t>202603182600646401</t>
+  </si>
+  <si>
+    <t>202603182600650901</t>
+  </si>
+  <si>
+    <t>202603182600651901</t>
+  </si>
+  <si>
+    <t>202603182600651902</t>
+  </si>
+  <si>
+    <t>202603182600651903</t>
+  </si>
+  <si>
+    <t>202603182600646201</t>
+  </si>
+  <si>
+    <t>202603182600654401</t>
+  </si>
+  <si>
+    <t>202603182600654402</t>
+  </si>
+  <si>
+    <t>202603182600646301</t>
+  </si>
+  <si>
+    <t>202603182600648301</t>
+  </si>
+  <si>
+    <t>202603182600649801</t>
+  </si>
+  <si>
+    <t>202603182600653001</t>
+  </si>
+  <si>
+    <t>202603172600635901</t>
+  </si>
+  <si>
+    <t>202603182600649301</t>
+  </si>
+  <si>
+    <t>202603182600649302</t>
+  </si>
+  <si>
+    <t>202603182600650001</t>
+  </si>
+  <si>
+    <t>202603182600653801</t>
+  </si>
+  <si>
+    <t>202603182600648901</t>
   </si>
 </sst>
 </file>
@@ -399,10 +1056,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -684,10 +1340,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D171"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="1"/>
@@ -705,867 +1361,1873 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
+      <c r="A2" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B11" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="B12" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="B13" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B14" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B15" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="B17" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="B18" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="B19" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>21</v>
+      <c r="B20" s="1" t="s">
+        <v>182</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="B25" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="B26" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="B27" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="B28" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="B29" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="B30" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="B31" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="B32" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="B33" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="B35" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>37</v>
+      <c r="B36" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="B45" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="B46" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="B47" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="B48" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+      <c r="B50" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+      <c r="B51" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+      <c r="B52" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+      <c r="B61" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>63</v>
+      <c r="B62" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>64</v>
+      <c r="A63" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>65</v>
+      <c r="A64" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>66</v>
+      <c r="A65" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>67</v>
+      <c r="A66" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>228</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>68</v>
+      <c r="A67" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>229</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>69</v>
+      <c r="A68" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>70</v>
+      <c r="A69" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>71</v>
+      <c r="A70" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>72</v>
+      <c r="A71" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>233</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>73</v>
+      <c r="A72" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>74</v>
+      <c r="A73" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>75</v>
+      <c r="A74" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>76</v>
+      <c r="A75" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>77</v>
+      <c r="A76" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>78</v>
+      <c r="A77" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>79</v>
+      <c r="A78" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>80</v>
+      <c r="A79" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>81</v>
+      <c r="A80" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>82</v>
+      <c r="A81" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>83</v>
+      <c r="A82" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>84</v>
+      <c r="A83" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>85</v>
+      <c r="A84" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>86</v>
+      <c r="A85" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>247</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>87</v>
+      <c r="A86" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>88</v>
+      <c r="A87" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>89</v>
+      <c r="A88" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
-        <v>90</v>
+      <c r="A89" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>251</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>91</v>
+      <c r="A90" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>252</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>92</v>
+      <c r="A91" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>253</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>93</v>
+      <c r="A92" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>254</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>94</v>
+      <c r="A93" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>255</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
-        <v>95</v>
+      <c r="A94" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>256</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>96</v>
+      <c r="A95" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>97</v>
+      <c r="A96" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
-        <v>98</v>
+      <c r="A97" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>259</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>99</v>
+      <c r="A98" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>100</v>
+      <c r="A99" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>261</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>101</v>
+      <c r="A100" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>262</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>102</v>
+      <c r="A101" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>263</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
-        <v>103</v>
+      <c r="A102" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>264</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
+      <c r="A103" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="B134" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C168" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>111</v>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01305C8-962A-4DAC-BCDC-51A971C9AFC5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF99B874-DE06-47BD-B0D3-D47983F3D13F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="263">
   <si>
     <t>UTK</t>
   </si>
@@ -123,9 +123,6 @@
     <t>260318-W00004941</t>
   </si>
   <si>
-    <t>260319-F00003819</t>
-  </si>
-  <si>
     <t>260319-F00006609</t>
   </si>
   <si>
@@ -237,9 +234,6 @@
     <t>304781438</t>
   </si>
   <si>
-    <t>304781499</t>
-  </si>
-  <si>
     <t>304781512</t>
   </si>
   <si>
@@ -288,7 +282,541 @@
     <t>99002227</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>SZ-829</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-827</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-840</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>267004130</t>
+  </si>
+  <si>
+    <t>267004210</t>
+  </si>
+  <si>
+    <t>267004220</t>
+  </si>
+  <si>
+    <t>26MPE0003125</t>
+  </si>
+  <si>
+    <t>26MPE0003128</t>
+  </si>
+  <si>
+    <t>26MPE0003161</t>
+  </si>
+  <si>
+    <t>26MPE0003165</t>
+  </si>
+  <si>
+    <t>ID5000_XD</t>
+  </si>
+  <si>
+    <t>NFD6-03-16-L63L</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-SUKB</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-UG8E</t>
+  </si>
+  <si>
+    <t>NFD6-03-18-DU35</t>
+  </si>
+  <si>
+    <t>NFD6-03-18-E855</t>
+  </si>
+  <si>
+    <t>NFD6-03-18-FFJJ</t>
+  </si>
+  <si>
+    <t>NFD6-03-18-QMWG</t>
+  </si>
+  <si>
+    <t>NFD6-03-18-T4HR</t>
+  </si>
+  <si>
+    <t>NFD6-03-18-TXYW</t>
+  </si>
+  <si>
+    <t>NFD6-03-18-XBS4</t>
+  </si>
+  <si>
+    <t>NFE6-03-17-L6SP</t>
+  </si>
+  <si>
+    <t>NFE6-03-17-SGZC</t>
+  </si>
+  <si>
+    <t>NFE6-03-18-363D</t>
+  </si>
+  <si>
+    <t>NFE6-03-18-GMFS</t>
+  </si>
+  <si>
+    <t>NFE6-03-18-MZG7</t>
+  </si>
+  <si>
+    <t>NFE6-03-18-PNFM</t>
+  </si>
+  <si>
+    <t>NFE6-03-18-TYWG</t>
+  </si>
+  <si>
+    <t>R412947</t>
+  </si>
+  <si>
+    <t>R413591</t>
+  </si>
+  <si>
+    <t>SA26/H001140</t>
+  </si>
+  <si>
+    <t>248744055/1</t>
+  </si>
+  <si>
+    <t>248744071/1</t>
+  </si>
+  <si>
+    <t>69ad4b0a51e7020fc80c82b8</t>
+  </si>
+  <si>
+    <t>69b96ed7d96b4f4a2437d49a</t>
+  </si>
+  <si>
+    <t>69b1469551e7020fc80ccffc</t>
+  </si>
+  <si>
+    <t>69b1469551e7020fc80ccffe</t>
+  </si>
+  <si>
+    <t>69baabf1d96b4f4a2437e8d6</t>
+  </si>
+  <si>
+    <t>69b363fc6967eb2a8b5ccda7</t>
+  </si>
+  <si>
+    <t>69ba72bfd96b4f4a2437e027</t>
+  </si>
+  <si>
+    <t>69b5679d6967eb2a8b5ce912</t>
+  </si>
+  <si>
+    <t>69ba5b78d96b4f4a2437dc8e</t>
+  </si>
+  <si>
+    <t>69b84086d96b4f4a2437c104</t>
+  </si>
+  <si>
+    <t>69b84086d96b4f4a2437c106</t>
+  </si>
+  <si>
+    <t>69b94bb9d96b4f4a2437cf21</t>
+  </si>
+  <si>
+    <t>69b9506ad96b4f4a2437cfb2</t>
+  </si>
+  <si>
+    <t>69b952bfd96b4f4a2437d00f</t>
+  </si>
+  <si>
+    <t>69b9551cd96b4f4a2437d08c</t>
+  </si>
+  <si>
+    <t>69baa180d96b4f4a2437e73c</t>
+  </si>
+  <si>
+    <t>69b99621d96b4f4a2437d8f6</t>
+  </si>
+  <si>
+    <t>69b97f48d96b4f4a2437d690</t>
+  </si>
+  <si>
+    <t>69b98780d96b4f4a2437d78f</t>
+  </si>
+  <si>
+    <t>69b97bc0d96b4f4a2437d645</t>
+  </si>
+  <si>
+    <t>69b96907d96b4f4a2437d3d3</t>
+  </si>
+  <si>
+    <t>69b97843d96b4f4a2437d5e4</t>
+  </si>
+  <si>
+    <t>69b981a6d96b4f4a2437d6f8</t>
+  </si>
+  <si>
+    <t>69b9a5f3d96b4f4a2437d9c2</t>
+  </si>
+  <si>
+    <t>69ba56ecd96b4f4a2437dc4d</t>
+  </si>
+  <si>
+    <t>69ba93dbd96b4f4a2437e568</t>
+  </si>
+  <si>
+    <t>69ba93dbd96b4f4a2437e570</t>
+  </si>
+  <si>
+    <t>69ba9758d96b4f4a2437e5f9</t>
+  </si>
+  <si>
+    <t>69bbe7a7d96b4f4a2437fc14</t>
+  </si>
+  <si>
+    <t>69bbe7a7d96b4f4a2437fc15</t>
+  </si>
+  <si>
+    <t>1449-135794</t>
+  </si>
+  <si>
+    <t>1449-281924</t>
+  </si>
+  <si>
+    <t>1449-699576</t>
+  </si>
+  <si>
+    <t>26MPE0003125/1</t>
+  </si>
+  <si>
+    <t>26MPE0003128/1</t>
+  </si>
+  <si>
+    <t>26MPE0003161/1</t>
+  </si>
+  <si>
+    <t>26MPE0003165/1</t>
+  </si>
+  <si>
+    <t>303480735/1</t>
+  </si>
+  <si>
+    <t>303480735/2</t>
+  </si>
+  <si>
+    <t>303710055/1</t>
+  </si>
+  <si>
+    <t>303752769/1</t>
+  </si>
+  <si>
+    <t>303931099/1</t>
+  </si>
+  <si>
+    <t>303972240/1</t>
+  </si>
+  <si>
+    <t>304149354/1</t>
+  </si>
+  <si>
+    <t>304149354/2</t>
+  </si>
+  <si>
+    <t>304149354/3</t>
+  </si>
+  <si>
+    <t>304308918/1</t>
+  </si>
+  <si>
+    <t>304362876/1</t>
+  </si>
+  <si>
+    <t>304362876/2</t>
+  </si>
+  <si>
+    <t>304362876/3</t>
+  </si>
+  <si>
+    <t>304429948/1</t>
+  </si>
+  <si>
+    <t>304429948/2</t>
+  </si>
+  <si>
+    <t>304429948/3</t>
+  </si>
+  <si>
+    <t>304430285/1</t>
+  </si>
+  <si>
+    <t>304430285/2</t>
+  </si>
+  <si>
+    <t>304487474/1</t>
+  </si>
+  <si>
+    <t>304487474/2</t>
+  </si>
+  <si>
+    <t>304487512/1</t>
+  </si>
+  <si>
+    <t>304487512/2</t>
+  </si>
+  <si>
+    <t>304544238/1</t>
+  </si>
+  <si>
+    <t>304619089/1</t>
+  </si>
+  <si>
+    <t>304619199/1</t>
+  </si>
+  <si>
+    <t>304619199/2</t>
+  </si>
+  <si>
+    <t>304619330/1</t>
+  </si>
+  <si>
+    <t>304619579/1</t>
+  </si>
+  <si>
+    <t>304675726/1</t>
+  </si>
+  <si>
+    <t>304675975/1</t>
+  </si>
+  <si>
+    <t>304676040/1</t>
+  </si>
+  <si>
+    <t>304676413/1</t>
+  </si>
+  <si>
+    <t>304726416/1</t>
+  </si>
+  <si>
+    <t>304726416/2</t>
+  </si>
+  <si>
+    <t>304726439/1</t>
+  </si>
+  <si>
+    <t>304726439/2</t>
+  </si>
+  <si>
+    <t>304726439/3</t>
+  </si>
+  <si>
+    <t>304726549/1</t>
+  </si>
+  <si>
+    <t>304727062/1</t>
+  </si>
+  <si>
+    <t>304727327/1</t>
+  </si>
+  <si>
+    <t>304780889/1</t>
+  </si>
+  <si>
+    <t>304780889/2</t>
+  </si>
+  <si>
+    <t>304780948/1</t>
+  </si>
+  <si>
+    <t>304781082/1</t>
+  </si>
+  <si>
+    <t>304781111/1</t>
+  </si>
+  <si>
+    <t>304781148/1</t>
+  </si>
+  <si>
+    <t>304781171/1</t>
+  </si>
+  <si>
+    <t>304781207/1</t>
+  </si>
+  <si>
+    <t>304781238/1</t>
+  </si>
+  <si>
+    <t>304781377/1</t>
+  </si>
+  <si>
+    <t>304781438/1</t>
+  </si>
+  <si>
+    <t>304781512/1</t>
+  </si>
+  <si>
+    <t>304781519/1</t>
+  </si>
+  <si>
+    <t>304781768/1</t>
+  </si>
+  <si>
+    <t>304781831/1</t>
+  </si>
+  <si>
+    <t>304826321/1</t>
+  </si>
+  <si>
+    <t>304826438/1</t>
+  </si>
+  <si>
+    <t>304826487/1</t>
+  </si>
+  <si>
+    <t>304826487/2</t>
+  </si>
+  <si>
+    <t>304826512/1</t>
+  </si>
+  <si>
+    <t>304826512/2</t>
+  </si>
+  <si>
+    <t>304826587/1</t>
+  </si>
+  <si>
+    <t>304826614/1</t>
+  </si>
+  <si>
+    <t>304826781/1</t>
+  </si>
+  <si>
+    <t>304826781/2</t>
+  </si>
+  <si>
+    <t>304826893/1</t>
+  </si>
+  <si>
+    <t>304827032/1</t>
+  </si>
+  <si>
+    <t>304874868/1</t>
+  </si>
+  <si>
+    <t>304925279/1</t>
+  </si>
+  <si>
+    <t>99002227/1</t>
+  </si>
+  <si>
+    <t>159995579538379048</t>
+  </si>
+  <si>
+    <t>202603172600639201</t>
+  </si>
+  <si>
+    <t>202603182600652601</t>
+  </si>
+  <si>
+    <t>202603182600652701</t>
+  </si>
+  <si>
+    <t>202603192600656301</t>
+  </si>
+  <si>
+    <t>202603192600661701</t>
+  </si>
+  <si>
+    <t>202603192600663401</t>
+  </si>
+  <si>
+    <t>202603192600663301</t>
+  </si>
+  <si>
+    <t>202603192600659001</t>
+  </si>
+  <si>
+    <t>202603192600659301</t>
+  </si>
+  <si>
+    <t>202603192600663201</t>
+  </si>
+  <si>
+    <t>202603182600645001</t>
+  </si>
+  <si>
+    <t>202603182600649401</t>
+  </si>
+  <si>
+    <t>202603182600649402</t>
+  </si>
+  <si>
+    <t>202603192600656101</t>
+  </si>
+  <si>
+    <t>202603192600664701</t>
+  </si>
+  <si>
+    <t>202603192600664201</t>
+  </si>
+  <si>
+    <t>202603192600664202</t>
+  </si>
+  <si>
+    <t>202603192600661101</t>
+  </si>
+  <si>
+    <t>202603192600656501</t>
+  </si>
+  <si>
+    <t>159995579538332449</t>
+  </si>
+  <si>
+    <t>159995579538332470</t>
+  </si>
+  <si>
+    <t>159995579538218521</t>
   </si>
 </sst>
 </file>
@@ -324,10 +852,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -609,16 +1136,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -629,668 +1156,1550 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="D4"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="B5" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B6" s="1" t="s">
+        <v>135</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>9</v>
+      <c r="B8" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="D8"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B15" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="B16" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="B17" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="B18" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="B19" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="B20" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="B21" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="B22" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="B23" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="B24" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="B25" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D25"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="B26" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="B27" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>29</v>
+      <c r="B28" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="D28"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D30"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="B31" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>33</v>
+      <c r="B32" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>34</v>
+        <v>85</v>
+      </c>
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>162</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>35</v>
+        <v>85</v>
+      </c>
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>36</v>
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>37</v>
+        <v>97</v>
+      </c>
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>38</v>
+        <v>88</v>
+      </c>
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>39</v>
+        <v>90</v>
+      </c>
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D40"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D41"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D42"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D43"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D44"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D45"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D46"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D48"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D49"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D50"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D51"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D52"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D53"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="B54" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D54"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D55"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D56"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="B57" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D57"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D58"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>60</v>
+      <c r="B59" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>61</v>
+      <c r="D59"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>62</v>
+      <c r="D60"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>63</v>
+        <v>100</v>
+      </c>
+      <c r="D61"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>191</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>64</v>
+        <v>100</v>
+      </c>
+      <c r="D62"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
+      </c>
+      <c r="D63"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>66</v>
+        <v>100</v>
+      </c>
+      <c r="D64"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>67</v>
+        <v>92</v>
+      </c>
+      <c r="D65"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>68</v>
+        <v>92</v>
+      </c>
+      <c r="D66"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>69</v>
+        <v>90</v>
+      </c>
+      <c r="D67"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>197</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>70</v>
+        <v>93</v>
+      </c>
+      <c r="D68"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>71</v>
+        <v>93</v>
+      </c>
+      <c r="D69"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>72</v>
+        <v>91</v>
+      </c>
+      <c r="D70"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>73</v>
+        <v>92</v>
+      </c>
+      <c r="D71"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>74</v>
+        <v>99</v>
+      </c>
+      <c r="D72"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
+      </c>
+      <c r="D73"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
+      </c>
+      <c r="D74"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>77</v>
+        <v>96</v>
+      </c>
+      <c r="D75"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
+      </c>
+      <c r="D76"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>79</v>
+        <v>96</v>
+      </c>
+      <c r="D77"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
+      </c>
+      <c r="D78"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
+      </c>
+      <c r="D79"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>209</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
+      </c>
+      <c r="D80"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
+      </c>
+      <c r="D81"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>211</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
+      </c>
+      <c r="D82"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>212</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
+      <c r="D83"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="D84"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>86</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>267004008</v>
+      </c>
+      <c r="B134" s="1">
+        <v>267004008</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991D175F-F12C-4FD2-8C10-758CB4A1BEA5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE702865-C9E0-4D1F-9615-753048269561}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="327">
   <si>
     <t>304013244</t>
   </si>
@@ -336,7 +336,679 @@
     <t>99002261</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>UTK</t>
+  </si>
+  <si>
+    <t>SZ-827</t>
+  </si>
+  <si>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>SZ-840</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-829</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZALLITOLEVELSZAM</t>
+  </si>
+  <si>
+    <t>267004357</t>
+  </si>
+  <si>
+    <t>NFD6-03-11-VHBG</t>
+  </si>
+  <si>
+    <t>NFD6-03-14-8H4W/CSXD</t>
+  </si>
+  <si>
+    <t>NFD6-03-14-B3WN/XD</t>
+  </si>
+  <si>
+    <t>NFD6-03-18-2D67</t>
+  </si>
+  <si>
+    <t>NFD6-03-19-AFQA</t>
+  </si>
+  <si>
+    <t>NFD6-03-19-PHF7</t>
+  </si>
+  <si>
+    <t>NFD6-03-20-C6JG</t>
+  </si>
+  <si>
+    <t>NFD6-03-20-XTR7</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-4FX2</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-8HG2</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-HN5S</t>
+  </si>
+  <si>
+    <t>NFD6-03-22-HYML</t>
+  </si>
+  <si>
+    <t>NFD6-03-23-6X2B</t>
+  </si>
+  <si>
+    <t>NFD6-03-23-MRJQ</t>
+  </si>
+  <si>
+    <t>NFD6-03-24-AQ3L</t>
+  </si>
+  <si>
+    <t>NFD6-03-24-DL5D</t>
+  </si>
+  <si>
+    <t>NFD6-03-24-F9FQ</t>
+  </si>
+  <si>
+    <t>NFD6-03-24-KAC2</t>
+  </si>
+  <si>
+    <t>NFD6-03-24-UQH8</t>
+  </si>
+  <si>
+    <t>NFE6-03-20-4R5P</t>
+  </si>
+  <si>
+    <t>NFE6-03-21-D5ZS</t>
+  </si>
+  <si>
+    <t>NFE6-03-22-CQ2S</t>
+  </si>
+  <si>
+    <t>NFE6-03-22-PZZA</t>
+  </si>
+  <si>
+    <t>NFE6-03-23-9TB8</t>
+  </si>
+  <si>
+    <t>NFE6-03-24-84YE</t>
+  </si>
+  <si>
+    <t>NFE6-03-24-JUVR</t>
+  </si>
+  <si>
+    <t>NFE6-03-24-QXCS</t>
+  </si>
+  <si>
+    <t>NFE6-03-24-RQLN</t>
+  </si>
+  <si>
+    <t>VA26/001323</t>
+  </si>
+  <si>
+    <t>vsi-2026/03919</t>
+  </si>
+  <si>
+    <t>vsi-2026/03954</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-7Y85</t>
+  </si>
+  <si>
+    <t>NFD6-03-22-MCTT</t>
+  </si>
+  <si>
+    <t>CSOMAGSZAM</t>
+  </si>
+  <si>
+    <t>69b580396967eb2a8b5cea90</t>
+  </si>
+  <si>
+    <t>69b5a6e26967eb2a8b5cec41</t>
+  </si>
+  <si>
+    <t>69bad57cd96b4f4a2437ee37</t>
+  </si>
+  <si>
+    <t>69bea567d96b4f4a2438242c</t>
+  </si>
+  <si>
+    <t>69c39f76d96b4f4a24386478</t>
+  </si>
+  <si>
+    <t>69c3ce70d96b4f4a24386bab</t>
+  </si>
+  <si>
+    <t>69bd8c65d96b4f4a24381a4c</t>
+  </si>
+  <si>
+    <t>69c3a917d96b4f4a243865fa</t>
+  </si>
+  <si>
+    <t>69becea7d96b4f4a2438269f</t>
+  </si>
+  <si>
+    <t>69beadd2d96b4f4a243824b7</t>
+  </si>
+  <si>
+    <t>69beadd2d96b4f4a243824b9</t>
+  </si>
+  <si>
+    <t>69c27be7d96b4f4a2438557e</t>
+  </si>
+  <si>
+    <t>69c164b7d96b4f4a24384720</t>
+  </si>
+  <si>
+    <t>69bfcd22d96b4f4a24382b96</t>
+  </si>
+  <si>
+    <t>69c39779d96b4f4a2438637d</t>
+  </si>
+  <si>
+    <t>69bf94b4d96b4f4a24382904</t>
+  </si>
+  <si>
+    <t>69bf94b4d96b4f4a24382905</t>
+  </si>
+  <si>
+    <t>69bfd072d96b4f4a24382bc4</t>
+  </si>
+  <si>
+    <t>69c2695dd96b4f4a24385337</t>
+  </si>
+  <si>
+    <t>69c0434bd96b4f4a24383167</t>
+  </si>
+  <si>
+    <t>69c103d7d96b4f4a24383617</t>
+  </si>
+  <si>
+    <t>69c13836d96b4f4a24383f69</t>
+  </si>
+  <si>
+    <t>69c3a6cdd96b4f4a24386592</t>
+  </si>
+  <si>
+    <t>69c15db9d96b4f4a24384624</t>
+  </si>
+  <si>
+    <t>69c105d9d96b4f4a2438366c</t>
+  </si>
+  <si>
+    <t>69c105d9d96b4f4a2438366e</t>
+  </si>
+  <si>
+    <t>69c134b7d96b4f4a24383ee1</t>
+  </si>
+  <si>
+    <t>69c134b7d96b4f4a24383ee2</t>
+  </si>
+  <si>
+    <t>69c14e82d96b4f4a24384368</t>
+  </si>
+  <si>
+    <t>69c15204d96b4f4a24384419</t>
+  </si>
+  <si>
+    <t>69c1696ed96b4f4a243847ab</t>
+  </si>
+  <si>
+    <t>69c1696ed96b4f4a243847ac</t>
+  </si>
+  <si>
+    <t>69c1c857d96b4f4a24384c0c</t>
+  </si>
+  <si>
+    <t>69c268f2d96b4f4a2438531f</t>
+  </si>
+  <si>
+    <t>69c2771ad96b4f4a24385516</t>
+  </si>
+  <si>
+    <t>69c2931fd96b4f4a243858d5</t>
+  </si>
+  <si>
+    <t>69c29939d96b4f4a243859de</t>
+  </si>
+  <si>
+    <t>69c29939d96b4f4a243859e0</t>
+  </si>
+  <si>
+    <t>69c2cc85d96b4f4a24385f82</t>
+  </si>
+  <si>
+    <t>69c27cdbd96b4f4a2438558d</t>
+  </si>
+  <si>
+    <t>69c290bdd96b4f4a2438584d</t>
+  </si>
+  <si>
+    <t>69c290bdd96b4f4a2438584e</t>
+  </si>
+  <si>
+    <t>69c2bfa1d96b4f4a24385e80</t>
+  </si>
+  <si>
+    <t>69c2c450d96b4f4a24385ee7</t>
+  </si>
+  <si>
+    <t>69c312d7d96b4f4a243861f2</t>
+  </si>
+  <si>
+    <t>69c3a7dfd96b4f4a243865be</t>
+  </si>
+  <si>
+    <t>69c3b815d96b4f4a24386878</t>
+  </si>
+  <si>
+    <t>69c3c748d96b4f4a24386ac5</t>
+  </si>
+  <si>
+    <t>69c3c748d96b4f4a24386ac6</t>
+  </si>
+  <si>
+    <t>69c3bcc9d96b4f4a24386935</t>
+  </si>
+  <si>
+    <t>69c3bcc9d96b4f4a24386936</t>
+  </si>
+  <si>
+    <t>FIZZ-1000840042</t>
+  </si>
+  <si>
+    <t>300160042/1</t>
+  </si>
+  <si>
+    <t>304013244/1</t>
+  </si>
+  <si>
+    <t>304487516/1</t>
+  </si>
+  <si>
+    <t>304727197/1</t>
+  </si>
+  <si>
+    <t>304781271/1</t>
+  </si>
+  <si>
+    <t>304826527/1</t>
+  </si>
+  <si>
+    <t>304826527/2</t>
+  </si>
+  <si>
+    <t>304875107/1</t>
+  </si>
+  <si>
+    <t>304875165/1</t>
+  </si>
+  <si>
+    <t>305007060/1</t>
+  </si>
+  <si>
+    <t>305007060/2</t>
+  </si>
+  <si>
+    <t>305007060/3</t>
+  </si>
+  <si>
+    <t>305007364/1</t>
+  </si>
+  <si>
+    <t>305007364/2</t>
+  </si>
+  <si>
+    <t>305007364/3</t>
+  </si>
+  <si>
+    <t>305007380/1</t>
+  </si>
+  <si>
+    <t>305007671/1</t>
+  </si>
+  <si>
+    <t>305007702/1</t>
+  </si>
+  <si>
+    <t>305113625/1</t>
+  </si>
+  <si>
+    <t>305113775/1</t>
+  </si>
+  <si>
+    <t>305170101/1</t>
+  </si>
+  <si>
+    <t>305170126/1</t>
+  </si>
+  <si>
+    <t>305170285/1</t>
+  </si>
+  <si>
+    <t>305170285/2</t>
+  </si>
+  <si>
+    <t>305225869/1</t>
+  </si>
+  <si>
+    <t>305225881/1</t>
+  </si>
+  <si>
+    <t>305226110/1</t>
+  </si>
+  <si>
+    <t>305226138/1</t>
+  </si>
+  <si>
+    <t>305272645/1</t>
+  </si>
+  <si>
+    <t>305315280/1</t>
+  </si>
+  <si>
+    <t>305315280/2</t>
+  </si>
+  <si>
+    <t>305315496/1</t>
+  </si>
+  <si>
+    <t>305315598/1</t>
+  </si>
+  <si>
+    <t>305315690/1</t>
+  </si>
+  <si>
+    <t>305316154/1</t>
+  </si>
+  <si>
+    <t>305367871/1</t>
+  </si>
+  <si>
+    <t>305367871/2</t>
+  </si>
+  <si>
+    <t>305368015/1</t>
+  </si>
+  <si>
+    <t>305368059/1</t>
+  </si>
+  <si>
+    <t>305368127/1</t>
+  </si>
+  <si>
+    <t>305368169/1</t>
+  </si>
+  <si>
+    <t>305368412/1</t>
+  </si>
+  <si>
+    <t>305368556/1</t>
+  </si>
+  <si>
+    <t>305368607/1</t>
+  </si>
+  <si>
+    <t>305411587/1</t>
+  </si>
+  <si>
+    <t>305412004/1</t>
+  </si>
+  <si>
+    <t>305412281/1</t>
+  </si>
+  <si>
+    <t>305412301/1</t>
+  </si>
+  <si>
+    <t>305412301/2</t>
+  </si>
+  <si>
+    <t>305412349/1</t>
+  </si>
+  <si>
+    <t>305461579/1</t>
+  </si>
+  <si>
+    <t>305461614/1</t>
+  </si>
+  <si>
+    <t>305461692/1</t>
+  </si>
+  <si>
+    <t>305461718/1</t>
+  </si>
+  <si>
+    <t>305461748/1</t>
+  </si>
+  <si>
+    <t>305461903/1</t>
+  </si>
+  <si>
+    <t>305462032/1</t>
+  </si>
+  <si>
+    <t>305462274/1</t>
+  </si>
+  <si>
+    <t>305462349/1</t>
+  </si>
+  <si>
+    <t>305514209/1</t>
+  </si>
+  <si>
+    <t>305514281/1</t>
+  </si>
+  <si>
+    <t>305514387/1</t>
+  </si>
+  <si>
+    <t>305514420/1</t>
+  </si>
+  <si>
+    <t>305514685/1</t>
+  </si>
+  <si>
+    <t>305514728/1</t>
+  </si>
+  <si>
+    <t>305514841/1</t>
+  </si>
+  <si>
+    <t>305514841/2</t>
+  </si>
+  <si>
+    <t>305514841/3</t>
+  </si>
+  <si>
+    <t>305514873/1</t>
+  </si>
+  <si>
+    <t>99002253/1</t>
+  </si>
+  <si>
+    <t>99002261/1</t>
+  </si>
+  <si>
+    <t>202603162600591601</t>
+  </si>
+  <si>
+    <t>159995579538520518</t>
+  </si>
+  <si>
+    <t>202603252600662901</t>
+  </si>
+  <si>
+    <t>202603252600669701</t>
+  </si>
+  <si>
+    <t>202603202600672501</t>
+  </si>
+  <si>
+    <t>202603232600680301</t>
+  </si>
+  <si>
+    <t>202603232600676901</t>
+  </si>
+  <si>
+    <t>202603232600687301</t>
+  </si>
+  <si>
+    <t>202603232600687302</t>
+  </si>
+  <si>
+    <t>202603232600691901</t>
+  </si>
+  <si>
+    <t>202603232600686801</t>
+  </si>
+  <si>
+    <t>NFD6-03-22-HYML-1</t>
+  </si>
+  <si>
+    <t>202603242600711101</t>
+  </si>
+  <si>
+    <t>202603242600711102</t>
+  </si>
+  <si>
+    <t>202603242600707501</t>
+  </si>
+  <si>
+    <t>202603252600720801</t>
+  </si>
+  <si>
+    <t>202603252600720901</t>
+  </si>
+  <si>
+    <t>202603252600718601</t>
+  </si>
+  <si>
+    <t>202603252600718602</t>
+  </si>
+  <si>
+    <t>202603252600722701</t>
+  </si>
+  <si>
+    <t>202603252600719801</t>
+  </si>
+  <si>
+    <t>202603232600682501</t>
+  </si>
+  <si>
+    <t>202603232600685901</t>
+  </si>
+  <si>
+    <t>202603232600685902</t>
+  </si>
+  <si>
+    <t>202603232600685903</t>
+  </si>
+  <si>
+    <t>202603232600685904</t>
+  </si>
+  <si>
+    <t>202603232600702001</t>
+  </si>
+  <si>
+    <t>202603232600700201</t>
+  </si>
+  <si>
+    <t>202603232600700202</t>
+  </si>
+  <si>
+    <t>202603232600700203</t>
+  </si>
+  <si>
+    <t>202603232600700204</t>
+  </si>
+  <si>
+    <t>202603242600705301</t>
+  </si>
+  <si>
+    <t>202603242600705302</t>
+  </si>
+  <si>
+    <t>202603252600718001</t>
+  </si>
+  <si>
+    <t>202603252600720001</t>
+  </si>
+  <si>
+    <t>202603252600720002</t>
+  </si>
+  <si>
+    <t>202603252600715901</t>
+  </si>
+  <si>
+    <t>202603252600715902</t>
+  </si>
+  <si>
+    <t>202603252600716101</t>
+  </si>
+  <si>
+    <t>202603252600716102</t>
+  </si>
+  <si>
+    <t>159995579538573309</t>
+  </si>
+  <si>
+    <t>159995579538520617</t>
+  </si>
+  <si>
+    <t>159995579538525544</t>
+  </si>
+  <si>
+    <t>159995579538525551</t>
+  </si>
+  <si>
+    <t>159995579538525568</t>
   </si>
 </sst>
 </file>
@@ -372,10 +1044,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -657,829 +1328,1916 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A2:D103"/>
+  <dimension ref="A1:D173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" t="s">
+        <v>102</v>
+      </c>
+    </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
+      <c r="B2" t="s">
+        <v>159</v>
+      </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
+      <c r="B3" t="s">
+        <v>160</v>
+      </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
+      <c r="B4" t="s">
+        <v>161</v>
+      </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
+      <c r="B5" t="s">
+        <v>162</v>
+      </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
+      <c r="B6" t="s">
+        <v>163</v>
+      </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
+      <c r="B7" t="s">
+        <v>164</v>
+      </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
+      <c r="B8" t="s">
+        <v>165</v>
+      </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
+      <c r="B9" t="s">
+        <v>166</v>
+      </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
         <v>11</v>
       </c>
+      <c r="B10" t="s">
+        <v>167</v>
+      </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" t="s">
         <v>12</v>
       </c>
+      <c r="B11" t="s">
+        <v>168</v>
+      </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="C12" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B13" t="s">
+        <v>170</v>
+      </c>
+      <c r="C13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="C13" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="C14" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="B15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="C15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="B16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="C16" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="B17" t="s">
+        <v>174</v>
+      </c>
+      <c r="C17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C18" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="C17" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="B19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="C18" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="B20" t="s">
+        <v>177</v>
+      </c>
+      <c r="C20" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="C19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="B21" t="s">
+        <v>178</v>
+      </c>
+      <c r="C21" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="C20" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="B22" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="C21" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="B23" t="s">
+        <v>180</v>
+      </c>
+      <c r="C23" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="C22" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="B24" t="s">
+        <v>181</v>
+      </c>
+      <c r="C24" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="C23" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="B25" t="s">
+        <v>182</v>
+      </c>
+      <c r="C25" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="C24" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="B26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>184</v>
+      </c>
+      <c r="C27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>26</v>
       </c>
-      <c r="C25" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="B28" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>27</v>
       </c>
-      <c r="C26" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="B30" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>28</v>
       </c>
-      <c r="C27" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="B31" t="s">
+        <v>188</v>
+      </c>
+      <c r="C31" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>29</v>
       </c>
-      <c r="C28" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="B32" t="s">
+        <v>189</v>
+      </c>
+      <c r="C32" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>190</v>
+      </c>
+      <c r="C33" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="C29" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="B34" t="s">
+        <v>191</v>
+      </c>
+      <c r="C34" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>31</v>
       </c>
-      <c r="C30" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="B35" t="s">
+        <v>192</v>
+      </c>
+      <c r="C35" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>32</v>
       </c>
-      <c r="C31" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="B36" t="s">
+        <v>193</v>
+      </c>
+      <c r="C36" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>33</v>
       </c>
-      <c r="C32" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="B37" t="s">
+        <v>194</v>
+      </c>
+      <c r="C37" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>34</v>
       </c>
-      <c r="C33" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="B38" t="s">
+        <v>195</v>
+      </c>
+      <c r="C38" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" t="s">
+        <v>196</v>
+      </c>
+      <c r="C39" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>35</v>
       </c>
-      <c r="C34" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="B40" t="s">
+        <v>197</v>
+      </c>
+      <c r="C40" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>36</v>
       </c>
-      <c r="C35" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+      <c r="B41" t="s">
+        <v>198</v>
+      </c>
+      <c r="C41" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>37</v>
       </c>
-      <c r="C36" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+      <c r="B42" t="s">
+        <v>199</v>
+      </c>
+      <c r="C42" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" t="s">
+        <v>200</v>
+      </c>
+      <c r="C43" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>38</v>
       </c>
-      <c r="C37" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="B44" t="s">
+        <v>201</v>
+      </c>
+      <c r="C44" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>39</v>
       </c>
-      <c r="C38" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="B45" t="s">
+        <v>202</v>
+      </c>
+      <c r="C45" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>40</v>
       </c>
-      <c r="C39" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="B46" t="s">
+        <v>203</v>
+      </c>
+      <c r="C46" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>41</v>
       </c>
-      <c r="C40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="B47" t="s">
+        <v>204</v>
+      </c>
+      <c r="C47" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>42</v>
       </c>
-      <c r="C41" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+      <c r="B48" t="s">
+        <v>205</v>
+      </c>
+      <c r="C48" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>43</v>
       </c>
-      <c r="C42" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+      <c r="B49" t="s">
+        <v>206</v>
+      </c>
+      <c r="C49" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" t="s">
+        <v>207</v>
+      </c>
+      <c r="C50" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>44</v>
       </c>
-      <c r="C43" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+      <c r="B51" t="s">
+        <v>208</v>
+      </c>
+      <c r="C51" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" t="s">
+        <v>209</v>
+      </c>
+      <c r="C52" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>45</v>
       </c>
-      <c r="C44" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+      <c r="B54" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>0</v>
       </c>
-      <c r="C45" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+      <c r="B55" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>46</v>
       </c>
-      <c r="C46" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+      <c r="B56" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>47</v>
       </c>
-      <c r="C47" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+      <c r="B57" t="s">
+        <v>214</v>
+      </c>
+      <c r="C57" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>48</v>
       </c>
-      <c r="C48" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+      <c r="B58" t="s">
+        <v>215</v>
+      </c>
+      <c r="C58" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>49</v>
       </c>
-      <c r="C49" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+      <c r="B59" t="s">
+        <v>216</v>
+      </c>
+      <c r="C59" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>49</v>
+      </c>
+      <c r="B60" t="s">
+        <v>217</v>
+      </c>
+      <c r="C60" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>50</v>
       </c>
-      <c r="C50" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
+      <c r="B61" t="s">
+        <v>218</v>
+      </c>
+      <c r="C61" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>51</v>
       </c>
-      <c r="C51" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+      <c r="B62" t="s">
+        <v>219</v>
+      </c>
+      <c r="C62" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>52</v>
       </c>
-      <c r="C52" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
+      <c r="B63" t="s">
+        <v>220</v>
+      </c>
+      <c r="C63" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>52</v>
+      </c>
+      <c r="B64" t="s">
+        <v>221</v>
+      </c>
+      <c r="C64" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>52</v>
+      </c>
+      <c r="B65" t="s">
+        <v>222</v>
+      </c>
+      <c r="C65" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>53</v>
       </c>
-      <c r="C53" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
+      <c r="B66" t="s">
+        <v>223</v>
+      </c>
+      <c r="C66" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>53</v>
+      </c>
+      <c r="B67" t="s">
+        <v>224</v>
+      </c>
+      <c r="C67" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>53</v>
+      </c>
+      <c r="B68" t="s">
+        <v>225</v>
+      </c>
+      <c r="C68" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>1</v>
       </c>
-      <c r="C54" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
+      <c r="B69" t="s">
+        <v>226</v>
+      </c>
+      <c r="C69" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>54</v>
       </c>
-      <c r="C55" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
+      <c r="B70" t="s">
+        <v>227</v>
+      </c>
+      <c r="C70" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>55</v>
       </c>
-      <c r="C56" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
+      <c r="B71" t="s">
+        <v>228</v>
+      </c>
+      <c r="C71" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>56</v>
       </c>
-      <c r="C57" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
+      <c r="B72" t="s">
+        <v>229</v>
+      </c>
+      <c r="C72" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>57</v>
       </c>
-      <c r="C58" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
+      <c r="B73" t="s">
+        <v>230</v>
+      </c>
+      <c r="C73" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>58</v>
       </c>
-      <c r="C59" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+      <c r="B74" t="s">
+        <v>231</v>
+      </c>
+      <c r="C74" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>59</v>
       </c>
-      <c r="C60" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
+      <c r="B75" t="s">
+        <v>232</v>
+      </c>
+      <c r="C75" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>60</v>
       </c>
-      <c r="C61" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
+      <c r="B76" t="s">
+        <v>233</v>
+      </c>
+      <c r="C76" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>60</v>
+      </c>
+      <c r="B77" t="s">
+        <v>234</v>
+      </c>
+      <c r="C77" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>61</v>
       </c>
-      <c r="C62" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
+      <c r="B78" t="s">
+        <v>235</v>
+      </c>
+      <c r="C78" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>62</v>
       </c>
-      <c r="C63" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
+      <c r="B79" t="s">
+        <v>236</v>
+      </c>
+      <c r="C79" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>63</v>
       </c>
-      <c r="C64" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
+      <c r="B80" t="s">
+        <v>237</v>
+      </c>
+      <c r="C80" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>64</v>
       </c>
-      <c r="C65" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
+      <c r="B81" t="s">
+        <v>238</v>
+      </c>
+      <c r="C81" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>65</v>
       </c>
-      <c r="C66" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
+      <c r="B82" t="s">
+        <v>239</v>
+      </c>
+      <c r="C82" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>66</v>
       </c>
-      <c r="C67" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
+      <c r="B83" t="s">
+        <v>240</v>
+      </c>
+      <c r="C83" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>66</v>
+      </c>
+      <c r="B84" t="s">
+        <v>241</v>
+      </c>
+      <c r="C84" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>67</v>
       </c>
-      <c r="C68" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
+      <c r="B85" t="s">
+        <v>242</v>
+      </c>
+      <c r="C85" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>68</v>
       </c>
-      <c r="C69" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
+      <c r="B86" t="s">
+        <v>243</v>
+      </c>
+      <c r="C86" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>69</v>
       </c>
-      <c r="C70" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
+      <c r="B87" t="s">
+        <v>244</v>
+      </c>
+      <c r="C87" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
         <v>70</v>
       </c>
-      <c r="C71" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
+      <c r="B88" t="s">
+        <v>245</v>
+      </c>
+      <c r="C88" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>71</v>
       </c>
-      <c r="C72" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
+      <c r="B89" t="s">
+        <v>246</v>
+      </c>
+      <c r="C89" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>71</v>
+      </c>
+      <c r="B90" t="s">
+        <v>247</v>
+      </c>
+      <c r="C90" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>72</v>
       </c>
-      <c r="C73" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
+      <c r="B91" t="s">
+        <v>248</v>
+      </c>
+      <c r="C91" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
         <v>73</v>
       </c>
-      <c r="C74" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
+      <c r="B92" t="s">
+        <v>249</v>
+      </c>
+      <c r="C92" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
         <v>74</v>
       </c>
-      <c r="C75" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
+      <c r="B93" t="s">
+        <v>250</v>
+      </c>
+      <c r="C93" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
         <v>2</v>
       </c>
-      <c r="C76" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
+      <c r="B94" t="s">
+        <v>251</v>
+      </c>
+      <c r="C94" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
         <v>75</v>
       </c>
-      <c r="C77" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
+      <c r="B95" t="s">
+        <v>252</v>
+      </c>
+      <c r="C95" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
         <v>76</v>
       </c>
-      <c r="C78" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
+      <c r="B96" t="s">
+        <v>253</v>
+      </c>
+      <c r="C96" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
         <v>77</v>
       </c>
-      <c r="C79" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
+      <c r="B97" t="s">
+        <v>254</v>
+      </c>
+      <c r="C97" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
         <v>78</v>
       </c>
-      <c r="C80" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
+      <c r="B98" t="s">
+        <v>255</v>
+      </c>
+      <c r="C98" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
         <v>79</v>
       </c>
-      <c r="C81" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
+      <c r="B99" t="s">
+        <v>256</v>
+      </c>
+      <c r="C99" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
         <v>80</v>
       </c>
-      <c r="C82" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
+      <c r="B100" t="s">
+        <v>257</v>
+      </c>
+      <c r="C100" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
         <v>81</v>
       </c>
-      <c r="C83" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
+      <c r="B101" t="s">
+        <v>258</v>
+      </c>
+      <c r="C101" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>81</v>
+      </c>
+      <c r="B102" t="s">
+        <v>259</v>
+      </c>
+      <c r="C102" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
         <v>82</v>
       </c>
-      <c r="C84" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
+      <c r="B103" t="s">
+        <v>260</v>
+      </c>
+      <c r="C103" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
         <v>83</v>
       </c>
-      <c r="C85" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
+      <c r="B104" t="s">
+        <v>261</v>
+      </c>
+      <c r="C104" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
         <v>84</v>
       </c>
-      <c r="C86" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
+      <c r="B105" t="s">
+        <v>262</v>
+      </c>
+      <c r="C105" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
         <v>85</v>
       </c>
-      <c r="C87" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
+      <c r="B106" t="s">
+        <v>263</v>
+      </c>
+      <c r="C106" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
         <v>86</v>
       </c>
-      <c r="C88" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
+      <c r="B107" t="s">
+        <v>264</v>
+      </c>
+      <c r="C107" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
         <v>87</v>
       </c>
-      <c r="C89" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
+      <c r="B108" t="s">
+        <v>265</v>
+      </c>
+      <c r="C108" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
         <v>88</v>
       </c>
-      <c r="C90" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
+      <c r="B109" t="s">
+        <v>266</v>
+      </c>
+      <c r="C109" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
         <v>89</v>
       </c>
-      <c r="C91" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
+      <c r="B110" t="s">
+        <v>267</v>
+      </c>
+      <c r="C110" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
         <v>90</v>
       </c>
-      <c r="C92" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
+      <c r="B111" t="s">
+        <v>268</v>
+      </c>
+      <c r="C111" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>91</v>
       </c>
-      <c r="C93" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
+      <c r="B112" t="s">
+        <v>269</v>
+      </c>
+      <c r="C112" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
         <v>92</v>
       </c>
-      <c r="C94" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
+      <c r="B113" t="s">
+        <v>270</v>
+      </c>
+      <c r="C113" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
         <v>93</v>
       </c>
-      <c r="C95" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
+      <c r="B114" t="s">
+        <v>271</v>
+      </c>
+      <c r="C114" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
         <v>94</v>
       </c>
-      <c r="C96" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
+      <c r="B115" t="s">
+        <v>272</v>
+      </c>
+      <c r="C115" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
         <v>95</v>
       </c>
-      <c r="C97" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
+      <c r="B116" t="s">
+        <v>273</v>
+      </c>
+      <c r="C116" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
         <v>96</v>
       </c>
-      <c r="C98" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
+      <c r="B117" t="s">
+        <v>274</v>
+      </c>
+      <c r="C117" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
         <v>97</v>
       </c>
-      <c r="C99" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
+      <c r="B118" t="s">
+        <v>275</v>
+      </c>
+      <c r="C118" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
         <v>98</v>
       </c>
-      <c r="C100" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
+      <c r="B119" t="s">
+        <v>276</v>
+      </c>
+      <c r="C119" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>98</v>
+      </c>
+      <c r="B120" t="s">
+        <v>277</v>
+      </c>
+      <c r="C120" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>98</v>
+      </c>
+      <c r="B121" t="s">
+        <v>278</v>
+      </c>
+      <c r="C121" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
         <v>99</v>
       </c>
-      <c r="C101" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
+      <c r="B122" t="s">
+        <v>279</v>
+      </c>
+      <c r="C122" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
         <v>100</v>
       </c>
-      <c r="C102" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
+      <c r="B123" t="s">
+        <v>280</v>
+      </c>
+      <c r="C123" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
         <v>101</v>
       </c>
-      <c r="C103" t="s">
-        <v>102</v>
+      <c r="B124" t="s">
+        <v>281</v>
+      </c>
+      <c r="C124" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>125</v>
+      </c>
+      <c r="B125" t="s">
+        <v>282</v>
+      </c>
+      <c r="C125" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>126</v>
+      </c>
+      <c r="B126" t="s">
+        <v>283</v>
+      </c>
+      <c r="C126" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>127</v>
+      </c>
+      <c r="B127" t="s">
+        <v>127</v>
+      </c>
+      <c r="C127" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>128</v>
+      </c>
+      <c r="B128" t="s">
+        <v>284</v>
+      </c>
+      <c r="C128" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>129</v>
+      </c>
+      <c r="B129" t="s">
+        <v>285</v>
+      </c>
+      <c r="C129" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>130</v>
+      </c>
+      <c r="B130" t="s">
+        <v>286</v>
+      </c>
+      <c r="C130" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>131</v>
+      </c>
+      <c r="B131" t="s">
+        <v>287</v>
+      </c>
+      <c r="C131" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>132</v>
+      </c>
+      <c r="B132" t="s">
+        <v>288</v>
+      </c>
+      <c r="C132" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>133</v>
+      </c>
+      <c r="B133" t="s">
+        <v>289</v>
+      </c>
+      <c r="C133" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>290</v>
+      </c>
+      <c r="C134" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>291</v>
+      </c>
+      <c r="C135" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>292</v>
+      </c>
+      <c r="C136" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>293</v>
+      </c>
+      <c r="C137" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>294</v>
+      </c>
+      <c r="C138" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>137</v>
+      </c>
+      <c r="B139" t="s">
+        <v>295</v>
+      </c>
+      <c r="C139" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>138</v>
+      </c>
+      <c r="B140" t="s">
+        <v>296</v>
+      </c>
+      <c r="C140" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>139</v>
+      </c>
+      <c r="B141" t="s">
+        <v>297</v>
+      </c>
+      <c r="C141" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>140</v>
+      </c>
+      <c r="B142" t="s">
+        <v>298</v>
+      </c>
+      <c r="C142" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>141</v>
+      </c>
+      <c r="B143" t="s">
+        <v>299</v>
+      </c>
+      <c r="C143" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>141</v>
+      </c>
+      <c r="B144" t="s">
+        <v>300</v>
+      </c>
+      <c r="C144" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>142</v>
+      </c>
+      <c r="B145" t="s">
+        <v>301</v>
+      </c>
+      <c r="C145" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>143</v>
+      </c>
+      <c r="B146" t="s">
+        <v>302</v>
+      </c>
+      <c r="C146" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>144</v>
+      </c>
+      <c r="B147" t="s">
+        <v>303</v>
+      </c>
+      <c r="C147" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>145</v>
+      </c>
+      <c r="B148" t="s">
+        <v>304</v>
+      </c>
+      <c r="C148" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>145</v>
+      </c>
+      <c r="B149" t="s">
+        <v>305</v>
+      </c>
+      <c r="C149" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>145</v>
+      </c>
+      <c r="B150" t="s">
+        <v>306</v>
+      </c>
+      <c r="C150" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>145</v>
+      </c>
+      <c r="B151" t="s">
+        <v>307</v>
+      </c>
+      <c r="C151" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>146</v>
+      </c>
+      <c r="B152" t="s">
+        <v>308</v>
+      </c>
+      <c r="C152" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>147</v>
+      </c>
+      <c r="B153" t="s">
+        <v>309</v>
+      </c>
+      <c r="C153" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>147</v>
+      </c>
+      <c r="B154" t="s">
+        <v>310</v>
+      </c>
+      <c r="C154" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>147</v>
+      </c>
+      <c r="B155" t="s">
+        <v>311</v>
+      </c>
+      <c r="C155" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>147</v>
+      </c>
+      <c r="B156" t="s">
+        <v>312</v>
+      </c>
+      <c r="C156" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>148</v>
+      </c>
+      <c r="B157" t="s">
+        <v>313</v>
+      </c>
+      <c r="C157" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>148</v>
+      </c>
+      <c r="B158" t="s">
+        <v>314</v>
+      </c>
+      <c r="C158" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>149</v>
+      </c>
+      <c r="B159" t="s">
+        <v>315</v>
+      </c>
+      <c r="C159" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>150</v>
+      </c>
+      <c r="B160" t="s">
+        <v>316</v>
+      </c>
+      <c r="C160" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>150</v>
+      </c>
+      <c r="B161" t="s">
+        <v>317</v>
+      </c>
+      <c r="C161" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>151</v>
+      </c>
+      <c r="B162" t="s">
+        <v>318</v>
+      </c>
+      <c r="C162" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>151</v>
+      </c>
+      <c r="B163" t="s">
+        <v>319</v>
+      </c>
+      <c r="C163" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>152</v>
+      </c>
+      <c r="B164" t="s">
+        <v>320</v>
+      </c>
+      <c r="C164" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>152</v>
+      </c>
+      <c r="B165" t="s">
+        <v>321</v>
+      </c>
+      <c r="C165" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>153</v>
+      </c>
+      <c r="B166" t="s">
+        <v>322</v>
+      </c>
+      <c r="C166" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>154</v>
+      </c>
+      <c r="B167" t="s">
+        <v>323</v>
+      </c>
+      <c r="C167" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>155</v>
+      </c>
+      <c r="B168" t="s">
+        <v>324</v>
+      </c>
+      <c r="C168" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>155</v>
+      </c>
+      <c r="B169" t="s">
+        <v>325</v>
+      </c>
+      <c r="C169" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>155</v>
+      </c>
+      <c r="B170" t="s">
+        <v>326</v>
+      </c>
+      <c r="C170" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>156</v>
+      </c>
+      <c r="B171" t="s">
+        <v>156</v>
+      </c>
+      <c r="C171" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>157</v>
+      </c>
+      <c r="B172" t="s">
+        <v>157</v>
+      </c>
+      <c r="C172" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>127</v>
+      </c>
+      <c r="B173" t="s">
+        <v>127</v>
+      </c>
+      <c r="C173" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D70EFA-2724-4400-928A-04465B27556F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC752D7-3D1D-4A72-8B21-0E1DBBDA1E3F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="279">
   <si>
     <t>260319-F00012082</t>
   </si>
@@ -66,9 +66,6 @@
     <t>260320-F00001288-1</t>
   </si>
   <si>
-    <t>260320-F00006265</t>
-  </si>
-  <si>
     <t>260320-F00007295-1</t>
   </si>
   <si>
@@ -315,7 +312,559 @@
     <t>305667360</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>260322-W00008003</t>
+  </si>
+  <si>
+    <t>267004465</t>
+  </si>
+  <si>
+    <t>267004466</t>
+  </si>
+  <si>
+    <t>26MPE0003293</t>
+  </si>
+  <si>
+    <t>26MPE0003300</t>
+  </si>
+  <si>
+    <t>NFD6-03-19-Z3KA</t>
+  </si>
+  <si>
+    <t>NFD6-03-20-Q6RK</t>
+  </si>
+  <si>
+    <t>NFD6-03-23-PHCH</t>
+  </si>
+  <si>
+    <t>NFD6-03-24-JSVU</t>
+  </si>
+  <si>
+    <t>NFD6-03-25-485U</t>
+  </si>
+  <si>
+    <t>NFD6-03-25-4UM4</t>
+  </si>
+  <si>
+    <t>NFD6-03-25-988N</t>
+  </si>
+  <si>
+    <t>NFD6-03-25-R44V</t>
+  </si>
+  <si>
+    <t>NFE6-03-21-2C5Z</t>
+  </si>
+  <si>
+    <t>NFE6-03-24-DK5Y</t>
+  </si>
+  <si>
+    <t>NFE6-03-25-2DQ7</t>
+  </si>
+  <si>
+    <t>NFE6-03-25-BG7K</t>
+  </si>
+  <si>
+    <t>R414292</t>
+  </si>
+  <si>
+    <t>SZ 2026 137593</t>
+  </si>
+  <si>
+    <t>248744972/1</t>
+  </si>
+  <si>
+    <t>69b13adf51e7020fc80cccc4</t>
+  </si>
+  <si>
+    <t>69c24e64d96b4f4a24384f09</t>
+  </si>
+  <si>
+    <t>69b9506ad96b4f4a2437cfb2</t>
+  </si>
+  <si>
+    <t>69c39f76d96b4f4a24386478</t>
+  </si>
+  <si>
+    <t>69c3c301d96b4f4a24386a3c</t>
+  </si>
+  <si>
+    <t>69c3b690d96b4f4a24386839</t>
+  </si>
+  <si>
+    <t>69c29331d96b4f4a243858db</t>
+  </si>
+  <si>
+    <t>69bd1d58d96b4f4a24380db3</t>
+  </si>
+  <si>
+    <t>69bd9114d96b4f4a24381a9a</t>
+  </si>
+  <si>
+    <t>69c3a917d96b4f4a243865fa</t>
+  </si>
+  <si>
+    <t>69c0434bd96b4f4a24383167</t>
+  </si>
+  <si>
+    <t>69c26760d96b4f4a243852e1</t>
+  </si>
+  <si>
+    <t>69c10e5fd96b4f4a24383804</t>
+  </si>
+  <si>
+    <t>69c10e5fd96b4f4a24383805</t>
+  </si>
+  <si>
+    <t>69c12eefd96b4f4a24383dc1</t>
+  </si>
+  <si>
+    <t>69c283e4d96b4f4a24385678</t>
+  </si>
+  <si>
+    <t>69c283e4d96b4f4a24385679</t>
+  </si>
+  <si>
+    <t>69c28e68d96b4f4a243857fb</t>
+  </si>
+  <si>
+    <t>69c290bdd96b4f4a2438584a</t>
+  </si>
+  <si>
+    <t>69c28f96d96b4f4a24385815</t>
+  </si>
+  <si>
+    <t>69c28f96d96b4f4a24385818</t>
+  </si>
+  <si>
+    <t>69c28f96d96b4f4a2438581a</t>
+  </si>
+  <si>
+    <t>69c2d979d96b4f4a2438608b</t>
+  </si>
+  <si>
+    <t>69c2d979d96b4f4a2438608c</t>
+  </si>
+  <si>
+    <t>69c312d7d96b4f4a243861f2</t>
+  </si>
+  <si>
+    <t>69c3b6e3d96b4f4a2438683f</t>
+  </si>
+  <si>
+    <t>69c3dce7d96b4f4a24386da8</t>
+  </si>
+  <si>
+    <t>69c3db40d96b4f4a24386d5f</t>
+  </si>
+  <si>
+    <t>69c3ef8bd96b4f4a24387068</t>
+  </si>
+  <si>
+    <t>69c408f5d96b4f4a243873a2</t>
+  </si>
+  <si>
+    <t>69c42f99d96b4f4a24387654</t>
+  </si>
+  <si>
+    <t>69c42f9ad96b4f4a24387657</t>
+  </si>
+  <si>
+    <t>69c3d560d96b4f4a24386c9b</t>
+  </si>
+  <si>
+    <t>69c3e162d96b4f4a24386e8b</t>
+  </si>
+  <si>
+    <t>69c43eeed96b4f4a243876f2</t>
+  </si>
+  <si>
+    <t>69c4fde1d96b4f4a24387c6c</t>
+  </si>
+  <si>
+    <t>FIZZ-1000849314</t>
+  </si>
+  <si>
+    <t>1449-948833</t>
+  </si>
+  <si>
+    <t>26MPE0003293/1</t>
+  </si>
+  <si>
+    <t>26MPE0003300/1</t>
+  </si>
+  <si>
+    <t>304576536/1</t>
+  </si>
+  <si>
+    <t>304826661/1</t>
+  </si>
+  <si>
+    <t>304826661/2</t>
+  </si>
+  <si>
+    <t>304826661/3</t>
+  </si>
+  <si>
+    <t>304875165/1</t>
+  </si>
+  <si>
+    <t>304875527/1</t>
+  </si>
+  <si>
+    <t>304925187/1</t>
+  </si>
+  <si>
+    <t>304963429/1</t>
+  </si>
+  <si>
+    <t>304963429/2</t>
+  </si>
+  <si>
+    <t>305169860/2/1</t>
+  </si>
+  <si>
+    <t>305169860/2/2</t>
+  </si>
+  <si>
+    <t>305169860/2/3</t>
+  </si>
+  <si>
+    <t>305225419/1</t>
+  </si>
+  <si>
+    <t>305225419/2</t>
+  </si>
+  <si>
+    <t>305272678/1</t>
+  </si>
+  <si>
+    <t>305273127/1</t>
+  </si>
+  <si>
+    <t>305273127/2</t>
+  </si>
+  <si>
+    <t>305273127/3</t>
+  </si>
+  <si>
+    <t>305273217/1</t>
+  </si>
+  <si>
+    <t>305273217/2</t>
+  </si>
+  <si>
+    <t>305316045/1</t>
+  </si>
+  <si>
+    <t>305367873/1</t>
+  </si>
+  <si>
+    <t>305367873/2</t>
+  </si>
+  <si>
+    <t>305368467/1</t>
+  </si>
+  <si>
+    <t>305411534/1</t>
+  </si>
+  <si>
+    <t>305411534/2</t>
+  </si>
+  <si>
+    <t>305411632/1</t>
+  </si>
+  <si>
+    <t>305411632/2</t>
+  </si>
+  <si>
+    <t>305411632/3</t>
+  </si>
+  <si>
+    <t>305412274/1</t>
+  </si>
+  <si>
+    <t>305461509/1</t>
+  </si>
+  <si>
+    <t>305461509/2</t>
+  </si>
+  <si>
+    <t>305461526/1</t>
+  </si>
+  <si>
+    <t>305461661/1</t>
+  </si>
+  <si>
+    <t>305461842/1</t>
+  </si>
+  <si>
+    <t>305461842/2</t>
+  </si>
+  <si>
+    <t>305462350/1</t>
+  </si>
+  <si>
+    <t>305514164/1</t>
+  </si>
+  <si>
+    <t>305514179/1</t>
+  </si>
+  <si>
+    <t>305514421/1</t>
+  </si>
+  <si>
+    <t>305514421/2</t>
+  </si>
+  <si>
+    <t>305514421/3</t>
+  </si>
+  <si>
+    <t>305514425/1</t>
+  </si>
+  <si>
+    <t>305514520/1</t>
+  </si>
+  <si>
+    <t>305514591/1</t>
+  </si>
+  <si>
+    <t>305556937/1</t>
+  </si>
+  <si>
+    <t>305557043/1</t>
+  </si>
+  <si>
+    <t>305557043/2</t>
+  </si>
+  <si>
+    <t>305557076/1</t>
+  </si>
+  <si>
+    <t>305557116/1</t>
+  </si>
+  <si>
+    <t>305557116/2</t>
+  </si>
+  <si>
+    <t>305557116/3</t>
+  </si>
+  <si>
+    <t>305557127/1</t>
+  </si>
+  <si>
+    <t>305557206/1</t>
+  </si>
+  <si>
+    <t>305557206/2</t>
+  </si>
+  <si>
+    <t>305557240/1</t>
+  </si>
+  <si>
+    <t>305557457/1</t>
+  </si>
+  <si>
+    <t>305557485/1</t>
+  </si>
+  <si>
+    <t>305557510/1</t>
+  </si>
+  <si>
+    <t>305557510/2</t>
+  </si>
+  <si>
+    <t>305557607/1</t>
+  </si>
+  <si>
+    <t>305557607/2</t>
+  </si>
+  <si>
+    <t>305557633/1</t>
+  </si>
+  <si>
+    <t>305557678/1</t>
+  </si>
+  <si>
+    <t>305557697/1</t>
+  </si>
+  <si>
+    <t>305557707/1</t>
+  </si>
+  <si>
+    <t>305627959/1</t>
+  </si>
+  <si>
+    <t>305627959/2</t>
+  </si>
+  <si>
+    <t>305628104/1</t>
+  </si>
+  <si>
+    <t>305628296/1</t>
+  </si>
+  <si>
+    <t>305628296/2</t>
+  </si>
+  <si>
+    <t>305628358/1</t>
+  </si>
+  <si>
+    <t>305628390/1</t>
+  </si>
+  <si>
+    <t>305628560/1</t>
+  </si>
+  <si>
+    <t>305628668/1</t>
+  </si>
+  <si>
+    <t>305628708/1</t>
+  </si>
+  <si>
+    <t>305628716/1</t>
+  </si>
+  <si>
+    <t>305628794/1</t>
+  </si>
+  <si>
+    <t>305666953/1</t>
+  </si>
+  <si>
+    <t>305666958/1</t>
+  </si>
+  <si>
+    <t>305666958/2</t>
+  </si>
+  <si>
+    <t>305667035/1</t>
+  </si>
+  <si>
+    <t>305667035/2</t>
+  </si>
+  <si>
+    <t>305667066/1</t>
+  </si>
+  <si>
+    <t>305667140/1</t>
+  </si>
+  <si>
+    <t>305667140/2</t>
+  </si>
+  <si>
+    <t>305667140/3</t>
+  </si>
+  <si>
+    <t>305667163/1</t>
+  </si>
+  <si>
+    <t>305667360/1</t>
+  </si>
+  <si>
+    <t>202603262600668601</t>
+  </si>
+  <si>
+    <t>202603262600677301</t>
+  </si>
+  <si>
+    <t>202603242600707601</t>
+  </si>
+  <si>
+    <t>202603252600719101</t>
+  </si>
+  <si>
+    <t>202603262600724901</t>
+  </si>
+  <si>
+    <t>202603262600725601</t>
+  </si>
+  <si>
+    <t>202603262600725602</t>
+  </si>
+  <si>
+    <t>202603262600725301</t>
+  </si>
+  <si>
+    <t>202603262600730601</t>
+  </si>
+  <si>
+    <t>202603232600686301</t>
+  </si>
+  <si>
+    <t>202603232600686302</t>
+  </si>
+  <si>
+    <t>202603252600718501</t>
+  </si>
+  <si>
+    <t>202603262600724401</t>
+  </si>
+  <si>
+    <t>202603262600730901</t>
+  </si>
+  <si>
+    <t>202603262600730902</t>
+  </si>
+  <si>
+    <t>159995579538580253</t>
+  </si>
+  <si>
+    <t>159995579538580260</t>
+  </si>
+  <si>
+    <t>159995579538580314</t>
+  </si>
+  <si>
+    <t>159995579538580321</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>SZ-829</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
   </si>
 </sst>
 </file>
@@ -351,10 +900,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -636,11 +1184,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="1"/>
   </cols>
@@ -657,739 +1205,1642 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
+      <c r="B2" t="s">
+        <v>113</v>
+      </c>
       <c r="C2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>133</v>
+      </c>
+      <c r="C22" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" t="s">
+        <v>138</v>
+      </c>
+      <c r="C27" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
+        <v>139</v>
+      </c>
+      <c r="C28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
+        <v>141</v>
+      </c>
+      <c r="C30" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C31" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
+        <v>145</v>
+      </c>
+      <c r="C34" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" t="s">
+        <v>146</v>
+      </c>
+      <c r="C35" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" t="s">
+        <v>147</v>
+      </c>
+      <c r="C36" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" t="s">
+        <v>148</v>
+      </c>
+      <c r="C37" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="B39" t="s">
+        <v>150</v>
+      </c>
+      <c r="C39" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" t="s">
+        <v>151</v>
+      </c>
+      <c r="C40" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41" t="s">
+        <v>152</v>
+      </c>
+      <c r="C41" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>98</v>
+      </c>
+      <c r="B42" t="s">
+        <v>153</v>
+      </c>
+      <c r="C42" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>35</v>
       </c>
-      <c r="C33" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="B43" t="s">
+        <v>154</v>
+      </c>
+      <c r="C43" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>36</v>
       </c>
-      <c r="C34" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="B44" t="s">
+        <v>155</v>
+      </c>
+      <c r="C44" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45" t="s">
+        <v>156</v>
+      </c>
+      <c r="C45" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" t="s">
+        <v>157</v>
+      </c>
+      <c r="C46" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>3</v>
+      </c>
+      <c r="B47" t="s">
+        <v>158</v>
+      </c>
+      <c r="C47" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>37</v>
       </c>
-      <c r="C35" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C36" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+      <c r="B48" t="s">
+        <v>159</v>
+      </c>
+      <c r="C48" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>38</v>
       </c>
-      <c r="C37" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="B49" t="s">
+        <v>160</v>
+      </c>
+      <c r="C49" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>39</v>
       </c>
-      <c r="C38" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="B50" t="s">
+        <v>161</v>
+      </c>
+      <c r="C50" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" t="s">
+        <v>162</v>
+      </c>
+      <c r="C51" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>40</v>
       </c>
-      <c r="C39" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="B52" t="s">
+        <v>163</v>
+      </c>
+      <c r="C52" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" t="s">
+        <v>164</v>
+      </c>
+      <c r="C53" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" t="s">
+        <v>165</v>
+      </c>
+      <c r="C54" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>41</v>
       </c>
-      <c r="C40" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="B55" t="s">
+        <v>166</v>
+      </c>
+      <c r="C55" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" t="s">
+        <v>167</v>
+      </c>
+      <c r="C56" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>42</v>
       </c>
-      <c r="C41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+      <c r="B57" t="s">
+        <v>168</v>
+      </c>
+      <c r="C57" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>43</v>
       </c>
-      <c r="C42" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+      <c r="B58" t="s">
+        <v>169</v>
+      </c>
+      <c r="C58" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" t="s">
+        <v>170</v>
+      </c>
+      <c r="C59" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" t="s">
+        <v>171</v>
+      </c>
+      <c r="C60" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>44</v>
       </c>
-      <c r="C43" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+      <c r="B61" t="s">
+        <v>172</v>
+      </c>
+      <c r="C61" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" t="s">
+        <v>173</v>
+      </c>
+      <c r="C62" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>45</v>
       </c>
-      <c r="C44" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+      <c r="B63" t="s">
+        <v>174</v>
+      </c>
+      <c r="C63" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>46</v>
       </c>
-      <c r="C45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+      <c r="B64" t="s">
+        <v>175</v>
+      </c>
+      <c r="C64" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>46</v>
+      </c>
+      <c r="B65" t="s">
+        <v>176</v>
+      </c>
+      <c r="C65" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>47</v>
       </c>
-      <c r="C46" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+      <c r="B66" t="s">
+        <v>177</v>
+      </c>
+      <c r="C66" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>48</v>
       </c>
-      <c r="C47" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+      <c r="B67" t="s">
+        <v>178</v>
+      </c>
+      <c r="C67" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>48</v>
+      </c>
+      <c r="B68" t="s">
+        <v>179</v>
+      </c>
+      <c r="C68" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>49</v>
       </c>
-      <c r="C48" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+      <c r="B69" t="s">
+        <v>180</v>
+      </c>
+      <c r="C69" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>49</v>
+      </c>
+      <c r="B70" t="s">
+        <v>181</v>
+      </c>
+      <c r="C70" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>49</v>
+      </c>
+      <c r="B71" t="s">
+        <v>182</v>
+      </c>
+      <c r="C71" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>50</v>
       </c>
-      <c r="C49" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+      <c r="B72" t="s">
+        <v>183</v>
+      </c>
+      <c r="C72" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>51</v>
       </c>
-      <c r="C50" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
+      <c r="B73" t="s">
+        <v>184</v>
+      </c>
+      <c r="C73" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>51</v>
+      </c>
+      <c r="B74" t="s">
+        <v>185</v>
+      </c>
+      <c r="C74" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>52</v>
       </c>
-      <c r="C51" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+      <c r="B75" t="s">
+        <v>186</v>
+      </c>
+      <c r="C75" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>53</v>
       </c>
-      <c r="C52" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
+      <c r="B76" t="s">
+        <v>187</v>
+      </c>
+      <c r="C76" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>54</v>
       </c>
-      <c r="C53" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
+      <c r="B77" t="s">
+        <v>188</v>
+      </c>
+      <c r="C77" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>54</v>
+      </c>
+      <c r="B78" t="s">
+        <v>189</v>
+      </c>
+      <c r="C78" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>55</v>
       </c>
-      <c r="C54" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
+      <c r="B79" t="s">
+        <v>190</v>
+      </c>
+      <c r="C79" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>56</v>
       </c>
-      <c r="C55" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
+      <c r="B80" t="s">
+        <v>191</v>
+      </c>
+      <c r="C80" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>57</v>
       </c>
-      <c r="C56" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
+      <c r="B81" t="s">
+        <v>192</v>
+      </c>
+      <c r="C81" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>58</v>
       </c>
-      <c r="C57" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
+      <c r="B82" t="s">
+        <v>193</v>
+      </c>
+      <c r="C82" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>58</v>
+      </c>
+      <c r="B83" t="s">
+        <v>194</v>
+      </c>
+      <c r="C83" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>58</v>
+      </c>
+      <c r="B84" t="s">
+        <v>195</v>
+      </c>
+      <c r="C84" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>59</v>
       </c>
-      <c r="C58" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
+      <c r="B85" t="s">
+        <v>196</v>
+      </c>
+      <c r="C85" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>60</v>
       </c>
-      <c r="C59" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+      <c r="B86" t="s">
+        <v>197</v>
+      </c>
+      <c r="C86" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>61</v>
       </c>
-      <c r="C60" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
+      <c r="B87" t="s">
+        <v>198</v>
+      </c>
+      <c r="C87" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
         <v>62</v>
       </c>
-      <c r="C61" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
+      <c r="B88" t="s">
+        <v>199</v>
+      </c>
+      <c r="C88" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>63</v>
       </c>
-      <c r="C62" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
+      <c r="B89" t="s">
+        <v>200</v>
+      </c>
+      <c r="C89" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>63</v>
+      </c>
+      <c r="B90" t="s">
+        <v>201</v>
+      </c>
+      <c r="C90" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>64</v>
       </c>
-      <c r="C63" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
+      <c r="B91" t="s">
+        <v>202</v>
+      </c>
+      <c r="C91" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
         <v>65</v>
       </c>
-      <c r="C64" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
+      <c r="B92" t="s">
+        <v>203</v>
+      </c>
+      <c r="C92" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>65</v>
+      </c>
+      <c r="B93" t="s">
+        <v>204</v>
+      </c>
+      <c r="C93" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>65</v>
+      </c>
+      <c r="B94" t="s">
+        <v>205</v>
+      </c>
+      <c r="C94" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
         <v>66</v>
       </c>
-      <c r="C65" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
+      <c r="B95" t="s">
+        <v>206</v>
+      </c>
+      <c r="C95" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
         <v>67</v>
       </c>
-      <c r="C66" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
+      <c r="B96" t="s">
+        <v>207</v>
+      </c>
+      <c r="C96" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>67</v>
+      </c>
+      <c r="B97" t="s">
+        <v>208</v>
+      </c>
+      <c r="C97" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
         <v>68</v>
       </c>
-      <c r="C67" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
+      <c r="B98" t="s">
+        <v>209</v>
+      </c>
+      <c r="C98" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
         <v>69</v>
       </c>
-      <c r="C68" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
+      <c r="B99" t="s">
+        <v>210</v>
+      </c>
+      <c r="C99" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
         <v>70</v>
       </c>
-      <c r="C69" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
+      <c r="B100" t="s">
+        <v>211</v>
+      </c>
+      <c r="C100" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
         <v>71</v>
       </c>
-      <c r="C70" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
+      <c r="B101" t="s">
+        <v>212</v>
+      </c>
+      <c r="C101" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>71</v>
+      </c>
+      <c r="B102" t="s">
+        <v>213</v>
+      </c>
+      <c r="C102" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
         <v>72</v>
       </c>
-      <c r="C71" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
+      <c r="B103" t="s">
+        <v>214</v>
+      </c>
+      <c r="C103" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>72</v>
+      </c>
+      <c r="B104" t="s">
+        <v>215</v>
+      </c>
+      <c r="C104" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
         <v>73</v>
       </c>
-      <c r="C72" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
+      <c r="B105" t="s">
+        <v>216</v>
+      </c>
+      <c r="C105" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
         <v>74</v>
       </c>
-      <c r="C73" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
+      <c r="B106" t="s">
+        <v>217</v>
+      </c>
+      <c r="C106" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
         <v>75</v>
       </c>
-      <c r="C74" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
+      <c r="B107" t="s">
+        <v>218</v>
+      </c>
+      <c r="C107" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
         <v>76</v>
       </c>
-      <c r="C75" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
+      <c r="B108" t="s">
+        <v>219</v>
+      </c>
+      <c r="C108" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
         <v>77</v>
       </c>
-      <c r="C76" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
+      <c r="B109" t="s">
+        <v>220</v>
+      </c>
+      <c r="C109" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>77</v>
+      </c>
+      <c r="B110" t="s">
+        <v>221</v>
+      </c>
+      <c r="C110" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
         <v>78</v>
       </c>
-      <c r="C77" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
+      <c r="B111" t="s">
+        <v>222</v>
+      </c>
+      <c r="C111" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>79</v>
       </c>
-      <c r="C78" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
+      <c r="B112" t="s">
+        <v>223</v>
+      </c>
+      <c r="C112" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>79</v>
+      </c>
+      <c r="B113" t="s">
+        <v>224</v>
+      </c>
+      <c r="C113" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
         <v>80</v>
       </c>
-      <c r="C79" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
+      <c r="B114" t="s">
+        <v>225</v>
+      </c>
+      <c r="C114" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
         <v>81</v>
       </c>
-      <c r="C80" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
+      <c r="B115" t="s">
+        <v>226</v>
+      </c>
+      <c r="C115" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
         <v>82</v>
       </c>
-      <c r="C81" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
+      <c r="B116" t="s">
+        <v>227</v>
+      </c>
+      <c r="C116" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
         <v>83</v>
       </c>
-      <c r="C82" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
+      <c r="B117" t="s">
+        <v>228</v>
+      </c>
+      <c r="C117" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
         <v>84</v>
       </c>
-      <c r="C83" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
+      <c r="B118" t="s">
+        <v>229</v>
+      </c>
+      <c r="C118" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
         <v>85</v>
       </c>
-      <c r="C84" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
+      <c r="B119" t="s">
+        <v>230</v>
+      </c>
+      <c r="C119" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
         <v>86</v>
       </c>
-      <c r="C85" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
+      <c r="B120" t="s">
+        <v>231</v>
+      </c>
+      <c r="C120" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
         <v>87</v>
       </c>
-      <c r="C86" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
+      <c r="B121" t="s">
+        <v>232</v>
+      </c>
+      <c r="C121" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
         <v>88</v>
       </c>
-      <c r="C87" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
+      <c r="B122" t="s">
+        <v>233</v>
+      </c>
+      <c r="C122" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>88</v>
+      </c>
+      <c r="B123" t="s">
+        <v>234</v>
+      </c>
+      <c r="C123" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
         <v>89</v>
       </c>
-      <c r="C88" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
+      <c r="B124" t="s">
+        <v>235</v>
+      </c>
+      <c r="C124" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>89</v>
+      </c>
+      <c r="B125" t="s">
+        <v>236</v>
+      </c>
+      <c r="C125" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
         <v>90</v>
       </c>
-      <c r="C89" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
+      <c r="B126" t="s">
+        <v>237</v>
+      </c>
+      <c r="C126" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
         <v>91</v>
       </c>
-      <c r="C90" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
+      <c r="B127" t="s">
+        <v>238</v>
+      </c>
+      <c r="C127" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>91</v>
+      </c>
+      <c r="B128" t="s">
+        <v>239</v>
+      </c>
+      <c r="C128" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>91</v>
+      </c>
+      <c r="B129" t="s">
+        <v>240</v>
+      </c>
+      <c r="C129" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
         <v>92</v>
       </c>
-      <c r="C91" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
+      <c r="B130" t="s">
+        <v>241</v>
+      </c>
+      <c r="C130" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
         <v>93</v>
       </c>
-      <c r="C92" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C93" t="s">
-        <v>95</v>
+      <c r="B131" t="s">
+        <v>242</v>
+      </c>
+      <c r="C131" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>99</v>
+      </c>
+      <c r="B132" t="s">
+        <v>243</v>
+      </c>
+      <c r="C132" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>100</v>
+      </c>
+      <c r="B133" t="s">
+        <v>244</v>
+      </c>
+      <c r="C133" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>101</v>
+      </c>
+      <c r="B134" t="s">
+        <v>245</v>
+      </c>
+      <c r="C134" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>102</v>
+      </c>
+      <c r="B135" t="s">
+        <v>246</v>
+      </c>
+      <c r="C135" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>103</v>
+      </c>
+      <c r="B136" t="s">
+        <v>247</v>
+      </c>
+      <c r="C136" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>104</v>
+      </c>
+      <c r="B137" t="s">
+        <v>248</v>
+      </c>
+      <c r="C137" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>104</v>
+      </c>
+      <c r="B138" t="s">
+        <v>249</v>
+      </c>
+      <c r="C138" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>105</v>
+      </c>
+      <c r="B139" t="s">
+        <v>250</v>
+      </c>
+      <c r="C139" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>106</v>
+      </c>
+      <c r="B140" t="s">
+        <v>251</v>
+      </c>
+      <c r="C140" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>107</v>
+      </c>
+      <c r="B141" t="s">
+        <v>252</v>
+      </c>
+      <c r="C141" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>107</v>
+      </c>
+      <c r="B142" t="s">
+        <v>253</v>
+      </c>
+      <c r="C142" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>108</v>
+      </c>
+      <c r="B143" t="s">
+        <v>254</v>
+      </c>
+      <c r="C143" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>109</v>
+      </c>
+      <c r="B144" t="s">
+        <v>255</v>
+      </c>
+      <c r="C144" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>110</v>
+      </c>
+      <c r="B145" t="s">
+        <v>256</v>
+      </c>
+      <c r="C145" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>110</v>
+      </c>
+      <c r="B146" t="s">
+        <v>257</v>
+      </c>
+      <c r="C146" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>111</v>
+      </c>
+      <c r="B147" t="s">
+        <v>258</v>
+      </c>
+      <c r="C147" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>111</v>
+      </c>
+      <c r="B148" t="s">
+        <v>259</v>
+      </c>
+      <c r="C148" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>112</v>
+      </c>
+      <c r="B149" t="s">
+        <v>260</v>
+      </c>
+      <c r="C149" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>112</v>
+      </c>
+      <c r="B150" t="s">
+        <v>261</v>
+      </c>
+      <c r="C150" t="s">
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F123E4D-7B1F-48D0-9ED9-441BBD2A808A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723E7951-332B-4D13-8B74-08F8D29D2DD5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="390">
   <si>
     <t>UTK</t>
   </si>
@@ -51,9 +51,6 @@
     <t>260310-F00003841</t>
   </si>
   <si>
-    <t>260318-F00012789-1</t>
-  </si>
-  <si>
     <t>260319-F00005275</t>
   </si>
   <si>
@@ -369,7 +366,838 @@
     <t>306334375</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>SZ-854</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>SZ-840</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-829</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-827</t>
+  </si>
+  <si>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>159995579538704314</t>
+  </si>
+  <si>
+    <t>248745052/1</t>
+  </si>
+  <si>
+    <t>69b538f86967eb2a8b5ce608</t>
+  </si>
+  <si>
+    <t>69c69d04d96b4f4a24389a65</t>
+  </si>
+  <si>
+    <t>69c29206d96b4f4a2438588e</t>
+  </si>
+  <si>
+    <t>69c24cffd96b4f4a24384ed2</t>
+  </si>
+  <si>
+    <t>69c24cffd96b4f4a24384ed3</t>
+  </si>
+  <si>
+    <t>69c6760ad96b4f4a2438954a</t>
+  </si>
+  <si>
+    <t>69c55217d96b4f4a2438876d</t>
+  </si>
+  <si>
+    <t>69c55217d96b4f4a2438876f</t>
+  </si>
+  <si>
+    <t>69c3d582d96b4f4a24386cb2</t>
+  </si>
+  <si>
+    <t>69ca44650ed4809420f49ad4</t>
+  </si>
+  <si>
+    <t>69c54304d96b4f4a243885de</t>
+  </si>
+  <si>
+    <t>69c54304d96b4f4a243885e0</t>
+  </si>
+  <si>
+    <t>69c5376cd96b4f4a24388417</t>
+  </si>
+  <si>
+    <t>69c52b8dd96b4f4a24388248</t>
+  </si>
+  <si>
+    <t>69c52b8dd96b4f4a2438824a</t>
+  </si>
+  <si>
+    <t>69c53e4cd96b4f4a2438851a</t>
+  </si>
+  <si>
+    <t>69c65b16d96b4f4a243891de</t>
+  </si>
+  <si>
+    <t>69c67f6bd96b4f4a243896a9</t>
+  </si>
+  <si>
+    <t>69c67f6bd96b4f4a243896aa</t>
+  </si>
+  <si>
+    <t>69c6b9fcd96b4f4a24389cb4</t>
+  </si>
+  <si>
+    <t>69c78bc00ed4809420f47cf0</t>
+  </si>
+  <si>
+    <t>69c7b4d10ed4809420f48163</t>
+  </si>
+  <si>
+    <t>69c7b4d10ed4809420f48164</t>
+  </si>
+  <si>
+    <t>69c806cd0ed4809420f486f5</t>
+  </si>
+  <si>
+    <t>69c806cd0ed4809420f486f6</t>
+  </si>
+  <si>
+    <t>69c81ab90ed4809420f487ee</t>
+  </si>
+  <si>
+    <t>69c8d2b70ed4809420f4899f</t>
+  </si>
+  <si>
+    <t>69c8d2b70ed4809420f489a1</t>
+  </si>
+  <si>
+    <t>69c9076e0ed4809420f48cb5</t>
+  </si>
+  <si>
+    <t>69c9076e0ed4809420f48cb6</t>
+  </si>
+  <si>
+    <t>69c911fd0ed4809420f48d37</t>
+  </si>
+  <si>
+    <t>69c96b100ed4809420f49262</t>
+  </si>
+  <si>
+    <t>69c981550ed4809420f49313</t>
+  </si>
+  <si>
+    <t>69c9a0f80ed4809420f49383</t>
+  </si>
+  <si>
+    <t>69ca42aa0ed4809420f49a6e</t>
+  </si>
+  <si>
+    <t>69ca5a1f0ed4809420f49e3c</t>
+  </si>
+  <si>
+    <t>FIZZ-1000851362</t>
+  </si>
+  <si>
+    <t>FIZZ-1000851624</t>
+  </si>
+  <si>
+    <t>FIZZ-1000855521</t>
+  </si>
+  <si>
+    <t>1449-352092</t>
+  </si>
+  <si>
+    <t>304676066/1/1</t>
+  </si>
+  <si>
+    <t>305368079/1</t>
+  </si>
+  <si>
+    <t>305368497/1</t>
+  </si>
+  <si>
+    <t>305412140/1</t>
+  </si>
+  <si>
+    <t>305461585/1</t>
+  </si>
+  <si>
+    <t>305462193/1</t>
+  </si>
+  <si>
+    <t>305462193/2</t>
+  </si>
+  <si>
+    <t>305462193/3</t>
+  </si>
+  <si>
+    <t>305462293/1</t>
+  </si>
+  <si>
+    <t>305462293/2</t>
+  </si>
+  <si>
+    <t>305557677/1</t>
+  </si>
+  <si>
+    <t>305557715/1</t>
+  </si>
+  <si>
+    <t>305557715/2</t>
+  </si>
+  <si>
+    <t>305666948/1</t>
+  </si>
+  <si>
+    <t>305667898/1</t>
+  </si>
+  <si>
+    <t>305725639/1</t>
+  </si>
+  <si>
+    <t>305725639/2</t>
+  </si>
+  <si>
+    <t>305725853/1</t>
+  </si>
+  <si>
+    <t>305725898/1</t>
+  </si>
+  <si>
+    <t>305726246/1</t>
+  </si>
+  <si>
+    <t>305781064/1</t>
+  </si>
+  <si>
+    <t>305781147/1</t>
+  </si>
+  <si>
+    <t>305781454/1</t>
+  </si>
+  <si>
+    <t>305782022/1</t>
+  </si>
+  <si>
+    <t>305782022/2</t>
+  </si>
+  <si>
+    <t>305830650/1</t>
+  </si>
+  <si>
+    <t>305830650/2</t>
+  </si>
+  <si>
+    <t>305830650/3</t>
+  </si>
+  <si>
+    <t>305830674/1</t>
+  </si>
+  <si>
+    <t>305830746/1</t>
+  </si>
+  <si>
+    <t>305831048/1</t>
+  </si>
+  <si>
+    <t>305831070/1</t>
+  </si>
+  <si>
+    <t>305831163/1</t>
+  </si>
+  <si>
+    <t>305831186/1</t>
+  </si>
+  <si>
+    <t>305831241/1</t>
+  </si>
+  <si>
+    <t>305831241/2</t>
+  </si>
+  <si>
+    <t>305831241/3</t>
+  </si>
+  <si>
+    <t>305831285/1</t>
+  </si>
+  <si>
+    <t>305901369/1</t>
+  </si>
+  <si>
+    <t>305901427/1</t>
+  </si>
+  <si>
+    <t>305901427/2</t>
+  </si>
+  <si>
+    <t>305901483/1</t>
+  </si>
+  <si>
+    <t>305901533/1</t>
+  </si>
+  <si>
+    <t>305901619/1</t>
+  </si>
+  <si>
+    <t>305901665/1</t>
+  </si>
+  <si>
+    <t>305901665/2</t>
+  </si>
+  <si>
+    <t>305901792/1</t>
+  </si>
+  <si>
+    <t>305901845/1</t>
+  </si>
+  <si>
+    <t>305901864/1</t>
+  </si>
+  <si>
+    <t>305901933/1</t>
+  </si>
+  <si>
+    <t>305902119/1</t>
+  </si>
+  <si>
+    <t>305902266/1</t>
+  </si>
+  <si>
+    <t>305954219/1</t>
+  </si>
+  <si>
+    <t>305954497/1</t>
+  </si>
+  <si>
+    <t>305954776/1</t>
+  </si>
+  <si>
+    <t>305954940/1</t>
+  </si>
+  <si>
+    <t>305955001/1</t>
+  </si>
+  <si>
+    <t>305955144/1</t>
+  </si>
+  <si>
+    <t>305955144/2</t>
+  </si>
+  <si>
+    <t>305955144/3</t>
+  </si>
+  <si>
+    <t>306025753/1</t>
+  </si>
+  <si>
+    <t>306025921/1</t>
+  </si>
+  <si>
+    <t>306025992/1</t>
+  </si>
+  <si>
+    <t>306026079/1</t>
+  </si>
+  <si>
+    <t>306026203/1</t>
+  </si>
+  <si>
+    <t>306026622/1</t>
+  </si>
+  <si>
+    <t>306078394/1</t>
+  </si>
+  <si>
+    <t>306078523/1</t>
+  </si>
+  <si>
+    <t>306078528/1</t>
+  </si>
+  <si>
+    <t>306078848/1</t>
+  </si>
+  <si>
+    <t>306078884/1</t>
+  </si>
+  <si>
+    <t>306078931/1</t>
+  </si>
+  <si>
+    <t>306078952/1</t>
+  </si>
+  <si>
+    <t>306078975/1</t>
+  </si>
+  <si>
+    <t>306079051/1</t>
+  </si>
+  <si>
+    <t>306079074/1</t>
+  </si>
+  <si>
+    <t>306079088/1</t>
+  </si>
+  <si>
+    <t>306079088/2</t>
+  </si>
+  <si>
+    <t>306079129/1</t>
+  </si>
+  <si>
+    <t>306079129/2</t>
+  </si>
+  <si>
+    <t>306079202/1</t>
+  </si>
+  <si>
+    <t>306079202/2</t>
+  </si>
+  <si>
+    <t>306146401/1</t>
+  </si>
+  <si>
+    <t>306146401/2</t>
+  </si>
+  <si>
+    <t>306146604/1</t>
+  </si>
+  <si>
+    <t>306146732/1</t>
+  </si>
+  <si>
+    <t>306146793/1</t>
+  </si>
+  <si>
+    <t>306146843/1</t>
+  </si>
+  <si>
+    <t>306146997/1</t>
+  </si>
+  <si>
+    <t>306147012/1</t>
+  </si>
+  <si>
+    <t>306147075/1</t>
+  </si>
+  <si>
+    <t>306180969/1</t>
+  </si>
+  <si>
+    <t>306181305/1</t>
+  </si>
+  <si>
+    <t>306181461/1</t>
+  </si>
+  <si>
+    <t>306226714/1</t>
+  </si>
+  <si>
+    <t>306277511/1</t>
+  </si>
+  <si>
+    <t>306277639/1</t>
+  </si>
+  <si>
+    <t>306334250/1</t>
+  </si>
+  <si>
+    <t>306334375/1</t>
+  </si>
+  <si>
+    <t>159995579538714764</t>
+  </si>
+  <si>
+    <t>202603272600688901</t>
+  </si>
+  <si>
+    <t>202603232600698901</t>
+  </si>
+  <si>
+    <t>202603232600698902</t>
+  </si>
+  <si>
+    <t>202603272600724301</t>
+  </si>
+  <si>
+    <t>202603272600739001</t>
+  </si>
+  <si>
+    <t>202603272600732401</t>
+  </si>
+  <si>
+    <t>202603302600749401</t>
+  </si>
+  <si>
+    <t>202603302600749301</t>
+  </si>
+  <si>
+    <t>202603302600749302</t>
+  </si>
+  <si>
+    <t>202603302600749303</t>
+  </si>
+  <si>
+    <t>202603302600749304</t>
+  </si>
+  <si>
+    <t>202603302600752401</t>
+  </si>
+  <si>
+    <t>202603302600749501</t>
+  </si>
+  <si>
+    <t>202603302600752201</t>
+  </si>
+  <si>
+    <t>202603302600752701</t>
+  </si>
+  <si>
+    <t>202603302600752001</t>
+  </si>
+  <si>
+    <t>202603302600747301</t>
+  </si>
+  <si>
+    <t>202603302600746701</t>
+  </si>
+  <si>
+    <t>202603302600746201</t>
+  </si>
+  <si>
+    <t>202603302600750201</t>
+  </si>
+  <si>
+    <t>202603302600750202</t>
+  </si>
+  <si>
+    <t>202603302600750203</t>
+  </si>
+  <si>
+    <t>202603302600750204</t>
+  </si>
+  <si>
+    <t>202603302600750205</t>
+  </si>
+  <si>
+    <t>202603302600756701</t>
+  </si>
+  <si>
+    <t>202603302600757501</t>
+  </si>
+  <si>
+    <t>202603302600757701</t>
+  </si>
+  <si>
+    <t>202603302600757702</t>
+  </si>
+  <si>
+    <t>202603302600757703</t>
+  </si>
+  <si>
+    <t>202603302600757704</t>
+  </si>
+  <si>
+    <t>202603302600761001</t>
+  </si>
+  <si>
+    <t>202603302600759301</t>
+  </si>
+  <si>
+    <t>202603302600759302</t>
+  </si>
+  <si>
+    <t>202603302600757201</t>
+  </si>
+  <si>
+    <t>202603302600754901</t>
+  </si>
+  <si>
+    <t>202603302600756801</t>
+  </si>
+  <si>
+    <t>202603302600755701</t>
+  </si>
+  <si>
+    <t>202603302600757601</t>
+  </si>
+  <si>
+    <t>202603232600695401</t>
+  </si>
+  <si>
+    <t>202603262600725501</t>
+  </si>
+  <si>
+    <t>202603262600725502</t>
+  </si>
+  <si>
+    <t>202603302600742301</t>
+  </si>
+  <si>
+    <t>202603302600742302</t>
+  </si>
+  <si>
+    <t>202603302600742303</t>
+  </si>
+  <si>
+    <t>202603302600742304</t>
+  </si>
+  <si>
+    <t>202603302600753601</t>
+  </si>
+  <si>
+    <t>202603302600753602</t>
+  </si>
+  <si>
+    <t>202603302600745701</t>
+  </si>
+  <si>
+    <t>202603302600750701</t>
+  </si>
+  <si>
+    <t>202603302600750702</t>
+  </si>
+  <si>
+    <t>202603302600763401</t>
+  </si>
+  <si>
+    <t>202603302600761801</t>
+  </si>
+  <si>
+    <t>202603302600758901</t>
+  </si>
+  <si>
+    <t>159995579538714986</t>
+  </si>
+  <si>
+    <t>159995579538716119</t>
+  </si>
+  <si>
+    <t>159995579538655180</t>
+  </si>
+  <si>
+    <t>159995579538714887</t>
+  </si>
+  <si>
+    <t>159995579538714894</t>
+  </si>
+  <si>
+    <t>159995579538717161</t>
+  </si>
+  <si>
+    <t>159995579538717178</t>
+  </si>
+  <si>
+    <t>159995579538717185</t>
+  </si>
+  <si>
+    <t>159995579538717192</t>
+  </si>
+  <si>
+    <t>159995579538717208</t>
+  </si>
+  <si>
+    <t>159995579538652448</t>
+  </si>
+  <si>
+    <t>159995579538652455</t>
+  </si>
+  <si>
+    <t>159995579538702426</t>
+  </si>
+  <si>
+    <t>159995579538702433</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-QWR4</t>
+  </si>
+  <si>
+    <t>1-2650/2026</t>
+  </si>
+  <si>
+    <t>267004537</t>
+  </si>
+  <si>
+    <t>267004553</t>
+  </si>
+  <si>
+    <t>267004633</t>
+  </si>
+  <si>
+    <t>267004642</t>
+  </si>
+  <si>
+    <t>NFD6-03-20-ZZ2L/XD</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-MZ5H</t>
+  </si>
+  <si>
+    <t>NFD6-03-22-KW7W</t>
+  </si>
+  <si>
+    <t>NFD6-03-25-CX4V</t>
+  </si>
+  <si>
+    <t>NFD6-03-26-GAT8</t>
+  </si>
+  <si>
+    <t>NFD6-03-26-PWPR</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-2ME3</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-8TEL</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-DTTW</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-GJFH</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-HXCH</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-LFWS</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-LNRR</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-T6X9</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-TAJV</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-U6YY</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-YEYP</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-2QQ6</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-8F7Y</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-8RQD</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-8XC2</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-DEVD</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-NA2F</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-S294</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-V9JX</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-WV3M</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-ZXGK</t>
+  </si>
+  <si>
+    <t>NFE6-03-22-W92M</t>
+  </si>
+  <si>
+    <t>NFE6-03-25-ZVXU</t>
+  </si>
+  <si>
+    <t>NFE6-03-27-TF48</t>
+  </si>
+  <si>
+    <t>NFE6-03-28-9QGF</t>
+  </si>
+  <si>
+    <t>NFE6-03-28-DXUP</t>
+  </si>
+  <si>
+    <t>NFE6-03-28-WASB</t>
+  </si>
+  <si>
+    <t>NFE6-03-29-2FKK</t>
+  </si>
+  <si>
+    <t>NFE6-03-29-F33V</t>
+  </si>
+  <si>
+    <t>NFE6-03-29-HQ5U</t>
+  </si>
+  <si>
+    <t>R413857</t>
+  </si>
+  <si>
+    <t>R414280</t>
+  </si>
+  <si>
+    <t>R414431</t>
+  </si>
+  <si>
+    <t>R414687</t>
+  </si>
+  <si>
+    <t>R414723</t>
+  </si>
+  <si>
+    <t>SA26/H001444</t>
+  </si>
+  <si>
+    <t>SA26/H001481</t>
   </si>
 </sst>
 </file>
@@ -405,10 +1233,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -690,7 +1517,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D211"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
@@ -711,17 +1538,23 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D2"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
+      <c r="B3" t="s">
+        <v>133</v>
       </c>
       <c r="C3" t="s">
         <v>113</v>
@@ -729,80 +1562,107 @@
       <c r="D3"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D4"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="B5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D5"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="C6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="B7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="C7" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="B9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="B10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D10"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>15</v>
+      <c r="B12" t="s">
+        <v>142</v>
       </c>
       <c r="C12" t="s">
         <v>113</v>
@@ -810,17 +1670,23 @@
       <c r="D12"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>16</v>
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>143</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D13"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>17</v>
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>144</v>
       </c>
       <c r="C14" t="s">
         <v>113</v>
@@ -828,8 +1694,11 @@
       <c r="D14"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>3</v>
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>145</v>
       </c>
       <c r="C15" t="s">
         <v>113</v>
@@ -837,17 +1706,23 @@
       <c r="D15"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>18</v>
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>146</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D16"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>19</v>
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>147</v>
       </c>
       <c r="C17" t="s">
         <v>113</v>
@@ -855,8 +1730,11 @@
       <c r="D17"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>20</v>
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>148</v>
       </c>
       <c r="C18" t="s">
         <v>113</v>
@@ -864,431 +1742,575 @@
       <c r="D18"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C20" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>151</v>
+      </c>
+      <c r="C21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>152</v>
+      </c>
+      <c r="C22" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" t="s">
+        <v>123</v>
+      </c>
+      <c r="D23"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>21</v>
       </c>
-      <c r="C19" t="s">
-        <v>113</v>
-      </c>
-      <c r="D19"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="B25" t="s">
+        <v>155</v>
+      </c>
+      <c r="C25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" t="s">
+        <v>156</v>
+      </c>
+      <c r="C26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>22</v>
       </c>
-      <c r="C20" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="B27" t="s">
+        <v>157</v>
+      </c>
+      <c r="C27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C28" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>23</v>
       </c>
-      <c r="C21" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="B29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C29" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>24</v>
       </c>
-      <c r="C22" t="s">
-        <v>113</v>
-      </c>
-      <c r="D22"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="B30" t="s">
+        <v>160</v>
+      </c>
+      <c r="C30" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" t="s">
+        <v>161</v>
+      </c>
+      <c r="C31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>25</v>
       </c>
-      <c r="C23" t="s">
-        <v>113</v>
-      </c>
-      <c r="D23"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="B32" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" t="s">
+        <v>125</v>
+      </c>
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>163</v>
+      </c>
+      <c r="C33" t="s">
+        <v>125</v>
+      </c>
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>26</v>
       </c>
-      <c r="C24" t="s">
-        <v>113</v>
-      </c>
-      <c r="D24"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="B34" t="s">
+        <v>164</v>
+      </c>
+      <c r="C34" t="s">
+        <v>124</v>
+      </c>
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>27</v>
       </c>
-      <c r="C25" t="s">
-        <v>113</v>
-      </c>
-      <c r="D25"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="B35" t="s">
+        <v>165</v>
+      </c>
+      <c r="C35" t="s">
+        <v>124</v>
+      </c>
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>28</v>
       </c>
-      <c r="C26" t="s">
-        <v>113</v>
-      </c>
-      <c r="D26"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="B36" t="s">
+        <v>166</v>
+      </c>
+      <c r="C36" t="s">
+        <v>126</v>
+      </c>
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>29</v>
       </c>
-      <c r="C27" t="s">
-        <v>113</v>
-      </c>
-      <c r="D27"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="B37" t="s">
+        <v>167</v>
+      </c>
+      <c r="C37" t="s">
+        <v>120</v>
+      </c>
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>30</v>
       </c>
-      <c r="C28" t="s">
-        <v>113</v>
-      </c>
-      <c r="D28"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="B38" t="s">
+        <v>168</v>
+      </c>
+      <c r="C38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>31</v>
       </c>
-      <c r="C29" t="s">
-        <v>113</v>
-      </c>
-      <c r="D29"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="B39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C39" t="s">
+        <v>127</v>
+      </c>
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>343</v>
+      </c>
+      <c r="B40" t="s">
+        <v>170</v>
+      </c>
+      <c r="C40" t="s">
+        <v>117</v>
+      </c>
+      <c r="D40"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>344</v>
+      </c>
+      <c r="B41" t="s">
+        <v>171</v>
+      </c>
+      <c r="C41" t="s">
+        <v>120</v>
+      </c>
+      <c r="D41"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>345</v>
+      </c>
+      <c r="B42" t="s">
+        <v>172</v>
+      </c>
+      <c r="C42" t="s">
+        <v>128</v>
+      </c>
+      <c r="D42"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>346</v>
+      </c>
+      <c r="B43" t="s">
+        <v>173</v>
+      </c>
+      <c r="C43" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>32</v>
       </c>
-      <c r="C30" t="s">
-        <v>113</v>
-      </c>
-      <c r="D30"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="B44" t="s">
+        <v>174</v>
+      </c>
+      <c r="C44" t="s">
+        <v>129</v>
+      </c>
+      <c r="D44"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>33</v>
       </c>
-      <c r="C31" t="s">
-        <v>113</v>
-      </c>
-      <c r="D31"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="B45" t="s">
+        <v>175</v>
+      </c>
+      <c r="C45" t="s">
+        <v>114</v>
+      </c>
+      <c r="D45"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>34</v>
       </c>
-      <c r="C32" t="s">
-        <v>113</v>
-      </c>
-      <c r="D32"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="B46" t="s">
+        <v>176</v>
+      </c>
+      <c r="C46" t="s">
+        <v>112</v>
+      </c>
+      <c r="D46"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" t="s">
+        <v>177</v>
+      </c>
+      <c r="C47" t="s">
+        <v>114</v>
+      </c>
+      <c r="D47"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>35</v>
       </c>
-      <c r="C33" t="s">
-        <v>113</v>
-      </c>
-      <c r="D33"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" t="s">
-        <v>113</v>
-      </c>
-      <c r="D34"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="B48" t="s">
+        <v>178</v>
+      </c>
+      <c r="C48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D48"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>36</v>
       </c>
-      <c r="C35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D35"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+      <c r="B49" t="s">
+        <v>179</v>
+      </c>
+      <c r="C49" t="s">
+        <v>128</v>
+      </c>
+      <c r="D49"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>36</v>
+      </c>
+      <c r="B50" t="s">
+        <v>180</v>
+      </c>
+      <c r="C50" t="s">
+        <v>128</v>
+      </c>
+      <c r="D50"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51" t="s">
+        <v>181</v>
+      </c>
+      <c r="C51" t="s">
+        <v>128</v>
+      </c>
+      <c r="D51"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>37</v>
       </c>
-      <c r="C36" t="s">
-        <v>113</v>
-      </c>
-      <c r="D36"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+      <c r="B52" t="s">
+        <v>182</v>
+      </c>
+      <c r="C52" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" t="s">
+        <v>183</v>
+      </c>
+      <c r="C53" t="s">
+        <v>126</v>
+      </c>
+      <c r="D53"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>38</v>
       </c>
-      <c r="C37" t="s">
-        <v>113</v>
-      </c>
-      <c r="D37"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="B54" t="s">
+        <v>184</v>
+      </c>
+      <c r="C54" t="s">
+        <v>116</v>
+      </c>
+      <c r="D54"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>39</v>
       </c>
-      <c r="C38" t="s">
-        <v>113</v>
-      </c>
-      <c r="D38"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="B55" t="s">
+        <v>185</v>
+      </c>
+      <c r="C55" t="s">
+        <v>118</v>
+      </c>
+      <c r="D55"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" t="s">
+        <v>186</v>
+      </c>
+      <c r="C56" t="s">
+        <v>118</v>
+      </c>
+      <c r="D56"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>40</v>
       </c>
-      <c r="C39" t="s">
-        <v>113</v>
-      </c>
-      <c r="D39"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="B57" t="s">
+        <v>187</v>
+      </c>
+      <c r="C57" t="s">
+        <v>128</v>
+      </c>
+      <c r="D57"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>41</v>
       </c>
-      <c r="C40" t="s">
-        <v>113</v>
-      </c>
-      <c r="D40"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="B58" t="s">
+        <v>188</v>
+      </c>
+      <c r="C58" t="s">
+        <v>121</v>
+      </c>
+      <c r="D58"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>42</v>
       </c>
-      <c r="C41" t="s">
-        <v>113</v>
-      </c>
-      <c r="D41"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+      <c r="B59" t="s">
+        <v>189</v>
+      </c>
+      <c r="C59" t="s">
+        <v>124</v>
+      </c>
+      <c r="D59"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" t="s">
+        <v>190</v>
+      </c>
+      <c r="C60" t="s">
+        <v>124</v>
+      </c>
+      <c r="D60"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>43</v>
       </c>
-      <c r="C42" t="s">
-        <v>113</v>
-      </c>
-      <c r="D42"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+      <c r="B61" t="s">
+        <v>191</v>
+      </c>
+      <c r="C61" t="s">
+        <v>112</v>
+      </c>
+      <c r="D61"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>44</v>
       </c>
-      <c r="C43" t="s">
-        <v>113</v>
-      </c>
-      <c r="D43"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+      <c r="B62" t="s">
+        <v>192</v>
+      </c>
+      <c r="C62" t="s">
+        <v>112</v>
+      </c>
+      <c r="D62"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>45</v>
       </c>
-      <c r="C44" t="s">
-        <v>113</v>
-      </c>
-      <c r="D44"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+      <c r="B63" t="s">
+        <v>193</v>
+      </c>
+      <c r="C63" t="s">
+        <v>130</v>
+      </c>
+      <c r="D63"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>46</v>
       </c>
-      <c r="C45" t="s">
-        <v>113</v>
-      </c>
-      <c r="D45"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+      <c r="B64" t="s">
+        <v>194</v>
+      </c>
+      <c r="C64" t="s">
+        <v>121</v>
+      </c>
+      <c r="D64"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>47</v>
       </c>
-      <c r="C46" t="s">
-        <v>113</v>
-      </c>
-      <c r="D46"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+      <c r="B65" t="s">
+        <v>195</v>
+      </c>
+      <c r="C65" t="s">
+        <v>115</v>
+      </c>
+      <c r="D65"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>48</v>
       </c>
-      <c r="C47" t="s">
-        <v>113</v>
-      </c>
-      <c r="D47"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C48" t="s">
-        <v>113</v>
-      </c>
-      <c r="D48"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C49" t="s">
-        <v>113</v>
-      </c>
-      <c r="D49"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C50" t="s">
-        <v>113</v>
-      </c>
-      <c r="D50"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C51" t="s">
-        <v>113</v>
-      </c>
-      <c r="D51"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C52" t="s">
-        <v>113</v>
-      </c>
-      <c r="D52"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C53" t="s">
-        <v>113</v>
-      </c>
-      <c r="D53"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" t="s">
-        <v>113</v>
-      </c>
-      <c r="D54"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C55" t="s">
-        <v>113</v>
-      </c>
-      <c r="D55"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56" t="s">
-        <v>113</v>
-      </c>
-      <c r="D56"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" t="s">
-        <v>113</v>
-      </c>
-      <c r="D57"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C58" t="s">
-        <v>113</v>
-      </c>
-      <c r="D58"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C59" t="s">
-        <v>113</v>
-      </c>
-      <c r="D59"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" t="s">
-        <v>113</v>
-      </c>
-      <c r="D60"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C61" t="s">
-        <v>113</v>
-      </c>
-      <c r="D61"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C62" t="s">
-        <v>113</v>
-      </c>
-      <c r="D62"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C63" t="s">
-        <v>113</v>
-      </c>
-      <c r="D63"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C64" t="s">
-        <v>113</v>
-      </c>
-      <c r="D64"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C65" t="s">
-        <v>113</v>
-      </c>
-      <c r="D65"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>67</v>
+      <c r="B66" t="s">
+        <v>196</v>
       </c>
       <c r="C66" t="s">
         <v>113</v>
@@ -1296,439 +2318,1644 @@
       <c r="D66"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>68</v>
+      <c r="A67" t="s">
+        <v>49</v>
+      </c>
+      <c r="B67" t="s">
+        <v>197</v>
       </c>
       <c r="C67" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D67"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>69</v>
+      <c r="A68" t="s">
+        <v>49</v>
+      </c>
+      <c r="B68" t="s">
+        <v>198</v>
       </c>
       <c r="C68" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D68"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>70</v>
+      <c r="A69" t="s">
+        <v>50</v>
+      </c>
+      <c r="B69" t="s">
+        <v>199</v>
       </c>
       <c r="C69" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D69"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>71</v>
+      <c r="A70" t="s">
+        <v>50</v>
+      </c>
+      <c r="B70" t="s">
+        <v>200</v>
       </c>
       <c r="C70" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D70"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>72</v>
+      <c r="A71" t="s">
+        <v>50</v>
+      </c>
+      <c r="B71" t="s">
+        <v>201</v>
       </c>
       <c r="C71" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D71"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>73</v>
+      <c r="A72" t="s">
+        <v>51</v>
+      </c>
+      <c r="B72" t="s">
+        <v>202</v>
       </c>
       <c r="C72" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D72"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>74</v>
+      <c r="A73" t="s">
+        <v>52</v>
+      </c>
+      <c r="B73" t="s">
+        <v>203</v>
       </c>
       <c r="C73" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D73"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>75</v>
+      <c r="A74" t="s">
+        <v>53</v>
+      </c>
+      <c r="B74" t="s">
+        <v>204</v>
       </c>
       <c r="C74" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D74"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>76</v>
+      <c r="A75" t="s">
+        <v>54</v>
+      </c>
+      <c r="B75" t="s">
+        <v>205</v>
       </c>
       <c r="C75" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D75"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>77</v>
+      <c r="A76" t="s">
+        <v>55</v>
+      </c>
+      <c r="B76" t="s">
+        <v>206</v>
       </c>
       <c r="C76" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="D76"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>78</v>
+      <c r="A77" t="s">
+        <v>56</v>
+      </c>
+      <c r="B77" t="s">
+        <v>207</v>
       </c>
       <c r="C77" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="D77"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>79</v>
+      <c r="A78" t="s">
+        <v>57</v>
+      </c>
+      <c r="B78" t="s">
+        <v>208</v>
       </c>
       <c r="C78" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D78"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>80</v>
+      <c r="A79" t="s">
+        <v>57</v>
+      </c>
+      <c r="B79" t="s">
+        <v>209</v>
       </c>
       <c r="C79" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D79"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>81</v>
+      <c r="A80" t="s">
+        <v>57</v>
+      </c>
+      <c r="B80" t="s">
+        <v>210</v>
       </c>
       <c r="C80" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D80"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>82</v>
+      <c r="A81" t="s">
+        <v>58</v>
+      </c>
+      <c r="B81" t="s">
+        <v>211</v>
       </c>
       <c r="C81" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D81"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B82" s="1"/>
+      <c r="A82" t="s">
+        <v>59</v>
+      </c>
+      <c r="B82" t="s">
+        <v>212</v>
+      </c>
       <c r="C82" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D82"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B83" s="1"/>
+      <c r="A83" t="s">
+        <v>60</v>
+      </c>
+      <c r="B83" t="s">
+        <v>213</v>
+      </c>
       <c r="C83" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="D83"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B84" s="1"/>
+      <c r="A84" t="s">
+        <v>60</v>
+      </c>
+      <c r="B84" t="s">
+        <v>214</v>
+      </c>
       <c r="C84" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="D84"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B85" s="1"/>
+      <c r="A85" t="s">
+        <v>61</v>
+      </c>
+      <c r="B85" t="s">
+        <v>215</v>
+      </c>
       <c r="C85" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="D85"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B86" s="1"/>
+      <c r="A86" t="s">
+        <v>62</v>
+      </c>
+      <c r="B86" t="s">
+        <v>216</v>
+      </c>
       <c r="C86" t="s">
         <v>113</v>
       </c>
       <c r="D86"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B87" s="1"/>
+      <c r="A87" t="s">
+        <v>63</v>
+      </c>
+      <c r="B87" t="s">
+        <v>217</v>
+      </c>
       <c r="C87" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="D87"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B88" s="1"/>
+      <c r="A88" t="s">
+        <v>64</v>
+      </c>
+      <c r="B88" t="s">
+        <v>218</v>
+      </c>
       <c r="C88" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D88"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B89" s="1"/>
+      <c r="A89" t="s">
+        <v>64</v>
+      </c>
+      <c r="B89" t="s">
+        <v>219</v>
+      </c>
       <c r="C89" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D89"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B90" s="1"/>
+      <c r="A90" t="s">
+        <v>65</v>
+      </c>
+      <c r="B90" t="s">
+        <v>220</v>
+      </c>
       <c r="C90" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D90"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B91" s="1"/>
+      <c r="A91" t="s">
+        <v>66</v>
+      </c>
+      <c r="B91" t="s">
+        <v>221</v>
+      </c>
       <c r="C91" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D91"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B92" s="1"/>
+      <c r="A92" t="s">
+        <v>67</v>
+      </c>
+      <c r="B92" t="s">
+        <v>222</v>
+      </c>
       <c r="C92" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="D92"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B93" s="1"/>
+      <c r="A93" t="s">
+        <v>68</v>
+      </c>
+      <c r="B93" t="s">
+        <v>223</v>
+      </c>
       <c r="C93" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="D93"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B94" s="1"/>
+      <c r="A94" t="s">
+        <v>69</v>
+      </c>
+      <c r="B94" t="s">
+        <v>224</v>
+      </c>
       <c r="C94" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D94"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B95" s="1"/>
+      <c r="A95" t="s">
+        <v>70</v>
+      </c>
+      <c r="B95" t="s">
+        <v>225</v>
+      </c>
       <c r="C95" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D95"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B96" s="1"/>
+      <c r="A96" t="s">
+        <v>71</v>
+      </c>
+      <c r="B96" t="s">
+        <v>226</v>
+      </c>
       <c r="C96" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D96"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B97" s="1"/>
+      <c r="A97" t="s">
+        <v>72</v>
+      </c>
+      <c r="B97" t="s">
+        <v>227</v>
+      </c>
       <c r="C97" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D97"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B98" s="1"/>
+      <c r="A98" t="s">
+        <v>73</v>
+      </c>
+      <c r="B98" t="s">
+        <v>228</v>
+      </c>
       <c r="C98" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D98"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B99" s="1"/>
+      <c r="A99" t="s">
+        <v>74</v>
+      </c>
+      <c r="B99" t="s">
+        <v>229</v>
+      </c>
       <c r="C99" t="s">
         <v>113</v>
       </c>
       <c r="D99"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B100" s="1"/>
+      <c r="A100" t="s">
+        <v>75</v>
+      </c>
+      <c r="B100" t="s">
+        <v>230</v>
+      </c>
       <c r="C100" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D100"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B101" s="1"/>
+      <c r="A101" t="s">
+        <v>76</v>
+      </c>
+      <c r="B101" t="s">
+        <v>231</v>
+      </c>
       <c r="C101" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D101"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B102" s="1"/>
+      <c r="A102" t="s">
+        <v>76</v>
+      </c>
+      <c r="B102" t="s">
+        <v>232</v>
+      </c>
       <c r="C102" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D102"/>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B103" s="1"/>
+      <c r="A103" t="s">
+        <v>76</v>
+      </c>
+      <c r="B103" t="s">
+        <v>233</v>
+      </c>
       <c r="C103" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D103"/>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B104" s="1"/>
+      <c r="A104" t="s">
+        <v>77</v>
+      </c>
+      <c r="B104" t="s">
+        <v>234</v>
+      </c>
       <c r="C104" t="s">
         <v>113</v>
       </c>
       <c r="D104"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B105" s="1"/>
+      <c r="A105" t="s">
+        <v>78</v>
+      </c>
+      <c r="B105" t="s">
+        <v>235</v>
+      </c>
       <c r="C105" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D105"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B106" s="1"/>
+      <c r="A106" t="s">
+        <v>79</v>
+      </c>
+      <c r="B106" t="s">
+        <v>236</v>
+      </c>
       <c r="C106" t="s">
         <v>113</v>
       </c>
       <c r="D106"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B107" s="1"/>
+      <c r="A107" t="s">
+        <v>80</v>
+      </c>
+      <c r="B107" t="s">
+        <v>237</v>
+      </c>
       <c r="C107" t="s">
         <v>113</v>
       </c>
       <c r="D107"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
+      <c r="A108" t="s">
+        <v>81</v>
+      </c>
+      <c r="B108" t="s">
+        <v>238</v>
+      </c>
+      <c r="C108" t="s">
+        <v>116</v>
+      </c>
+      <c r="D108"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>82</v>
+      </c>
+      <c r="B109" t="s">
+        <v>239</v>
+      </c>
+      <c r="C109" t="s">
+        <v>124</v>
+      </c>
+      <c r="D109"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>83</v>
+      </c>
+      <c r="B110" t="s">
+        <v>240</v>
+      </c>
+      <c r="C110" t="s">
+        <v>112</v>
+      </c>
+      <c r="D110"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>84</v>
+      </c>
+      <c r="B111" t="s">
+        <v>241</v>
+      </c>
+      <c r="C111" t="s">
+        <v>114</v>
+      </c>
+      <c r="D111"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>85</v>
+      </c>
+      <c r="B112" t="s">
+        <v>242</v>
+      </c>
+      <c r="C112" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>86</v>
+      </c>
+      <c r="B113" t="s">
+        <v>243</v>
+      </c>
+      <c r="C113" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>87</v>
+      </c>
+      <c r="B114" t="s">
+        <v>244</v>
+      </c>
+      <c r="C114" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>88</v>
+      </c>
+      <c r="B115" t="s">
+        <v>245</v>
+      </c>
+      <c r="C115" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>89</v>
+      </c>
+      <c r="B116" t="s">
+        <v>246</v>
+      </c>
+      <c r="C116" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>90</v>
+      </c>
+      <c r="B117" t="s">
+        <v>247</v>
+      </c>
+      <c r="C117" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>91</v>
+      </c>
+      <c r="B118" t="s">
+        <v>248</v>
+      </c>
+      <c r="C118" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>92</v>
+      </c>
+      <c r="B119" t="s">
+        <v>249</v>
+      </c>
+      <c r="C119" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>93</v>
+      </c>
+      <c r="B120" t="s">
+        <v>250</v>
+      </c>
+      <c r="C120" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>93</v>
+      </c>
+      <c r="B121" t="s">
+        <v>251</v>
+      </c>
+      <c r="C121" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>94</v>
+      </c>
+      <c r="B122" t="s">
+        <v>252</v>
+      </c>
+      <c r="C122" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>94</v>
+      </c>
+      <c r="B123" t="s">
+        <v>253</v>
+      </c>
+      <c r="C123" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>95</v>
+      </c>
+      <c r="B124" t="s">
+        <v>254</v>
+      </c>
+      <c r="C124" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>95</v>
+      </c>
+      <c r="B125" t="s">
+        <v>255</v>
+      </c>
+      <c r="C125" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>96</v>
+      </c>
+      <c r="B126" t="s">
+        <v>256</v>
+      </c>
+      <c r="C126" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>96</v>
+      </c>
+      <c r="B127" t="s">
+        <v>257</v>
+      </c>
+      <c r="C127" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>97</v>
+      </c>
+      <c r="B128" t="s">
+        <v>258</v>
+      </c>
+      <c r="C128" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>98</v>
+      </c>
+      <c r="B129" t="s">
+        <v>259</v>
+      </c>
+      <c r="C129" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>99</v>
+      </c>
+      <c r="B130" t="s">
+        <v>260</v>
+      </c>
+      <c r="C130" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>100</v>
+      </c>
+      <c r="B131" t="s">
+        <v>261</v>
+      </c>
+      <c r="C131" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>101</v>
+      </c>
+      <c r="B132" t="s">
+        <v>262</v>
+      </c>
+      <c r="C132" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>102</v>
+      </c>
+      <c r="B133" t="s">
+        <v>263</v>
+      </c>
+      <c r="C133" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>103</v>
+      </c>
+      <c r="B134" t="s">
+        <v>264</v>
+      </c>
+      <c r="C134" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>104</v>
+      </c>
+      <c r="B135" t="s">
+        <v>265</v>
+      </c>
+      <c r="C135" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>105</v>
+      </c>
+      <c r="B136" t="s">
+        <v>266</v>
+      </c>
+      <c r="C136" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>106</v>
+      </c>
+      <c r="B137" t="s">
+        <v>267</v>
+      </c>
+      <c r="C137" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>107</v>
+      </c>
+      <c r="B138" t="s">
+        <v>268</v>
+      </c>
+      <c r="C138" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>108</v>
+      </c>
+      <c r="B139" t="s">
+        <v>269</v>
+      </c>
+      <c r="C139" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
         <v>109</v>
       </c>
-      <c r="B108" s="1"/>
-      <c r="C108" t="s">
+      <c r="B140" t="s">
+        <v>270</v>
+      </c>
+      <c r="C140" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>110</v>
+      </c>
+      <c r="B141" t="s">
+        <v>271</v>
+      </c>
+      <c r="C141" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>111</v>
+      </c>
+      <c r="B142" t="s">
+        <v>272</v>
+      </c>
+      <c r="C142" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>347</v>
+      </c>
+      <c r="B143" t="s">
+        <v>273</v>
+      </c>
+      <c r="C143" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>348</v>
+      </c>
+      <c r="B144" t="s">
+        <v>274</v>
+      </c>
+      <c r="C144" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>349</v>
+      </c>
+      <c r="B145" t="s">
+        <v>275</v>
+      </c>
+      <c r="C145" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>349</v>
+      </c>
+      <c r="B146" t="s">
+        <v>276</v>
+      </c>
+      <c r="C146" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>350</v>
+      </c>
+      <c r="B147" t="s">
+        <v>277</v>
+      </c>
+      <c r="C147" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>351</v>
+      </c>
+      <c r="B148" t="s">
+        <v>278</v>
+      </c>
+      <c r="C148" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>352</v>
+      </c>
+      <c r="B149" t="s">
+        <v>279</v>
+      </c>
+      <c r="C149" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>353</v>
+      </c>
+      <c r="B150" t="s">
+        <v>280</v>
+      </c>
+      <c r="C150" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>354</v>
+      </c>
+      <c r="B151" t="s">
+        <v>281</v>
+      </c>
+      <c r="C151" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>354</v>
+      </c>
+      <c r="B152" t="s">
+        <v>282</v>
+      </c>
+      <c r="C152" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>354</v>
+      </c>
+      <c r="B153" t="s">
+        <v>283</v>
+      </c>
+      <c r="C153" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>354</v>
+      </c>
+      <c r="B154" t="s">
+        <v>284</v>
+      </c>
+      <c r="C154" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>355</v>
+      </c>
+      <c r="B155" t="s">
+        <v>285</v>
+      </c>
+      <c r="C155" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>356</v>
+      </c>
+      <c r="B156" t="s">
+        <v>286</v>
+      </c>
+      <c r="C156" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>357</v>
+      </c>
+      <c r="B157" t="s">
+        <v>287</v>
+      </c>
+      <c r="C157" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>358</v>
+      </c>
+      <c r="B158" t="s">
+        <v>288</v>
+      </c>
+      <c r="C158" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>359</v>
+      </c>
+      <c r="B159" t="s">
+        <v>289</v>
+      </c>
+      <c r="C159" t="s">
         <v>113</v>
       </c>
-      <c r="D108"/>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B109" s="1"/>
-      <c r="C109" t="s">
-        <v>113</v>
-      </c>
-      <c r="D109"/>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B110" s="1"/>
-      <c r="C110" t="s">
-        <v>113</v>
-      </c>
-      <c r="D110"/>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>360</v>
+      </c>
+      <c r="B160" t="s">
+        <v>290</v>
+      </c>
+      <c r="C160" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>361</v>
+      </c>
+      <c r="B161" t="s">
+        <v>291</v>
+      </c>
+      <c r="C161" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>362</v>
+      </c>
+      <c r="B162" t="s">
+        <v>292</v>
+      </c>
+      <c r="C162" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>363</v>
+      </c>
+      <c r="B163" t="s">
+        <v>293</v>
+      </c>
+      <c r="C163" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>363</v>
+      </c>
+      <c r="B164" t="s">
+        <v>294</v>
+      </c>
+      <c r="C164" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>363</v>
+      </c>
+      <c r="B165" t="s">
+        <v>295</v>
+      </c>
+      <c r="C165" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>363</v>
+      </c>
+      <c r="B166" t="s">
+        <v>296</v>
+      </c>
+      <c r="C166" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>363</v>
+      </c>
+      <c r="B167" t="s">
+        <v>297</v>
+      </c>
+      <c r="C167" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>364</v>
+      </c>
+      <c r="B168" t="s">
+        <v>298</v>
+      </c>
+      <c r="C168" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>365</v>
+      </c>
+      <c r="B169" t="s">
+        <v>299</v>
+      </c>
+      <c r="C169" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>366</v>
+      </c>
+      <c r="B170" t="s">
+        <v>300</v>
+      </c>
+      <c r="C170" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>366</v>
+      </c>
+      <c r="B171" t="s">
+        <v>301</v>
+      </c>
+      <c r="C171" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>366</v>
+      </c>
+      <c r="B172" t="s">
+        <v>302</v>
+      </c>
+      <c r="C172" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>366</v>
+      </c>
+      <c r="B173" t="s">
+        <v>303</v>
+      </c>
+      <c r="C173" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>367</v>
+      </c>
+      <c r="B174" t="s">
+        <v>304</v>
+      </c>
+      <c r="C174" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>368</v>
+      </c>
+      <c r="B175" t="s">
+        <v>305</v>
+      </c>
+      <c r="C175" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>368</v>
+      </c>
+      <c r="B176" t="s">
+        <v>306</v>
+      </c>
+      <c r="C176" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>369</v>
+      </c>
+      <c r="B177" t="s">
+        <v>307</v>
+      </c>
+      <c r="C177" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>370</v>
+      </c>
+      <c r="B178" t="s">
+        <v>308</v>
+      </c>
+      <c r="C178" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>371</v>
+      </c>
+      <c r="B179" t="s">
+        <v>309</v>
+      </c>
+      <c r="C179" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>372</v>
+      </c>
+      <c r="B180" t="s">
+        <v>310</v>
+      </c>
+      <c r="C180" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>373</v>
+      </c>
+      <c r="B181" t="s">
+        <v>311</v>
+      </c>
+      <c r="C181" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>374</v>
+      </c>
+      <c r="B182" t="s">
+        <v>312</v>
+      </c>
+      <c r="C182" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>375</v>
+      </c>
+      <c r="B183" t="s">
+        <v>313</v>
+      </c>
+      <c r="C183" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>375</v>
+      </c>
+      <c r="B184" t="s">
+        <v>314</v>
+      </c>
+      <c r="C184" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>376</v>
+      </c>
+      <c r="B185" t="s">
+        <v>315</v>
+      </c>
+      <c r="C185" t="s">
         <v>112</v>
       </c>
-      <c r="B111" s="1"/>
-      <c r="C111" t="s">
-        <v>113</v>
-      </c>
-      <c r="D111"/>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>376</v>
+      </c>
+      <c r="B186" t="s">
+        <v>316</v>
+      </c>
+      <c r="C186" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>376</v>
+      </c>
+      <c r="B187" t="s">
+        <v>317</v>
+      </c>
+      <c r="C187" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>376</v>
+      </c>
+      <c r="B188" t="s">
+        <v>318</v>
+      </c>
+      <c r="C188" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>377</v>
+      </c>
+      <c r="B189" t="s">
+        <v>319</v>
+      </c>
+      <c r="C189" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>377</v>
+      </c>
+      <c r="B190" t="s">
+        <v>320</v>
+      </c>
+      <c r="C190" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>378</v>
+      </c>
+      <c r="B191" t="s">
+        <v>321</v>
+      </c>
+      <c r="C191" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>379</v>
+      </c>
+      <c r="B192" t="s">
+        <v>322</v>
+      </c>
+      <c r="C192" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>379</v>
+      </c>
+      <c r="B193" t="s">
+        <v>323</v>
+      </c>
+      <c r="C193" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>380</v>
+      </c>
+      <c r="B194" t="s">
+        <v>324</v>
+      </c>
+      <c r="C194" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>381</v>
+      </c>
+      <c r="B195" t="s">
+        <v>325</v>
+      </c>
+      <c r="C195" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>382</v>
+      </c>
+      <c r="B196" t="s">
+        <v>326</v>
+      </c>
+      <c r="C196" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>383</v>
+      </c>
+      <c r="B197" t="s">
+        <v>327</v>
+      </c>
+      <c r="C197" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>384</v>
+      </c>
+      <c r="B198" t="s">
+        <v>328</v>
+      </c>
+      <c r="C198" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>385</v>
+      </c>
+      <c r="B199" t="s">
+        <v>329</v>
+      </c>
+      <c r="C199" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>386</v>
+      </c>
+      <c r="B200" t="s">
+        <v>330</v>
+      </c>
+      <c r="C200" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>386</v>
+      </c>
+      <c r="B201" t="s">
+        <v>331</v>
+      </c>
+      <c r="C201" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>387</v>
+      </c>
+      <c r="B202" t="s">
+        <v>332</v>
+      </c>
+      <c r="C202" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>387</v>
+      </c>
+      <c r="B203" t="s">
+        <v>333</v>
+      </c>
+      <c r="C203" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>387</v>
+      </c>
+      <c r="B204" t="s">
+        <v>334</v>
+      </c>
+      <c r="C204" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>387</v>
+      </c>
+      <c r="B205" t="s">
+        <v>335</v>
+      </c>
+      <c r="C205" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>387</v>
+      </c>
+      <c r="B206" t="s">
+        <v>336</v>
+      </c>
+      <c r="C206" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>388</v>
+      </c>
+      <c r="B207" t="s">
+        <v>337</v>
+      </c>
+      <c r="C207" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>388</v>
+      </c>
+      <c r="B208" t="s">
+        <v>338</v>
+      </c>
+      <c r="C208" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>389</v>
+      </c>
+      <c r="B209" t="s">
+        <v>339</v>
+      </c>
+      <c r="C209" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>389</v>
+      </c>
+      <c r="B210" t="s">
+        <v>340</v>
+      </c>
+      <c r="C210" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>341</v>
+      </c>
+      <c r="B211" t="s">
+        <v>341</v>
+      </c>
+      <c r="C211" t="s">
+        <v>130</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="C1" xr:uid="{66E3D377-5F1B-48CD-A9ED-4AF810829D06}"/>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352AB7B0-E907-4906-86A1-47FDAE07510C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31ED316F-978E-443B-B7FC-B6468B2FA782}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="258">
   <si>
     <t>UTK</t>
   </si>
@@ -297,7 +297,511 @@
     <t>99002333</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>1-2858/2026</t>
+  </si>
+  <si>
+    <t>2026/04430</t>
+  </si>
+  <si>
+    <t>267004961</t>
+  </si>
+  <si>
+    <t>NFD6-03-31-EEFN</t>
+  </si>
+  <si>
+    <t>NFD6-04-07-5GR8</t>
+  </si>
+  <si>
+    <t>NFD6-04-07-8F7R</t>
+  </si>
+  <si>
+    <t>NFD6-04-07-GKGL</t>
+  </si>
+  <si>
+    <t>NFD6-04-07-UNT7</t>
+  </si>
+  <si>
+    <t>NFD6-04-07-YB8U</t>
+  </si>
+  <si>
+    <t>NFD6-04-08-7N88</t>
+  </si>
+  <si>
+    <t>NFD6-04-08-BV6F</t>
+  </si>
+  <si>
+    <t>NFD6-04-08-EX7U</t>
+  </si>
+  <si>
+    <t>NFD6-04-08-LKEQ</t>
+  </si>
+  <si>
+    <t>NFD6-04-08-RX93</t>
+  </si>
+  <si>
+    <t>NFE6-04-07-3YQP</t>
+  </si>
+  <si>
+    <t>NFE6-04-07-K4EQ</t>
+  </si>
+  <si>
+    <t>NFE6-04-08-36J8</t>
+  </si>
+  <si>
+    <t>159995579538885747</t>
+  </si>
+  <si>
+    <t>159995579538943201</t>
+  </si>
+  <si>
+    <t>159995579538943218</t>
+  </si>
+  <si>
+    <t>69d652975cef447acab8b52b</t>
+  </si>
+  <si>
+    <t>69cd3d8b5cef447acab85d32</t>
+  </si>
+  <si>
+    <t>69d610005cef447acab8aa15</t>
+  </si>
+  <si>
+    <t>69d4b40c5cef447acab88d78</t>
+  </si>
+  <si>
+    <t>69cfe1bd5cef447acab87746</t>
+  </si>
+  <si>
+    <t>69cfe1bd5cef447acab87749</t>
+  </si>
+  <si>
+    <t>69d225d45cef447acab882dd</t>
+  </si>
+  <si>
+    <t>69d403fb5cef447acab88a4c</t>
+  </si>
+  <si>
+    <t>69d504c25cef447acab89c8f</t>
+  </si>
+  <si>
+    <t>69d61ed15cef447acab8aca9</t>
+  </si>
+  <si>
+    <t>69d67da35cef447acab8bad0</t>
+  </si>
+  <si>
+    <t>69d77b7f5cef447acab8c723</t>
+  </si>
+  <si>
+    <t>69d512ad5cef447acab89f05</t>
+  </si>
+  <si>
+    <t>69d520b85cef447acab8a119</t>
+  </si>
+  <si>
+    <t>69d51af75cef447acab8a050</t>
+  </si>
+  <si>
+    <t>69d526975cef447acab8a1e0</t>
+  </si>
+  <si>
+    <t>69d5316b5cef447acab8a30b</t>
+  </si>
+  <si>
+    <t>69d5316b5cef447acab8a30c</t>
+  </si>
+  <si>
+    <t>69d543e25cef447acab8a444</t>
+  </si>
+  <si>
+    <t>69d548915cef447acab8a480</t>
+  </si>
+  <si>
+    <t>69d553165cef447acab8a4f2</t>
+  </si>
+  <si>
+    <t>69d553165cef447acab8a4f3</t>
+  </si>
+  <si>
+    <t>69d578985cef447acab8a5a8</t>
+  </si>
+  <si>
+    <t>69d604105cef447acab8a802</t>
+  </si>
+  <si>
+    <t>69d64cb55cef447acab8b40d</t>
+  </si>
+  <si>
+    <t>69d64cb55cef447acab8b40f</t>
+  </si>
+  <si>
+    <t>69d64cde5cef447acab8b431</t>
+  </si>
+  <si>
+    <t>69d662f85cef447acab8b7c9</t>
+  </si>
+  <si>
+    <t>69d66a015cef447acab8b8df</t>
+  </si>
+  <si>
+    <t>69d5b6c25cef447acab8a5d7</t>
+  </si>
+  <si>
+    <t>69d6599b5cef447acab8b667</t>
+  </si>
+  <si>
+    <t>69d6599b5cef447acab8b668</t>
+  </si>
+  <si>
+    <t>69d6887e5cef447acab8bbcd</t>
+  </si>
+  <si>
+    <t>69d77b785cef447acab8c71e</t>
+  </si>
+  <si>
+    <t>69d77b785cef447acab8c720</t>
+  </si>
+  <si>
+    <t>69d77bcc5cef447acab8c745</t>
+  </si>
+  <si>
+    <t>69d77b6f5cef447acab8c71b</t>
+  </si>
+  <si>
+    <t>69d77b8e5cef447acab8c72a</t>
+  </si>
+  <si>
+    <t>69d77b995cef447acab8c72d</t>
+  </si>
+  <si>
+    <t>69d779e45cef447acab8c6c8</t>
+  </si>
+  <si>
+    <t>FIZZ-1000865185</t>
+  </si>
+  <si>
+    <t>304065244/1</t>
+  </si>
+  <si>
+    <t>305514971/1</t>
+  </si>
+  <si>
+    <t>305514971/2</t>
+  </si>
+  <si>
+    <t>305514971/3</t>
+  </si>
+  <si>
+    <t>306276867/1</t>
+  </si>
+  <si>
+    <t>306276867/2</t>
+  </si>
+  <si>
+    <t>306621355/1</t>
+  </si>
+  <si>
+    <t>306721122/1</t>
+  </si>
+  <si>
+    <t>306721122/2</t>
+  </si>
+  <si>
+    <t>306721122/3</t>
+  </si>
+  <si>
+    <t>306721194/1</t>
+  </si>
+  <si>
+    <t>306721577/1</t>
+  </si>
+  <si>
+    <t>306721577/2</t>
+  </si>
+  <si>
+    <t>306721577/3</t>
+  </si>
+  <si>
+    <t>306766315/1</t>
+  </si>
+  <si>
+    <t>306891106/1</t>
+  </si>
+  <si>
+    <t>306891106/2</t>
+  </si>
+  <si>
+    <t>306891149/1</t>
+  </si>
+  <si>
+    <t>306891149/2</t>
+  </si>
+  <si>
+    <t>306891149/3</t>
+  </si>
+  <si>
+    <t>306949074/1</t>
+  </si>
+  <si>
+    <t>306949074/2</t>
+  </si>
+  <si>
+    <t>306949074/3</t>
+  </si>
+  <si>
+    <t>306949363/1</t>
+  </si>
+  <si>
+    <t>306949363/2</t>
+  </si>
+  <si>
+    <t>307015937/1</t>
+  </si>
+  <si>
+    <t>307080919/1</t>
+  </si>
+  <si>
+    <t>307081059/1</t>
+  </si>
+  <si>
+    <t>307081059/2</t>
+  </si>
+  <si>
+    <t>307081059/3</t>
+  </si>
+  <si>
+    <t>307081532/1</t>
+  </si>
+  <si>
+    <t>307081532/2</t>
+  </si>
+  <si>
+    <t>307141490/1</t>
+  </si>
+  <si>
+    <t>307141507/1</t>
+  </si>
+  <si>
+    <t>307141507/2</t>
+  </si>
+  <si>
+    <t>307141586/1</t>
+  </si>
+  <si>
+    <t>307141586/2</t>
+  </si>
+  <si>
+    <t>307141586/3</t>
+  </si>
+  <si>
+    <t>307141716/1</t>
+  </si>
+  <si>
+    <t>307141716/2</t>
+  </si>
+  <si>
+    <t>307141891/1</t>
+  </si>
+  <si>
+    <t>307197669/1</t>
+  </si>
+  <si>
+    <t>307197779/1</t>
+  </si>
+  <si>
+    <t>307197880/1</t>
+  </si>
+  <si>
+    <t>307198088/1</t>
+  </si>
+  <si>
+    <t>307237812/1</t>
+  </si>
+  <si>
+    <t>307237812/2</t>
+  </si>
+  <si>
+    <t>307237837/1</t>
+  </si>
+  <si>
+    <t>307237999/1</t>
+  </si>
+  <si>
+    <t>307238407/1</t>
+  </si>
+  <si>
+    <t>307238455/1</t>
+  </si>
+  <si>
+    <t>307278702/1</t>
+  </si>
+  <si>
+    <t>307278970/1</t>
+  </si>
+  <si>
+    <t>307279018/1</t>
+  </si>
+  <si>
+    <t>307279166/1</t>
+  </si>
+  <si>
+    <t>307279464/1</t>
+  </si>
+  <si>
+    <t>307279511/1</t>
+  </si>
+  <si>
+    <t>307342887/1</t>
+  </si>
+  <si>
+    <t>307342965/1</t>
+  </si>
+  <si>
+    <t>307343270/1</t>
+  </si>
+  <si>
+    <t>307343363/1</t>
+  </si>
+  <si>
+    <t>307343487/1</t>
+  </si>
+  <si>
+    <t>307343616/1</t>
+  </si>
+  <si>
+    <t>307343670/1</t>
+  </si>
+  <si>
+    <t>307343706/1</t>
+  </si>
+  <si>
+    <t>307378951/1</t>
+  </si>
+  <si>
+    <t>307379247/1</t>
+  </si>
+  <si>
+    <t>307379284/1</t>
+  </si>
+  <si>
+    <t>307379364/1</t>
+  </si>
+  <si>
+    <t>307379471/1</t>
+  </si>
+  <si>
+    <t>307379557/1</t>
+  </si>
+  <si>
+    <t>307426993/1</t>
+  </si>
+  <si>
+    <t>99002333/1</t>
+  </si>
+  <si>
+    <t>202604092600773501</t>
+  </si>
+  <si>
+    <t>202604082600806701</t>
+  </si>
+  <si>
+    <t>202604082600812301</t>
+  </si>
+  <si>
+    <t>202604082600812302</t>
+  </si>
+  <si>
+    <t>202604082600807101</t>
+  </si>
+  <si>
+    <t>202604082600807102</t>
+  </si>
+  <si>
+    <t>202604082600807701</t>
+  </si>
+  <si>
+    <t>202604082600809101</t>
+  </si>
+  <si>
+    <t>202604092600821201</t>
+  </si>
+  <si>
+    <t>202604092600822501</t>
+  </si>
+  <si>
+    <t>202604092600822901</t>
+  </si>
+  <si>
+    <t>202604092600823601</t>
+  </si>
+  <si>
+    <t>202604092600823201</t>
+  </si>
+  <si>
+    <t>202604072600813302</t>
+  </si>
+  <si>
+    <t>202604082600813301</t>
+  </si>
+  <si>
+    <t>202604082600813901</t>
+  </si>
+  <si>
+    <t>202604092600823501</t>
+  </si>
+  <si>
+    <t>202604092600823502</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>SZ-827</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>SZ-840</t>
   </si>
 </sst>
 </file>
@@ -333,10 +837,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -618,10 +1121,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D136"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="1"/>
@@ -639,778 +1142,1575 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D3"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D4"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D5"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="B6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" t="s">
+        <v>241</v>
+      </c>
+      <c r="D6"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="B7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D7"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" t="s">
+        <v>245</v>
+      </c>
+      <c r="D8"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="C6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="B9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D9"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D10"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="C7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="B11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" t="s">
+        <v>244</v>
+      </c>
+      <c r="D11"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>3</v>
       </c>
-      <c r="C8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="B12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" t="s">
+        <v>242</v>
+      </c>
+      <c r="D12"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>11</v>
       </c>
-      <c r="C9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" t="s">
+        <v>247</v>
+      </c>
+      <c r="D13"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>4</v>
       </c>
-      <c r="C10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="B14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" t="s">
+        <v>248</v>
+      </c>
+      <c r="D14"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>12</v>
       </c>
-      <c r="C11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="B15" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" t="s">
+        <v>249</v>
+      </c>
+      <c r="D15"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>13</v>
       </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" t="s">
+        <v>250</v>
+      </c>
+      <c r="D16"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>14</v>
       </c>
-      <c r="C13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" t="s">
+        <v>251</v>
+      </c>
+      <c r="D17"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>15</v>
       </c>
-      <c r="C14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="B18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" t="s">
+        <v>246</v>
+      </c>
+      <c r="D18"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>16</v>
       </c>
-      <c r="C15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="B19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" t="s">
+        <v>252</v>
+      </c>
+      <c r="D19"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>17</v>
       </c>
-      <c r="C16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="B20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" t="s">
+        <v>243</v>
+      </c>
+      <c r="D20"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>18</v>
       </c>
-      <c r="C17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="B21" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" t="s">
+        <v>244</v>
+      </c>
+      <c r="D21"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" t="s">
+        <v>244</v>
+      </c>
+      <c r="D22"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>19</v>
       </c>
-      <c r="C18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="B23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" t="s">
+        <v>253</v>
+      </c>
+      <c r="D23"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>20</v>
       </c>
-      <c r="C19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="B24" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" t="s">
+        <v>252</v>
+      </c>
+      <c r="D24"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>21</v>
       </c>
-      <c r="C20" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="B25" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" t="s">
+        <v>245</v>
+      </c>
+      <c r="D25"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" t="s">
+        <v>245</v>
+      </c>
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>22</v>
       </c>
-      <c r="C21" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="B27" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" t="s">
+        <v>242</v>
+      </c>
+      <c r="D27"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>23</v>
       </c>
-      <c r="C22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="B28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" t="s">
+        <v>251</v>
+      </c>
+      <c r="D28"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>24</v>
       </c>
-      <c r="C23" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="B29" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" t="s">
+        <v>250</v>
+      </c>
+      <c r="D29"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" t="s">
+        <v>250</v>
+      </c>
+      <c r="D30"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>25</v>
       </c>
-      <c r="C24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D24"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="B31" t="s">
+        <v>135</v>
+      </c>
+      <c r="C31" t="s">
+        <v>241</v>
+      </c>
+      <c r="D31"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>26</v>
       </c>
-      <c r="C25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D25"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="B32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" t="s">
+        <v>250</v>
+      </c>
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>27</v>
       </c>
-      <c r="C26" t="s">
-        <v>89</v>
-      </c>
-      <c r="D26"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="B33" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" t="s">
+        <v>246</v>
+      </c>
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>28</v>
       </c>
-      <c r="C27" t="s">
-        <v>89</v>
-      </c>
-      <c r="D27"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="B34" t="s">
+        <v>138</v>
+      </c>
+      <c r="C34" t="s">
+        <v>251</v>
+      </c>
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>29</v>
       </c>
-      <c r="C28" t="s">
-        <v>89</v>
-      </c>
-      <c r="D28"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="B35" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" t="s">
+        <v>248</v>
+      </c>
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" t="s">
+        <v>248</v>
+      </c>
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>30</v>
       </c>
-      <c r="C29" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="B37" t="s">
+        <v>141</v>
+      </c>
+      <c r="C37" t="s">
+        <v>254</v>
+      </c>
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>31</v>
       </c>
-      <c r="C30" t="s">
-        <v>89</v>
-      </c>
-      <c r="D30"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="B38" t="s">
+        <v>142</v>
+      </c>
+      <c r="C38" t="s">
+        <v>243</v>
+      </c>
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39" t="s">
+        <v>143</v>
+      </c>
+      <c r="C39" t="s">
+        <v>243</v>
+      </c>
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>32</v>
       </c>
-      <c r="C31" t="s">
-        <v>89</v>
-      </c>
-      <c r="D31"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="B40" t="s">
+        <v>144</v>
+      </c>
+      <c r="C40" t="s">
+        <v>253</v>
+      </c>
+      <c r="D40"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>33</v>
       </c>
-      <c r="C32" t="s">
-        <v>89</v>
-      </c>
-      <c r="D32"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="B41" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" t="s">
+        <v>255</v>
+      </c>
+      <c r="D41"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>34</v>
       </c>
-      <c r="C33" t="s">
-        <v>89</v>
-      </c>
-      <c r="D33"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="B42" t="s">
+        <v>146</v>
+      </c>
+      <c r="C42" t="s">
+        <v>241</v>
+      </c>
+      <c r="D42"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>35</v>
       </c>
-      <c r="C34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D34"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="B43" t="s">
+        <v>147</v>
+      </c>
+      <c r="C43" t="s">
+        <v>243</v>
+      </c>
+      <c r="D43"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>36</v>
       </c>
-      <c r="C35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D35"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+      <c r="B44" t="s">
+        <v>148</v>
+      </c>
+      <c r="C44" t="s">
+        <v>241</v>
+      </c>
+      <c r="D44"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>91</v>
+      </c>
+      <c r="B45" t="s">
+        <v>149</v>
+      </c>
+      <c r="C45" t="s">
+        <v>256</v>
+      </c>
+      <c r="D45"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>37</v>
       </c>
-      <c r="C36" t="s">
-        <v>89</v>
-      </c>
-      <c r="D36"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+      <c r="B46" t="s">
+        <v>150</v>
+      </c>
+      <c r="C46" t="s">
+        <v>245</v>
+      </c>
+      <c r="D46"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>38</v>
       </c>
-      <c r="C37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D37"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="B47" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47" t="s">
+        <v>247</v>
+      </c>
+      <c r="D47"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" t="s">
+        <v>152</v>
+      </c>
+      <c r="C48" t="s">
+        <v>247</v>
+      </c>
+      <c r="D48"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" t="s">
+        <v>153</v>
+      </c>
+      <c r="C49" t="s">
+        <v>247</v>
+      </c>
+      <c r="D49"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>39</v>
       </c>
-      <c r="C38" t="s">
-        <v>89</v>
-      </c>
-      <c r="D38"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="B50" t="s">
+        <v>154</v>
+      </c>
+      <c r="C50" t="s">
+        <v>247</v>
+      </c>
+      <c r="D50"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" t="s">
+        <v>155</v>
+      </c>
+      <c r="C51" t="s">
+        <v>247</v>
+      </c>
+      <c r="D51"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>40</v>
       </c>
-      <c r="C39" t="s">
-        <v>89</v>
-      </c>
-      <c r="D39"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="B52" t="s">
+        <v>156</v>
+      </c>
+      <c r="C52" t="s">
+        <v>246</v>
+      </c>
+      <c r="D52"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>41</v>
       </c>
-      <c r="C40" t="s">
-        <v>89</v>
-      </c>
-      <c r="D40"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="B53" t="s">
+        <v>157</v>
+      </c>
+      <c r="C53" t="s">
+        <v>241</v>
+      </c>
+      <c r="D53"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>41</v>
+      </c>
+      <c r="B54" t="s">
+        <v>158</v>
+      </c>
+      <c r="C54" t="s">
+        <v>241</v>
+      </c>
+      <c r="D54"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" t="s">
+        <v>159</v>
+      </c>
+      <c r="C55" t="s">
+        <v>241</v>
+      </c>
+      <c r="D55"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>42</v>
       </c>
-      <c r="C41" t="s">
-        <v>89</v>
-      </c>
-      <c r="D41"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+      <c r="B56" t="s">
+        <v>160</v>
+      </c>
+      <c r="C56" t="s">
+        <v>255</v>
+      </c>
+      <c r="D56"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>43</v>
       </c>
-      <c r="C42" t="s">
-        <v>89</v>
-      </c>
-      <c r="D42"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+      <c r="B57" t="s">
+        <v>161</v>
+      </c>
+      <c r="C57" t="s">
+        <v>245</v>
+      </c>
+      <c r="D57"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" t="s">
+        <v>162</v>
+      </c>
+      <c r="C58" t="s">
+        <v>245</v>
+      </c>
+      <c r="D58"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" t="s">
+        <v>163</v>
+      </c>
+      <c r="C59" t="s">
+        <v>245</v>
+      </c>
+      <c r="D59"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>44</v>
       </c>
-      <c r="C43" t="s">
-        <v>89</v>
-      </c>
-      <c r="D43"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+      <c r="B60" t="s">
+        <v>164</v>
+      </c>
+      <c r="C60" t="s">
+        <v>242</v>
+      </c>
+      <c r="D60"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>45</v>
       </c>
-      <c r="C44" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+      <c r="B61" t="s">
+        <v>165</v>
+      </c>
+      <c r="C61" t="s">
+        <v>254</v>
+      </c>
+      <c r="D61"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" t="s">
+        <v>166</v>
+      </c>
+      <c r="C62" t="s">
+        <v>254</v>
+      </c>
+      <c r="D62"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>46</v>
       </c>
-      <c r="C45" t="s">
-        <v>89</v>
-      </c>
-      <c r="D45"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+      <c r="B63" t="s">
+        <v>167</v>
+      </c>
+      <c r="C63" t="s">
+        <v>253</v>
+      </c>
+      <c r="D63"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>46</v>
+      </c>
+      <c r="B64" t="s">
+        <v>168</v>
+      </c>
+      <c r="C64" t="s">
+        <v>253</v>
+      </c>
+      <c r="D64"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>46</v>
+      </c>
+      <c r="B65" t="s">
+        <v>169</v>
+      </c>
+      <c r="C65" t="s">
+        <v>253</v>
+      </c>
+      <c r="D65"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>47</v>
       </c>
-      <c r="C46" t="s">
-        <v>89</v>
-      </c>
-      <c r="D46"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+      <c r="B66" t="s">
+        <v>170</v>
+      </c>
+      <c r="C66" t="s">
+        <v>255</v>
+      </c>
+      <c r="D66"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>47</v>
+      </c>
+      <c r="B67" t="s">
+        <v>171</v>
+      </c>
+      <c r="C67" t="s">
+        <v>255</v>
+      </c>
+      <c r="D67"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>47</v>
+      </c>
+      <c r="B68" t="s">
+        <v>172</v>
+      </c>
+      <c r="C68" t="s">
+        <v>255</v>
+      </c>
+      <c r="D68"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>48</v>
       </c>
-      <c r="C47" t="s">
-        <v>89</v>
-      </c>
-      <c r="D47"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+      <c r="B69" t="s">
+        <v>173</v>
+      </c>
+      <c r="C69" t="s">
+        <v>251</v>
+      </c>
+      <c r="D69"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>48</v>
+      </c>
+      <c r="B70" t="s">
+        <v>174</v>
+      </c>
+      <c r="C70" t="s">
+        <v>251</v>
+      </c>
+      <c r="D70"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>49</v>
       </c>
-      <c r="C48" t="s">
-        <v>89</v>
-      </c>
-      <c r="D48"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+      <c r="B71" t="s">
+        <v>175</v>
+      </c>
+      <c r="C71" t="s">
+        <v>244</v>
+      </c>
+      <c r="D71"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>50</v>
       </c>
-      <c r="C49" t="s">
-        <v>89</v>
-      </c>
-      <c r="D49"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+      <c r="B72" t="s">
+        <v>176</v>
+      </c>
+      <c r="C72" t="s">
+        <v>246</v>
+      </c>
+      <c r="D72"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>51</v>
       </c>
-      <c r="C50" t="s">
-        <v>89</v>
-      </c>
-      <c r="D50"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
+      <c r="B73" t="s">
+        <v>177</v>
+      </c>
+      <c r="C73" t="s">
+        <v>255</v>
+      </c>
+      <c r="D73"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>51</v>
+      </c>
+      <c r="B74" t="s">
+        <v>178</v>
+      </c>
+      <c r="C74" t="s">
+        <v>255</v>
+      </c>
+      <c r="D74"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>51</v>
+      </c>
+      <c r="B75" t="s">
+        <v>179</v>
+      </c>
+      <c r="C75" t="s">
+        <v>255</v>
+      </c>
+      <c r="D75"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>52</v>
       </c>
-      <c r="C51" t="s">
-        <v>89</v>
-      </c>
-      <c r="D51"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+      <c r="B76" t="s">
+        <v>180</v>
+      </c>
+      <c r="C76" t="s">
+        <v>247</v>
+      </c>
+      <c r="D76"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>52</v>
+      </c>
+      <c r="B77" t="s">
+        <v>181</v>
+      </c>
+      <c r="C77" t="s">
+        <v>247</v>
+      </c>
+      <c r="D77"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>53</v>
       </c>
-      <c r="C52" t="s">
-        <v>89</v>
-      </c>
-      <c r="D52"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
+      <c r="B78" t="s">
+        <v>182</v>
+      </c>
+      <c r="C78" t="s">
+        <v>252</v>
+      </c>
+      <c r="D78"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>54</v>
       </c>
-      <c r="C53" t="s">
-        <v>89</v>
-      </c>
-      <c r="D53"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
+      <c r="B79" t="s">
+        <v>183</v>
+      </c>
+      <c r="C79" t="s">
+        <v>244</v>
+      </c>
+      <c r="D79"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>54</v>
+      </c>
+      <c r="B80" t="s">
+        <v>184</v>
+      </c>
+      <c r="C80" t="s">
+        <v>244</v>
+      </c>
+      <c r="D80"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>55</v>
       </c>
-      <c r="C54" t="s">
-        <v>89</v>
-      </c>
-      <c r="D54"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
+      <c r="B81" t="s">
+        <v>185</v>
+      </c>
+      <c r="C81" t="s">
+        <v>257</v>
+      </c>
+      <c r="D81"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>55</v>
+      </c>
+      <c r="B82" t="s">
+        <v>186</v>
+      </c>
+      <c r="C82" t="s">
+        <v>257</v>
+      </c>
+      <c r="D82"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>55</v>
+      </c>
+      <c r="B83" t="s">
+        <v>187</v>
+      </c>
+      <c r="C83" t="s">
+        <v>257</v>
+      </c>
+      <c r="D83"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>56</v>
       </c>
-      <c r="C55" t="s">
-        <v>89</v>
-      </c>
-      <c r="D55"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
+      <c r="B84" t="s">
+        <v>188</v>
+      </c>
+      <c r="C84" t="s">
+        <v>253</v>
+      </c>
+      <c r="D84"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>56</v>
+      </c>
+      <c r="B85" t="s">
+        <v>189</v>
+      </c>
+      <c r="C85" t="s">
+        <v>253</v>
+      </c>
+      <c r="D85"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>57</v>
       </c>
-      <c r="C56" t="s">
-        <v>89</v>
-      </c>
-      <c r="D56"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
+      <c r="B86" t="s">
+        <v>190</v>
+      </c>
+      <c r="C86" t="s">
+        <v>241</v>
+      </c>
+      <c r="D86"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>58</v>
       </c>
-      <c r="C57" t="s">
-        <v>89</v>
-      </c>
-      <c r="D57"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
+      <c r="B87" t="s">
+        <v>191</v>
+      </c>
+      <c r="C87" t="s">
+        <v>253</v>
+      </c>
+      <c r="D87"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
         <v>59</v>
       </c>
-      <c r="C58" t="s">
-        <v>89</v>
-      </c>
-      <c r="D58"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
+      <c r="B88" t="s">
+        <v>192</v>
+      </c>
+      <c r="C88" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>60</v>
       </c>
-      <c r="C59" t="s">
-        <v>89</v>
-      </c>
-      <c r="D59"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+      <c r="B89" t="s">
+        <v>193</v>
+      </c>
+      <c r="C89" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>61</v>
       </c>
-      <c r="C60" t="s">
-        <v>89</v>
-      </c>
-      <c r="D60"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
+      <c r="B90" t="s">
+        <v>194</v>
+      </c>
+      <c r="C90" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>62</v>
       </c>
-      <c r="C61" t="s">
-        <v>89</v>
-      </c>
-      <c r="D61"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
+      <c r="B91" t="s">
+        <v>195</v>
+      </c>
+      <c r="C91" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>62</v>
+      </c>
+      <c r="B92" t="s">
+        <v>196</v>
+      </c>
+      <c r="C92" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
         <v>63</v>
       </c>
-      <c r="C62" t="s">
-        <v>89</v>
-      </c>
-      <c r="D62"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
+      <c r="B93" t="s">
+        <v>197</v>
+      </c>
+      <c r="C93" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
         <v>64</v>
       </c>
-      <c r="C63" t="s">
-        <v>89</v>
-      </c>
-      <c r="D63"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
+      <c r="B94" t="s">
+        <v>198</v>
+      </c>
+      <c r="C94" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
         <v>65</v>
       </c>
-      <c r="C64" t="s">
-        <v>89</v>
-      </c>
-      <c r="D64"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
+      <c r="B95" t="s">
+        <v>199</v>
+      </c>
+      <c r="C95" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
         <v>66</v>
       </c>
-      <c r="C65" t="s">
-        <v>89</v>
-      </c>
-      <c r="D65"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
+      <c r="B96" t="s">
+        <v>200</v>
+      </c>
+      <c r="C96" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
         <v>67</v>
       </c>
-      <c r="C66" t="s">
-        <v>89</v>
-      </c>
-      <c r="D66"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
+      <c r="B97" t="s">
+        <v>201</v>
+      </c>
+      <c r="C97" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
         <v>68</v>
       </c>
-      <c r="C67" t="s">
-        <v>89</v>
-      </c>
-      <c r="D67"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
+      <c r="B98" t="s">
+        <v>202</v>
+      </c>
+      <c r="C98" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
         <v>69</v>
       </c>
-      <c r="C68" t="s">
-        <v>89</v>
-      </c>
-      <c r="D68"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
+      <c r="B99" t="s">
+        <v>203</v>
+      </c>
+      <c r="C99" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
         <v>70</v>
       </c>
-      <c r="C69" t="s">
-        <v>89</v>
-      </c>
-      <c r="D69"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
+      <c r="B100" t="s">
+        <v>204</v>
+      </c>
+      <c r="C100" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
         <v>71</v>
       </c>
-      <c r="C70" t="s">
-        <v>89</v>
-      </c>
-      <c r="D70"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
+      <c r="B101" t="s">
+        <v>205</v>
+      </c>
+      <c r="C101" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
         <v>72</v>
       </c>
-      <c r="C71" t="s">
-        <v>89</v>
-      </c>
-      <c r="D71"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
+      <c r="B102" t="s">
+        <v>206</v>
+      </c>
+      <c r="C102" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
         <v>73</v>
       </c>
-      <c r="C72" t="s">
-        <v>89</v>
-      </c>
-      <c r="D72"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
+      <c r="B103" t="s">
+        <v>207</v>
+      </c>
+      <c r="C103" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
         <v>74</v>
       </c>
-      <c r="C73" t="s">
-        <v>89</v>
-      </c>
-      <c r="D73"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
+      <c r="B104" t="s">
+        <v>208</v>
+      </c>
+      <c r="C104" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
         <v>75</v>
       </c>
-      <c r="C74" t="s">
-        <v>89</v>
-      </c>
-      <c r="D74"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
+      <c r="B105" t="s">
+        <v>209</v>
+      </c>
+      <c r="C105" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
         <v>76</v>
       </c>
-      <c r="C75" t="s">
-        <v>89</v>
-      </c>
-      <c r="D75"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
+      <c r="B106" t="s">
+        <v>210</v>
+      </c>
+      <c r="C106" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
         <v>77</v>
       </c>
-      <c r="C76" t="s">
-        <v>89</v>
-      </c>
-      <c r="D76"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
+      <c r="B107" t="s">
+        <v>211</v>
+      </c>
+      <c r="C107" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
         <v>78</v>
       </c>
-      <c r="C77" t="s">
-        <v>89</v>
-      </c>
-      <c r="D77"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
+      <c r="B108" t="s">
+        <v>212</v>
+      </c>
+      <c r="C108" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
         <v>79</v>
       </c>
-      <c r="C78" t="s">
-        <v>89</v>
-      </c>
-      <c r="D78"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
+      <c r="B109" t="s">
+        <v>213</v>
+      </c>
+      <c r="C109" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
         <v>80</v>
       </c>
-      <c r="C79" t="s">
-        <v>89</v>
-      </c>
-      <c r="D79"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
+      <c r="B110" t="s">
+        <v>214</v>
+      </c>
+      <c r="C110" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
         <v>81</v>
       </c>
-      <c r="C80" t="s">
-        <v>89</v>
-      </c>
-      <c r="D80"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
+      <c r="B111" t="s">
+        <v>215</v>
+      </c>
+      <c r="C111" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>82</v>
       </c>
-      <c r="C81" t="s">
-        <v>89</v>
-      </c>
-      <c r="D81"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
+      <c r="B112" t="s">
+        <v>216</v>
+      </c>
+      <c r="C112" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
         <v>83</v>
       </c>
-      <c r="C82" t="s">
-        <v>89</v>
-      </c>
-      <c r="D82"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
+      <c r="B113" t="s">
+        <v>217</v>
+      </c>
+      <c r="C113" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
         <v>84</v>
       </c>
-      <c r="C83" t="s">
-        <v>89</v>
-      </c>
-      <c r="D83"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
+      <c r="B114" t="s">
+        <v>218</v>
+      </c>
+      <c r="C114" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
         <v>85</v>
       </c>
-      <c r="C84" t="s">
-        <v>89</v>
-      </c>
-      <c r="D84"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
+      <c r="B115" t="s">
+        <v>219</v>
+      </c>
+      <c r="C115" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
         <v>86</v>
       </c>
-      <c r="C85" t="s">
-        <v>89</v>
-      </c>
-      <c r="D85"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
+      <c r="B116" t="s">
+        <v>220</v>
+      </c>
+      <c r="C116" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
         <v>87</v>
       </c>
-      <c r="C86" t="s">
-        <v>89</v>
-      </c>
-      <c r="D86"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
+      <c r="B117" t="s">
+        <v>221</v>
+      </c>
+      <c r="C117" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
         <v>88</v>
       </c>
-      <c r="C87" t="s">
-        <v>89</v>
-      </c>
-      <c r="D87"/>
+      <c r="B118" t="s">
+        <v>222</v>
+      </c>
+      <c r="C118" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>92</v>
+      </c>
+      <c r="B119" t="s">
+        <v>223</v>
+      </c>
+      <c r="C119" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>93</v>
+      </c>
+      <c r="B120" t="s">
+        <v>224</v>
+      </c>
+      <c r="C120" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>94</v>
+      </c>
+      <c r="B121" t="s">
+        <v>225</v>
+      </c>
+      <c r="C121" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>94</v>
+      </c>
+      <c r="B122" t="s">
+        <v>226</v>
+      </c>
+      <c r="C122" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>95</v>
+      </c>
+      <c r="B123" t="s">
+        <v>227</v>
+      </c>
+      <c r="C123" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>95</v>
+      </c>
+      <c r="B124" t="s">
+        <v>228</v>
+      </c>
+      <c r="C124" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>96</v>
+      </c>
+      <c r="B125" t="s">
+        <v>229</v>
+      </c>
+      <c r="C125" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>97</v>
+      </c>
+      <c r="B126" t="s">
+        <v>230</v>
+      </c>
+      <c r="C126" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>98</v>
+      </c>
+      <c r="B127" t="s">
+        <v>231</v>
+      </c>
+      <c r="C127" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>99</v>
+      </c>
+      <c r="B128" t="s">
+        <v>232</v>
+      </c>
+      <c r="C128" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>100</v>
+      </c>
+      <c r="B129" t="s">
+        <v>233</v>
+      </c>
+      <c r="C129" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>101</v>
+      </c>
+      <c r="B130" t="s">
+        <v>234</v>
+      </c>
+      <c r="C130" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>102</v>
+      </c>
+      <c r="B131" t="s">
+        <v>235</v>
+      </c>
+      <c r="C131" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>103</v>
+      </c>
+      <c r="B132" t="s">
+        <v>236</v>
+      </c>
+      <c r="C132" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>103</v>
+      </c>
+      <c r="B133" t="s">
+        <v>237</v>
+      </c>
+      <c r="C133" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>104</v>
+      </c>
+      <c r="B134" t="s">
+        <v>238</v>
+      </c>
+      <c r="C134" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>105</v>
+      </c>
+      <c r="B135" t="s">
+        <v>239</v>
+      </c>
+      <c r="C135" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>105</v>
+      </c>
+      <c r="B136" t="s">
+        <v>240</v>
+      </c>
+      <c r="C136" t="s">
+        <v>246</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="C1" xr:uid="{66E3D377-5F1B-48CD-A9ED-4AF810829D06}"/>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC133256-BEE6-4366-BADF-3F17242F722A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9522978-9927-4B56-BBF9-152786E25B09}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="285">
   <si>
     <t>UTK</t>
   </si>
@@ -333,7 +333,556 @@
     <t>99002335</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>SZ-840</t>
+  </si>
+  <si>
+    <t>SZ-860</t>
+  </si>
+  <si>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-800</t>
+  </si>
+  <si>
+    <t>267004973</t>
+  </si>
+  <si>
+    <t>267004978</t>
+  </si>
+  <si>
+    <t>26MPE0003708</t>
+  </si>
+  <si>
+    <t>26MPE0003710</t>
+  </si>
+  <si>
+    <t>26MPE0003719</t>
+  </si>
+  <si>
+    <t>26MPE0003757</t>
+  </si>
+  <si>
+    <t>26MPE0003826</t>
+  </si>
+  <si>
+    <t>NFD6-04-01-H7FC</t>
+  </si>
+  <si>
+    <t>NFD6-04-02-SZQD</t>
+  </si>
+  <si>
+    <t>NFD6-04-07-J4DB</t>
+  </si>
+  <si>
+    <t>NFD6-04-09-7QM7</t>
+  </si>
+  <si>
+    <t>NFD6-04-09-B4MB</t>
+  </si>
+  <si>
+    <t>NFD6-04-09-KCU2</t>
+  </si>
+  <si>
+    <t>NFD6-04-09-N5U2</t>
+  </si>
+  <si>
+    <t>NFD6-04-09-PL9X</t>
+  </si>
+  <si>
+    <t>NFD6-04-09-TJEY</t>
+  </si>
+  <si>
+    <t>NFE6-04-09-LBAF</t>
+  </si>
+  <si>
+    <t>NFE6-04-09-MYLR</t>
+  </si>
+  <si>
+    <t>NFE6-04-09-SDP3</t>
+  </si>
+  <si>
+    <t>NFE6-04-09-Y5KC</t>
+  </si>
+  <si>
+    <t>NFE6-04-09-ZLLP</t>
+  </si>
+  <si>
+    <t>248745386/1</t>
+  </si>
+  <si>
+    <t>248745393/1</t>
+  </si>
+  <si>
+    <t>69d78d8b5cef447acab8c9ee</t>
+  </si>
+  <si>
+    <t>69cc0a870ed4809420f4bf46</t>
+  </si>
+  <si>
+    <t>69d7acc05cef447acab8cf76</t>
+  </si>
+  <si>
+    <t>69d89a0f5cef447acab8d91e</t>
+  </si>
+  <si>
+    <t>69d8bdb85cef447acab8ddff</t>
+  </si>
+  <si>
+    <t>69d661415cef447acab8b79a</t>
+  </si>
+  <si>
+    <t>69ce33b05cef447acab8653d</t>
+  </si>
+  <si>
+    <t>69ce33b05cef447acab8653e</t>
+  </si>
+  <si>
+    <t>69ceaeba5cef447acab872a5</t>
+  </si>
+  <si>
+    <t>69d8ce805cef447acab8e0b9</t>
+  </si>
+  <si>
+    <t>69d89a715cef447acab8d930</t>
+  </si>
+  <si>
+    <t>69d4c42b5cef447acab890b6</t>
+  </si>
+  <si>
+    <t>69d61ed15cef447acab8aca9</t>
+  </si>
+  <si>
+    <t>69d57b135cef447acab8a5b1</t>
+  </si>
+  <si>
+    <t>69d7e8a45cef447acab8d68b</t>
+  </si>
+  <si>
+    <t>69d62bee5cef447acab8af26</t>
+  </si>
+  <si>
+    <t>69d62bee5cef447acab8af27</t>
+  </si>
+  <si>
+    <t>69d6447b5cef447acab8b2ae</t>
+  </si>
+  <si>
+    <t>69d67a6d5cef447acab8ba89</t>
+  </si>
+  <si>
+    <t>69d694485cef447acab8bcad</t>
+  </si>
+  <si>
+    <t>69d77ab65cef447acab8c6dc</t>
+  </si>
+  <si>
+    <t>69d7da325cef447acab8d56c</t>
+  </si>
+  <si>
+    <t>69d76e2e5cef447acab8c498</t>
+  </si>
+  <si>
+    <t>69d7ac575cef447acab8cf61</t>
+  </si>
+  <si>
+    <t>69d7ac575cef447acab8cf62</t>
+  </si>
+  <si>
+    <t>69d7ad735cef447acab8cf98</t>
+  </si>
+  <si>
+    <t>69d7ad735cef447acab8cf99</t>
+  </si>
+  <si>
+    <t>69d7bf0d5cef447acab8d2d5</t>
+  </si>
+  <si>
+    <t>69d8b3f65cef447acab8dc1a</t>
+  </si>
+  <si>
+    <t>69d8b3f65cef447acab8dc1b</t>
+  </si>
+  <si>
+    <t>69d8c32f5cef447acab8def3</t>
+  </si>
+  <si>
+    <t>69d846f15cef447acab8d829</t>
+  </si>
+  <si>
+    <t>69d8c45e5cef447acab8df3a</t>
+  </si>
+  <si>
+    <t>69d8d96e5cef447acab8e22e</t>
+  </si>
+  <si>
+    <t>FIZZ-1000860285</t>
+  </si>
+  <si>
+    <t>FIZZ-1000862427</t>
+  </si>
+  <si>
+    <t>26MPE0003708/1</t>
+  </si>
+  <si>
+    <t>26MPE0003710/1</t>
+  </si>
+  <si>
+    <t>26MPE0003719/1</t>
+  </si>
+  <si>
+    <t>26MPE0003757/1</t>
+  </si>
+  <si>
+    <t>26MPE0003826/1</t>
+  </si>
+  <si>
+    <t>300523974/1</t>
+  </si>
+  <si>
+    <t>305557116/1</t>
+  </si>
+  <si>
+    <t>305557116/2</t>
+  </si>
+  <si>
+    <t>305557116/3</t>
+  </si>
+  <si>
+    <t>305830892/1</t>
+  </si>
+  <si>
+    <t>305830892/2</t>
+  </si>
+  <si>
+    <t>306621232/1</t>
+  </si>
+  <si>
+    <t>306669492/1</t>
+  </si>
+  <si>
+    <t>306669492/2</t>
+  </si>
+  <si>
+    <t>306766498/1</t>
+  </si>
+  <si>
+    <t>306823916/1</t>
+  </si>
+  <si>
+    <t>306823916/2</t>
+  </si>
+  <si>
+    <t>306891294/1</t>
+  </si>
+  <si>
+    <t>306891294/2</t>
+  </si>
+  <si>
+    <t>307081008/1</t>
+  </si>
+  <si>
+    <t>307081249/1</t>
+  </si>
+  <si>
+    <t>307081249/2</t>
+  </si>
+  <si>
+    <t>307081249/3</t>
+  </si>
+  <si>
+    <t>307081428/1</t>
+  </si>
+  <si>
+    <t>307141884/1</t>
+  </si>
+  <si>
+    <t>307198140/1</t>
+  </si>
+  <si>
+    <t>307198140/2</t>
+  </si>
+  <si>
+    <t>307237760/1</t>
+  </si>
+  <si>
+    <t>307238085/1</t>
+  </si>
+  <si>
+    <t>307238509/1</t>
+  </si>
+  <si>
+    <t>307278644/1</t>
+  </si>
+  <si>
+    <t>307278768/1</t>
+  </si>
+  <si>
+    <t>307278791/1</t>
+  </si>
+  <si>
+    <t>307279268/1</t>
+  </si>
+  <si>
+    <t>307279324/1</t>
+  </si>
+  <si>
+    <t>307279397/1</t>
+  </si>
+  <si>
+    <t>307279479/1</t>
+  </si>
+  <si>
+    <t>307342850/1</t>
+  </si>
+  <si>
+    <t>307343263/1</t>
+  </si>
+  <si>
+    <t>307379077/2/1</t>
+  </si>
+  <si>
+    <t>307379439/1</t>
+  </si>
+  <si>
+    <t>307379439/2</t>
+  </si>
+  <si>
+    <t>307379669/1</t>
+  </si>
+  <si>
+    <t>307379894/1</t>
+  </si>
+  <si>
+    <t>307379931/1</t>
+  </si>
+  <si>
+    <t>307426389/1</t>
+  </si>
+  <si>
+    <t>307426557/1</t>
+  </si>
+  <si>
+    <t>307426610/1</t>
+  </si>
+  <si>
+    <t>307426668/1</t>
+  </si>
+  <si>
+    <t>307426710/1</t>
+  </si>
+  <si>
+    <t>307426887/1</t>
+  </si>
+  <si>
+    <t>307426936/1</t>
+  </si>
+  <si>
+    <t>307426936/2</t>
+  </si>
+  <si>
+    <t>307427078/1</t>
+  </si>
+  <si>
+    <t>307427165/1</t>
+  </si>
+  <si>
+    <t>307482401/1</t>
+  </si>
+  <si>
+    <t>307482401/2</t>
+  </si>
+  <si>
+    <t>307482484/1</t>
+  </si>
+  <si>
+    <t>307482627/1</t>
+  </si>
+  <si>
+    <t>307482743/1</t>
+  </si>
+  <si>
+    <t>307482871/1</t>
+  </si>
+  <si>
+    <t>307482902/1</t>
+  </si>
+  <si>
+    <t>307483072/1</t>
+  </si>
+  <si>
+    <t>307483214/1</t>
+  </si>
+  <si>
+    <t>307483270/1</t>
+  </si>
+  <si>
+    <t>307483270/2</t>
+  </si>
+  <si>
+    <t>307483270/3</t>
+  </si>
+  <si>
+    <t>307530336/1</t>
+  </si>
+  <si>
+    <t>307530358/1</t>
+  </si>
+  <si>
+    <t>307530520/1</t>
+  </si>
+  <si>
+    <t>307530564/1</t>
+  </si>
+  <si>
+    <t>307530620/1</t>
+  </si>
+  <si>
+    <t>307530962/1</t>
+  </si>
+  <si>
+    <t>307530981/1</t>
+  </si>
+  <si>
+    <t>307531024/1</t>
+  </si>
+  <si>
+    <t>307579790/1</t>
+  </si>
+  <si>
+    <t>307628153/1</t>
+  </si>
+  <si>
+    <t>307628153/2</t>
+  </si>
+  <si>
+    <t>307628394/1</t>
+  </si>
+  <si>
+    <t>307689408/1</t>
+  </si>
+  <si>
+    <t>307741125/1</t>
+  </si>
+  <si>
+    <t>307741256/1</t>
+  </si>
+  <si>
+    <t>307741380/1</t>
+  </si>
+  <si>
+    <t>307741380/2</t>
+  </si>
+  <si>
+    <t>307806493/1</t>
+  </si>
+  <si>
+    <t>307806637/1</t>
+  </si>
+  <si>
+    <t>99002327/1</t>
+  </si>
+  <si>
+    <t>99002335/1</t>
+  </si>
+  <si>
+    <t>202604102600779201</t>
+  </si>
+  <si>
+    <t>202604102600786401</t>
+  </si>
+  <si>
+    <t>202604102600786402</t>
+  </si>
+  <si>
+    <t>202604102600786403</t>
+  </si>
+  <si>
+    <t>202604082600809501</t>
+  </si>
+  <si>
+    <t>202604102600830601</t>
+  </si>
+  <si>
+    <t>202604102600831101</t>
+  </si>
+  <si>
+    <t>202604102600827301</t>
+  </si>
+  <si>
+    <t>202604102600829201</t>
+  </si>
+  <si>
+    <t>202604102600832201</t>
+  </si>
+  <si>
+    <t>202604102600827901</t>
+  </si>
+  <si>
+    <t>202604102600833401</t>
+  </si>
+  <si>
+    <t>202604102600828601</t>
+  </si>
+  <si>
+    <t>202604102600834601</t>
+  </si>
+  <si>
+    <t>202604102600832301</t>
+  </si>
+  <si>
+    <t>202604102600831001</t>
   </si>
 </sst>
 </file>
@@ -369,10 +918,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -654,7 +1202,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
@@ -675,8 +1223,11 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>143</v>
       </c>
       <c r="C2" t="s">
         <v>101</v>
@@ -684,242 +1235,323 @@
       <c r="D2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
+      <c r="B3" t="s">
+        <v>144</v>
+      </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D3"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
+      <c r="B4" t="s">
+        <v>145</v>
+      </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D4"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
+      <c r="B5" t="s">
+        <v>146</v>
+      </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D5"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
+      <c r="B6" t="s">
+        <v>147</v>
+      </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D6"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
+      <c r="B7" t="s">
+        <v>148</v>
+      </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D7"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
+      <c r="B8" t="s">
+        <v>149</v>
+      </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D8"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>11</v>
       </c>
+      <c r="B9" t="s">
+        <v>150</v>
+      </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D9"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
+      <c r="B10" t="s">
+        <v>151</v>
+      </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D10"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="C11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="B12" t="s">
+        <v>153</v>
+      </c>
+      <c r="C12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="C12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D12"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>15</v>
       </c>
-      <c r="C13" t="s">
-        <v>101</v>
-      </c>
-      <c r="D13"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>16</v>
       </c>
-      <c r="C14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="B15" t="s">
+        <v>156</v>
+      </c>
+      <c r="C15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>3</v>
       </c>
-      <c r="C15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D15"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="B16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="C16" t="s">
-        <v>101</v>
-      </c>
-      <c r="D16"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="B17" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="C17" t="s">
-        <v>101</v>
-      </c>
-      <c r="D17"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="B18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="C18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="B19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>161</v>
+      </c>
+      <c r="C20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="C19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="B21" t="s">
+        <v>162</v>
+      </c>
+      <c r="C21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="C20" t="s">
-        <v>101</v>
-      </c>
-      <c r="D20"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="B22" t="s">
+        <v>163</v>
+      </c>
+      <c r="C22" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="C21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="B23" t="s">
+        <v>164</v>
+      </c>
+      <c r="C23" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="C22" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="B24" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="C23" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="B25" t="s">
+        <v>166</v>
+      </c>
+      <c r="C25" t="s">
+        <v>102</v>
+      </c>
+      <c r="D25"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="C24" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="B26" t="s">
+        <v>167</v>
+      </c>
+      <c r="C26" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>26</v>
       </c>
-      <c r="C25" t="s">
-        <v>101</v>
-      </c>
-      <c r="D25"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="B27" t="s">
+        <v>168</v>
+      </c>
+      <c r="C27" t="s">
+        <v>102</v>
+      </c>
+      <c r="D27"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>169</v>
+      </c>
+      <c r="C28" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>27</v>
       </c>
-      <c r="C26" t="s">
-        <v>101</v>
-      </c>
-      <c r="D26"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" t="s">
-        <v>101</v>
-      </c>
-      <c r="D27"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" t="s">
-        <v>101</v>
-      </c>
-      <c r="D28"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>30</v>
+      <c r="B29" t="s">
+        <v>170</v>
       </c>
       <c r="C29" t="s">
         <v>101</v>
@@ -927,8 +1559,11 @@
       <c r="D29"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>31</v>
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>171</v>
       </c>
       <c r="C30" t="s">
         <v>101</v>
@@ -936,62 +1571,83 @@
       <c r="D30"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>172</v>
+      </c>
+      <c r="C31" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>173</v>
+      </c>
+      <c r="C32" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>174</v>
+      </c>
+      <c r="C33" t="s">
+        <v>116</v>
+      </c>
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
+        <v>175</v>
+      </c>
+      <c r="C34" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" t="s">
+        <v>176</v>
+      </c>
+      <c r="C35" t="s">
+        <v>105</v>
+      </c>
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>32</v>
       </c>
-      <c r="C31" t="s">
-        <v>101</v>
-      </c>
-      <c r="D31"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="B36" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" t="s">
+        <v>115</v>
+      </c>
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>33</v>
       </c>
-      <c r="C32" t="s">
-        <v>101</v>
-      </c>
-      <c r="D32"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" t="s">
-        <v>101</v>
-      </c>
-      <c r="D33"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" t="s">
-        <v>101</v>
-      </c>
-      <c r="D34"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" t="s">
-        <v>101</v>
-      </c>
-      <c r="D35"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" t="s">
-        <v>101</v>
-      </c>
-      <c r="D36"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>38</v>
+      <c r="B37" t="s">
+        <v>178</v>
       </c>
       <c r="C37" t="s">
         <v>101</v>
@@ -999,233 +1655,311 @@
       <c r="D37"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="A38" t="s">
+        <v>122</v>
+      </c>
+      <c r="B38" t="s">
+        <v>179</v>
+      </c>
+      <c r="C38" t="s">
+        <v>114</v>
+      </c>
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39" t="s">
+        <v>180</v>
+      </c>
+      <c r="C39" t="s">
+        <v>115</v>
+      </c>
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>124</v>
+      </c>
+      <c r="B40" t="s">
+        <v>181</v>
+      </c>
+      <c r="C40" t="s">
+        <v>117</v>
+      </c>
+      <c r="D40"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>125</v>
+      </c>
+      <c r="B41" t="s">
+        <v>182</v>
+      </c>
+      <c r="C41" t="s">
+        <v>118</v>
+      </c>
+      <c r="D41"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>126</v>
+      </c>
+      <c r="B42" t="s">
+        <v>183</v>
+      </c>
+      <c r="C42" t="s">
+        <v>118</v>
+      </c>
+      <c r="D42"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" t="s">
+        <v>184</v>
+      </c>
+      <c r="C43" t="s">
+        <v>119</v>
+      </c>
+      <c r="D43"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>128</v>
+      </c>
+      <c r="B44" t="s">
+        <v>185</v>
+      </c>
+      <c r="C44" t="s">
+        <v>114</v>
+      </c>
+      <c r="D44"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" t="s">
+        <v>186</v>
+      </c>
+      <c r="C45" t="s">
+        <v>120</v>
+      </c>
+      <c r="D45"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" t="s">
+        <v>187</v>
+      </c>
+      <c r="C46" t="s">
+        <v>102</v>
+      </c>
+      <c r="D46"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" t="s">
+        <v>188</v>
+      </c>
+      <c r="C47" t="s">
+        <v>102</v>
+      </c>
+      <c r="D47"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" t="s">
+        <v>189</v>
+      </c>
+      <c r="C48" t="s">
+        <v>102</v>
+      </c>
+      <c r="D48"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B49" t="s">
+        <v>190</v>
+      </c>
+      <c r="C49" t="s">
+        <v>115</v>
+      </c>
+      <c r="D49"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>36</v>
+      </c>
+      <c r="B50" t="s">
+        <v>191</v>
+      </c>
+      <c r="C50" t="s">
+        <v>115</v>
+      </c>
+      <c r="D50"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" t="s">
+        <v>192</v>
+      </c>
+      <c r="C51" t="s">
+        <v>105</v>
+      </c>
+      <c r="D51"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" t="s">
+        <v>193</v>
+      </c>
+      <c r="C52" t="s">
+        <v>119</v>
+      </c>
+      <c r="D52"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" t="s">
+        <v>194</v>
+      </c>
+      <c r="C53" t="s">
+        <v>119</v>
+      </c>
+      <c r="D53"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>39</v>
       </c>
-      <c r="C38" t="s">
-        <v>101</v>
-      </c>
-      <c r="D38"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="B54" t="s">
+        <v>195</v>
+      </c>
+      <c r="C54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D54"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>40</v>
       </c>
-      <c r="C39" t="s">
-        <v>101</v>
-      </c>
-      <c r="D39"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="B55" t="s">
+        <v>196</v>
+      </c>
+      <c r="C55" t="s">
+        <v>116</v>
+      </c>
+      <c r="D55"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" t="s">
+        <v>197</v>
+      </c>
+      <c r="C56" t="s">
+        <v>116</v>
+      </c>
+      <c r="D56"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>41</v>
       </c>
-      <c r="C40" t="s">
-        <v>101</v>
-      </c>
-      <c r="D40"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="B57" t="s">
+        <v>198</v>
+      </c>
+      <c r="C57" t="s">
+        <v>118</v>
+      </c>
+      <c r="D57"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" t="s">
+        <v>199</v>
+      </c>
+      <c r="C58" t="s">
+        <v>118</v>
+      </c>
+      <c r="D58"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>42</v>
       </c>
-      <c r="C41" t="s">
-        <v>101</v>
-      </c>
-      <c r="D41"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+      <c r="B59" t="s">
+        <v>200</v>
+      </c>
+      <c r="C59" t="s">
+        <v>107</v>
+      </c>
+      <c r="D59"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>43</v>
       </c>
-      <c r="C42" t="s">
-        <v>101</v>
-      </c>
-      <c r="D42"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+      <c r="B60" t="s">
+        <v>201</v>
+      </c>
+      <c r="C60" t="s">
+        <v>118</v>
+      </c>
+      <c r="D60"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" t="s">
+        <v>202</v>
+      </c>
+      <c r="C61" t="s">
+        <v>118</v>
+      </c>
+      <c r="D61"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>43</v>
+      </c>
+      <c r="B62" t="s">
+        <v>203</v>
+      </c>
+      <c r="C62" t="s">
+        <v>118</v>
+      </c>
+      <c r="D62"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>44</v>
       </c>
-      <c r="C43" t="s">
-        <v>101</v>
-      </c>
-      <c r="D43"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C44" t="s">
-        <v>101</v>
-      </c>
-      <c r="D44"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45" t="s">
-        <v>101</v>
-      </c>
-      <c r="D45"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C46" t="s">
-        <v>101</v>
-      </c>
-      <c r="D46"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" t="s">
-        <v>101</v>
-      </c>
-      <c r="D47"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C48" t="s">
-        <v>101</v>
-      </c>
-      <c r="D48"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C49" t="s">
-        <v>101</v>
-      </c>
-      <c r="D49"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C50" t="s">
-        <v>101</v>
-      </c>
-      <c r="D50"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C51" t="s">
-        <v>101</v>
-      </c>
-      <c r="D51"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C52" t="s">
-        <v>101</v>
-      </c>
-      <c r="D52"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C53" t="s">
-        <v>101</v>
-      </c>
-      <c r="D53"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" t="s">
-        <v>101</v>
-      </c>
-      <c r="D54"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C55" t="s">
-        <v>101</v>
-      </c>
-      <c r="D55"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56" t="s">
-        <v>101</v>
-      </c>
-      <c r="D56"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" t="s">
-        <v>101</v>
-      </c>
-      <c r="D57"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C58" t="s">
-        <v>101</v>
-      </c>
-      <c r="D58"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C59" t="s">
-        <v>101</v>
-      </c>
-      <c r="D59"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" t="s">
-        <v>101</v>
-      </c>
-      <c r="D60"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C61" t="s">
-        <v>101</v>
-      </c>
-      <c r="D61"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C62" t="s">
-        <v>101</v>
-      </c>
-      <c r="D62"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>64</v>
+      <c r="B63" t="s">
+        <v>204</v>
       </c>
       <c r="C63" t="s">
         <v>101</v>
@@ -1233,188 +1967,251 @@
       <c r="D63"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>65</v>
+      <c r="A64" t="s">
+        <v>45</v>
+      </c>
+      <c r="B64" t="s">
+        <v>205</v>
       </c>
       <c r="C64" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D64"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>66</v>
+      <c r="A65" t="s">
+        <v>46</v>
+      </c>
+      <c r="B65" t="s">
+        <v>206</v>
       </c>
       <c r="C65" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D65"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>67</v>
+      <c r="A66" t="s">
+        <v>46</v>
+      </c>
+      <c r="B66" t="s">
+        <v>207</v>
       </c>
       <c r="C66" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D66"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>68</v>
+      <c r="A67" t="s">
+        <v>47</v>
+      </c>
+      <c r="B67" t="s">
+        <v>208</v>
       </c>
       <c r="C67" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D67"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>69</v>
+      <c r="A68" t="s">
+        <v>48</v>
+      </c>
+      <c r="B68" t="s">
+        <v>209</v>
       </c>
       <c r="C68" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D68"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>70</v>
+      <c r="A69" t="s">
+        <v>49</v>
+      </c>
+      <c r="B69" t="s">
+        <v>210</v>
       </c>
       <c r="C69" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D69"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>71</v>
+      <c r="A70" t="s">
+        <v>50</v>
+      </c>
+      <c r="B70" t="s">
+        <v>211</v>
       </c>
       <c r="C70" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D70"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>72</v>
+      <c r="A71" t="s">
+        <v>51</v>
+      </c>
+      <c r="B71" t="s">
+        <v>212</v>
       </c>
       <c r="C71" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="D71"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>73</v>
+      <c r="A72" t="s">
+        <v>52</v>
+      </c>
+      <c r="B72" t="s">
+        <v>213</v>
       </c>
       <c r="C72" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D72"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>74</v>
+      <c r="A73" t="s">
+        <v>53</v>
+      </c>
+      <c r="B73" t="s">
+        <v>214</v>
       </c>
       <c r="C73" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D73"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>75</v>
+      <c r="A74" t="s">
+        <v>54</v>
+      </c>
+      <c r="B74" t="s">
+        <v>215</v>
       </c>
       <c r="C74" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D74"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>76</v>
+      <c r="A75" t="s">
+        <v>55</v>
+      </c>
+      <c r="B75" t="s">
+        <v>216</v>
       </c>
       <c r="C75" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D75"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>77</v>
+      <c r="A76" t="s">
+        <v>56</v>
+      </c>
+      <c r="B76" t="s">
+        <v>217</v>
       </c>
       <c r="C76" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="D76"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>78</v>
+      <c r="A77" t="s">
+        <v>57</v>
+      </c>
+      <c r="B77" t="s">
+        <v>218</v>
       </c>
       <c r="C77" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="D77"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>79</v>
+      <c r="A78" t="s">
+        <v>58</v>
+      </c>
+      <c r="B78" t="s">
+        <v>219</v>
       </c>
       <c r="C78" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D78"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>80</v>
+      <c r="A79" t="s">
+        <v>59</v>
+      </c>
+      <c r="B79" t="s">
+        <v>220</v>
       </c>
       <c r="C79" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D79"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>81</v>
+      <c r="A80" t="s">
+        <v>60</v>
+      </c>
+      <c r="B80" t="s">
+        <v>221</v>
       </c>
       <c r="C80" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D80"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>82</v>
+      <c r="A81" t="s">
+        <v>60</v>
+      </c>
+      <c r="B81" t="s">
+        <v>222</v>
       </c>
       <c r="C81" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D81"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>83</v>
+      <c r="A82" t="s">
+        <v>61</v>
+      </c>
+      <c r="B82" t="s">
+        <v>223</v>
       </c>
       <c r="C82" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D82"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>84</v>
+      <c r="A83" t="s">
+        <v>62</v>
+      </c>
+      <c r="B83" t="s">
+        <v>224</v>
       </c>
       <c r="C83" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D83"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>85</v>
+      <c r="A84" t="s">
+        <v>63</v>
+      </c>
+      <c r="B84" t="s">
+        <v>225</v>
       </c>
       <c r="C84" t="s">
         <v>101</v>
@@ -1422,126 +2219,655 @@
       <c r="D84"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>86</v>
+      <c r="A85" t="s">
+        <v>64</v>
+      </c>
+      <c r="B85" t="s">
+        <v>226</v>
       </c>
       <c r="C85" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D85"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>87</v>
+      <c r="A86" t="s">
+        <v>65</v>
+      </c>
+      <c r="B86" t="s">
+        <v>227</v>
       </c>
       <c r="C86" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D86"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>88</v>
+      <c r="A87" t="s">
+        <v>66</v>
+      </c>
+      <c r="B87" t="s">
+        <v>228</v>
       </c>
       <c r="C87" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D87"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>89</v>
+      <c r="A88" t="s">
+        <v>67</v>
+      </c>
+      <c r="B88" t="s">
+        <v>229</v>
       </c>
       <c r="C88" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
-        <v>90</v>
+      <c r="A89" t="s">
+        <v>68</v>
+      </c>
+      <c r="B89" t="s">
+        <v>230</v>
       </c>
       <c r="C89" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>91</v>
+      <c r="A90" t="s">
+        <v>69</v>
+      </c>
+      <c r="B90" t="s">
+        <v>231</v>
       </c>
       <c r="C90" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>92</v>
+      <c r="A91" t="s">
+        <v>70</v>
+      </c>
+      <c r="B91" t="s">
+        <v>232</v>
       </c>
       <c r="C91" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>93</v>
+      <c r="A92" t="s">
+        <v>70</v>
+      </c>
+      <c r="B92" t="s">
+        <v>233</v>
       </c>
       <c r="C92" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>94</v>
+      <c r="A93" t="s">
+        <v>71</v>
+      </c>
+      <c r="B93" t="s">
+        <v>234</v>
       </c>
       <c r="C93" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
-        <v>95</v>
+      <c r="A94" t="s">
+        <v>72</v>
+      </c>
+      <c r="B94" t="s">
+        <v>235</v>
       </c>
       <c r="C94" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>96</v>
+      <c r="A95" t="s">
+        <v>73</v>
+      </c>
+      <c r="B95" t="s">
+        <v>236</v>
       </c>
       <c r="C95" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>97</v>
+      <c r="A96" t="s">
+        <v>73</v>
+      </c>
+      <c r="B96" t="s">
+        <v>237</v>
       </c>
       <c r="C96" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
-        <v>98</v>
+      <c r="A97" t="s">
+        <v>74</v>
+      </c>
+      <c r="B97" t="s">
+        <v>238</v>
       </c>
       <c r="C97" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>99</v>
+      <c r="A98" t="s">
+        <v>75</v>
+      </c>
+      <c r="B98" t="s">
+        <v>239</v>
       </c>
       <c r="C98" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>100</v>
+      <c r="A99" t="s">
+        <v>76</v>
+      </c>
+      <c r="B99" t="s">
+        <v>240</v>
       </c>
       <c r="C99" t="s">
         <v>101</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>77</v>
+      </c>
+      <c r="B100" t="s">
+        <v>241</v>
+      </c>
+      <c r="C100" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>78</v>
+      </c>
+      <c r="B101" t="s">
+        <v>242</v>
+      </c>
+      <c r="C101" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>79</v>
+      </c>
+      <c r="B102" t="s">
+        <v>243</v>
+      </c>
+      <c r="C102" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>80</v>
+      </c>
+      <c r="B103" t="s">
+        <v>244</v>
+      </c>
+      <c r="C103" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>81</v>
+      </c>
+      <c r="B104" t="s">
+        <v>245</v>
+      </c>
+      <c r="C104" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>81</v>
+      </c>
+      <c r="B105" t="s">
+        <v>246</v>
+      </c>
+      <c r="C105" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>81</v>
+      </c>
+      <c r="B106" t="s">
+        <v>247</v>
+      </c>
+      <c r="C106" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>82</v>
+      </c>
+      <c r="B107" t="s">
+        <v>248</v>
+      </c>
+      <c r="C107" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>83</v>
+      </c>
+      <c r="B108" t="s">
+        <v>249</v>
+      </c>
+      <c r="C108" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>84</v>
+      </c>
+      <c r="B109" t="s">
+        <v>250</v>
+      </c>
+      <c r="C109" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>85</v>
+      </c>
+      <c r="B110" t="s">
+        <v>251</v>
+      </c>
+      <c r="C110" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>86</v>
+      </c>
+      <c r="B111" t="s">
+        <v>252</v>
+      </c>
+      <c r="C111" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>87</v>
+      </c>
+      <c r="B112" t="s">
+        <v>253</v>
+      </c>
+      <c r="C112" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>88</v>
+      </c>
+      <c r="B113" t="s">
+        <v>254</v>
+      </c>
+      <c r="C113" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>89</v>
+      </c>
+      <c r="B114" t="s">
+        <v>255</v>
+      </c>
+      <c r="C114" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>90</v>
+      </c>
+      <c r="B115" t="s">
+        <v>256</v>
+      </c>
+      <c r="C115" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>91</v>
+      </c>
+      <c r="B116" t="s">
+        <v>257</v>
+      </c>
+      <c r="C116" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>91</v>
+      </c>
+      <c r="B117" t="s">
+        <v>258</v>
+      </c>
+      <c r="C117" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>92</v>
+      </c>
+      <c r="B118" t="s">
+        <v>259</v>
+      </c>
+      <c r="C118" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>93</v>
+      </c>
+      <c r="B119" t="s">
+        <v>260</v>
+      </c>
+      <c r="C119" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>94</v>
+      </c>
+      <c r="B120" t="s">
+        <v>261</v>
+      </c>
+      <c r="C120" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>95</v>
+      </c>
+      <c r="B121" t="s">
+        <v>262</v>
+      </c>
+      <c r="C121" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>96</v>
+      </c>
+      <c r="B122" t="s">
+        <v>263</v>
+      </c>
+      <c r="C122" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>96</v>
+      </c>
+      <c r="B123" t="s">
+        <v>264</v>
+      </c>
+      <c r="C123" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>97</v>
+      </c>
+      <c r="B124" t="s">
+        <v>265</v>
+      </c>
+      <c r="C124" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>98</v>
+      </c>
+      <c r="B125" t="s">
+        <v>266</v>
+      </c>
+      <c r="C125" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>99</v>
+      </c>
+      <c r="B126" t="s">
+        <v>267</v>
+      </c>
+      <c r="C126" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>100</v>
+      </c>
+      <c r="B127" t="s">
+        <v>268</v>
+      </c>
+      <c r="C127" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>129</v>
+      </c>
+      <c r="B128" t="s">
+        <v>269</v>
+      </c>
+      <c r="C128" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>130</v>
+      </c>
+      <c r="B129" t="s">
+        <v>270</v>
+      </c>
+      <c r="C129" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>130</v>
+      </c>
+      <c r="B130" t="s">
+        <v>271</v>
+      </c>
+      <c r="C130" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>272</v>
+      </c>
+      <c r="C131" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>273</v>
+      </c>
+      <c r="C132" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>274</v>
+      </c>
+      <c r="C133" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>275</v>
+      </c>
+      <c r="C134" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>276</v>
+      </c>
+      <c r="C135" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>277</v>
+      </c>
+      <c r="C136" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>278</v>
+      </c>
+      <c r="C137" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>279</v>
+      </c>
+      <c r="C138" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>280</v>
+      </c>
+      <c r="C139" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>281</v>
+      </c>
+      <c r="C140" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>282</v>
+      </c>
+      <c r="C141" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>283</v>
+      </c>
+      <c r="C142" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>284</v>
+      </c>
+      <c r="C143" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18619DD-4CFB-4588-82B1-C486B810FB27}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8AE0329-06D4-400E-98B9-627231647AA8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="415">
   <si>
     <t>UTK</t>
   </si>
@@ -378,7 +378,901 @@
     <t>307807008</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>SZ-850</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-827</t>
+  </si>
+  <si>
+    <t>SZ-860</t>
+  </si>
+  <si>
+    <t>SZ-840</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>159995579539097170</t>
+  </si>
+  <si>
+    <t>248745408/1</t>
+  </si>
+  <si>
+    <t>69d7a3255cef447acab8cdf1</t>
+  </si>
+  <si>
+    <t>69d63fc65cef447acab8b219</t>
+  </si>
+  <si>
+    <t>69dcc0fa5cef447acab90da8</t>
+  </si>
+  <si>
+    <t>69d8a15e5cef447acab8d9a6</t>
+  </si>
+  <si>
+    <t>69d8a49c5cef447acab8d9fb</t>
+  </si>
+  <si>
+    <t>69d8ce805cef447acab8e0b9</t>
+  </si>
+  <si>
+    <t>69d125305cef447acab87ff1</t>
+  </si>
+  <si>
+    <t>69d7b5b35cef447acab8d158</t>
+  </si>
+  <si>
+    <t>69d7be7a5cef447acab8d2ae</t>
+  </si>
+  <si>
+    <t>69d7be7a5cef447acab8d2af</t>
+  </si>
+  <si>
+    <t>69d7b9735cef447acab8d1e0</t>
+  </si>
+  <si>
+    <t>69d545085cef447acab8a460</t>
+  </si>
+  <si>
+    <t>69d643555cef447acab8b2a8</t>
+  </si>
+  <si>
+    <t>69d64b8f5cef447acab8b3cc</t>
+  </si>
+  <si>
+    <t>69d64b8f5cef447acab8b3cd</t>
+  </si>
+  <si>
+    <t>69d64b8f5cef447acab8b3cf</t>
+  </si>
+  <si>
+    <t>69d759195cef447acab8c08d</t>
+  </si>
+  <si>
+    <t>69d74d895cef447acab8bee6</t>
+  </si>
+  <si>
+    <t>69d74d895cef447acab8bee7</t>
+  </si>
+  <si>
+    <t>69d749cf5cef447acab8be8a</t>
+  </si>
+  <si>
+    <t>69d7b2225cef447acab8d096</t>
+  </si>
+  <si>
+    <t>69d7b2225cef447acab8d097</t>
+  </si>
+  <si>
+    <t>69d7ad835cef447acab8cfc3</t>
+  </si>
+  <si>
+    <t>69d7c2865cef447acab8d32a</t>
+  </si>
+  <si>
+    <t>69d7c4eb5cef447acab8d371</t>
+  </si>
+  <si>
+    <t>69d7c4eb5cef447acab8d372</t>
+  </si>
+  <si>
+    <t>69d90aa85cef447acab8ea34</t>
+  </si>
+  <si>
+    <t>69d9014f5cef447acab8e8bc</t>
+  </si>
+  <si>
+    <t>69d935ff5cef447acab8ede5</t>
+  </si>
+  <si>
+    <t>69d89c805cef447acab8d947</t>
+  </si>
+  <si>
+    <t>69d8ae505cef447acab8db7e</t>
+  </si>
+  <si>
+    <t>69d8ae505cef447acab8db80</t>
+  </si>
+  <si>
+    <t>69d8f9115cef447acab8e74e</t>
+  </si>
+  <si>
+    <t>69d917905cef447acab8ebce</t>
+  </si>
+  <si>
+    <t>69dcb3755cef447acab90bc4</t>
+  </si>
+  <si>
+    <t>69da49a15cef447acab8f857</t>
+  </si>
+  <si>
+    <t>69dbb01d5cef447acab90300</t>
+  </si>
+  <si>
+    <t>69dba31b5cef447acab9024a</t>
+  </si>
+  <si>
+    <t>69dcc1cb5cef447acab90deb</t>
+  </si>
+  <si>
+    <t>69dcb1e15cef447acab90b7a</t>
+  </si>
+  <si>
+    <t>69dcb1e15cef447acab90b7b</t>
+  </si>
+  <si>
+    <t>69dc95ba5cef447acab906e1</t>
+  </si>
+  <si>
+    <t>69dcad275cef447acab90aa9</t>
+  </si>
+  <si>
+    <t>1449-167564</t>
+  </si>
+  <si>
+    <t>FIZZ-1000861023</t>
+  </si>
+  <si>
+    <t>FIZZ-1000868812</t>
+  </si>
+  <si>
+    <t>FIZZ-1000869350</t>
+  </si>
+  <si>
+    <t>FIZZ-1000869999</t>
+  </si>
+  <si>
+    <t>FIZZ-1000870832</t>
+  </si>
+  <si>
+    <t>FIZZ-1000870939</t>
+  </si>
+  <si>
+    <t>301281314/1</t>
+  </si>
+  <si>
+    <t>304875752/1</t>
+  </si>
+  <si>
+    <t>304875752/2</t>
+  </si>
+  <si>
+    <t>306457853/1</t>
+  </si>
+  <si>
+    <t>306457853/2</t>
+  </si>
+  <si>
+    <t>306621355/1</t>
+  </si>
+  <si>
+    <t>306721180/1</t>
+  </si>
+  <si>
+    <t>306823736/1</t>
+  </si>
+  <si>
+    <t>306890648/2/1</t>
+  </si>
+  <si>
+    <t>306890648/2/2</t>
+  </si>
+  <si>
+    <t>307081145/1</t>
+  </si>
+  <si>
+    <t>307081145/2</t>
+  </si>
+  <si>
+    <t>307141764/1</t>
+  </si>
+  <si>
+    <t>307141764/2</t>
+  </si>
+  <si>
+    <t>307141884/1</t>
+  </si>
+  <si>
+    <t>307198032/1</t>
+  </si>
+  <si>
+    <t>307198032/2</t>
+  </si>
+  <si>
+    <t>307198032/3</t>
+  </si>
+  <si>
+    <t>307238580/1</t>
+  </si>
+  <si>
+    <t>307279136/1</t>
+  </si>
+  <si>
+    <t>307279136/2</t>
+  </si>
+  <si>
+    <t>307343085/1</t>
+  </si>
+  <si>
+    <t>307343452/1</t>
+  </si>
+  <si>
+    <t>307343662/1</t>
+  </si>
+  <si>
+    <t>307378990/1</t>
+  </si>
+  <si>
+    <t>307379683/1</t>
+  </si>
+  <si>
+    <t>307379683/2</t>
+  </si>
+  <si>
+    <t>307426249/1</t>
+  </si>
+  <si>
+    <t>307426249/2</t>
+  </si>
+  <si>
+    <t>307426300/1</t>
+  </si>
+  <si>
+    <t>307427054/1</t>
+  </si>
+  <si>
+    <t>307427054/2</t>
+  </si>
+  <si>
+    <t>307482603/1</t>
+  </si>
+  <si>
+    <t>307482949/1</t>
+  </si>
+  <si>
+    <t>307482966/1</t>
+  </si>
+  <si>
+    <t>307483162/1</t>
+  </si>
+  <si>
+    <t>307530057/1</t>
+  </si>
+  <si>
+    <t>307530383/1</t>
+  </si>
+  <si>
+    <t>307530443/1</t>
+  </si>
+  <si>
+    <t>307530746/1</t>
+  </si>
+  <si>
+    <t>307530770/1</t>
+  </si>
+  <si>
+    <t>307579435/1</t>
+  </si>
+  <si>
+    <t>307579464/1</t>
+  </si>
+  <si>
+    <t>307579514/1</t>
+  </si>
+  <si>
+    <t>307579536/1</t>
+  </si>
+  <si>
+    <t>307579705/1</t>
+  </si>
+  <si>
+    <t>307579705/2</t>
+  </si>
+  <si>
+    <t>307579813/1</t>
+  </si>
+  <si>
+    <t>307579813/2</t>
+  </si>
+  <si>
+    <t>307579992/1</t>
+  </si>
+  <si>
+    <t>307627776/1</t>
+  </si>
+  <si>
+    <t>307627826/1</t>
+  </si>
+  <si>
+    <t>307627906/1</t>
+  </si>
+  <si>
+    <t>307628001/1</t>
+  </si>
+  <si>
+    <t>307628048/1</t>
+  </si>
+  <si>
+    <t>307628153/1</t>
+  </si>
+  <si>
+    <t>307628153/2</t>
+  </si>
+  <si>
+    <t>307628223/1</t>
+  </si>
+  <si>
+    <t>307628548/1</t>
+  </si>
+  <si>
+    <t>307628658/1</t>
+  </si>
+  <si>
+    <t>307628658/2</t>
+  </si>
+  <si>
+    <t>307688669/1</t>
+  </si>
+  <si>
+    <t>307688816/1</t>
+  </si>
+  <si>
+    <t>307688992/1</t>
+  </si>
+  <si>
+    <t>307689103/1</t>
+  </si>
+  <si>
+    <t>307689158/1</t>
+  </si>
+  <si>
+    <t>307689164/1</t>
+  </si>
+  <si>
+    <t>307689174/1</t>
+  </si>
+  <si>
+    <t>307689224/1</t>
+  </si>
+  <si>
+    <t>307689459/1</t>
+  </si>
+  <si>
+    <t>307689522/1</t>
+  </si>
+  <si>
+    <t>307689552/1</t>
+  </si>
+  <si>
+    <t>307740581/1</t>
+  </si>
+  <si>
+    <t>307740878/1</t>
+  </si>
+  <si>
+    <t>307740887/1</t>
+  </si>
+  <si>
+    <t>307741091/1</t>
+  </si>
+  <si>
+    <t>307741229/1</t>
+  </si>
+  <si>
+    <t>307741234/1</t>
+  </si>
+  <si>
+    <t>307741341/1</t>
+  </si>
+  <si>
+    <t>307806234/1</t>
+  </si>
+  <si>
+    <t>307806234/2</t>
+  </si>
+  <si>
+    <t>307806310/1</t>
+  </si>
+  <si>
+    <t>307806404/1</t>
+  </si>
+  <si>
+    <t>307806426/1</t>
+  </si>
+  <si>
+    <t>307806470/1</t>
+  </si>
+  <si>
+    <t>307806535/1</t>
+  </si>
+  <si>
+    <t>307806552/1</t>
+  </si>
+  <si>
+    <t>307806590/1</t>
+  </si>
+  <si>
+    <t>307806699/1</t>
+  </si>
+  <si>
+    <t>307806757/1</t>
+  </si>
+  <si>
+    <t>307806757/2</t>
+  </si>
+  <si>
+    <t>307806757/3</t>
+  </si>
+  <si>
+    <t>307806941/1</t>
+  </si>
+  <si>
+    <t>307806973/1</t>
+  </si>
+  <si>
+    <t>307807008/1</t>
+  </si>
+  <si>
+    <t>202604132600784501</t>
+  </si>
+  <si>
+    <t>202604132600811501</t>
+  </si>
+  <si>
+    <t>202604092600825401</t>
+  </si>
+  <si>
+    <t>202604102600830201</t>
+  </si>
+  <si>
+    <t>202604102600829101</t>
+  </si>
+  <si>
+    <t>202604102600829102</t>
+  </si>
+  <si>
+    <t>202604102600829103</t>
+  </si>
+  <si>
+    <t>202604102600829104</t>
+  </si>
+  <si>
+    <t>202604102600829105</t>
+  </si>
+  <si>
+    <t>202604102600829106</t>
+  </si>
+  <si>
+    <t>202604102600829107</t>
+  </si>
+  <si>
+    <t>202604132600837401</t>
+  </si>
+  <si>
+    <t>202604132600840901</t>
+  </si>
+  <si>
+    <t>202604132600843401</t>
+  </si>
+  <si>
+    <t>202604132600836301</t>
+  </si>
+  <si>
+    <t>202604132600837301</t>
+  </si>
+  <si>
+    <t>202604132600840101</t>
+  </si>
+  <si>
+    <t>202604132600844401</t>
+  </si>
+  <si>
+    <t>202604132600841901</t>
+  </si>
+  <si>
+    <t>202604132600841501</t>
+  </si>
+  <si>
+    <t>202604132600838501</t>
+  </si>
+  <si>
+    <t>202604132600840401</t>
+  </si>
+  <si>
+    <t>202604132600840001</t>
+  </si>
+  <si>
+    <t>202604132600840002</t>
+  </si>
+  <si>
+    <t>202604132600844101</t>
+  </si>
+  <si>
+    <t>202604132600846401</t>
+  </si>
+  <si>
+    <t>202604132600837101</t>
+  </si>
+  <si>
+    <t>202604132600844501</t>
+  </si>
+  <si>
+    <t>202604132600837201</t>
+  </si>
+  <si>
+    <t>202604132600844001</t>
+  </si>
+  <si>
+    <t>202604132600838901</t>
+  </si>
+  <si>
+    <t>202604132600844601</t>
+  </si>
+  <si>
+    <t>202604132600858301</t>
+  </si>
+  <si>
+    <t>202604132600858302</t>
+  </si>
+  <si>
+    <t>202604132600859501</t>
+  </si>
+  <si>
+    <t>202604132600861201</t>
+  </si>
+  <si>
+    <t>202604132600857001</t>
+  </si>
+  <si>
+    <t>202604132600854201</t>
+  </si>
+  <si>
+    <t>202604132600855401</t>
+  </si>
+  <si>
+    <t>202604132600857901</t>
+  </si>
+  <si>
+    <t>202604132600858401</t>
+  </si>
+  <si>
+    <t>202604132600863001</t>
+  </si>
+  <si>
+    <t>202604132600863801</t>
+  </si>
+  <si>
+    <t>202604132600863802</t>
+  </si>
+  <si>
+    <t>202604132600866601</t>
+  </si>
+  <si>
+    <t>202604132600864301</t>
+  </si>
+  <si>
+    <t>202604132600862601</t>
+  </si>
+  <si>
+    <t>202604132600865101</t>
+  </si>
+  <si>
+    <t>202604132600865102</t>
+  </si>
+  <si>
+    <t>202604132600865103</t>
+  </si>
+  <si>
+    <t>202604132600865104</t>
+  </si>
+  <si>
+    <t>202604132600865105</t>
+  </si>
+  <si>
+    <t>202604132600862001</t>
+  </si>
+  <si>
+    <t>202604132600862002</t>
+  </si>
+  <si>
+    <t>202604132600862003</t>
+  </si>
+  <si>
+    <t>202604132600862004</t>
+  </si>
+  <si>
+    <t>202604132600864801</t>
+  </si>
+  <si>
+    <t>202604132600865201</t>
+  </si>
+  <si>
+    <t>202604132600864401</t>
+  </si>
+  <si>
+    <t>202604102600830801</t>
+  </si>
+  <si>
+    <t>202604132600859001</t>
+  </si>
+  <si>
+    <t>202604132600859002</t>
+  </si>
+  <si>
+    <t>202604132600856001</t>
+  </si>
+  <si>
+    <t>202604132600856002</t>
+  </si>
+  <si>
+    <t>202604132600856003</t>
+  </si>
+  <si>
+    <t>202604132600856004</t>
+  </si>
+  <si>
+    <t>159995579539076359</t>
+  </si>
+  <si>
+    <t>159995579539076366</t>
+  </si>
+  <si>
+    <t>159995579539076373</t>
+  </si>
+  <si>
+    <t>159995579539076380</t>
+  </si>
+  <si>
+    <t>159995579539076397</t>
+  </si>
+  <si>
+    <t>159995579539076281</t>
+  </si>
+  <si>
+    <t>159995579538917837</t>
+  </si>
+  <si>
+    <t>159995579538917844</t>
+  </si>
+  <si>
+    <t>1-3059/2026</t>
+  </si>
+  <si>
+    <t>267004770</t>
+  </si>
+  <si>
+    <t>267004888</t>
+  </si>
+  <si>
+    <t>267005103</t>
+  </si>
+  <si>
+    <t>267005111</t>
+  </si>
+  <si>
+    <t>267005156</t>
+  </si>
+  <si>
+    <t>267005161</t>
+  </si>
+  <si>
+    <t>267005164</t>
+  </si>
+  <si>
+    <t>NFD6-04-02-537V</t>
+  </si>
+  <si>
+    <t>NFD6-04-07-VGNX</t>
+  </si>
+  <si>
+    <t>NFD6-04-08-VQLD</t>
+  </si>
+  <si>
+    <t>NFD6-04-09-GCSW</t>
+  </si>
+  <si>
+    <t>NFD6-04-09-WNFS</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-2N8Q</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-37AR</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-5QWF</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-5ZLZ</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-ABK2</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-BS88</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-CH4X</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-CUEF</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-DZ8P</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-ERL8</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-FEAT</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-GQGC</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-HPMX</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-L3H6</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-L7L2</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-NASX</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-SC2K</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-VE4L</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-XG52</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-ZCW2</t>
+  </si>
+  <si>
+    <t>NFD6-04-11-ANMF</t>
+  </si>
+  <si>
+    <t>NFD6-04-11-KK77</t>
+  </si>
+  <si>
+    <t>NFD6-04-11-KQD9</t>
+  </si>
+  <si>
+    <t>NFD6-04-11-KVJ9</t>
+  </si>
+  <si>
+    <t>NFD6-04-11-LPP4</t>
+  </si>
+  <si>
+    <t>NFD6-04-11-TZQR</t>
+  </si>
+  <si>
+    <t>NFD6-04-11-W7RD</t>
+  </si>
+  <si>
+    <t>NFD6-04-11-WS9L</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-2E7D</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-2RYP</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-2YG9</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-4ECA</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-55F4</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-6N7A</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-7CCY</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-GVVJ</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-JVPH</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-RD45</t>
+  </si>
+  <si>
+    <t>NFE6-04-09-7WKK</t>
+  </si>
+  <si>
+    <t>NFE6-04-11-P6L8</t>
+  </si>
+  <si>
+    <t>NFE6-04-11-SUUL</t>
+  </si>
+  <si>
+    <t>R415499</t>
+  </si>
+  <si>
+    <t>R416494</t>
+  </si>
+  <si>
+    <t>SA26/H001709</t>
   </si>
 </sst>
 </file>
@@ -414,10 +1308,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -699,16 +1592,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D114"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D222"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -719,1049 +1612,2549 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B2" t="s">
+        <v>137</v>
       </c>
       <c r="C2" t="s">
         <v>116</v>
       </c>
       <c r="D2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D4"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="B5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
-        <v>116</v>
-      </c>
-      <c r="D5"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="B6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="B7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="C7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="B8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>3</v>
       </c>
-      <c r="C8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="B9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="B10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="C10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D10"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="B11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="C11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D11"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="B12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>15</v>
       </c>
-      <c r="C12" t="s">
-        <v>116</v>
-      </c>
-      <c r="D12"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="B14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>16</v>
       </c>
-      <c r="C13" t="s">
-        <v>116</v>
-      </c>
-      <c r="D13"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="B15" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>17</v>
       </c>
-      <c r="C14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" t="s">
-        <v>116</v>
-      </c>
-      <c r="D15"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>19</v>
+      <c r="B16" t="s">
+        <v>151</v>
       </c>
       <c r="C16" t="s">
         <v>116</v>
       </c>
       <c r="D16"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C17" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>154</v>
+      </c>
+      <c r="C19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>155</v>
+      </c>
+      <c r="C20" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="C17" t="s">
-        <v>116</v>
-      </c>
-      <c r="D17"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D18"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" t="s">
-        <v>116</v>
-      </c>
-      <c r="D19"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" t="s">
-        <v>116</v>
-      </c>
-      <c r="D20"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>24</v>
+      <c r="B21" t="s">
+        <v>156</v>
       </c>
       <c r="C21" t="s">
         <v>116</v>
       </c>
       <c r="D21"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>25</v>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>157</v>
       </c>
       <c r="C22" t="s">
         <v>116</v>
       </c>
       <c r="D22"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>158</v>
+      </c>
+      <c r="C23" t="s">
+        <v>125</v>
+      </c>
+      <c r="D23"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>160</v>
+      </c>
+      <c r="C25" t="s">
+        <v>122</v>
+      </c>
+      <c r="D25"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>161</v>
+      </c>
+      <c r="C26" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>162</v>
+      </c>
+      <c r="C27" t="s">
+        <v>126</v>
+      </c>
+      <c r="D27"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>163</v>
+      </c>
+      <c r="C28" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>164</v>
+      </c>
+      <c r="C29" t="s">
+        <v>127</v>
+      </c>
+      <c r="D29"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>26</v>
       </c>
-      <c r="C23" t="s">
-        <v>116</v>
-      </c>
-      <c r="D23"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="B30" t="s">
+        <v>165</v>
+      </c>
+      <c r="C30" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>27</v>
       </c>
-      <c r="C24" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="B31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C31" t="s">
+        <v>129</v>
+      </c>
+      <c r="D31"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>28</v>
       </c>
-      <c r="C25" t="s">
-        <v>116</v>
-      </c>
-      <c r="D25"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="B32" t="s">
+        <v>167</v>
+      </c>
+      <c r="C32" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>29</v>
       </c>
-      <c r="C26" t="s">
-        <v>116</v>
-      </c>
-      <c r="D26"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="B33" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" t="s">
+        <v>129</v>
+      </c>
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="C27" t="s">
-        <v>116</v>
-      </c>
-      <c r="D27"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="B34" t="s">
+        <v>169</v>
+      </c>
+      <c r="C34" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" t="s">
+        <v>170</v>
+      </c>
+      <c r="C35" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>31</v>
       </c>
-      <c r="C28" t="s">
-        <v>116</v>
-      </c>
-      <c r="D28"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="B36" t="s">
+        <v>171</v>
+      </c>
+      <c r="C36" t="s">
+        <v>129</v>
+      </c>
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>32</v>
       </c>
-      <c r="C29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D29"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="B37" t="s">
+        <v>172</v>
+      </c>
+      <c r="C37" t="s">
+        <v>119</v>
+      </c>
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>33</v>
       </c>
-      <c r="C30" t="s">
-        <v>116</v>
-      </c>
-      <c r="D30"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="B38" t="s">
+        <v>173</v>
+      </c>
+      <c r="C38" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>34</v>
       </c>
-      <c r="C31" t="s">
-        <v>116</v>
-      </c>
-      <c r="D31"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+      <c r="B39" t="s">
+        <v>174</v>
+      </c>
+      <c r="C39" t="s">
+        <v>131</v>
+      </c>
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>35</v>
       </c>
-      <c r="C32" t="s">
-        <v>116</v>
-      </c>
-      <c r="D32"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+      <c r="B40" t="s">
+        <v>175</v>
+      </c>
+      <c r="C40" t="s">
+        <v>132</v>
+      </c>
+      <c r="D40"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>36</v>
       </c>
-      <c r="C33" t="s">
-        <v>116</v>
-      </c>
-      <c r="D33"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="B41" t="s">
+        <v>176</v>
+      </c>
+      <c r="C41" t="s">
+        <v>119</v>
+      </c>
+      <c r="D41"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>37</v>
       </c>
-      <c r="C34" t="s">
-        <v>116</v>
-      </c>
-      <c r="D34"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+      <c r="B42" t="s">
+        <v>177</v>
+      </c>
+      <c r="C42" t="s">
+        <v>133</v>
+      </c>
+      <c r="D42"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>38</v>
       </c>
-      <c r="C35" t="s">
-        <v>116</v>
-      </c>
-      <c r="D35"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="B43" t="s">
+        <v>178</v>
+      </c>
+      <c r="C43" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" t="s">
+        <v>179</v>
+      </c>
+      <c r="C44" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>39</v>
       </c>
-      <c r="C36" t="s">
-        <v>116</v>
-      </c>
-      <c r="D36"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C37" t="s">
-        <v>116</v>
-      </c>
-      <c r="D37"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C38" t="s">
-        <v>116</v>
-      </c>
-      <c r="D38"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C39" t="s">
-        <v>116</v>
-      </c>
-      <c r="D39"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" t="s">
-        <v>116</v>
-      </c>
-      <c r="D40"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C41" t="s">
-        <v>116</v>
-      </c>
-      <c r="D41"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C42" t="s">
-        <v>116</v>
-      </c>
-      <c r="D42"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" t="s">
-        <v>116</v>
-      </c>
-      <c r="D43"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C44" t="s">
-        <v>116</v>
-      </c>
-      <c r="D44"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>48</v>
+      <c r="B45" t="s">
+        <v>180</v>
       </c>
       <c r="C45" t="s">
         <v>116</v>
       </c>
       <c r="D45"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>49</v>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" t="s">
+        <v>181</v>
       </c>
       <c r="C46" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D46"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>4</v>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>359</v>
+      </c>
+      <c r="B47" t="s">
+        <v>182</v>
       </c>
       <c r="C47" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D47"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>50</v>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>360</v>
+      </c>
+      <c r="B48" t="s">
+        <v>183</v>
       </c>
       <c r="C48" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D48"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>51</v>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>361</v>
+      </c>
+      <c r="B49" t="s">
+        <v>184</v>
       </c>
       <c r="C49" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="D49"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>52</v>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>362</v>
+      </c>
+      <c r="B50" t="s">
+        <v>185</v>
       </c>
       <c r="C50" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="D50"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>53</v>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>363</v>
+      </c>
+      <c r="B51" t="s">
+        <v>186</v>
       </c>
       <c r="C51" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D51"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>54</v>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>364</v>
+      </c>
+      <c r="B52" t="s">
+        <v>187</v>
       </c>
       <c r="C52" t="s">
         <v>116</v>
       </c>
       <c r="D52"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>365</v>
+      </c>
+      <c r="B53" t="s">
+        <v>188</v>
+      </c>
+      <c r="C53" t="s">
+        <v>123</v>
+      </c>
+      <c r="D53"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>41</v>
+      </c>
+      <c r="B54" t="s">
+        <v>189</v>
+      </c>
+      <c r="C54" t="s">
+        <v>132</v>
+      </c>
+      <c r="D54"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" t="s">
+        <v>190</v>
+      </c>
+      <c r="C55" t="s">
+        <v>118</v>
+      </c>
+      <c r="D55"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" t="s">
+        <v>191</v>
+      </c>
+      <c r="C56" t="s">
+        <v>118</v>
+      </c>
+      <c r="D56"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" t="s">
+        <v>192</v>
+      </c>
+      <c r="C57" t="s">
+        <v>124</v>
+      </c>
+      <c r="D57"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" t="s">
+        <v>193</v>
+      </c>
+      <c r="C58" t="s">
+        <v>124</v>
+      </c>
+      <c r="D58"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" t="s">
+        <v>194</v>
+      </c>
+      <c r="C59" t="s">
+        <v>129</v>
+      </c>
+      <c r="D59"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" t="s">
+        <v>195</v>
+      </c>
+      <c r="C60" t="s">
+        <v>119</v>
+      </c>
+      <c r="D60"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>46</v>
+      </c>
+      <c r="B61" t="s">
+        <v>196</v>
+      </c>
+      <c r="C61" t="s">
+        <v>122</v>
+      </c>
+      <c r="D61"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>47</v>
+      </c>
+      <c r="B62" t="s">
+        <v>197</v>
+      </c>
+      <c r="C62" t="s">
+        <v>117</v>
+      </c>
+      <c r="D62"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>47</v>
+      </c>
+      <c r="B63" t="s">
+        <v>198</v>
+      </c>
+      <c r="C63" t="s">
+        <v>117</v>
+      </c>
+      <c r="D63"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>48</v>
+      </c>
+      <c r="B64" t="s">
+        <v>199</v>
+      </c>
+      <c r="C64" t="s">
+        <v>134</v>
+      </c>
+      <c r="D64"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>48</v>
+      </c>
+      <c r="B65" t="s">
+        <v>200</v>
+      </c>
+      <c r="C65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D65"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>49</v>
+      </c>
+      <c r="B66" t="s">
+        <v>201</v>
+      </c>
+      <c r="C66" t="s">
+        <v>121</v>
+      </c>
+      <c r="D66"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>49</v>
+      </c>
+      <c r="B67" t="s">
+        <v>202</v>
+      </c>
+      <c r="C67" t="s">
+        <v>121</v>
+      </c>
+      <c r="D67"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" t="s">
+        <v>203</v>
+      </c>
+      <c r="C68" t="s">
+        <v>119</v>
+      </c>
+      <c r="D68"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>50</v>
+      </c>
+      <c r="B69" t="s">
+        <v>204</v>
+      </c>
+      <c r="C69" t="s">
+        <v>127</v>
+      </c>
+      <c r="D69"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>50</v>
+      </c>
+      <c r="B70" t="s">
+        <v>205</v>
+      </c>
+      <c r="C70" t="s">
+        <v>127</v>
+      </c>
+      <c r="D70"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>50</v>
+      </c>
+      <c r="B71" t="s">
+        <v>206</v>
+      </c>
+      <c r="C71" t="s">
+        <v>127</v>
+      </c>
+      <c r="D71"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>51</v>
+      </c>
+      <c r="B72" t="s">
+        <v>207</v>
+      </c>
+      <c r="C72" t="s">
+        <v>135</v>
+      </c>
+      <c r="D72"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>52</v>
+      </c>
+      <c r="B73" t="s">
+        <v>208</v>
+      </c>
+      <c r="C73" t="s">
+        <v>122</v>
+      </c>
+      <c r="D73"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>52</v>
+      </c>
+      <c r="B74" t="s">
+        <v>209</v>
+      </c>
+      <c r="C74" t="s">
+        <v>122</v>
+      </c>
+      <c r="D74"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>53</v>
+      </c>
+      <c r="B75" t="s">
+        <v>210</v>
+      </c>
+      <c r="C75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D75"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>54</v>
+      </c>
+      <c r="B76" t="s">
+        <v>211</v>
+      </c>
+      <c r="C76" t="s">
+        <v>120</v>
+      </c>
+      <c r="D76"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>55</v>
       </c>
-      <c r="C53" t="s">
-        <v>116</v>
-      </c>
-      <c r="D53"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
+      <c r="B77" t="s">
+        <v>212</v>
+      </c>
+      <c r="C77" t="s">
+        <v>133</v>
+      </c>
+      <c r="D77"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>56</v>
       </c>
-      <c r="C54" t="s">
-        <v>116</v>
-      </c>
-      <c r="D54"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C55" t="s">
-        <v>116</v>
-      </c>
-      <c r="D55"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C56" t="s">
-        <v>116</v>
-      </c>
-      <c r="D56"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C57" t="s">
-        <v>116</v>
-      </c>
-      <c r="D57"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C58" t="s">
-        <v>116</v>
-      </c>
-      <c r="D58"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C59" t="s">
-        <v>116</v>
-      </c>
-      <c r="D59"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C60" t="s">
-        <v>116</v>
-      </c>
-      <c r="D60"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C61" t="s">
-        <v>116</v>
-      </c>
-      <c r="D61"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C62" t="s">
-        <v>116</v>
-      </c>
-      <c r="D62"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C63" t="s">
-        <v>116</v>
-      </c>
-      <c r="D63"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C64" t="s">
-        <v>116</v>
-      </c>
-      <c r="D64"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C65" t="s">
-        <v>116</v>
-      </c>
-      <c r="D65"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C66" t="s">
-        <v>116</v>
-      </c>
-      <c r="D66"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C67" t="s">
-        <v>116</v>
-      </c>
-      <c r="D67"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C68" t="s">
-        <v>116</v>
-      </c>
-      <c r="D68"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C69" t="s">
-        <v>116</v>
-      </c>
-      <c r="D69"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C70" t="s">
-        <v>116</v>
-      </c>
-      <c r="D70"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C71" t="s">
-        <v>116</v>
-      </c>
-      <c r="D71"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C72" t="s">
-        <v>116</v>
-      </c>
-      <c r="D72"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C73" t="s">
-        <v>116</v>
-      </c>
-      <c r="D73"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C74" t="s">
-        <v>116</v>
-      </c>
-      <c r="D74"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C75" t="s">
-        <v>116</v>
-      </c>
-      <c r="D75"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C76" t="s">
-        <v>116</v>
-      </c>
-      <c r="D76"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C77" t="s">
-        <v>116</v>
-      </c>
-      <c r="D77"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
-        <v>80</v>
+      <c r="B78" t="s">
+        <v>213</v>
       </c>
       <c r="C78" t="s">
         <v>116</v>
       </c>
       <c r="D78"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
-        <v>81</v>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>57</v>
+      </c>
+      <c r="B79" t="s">
+        <v>214</v>
       </c>
       <c r="C79" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D79"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
-        <v>5</v>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>57</v>
+      </c>
+      <c r="B80" t="s">
+        <v>215</v>
       </c>
       <c r="C80" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D80"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
-        <v>82</v>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>58</v>
+      </c>
+      <c r="B81" t="s">
+        <v>216</v>
       </c>
       <c r="C81" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D81"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
-        <v>83</v>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>58</v>
+      </c>
+      <c r="B82" t="s">
+        <v>217</v>
       </c>
       <c r="C82" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D82"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="2" t="s">
-        <v>84</v>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>59</v>
+      </c>
+      <c r="B83" t="s">
+        <v>218</v>
       </c>
       <c r="C83" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D83"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
-        <v>85</v>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>60</v>
+      </c>
+      <c r="B84" t="s">
+        <v>219</v>
       </c>
       <c r="C84" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D84"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="2" t="s">
-        <v>86</v>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>60</v>
+      </c>
+      <c r="B85" t="s">
+        <v>220</v>
       </c>
       <c r="C85" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D85"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
-        <v>87</v>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>61</v>
+      </c>
+      <c r="B86" t="s">
+        <v>221</v>
       </c>
       <c r="C86" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D86"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
-        <v>88</v>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>62</v>
+      </c>
+      <c r="B87" t="s">
+        <v>222</v>
       </c>
       <c r="C87" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="D87"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B88" s="1"/>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>63</v>
+      </c>
+      <c r="B88" t="s">
+        <v>223</v>
+      </c>
       <c r="C88" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D88"/>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B89" s="1"/>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>64</v>
+      </c>
+      <c r="B89" t="s">
+        <v>224</v>
+      </c>
       <c r="C89" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D89"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B90" s="1"/>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>65</v>
+      </c>
+      <c r="B90" t="s">
+        <v>225</v>
+      </c>
       <c r="C90" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D90"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B91" s="1"/>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>66</v>
+      </c>
+      <c r="B91" t="s">
+        <v>226</v>
+      </c>
       <c r="C91" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="D91"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B92" s="1"/>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>67</v>
+      </c>
+      <c r="B92" t="s">
+        <v>227</v>
+      </c>
       <c r="C92" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D92"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B93" s="1"/>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>68</v>
+      </c>
+      <c r="B93" t="s">
+        <v>228</v>
+      </c>
       <c r="C93" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="D93"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B94" s="1"/>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>69</v>
+      </c>
+      <c r="B94" t="s">
+        <v>229</v>
+      </c>
       <c r="C94" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D94"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B95" s="1"/>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>70</v>
+      </c>
+      <c r="B95" t="s">
+        <v>230</v>
+      </c>
       <c r="C95" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="D95"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B96" s="1"/>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>71</v>
+      </c>
+      <c r="B96" t="s">
+        <v>231</v>
+      </c>
       <c r="C96" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="D96"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B97" s="1"/>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>72</v>
+      </c>
+      <c r="B97" t="s">
+        <v>232</v>
+      </c>
       <c r="C97" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D97"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B98" s="1"/>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>73</v>
+      </c>
+      <c r="B98" t="s">
+        <v>233</v>
+      </c>
       <c r="C98" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D98"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B99" s="1"/>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>74</v>
+      </c>
+      <c r="B99" t="s">
+        <v>234</v>
+      </c>
       <c r="C99" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="D99"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B100" s="1"/>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>74</v>
+      </c>
+      <c r="B100" t="s">
+        <v>235</v>
+      </c>
       <c r="C100" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="D100"/>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B101" s="1"/>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>75</v>
+      </c>
+      <c r="B101" t="s">
+        <v>236</v>
+      </c>
       <c r="C101" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="D101"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B102" s="1"/>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>75</v>
+      </c>
+      <c r="B102" t="s">
+        <v>237</v>
+      </c>
       <c r="C102" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="D102"/>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B103" s="1"/>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>76</v>
+      </c>
+      <c r="B103" t="s">
+        <v>238</v>
+      </c>
       <c r="C103" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="D103"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B104" s="1"/>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>77</v>
+      </c>
+      <c r="B104" t="s">
+        <v>239</v>
+      </c>
       <c r="C104" t="s">
         <v>116</v>
       </c>
       <c r="D104"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B105" s="1"/>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>78</v>
+      </c>
+      <c r="B105" t="s">
+        <v>240</v>
+      </c>
       <c r="C105" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="D105"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B106" s="1"/>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>79</v>
+      </c>
+      <c r="B106" t="s">
+        <v>241</v>
+      </c>
       <c r="C106" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="D106"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B107" s="1"/>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>80</v>
+      </c>
+      <c r="B107" t="s">
+        <v>242</v>
+      </c>
       <c r="C107" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="D107"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B108" s="1"/>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>81</v>
+      </c>
+      <c r="B108" t="s">
+        <v>243</v>
+      </c>
       <c r="C108" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D108"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B109" s="1"/>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>5</v>
+      </c>
+      <c r="B109" t="s">
+        <v>244</v>
+      </c>
       <c r="C109" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D109"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B110" s="1"/>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>5</v>
+      </c>
+      <c r="B110" t="s">
+        <v>245</v>
+      </c>
       <c r="C110" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D110"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B111" s="1"/>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>82</v>
+      </c>
+      <c r="B111" t="s">
+        <v>246</v>
+      </c>
       <c r="C111" t="s">
         <v>116</v>
       </c>
       <c r="D111"/>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="2" t="s">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>83</v>
+      </c>
+      <c r="B112" t="s">
+        <v>247</v>
+      </c>
+      <c r="C112" t="s">
+        <v>133</v>
+      </c>
+      <c r="D112"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>84</v>
+      </c>
+      <c r="B113" t="s">
+        <v>248</v>
+      </c>
+      <c r="C113" t="s">
+        <v>132</v>
+      </c>
+      <c r="D113"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>84</v>
+      </c>
+      <c r="B114" t="s">
+        <v>249</v>
+      </c>
+      <c r="C114" t="s">
+        <v>132</v>
+      </c>
+      <c r="D114"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>85</v>
+      </c>
+      <c r="B115" t="s">
+        <v>250</v>
+      </c>
+      <c r="C115" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>86</v>
+      </c>
+      <c r="B116" t="s">
+        <v>251</v>
+      </c>
+      <c r="C116" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>87</v>
+      </c>
+      <c r="B117" t="s">
+        <v>252</v>
+      </c>
+      <c r="C117" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>88</v>
+      </c>
+      <c r="B118" t="s">
+        <v>253</v>
+      </c>
+      <c r="C118" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>89</v>
+      </c>
+      <c r="B119" t="s">
+        <v>254</v>
+      </c>
+      <c r="C119" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>90</v>
+      </c>
+      <c r="B120" t="s">
+        <v>255</v>
+      </c>
+      <c r="C120" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>91</v>
+      </c>
+      <c r="B121" t="s">
+        <v>256</v>
+      </c>
+      <c r="C121" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>92</v>
+      </c>
+      <c r="B122" t="s">
+        <v>257</v>
+      </c>
+      <c r="C122" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>93</v>
+      </c>
+      <c r="B123" t="s">
+        <v>258</v>
+      </c>
+      <c r="C123" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>94</v>
+      </c>
+      <c r="B124" t="s">
+        <v>259</v>
+      </c>
+      <c r="C124" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>95</v>
+      </c>
+      <c r="B125" t="s">
+        <v>260</v>
+      </c>
+      <c r="C125" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>96</v>
+      </c>
+      <c r="B126" t="s">
+        <v>261</v>
+      </c>
+      <c r="C126" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>97</v>
+      </c>
+      <c r="B127" t="s">
+        <v>262</v>
+      </c>
+      <c r="C127" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>98</v>
+      </c>
+      <c r="B128" t="s">
+        <v>263</v>
+      </c>
+      <c r="C128" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>99</v>
+      </c>
+      <c r="B129" t="s">
+        <v>264</v>
+      </c>
+      <c r="C129" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>100</v>
+      </c>
+      <c r="B130" t="s">
+        <v>265</v>
+      </c>
+      <c r="C130" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>101</v>
+      </c>
+      <c r="B131" t="s">
+        <v>266</v>
+      </c>
+      <c r="C131" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>102</v>
+      </c>
+      <c r="B132" t="s">
+        <v>267</v>
+      </c>
+      <c r="C132" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>103</v>
+      </c>
+      <c r="B133" t="s">
+        <v>268</v>
+      </c>
+      <c r="C133" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>103</v>
+      </c>
+      <c r="B134" t="s">
+        <v>269</v>
+      </c>
+      <c r="C134" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>104</v>
+      </c>
+      <c r="B135" t="s">
+        <v>270</v>
+      </c>
+      <c r="C135" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>105</v>
+      </c>
+      <c r="B136" t="s">
+        <v>271</v>
+      </c>
+      <c r="C136" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>106</v>
+      </c>
+      <c r="B137" t="s">
+        <v>272</v>
+      </c>
+      <c r="C137" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>107</v>
+      </c>
+      <c r="B138" t="s">
+        <v>273</v>
+      </c>
+      <c r="C138" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>108</v>
+      </c>
+      <c r="B139" t="s">
+        <v>274</v>
+      </c>
+      <c r="C139" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>109</v>
+      </c>
+      <c r="B140" t="s">
+        <v>275</v>
+      </c>
+      <c r="C140" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>110</v>
+      </c>
+      <c r="B141" t="s">
+        <v>276</v>
+      </c>
+      <c r="C141" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>111</v>
+      </c>
+      <c r="B142" t="s">
+        <v>277</v>
+      </c>
+      <c r="C142" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>112</v>
+      </c>
+      <c r="B143" t="s">
+        <v>278</v>
+      </c>
+      <c r="C143" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>112</v>
+      </c>
+      <c r="B144" t="s">
+        <v>279</v>
+      </c>
+      <c r="C144" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>112</v>
+      </c>
+      <c r="B145" t="s">
+        <v>280</v>
+      </c>
+      <c r="C145" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
         <v>113</v>
       </c>
-      <c r="B112" s="1"/>
-      <c r="C112" t="s">
+      <c r="B146" t="s">
+        <v>281</v>
+      </c>
+      <c r="C146" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>114</v>
+      </c>
+      <c r="B147" t="s">
+        <v>282</v>
+      </c>
+      <c r="C147" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>115</v>
+      </c>
+      <c r="B148" t="s">
+        <v>283</v>
+      </c>
+      <c r="C148" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>366</v>
+      </c>
+      <c r="B149" t="s">
+        <v>284</v>
+      </c>
+      <c r="C149" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>367</v>
+      </c>
+      <c r="B150" t="s">
+        <v>285</v>
+      </c>
+      <c r="C150" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>368</v>
+      </c>
+      <c r="B151" t="s">
+        <v>286</v>
+      </c>
+      <c r="C151" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>369</v>
+      </c>
+      <c r="B152" t="s">
+        <v>287</v>
+      </c>
+      <c r="C152" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>370</v>
+      </c>
+      <c r="B153" t="s">
+        <v>288</v>
+      </c>
+      <c r="C153" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>370</v>
+      </c>
+      <c r="B154" t="s">
+        <v>289</v>
+      </c>
+      <c r="C154" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>370</v>
+      </c>
+      <c r="B155" t="s">
+        <v>290</v>
+      </c>
+      <c r="C155" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>370</v>
+      </c>
+      <c r="B156" t="s">
+        <v>291</v>
+      </c>
+      <c r="C156" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>370</v>
+      </c>
+      <c r="B157" t="s">
+        <v>292</v>
+      </c>
+      <c r="C157" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>370</v>
+      </c>
+      <c r="B158" t="s">
+        <v>293</v>
+      </c>
+      <c r="C158" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>370</v>
+      </c>
+      <c r="B159" t="s">
+        <v>294</v>
+      </c>
+      <c r="C159" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>371</v>
+      </c>
+      <c r="B160" t="s">
+        <v>295</v>
+      </c>
+      <c r="C160" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>372</v>
+      </c>
+      <c r="B161" t="s">
+        <v>296</v>
+      </c>
+      <c r="C161" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>373</v>
+      </c>
+      <c r="B162" t="s">
+        <v>297</v>
+      </c>
+      <c r="C162" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>374</v>
+      </c>
+      <c r="B163" t="s">
+        <v>298</v>
+      </c>
+      <c r="C163" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>375</v>
+      </c>
+      <c r="B164" t="s">
+        <v>299</v>
+      </c>
+      <c r="C164" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>376</v>
+      </c>
+      <c r="B165" t="s">
+        <v>300</v>
+      </c>
+      <c r="C165" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>377</v>
+      </c>
+      <c r="B166" t="s">
+        <v>301</v>
+      </c>
+      <c r="C166" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>378</v>
+      </c>
+      <c r="B167" t="s">
+        <v>302</v>
+      </c>
+      <c r="C167" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>379</v>
+      </c>
+      <c r="B168" t="s">
+        <v>303</v>
+      </c>
+      <c r="C168" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>380</v>
+      </c>
+      <c r="B169" t="s">
+        <v>304</v>
+      </c>
+      <c r="C169" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>381</v>
+      </c>
+      <c r="B170" t="s">
+        <v>305</v>
+      </c>
+      <c r="C170" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>382</v>
+      </c>
+      <c r="B171" t="s">
+        <v>306</v>
+      </c>
+      <c r="C171" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>382</v>
+      </c>
+      <c r="B172" t="s">
+        <v>307</v>
+      </c>
+      <c r="C172" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>383</v>
+      </c>
+      <c r="B173" t="s">
+        <v>308</v>
+      </c>
+      <c r="C173" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>384</v>
+      </c>
+      <c r="B174" t="s">
+        <v>309</v>
+      </c>
+      <c r="C174" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>385</v>
+      </c>
+      <c r="B175" t="s">
+        <v>310</v>
+      </c>
+      <c r="C175" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>386</v>
+      </c>
+      <c r="B176" t="s">
+        <v>311</v>
+      </c>
+      <c r="C176" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>387</v>
+      </c>
+      <c r="B177" t="s">
+        <v>312</v>
+      </c>
+      <c r="C177" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>388</v>
+      </c>
+      <c r="B178" t="s">
+        <v>313</v>
+      </c>
+      <c r="C178" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>389</v>
+      </c>
+      <c r="B179" t="s">
+        <v>314</v>
+      </c>
+      <c r="C179" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>390</v>
+      </c>
+      <c r="B180" t="s">
+        <v>315</v>
+      </c>
+      <c r="C180" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>391</v>
+      </c>
+      <c r="B181" t="s">
+        <v>316</v>
+      </c>
+      <c r="C181" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>391</v>
+      </c>
+      <c r="B182" t="s">
+        <v>317</v>
+      </c>
+      <c r="C182" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>392</v>
+      </c>
+      <c r="B183" t="s">
+        <v>318</v>
+      </c>
+      <c r="C183" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>393</v>
+      </c>
+      <c r="B184" t="s">
+        <v>319</v>
+      </c>
+      <c r="C184" t="s">
         <v>116</v>
       </c>
-      <c r="D112"/>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B113" s="1"/>
-      <c r="C113" t="s">
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>394</v>
+      </c>
+      <c r="B185" t="s">
+        <v>320</v>
+      </c>
+      <c r="C185" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>395</v>
+      </c>
+      <c r="B186" t="s">
+        <v>321</v>
+      </c>
+      <c r="C186" t="s">
         <v>116</v>
       </c>
-      <c r="D113"/>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B114" s="1"/>
-      <c r="C114" t="s">
-        <v>116</v>
-      </c>
-      <c r="D114"/>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>396</v>
+      </c>
+      <c r="B187" t="s">
+        <v>322</v>
+      </c>
+      <c r="C187" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>397</v>
+      </c>
+      <c r="B188" t="s">
+        <v>323</v>
+      </c>
+      <c r="C188" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>398</v>
+      </c>
+      <c r="B189" t="s">
+        <v>324</v>
+      </c>
+      <c r="C189" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>399</v>
+      </c>
+      <c r="B190" t="s">
+        <v>325</v>
+      </c>
+      <c r="C190" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>400</v>
+      </c>
+      <c r="B191" t="s">
+        <v>326</v>
+      </c>
+      <c r="C191" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>400</v>
+      </c>
+      <c r="B192" t="s">
+        <v>327</v>
+      </c>
+      <c r="C192" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>401</v>
+      </c>
+      <c r="B193" t="s">
+        <v>328</v>
+      </c>
+      <c r="C193" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>402</v>
+      </c>
+      <c r="B194" t="s">
+        <v>329</v>
+      </c>
+      <c r="C194" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>403</v>
+      </c>
+      <c r="B195" t="s">
+        <v>330</v>
+      </c>
+      <c r="C195" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>404</v>
+      </c>
+      <c r="B196" t="s">
+        <v>331</v>
+      </c>
+      <c r="C196" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>404</v>
+      </c>
+      <c r="B197" t="s">
+        <v>332</v>
+      </c>
+      <c r="C197" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>404</v>
+      </c>
+      <c r="B198" t="s">
+        <v>333</v>
+      </c>
+      <c r="C198" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>404</v>
+      </c>
+      <c r="B199" t="s">
+        <v>334</v>
+      </c>
+      <c r="C199" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>404</v>
+      </c>
+      <c r="B200" t="s">
+        <v>335</v>
+      </c>
+      <c r="C200" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>405</v>
+      </c>
+      <c r="B201" t="s">
+        <v>336</v>
+      </c>
+      <c r="C201" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>405</v>
+      </c>
+      <c r="B202" t="s">
+        <v>337</v>
+      </c>
+      <c r="C202" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>405</v>
+      </c>
+      <c r="B203" t="s">
+        <v>338</v>
+      </c>
+      <c r="C203" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>405</v>
+      </c>
+      <c r="B204" t="s">
+        <v>339</v>
+      </c>
+      <c r="C204" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>406</v>
+      </c>
+      <c r="B205" t="s">
+        <v>340</v>
+      </c>
+      <c r="C205" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>407</v>
+      </c>
+      <c r="B206" t="s">
+        <v>341</v>
+      </c>
+      <c r="C206" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>408</v>
+      </c>
+      <c r="B207" t="s">
+        <v>342</v>
+      </c>
+      <c r="C207" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>409</v>
+      </c>
+      <c r="B208" t="s">
+        <v>343</v>
+      </c>
+      <c r="C208" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>410</v>
+      </c>
+      <c r="B209" t="s">
+        <v>344</v>
+      </c>
+      <c r="C209" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>410</v>
+      </c>
+      <c r="B210" t="s">
+        <v>345</v>
+      </c>
+      <c r="C210" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>411</v>
+      </c>
+      <c r="B211" t="s">
+        <v>346</v>
+      </c>
+      <c r="C211" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>411</v>
+      </c>
+      <c r="B212" t="s">
+        <v>347</v>
+      </c>
+      <c r="C212" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>411</v>
+      </c>
+      <c r="B213" t="s">
+        <v>348</v>
+      </c>
+      <c r="C213" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>411</v>
+      </c>
+      <c r="B214" t="s">
+        <v>349</v>
+      </c>
+      <c r="C214" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>412</v>
+      </c>
+      <c r="B215" t="s">
+        <v>350</v>
+      </c>
+      <c r="C215" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>412</v>
+      </c>
+      <c r="B216" t="s">
+        <v>351</v>
+      </c>
+      <c r="C216" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>412</v>
+      </c>
+      <c r="B217" t="s">
+        <v>352</v>
+      </c>
+      <c r="C217" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>412</v>
+      </c>
+      <c r="B218" t="s">
+        <v>353</v>
+      </c>
+      <c r="C218" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>412</v>
+      </c>
+      <c r="B219" t="s">
+        <v>354</v>
+      </c>
+      <c r="C219" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>413</v>
+      </c>
+      <c r="B220" t="s">
+        <v>355</v>
+      </c>
+      <c r="C220" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>414</v>
+      </c>
+      <c r="B221" t="s">
+        <v>356</v>
+      </c>
+      <c r="C221" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>414</v>
+      </c>
+      <c r="B222" t="s">
+        <v>357</v>
+      </c>
+      <c r="C222" t="s">
+        <v>131</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="C1" xr:uid="{66E3D377-5F1B-48CD-A9ED-4AF810829D06}"/>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACFDEEA-2D4A-43AA-941F-B9831D821B02}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CC165D-C2A5-423C-8C40-7FE4A6FFF157}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="327">
   <si>
     <t>UTK</t>
   </si>
@@ -357,7 +357,658 @@
     <t>99002349</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>SZ-840</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-850</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>SZ-810</t>
+  </si>
+  <si>
+    <t>SZ-807</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-8101</t>
+  </si>
+  <si>
+    <t>267004989</t>
+  </si>
+  <si>
+    <t>267005187</t>
+  </si>
+  <si>
+    <t>267005200</t>
+  </si>
+  <si>
+    <t>267005213</t>
+  </si>
+  <si>
+    <t>267005230</t>
+  </si>
+  <si>
+    <t>267005262</t>
+  </si>
+  <si>
+    <t>267005274</t>
+  </si>
+  <si>
+    <t>26MPE0003964</t>
+  </si>
+  <si>
+    <t>26MPE0004014</t>
+  </si>
+  <si>
+    <t>26MPE0004016</t>
+  </si>
+  <si>
+    <t>26MPE0004017</t>
+  </si>
+  <si>
+    <t>NFD6-04-08-DER2</t>
+  </si>
+  <si>
+    <t>NFD6-04-09-JG6D</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-XQV2</t>
+  </si>
+  <si>
+    <t>NFD6-04-13-MJWR</t>
+  </si>
+  <si>
+    <t>NFD6-04-14-3XBE</t>
+  </si>
+  <si>
+    <t>NFD6-04-14-FMAB</t>
+  </si>
+  <si>
+    <t>NFD6-04-14-G7P9</t>
+  </si>
+  <si>
+    <t>NFD6-04-14-HTVX</t>
+  </si>
+  <si>
+    <t>NFD6-04-14-LJHG</t>
+  </si>
+  <si>
+    <t>NFD6-04-14-S2RQ</t>
+  </si>
+  <si>
+    <t>NFE6-04-08-BV2R</t>
+  </si>
+  <si>
+    <t>NFE6-04-09-SZ7H</t>
+  </si>
+  <si>
+    <t>NFE6-04-10-4QLG</t>
+  </si>
+  <si>
+    <t>NFE6-04-13-R4DK</t>
+  </si>
+  <si>
+    <t>NFE6-04-14-FRHH</t>
+  </si>
+  <si>
+    <t>SA26/H001915</t>
+  </si>
+  <si>
+    <t>SA26/H001916</t>
+  </si>
+  <si>
+    <t>NFD6-04-15-5BLZ</t>
+  </si>
+  <si>
+    <t>69ce5dd35cef447acab86aaf</t>
+  </si>
+  <si>
+    <t>69cfeea45cef447acab87794</t>
+  </si>
+  <si>
+    <t>69d0e2625cef447acab87c9b</t>
+  </si>
+  <si>
+    <t>69d0e2625cef447acab87c9c</t>
+  </si>
+  <si>
+    <t>69de14ed5cef447acab925c2</t>
+  </si>
+  <si>
+    <t>69d53bdc5cef447acab8a3cc</t>
+  </si>
+  <si>
+    <t>69d63d805cef447acab8b1c9</t>
+  </si>
+  <si>
+    <t>69de1ce45cef447acab92711</t>
+  </si>
+  <si>
+    <t>69de41b55cef447acab92d59</t>
+  </si>
+  <si>
+    <t>69d68e505cef447acab8bc3a</t>
+  </si>
+  <si>
+    <t>69d9353a5cef447acab8ede2</t>
+  </si>
+  <si>
+    <t>69df57f85cef447acab93c9d</t>
+  </si>
+  <si>
+    <t>69df57f85cef447acab93c9f</t>
+  </si>
+  <si>
+    <t>69d7629d5cef447acab8c29f</t>
+  </si>
+  <si>
+    <t>69d8b3f65cef447acab8dc1a</t>
+  </si>
+  <si>
+    <t>69d8b3f65cef447acab8dc1b</t>
+  </si>
+  <si>
+    <t>69d8ee8d5cef447acab8e5a1</t>
+  </si>
+  <si>
+    <t>69d8ee8d5cef447acab8e5a2</t>
+  </si>
+  <si>
+    <t>69d900235cef447acab8e898</t>
+  </si>
+  <si>
+    <t>69d911ae5cef447acab8eafb</t>
+  </si>
+  <si>
+    <t>69d911ae5cef447acab8eafd</t>
+  </si>
+  <si>
+    <t>69da10275cef447acab8f374</t>
+  </si>
+  <si>
+    <t>69da1a8b5cef447acab8f486</t>
+  </si>
+  <si>
+    <t>69da1a8b5cef447acab8f487</t>
+  </si>
+  <si>
+    <t>69df6f505cef447acab940a0</t>
+  </si>
+  <si>
+    <t>69d9d8f05cef447acab8ef82</t>
+  </si>
+  <si>
+    <t>69d9d8f05cef447acab8ef83</t>
+  </si>
+  <si>
+    <t>69d9e1195cef447acab8ef9a</t>
+  </si>
+  <si>
+    <t>69da1bb05cef447acab8f494</t>
+  </si>
+  <si>
+    <t>69da55215cef447acab8f92d</t>
+  </si>
+  <si>
+    <t>69da66b65cef447acab8fa3d</t>
+  </si>
+  <si>
+    <t>69da66b65cef447acab8fa3e</t>
+  </si>
+  <si>
+    <t>69da690d5cef447acab8fa4d</t>
+  </si>
+  <si>
+    <t>69db630b5cef447acab8fe8c</t>
+  </si>
+  <si>
+    <t>69dbab4f5cef447acab902c3</t>
+  </si>
+  <si>
+    <t>69db5f235cef447acab8fe48</t>
+  </si>
+  <si>
+    <t>69db66295cef447acab8fea6</t>
+  </si>
+  <si>
+    <t>69db66295cef447acab8fea7</t>
+  </si>
+  <si>
+    <t>69dbaed75cef447acab902ed</t>
+  </si>
+  <si>
+    <t>69dbf77b5cef447acab905aa</t>
+  </si>
+  <si>
+    <t>69dd0f8d5cef447acab917dc</t>
+  </si>
+  <si>
+    <t>69dd1a1b5cef447acab918cd</t>
+  </si>
+  <si>
+    <t>69dd2d0f5cef447acab91a24</t>
+  </si>
+  <si>
+    <t>69dd2d0f5cef447acab91a25</t>
+  </si>
+  <si>
+    <t>69dd50025cef447acab91b65</t>
+  </si>
+  <si>
+    <t>69dd50025cef447acab91b66</t>
+  </si>
+  <si>
+    <t>69dd50035cef447acab91b6e</t>
+  </si>
+  <si>
+    <t>69dd50035cef447acab91b6f</t>
+  </si>
+  <si>
+    <t>69ddf6845cef447acab92010</t>
+  </si>
+  <si>
+    <t>69ddf6845cef447acab92012</t>
+  </si>
+  <si>
+    <t>69de0f0f5cef447acab924ea</t>
+  </si>
+  <si>
+    <t>69de199c5cef447acab92697</t>
+  </si>
+  <si>
+    <t>69de1e545cef447acab92768</t>
+  </si>
+  <si>
+    <t>69de7d635cef447acab9341c</t>
+  </si>
+  <si>
+    <t>69de7d635cef447acab9341d</t>
+  </si>
+  <si>
+    <t>69de93755cef447acab93544</t>
+  </si>
+  <si>
+    <t>69ddf43b5cef447acab91f96</t>
+  </si>
+  <si>
+    <t>69de05ac5cef447acab92316</t>
+  </si>
+  <si>
+    <t>69de0a685cef447acab92411</t>
+  </si>
+  <si>
+    <t>69de38195cef447acab92b4b</t>
+  </si>
+  <si>
+    <t>69de56995cef447acab9306e</t>
+  </si>
+  <si>
+    <t>69de9bad5cef447acab9358d</t>
+  </si>
+  <si>
+    <t>69de9bad5cef447acab9358e</t>
+  </si>
+  <si>
+    <t>69df40e45cef447acab9380b</t>
+  </si>
+  <si>
+    <t>69df5ac35cef447acab93d4f</t>
+  </si>
+  <si>
+    <t>69df3e8c5cef447acab93792</t>
+  </si>
+  <si>
+    <t>69df75a65cef447acab94187</t>
+  </si>
+  <si>
+    <t>FIZZ-1000866185</t>
+  </si>
+  <si>
+    <t>FIZZ-1000871305</t>
+  </si>
+  <si>
+    <t>FIZZ-1000871578</t>
+  </si>
+  <si>
+    <t>1449-872830</t>
+  </si>
+  <si>
+    <t>FIZZ-1000872708</t>
+  </si>
+  <si>
+    <t>1449-913827</t>
+  </si>
+  <si>
+    <t>1449-569947</t>
+  </si>
+  <si>
+    <t>26MPE0003964/1</t>
+  </si>
+  <si>
+    <t>26MPE0004014/1</t>
+  </si>
+  <si>
+    <t>26MPE0004016/1</t>
+  </si>
+  <si>
+    <t>26MPE0004017/1</t>
+  </si>
+  <si>
+    <t>305412294/1</t>
+  </si>
+  <si>
+    <t>305412294/2</t>
+  </si>
+  <si>
+    <t>306181540/1</t>
+  </si>
+  <si>
+    <t>306669492/1</t>
+  </si>
+  <si>
+    <t>306669492/2</t>
+  </si>
+  <si>
+    <t>307279408/1</t>
+  </si>
+  <si>
+    <t>307343188/1</t>
+  </si>
+  <si>
+    <t>307343188/2</t>
+  </si>
+  <si>
+    <t>307426534/1</t>
+  </si>
+  <si>
+    <t>307483214/1</t>
+  </si>
+  <si>
+    <t>307579626/1</t>
+  </si>
+  <si>
+    <t>307628437/1</t>
+  </si>
+  <si>
+    <t>307688975/1</t>
+  </si>
+  <si>
+    <t>307688975/2</t>
+  </si>
+  <si>
+    <t>307689582/1</t>
+  </si>
+  <si>
+    <t>307806371/1</t>
+  </si>
+  <si>
+    <t>307850102/1</t>
+  </si>
+  <si>
+    <t>307850124/1</t>
+  </si>
+  <si>
+    <t>307850124/2</t>
+  </si>
+  <si>
+    <t>307850145/1</t>
+  </si>
+  <si>
+    <t>307850338/1</t>
+  </si>
+  <si>
+    <t>307850342/1</t>
+  </si>
+  <si>
+    <t>307850380/1</t>
+  </si>
+  <si>
+    <t>307850571/1</t>
+  </si>
+  <si>
+    <t>307850581/1</t>
+  </si>
+  <si>
+    <t>307850756/1</t>
+  </si>
+  <si>
+    <t>307850756/2</t>
+  </si>
+  <si>
+    <t>307936293/1</t>
+  </si>
+  <si>
+    <t>307936479/1</t>
+  </si>
+  <si>
+    <t>307936703/1</t>
+  </si>
+  <si>
+    <t>307936703/2</t>
+  </si>
+  <si>
+    <t>307936719/1</t>
+  </si>
+  <si>
+    <t>307936719/2</t>
+  </si>
+  <si>
+    <t>307937029/1</t>
+  </si>
+  <si>
+    <t>307937080/1</t>
+  </si>
+  <si>
+    <t>307937090/1</t>
+  </si>
+  <si>
+    <t>307937090/2</t>
+  </si>
+  <si>
+    <t>308008940/1</t>
+  </si>
+  <si>
+    <t>308008969/1</t>
+  </si>
+  <si>
+    <t>308008969/2</t>
+  </si>
+  <si>
+    <t>308009041/1</t>
+  </si>
+  <si>
+    <t>308009137/1</t>
+  </si>
+  <si>
+    <t>308009234/1</t>
+  </si>
+  <si>
+    <t>308009334/1</t>
+  </si>
+  <si>
+    <t>308009431/1</t>
+  </si>
+  <si>
+    <t>308009431/2</t>
+  </si>
+  <si>
+    <t>308009431/3</t>
+  </si>
+  <si>
+    <t>308009580/1</t>
+  </si>
+  <si>
+    <t>308009580/2</t>
+  </si>
+  <si>
+    <t>308009696/1</t>
+  </si>
+  <si>
+    <t>308092365/1</t>
+  </si>
+  <si>
+    <t>308092471/1</t>
+  </si>
+  <si>
+    <t>308092562/1</t>
+  </si>
+  <si>
+    <t>308092638/1</t>
+  </si>
+  <si>
+    <t>308092735/1</t>
+  </si>
+  <si>
+    <t>308092925/1</t>
+  </si>
+  <si>
+    <t>308092928/1</t>
+  </si>
+  <si>
+    <t>308092928/2</t>
+  </si>
+  <si>
+    <t>308092988/1</t>
+  </si>
+  <si>
+    <t>308093029/1</t>
+  </si>
+  <si>
+    <t>308093122/1</t>
+  </si>
+  <si>
+    <t>308093165/1</t>
+  </si>
+  <si>
+    <t>308139755/1</t>
+  </si>
+  <si>
+    <t>308139817/1</t>
+  </si>
+  <si>
+    <t>308140115/1</t>
+  </si>
+  <si>
+    <t>308140211/1</t>
+  </si>
+  <si>
+    <t>308196316/1</t>
+  </si>
+  <si>
+    <t>99002349/1</t>
+  </si>
+  <si>
+    <t>202604152600825501</t>
+  </si>
+  <si>
+    <t>202604152600833201</t>
+  </si>
+  <si>
+    <t>202604132600863101</t>
+  </si>
+  <si>
+    <t>NFD6-04-13-MJWR-1</t>
+  </si>
+  <si>
+    <t>202604152600877301</t>
+  </si>
+  <si>
+    <t>202604152600877302</t>
+  </si>
+  <si>
+    <t>202604152600875901</t>
+  </si>
+  <si>
+    <t>202604152600879701</t>
+  </si>
+  <si>
+    <t>202604152600875801</t>
+  </si>
+  <si>
+    <t>NFD6-04-14-LJHG-1</t>
+  </si>
+  <si>
+    <t>202604152600875201</t>
+  </si>
+  <si>
+    <t>202604092600826101</t>
+  </si>
+  <si>
+    <t>202604092600826102</t>
+  </si>
+  <si>
+    <t>202604092600826103</t>
+  </si>
+  <si>
+    <t>202604152600833101</t>
+  </si>
+  <si>
+    <t>202604132600836201</t>
+  </si>
+  <si>
+    <t>202604102600868702</t>
+  </si>
+  <si>
+    <t>202604142600868701</t>
+  </si>
+  <si>
+    <t>202604152600876701</t>
+  </si>
+  <si>
+    <t>159995579539150769</t>
+  </si>
+  <si>
+    <t>159995579539150776</t>
+  </si>
+  <si>
+    <t>159995579539150950</t>
   </si>
 </sst>
 </file>
@@ -393,10 +1044,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -678,20 +1328,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D170"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>2</v>
       </c>
       <c r="C1" t="s">
@@ -699,8 +1349,11 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>159</v>
       </c>
       <c r="C2" t="s">
         <v>109</v>
@@ -708,602 +1361,803 @@
       <c r="D2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
+      <c r="B3" t="s">
+        <v>160</v>
+      </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D3"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
+      <c r="B4" t="s">
+        <v>161</v>
+      </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D4"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="C6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="B7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="C7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="B8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="B9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="C10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="B11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>3</v>
       </c>
-      <c r="C11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D11"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="B12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="C12" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B13" t="s">
+        <v>170</v>
+      </c>
+      <c r="C13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="C13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="C14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D14"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="B16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>174</v>
+      </c>
+      <c r="C17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="C15" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="B18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" t="s">
+        <v>119</v>
+      </c>
+      <c r="D19"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>18</v>
       </c>
-      <c r="C16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D16"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="B20" t="s">
+        <v>177</v>
+      </c>
+      <c r="C20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="C17" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="B21" t="s">
+        <v>178</v>
+      </c>
+      <c r="C21" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>20</v>
       </c>
-      <c r="C18" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="B23" t="s">
+        <v>180</v>
+      </c>
+      <c r="C23" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>21</v>
       </c>
-      <c r="C19" t="s">
-        <v>109</v>
-      </c>
-      <c r="D19"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="B24" t="s">
+        <v>181</v>
+      </c>
+      <c r="C24" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
+        <v>182</v>
+      </c>
+      <c r="C25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>22</v>
       </c>
-      <c r="C20" t="s">
-        <v>109</v>
-      </c>
-      <c r="D20"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="B26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>23</v>
       </c>
-      <c r="C21" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="B27" t="s">
+        <v>184</v>
+      </c>
+      <c r="C27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>24</v>
       </c>
-      <c r="C22" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="B29" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" t="s">
+        <v>122</v>
+      </c>
+      <c r="D29"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>25</v>
       </c>
-      <c r="C23" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="B30" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>4</v>
       </c>
-      <c r="C24" t="s">
-        <v>109</v>
-      </c>
-      <c r="D24"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="B31" t="s">
+        <v>188</v>
+      </c>
+      <c r="C31" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>26</v>
       </c>
-      <c r="C25" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="B32" t="s">
+        <v>189</v>
+      </c>
+      <c r="C32" t="s">
+        <v>113</v>
+      </c>
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" t="s">
+        <v>190</v>
+      </c>
+      <c r="C33" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>27</v>
       </c>
-      <c r="C26" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="B34" t="s">
+        <v>191</v>
+      </c>
+      <c r="C34" t="s">
+        <v>118</v>
+      </c>
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>28</v>
       </c>
-      <c r="C27" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="B35" t="s">
+        <v>192</v>
+      </c>
+      <c r="C35" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>29</v>
       </c>
-      <c r="C28" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="B36" t="s">
+        <v>193</v>
+      </c>
+      <c r="C36" t="s">
+        <v>114</v>
+      </c>
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>30</v>
       </c>
-      <c r="C29" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="B37" t="s">
+        <v>194</v>
+      </c>
+      <c r="C37" t="s">
+        <v>110</v>
+      </c>
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>31</v>
       </c>
-      <c r="C30" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="B38" t="s">
+        <v>195</v>
+      </c>
+      <c r="C38" t="s">
+        <v>123</v>
+      </c>
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39" t="s">
+        <v>196</v>
+      </c>
+      <c r="C39" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>32</v>
       </c>
-      <c r="C31" t="s">
-        <v>109</v>
-      </c>
-      <c r="D31"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="B40" t="s">
+        <v>197</v>
+      </c>
+      <c r="C40" t="s">
+        <v>110</v>
+      </c>
+      <c r="D40"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>33</v>
       </c>
-      <c r="C32" t="s">
-        <v>109</v>
-      </c>
-      <c r="D32"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="B41" t="s">
+        <v>198</v>
+      </c>
+      <c r="C41" t="s">
+        <v>120</v>
+      </c>
+      <c r="D41"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>34</v>
       </c>
-      <c r="C33" t="s">
-        <v>109</v>
-      </c>
-      <c r="D33"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="B42" t="s">
+        <v>199</v>
+      </c>
+      <c r="C42" t="s">
+        <v>118</v>
+      </c>
+      <c r="D42"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>35</v>
       </c>
-      <c r="C34" t="s">
-        <v>109</v>
-      </c>
-      <c r="D34"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="B43" t="s">
+        <v>200</v>
+      </c>
+      <c r="C43" t="s">
+        <v>124</v>
+      </c>
+      <c r="D43"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>36</v>
       </c>
-      <c r="C35" t="s">
-        <v>109</v>
-      </c>
-      <c r="D35"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+      <c r="B44" t="s">
+        <v>201</v>
+      </c>
+      <c r="C44" t="s">
+        <v>119</v>
+      </c>
+      <c r="D44"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45" t="s">
+        <v>202</v>
+      </c>
+      <c r="C45" t="s">
+        <v>119</v>
+      </c>
+      <c r="D45"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>37</v>
       </c>
-      <c r="C36" t="s">
-        <v>109</v>
-      </c>
-      <c r="D36"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+      <c r="B46" t="s">
+        <v>203</v>
+      </c>
+      <c r="C46" t="s">
+        <v>120</v>
+      </c>
+      <c r="D46"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" t="s">
+        <v>204</v>
+      </c>
+      <c r="C47" t="s">
+        <v>120</v>
+      </c>
+      <c r="D47"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>38</v>
       </c>
-      <c r="C37" t="s">
-        <v>109</v>
-      </c>
-      <c r="D37"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="B48" t="s">
+        <v>205</v>
+      </c>
+      <c r="C48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D48"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" t="s">
+        <v>206</v>
+      </c>
+      <c r="C49" t="s">
+        <v>117</v>
+      </c>
+      <c r="D49"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>39</v>
       </c>
-      <c r="C38" t="s">
-        <v>109</v>
-      </c>
-      <c r="D38"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="B50" t="s">
+        <v>207</v>
+      </c>
+      <c r="C50" t="s">
+        <v>116</v>
+      </c>
+      <c r="D50"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" t="s">
+        <v>208</v>
+      </c>
+      <c r="C51" t="s">
+        <v>116</v>
+      </c>
+      <c r="D51"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>40</v>
       </c>
-      <c r="C39" t="s">
-        <v>109</v>
-      </c>
-      <c r="D39"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="B52" t="s">
+        <v>209</v>
+      </c>
+      <c r="C52" t="s">
+        <v>110</v>
+      </c>
+      <c r="D52"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>41</v>
       </c>
-      <c r="C40" t="s">
-        <v>109</v>
-      </c>
-      <c r="D40"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="B53" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" t="s">
+        <v>122</v>
+      </c>
+      <c r="D53"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>42</v>
       </c>
-      <c r="C41" t="s">
-        <v>109</v>
-      </c>
-      <c r="D41"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+      <c r="B54" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" t="s">
+        <v>122</v>
+      </c>
+      <c r="D54"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>43</v>
       </c>
-      <c r="C42" t="s">
-        <v>109</v>
-      </c>
-      <c r="D42"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+      <c r="B55" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" t="s">
+        <v>121</v>
+      </c>
+      <c r="D55"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>43</v>
+      </c>
+      <c r="B56" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" t="s">
+        <v>121</v>
+      </c>
+      <c r="D56"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>44</v>
       </c>
-      <c r="C43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D43"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+      <c r="B57" t="s">
+        <v>214</v>
+      </c>
+      <c r="C57" t="s">
+        <v>111</v>
+      </c>
+      <c r="D57"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>45</v>
       </c>
-      <c r="C44" t="s">
-        <v>109</v>
-      </c>
-      <c r="D44"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+      <c r="B58" t="s">
+        <v>215</v>
+      </c>
+      <c r="C58" t="s">
+        <v>110</v>
+      </c>
+      <c r="D58"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>46</v>
       </c>
-      <c r="C45" t="s">
-        <v>109</v>
-      </c>
-      <c r="D45"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+      <c r="B59" t="s">
+        <v>216</v>
+      </c>
+      <c r="C59" t="s">
+        <v>110</v>
+      </c>
+      <c r="D59"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>47</v>
       </c>
-      <c r="C46" t="s">
-        <v>109</v>
-      </c>
-      <c r="D46"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+      <c r="B60" t="s">
+        <v>217</v>
+      </c>
+      <c r="C60" t="s">
+        <v>112</v>
+      </c>
+      <c r="D60"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>48</v>
       </c>
-      <c r="C47" t="s">
-        <v>109</v>
-      </c>
-      <c r="D47"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+      <c r="B61" t="s">
+        <v>218</v>
+      </c>
+      <c r="C61" t="s">
+        <v>117</v>
+      </c>
+      <c r="D61"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>49</v>
       </c>
-      <c r="C48" t="s">
-        <v>109</v>
-      </c>
-      <c r="D48"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+      <c r="B62" t="s">
+        <v>219</v>
+      </c>
+      <c r="C62" t="s">
+        <v>125</v>
+      </c>
+      <c r="D62"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>50</v>
       </c>
-      <c r="C49" t="s">
-        <v>109</v>
-      </c>
-      <c r="D49"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+      <c r="B63" t="s">
+        <v>220</v>
+      </c>
+      <c r="C63" t="s">
+        <v>116</v>
+      </c>
+      <c r="D63"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>50</v>
+      </c>
+      <c r="B64" t="s">
+        <v>221</v>
+      </c>
+      <c r="C64" t="s">
+        <v>116</v>
+      </c>
+      <c r="D64"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>51</v>
       </c>
-      <c r="C50" t="s">
-        <v>109</v>
-      </c>
-      <c r="D50"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
+      <c r="B65" t="s">
+        <v>222</v>
+      </c>
+      <c r="C65" t="s">
+        <v>119</v>
+      </c>
+      <c r="D65"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>52</v>
       </c>
-      <c r="C51" t="s">
-        <v>109</v>
-      </c>
-      <c r="D51"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+      <c r="B66" t="s">
+        <v>223</v>
+      </c>
+      <c r="C66" t="s">
+        <v>121</v>
+      </c>
+      <c r="D66"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>53</v>
       </c>
-      <c r="C52" t="s">
-        <v>109</v>
-      </c>
-      <c r="D52"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
+      <c r="B67" t="s">
+        <v>224</v>
+      </c>
+      <c r="C67" t="s">
+        <v>126</v>
+      </c>
+      <c r="D67"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>54</v>
       </c>
-      <c r="C53" t="s">
-        <v>109</v>
-      </c>
-      <c r="D53"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" t="s">
-        <v>109</v>
-      </c>
-      <c r="D54"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C55" t="s">
-        <v>109</v>
-      </c>
-      <c r="D55"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56" t="s">
-        <v>109</v>
-      </c>
-      <c r="D56"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" t="s">
-        <v>109</v>
-      </c>
-      <c r="D57"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C58" t="s">
-        <v>109</v>
-      </c>
-      <c r="D58"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C59" t="s">
-        <v>109</v>
-      </c>
-      <c r="D59"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" t="s">
-        <v>109</v>
-      </c>
-      <c r="D60"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C61" t="s">
-        <v>109</v>
-      </c>
-      <c r="D61"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C62" t="s">
-        <v>109</v>
-      </c>
-      <c r="D62"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C63" t="s">
-        <v>109</v>
-      </c>
-      <c r="D63"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C64" t="s">
-        <v>109</v>
-      </c>
-      <c r="D64"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C65" t="s">
-        <v>109</v>
-      </c>
-      <c r="D65"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C66" t="s">
-        <v>109</v>
-      </c>
-      <c r="D66"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C67" t="s">
-        <v>109</v>
-      </c>
-      <c r="D67"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>69</v>
+      <c r="B68" t="s">
+        <v>225</v>
       </c>
       <c r="C68" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="D68"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>70</v>
+      <c r="A69" t="s">
+        <v>130</v>
+      </c>
+      <c r="B69" t="s">
+        <v>226</v>
       </c>
       <c r="C69" t="s">
         <v>109</v>
@@ -1311,17 +2165,23 @@
       <c r="D69"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>71</v>
+      <c r="A70" t="s">
+        <v>131</v>
+      </c>
+      <c r="B70" t="s">
+        <v>227</v>
       </c>
       <c r="C70" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D70"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>72</v>
+      <c r="A71" t="s">
+        <v>132</v>
+      </c>
+      <c r="B71" t="s">
+        <v>228</v>
       </c>
       <c r="C71" t="s">
         <v>109</v>
@@ -1329,8 +2189,11 @@
       <c r="D71"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>73</v>
+      <c r="A72" t="s">
+        <v>133</v>
+      </c>
+      <c r="B72" t="s">
+        <v>229</v>
       </c>
       <c r="C72" t="s">
         <v>109</v>
@@ -1338,206 +2201,275 @@
       <c r="D72"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>74</v>
+      <c r="A73" t="s">
+        <v>134</v>
+      </c>
+      <c r="B73" t="s">
+        <v>230</v>
       </c>
       <c r="C73" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="D73"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>75</v>
+      <c r="A74" t="s">
+        <v>135</v>
+      </c>
+      <c r="B74" t="s">
+        <v>231</v>
       </c>
       <c r="C74" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D74"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>76</v>
+      <c r="A75" t="s">
+        <v>136</v>
+      </c>
+      <c r="B75" t="s">
+        <v>232</v>
       </c>
       <c r="C75" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D75"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>77</v>
+      <c r="A76" t="s">
+        <v>137</v>
+      </c>
+      <c r="B76" t="s">
+        <v>233</v>
       </c>
       <c r="C76" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D76"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>78</v>
+      <c r="A77" t="s">
+        <v>138</v>
+      </c>
+      <c r="B77" t="s">
+        <v>234</v>
       </c>
       <c r="C77" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="D77"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>79</v>
+      <c r="A78" t="s">
+        <v>139</v>
+      </c>
+      <c r="B78" t="s">
+        <v>235</v>
       </c>
       <c r="C78" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="D78"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>80</v>
+      <c r="A79" t="s">
+        <v>140</v>
+      </c>
+      <c r="B79" t="s">
+        <v>236</v>
       </c>
       <c r="C79" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="D79"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>81</v>
+      <c r="A80" t="s">
+        <v>55</v>
+      </c>
+      <c r="B80" t="s">
+        <v>237</v>
       </c>
       <c r="C80" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D80"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>82</v>
+      <c r="A81" t="s">
+        <v>55</v>
+      </c>
+      <c r="B81" t="s">
+        <v>238</v>
       </c>
       <c r="C81" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D81"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>83</v>
+      <c r="A82" t="s">
+        <v>56</v>
+      </c>
+      <c r="B82" t="s">
+        <v>239</v>
       </c>
       <c r="C82" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D82"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>84</v>
+      <c r="A83" t="s">
+        <v>57</v>
+      </c>
+      <c r="B83" t="s">
+        <v>240</v>
       </c>
       <c r="C83" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="D83"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>85</v>
+      <c r="A84" t="s">
+        <v>57</v>
+      </c>
+      <c r="B84" t="s">
+        <v>241</v>
       </c>
       <c r="C84" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="D84"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>86</v>
+      <c r="A85" t="s">
+        <v>58</v>
+      </c>
+      <c r="B85" t="s">
+        <v>242</v>
       </c>
       <c r="C85" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D85"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>87</v>
+      <c r="A86" t="s">
+        <v>59</v>
+      </c>
+      <c r="B86" t="s">
+        <v>243</v>
       </c>
       <c r="C86" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D86"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>88</v>
+      <c r="A87" t="s">
+        <v>59</v>
+      </c>
+      <c r="B87" t="s">
+        <v>244</v>
       </c>
       <c r="C87" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D87"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>89</v>
+      <c r="A88" t="s">
+        <v>60</v>
+      </c>
+      <c r="B88" t="s">
+        <v>245</v>
       </c>
       <c r="C88" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="D88"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
-        <v>90</v>
+      <c r="A89" t="s">
+        <v>61</v>
+      </c>
+      <c r="B89" t="s">
+        <v>246</v>
       </c>
       <c r="C89" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="D89"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>91</v>
+      <c r="A90" t="s">
+        <v>62</v>
+      </c>
+      <c r="B90" t="s">
+        <v>247</v>
       </c>
       <c r="C90" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D90"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>92</v>
+      <c r="A91" t="s">
+        <v>63</v>
+      </c>
+      <c r="B91" t="s">
+        <v>248</v>
       </c>
       <c r="C91" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D91"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>93</v>
+      <c r="A92" t="s">
+        <v>64</v>
+      </c>
+      <c r="B92" t="s">
+        <v>249</v>
       </c>
       <c r="C92" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D92"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>94</v>
+      <c r="A93" t="s">
+        <v>64</v>
+      </c>
+      <c r="B93" t="s">
+        <v>250</v>
       </c>
       <c r="C93" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D93"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
-        <v>95</v>
+      <c r="A94" t="s">
+        <v>65</v>
+      </c>
+      <c r="B94" t="s">
+        <v>251</v>
       </c>
       <c r="C94" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D94"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>96</v>
+      <c r="A95" t="s">
+        <v>66</v>
+      </c>
+      <c r="B95" t="s">
+        <v>252</v>
       </c>
       <c r="C95" t="s">
         <v>109</v>
@@ -1545,106 +2477,835 @@
       <c r="D95"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
+      <c r="A96" t="s">
+        <v>67</v>
+      </c>
+      <c r="B96" t="s">
+        <v>253</v>
+      </c>
+      <c r="C96" t="s">
+        <v>110</v>
+      </c>
+      <c r="D96"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>68</v>
+      </c>
+      <c r="B97" t="s">
+        <v>254</v>
+      </c>
+      <c r="C97" t="s">
+        <v>114</v>
+      </c>
+      <c r="D97"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>68</v>
+      </c>
+      <c r="B98" t="s">
+        <v>255</v>
+      </c>
+      <c r="C98" t="s">
+        <v>114</v>
+      </c>
+      <c r="D98"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>69</v>
+      </c>
+      <c r="B99" t="s">
+        <v>256</v>
+      </c>
+      <c r="C99" t="s">
+        <v>120</v>
+      </c>
+      <c r="D99"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>70</v>
+      </c>
+      <c r="B100" t="s">
+        <v>257</v>
+      </c>
+      <c r="C100" t="s">
+        <v>113</v>
+      </c>
+      <c r="D100"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>71</v>
+      </c>
+      <c r="B101" t="s">
+        <v>258</v>
+      </c>
+      <c r="C101" t="s">
+        <v>119</v>
+      </c>
+      <c r="D101"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>72</v>
+      </c>
+      <c r="B102" t="s">
+        <v>259</v>
+      </c>
+      <c r="C102" t="s">
+        <v>115</v>
+      </c>
+      <c r="D102"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>73</v>
+      </c>
+      <c r="B103" t="s">
+        <v>260</v>
+      </c>
+      <c r="C103" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>74</v>
+      </c>
+      <c r="B104" t="s">
+        <v>261</v>
+      </c>
+      <c r="C104" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>75</v>
+      </c>
+      <c r="B105" t="s">
+        <v>262</v>
+      </c>
+      <c r="C105" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>75</v>
+      </c>
+      <c r="B106" t="s">
+        <v>263</v>
+      </c>
+      <c r="C106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>76</v>
+      </c>
+      <c r="B107" t="s">
+        <v>264</v>
+      </c>
+      <c r="C107" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>77</v>
+      </c>
+      <c r="B108" t="s">
+        <v>265</v>
+      </c>
+      <c r="C108" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>78</v>
+      </c>
+      <c r="B109" t="s">
+        <v>266</v>
+      </c>
+      <c r="C109" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>78</v>
+      </c>
+      <c r="B110" t="s">
+        <v>267</v>
+      </c>
+      <c r="C110" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>79</v>
+      </c>
+      <c r="B111" t="s">
+        <v>268</v>
+      </c>
+      <c r="C111" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>79</v>
+      </c>
+      <c r="B112" t="s">
+        <v>269</v>
+      </c>
+      <c r="C112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>80</v>
+      </c>
+      <c r="B113" t="s">
+        <v>270</v>
+      </c>
+      <c r="C113" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>81</v>
+      </c>
+      <c r="B114" t="s">
+        <v>271</v>
+      </c>
+      <c r="C114" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>82</v>
+      </c>
+      <c r="B115" t="s">
+        <v>272</v>
+      </c>
+      <c r="C115" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>82</v>
+      </c>
+      <c r="B116" t="s">
+        <v>273</v>
+      </c>
+      <c r="C116" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>83</v>
+      </c>
+      <c r="B117" t="s">
+        <v>274</v>
+      </c>
+      <c r="C117" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>84</v>
+      </c>
+      <c r="B118" t="s">
+        <v>275</v>
+      </c>
+      <c r="C118" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>84</v>
+      </c>
+      <c r="B119" t="s">
+        <v>276</v>
+      </c>
+      <c r="C119" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>85</v>
+      </c>
+      <c r="B120" t="s">
+        <v>277</v>
+      </c>
+      <c r="C120" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>86</v>
+      </c>
+      <c r="B121" t="s">
+        <v>278</v>
+      </c>
+      <c r="C121" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>87</v>
+      </c>
+      <c r="B122" t="s">
+        <v>279</v>
+      </c>
+      <c r="C122" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>88</v>
+      </c>
+      <c r="B123" t="s">
+        <v>280</v>
+      </c>
+      <c r="C123" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>89</v>
+      </c>
+      <c r="B124" t="s">
+        <v>281</v>
+      </c>
+      <c r="C124" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>89</v>
+      </c>
+      <c r="B125" t="s">
+        <v>282</v>
+      </c>
+      <c r="C125" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>89</v>
+      </c>
+      <c r="B126" t="s">
+        <v>283</v>
+      </c>
+      <c r="C126" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>90</v>
+      </c>
+      <c r="B127" t="s">
+        <v>284</v>
+      </c>
+      <c r="C127" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>90</v>
+      </c>
+      <c r="B128" t="s">
+        <v>285</v>
+      </c>
+      <c r="C128" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>91</v>
+      </c>
+      <c r="B129" t="s">
+        <v>286</v>
+      </c>
+      <c r="C129" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>92</v>
+      </c>
+      <c r="B130" t="s">
+        <v>287</v>
+      </c>
+      <c r="C130" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>93</v>
+      </c>
+      <c r="B131" t="s">
+        <v>288</v>
+      </c>
+      <c r="C131" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>94</v>
+      </c>
+      <c r="B132" t="s">
+        <v>289</v>
+      </c>
+      <c r="C132" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>95</v>
+      </c>
+      <c r="B133" t="s">
+        <v>290</v>
+      </c>
+      <c r="C133" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>96</v>
+      </c>
+      <c r="B134" t="s">
+        <v>291</v>
+      </c>
+      <c r="C134" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
         <v>97</v>
       </c>
-      <c r="C96" t="s">
+      <c r="B135" t="s">
+        <v>292</v>
+      </c>
+      <c r="C135" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>98</v>
+      </c>
+      <c r="B136" t="s">
+        <v>293</v>
+      </c>
+      <c r="C136" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>98</v>
+      </c>
+      <c r="B137" t="s">
+        <v>294</v>
+      </c>
+      <c r="C137" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>99</v>
+      </c>
+      <c r="B138" t="s">
+        <v>295</v>
+      </c>
+      <c r="C138" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>100</v>
+      </c>
+      <c r="B139" t="s">
+        <v>296</v>
+      </c>
+      <c r="C139" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>101</v>
+      </c>
+      <c r="B140" t="s">
+        <v>297</v>
+      </c>
+      <c r="C140" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>102</v>
+      </c>
+      <c r="B141" t="s">
+        <v>298</v>
+      </c>
+      <c r="C141" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>103</v>
+      </c>
+      <c r="B142" t="s">
+        <v>299</v>
+      </c>
+      <c r="C142" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>104</v>
+      </c>
+      <c r="B143" t="s">
+        <v>300</v>
+      </c>
+      <c r="C143" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>105</v>
+      </c>
+      <c r="B144" t="s">
+        <v>301</v>
+      </c>
+      <c r="C144" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>106</v>
+      </c>
+      <c r="B145" t="s">
+        <v>302</v>
+      </c>
+      <c r="C145" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>107</v>
+      </c>
+      <c r="B146" t="s">
+        <v>303</v>
+      </c>
+      <c r="C146" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>108</v>
+      </c>
+      <c r="B147" t="s">
+        <v>304</v>
+      </c>
+      <c r="C147" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>141</v>
+      </c>
+      <c r="B148" t="s">
+        <v>305</v>
+      </c>
+      <c r="C148" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>142</v>
+      </c>
+      <c r="B149" t="s">
+        <v>306</v>
+      </c>
+      <c r="C149" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>143</v>
+      </c>
+      <c r="B150" t="s">
+        <v>307</v>
+      </c>
+      <c r="C150" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>144</v>
+      </c>
+      <c r="B151" t="s">
+        <v>308</v>
+      </c>
+      <c r="C151" t="s">
         <v>109</v>
       </c>
-      <c r="D96"/>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C97" t="s">
-        <v>109</v>
-      </c>
-      <c r="D97"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C98" t="s">
-        <v>109</v>
-      </c>
-      <c r="D98"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C99" t="s">
-        <v>109</v>
-      </c>
-      <c r="D99"/>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C100" t="s">
-        <v>109</v>
-      </c>
-      <c r="D100"/>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C101" t="s">
-        <v>109</v>
-      </c>
-      <c r="D101"/>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C102" t="s">
-        <v>109</v>
-      </c>
-      <c r="D102"/>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C103" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C104" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C105" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C106" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C107" t="s">
-        <v>109</v>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>145</v>
+      </c>
+      <c r="B152" t="s">
+        <v>309</v>
+      </c>
+      <c r="C152" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>145</v>
+      </c>
+      <c r="B153" t="s">
+        <v>310</v>
+      </c>
+      <c r="C153" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>146</v>
+      </c>
+      <c r="B154" t="s">
+        <v>311</v>
+      </c>
+      <c r="C154" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>147</v>
+      </c>
+      <c r="B155" t="s">
+        <v>312</v>
+      </c>
+      <c r="C155" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>148</v>
+      </c>
+      <c r="B156" t="s">
+        <v>313</v>
+      </c>
+      <c r="C156" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>149</v>
+      </c>
+      <c r="B157" t="s">
+        <v>314</v>
+      </c>
+      <c r="C157" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>150</v>
+      </c>
+      <c r="B158" t="s">
+        <v>315</v>
+      </c>
+      <c r="C158" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>151</v>
+      </c>
+      <c r="B159" t="s">
+        <v>316</v>
+      </c>
+      <c r="C159" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>151</v>
+      </c>
+      <c r="B160" t="s">
+        <v>317</v>
+      </c>
+      <c r="C160" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>151</v>
+      </c>
+      <c r="B161" t="s">
+        <v>318</v>
+      </c>
+      <c r="C161" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>152</v>
+      </c>
+      <c r="B162" t="s">
+        <v>319</v>
+      </c>
+      <c r="C162" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>153</v>
+      </c>
+      <c r="B163" t="s">
+        <v>320</v>
+      </c>
+      <c r="C163" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>154</v>
+      </c>
+      <c r="B164" t="s">
+        <v>321</v>
+      </c>
+      <c r="C164" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>154</v>
+      </c>
+      <c r="B165" t="s">
+        <v>322</v>
+      </c>
+      <c r="C165" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>155</v>
+      </c>
+      <c r="B166" t="s">
+        <v>323</v>
+      </c>
+      <c r="C166" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>156</v>
+      </c>
+      <c r="B167" t="s">
+        <v>324</v>
+      </c>
+      <c r="C167" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>156</v>
+      </c>
+      <c r="B168" t="s">
+        <v>325</v>
+      </c>
+      <c r="C168" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>157</v>
+      </c>
+      <c r="B169" t="s">
+        <v>326</v>
+      </c>
+      <c r="C169" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>158</v>
+      </c>
+      <c r="B170" t="s">
+        <v>158</v>
+      </c>
+      <c r="C170" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EC27D4-DAA0-49B9-B0A4-92C0BA2D2DE7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D53557-A34E-4AF6-8586-DCAA2CC261B4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="284">
   <si>
     <t>UTK</t>
   </si>
@@ -267,7 +267,619 @@
     <t>308368203</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>SZ-827</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-860</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-840</t>
+  </si>
+  <si>
+    <t>SZ-850</t>
+  </si>
+  <si>
+    <t>69dca8635cef447acab909b9</t>
+  </si>
+  <si>
+    <t>69e0c5ab5cef447acab95993</t>
+  </si>
+  <si>
+    <t>69df85fe5cef447acab943f7</t>
+  </si>
+  <si>
+    <t>69df85fe5cef447acab943f8</t>
+  </si>
+  <si>
+    <t>69d90e525cef447acab8eaa2</t>
+  </si>
+  <si>
+    <t>69e20b055cef447acab96efa</t>
+  </si>
+  <si>
+    <t>69df87b85cef447acab9444f</t>
+  </si>
+  <si>
+    <t>69dbaa285cef447acab902af</t>
+  </si>
+  <si>
+    <t>69dceec35cef447acab914a5</t>
+  </si>
+  <si>
+    <t>69e216c25cef447acab970c6</t>
+  </si>
+  <si>
+    <t>69df7b7c5cef447acab94266</t>
+  </si>
+  <si>
+    <t>69dfb3b95cef447acab94aaa</t>
+  </si>
+  <si>
+    <t>69dff5625cef447acab94e68</t>
+  </si>
+  <si>
+    <t>69dff1d95cef447acab94e53</t>
+  </si>
+  <si>
+    <t>69e0ab045cef447acab9558e</t>
+  </si>
+  <si>
+    <t>69e0ab045cef447acab9558f</t>
+  </si>
+  <si>
+    <t>69e0ac2b5cef447acab955d3</t>
+  </si>
+  <si>
+    <t>69e0f2815cef447acab960ad</t>
+  </si>
+  <si>
+    <t>69e0a2cd5cef447acab95417</t>
+  </si>
+  <si>
+    <t>69e0b2195cef447acab956f7</t>
+  </si>
+  <si>
+    <t>69e0b2195cef447acab956f8</t>
+  </si>
+  <si>
+    <t>69e1cc435cef447acab9669c</t>
+  </si>
+  <si>
+    <t>69e1cc435cef447acab9669e</t>
+  </si>
+  <si>
+    <t>69e130a25cef447acab96597</t>
+  </si>
+  <si>
+    <t>69e209755cef447acab96eb6</t>
+  </si>
+  <si>
+    <t>69e215215cef447acab9708a</t>
+  </si>
+  <si>
+    <t>69e214115cef447acab97068</t>
+  </si>
+  <si>
+    <t>69e217785cef447acab970ec</t>
+  </si>
+  <si>
+    <t>69e20e195cef447acab96f7a</t>
+  </si>
+  <si>
+    <t>FIZZ-1000875264</t>
+  </si>
+  <si>
+    <t>FIZZ-1000875527</t>
+  </si>
+  <si>
+    <t>FIZZ-1000877136</t>
+  </si>
+  <si>
+    <t>FIZZ-1000877886</t>
+  </si>
+  <si>
+    <t>FIZZ-1000879227</t>
+  </si>
+  <si>
+    <t>FIZZ-1000879375</t>
+  </si>
+  <si>
+    <t>FIZZ-1000879399</t>
+  </si>
+  <si>
+    <t>FIZZ-1000879438</t>
+  </si>
+  <si>
+    <t>1449-285949/1</t>
+  </si>
+  <si>
+    <t>1449-285949/2</t>
+  </si>
+  <si>
+    <t>1449-285949/3</t>
+  </si>
+  <si>
+    <t>FIZZ-1000879915</t>
+  </si>
+  <si>
+    <t>FIZZ-1000880303</t>
+  </si>
+  <si>
+    <t>26MPE0004080/1</t>
+  </si>
+  <si>
+    <t>307278602/1</t>
+  </si>
+  <si>
+    <t>307278602/2</t>
+  </si>
+  <si>
+    <t>307278602/3</t>
+  </si>
+  <si>
+    <t>307850771/1</t>
+  </si>
+  <si>
+    <t>307937117/1</t>
+  </si>
+  <si>
+    <t>307937117/2</t>
+  </si>
+  <si>
+    <t>308093048/1</t>
+  </si>
+  <si>
+    <t>308139973/1</t>
+  </si>
+  <si>
+    <t>308139991/1</t>
+  </si>
+  <si>
+    <t>308140237/1</t>
+  </si>
+  <si>
+    <t>308140284/1</t>
+  </si>
+  <si>
+    <t>308140298/1</t>
+  </si>
+  <si>
+    <t>308140452/1</t>
+  </si>
+  <si>
+    <t>308140452/2</t>
+  </si>
+  <si>
+    <t>308140536/1</t>
+  </si>
+  <si>
+    <t>308197133/1</t>
+  </si>
+  <si>
+    <t>308240552/1</t>
+  </si>
+  <si>
+    <t>308240552/2</t>
+  </si>
+  <si>
+    <t>308240690/1</t>
+  </si>
+  <si>
+    <t>308240712/1</t>
+  </si>
+  <si>
+    <t>308241014/1</t>
+  </si>
+  <si>
+    <t>308241035/1</t>
+  </si>
+  <si>
+    <t>308241061/1</t>
+  </si>
+  <si>
+    <t>308241173/1</t>
+  </si>
+  <si>
+    <t>308241198/1</t>
+  </si>
+  <si>
+    <t>308241198/2</t>
+  </si>
+  <si>
+    <t>308241198/3</t>
+  </si>
+  <si>
+    <t>308241209/1</t>
+  </si>
+  <si>
+    <t>308241251/1</t>
+  </si>
+  <si>
+    <t>308241311/1</t>
+  </si>
+  <si>
+    <t>308241361/1</t>
+  </si>
+  <si>
+    <t>308241385/1</t>
+  </si>
+  <si>
+    <t>308241385/2</t>
+  </si>
+  <si>
+    <t>308241423/1</t>
+  </si>
+  <si>
+    <t>308241454/1</t>
+  </si>
+  <si>
+    <t>308241464/1</t>
+  </si>
+  <si>
+    <t>308241493/1</t>
+  </si>
+  <si>
+    <t>308294529/1</t>
+  </si>
+  <si>
+    <t>308294581/1</t>
+  </si>
+  <si>
+    <t>308294753/1</t>
+  </si>
+  <si>
+    <t>308294753/2</t>
+  </si>
+  <si>
+    <t>308294777/1</t>
+  </si>
+  <si>
+    <t>308294912/1</t>
+  </si>
+  <si>
+    <t>308294915/1</t>
+  </si>
+  <si>
+    <t>308294930/1</t>
+  </si>
+  <si>
+    <t>308294930/2</t>
+  </si>
+  <si>
+    <t>308295015/1</t>
+  </si>
+  <si>
+    <t>308295201/1</t>
+  </si>
+  <si>
+    <t>308313895/1</t>
+  </si>
+  <si>
+    <t>308337288/1</t>
+  </si>
+  <si>
+    <t>308337817/1</t>
+  </si>
+  <si>
+    <t>308338086/1</t>
+  </si>
+  <si>
+    <t>308338086/2</t>
+  </si>
+  <si>
+    <t>308338131/1</t>
+  </si>
+  <si>
+    <t>308338131/2</t>
+  </si>
+  <si>
+    <t>308338147/1</t>
+  </si>
+  <si>
+    <t>308367545/1</t>
+  </si>
+  <si>
+    <t>308367566/1</t>
+  </si>
+  <si>
+    <t>308367674/1</t>
+  </si>
+  <si>
+    <t>308367772/1</t>
+  </si>
+  <si>
+    <t>308367868/1</t>
+  </si>
+  <si>
+    <t>308368091/1</t>
+  </si>
+  <si>
+    <t>308368107/1</t>
+  </si>
+  <si>
+    <t>308368156/1</t>
+  </si>
+  <si>
+    <t>308368203/1</t>
+  </si>
+  <si>
+    <t>202604162600832401</t>
+  </si>
+  <si>
+    <t>202604162600832402</t>
+  </si>
+  <si>
+    <t>202604172600860301</t>
+  </si>
+  <si>
+    <t>202604132600861901</t>
+  </si>
+  <si>
+    <t>202604132600861902</t>
+  </si>
+  <si>
+    <t>202604172600864601</t>
+  </si>
+  <si>
+    <t>202604172600871501</t>
+  </si>
+  <si>
+    <t>202604172600870301</t>
+  </si>
+  <si>
+    <t>202604142600872201</t>
+  </si>
+  <si>
+    <t>NFD6-04-14-LJHG-1</t>
+  </si>
+  <si>
+    <t>202604172600877901</t>
+  </si>
+  <si>
+    <t>NFD6-04-14-VS6A-1</t>
+  </si>
+  <si>
+    <t>202604172600882601</t>
+  </si>
+  <si>
+    <t>202604172600881701</t>
+  </si>
+  <si>
+    <t>202604172600883901</t>
+  </si>
+  <si>
+    <t>202604172600884001</t>
+  </si>
+  <si>
+    <t>202604172600881601</t>
+  </si>
+  <si>
+    <t>202604172600882701</t>
+  </si>
+  <si>
+    <t>202604172600883001</t>
+  </si>
+  <si>
+    <t>202604172600883501</t>
+  </si>
+  <si>
+    <t>202604172600887401</t>
+  </si>
+  <si>
+    <t>202604172600887402</t>
+  </si>
+  <si>
+    <t>202604172600888201</t>
+  </si>
+  <si>
+    <t>202604202600895101</t>
+  </si>
+  <si>
+    <t>202604172600870901</t>
+  </si>
+  <si>
+    <t>202604172600869101</t>
+  </si>
+  <si>
+    <t>202604172600884601</t>
+  </si>
+  <si>
+    <t>202604172600883701</t>
+  </si>
+  <si>
+    <t>202604172600888001</t>
+  </si>
+  <si>
+    <t>202604172600890001</t>
+  </si>
+  <si>
+    <t>159995579539247001</t>
+  </si>
+  <si>
+    <t>NFD6-03-19-L5RZ</t>
+  </si>
+  <si>
+    <t>NFD6-04-16-B8WC</t>
+  </si>
+  <si>
+    <t>267005343</t>
+  </si>
+  <si>
+    <t>267005357</t>
+  </si>
+  <si>
+    <t>267005416</t>
+  </si>
+  <si>
+    <t>267005495</t>
+  </si>
+  <si>
+    <t>267005552</t>
+  </si>
+  <si>
+    <t>267005562</t>
+  </si>
+  <si>
+    <t>267005563</t>
+  </si>
+  <si>
+    <t>267005567</t>
+  </si>
+  <si>
+    <t>267005582</t>
+  </si>
+  <si>
+    <t>267005593</t>
+  </si>
+  <si>
+    <t>267005602</t>
+  </si>
+  <si>
+    <t>26MPE0004080</t>
+  </si>
+  <si>
+    <t>308139973</t>
+  </si>
+  <si>
+    <t>308140536</t>
+  </si>
+  <si>
+    <t>NFD6-04-09-2F6M</t>
+  </si>
+  <si>
+    <t>NFD6-04-11-6DE6</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-R4RZ</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-TK26</t>
+  </si>
+  <si>
+    <t>NFD6-04-13-AD7J</t>
+  </si>
+  <si>
+    <t>NFD6-04-13-XACD</t>
+  </si>
+  <si>
+    <t>NFD6-04-13-Z7LD</t>
+  </si>
+  <si>
+    <t>NFD6-04-14-LJHG</t>
+  </si>
+  <si>
+    <t>NFD6-04-14-R88T</t>
+  </si>
+  <si>
+    <t>NFD6-04-14-VS6A</t>
+  </si>
+  <si>
+    <t>NFD6-04-15-7XNT</t>
+  </si>
+  <si>
+    <t>NFD6-04-15-95HJ</t>
+  </si>
+  <si>
+    <t>NFD6-04-15-A6U4</t>
+  </si>
+  <si>
+    <t>NFD6-04-15-EFAR</t>
+  </si>
+  <si>
+    <t>NFD6-04-15-GMM6</t>
+  </si>
+  <si>
+    <t>NFD6-04-15-GXRT</t>
+  </si>
+  <si>
+    <t>NFD6-04-15-JMWC</t>
+  </si>
+  <si>
+    <t>NFD6-04-15-YME8</t>
+  </si>
+  <si>
+    <t>NFD6-04-16-6JB5</t>
+  </si>
+  <si>
+    <t>NFD6-04-16-LN7A</t>
+  </si>
+  <si>
+    <t>NFD6-04-17-EQN3</t>
+  </si>
+  <si>
+    <t>NFE6-04-13-4HX7</t>
+  </si>
+  <si>
+    <t>NFE6-04-13-LKE3</t>
+  </si>
+  <si>
+    <t>NFE6-04-15-2DJ3</t>
+  </si>
+  <si>
+    <t>NFE6-04-15-W33C</t>
+  </si>
+  <si>
+    <t>NFE6-04-16-59YQ</t>
+  </si>
+  <si>
+    <t>NFE6-04-16-UFP2</t>
+  </si>
+  <si>
+    <t>VA26/001580/1_csere</t>
   </si>
 </sst>
 </file>
@@ -303,10 +915,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -588,7 +1199,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
@@ -609,8 +1220,11 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>101</v>
       </c>
       <c r="C2" t="s">
         <v>79</v>
@@ -618,665 +1232,887 @@
       <c r="D2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
+      <c r="B3" t="s">
+        <v>102</v>
+      </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D3"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
+      <c r="B4" t="s">
+        <v>103</v>
+      </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D4"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="B7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="B8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="C8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="B9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="C9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="B11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="C11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="B12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="C12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>15</v>
       </c>
-      <c r="C13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>16</v>
       </c>
-      <c r="C14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="B15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>17</v>
       </c>
-      <c r="C15" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="B16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="C16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="B18" t="s">
+        <v>117</v>
+      </c>
+      <c r="C18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="C17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="B19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="C18" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="B20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="C19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="B21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="C20" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="B23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>23</v>
       </c>
-      <c r="C21" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="B25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>24</v>
       </c>
-      <c r="C22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="B26" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>25</v>
       </c>
-      <c r="C23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="B27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>26</v>
       </c>
-      <c r="C24" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="B28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C28" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>27</v>
       </c>
-      <c r="C25" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="B29" t="s">
+        <v>128</v>
+      </c>
+      <c r="C29" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>28</v>
       </c>
-      <c r="C26" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="B30" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>242</v>
+      </c>
+      <c r="B31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>243</v>
+      </c>
+      <c r="B32" t="s">
+        <v>131</v>
+      </c>
+      <c r="C32" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>244</v>
+      </c>
+      <c r="B33" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" t="s">
+        <v>95</v>
+      </c>
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>245</v>
+      </c>
+      <c r="B34" t="s">
+        <v>133</v>
+      </c>
+      <c r="C34" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>246</v>
+      </c>
+      <c r="B35" t="s">
+        <v>134</v>
+      </c>
+      <c r="C35" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>247</v>
+      </c>
+      <c r="B36" t="s">
+        <v>135</v>
+      </c>
+      <c r="C36" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>248</v>
+      </c>
+      <c r="B37" t="s">
+        <v>136</v>
+      </c>
+      <c r="C37" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>249</v>
+      </c>
+      <c r="B38" t="s">
+        <v>137</v>
+      </c>
+      <c r="C38" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>250</v>
+      </c>
+      <c r="B39" t="s">
+        <v>138</v>
+      </c>
+      <c r="C39" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>250</v>
+      </c>
+      <c r="B40" t="s">
+        <v>139</v>
+      </c>
+      <c r="C40" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>250</v>
+      </c>
+      <c r="B41" t="s">
+        <v>140</v>
+      </c>
+      <c r="C41" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>251</v>
+      </c>
+      <c r="B42" t="s">
+        <v>141</v>
+      </c>
+      <c r="C42" t="s">
+        <v>84</v>
+      </c>
+      <c r="D42"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>252</v>
+      </c>
+      <c r="B43" t="s">
+        <v>142</v>
+      </c>
+      <c r="C43" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>253</v>
+      </c>
+      <c r="B44" t="s">
+        <v>143</v>
+      </c>
+      <c r="C44" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>29</v>
       </c>
-      <c r="C27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="B45" t="s">
+        <v>144</v>
+      </c>
+      <c r="C45" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B46" t="s">
+        <v>145</v>
+      </c>
+      <c r="C46" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>29</v>
+      </c>
+      <c r="B47" t="s">
+        <v>146</v>
+      </c>
+      <c r="C47" t="s">
+        <v>91</v>
+      </c>
+      <c r="D47"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>30</v>
       </c>
-      <c r="C28" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="B48" t="s">
+        <v>147</v>
+      </c>
+      <c r="C48" t="s">
+        <v>96</v>
+      </c>
+      <c r="D48"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>31</v>
       </c>
-      <c r="C29" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="B49" t="s">
+        <v>148</v>
+      </c>
+      <c r="C49" t="s">
+        <v>95</v>
+      </c>
+      <c r="D49"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>31</v>
+      </c>
+      <c r="B50" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" t="s">
+        <v>95</v>
+      </c>
+      <c r="D50"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>3</v>
       </c>
-      <c r="C30" t="s">
-        <v>79</v>
-      </c>
-      <c r="D30"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="B51" t="s">
+        <v>150</v>
+      </c>
+      <c r="C51" t="s">
+        <v>82</v>
+      </c>
+      <c r="D51"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>254</v>
+      </c>
+      <c r="B52" t="s">
+        <v>151</v>
+      </c>
+      <c r="C52" t="s">
+        <v>83</v>
+      </c>
+      <c r="D52"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>32</v>
       </c>
-      <c r="C31" t="s">
-        <v>79</v>
-      </c>
-      <c r="D31"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="B53" t="s">
+        <v>152</v>
+      </c>
+      <c r="C53" t="s">
+        <v>89</v>
+      </c>
+      <c r="D53"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>33</v>
       </c>
-      <c r="C32" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="B54" t="s">
+        <v>153</v>
+      </c>
+      <c r="C54" t="s">
+        <v>85</v>
+      </c>
+      <c r="D54"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>34</v>
       </c>
-      <c r="C33" t="s">
-        <v>79</v>
-      </c>
-      <c r="D33"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="B55" t="s">
+        <v>154</v>
+      </c>
+      <c r="C55" t="s">
+        <v>88</v>
+      </c>
+      <c r="D55"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>35</v>
       </c>
-      <c r="C34" t="s">
-        <v>79</v>
-      </c>
-      <c r="D34"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="B56" t="s">
+        <v>155</v>
+      </c>
+      <c r="C56" t="s">
+        <v>95</v>
+      </c>
+      <c r="D56"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>36</v>
       </c>
-      <c r="C35" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+      <c r="B57" t="s">
+        <v>156</v>
+      </c>
+      <c r="C57" t="s">
+        <v>82</v>
+      </c>
+      <c r="D57"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>36</v>
+      </c>
+      <c r="B58" t="s">
+        <v>157</v>
+      </c>
+      <c r="C58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D58"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>255</v>
+      </c>
+      <c r="B59" t="s">
+        <v>158</v>
+      </c>
+      <c r="C59" t="s">
+        <v>96</v>
+      </c>
+      <c r="D59"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>37</v>
       </c>
-      <c r="C36" t="s">
-        <v>79</v>
-      </c>
-      <c r="D36"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+      <c r="B60" t="s">
+        <v>159</v>
+      </c>
+      <c r="C60" t="s">
+        <v>84</v>
+      </c>
+      <c r="D60"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>38</v>
       </c>
-      <c r="C37" t="s">
-        <v>79</v>
-      </c>
-      <c r="D37"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="B61" t="s">
+        <v>160</v>
+      </c>
+      <c r="C61" t="s">
+        <v>97</v>
+      </c>
+      <c r="D61"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" t="s">
+        <v>161</v>
+      </c>
+      <c r="C62" t="s">
+        <v>97</v>
+      </c>
+      <c r="D62"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>39</v>
       </c>
-      <c r="C38" t="s">
-        <v>79</v>
-      </c>
-      <c r="D38"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="B63" t="s">
+        <v>162</v>
+      </c>
+      <c r="C63" t="s">
+        <v>92</v>
+      </c>
+      <c r="D63"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>40</v>
       </c>
-      <c r="C39" t="s">
-        <v>79</v>
-      </c>
-      <c r="D39"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="B64" t="s">
+        <v>163</v>
+      </c>
+      <c r="C64" t="s">
+        <v>84</v>
+      </c>
+      <c r="D64"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>41</v>
       </c>
-      <c r="C40" t="s">
-        <v>79</v>
-      </c>
-      <c r="D40"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="B65" t="s">
+        <v>164</v>
+      </c>
+      <c r="C65" t="s">
+        <v>97</v>
+      </c>
+      <c r="D65"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>42</v>
       </c>
-      <c r="C41" t="s">
-        <v>79</v>
-      </c>
-      <c r="D41"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+      <c r="B66" t="s">
+        <v>165</v>
+      </c>
+      <c r="C66" t="s">
+        <v>90</v>
+      </c>
+      <c r="D66"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>43</v>
       </c>
-      <c r="C42" t="s">
-        <v>79</v>
-      </c>
-      <c r="D42"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+      <c r="B67" t="s">
+        <v>166</v>
+      </c>
+      <c r="C67" t="s">
+        <v>82</v>
+      </c>
+      <c r="D67"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>44</v>
       </c>
-      <c r="C43" t="s">
-        <v>79</v>
-      </c>
-      <c r="D43"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+      <c r="B68" t="s">
+        <v>167</v>
+      </c>
+      <c r="C68" t="s">
+        <v>90</v>
+      </c>
+      <c r="D68"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>45</v>
       </c>
-      <c r="C44" t="s">
-        <v>79</v>
-      </c>
-      <c r="D44"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+      <c r="B69" t="s">
+        <v>168</v>
+      </c>
+      <c r="C69" t="s">
+        <v>96</v>
+      </c>
+      <c r="D69"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>45</v>
+      </c>
+      <c r="B70" t="s">
+        <v>169</v>
+      </c>
+      <c r="C70" t="s">
+        <v>96</v>
+      </c>
+      <c r="D70"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>45</v>
+      </c>
+      <c r="B71" t="s">
+        <v>170</v>
+      </c>
+      <c r="C71" t="s">
+        <v>96</v>
+      </c>
+      <c r="D71"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>46</v>
       </c>
-      <c r="C45" t="s">
-        <v>79</v>
-      </c>
-      <c r="D45"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+      <c r="B72" t="s">
+        <v>171</v>
+      </c>
+      <c r="C72" t="s">
+        <v>84</v>
+      </c>
+      <c r="D72"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>47</v>
       </c>
-      <c r="C46" t="s">
-        <v>79</v>
-      </c>
-      <c r="D46"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+      <c r="B73" t="s">
+        <v>172</v>
+      </c>
+      <c r="C73" t="s">
+        <v>98</v>
+      </c>
+      <c r="D73"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>48</v>
       </c>
-      <c r="C47" t="s">
-        <v>79</v>
-      </c>
-      <c r="D47"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+      <c r="B74" t="s">
+        <v>173</v>
+      </c>
+      <c r="C74" t="s">
+        <v>84</v>
+      </c>
+      <c r="D74"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>49</v>
       </c>
-      <c r="C48" t="s">
-        <v>79</v>
-      </c>
-      <c r="D48"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+      <c r="B75" t="s">
+        <v>174</v>
+      </c>
+      <c r="C75" t="s">
+        <v>87</v>
+      </c>
+      <c r="D75"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>50</v>
       </c>
-      <c r="C49" t="s">
-        <v>79</v>
-      </c>
-      <c r="D49"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C50" t="s">
-        <v>79</v>
-      </c>
-      <c r="D50"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C51" t="s">
-        <v>79</v>
-      </c>
-      <c r="D51"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C52" t="s">
-        <v>79</v>
-      </c>
-      <c r="D52"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C53" t="s">
-        <v>79</v>
-      </c>
-      <c r="D53"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" t="s">
-        <v>79</v>
-      </c>
-      <c r="D54"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C55" t="s">
-        <v>79</v>
-      </c>
-      <c r="D55"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56" t="s">
-        <v>79</v>
-      </c>
-      <c r="D56"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" t="s">
-        <v>79</v>
-      </c>
-      <c r="D57"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C58" t="s">
-        <v>79</v>
-      </c>
-      <c r="D58"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C59" t="s">
-        <v>79</v>
-      </c>
-      <c r="D59"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" t="s">
-        <v>79</v>
-      </c>
-      <c r="D60"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C61" t="s">
-        <v>79</v>
-      </c>
-      <c r="D61"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C62" t="s">
-        <v>79</v>
-      </c>
-      <c r="D62"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C63" t="s">
-        <v>79</v>
-      </c>
-      <c r="D63"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C64" t="s">
-        <v>79</v>
-      </c>
-      <c r="D64"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C65" t="s">
-        <v>79</v>
-      </c>
-      <c r="D65"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C66" t="s">
-        <v>79</v>
-      </c>
-      <c r="D66"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C67" t="s">
-        <v>79</v>
-      </c>
-      <c r="D67"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C68" t="s">
-        <v>79</v>
-      </c>
-      <c r="D68"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C69" t="s">
-        <v>79</v>
-      </c>
-      <c r="D69"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C70" t="s">
-        <v>79</v>
-      </c>
-      <c r="D70"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C71" t="s">
-        <v>79</v>
-      </c>
-      <c r="D71"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C72" t="s">
-        <v>79</v>
-      </c>
-      <c r="D72"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C73" t="s">
-        <v>79</v>
-      </c>
-      <c r="D73"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C74" t="s">
-        <v>79</v>
-      </c>
-      <c r="D74"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C75" t="s">
-        <v>79</v>
-      </c>
-      <c r="D75"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>77</v>
+      <c r="B76" t="s">
+        <v>175</v>
       </c>
       <c r="C76" t="s">
         <v>79</v>
@@ -1284,8 +2120,11 @@
       <c r="D76"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>78</v>
+      <c r="A77" t="s">
+        <v>50</v>
+      </c>
+      <c r="B77" t="s">
+        <v>176</v>
       </c>
       <c r="C77" t="s">
         <v>79</v>
@@ -1293,49 +2132,745 @@
       <c r="D77"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>51</v>
+      </c>
+      <c r="B78" t="s">
+        <v>177</v>
+      </c>
+      <c r="C78" t="s">
+        <v>81</v>
+      </c>
       <c r="D78"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>52</v>
+      </c>
+      <c r="B79" t="s">
+        <v>178</v>
+      </c>
+      <c r="C79" t="s">
+        <v>86</v>
+      </c>
       <c r="D79"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>53</v>
+      </c>
+      <c r="B80" t="s">
+        <v>179</v>
+      </c>
+      <c r="C80" t="s">
+        <v>94</v>
+      </c>
       <c r="D80"/>
     </row>
-    <row r="81" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>54</v>
+      </c>
+      <c r="B81" t="s">
+        <v>180</v>
+      </c>
+      <c r="C81" t="s">
+        <v>81</v>
+      </c>
       <c r="D81"/>
     </row>
-    <row r="82" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>55</v>
+      </c>
+      <c r="B82" t="s">
+        <v>181</v>
+      </c>
+      <c r="C82" t="s">
+        <v>81</v>
+      </c>
       <c r="D82"/>
     </row>
-    <row r="83" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>56</v>
+      </c>
+      <c r="B83" t="s">
+        <v>182</v>
+      </c>
+      <c r="C83" t="s">
+        <v>99</v>
+      </c>
       <c r="D83"/>
     </row>
-    <row r="84" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>57</v>
+      </c>
+      <c r="B84" t="s">
+        <v>183</v>
+      </c>
+      <c r="C84" t="s">
+        <v>81</v>
+      </c>
       <c r="D84"/>
     </row>
-    <row r="85" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>57</v>
+      </c>
+      <c r="B85" t="s">
+        <v>184</v>
+      </c>
+      <c r="C85" t="s">
+        <v>81</v>
+      </c>
       <c r="D85"/>
     </row>
-    <row r="86" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>58</v>
+      </c>
+      <c r="B86" t="s">
+        <v>185</v>
+      </c>
+      <c r="C86" t="s">
+        <v>84</v>
+      </c>
       <c r="D86"/>
     </row>
-    <row r="87" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>59</v>
+      </c>
+      <c r="B87" t="s">
+        <v>186</v>
+      </c>
+      <c r="C87" t="s">
+        <v>85</v>
+      </c>
       <c r="D87"/>
     </row>
-    <row r="88" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>60</v>
+      </c>
+      <c r="B88" t="s">
+        <v>187</v>
+      </c>
+      <c r="C88" t="s">
+        <v>85</v>
+      </c>
       <c r="D88"/>
     </row>
-    <row r="89" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>61</v>
+      </c>
+      <c r="B89" t="s">
+        <v>188</v>
+      </c>
+      <c r="C89" t="s">
+        <v>100</v>
+      </c>
       <c r="D89"/>
     </row>
-    <row r="90" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>61</v>
+      </c>
+      <c r="B90" t="s">
+        <v>189</v>
+      </c>
+      <c r="C90" t="s">
+        <v>100</v>
+      </c>
       <c r="D90"/>
     </row>
-    <row r="91" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>62</v>
+      </c>
+      <c r="B91" t="s">
+        <v>190</v>
+      </c>
+      <c r="C91" t="s">
+        <v>85</v>
+      </c>
       <c r="D91"/>
     </row>
-    <row r="92" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>63</v>
+      </c>
+      <c r="B92" t="s">
+        <v>191</v>
+      </c>
+      <c r="C92" t="s">
+        <v>81</v>
+      </c>
       <c r="D92"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>64</v>
+      </c>
+      <c r="B93" t="s">
+        <v>192</v>
+      </c>
+      <c r="C93" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>65</v>
+      </c>
+      <c r="B94" t="s">
+        <v>193</v>
+      </c>
+      <c r="C94" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>66</v>
+      </c>
+      <c r="B95" t="s">
+        <v>194</v>
+      </c>
+      <c r="C95" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>67</v>
+      </c>
+      <c r="B96" t="s">
+        <v>195</v>
+      </c>
+      <c r="C96" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>67</v>
+      </c>
+      <c r="B97" t="s">
+        <v>196</v>
+      </c>
+      <c r="C97" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>68</v>
+      </c>
+      <c r="B98" t="s">
+        <v>197</v>
+      </c>
+      <c r="C98" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>68</v>
+      </c>
+      <c r="B99" t="s">
+        <v>198</v>
+      </c>
+      <c r="C99" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>69</v>
+      </c>
+      <c r="B100" t="s">
+        <v>199</v>
+      </c>
+      <c r="C100" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>70</v>
+      </c>
+      <c r="B101" t="s">
+        <v>200</v>
+      </c>
+      <c r="C101" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>71</v>
+      </c>
+      <c r="B102" t="s">
+        <v>201</v>
+      </c>
+      <c r="C102" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>72</v>
+      </c>
+      <c r="B103" t="s">
+        <v>202</v>
+      </c>
+      <c r="C103" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>73</v>
+      </c>
+      <c r="B104" t="s">
+        <v>203</v>
+      </c>
+      <c r="C104" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>74</v>
+      </c>
+      <c r="B105" t="s">
+        <v>204</v>
+      </c>
+      <c r="C105" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>75</v>
+      </c>
+      <c r="B106" t="s">
+        <v>205</v>
+      </c>
+      <c r="C106" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>76</v>
+      </c>
+      <c r="B107" t="s">
+        <v>206</v>
+      </c>
+      <c r="C107" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>77</v>
+      </c>
+      <c r="B108" t="s">
+        <v>207</v>
+      </c>
+      <c r="C108" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>78</v>
+      </c>
+      <c r="B109" t="s">
+        <v>208</v>
+      </c>
+      <c r="C109" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>256</v>
+      </c>
+      <c r="B110" t="s">
+        <v>209</v>
+      </c>
+      <c r="C110" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>256</v>
+      </c>
+      <c r="B111" t="s">
+        <v>210</v>
+      </c>
+      <c r="C111" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>257</v>
+      </c>
+      <c r="B112" t="s">
+        <v>211</v>
+      </c>
+      <c r="C112" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>258</v>
+      </c>
+      <c r="B113" t="s">
+        <v>212</v>
+      </c>
+      <c r="C113" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>258</v>
+      </c>
+      <c r="B114" t="s">
+        <v>213</v>
+      </c>
+      <c r="C114" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>259</v>
+      </c>
+      <c r="B115" t="s">
+        <v>214</v>
+      </c>
+      <c r="C115" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>260</v>
+      </c>
+      <c r="B116" t="s">
+        <v>215</v>
+      </c>
+      <c r="C116" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>261</v>
+      </c>
+      <c r="B117" t="s">
+        <v>216</v>
+      </c>
+      <c r="C117" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>262</v>
+      </c>
+      <c r="B118" t="s">
+        <v>217</v>
+      </c>
+      <c r="C118" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>263</v>
+      </c>
+      <c r="B119" t="s">
+        <v>218</v>
+      </c>
+      <c r="C119" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>264</v>
+      </c>
+      <c r="B120" t="s">
+        <v>219</v>
+      </c>
+      <c r="C120" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>265</v>
+      </c>
+      <c r="B121" t="s">
+        <v>220</v>
+      </c>
+      <c r="C121" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>266</v>
+      </c>
+      <c r="B122" t="s">
+        <v>221</v>
+      </c>
+      <c r="C122" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>267</v>
+      </c>
+      <c r="B123" t="s">
+        <v>222</v>
+      </c>
+      <c r="C123" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>268</v>
+      </c>
+      <c r="B124" t="s">
+        <v>223</v>
+      </c>
+      <c r="C124" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>269</v>
+      </c>
+      <c r="B125" t="s">
+        <v>224</v>
+      </c>
+      <c r="C125" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>270</v>
+      </c>
+      <c r="B126" t="s">
+        <v>225</v>
+      </c>
+      <c r="C126" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>271</v>
+      </c>
+      <c r="B127" t="s">
+        <v>226</v>
+      </c>
+      <c r="C127" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>272</v>
+      </c>
+      <c r="B128" t="s">
+        <v>227</v>
+      </c>
+      <c r="C128" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>273</v>
+      </c>
+      <c r="B129" t="s">
+        <v>228</v>
+      </c>
+      <c r="C129" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>274</v>
+      </c>
+      <c r="B130" t="s">
+        <v>229</v>
+      </c>
+      <c r="C130" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>274</v>
+      </c>
+      <c r="B131" t="s">
+        <v>230</v>
+      </c>
+      <c r="C131" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>275</v>
+      </c>
+      <c r="B132" t="s">
+        <v>231</v>
+      </c>
+      <c r="C132" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>276</v>
+      </c>
+      <c r="B133" t="s">
+        <v>232</v>
+      </c>
+      <c r="C133" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>277</v>
+      </c>
+      <c r="B134" t="s">
+        <v>233</v>
+      </c>
+      <c r="C134" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>278</v>
+      </c>
+      <c r="B135" t="s">
+        <v>234</v>
+      </c>
+      <c r="C135" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>279</v>
+      </c>
+      <c r="B136" t="s">
+        <v>235</v>
+      </c>
+      <c r="C136" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>280</v>
+      </c>
+      <c r="B137" t="s">
+        <v>236</v>
+      </c>
+      <c r="C137" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>281</v>
+      </c>
+      <c r="B138" t="s">
+        <v>237</v>
+      </c>
+      <c r="C138" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>282</v>
+      </c>
+      <c r="B139" t="s">
+        <v>238</v>
+      </c>
+      <c r="C139" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>283</v>
+      </c>
+      <c r="B140" t="s">
+        <v>239</v>
+      </c>
+      <c r="C140" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>240</v>
+      </c>
+      <c r="B141" t="s">
+        <v>240</v>
+      </c>
+      <c r="C141" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>240</v>
+      </c>
+      <c r="B142" t="s">
+        <v>240</v>
+      </c>
+      <c r="C142" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>241</v>
+      </c>
+      <c r="B143" t="s">
+        <v>241</v>
+      </c>
+      <c r="C143" t="s">
+        <v>80</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="C1" xr:uid="{66E3D377-5F1B-48CD-A9ED-4AF810829D06}"/>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB7221A-0846-4D0C-A2F7-E72D8F9E722F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E51558F-D9FD-408B-9B72-CA14C796FB75}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="267">
   <si>
     <t>UTK</t>
   </si>
@@ -820,6 +820,15 @@
   </si>
   <si>
     <t>SZ 2026 140442</t>
+  </si>
+  <si>
+    <t>NFD6-04-24-5DAV</t>
+  </si>
+  <si>
+    <t>NFD6-04-22-PRGH</t>
+  </si>
+  <si>
+    <t>NFD6-04-23-WSR4</t>
   </si>
 </sst>
 </file>
@@ -1139,1520 +1148,1597 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D144"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="A33" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="A34" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="A35" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="A36" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="A37" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="A38" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="A39" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="A40" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="A41" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="A42" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="A44" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="A45" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="A48" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="A49" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="A51" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="A52" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="A53" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="A54" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="A55" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="A56" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="A57" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="A58" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="A59" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="1" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="A60" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="1" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="A61" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="1" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="A62" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="A63" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="A64" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="A65" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+      <c r="A66" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="A67" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+      <c r="A68" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+      <c r="A69" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+      <c r="A70" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="A71" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+      <c r="A72" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="A73" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+      <c r="A74" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+      <c r="A75" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+      <c r="A76" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="1" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+      <c r="A77" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="1" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+      <c r="A78" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+      <c r="A79" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+      <c r="A80" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+      <c r="A81" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+      <c r="A82" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+      <c r="A83" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+      <c r="A84" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="1" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+      <c r="A85" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+      <c r="A86" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+      <c r="A87" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+      <c r="A88" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+      <c r="A89" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+      <c r="A90" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+      <c r="A91" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="1" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+      <c r="A92" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+      <c r="A93" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+      <c r="A94" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+      <c r="A95" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+      <c r="A96" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+      <c r="A97" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+      <c r="A98" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
+      <c r="A99" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+      <c r="A100" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+      <c r="A101" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+      <c r="A102" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+      <c r="A103" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="1" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+      <c r="A104" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+      <c r="A105" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+      <c r="A106" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+      <c r="A107" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+      <c r="A108" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+      <c r="A109" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="1" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+      <c r="A110" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+      <c r="A111" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="1" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+      <c r="A112" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
+      <c r="A113" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
+      <c r="A114" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
+      <c r="A115" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
+      <c r="A116" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
+      <c r="A117" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
+      <c r="A118" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
+      <c r="A119" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
+      <c r="A120" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
+      <c r="A121" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C121" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
+      <c r="A122" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C122" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
+      <c r="A123" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C123" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
+      <c r="A124" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C124" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
+      <c r="A125" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C125" s="1" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
+      <c r="A126" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C126" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
+      <c r="A127" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C127" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
+      <c r="A128" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C128" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
+      <c r="A129" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C129" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
+      <c r="A130" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C130" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
+      <c r="A131" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C131" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
+      <c r="A132" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C132" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
+      <c r="A133" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C133" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
+      <c r="A134" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C134" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
+      <c r="A135" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C135" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
+      <c r="A136" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C136" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
+      <c r="A137" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C137" s="1" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>267006081</v>
+      </c>
+      <c r="B138" s="1">
+        <v>267006081</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>267006035</v>
+      </c>
+      <c r="B140" s="1">
+        <v>267006035</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
+        <v>267006021</v>
+      </c>
+      <c r="B141" s="1">
+        <v>267006021</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" s="1">
+        <v>267006036</v>
+      </c>
+      <c r="B142" s="1">
+        <v>267006036</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAEF2A02-D89A-488E-894A-CCE51F716477}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1C6ACB-7E32-464D-9B52-840A1003F9CE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="290">
   <si>
     <t>UTK</t>
   </si>
@@ -765,12 +765,6 @@
     <t>202604302600978901</t>
   </si>
   <si>
-    <t>NFD6-04-30-MHGX/1</t>
-  </si>
-  <si>
-    <t>NFD6-05-03-SZ9T/1</t>
-  </si>
-  <si>
     <t>202604292600973101</t>
   </si>
   <si>
@@ -876,12 +870,6 @@
     <t>NFD6-04-29-SART</t>
   </si>
   <si>
-    <t>NFD6-04-30-MHGX</t>
-  </si>
-  <si>
-    <t>NFD6-05-03-SZ9T</t>
-  </si>
-  <si>
     <t>NFE6-04-28-E7BH</t>
   </si>
   <si>
@@ -907,6 +895,9 @@
   </si>
   <si>
     <t>260429-F00004477</t>
+  </si>
+  <si>
+    <t>NFD6-04-27-GCQ7/2</t>
   </si>
 </sst>
 </file>
@@ -1226,7 +1217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D144"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" style="1" bestFit="1" customWidth="1"/>
@@ -1704,7 +1695,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>39</v>
@@ -1716,7 +1707,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>40</v>
@@ -1728,7 +1719,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>41</v>
@@ -1740,7 +1731,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>42</v>
@@ -1752,7 +1743,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>43</v>
@@ -1764,7 +1755,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>44</v>
@@ -1776,7 +1767,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>45</v>
@@ -1788,7 +1779,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>46</v>
@@ -1800,7 +1791,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>47</v>
@@ -1812,7 +1803,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>166</v>
@@ -2625,7 +2616,7 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>235</v>
@@ -2636,7 +2627,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>236</v>
@@ -2647,7 +2638,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>237</v>
@@ -2658,7 +2649,7 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>238</v>
@@ -2669,7 +2660,7 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>239</v>
@@ -2680,7 +2671,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>240</v>
@@ -2691,7 +2682,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>241</v>
@@ -2702,7 +2693,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>242</v>
@@ -2713,7 +2704,7 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>243</v>
@@ -2724,7 +2715,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>244</v>
@@ -2735,18 +2726,18 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>245</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>246</v>
@@ -2757,51 +2748,51 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>247</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>248</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>249</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>250</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>251</v>
@@ -2812,112 +2803,101 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>252</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>253</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>254</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>255</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>256</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>290</v>
+        <v>257</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>257</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A141" s="1" t="s">
-        <v>291</v>
+      <c r="A141" s="1">
+        <v>310143527</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>258</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>259</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A143" s="1">
-        <v>310143527</v>
+      <c r="A143" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A144" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64383A70-6D4A-46D8-BD4D-4A59F0101EF3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D41598-E8DE-40EA-ABCF-FB9085FCEB0B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="122">
   <si>
     <t>UTK</t>
   </si>
@@ -39,370 +39,358 @@
     <t>CSOMAGSZAM</t>
   </si>
   <si>
-    <t>260424-F00009501</t>
-  </si>
-  <si>
-    <t>260427-F00015844</t>
-  </si>
-  <si>
-    <t>260429-F00004477</t>
-  </si>
-  <si>
-    <t>248745523</t>
-  </si>
-  <si>
-    <t>248745709</t>
-  </si>
-  <si>
-    <t>260207-F00002720-1</t>
-  </si>
-  <si>
-    <t>260410-F00014398</t>
-  </si>
-  <si>
-    <t>260420-F00000911</t>
-  </si>
-  <si>
-    <t>260420-F00015264</t>
-  </si>
-  <si>
-    <t>260424-W00003832</t>
-  </si>
-  <si>
-    <t>260425-F00000960</t>
-  </si>
-  <si>
-    <t>260425-F00002647</t>
-  </si>
-  <si>
-    <t>260427-F00004732</t>
-  </si>
-  <si>
-    <t>260427-W00004706</t>
-  </si>
-  <si>
-    <t>260428-F00003850</t>
-  </si>
-  <si>
-    <t>260428-F00011235</t>
-  </si>
-  <si>
     <t>260429-F00002639</t>
   </si>
   <si>
-    <t>260429-F00012274</t>
-  </si>
-  <si>
-    <t>260429-W00003092</t>
-  </si>
-  <si>
-    <t>260429-W00006970</t>
-  </si>
-  <si>
-    <t>260430-F00004514</t>
-  </si>
-  <si>
-    <t>260430-F00005595</t>
-  </si>
-  <si>
-    <t>260430-F00006181</t>
-  </si>
-  <si>
-    <t>260430-F00012172</t>
-  </si>
-  <si>
-    <t>260430-F00012282</t>
-  </si>
-  <si>
-    <t>260430-F00012917</t>
-  </si>
-  <si>
-    <t>260430-W00002397</t>
-  </si>
-  <si>
-    <t>260430-W00003952</t>
-  </si>
-  <si>
-    <t>260430-W00005114</t>
-  </si>
-  <si>
-    <t>260430-W00005295</t>
-  </si>
-  <si>
-    <t>260430-W00007134</t>
-  </si>
-  <si>
-    <t>260430-W00008791</t>
-  </si>
-  <si>
-    <t>260502-F00003150</t>
-  </si>
-  <si>
-    <t>260502-F00003814</t>
-  </si>
-  <si>
-    <t>260502-W00001695</t>
-  </si>
-  <si>
-    <t>260502-W00002225</t>
-  </si>
-  <si>
-    <t>260502-W00003983-2</t>
-  </si>
-  <si>
-    <t>260503-F00002164</t>
-  </si>
-  <si>
-    <t>260503-W00003651</t>
-  </si>
-  <si>
-    <t>260504-W00004741</t>
-  </si>
-  <si>
-    <t>260504-W00004916</t>
-  </si>
-  <si>
-    <t>FIZZ-1000889860</t>
-  </si>
-  <si>
-    <t>FIZZ-1000895534</t>
-  </si>
-  <si>
-    <t>FIZZ-1000895967</t>
-  </si>
-  <si>
-    <t>FIZZ-1000897201</t>
-  </si>
-  <si>
-    <t>FIZZ-1000897605</t>
-  </si>
-  <si>
-    <t>1449-567859</t>
-  </si>
-  <si>
-    <t>FIZZ-1000897808</t>
-  </si>
-  <si>
-    <t>FIZZ-1000898107</t>
-  </si>
-  <si>
-    <t>FIZZ-1000898185</t>
-  </si>
-  <si>
     <t>301872897/2</t>
   </si>
   <si>
-    <t>308294708</t>
-  </si>
-  <si>
-    <t>308466998</t>
-  </si>
-  <si>
-    <t>309199560</t>
-  </si>
-  <si>
-    <t>309261210</t>
-  </si>
-  <si>
-    <t>309339752</t>
-  </si>
-  <si>
-    <t>309404433</t>
-  </si>
-  <si>
-    <t>309589622</t>
-  </si>
-  <si>
-    <t>309683633</t>
-  </si>
-  <si>
-    <t>309684429</t>
-  </si>
-  <si>
-    <t>309829984</t>
-  </si>
-  <si>
-    <t>309830110</t>
-  </si>
-  <si>
-    <t>309884314</t>
-  </si>
-  <si>
-    <t>309884496</t>
-  </si>
-  <si>
-    <t>309884889</t>
-  </si>
-  <si>
-    <t>309884958</t>
-  </si>
-  <si>
-    <t>309885262</t>
-  </si>
-  <si>
-    <t>309940506</t>
-  </si>
-  <si>
-    <t>309940617</t>
-  </si>
-  <si>
-    <t>309940792</t>
-  </si>
-  <si>
-    <t>309940879</t>
-  </si>
-  <si>
-    <t>309941096</t>
-  </si>
-  <si>
-    <t>309941151</t>
-  </si>
-  <si>
-    <t>309999974</t>
-  </si>
-  <si>
-    <t>310000072</t>
-  </si>
-  <si>
-    <t>310000303</t>
-  </si>
-  <si>
-    <t>310000366</t>
-  </si>
-  <si>
-    <t>310000502</t>
-  </si>
-  <si>
-    <t>310000896</t>
-  </si>
-  <si>
-    <t>310062969</t>
-  </si>
-  <si>
-    <t>310063158</t>
-  </si>
-  <si>
-    <t>310063196</t>
-  </si>
-  <si>
-    <t>310063463</t>
-  </si>
-  <si>
-    <t>310063619</t>
-  </si>
-  <si>
-    <t>310063786</t>
-  </si>
-  <si>
     <t>310143662</t>
   </si>
   <si>
-    <t>310143863</t>
-  </si>
-  <si>
-    <t>310143993</t>
-  </si>
-  <si>
-    <t>310144044</t>
-  </si>
-  <si>
-    <t>310144099</t>
-  </si>
-  <si>
-    <t>310144149</t>
-  </si>
-  <si>
-    <t>310144221</t>
-  </si>
-  <si>
-    <t>310144250</t>
-  </si>
-  <si>
-    <t>310228415</t>
-  </si>
-  <si>
-    <t>310228854</t>
-  </si>
-  <si>
-    <t>310228916</t>
-  </si>
-  <si>
-    <t>310229207</t>
-  </si>
-  <si>
-    <t>310229269</t>
-  </si>
-  <si>
-    <t>310299613</t>
-  </si>
-  <si>
-    <t>310299751</t>
-  </si>
-  <si>
-    <t>310299826</t>
-  </si>
-  <si>
-    <t>310300020</t>
-  </si>
-  <si>
-    <t>310300035</t>
-  </si>
-  <si>
-    <t>310300156</t>
-  </si>
-  <si>
-    <t>310300249</t>
-  </si>
-  <si>
-    <t>310300295</t>
-  </si>
-  <si>
-    <t>310300302</t>
-  </si>
-  <si>
-    <t>310300362</t>
-  </si>
-  <si>
-    <t>310300444</t>
-  </si>
-  <si>
-    <t>310300465</t>
-  </si>
-  <si>
-    <t>310353797</t>
-  </si>
-  <si>
-    <t>310353867</t>
-  </si>
-  <si>
-    <t>310354078</t>
-  </si>
-  <si>
-    <t>310354167</t>
-  </si>
-  <si>
-    <t>310354322</t>
-  </si>
-  <si>
-    <t>310412520</t>
-  </si>
-  <si>
-    <t>310412592</t>
-  </si>
-  <si>
-    <t>310412777</t>
-  </si>
-  <si>
-    <t>310412839</t>
-  </si>
-  <si>
-    <t>310467744</t>
-  </si>
-  <si>
-    <t>99002444</t>
-  </si>
-  <si>
-    <t>99002473</t>
+    <t>260427-F00011882</t>
+  </si>
+  <si>
+    <t>260427-F00013298</t>
+  </si>
+  <si>
+    <t>260427-W00007227</t>
+  </si>
+  <si>
+    <t>260427-W00010379</t>
+  </si>
+  <si>
+    <t>260428-F00011880</t>
+  </si>
+  <si>
+    <t>260429-F00014028</t>
+  </si>
+  <si>
+    <t>260429-W00006100</t>
+  </si>
+  <si>
+    <t>260430-F00008634</t>
+  </si>
+  <si>
+    <t>260430-F00013137</t>
+  </si>
+  <si>
+    <t>260430-F00013189</t>
+  </si>
+  <si>
+    <t>260430-W00004215</t>
+  </si>
+  <si>
+    <t>260430-W00004697</t>
+  </si>
+  <si>
+    <t>260430-W00004975</t>
+  </si>
+  <si>
+    <t>260430-W00007130</t>
+  </si>
+  <si>
+    <t>260430-W00007179</t>
+  </si>
+  <si>
+    <t>260501-F00000519</t>
+  </si>
+  <si>
+    <t>260501-W00004077</t>
+  </si>
+  <si>
+    <t>260501-W00007408</t>
+  </si>
+  <si>
+    <t>260502-F00005298</t>
+  </si>
+  <si>
+    <t>260502-W00001444</t>
+  </si>
+  <si>
+    <t>260502-W00001605</t>
+  </si>
+  <si>
+    <t>260502-W00002739</t>
+  </si>
+  <si>
+    <t>260502-W00003874</t>
+  </si>
+  <si>
+    <t>260502-W00004825</t>
+  </si>
+  <si>
+    <t>260502-W00005810</t>
+  </si>
+  <si>
+    <t>260502-W00008308</t>
+  </si>
+  <si>
+    <t>260503-F00001916</t>
+  </si>
+  <si>
+    <t>260503-F00002032-1</t>
+  </si>
+  <si>
+    <t>260503-F00002084</t>
+  </si>
+  <si>
+    <t>260503-F00002579</t>
+  </si>
+  <si>
+    <t>260503-F00003021</t>
+  </si>
+  <si>
+    <t>260503-W00001387</t>
+  </si>
+  <si>
+    <t>260503-W00001972</t>
+  </si>
+  <si>
+    <t>260503-W00003312</t>
+  </si>
+  <si>
+    <t>260503-W00004055</t>
+  </si>
+  <si>
+    <t>260503-W00004881</t>
+  </si>
+  <si>
+    <t>260503-W00007719</t>
+  </si>
+  <si>
+    <t>260504-F00002814</t>
+  </si>
+  <si>
+    <t>260504-F00004680</t>
+  </si>
+  <si>
+    <t>260504-F00004967</t>
+  </si>
+  <si>
+    <t>260504-F00014772</t>
+  </si>
+  <si>
+    <t>260504-W00004142</t>
+  </si>
+  <si>
+    <t>260504-W00012214</t>
+  </si>
+  <si>
+    <t>260505-W00001380</t>
+  </si>
+  <si>
+    <t>260505-W00004243</t>
+  </si>
+  <si>
+    <t>305411701</t>
+  </si>
+  <si>
+    <t>308543554</t>
+  </si>
+  <si>
+    <t>309261743</t>
+  </si>
+  <si>
+    <t>309338917</t>
+  </si>
+  <si>
+    <t>309684549</t>
+  </si>
+  <si>
+    <t>309729179</t>
+  </si>
+  <si>
+    <t>309779586</t>
+  </si>
+  <si>
+    <t>309780218</t>
+  </si>
+  <si>
+    <t>309829735</t>
+  </si>
+  <si>
+    <t>309884570</t>
+  </si>
+  <si>
+    <t>309885095</t>
+  </si>
+  <si>
+    <t>309885104</t>
+  </si>
+  <si>
+    <t>309940421</t>
+  </si>
+  <si>
+    <t>309940713</t>
+  </si>
+  <si>
+    <t>309941097</t>
+  </si>
+  <si>
+    <t>309941134</t>
+  </si>
+  <si>
+    <t>309999943</t>
+  </si>
+  <si>
+    <t>309999999</t>
+  </si>
+  <si>
+    <t>310000341</t>
+  </si>
+  <si>
+    <t>310062876</t>
+  </si>
+  <si>
+    <t>310063075</t>
+  </si>
+  <si>
+    <t>310063320</t>
+  </si>
+  <si>
+    <t>310143421</t>
+  </si>
+  <si>
+    <t>310144322</t>
+  </si>
+  <si>
+    <t>310144324</t>
+  </si>
+  <si>
+    <t>310228344</t>
+  </si>
+  <si>
+    <t>310228472</t>
+  </si>
+  <si>
+    <t>310228586</t>
+  </si>
+  <si>
+    <t>310228649</t>
+  </si>
+  <si>
+    <t>310229022</t>
+  </si>
+  <si>
+    <t>310229098</t>
+  </si>
+  <si>
+    <t>310229240</t>
+  </si>
+  <si>
+    <t>310299837</t>
+  </si>
+  <si>
+    <t>310299842</t>
+  </si>
+  <si>
+    <t>310299960</t>
+  </si>
+  <si>
+    <t>310300118</t>
+  </si>
+  <si>
+    <t>310300459</t>
+  </si>
+  <si>
+    <t>310353751</t>
+  </si>
+  <si>
+    <t>310353927</t>
+  </si>
+  <si>
+    <t>310353969</t>
+  </si>
+  <si>
+    <t>310354121</t>
+  </si>
+  <si>
+    <t>310354381</t>
+  </si>
+  <si>
+    <t>310354452</t>
+  </si>
+  <si>
+    <t>310354526</t>
+  </si>
+  <si>
+    <t>310411968</t>
+  </si>
+  <si>
+    <t>310411973</t>
+  </si>
+  <si>
+    <t>310412055</t>
+  </si>
+  <si>
+    <t>310412136</t>
+  </si>
+  <si>
+    <t>310412195</t>
+  </si>
+  <si>
+    <t>310412240</t>
+  </si>
+  <si>
+    <t>310412349</t>
+  </si>
+  <si>
+    <t>310412439</t>
+  </si>
+  <si>
+    <t>310412474</t>
+  </si>
+  <si>
+    <t>310412678</t>
+  </si>
+  <si>
+    <t>310412756</t>
+  </si>
+  <si>
+    <t>310412786</t>
+  </si>
+  <si>
+    <t>310467815</t>
+  </si>
+  <si>
+    <t>310467829</t>
+  </si>
+  <si>
+    <t>310467931</t>
+  </si>
+  <si>
+    <t>310467973</t>
+  </si>
+  <si>
+    <t>310467992</t>
+  </si>
+  <si>
+    <t>310468104</t>
+  </si>
+  <si>
+    <t>310468231</t>
+  </si>
+  <si>
+    <t>310468335</t>
+  </si>
+  <si>
+    <t>310468419</t>
+  </si>
+  <si>
+    <t>310468448</t>
+  </si>
+  <si>
+    <t>310573122</t>
+  </si>
+  <si>
+    <t>310620145</t>
+  </si>
+  <si>
+    <t>99002470</t>
+  </si>
+  <si>
+    <t>99002472</t>
   </si>
   <si>
     <t>SZ</t>
@@ -726,23 +714,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -750,8 +738,8 @@
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>125</v>
+      <c r="C2" t="s">
+        <v>121</v>
       </c>
       <c r="D2"/>
     </row>
@@ -759,8 +747,8 @@
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>125</v>
+      <c r="C3" t="s">
+        <v>121</v>
       </c>
       <c r="D3"/>
     </row>
@@ -768,8 +756,8 @@
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>125</v>
+      <c r="C4" t="s">
+        <v>121</v>
       </c>
       <c r="D4"/>
     </row>
@@ -777,8 +765,8 @@
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>125</v>
+      <c r="C5" t="s">
+        <v>121</v>
       </c>
       <c r="D5"/>
     </row>
@@ -786,26 +774,26 @@
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>125</v>
+      <c r="C6" t="s">
+        <v>121</v>
       </c>
       <c r="D6"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>125</v>
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>121</v>
       </c>
       <c r="D7"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>125</v>
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>121</v>
       </c>
       <c r="D8"/>
     </row>
@@ -813,8 +801,8 @@
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>125</v>
+      <c r="C9" t="s">
+        <v>121</v>
       </c>
       <c r="D9"/>
     </row>
@@ -822,8 +810,8 @@
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>125</v>
+      <c r="C10" t="s">
+        <v>121</v>
       </c>
       <c r="D10"/>
     </row>
@@ -831,8 +819,8 @@
       <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>125</v>
+      <c r="C11" t="s">
+        <v>121</v>
       </c>
       <c r="D11"/>
     </row>
@@ -840,548 +828,548 @@
       <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>125</v>
+      <c r="C12" t="s">
+        <v>121</v>
       </c>
       <c r="D12"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>125</v>
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>121</v>
       </c>
       <c r="D13"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>125</v>
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>121</v>
       </c>
       <c r="D14"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>125</v>
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>121</v>
       </c>
       <c r="D15"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>125</v>
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>121</v>
       </c>
       <c r="D16"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>125</v>
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>121</v>
       </c>
       <c r="D17"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>125</v>
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
+        <v>121</v>
       </c>
       <c r="D18"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>125</v>
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
+        <v>121</v>
       </c>
       <c r="D19"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>125</v>
+        <v>23</v>
+      </c>
+      <c r="C20" t="s">
+        <v>121</v>
       </c>
       <c r="D20"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>125</v>
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>121</v>
       </c>
       <c r="D21"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>125</v>
+        <v>25</v>
+      </c>
+      <c r="C22" t="s">
+        <v>121</v>
       </c>
       <c r="D22"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>125</v>
+        <v>26</v>
+      </c>
+      <c r="C23" t="s">
+        <v>121</v>
       </c>
       <c r="D23"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>125</v>
+        <v>27</v>
+      </c>
+      <c r="C24" t="s">
+        <v>121</v>
       </c>
       <c r="D24"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>125</v>
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
+        <v>121</v>
       </c>
       <c r="D25"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>125</v>
+        <v>29</v>
+      </c>
+      <c r="C26" t="s">
+        <v>121</v>
       </c>
       <c r="D26"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>125</v>
+        <v>30</v>
+      </c>
+      <c r="C27" t="s">
+        <v>121</v>
       </c>
       <c r="D27"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>125</v>
+        <v>31</v>
+      </c>
+      <c r="C28" t="s">
+        <v>121</v>
       </c>
       <c r="D28"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>125</v>
+        <v>32</v>
+      </c>
+      <c r="C29" t="s">
+        <v>121</v>
       </c>
       <c r="D29"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>125</v>
+        <v>33</v>
+      </c>
+      <c r="C30" t="s">
+        <v>121</v>
       </c>
       <c r="D30"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>125</v>
+        <v>34</v>
+      </c>
+      <c r="C31" t="s">
+        <v>121</v>
       </c>
       <c r="D31"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>125</v>
+        <v>35</v>
+      </c>
+      <c r="C32" t="s">
+        <v>121</v>
       </c>
       <c r="D32"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>125</v>
+        <v>36</v>
+      </c>
+      <c r="C33" t="s">
+        <v>121</v>
       </c>
       <c r="D33"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>125</v>
+        <v>37</v>
+      </c>
+      <c r="C34" t="s">
+        <v>121</v>
       </c>
       <c r="D34"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>125</v>
+        <v>38</v>
+      </c>
+      <c r="C35" t="s">
+        <v>121</v>
       </c>
       <c r="D35"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>125</v>
+        <v>39</v>
+      </c>
+      <c r="C36" t="s">
+        <v>121</v>
       </c>
       <c r="D36"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>125</v>
+        <v>40</v>
+      </c>
+      <c r="C37" t="s">
+        <v>121</v>
       </c>
       <c r="D37"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
+      </c>
+      <c r="C38" t="s">
+        <v>121</v>
       </c>
       <c r="D38"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>125</v>
+        <v>42</v>
+      </c>
+      <c r="C39" t="s">
+        <v>121</v>
       </c>
       <c r="D39"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>125</v>
+        <v>43</v>
+      </c>
+      <c r="C40" t="s">
+        <v>121</v>
       </c>
       <c r="D40"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>125</v>
+        <v>44</v>
+      </c>
+      <c r="C41" t="s">
+        <v>121</v>
       </c>
       <c r="D41"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>125</v>
+        <v>45</v>
+      </c>
+      <c r="C42" t="s">
+        <v>121</v>
       </c>
       <c r="D42"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>125</v>
+        <v>46</v>
+      </c>
+      <c r="C43" t="s">
+        <v>121</v>
       </c>
       <c r="D43"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>125</v>
+        <v>47</v>
+      </c>
+      <c r="C44" t="s">
+        <v>121</v>
       </c>
       <c r="D44"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>125</v>
+        <v>48</v>
+      </c>
+      <c r="C45" t="s">
+        <v>121</v>
       </c>
       <c r="D45"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>125</v>
+        <v>49</v>
+      </c>
+      <c r="C46" t="s">
+        <v>121</v>
       </c>
       <c r="D46"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>125</v>
+        <v>50</v>
+      </c>
+      <c r="C47" t="s">
+        <v>121</v>
       </c>
       <c r="D47"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>125</v>
+        <v>4</v>
+      </c>
+      <c r="C48" t="s">
+        <v>121</v>
       </c>
       <c r="D48"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>125</v>
+        <v>51</v>
+      </c>
+      <c r="C49" t="s">
+        <v>121</v>
       </c>
       <c r="D49"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>125</v>
+        <v>52</v>
+      </c>
+      <c r="C50" t="s">
+        <v>121</v>
       </c>
       <c r="D50"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>125</v>
+        <v>53</v>
+      </c>
+      <c r="C51" t="s">
+        <v>121</v>
       </c>
       <c r="D51"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>125</v>
+        <v>54</v>
+      </c>
+      <c r="C52" t="s">
+        <v>121</v>
       </c>
       <c r="D52"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>125</v>
+        <v>55</v>
+      </c>
+      <c r="C53" t="s">
+        <v>121</v>
       </c>
       <c r="D53"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>125</v>
+        <v>56</v>
+      </c>
+      <c r="C54" t="s">
+        <v>121</v>
       </c>
       <c r="D54"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>125</v>
+        <v>57</v>
+      </c>
+      <c r="C55" t="s">
+        <v>121</v>
       </c>
       <c r="D55"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>125</v>
+        <v>58</v>
+      </c>
+      <c r="C56" t="s">
+        <v>121</v>
       </c>
       <c r="D56"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>125</v>
+        <v>59</v>
+      </c>
+      <c r="C57" t="s">
+        <v>121</v>
       </c>
       <c r="D57"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>125</v>
+        <v>60</v>
+      </c>
+      <c r="C58" t="s">
+        <v>121</v>
       </c>
       <c r="D58"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>125</v>
+        <v>61</v>
+      </c>
+      <c r="C59" t="s">
+        <v>121</v>
       </c>
       <c r="D59"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>125</v>
+        <v>62</v>
+      </c>
+      <c r="C60" t="s">
+        <v>121</v>
       </c>
       <c r="D60"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>125</v>
+        <v>63</v>
+      </c>
+      <c r="C61" t="s">
+        <v>121</v>
       </c>
       <c r="D61"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>125</v>
+        <v>64</v>
+      </c>
+      <c r="C62" t="s">
+        <v>121</v>
       </c>
       <c r="D62"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>125</v>
+        <v>65</v>
+      </c>
+      <c r="C63" t="s">
+        <v>121</v>
       </c>
       <c r="D63"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>125</v>
+        <v>66</v>
+      </c>
+      <c r="C64" t="s">
+        <v>121</v>
       </c>
       <c r="D64"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>125</v>
+        <v>67</v>
+      </c>
+      <c r="C65" t="s">
+        <v>121</v>
       </c>
       <c r="D65"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>125</v>
+        <v>68</v>
+      </c>
+      <c r="C66" t="s">
+        <v>121</v>
       </c>
       <c r="D66"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>125</v>
+        <v>69</v>
+      </c>
+      <c r="C67" t="s">
+        <v>121</v>
       </c>
       <c r="D67"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>125</v>
+        <v>70</v>
+      </c>
+      <c r="C68" t="s">
+        <v>121</v>
       </c>
       <c r="D68"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>125</v>
+        <v>71</v>
+      </c>
+      <c r="C69" t="s">
+        <v>121</v>
       </c>
       <c r="D69"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>125</v>
+        <v>72</v>
+      </c>
+      <c r="C70" t="s">
+        <v>121</v>
       </c>
       <c r="D70"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>125</v>
+        <v>73</v>
+      </c>
+      <c r="C71" t="s">
+        <v>121</v>
       </c>
       <c r="D71"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>125</v>
+        <v>5</v>
+      </c>
+      <c r="C72" t="s">
+        <v>121</v>
       </c>
       <c r="D72"/>
     </row>
@@ -1389,8 +1377,8 @@
       <c r="A73" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>125</v>
+      <c r="C73" t="s">
+        <v>121</v>
       </c>
       <c r="D73"/>
     </row>
@@ -1398,8 +1386,8 @@
       <c r="A74" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>125</v>
+      <c r="C74" t="s">
+        <v>121</v>
       </c>
       <c r="D74"/>
     </row>
@@ -1407,8 +1395,8 @@
       <c r="A75" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>125</v>
+      <c r="C75" t="s">
+        <v>121</v>
       </c>
       <c r="D75"/>
     </row>
@@ -1416,8 +1404,8 @@
       <c r="A76" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>125</v>
+      <c r="C76" t="s">
+        <v>121</v>
       </c>
       <c r="D76"/>
     </row>
@@ -1425,8 +1413,8 @@
       <c r="A77" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>125</v>
+      <c r="C77" t="s">
+        <v>121</v>
       </c>
       <c r="D77"/>
     </row>
@@ -1434,8 +1422,8 @@
       <c r="A78" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>125</v>
+      <c r="C78" t="s">
+        <v>121</v>
       </c>
       <c r="D78"/>
     </row>
@@ -1443,8 +1431,8 @@
       <c r="A79" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>125</v>
+      <c r="C79" t="s">
+        <v>121</v>
       </c>
       <c r="D79"/>
     </row>
@@ -1452,8 +1440,8 @@
       <c r="A80" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>125</v>
+      <c r="C80" t="s">
+        <v>121</v>
       </c>
       <c r="D80"/>
     </row>
@@ -1461,8 +1449,8 @@
       <c r="A81" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>125</v>
+      <c r="C81" t="s">
+        <v>121</v>
       </c>
       <c r="D81"/>
     </row>
@@ -1470,8 +1458,8 @@
       <c r="A82" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>125</v>
+      <c r="C82" t="s">
+        <v>121</v>
       </c>
       <c r="D82"/>
     </row>
@@ -1479,8 +1467,8 @@
       <c r="A83" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>125</v>
+      <c r="C83" t="s">
+        <v>121</v>
       </c>
       <c r="D83"/>
     </row>
@@ -1488,8 +1476,8 @@
       <c r="A84" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>125</v>
+      <c r="C84" t="s">
+        <v>121</v>
       </c>
       <c r="D84"/>
     </row>
@@ -1497,8 +1485,8 @@
       <c r="A85" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>125</v>
+      <c r="C85" t="s">
+        <v>121</v>
       </c>
       <c r="D85"/>
     </row>
@@ -1506,8 +1494,8 @@
       <c r="A86" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>125</v>
+      <c r="C86" t="s">
+        <v>121</v>
       </c>
       <c r="D86"/>
     </row>
@@ -1515,8 +1503,8 @@
       <c r="A87" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>125</v>
+      <c r="C87" t="s">
+        <v>121</v>
       </c>
       <c r="D87"/>
     </row>
@@ -1524,8 +1512,8 @@
       <c r="A88" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>125</v>
+      <c r="C88" t="s">
+        <v>121</v>
       </c>
       <c r="D88"/>
     </row>
@@ -1533,8 +1521,8 @@
       <c r="A89" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>125</v>
+      <c r="C89" t="s">
+        <v>121</v>
       </c>
       <c r="D89"/>
     </row>
@@ -1542,8 +1530,8 @@
       <c r="A90" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>125</v>
+      <c r="C90" t="s">
+        <v>121</v>
       </c>
       <c r="D90"/>
     </row>
@@ -1551,8 +1539,8 @@
       <c r="A91" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>125</v>
+      <c r="C91" t="s">
+        <v>121</v>
       </c>
       <c r="D91"/>
     </row>
@@ -1560,8 +1548,8 @@
       <c r="A92" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>125</v>
+      <c r="C92" t="s">
+        <v>121</v>
       </c>
       <c r="D92"/>
     </row>
@@ -1569,8 +1557,8 @@
       <c r="A93" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>125</v>
+      <c r="C93" t="s">
+        <v>121</v>
       </c>
       <c r="D93"/>
     </row>
@@ -1578,8 +1566,8 @@
       <c r="A94" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>125</v>
+      <c r="C94" t="s">
+        <v>121</v>
       </c>
       <c r="D94"/>
     </row>
@@ -1587,8 +1575,8 @@
       <c r="A95" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>125</v>
+      <c r="C95" t="s">
+        <v>121</v>
       </c>
       <c r="D95"/>
     </row>
@@ -1596,8 +1584,8 @@
       <c r="A96" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>125</v>
+      <c r="C96" t="s">
+        <v>121</v>
       </c>
       <c r="D96"/>
     </row>
@@ -1605,8 +1593,8 @@
       <c r="A97" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>125</v>
+      <c r="C97" t="s">
+        <v>121</v>
       </c>
       <c r="D97"/>
     </row>
@@ -1614,8 +1602,8 @@
       <c r="A98" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>125</v>
+      <c r="C98" t="s">
+        <v>121</v>
       </c>
       <c r="D98"/>
     </row>
@@ -1623,204 +1611,168 @@
       <c r="A99" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D99"/>
+      <c r="C99" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D100"/>
+      <c r="C100" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D101"/>
+      <c r="C101" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D102"/>
+      <c r="C102" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>125</v>
+      <c r="C103" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>125</v>
+      <c r="C104" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>125</v>
+      <c r="C105" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C106" s="1" t="s">
-        <v>125</v>
+      <c r="C106" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>125</v>
+      <c r="C107" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>125</v>
+      <c r="C108" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>125</v>
+      <c r="C109" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>125</v>
+      <c r="C110" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>125</v>
+      <c r="C111" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>125</v>
+      <c r="C112" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>125</v>
+      <c r="C113" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>125</v>
+      <c r="C114" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>125</v>
+      <c r="C115" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>125</v>
+      <c r="C116" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>125</v>
+      <c r="C117" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>125</v>
+      <c r="C118" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>125</v>
+      <c r="C119" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538FE6A4-E100-49EB-84F2-1149C49DD10F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B538A706-FDD2-4220-BB85-2D0309148877}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="376">
   <si>
     <t>UTK</t>
   </si>
@@ -150,9 +150,6 @@
     <t>260506-F00006630</t>
   </si>
   <si>
-    <t>260506-W00001842</t>
-  </si>
-  <si>
     <t>260506-W00002059</t>
   </si>
   <si>
@@ -411,7 +408,754 @@
     <t>310715811</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-802</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-840</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-860</t>
+  </si>
+  <si>
+    <t>SZ-800</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>SZ-850</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-870</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>267006436</t>
+  </si>
+  <si>
+    <t>267006513</t>
+  </si>
+  <si>
+    <t>267006514</t>
+  </si>
+  <si>
+    <t>267006546</t>
+  </si>
+  <si>
+    <t>267006549</t>
+  </si>
+  <si>
+    <t>267006550</t>
+  </si>
+  <si>
+    <t>267006551</t>
+  </si>
+  <si>
+    <t>267006553</t>
+  </si>
+  <si>
+    <t>267006558</t>
+  </si>
+  <si>
+    <t>267006559</t>
+  </si>
+  <si>
+    <t>267006560</t>
+  </si>
+  <si>
+    <t>267006576</t>
+  </si>
+  <si>
+    <t>267006584</t>
+  </si>
+  <si>
+    <t>267006593</t>
+  </si>
+  <si>
+    <t>267006597</t>
+  </si>
+  <si>
+    <t>267006607</t>
+  </si>
+  <si>
+    <t>267006609</t>
+  </si>
+  <si>
+    <t>267006622</t>
+  </si>
+  <si>
+    <t>267006639</t>
+  </si>
+  <si>
+    <t>267006642</t>
+  </si>
+  <si>
+    <t>267006670</t>
+  </si>
+  <si>
+    <t>267006680</t>
+  </si>
+  <si>
+    <t>267006691</t>
+  </si>
+  <si>
+    <t>267006692</t>
+  </si>
+  <si>
+    <t>267006718</t>
+  </si>
+  <si>
+    <t>267006723</t>
+  </si>
+  <si>
+    <t>267006737</t>
+  </si>
+  <si>
+    <t>26MPE0004709</t>
+  </si>
+  <si>
+    <t>26MPE0004716</t>
+  </si>
+  <si>
+    <t>26MPE0004768</t>
+  </si>
+  <si>
+    <t>NFD6-04-28-G7BD</t>
+  </si>
+  <si>
+    <t>NFD6-04-28-TD4B</t>
+  </si>
+  <si>
+    <t>NFD6-04-29-DXGR</t>
+  </si>
+  <si>
+    <t>NFD6-04-29-JA47</t>
+  </si>
+  <si>
+    <t>NFD6-05-02-3TEY</t>
+  </si>
+  <si>
+    <t>NFD6-05-04-LMXR</t>
+  </si>
+  <si>
+    <t>NFD6-05-04-X4B9</t>
+  </si>
+  <si>
+    <t>NFD6-05-05-5KE9</t>
+  </si>
+  <si>
+    <t>NFD6-05-05-7BU5</t>
+  </si>
+  <si>
+    <t>NFD6-05-05-A6QP</t>
+  </si>
+  <si>
+    <t>NFD6-05-05-D33Q</t>
+  </si>
+  <si>
+    <t>NFD6-05-05-GMG7</t>
+  </si>
+  <si>
+    <t>NFD6-05-05-K4SC</t>
+  </si>
+  <si>
+    <t>NFD6-05-05-NT6E</t>
+  </si>
+  <si>
+    <t>NFD6-05-05-Q3J7</t>
+  </si>
+  <si>
+    <t>NFD6-05-05-S3ZC</t>
+  </si>
+  <si>
+    <t>NFD6-05-05-YVTK</t>
+  </si>
+  <si>
+    <t>NFE6-04-28-KMAC</t>
+  </si>
+  <si>
+    <t>NFE6-04-29-7MN6</t>
+  </si>
+  <si>
+    <t>NFE6-04-29-PVTQ</t>
+  </si>
+  <si>
+    <t>NFE6-04-29-ZEYC</t>
+  </si>
+  <si>
+    <t>NFE6-05-01-R5RW</t>
+  </si>
+  <si>
+    <t>NFE6-05-05-U9BT</t>
+  </si>
+  <si>
+    <t>NFE6-05-05-YWKJ</t>
+  </si>
+  <si>
+    <t>R418031</t>
+  </si>
+  <si>
+    <t>SA26/H002439</t>
+  </si>
+  <si>
+    <t>SA26/H002440</t>
+  </si>
+  <si>
+    <t>SA26/H002443</t>
+  </si>
+  <si>
+    <t>SA26/H002487</t>
+  </si>
+  <si>
+    <t>SA26/H002500</t>
+  </si>
+  <si>
+    <t>SA26/H002514</t>
+  </si>
+  <si>
+    <t>69f1c6af7d88c5c4ea84c399</t>
+  </si>
+  <si>
+    <t>69f8d44d47d1aed7c38629cc</t>
+  </si>
+  <si>
+    <t>69f30d9e47d1aed7c385ea0d</t>
+  </si>
+  <si>
+    <t>69f9c77247d1aed7c386363c</t>
+  </si>
+  <si>
+    <t>69faf3b947d1aed7c38649b4</t>
+  </si>
+  <si>
+    <t>69fae61947d1aed7c38647c0</t>
+  </si>
+  <si>
+    <t>69f3966447d1aed7c385f9d0</t>
+  </si>
+  <si>
+    <t>69f3474f47d1aed7c385f254</t>
+  </si>
+  <si>
+    <t>69f3596947d1aed7c385f4d5</t>
+  </si>
+  <si>
+    <t>69f44ad947d1aed7c385fb12</t>
+  </si>
+  <si>
+    <t>69f4a9c247d1aed7c385fd25</t>
+  </si>
+  <si>
+    <t>69f4e0cf47d1aed7c385fe49</t>
+  </si>
+  <si>
+    <t>69f4edb647d1aed7c385fe89</t>
+  </si>
+  <si>
+    <t>69f628f247d1aed7c3860771</t>
+  </si>
+  <si>
+    <t>69f628f247d1aed7c3860772</t>
+  </si>
+  <si>
+    <t>69f5cb3047d1aed7c386029a</t>
+  </si>
+  <si>
+    <t>69f5cb3047d1aed7c386029c</t>
+  </si>
+  <si>
+    <t>69f7009647d1aed7c3860980</t>
+  </si>
+  <si>
+    <t>69f7009647d1aed7c3860981</t>
+  </si>
+  <si>
+    <t>69f7009647d1aed7c3860983</t>
+  </si>
+  <si>
+    <t>69f9e22847d1aed7c3863b06</t>
+  </si>
+  <si>
+    <t>69faf34047d1aed7c38649b0</t>
+  </si>
+  <si>
+    <t>69faf34047d1aed7c38649b1</t>
+  </si>
+  <si>
+    <t>69f8847e47d1aed7c3861ec9</t>
+  </si>
+  <si>
+    <t>69f8847e47d1aed7c3861ecb</t>
+  </si>
+  <si>
+    <t>69f8847547d1aed7c3861ea3</t>
+  </si>
+  <si>
+    <t>69f8afd847d1aed7c38625be</t>
+  </si>
+  <si>
+    <t>69f8afd847d1aed7c38625bf</t>
+  </si>
+  <si>
+    <t>69f8bf0c47d1aed7c38627a8</t>
+  </si>
+  <si>
+    <t>69f8bf0c47d1aed7c38627a9</t>
+  </si>
+  <si>
+    <t>69f8591d47d1aed7c3861645</t>
+  </si>
+  <si>
+    <t>69f8a67b47d1aed7c386247a</t>
+  </si>
+  <si>
+    <t>69f8dc5747d1aed7c3862a4d</t>
+  </si>
+  <si>
+    <t>69f8f3cd47d1aed7c3862b6c</t>
+  </si>
+  <si>
+    <t>69f8f87c47d1aed7c3862b9a</t>
+  </si>
+  <si>
+    <t>69f907ba47d1aed7c3862be0</t>
+  </si>
+  <si>
+    <t>69fa222347d1aed7c38643c8</t>
+  </si>
+  <si>
+    <t>69fa222347d1aed7c38643cc</t>
+  </si>
+  <si>
+    <t>69fa34eb47d1aed7c3864523</t>
+  </si>
+  <si>
+    <t>69fa34eb47d1aed7c3864524</t>
+  </si>
+  <si>
+    <t>69f9920147d1aed7c3862d1d</t>
+  </si>
+  <si>
+    <t>69f9b2d947d1aed7c38632ec</t>
+  </si>
+  <si>
+    <t>69f9e1b647d1aed7c3863adf</t>
+  </si>
+  <si>
+    <t>69f9f6d447d1aed7c3863e74</t>
+  </si>
+  <si>
+    <t>69fb184447d1aed7c3865092</t>
+  </si>
+  <si>
+    <t>69fb171047d1aed7c3865045</t>
+  </si>
+  <si>
+    <t>69faee1947d1aed7c38648da</t>
+  </si>
+  <si>
+    <t>69fb07d247d1aed7c3864d9e</t>
+  </si>
+  <si>
+    <t>69fb1a9947d1aed7c38650c2</t>
+  </si>
+  <si>
+    <t>69fb1a9947d1aed7c38650c3</t>
+  </si>
+  <si>
+    <t>26MPE0004709/1</t>
+  </si>
+  <si>
+    <t>26MPE0004716/1</t>
+  </si>
+  <si>
+    <t>26MPE0004768/1</t>
+  </si>
+  <si>
+    <t>308467671/1</t>
+  </si>
+  <si>
+    <t>308467671/2</t>
+  </si>
+  <si>
+    <t>308650182/1</t>
+  </si>
+  <si>
+    <t>308650940/1</t>
+  </si>
+  <si>
+    <t>309632428/1</t>
+  </si>
+  <si>
+    <t>309632428/2</t>
+  </si>
+  <si>
+    <t>309830253/1</t>
+  </si>
+  <si>
+    <t>309884483/1</t>
+  </si>
+  <si>
+    <t>309884555/1</t>
+  </si>
+  <si>
+    <t>309884555/2</t>
+  </si>
+  <si>
+    <t>309884758/1</t>
+  </si>
+  <si>
+    <t>309940549/1</t>
+  </si>
+  <si>
+    <t>309940549/2</t>
+  </si>
+  <si>
+    <t>309940591/1</t>
+  </si>
+  <si>
+    <t>309940681/1</t>
+  </si>
+  <si>
+    <t>310000238/1</t>
+  </si>
+  <si>
+    <t>310000549/1</t>
+  </si>
+  <si>
+    <t>310000759/1</t>
+  </si>
+  <si>
+    <t>310229134/1</t>
+  </si>
+  <si>
+    <t>310229134/2</t>
+  </si>
+  <si>
+    <t>310299868/1</t>
+  </si>
+  <si>
+    <t>310299944/1</t>
+  </si>
+  <si>
+    <t>310354214/1</t>
+  </si>
+  <si>
+    <t>310467662/1</t>
+  </si>
+  <si>
+    <t>310467718/1</t>
+  </si>
+  <si>
+    <t>310467718/2</t>
+  </si>
+  <si>
+    <t>310467718/3</t>
+  </si>
+  <si>
+    <t>310468079/1</t>
+  </si>
+  <si>
+    <t>310468079/2</t>
+  </si>
+  <si>
+    <t>310468179/1</t>
+  </si>
+  <si>
+    <t>310468443/1</t>
+  </si>
+  <si>
+    <t>310468443/2</t>
+  </si>
+  <si>
+    <t>310468443/3</t>
+  </si>
+  <si>
+    <t>310468624/1</t>
+  </si>
+  <si>
+    <t>310520603/1</t>
+  </si>
+  <si>
+    <t>310520634/1</t>
+  </si>
+  <si>
+    <t>310520849/1</t>
+  </si>
+  <si>
+    <t>310520849/2</t>
+  </si>
+  <si>
+    <t>310520849/3</t>
+  </si>
+  <si>
+    <t>310520864/1</t>
+  </si>
+  <si>
+    <t>310520875/1</t>
+  </si>
+  <si>
+    <t>310520929/1</t>
+  </si>
+  <si>
+    <t>310520973/1</t>
+  </si>
+  <si>
+    <t>310521000/1</t>
+  </si>
+  <si>
+    <t>310521094/1</t>
+  </si>
+  <si>
+    <t>310521174/1</t>
+  </si>
+  <si>
+    <t>310521212/1</t>
+  </si>
+  <si>
+    <t>310521295/1</t>
+  </si>
+  <si>
+    <t>310521312/1</t>
+  </si>
+  <si>
+    <t>310521403/1</t>
+  </si>
+  <si>
+    <t>310521403/2</t>
+  </si>
+  <si>
+    <t>310572585/1</t>
+  </si>
+  <si>
+    <t>310572614/1</t>
+  </si>
+  <si>
+    <t>310572720/1</t>
+  </si>
+  <si>
+    <t>310572720/2</t>
+  </si>
+  <si>
+    <t>310572743/1</t>
+  </si>
+  <si>
+    <t>310572860/1</t>
+  </si>
+  <si>
+    <t>310572903/1</t>
+  </si>
+  <si>
+    <t>310572943/1</t>
+  </si>
+  <si>
+    <t>310573013/1</t>
+  </si>
+  <si>
+    <t>310573050/1</t>
+  </si>
+  <si>
+    <t>310573149/1</t>
+  </si>
+  <si>
+    <t>310573194/1</t>
+  </si>
+  <si>
+    <t>310573194/2</t>
+  </si>
+  <si>
+    <t>310573347/1</t>
+  </si>
+  <si>
+    <t>310573347/2</t>
+  </si>
+  <si>
+    <t>310573347/3</t>
+  </si>
+  <si>
+    <t>310573384/1</t>
+  </si>
+  <si>
+    <t>310573384/2</t>
+  </si>
+  <si>
+    <t>310620191/1</t>
+  </si>
+  <si>
+    <t>310620300/1</t>
+  </si>
+  <si>
+    <t>310620427/1</t>
+  </si>
+  <si>
+    <t>310715688/1</t>
+  </si>
+  <si>
+    <t>310715811/1</t>
+  </si>
+  <si>
+    <t>NFD6-04-28-G7BD/1</t>
+  </si>
+  <si>
+    <t>202605062600971101</t>
+  </si>
+  <si>
+    <t>202605062600977101</t>
+  </si>
+  <si>
+    <t>202605062600975201</t>
+  </si>
+  <si>
+    <t>202605042600989601</t>
+  </si>
+  <si>
+    <t>202605052600999901</t>
+  </si>
+  <si>
+    <t>202605052600999201</t>
+  </si>
+  <si>
+    <t>202605062601009201</t>
+  </si>
+  <si>
+    <t>202605062601006001</t>
+  </si>
+  <si>
+    <t>202605062601005301</t>
+  </si>
+  <si>
+    <t>202605062601005302</t>
+  </si>
+  <si>
+    <t>202605062601006901</t>
+  </si>
+  <si>
+    <t>202605062601007001</t>
+  </si>
+  <si>
+    <t>202605062601010201</t>
+  </si>
+  <si>
+    <t>202605062601008801</t>
+  </si>
+  <si>
+    <t>202605062601006601</t>
+  </si>
+  <si>
+    <t>202605062601006201</t>
+  </si>
+  <si>
+    <t>202605062601005401</t>
+  </si>
+  <si>
+    <t>202605062600969401</t>
+  </si>
+  <si>
+    <t>202605062600974901</t>
+  </si>
+  <si>
+    <t>202605062600976901</t>
+  </si>
+  <si>
+    <t>202605062600978301</t>
+  </si>
+  <si>
+    <t>202605042600986401</t>
+  </si>
+  <si>
+    <t>202605062601007901</t>
+  </si>
+  <si>
+    <t>202605062601007902</t>
+  </si>
+  <si>
+    <t>202605062601007301</t>
+  </si>
+  <si>
+    <t>159995579539636348</t>
+  </si>
+  <si>
+    <t>159995579539789976</t>
+  </si>
+  <si>
+    <t>159995579539789983</t>
+  </si>
+  <si>
+    <t>159995579539789990</t>
+  </si>
+  <si>
+    <t>159995579539790033</t>
+  </si>
+  <si>
+    <t>159995579539790040</t>
+  </si>
+  <si>
+    <t>159995579539790057</t>
+  </si>
+  <si>
+    <t>159995579539800978</t>
+  </si>
+  <si>
+    <t>159995579539800985</t>
+  </si>
+  <si>
+    <t>159995579539873019</t>
+  </si>
+  <si>
+    <t>159995579539881854</t>
+  </si>
+  <si>
+    <t>159995579539881861</t>
+  </si>
+  <si>
+    <t>159995579539891587</t>
   </si>
 </sst>
 </file>
@@ -447,10 +1191,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -732,7 +1475,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D194"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
@@ -753,995 +1496,2126 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
+      <c r="B2" t="s">
+        <v>210</v>
+      </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>211</v>
       </c>
       <c r="C3" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
+      <c r="B4" t="s">
+        <v>212</v>
+      </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
+      <c r="B5" t="s">
+        <v>213</v>
+      </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
+      <c r="B6" t="s">
+        <v>214</v>
+      </c>
       <c r="C6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>11</v>
       </c>
+      <c r="B7" t="s">
+        <v>215</v>
+      </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>3</v>
       </c>
+      <c r="B8" t="s">
+        <v>216</v>
+      </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>4</v>
       </c>
+      <c r="B9" t="s">
+        <v>217</v>
+      </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
+      <c r="B10" t="s">
+        <v>218</v>
+      </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" t="s">
         <v>13</v>
       </c>
+      <c r="B11" t="s">
+        <v>219</v>
+      </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" t="s">
         <v>14</v>
       </c>
+      <c r="B12" t="s">
+        <v>220</v>
+      </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" t="s">
         <v>15</v>
       </c>
+      <c r="B13" t="s">
+        <v>221</v>
+      </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" t="s">
         <v>16</v>
       </c>
+      <c r="B14" t="s">
+        <v>222</v>
+      </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" t="s">
         <v>5</v>
       </c>
+      <c r="B15" t="s">
+        <v>223</v>
+      </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>224</v>
+      </c>
+      <c r="C16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="C16" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="B17" t="s">
+        <v>225</v>
+      </c>
+      <c r="C17" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>226</v>
+      </c>
+      <c r="C18" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="C17" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="B19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>228</v>
+      </c>
+      <c r="C20" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>229</v>
+      </c>
+      <c r="C21" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>19</v>
       </c>
-      <c r="C18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="B22" t="s">
+        <v>230</v>
+      </c>
+      <c r="C22" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>20</v>
       </c>
-      <c r="C19" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="B23" t="s">
+        <v>231</v>
+      </c>
+      <c r="C23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>232</v>
+      </c>
+      <c r="C24" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>21</v>
       </c>
-      <c r="C20" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="B25" t="s">
+        <v>233</v>
+      </c>
+      <c r="C25" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" t="s">
+        <v>234</v>
+      </c>
+      <c r="C26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>22</v>
       </c>
-      <c r="C21" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="B27" t="s">
+        <v>235</v>
+      </c>
+      <c r="C27" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>23</v>
       </c>
-      <c r="C22" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="B28" t="s">
+        <v>236</v>
+      </c>
+      <c r="C28" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>237</v>
+      </c>
+      <c r="C29" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>24</v>
       </c>
-      <c r="C23" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="B30" t="s">
+        <v>238</v>
+      </c>
+      <c r="C30" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" t="s">
+        <v>239</v>
+      </c>
+      <c r="C31" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>25</v>
       </c>
-      <c r="C24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="B32" t="s">
+        <v>240</v>
+      </c>
+      <c r="C32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>26</v>
       </c>
-      <c r="C25" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="B33" t="s">
+        <v>241</v>
+      </c>
+      <c r="C33" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>27</v>
       </c>
-      <c r="C26" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="B34" t="s">
+        <v>242</v>
+      </c>
+      <c r="C34" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>28</v>
       </c>
-      <c r="C27" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="B35" t="s">
+        <v>243</v>
+      </c>
+      <c r="C35" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>29</v>
       </c>
-      <c r="C28" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="B36" t="s">
+        <v>244</v>
+      </c>
+      <c r="C36" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>30</v>
       </c>
-      <c r="C29" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="B37" t="s">
+        <v>245</v>
+      </c>
+      <c r="C37" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>31</v>
       </c>
-      <c r="C30" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="B38" t="s">
+        <v>246</v>
+      </c>
+      <c r="C38" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>32</v>
       </c>
-      <c r="C31" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="B39" t="s">
+        <v>247</v>
+      </c>
+      <c r="C39" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>33</v>
       </c>
-      <c r="C32" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="B40" t="s">
+        <v>248</v>
+      </c>
+      <c r="C40" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" t="s">
+        <v>249</v>
+      </c>
+      <c r="C41" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>34</v>
       </c>
-      <c r="C33" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>43</v>
+      <c r="B42" t="s">
+        <v>250</v>
       </c>
       <c r="C42" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+      <c r="A43" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" t="s">
+        <v>251</v>
+      </c>
+      <c r="C43" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" t="s">
+        <v>252</v>
+      </c>
+      <c r="C44" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" t="s">
+        <v>253</v>
+      </c>
+      <c r="C45" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" t="s">
+        <v>254</v>
+      </c>
+      <c r="C46" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" t="s">
+        <v>255</v>
+      </c>
+      <c r="C47" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" t="s">
+        <v>256</v>
+      </c>
+      <c r="C48" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" t="s">
+        <v>257</v>
+      </c>
+      <c r="C49" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" t="s">
+        <v>258</v>
+      </c>
+      <c r="C50" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51" t="s">
+        <v>259</v>
+      </c>
+      <c r="C51" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>149</v>
+      </c>
+      <c r="B52" t="s">
+        <v>43</v>
+      </c>
+      <c r="C52" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>150</v>
+      </c>
+      <c r="B53" t="s">
         <v>44</v>
       </c>
-      <c r="C43" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+      <c r="C53" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>151</v>
+      </c>
+      <c r="B54" t="s">
         <v>45</v>
       </c>
-      <c r="C44" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+      <c r="C54" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>152</v>
+      </c>
+      <c r="B55" t="s">
         <v>46</v>
       </c>
-      <c r="C45" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+      <c r="C55" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>153</v>
+      </c>
+      <c r="B56" t="s">
         <v>47</v>
       </c>
-      <c r="C46" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+      <c r="C56" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>154</v>
+      </c>
+      <c r="B57" t="s">
         <v>48</v>
       </c>
-      <c r="C47" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+      <c r="C57" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>155</v>
+      </c>
+      <c r="B58" t="s">
         <v>49</v>
       </c>
-      <c r="C48" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+      <c r="C58" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>156</v>
+      </c>
+      <c r="B59" t="s">
         <v>50</v>
       </c>
-      <c r="C49" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+      <c r="C59" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>157</v>
+      </c>
+      <c r="B60" t="s">
         <v>51</v>
       </c>
-      <c r="C50" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
+      <c r="C60" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>158</v>
+      </c>
+      <c r="B61" t="s">
         <v>52</v>
       </c>
-      <c r="C51" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+      <c r="C61" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>159</v>
+      </c>
+      <c r="B62" t="s">
         <v>53</v>
       </c>
-      <c r="C52" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
+      <c r="C62" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>160</v>
+      </c>
+      <c r="B63" t="s">
         <v>54</v>
       </c>
-      <c r="C53" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
+      <c r="C63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>161</v>
+      </c>
+      <c r="B64" t="s">
         <v>55</v>
       </c>
-      <c r="C54" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
+      <c r="C64" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>162</v>
+      </c>
+      <c r="B65" t="s">
         <v>56</v>
       </c>
-      <c r="C55" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
+      <c r="C65" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>163</v>
+      </c>
+      <c r="B66" t="s">
         <v>57</v>
       </c>
-      <c r="C56" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
+      <c r="C66" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>164</v>
+      </c>
+      <c r="B67" t="s">
         <v>58</v>
       </c>
-      <c r="C57" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
+      <c r="C67" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>165</v>
+      </c>
+      <c r="B68" t="s">
         <v>59</v>
       </c>
-      <c r="C58" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
+      <c r="C68" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>166</v>
+      </c>
+      <c r="B69" t="s">
         <v>60</v>
       </c>
-      <c r="C59" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+      <c r="C69" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>167</v>
+      </c>
+      <c r="B70" t="s">
         <v>61</v>
       </c>
-      <c r="C60" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
+      <c r="C70" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>168</v>
+      </c>
+      <c r="B71" t="s">
         <v>62</v>
       </c>
-      <c r="C61" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
+      <c r="C71" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>169</v>
+      </c>
+      <c r="B72" t="s">
         <v>63</v>
       </c>
-      <c r="C62" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
+      <c r="C72" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>170</v>
+      </c>
+      <c r="B73" t="s">
         <v>64</v>
       </c>
-      <c r="C63" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
+      <c r="C73" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>171</v>
+      </c>
+      <c r="B74" t="s">
         <v>65</v>
       </c>
-      <c r="C64" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
+      <c r="C74" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>172</v>
+      </c>
+      <c r="B75" t="s">
         <v>66</v>
       </c>
-      <c r="C65" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
+      <c r="C75" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>173</v>
+      </c>
+      <c r="B76" t="s">
         <v>67</v>
       </c>
-      <c r="C66" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
+      <c r="C76" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>174</v>
+      </c>
+      <c r="B77" t="s">
         <v>68</v>
       </c>
-      <c r="C67" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
+      <c r="C77" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>175</v>
+      </c>
+      <c r="B78" t="s">
         <v>69</v>
       </c>
-      <c r="C68" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
+      <c r="C78" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>176</v>
+      </c>
+      <c r="B79" t="s">
+        <v>260</v>
+      </c>
+      <c r="C79" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>177</v>
+      </c>
+      <c r="B80" t="s">
+        <v>261</v>
+      </c>
+      <c r="C80" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" t="s">
+        <v>262</v>
+      </c>
+      <c r="C81" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>70</v>
       </c>
-      <c r="C69" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
+      <c r="B82" t="s">
+        <v>263</v>
+      </c>
+      <c r="C82" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>70</v>
+      </c>
+      <c r="B83" t="s">
+        <v>264</v>
+      </c>
+      <c r="C83" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>71</v>
       </c>
-      <c r="C70" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
+      <c r="B84" t="s">
+        <v>265</v>
+      </c>
+      <c r="C84" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>72</v>
       </c>
-      <c r="C71" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
+      <c r="B85" t="s">
+        <v>266</v>
+      </c>
+      <c r="C85" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>73</v>
       </c>
-      <c r="C72" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
+      <c r="B86" t="s">
+        <v>267</v>
+      </c>
+      <c r="C86" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>73</v>
+      </c>
+      <c r="B87" t="s">
+        <v>268</v>
+      </c>
+      <c r="C87" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
         <v>74</v>
       </c>
-      <c r="C73" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
+      <c r="B88" t="s">
+        <v>269</v>
+      </c>
+      <c r="C88" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>75</v>
       </c>
-      <c r="C74" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
+      <c r="B89" t="s">
+        <v>270</v>
+      </c>
+      <c r="C89" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>76</v>
       </c>
-      <c r="C75" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C76" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C77" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C78" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C79" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C80" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C81" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C82" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C83" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C84" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C85" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C86" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C87" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C88" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C89" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>91</v>
+      <c r="B90" t="s">
+        <v>271</v>
       </c>
       <c r="C90" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>92</v>
+      <c r="A91" t="s">
+        <v>76</v>
+      </c>
+      <c r="B91" t="s">
+        <v>272</v>
       </c>
       <c r="C91" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>93</v>
+      <c r="A92" t="s">
+        <v>77</v>
+      </c>
+      <c r="B92" t="s">
+        <v>273</v>
       </c>
       <c r="C92" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>94</v>
+      <c r="A93" t="s">
+        <v>78</v>
+      </c>
+      <c r="B93" t="s">
+        <v>274</v>
       </c>
       <c r="C93" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
-        <v>95</v>
+      <c r="A94" t="s">
+        <v>78</v>
+      </c>
+      <c r="B94" t="s">
+        <v>275</v>
       </c>
       <c r="C94" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>96</v>
+      <c r="A95" t="s">
+        <v>79</v>
+      </c>
+      <c r="B95" t="s">
+        <v>276</v>
       </c>
       <c r="C95" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>97</v>
+      <c r="A96" t="s">
+        <v>80</v>
+      </c>
+      <c r="B96" t="s">
+        <v>277</v>
       </c>
       <c r="C96" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
-        <v>98</v>
+      <c r="A97" t="s">
+        <v>81</v>
+      </c>
+      <c r="B97" t="s">
+        <v>278</v>
       </c>
       <c r="C97" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>99</v>
+      <c r="A98" t="s">
+        <v>82</v>
+      </c>
+      <c r="B98" t="s">
+        <v>279</v>
       </c>
       <c r="C98" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>100</v>
+      <c r="A99" t="s">
+        <v>83</v>
+      </c>
+      <c r="B99" t="s">
+        <v>280</v>
       </c>
       <c r="C99" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>101</v>
+      <c r="A100" t="s">
+        <v>84</v>
+      </c>
+      <c r="B100" t="s">
+        <v>281</v>
       </c>
       <c r="C100" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>102</v>
+      <c r="A101" t="s">
+        <v>84</v>
+      </c>
+      <c r="B101" t="s">
+        <v>282</v>
       </c>
       <c r="C101" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
-        <v>103</v>
+      <c r="A102" t="s">
+        <v>85</v>
+      </c>
+      <c r="B102" t="s">
+        <v>283</v>
       </c>
       <c r="C102" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
-        <v>104</v>
+      <c r="A103" t="s">
+        <v>86</v>
+      </c>
+      <c r="B103" t="s">
+        <v>284</v>
       </c>
       <c r="C103" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
-        <v>105</v>
+      <c r="A104" t="s">
+        <v>87</v>
+      </c>
+      <c r="B104" t="s">
+        <v>285</v>
       </c>
       <c r="C104" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
-        <v>106</v>
+      <c r="A105" t="s">
+        <v>88</v>
+      </c>
+      <c r="B105" t="s">
+        <v>286</v>
       </c>
       <c r="C105" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
+      <c r="A106" t="s">
+        <v>89</v>
+      </c>
+      <c r="B106" t="s">
+        <v>287</v>
+      </c>
+      <c r="C106" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>89</v>
+      </c>
+      <c r="B107" t="s">
+        <v>288</v>
+      </c>
+      <c r="C107" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>89</v>
+      </c>
+      <c r="B108" t="s">
+        <v>289</v>
+      </c>
+      <c r="C108" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>90</v>
+      </c>
+      <c r="B109" t="s">
+        <v>290</v>
+      </c>
+      <c r="C109" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>90</v>
+      </c>
+      <c r="B110" t="s">
+        <v>291</v>
+      </c>
+      <c r="C110" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>91</v>
+      </c>
+      <c r="B111" t="s">
+        <v>292</v>
+      </c>
+      <c r="C111" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>92</v>
+      </c>
+      <c r="B112" t="s">
+        <v>293</v>
+      </c>
+      <c r="C112" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>92</v>
+      </c>
+      <c r="B113" t="s">
+        <v>294</v>
+      </c>
+      <c r="C113" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>92</v>
+      </c>
+      <c r="B114" t="s">
+        <v>295</v>
+      </c>
+      <c r="C114" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>93</v>
+      </c>
+      <c r="B115" t="s">
+        <v>296</v>
+      </c>
+      <c r="C115" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>94</v>
+      </c>
+      <c r="B116" t="s">
+        <v>297</v>
+      </c>
+      <c r="C116" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>95</v>
+      </c>
+      <c r="B117" t="s">
+        <v>298</v>
+      </c>
+      <c r="C117" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>96</v>
+      </c>
+      <c r="B118" t="s">
+        <v>299</v>
+      </c>
+      <c r="C118" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>96</v>
+      </c>
+      <c r="B119" t="s">
+        <v>300</v>
+      </c>
+      <c r="C119" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>96</v>
+      </c>
+      <c r="B120" t="s">
+        <v>301</v>
+      </c>
+      <c r="C120" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>97</v>
+      </c>
+      <c r="B121" t="s">
+        <v>302</v>
+      </c>
+      <c r="C121" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>98</v>
+      </c>
+      <c r="B122" t="s">
+        <v>303</v>
+      </c>
+      <c r="C122" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>99</v>
+      </c>
+      <c r="B123" t="s">
+        <v>304</v>
+      </c>
+      <c r="C123" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>100</v>
+      </c>
+      <c r="B124" t="s">
+        <v>305</v>
+      </c>
+      <c r="C124" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>101</v>
+      </c>
+      <c r="B125" t="s">
+        <v>306</v>
+      </c>
+      <c r="C125" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>102</v>
+      </c>
+      <c r="B126" t="s">
+        <v>307</v>
+      </c>
+      <c r="C126" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>103</v>
+      </c>
+      <c r="B127" t="s">
+        <v>308</v>
+      </c>
+      <c r="C127" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>104</v>
+      </c>
+      <c r="B128" t="s">
+        <v>309</v>
+      </c>
+      <c r="C128" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>105</v>
+      </c>
+      <c r="B129" t="s">
+        <v>310</v>
+      </c>
+      <c r="C129" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>106</v>
+      </c>
+      <c r="B130" t="s">
+        <v>311</v>
+      </c>
+      <c r="C130" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
         <v>107</v>
       </c>
-      <c r="C106" t="s">
+      <c r="B131" t="s">
+        <v>312</v>
+      </c>
+      <c r="C131" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>107</v>
+      </c>
+      <c r="B132" t="s">
+        <v>313</v>
+      </c>
+      <c r="C132" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>108</v>
+      </c>
+      <c r="B133" t="s">
+        <v>314</v>
+      </c>
+      <c r="C133" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>109</v>
+      </c>
+      <c r="B134" t="s">
+        <v>315</v>
+      </c>
+      <c r="C134" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>110</v>
+      </c>
+      <c r="B135" t="s">
+        <v>316</v>
+      </c>
+      <c r="C135" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>110</v>
+      </c>
+      <c r="B136" t="s">
+        <v>317</v>
+      </c>
+      <c r="C136" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>111</v>
+      </c>
+      <c r="B137" t="s">
+        <v>318</v>
+      </c>
+      <c r="C137" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>112</v>
+      </c>
+      <c r="B138" t="s">
+        <v>319</v>
+      </c>
+      <c r="C138" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>113</v>
+      </c>
+      <c r="B139" t="s">
+        <v>320</v>
+      </c>
+      <c r="C139" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>114</v>
+      </c>
+      <c r="B140" t="s">
+        <v>321</v>
+      </c>
+      <c r="C140" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>115</v>
+      </c>
+      <c r="B141" t="s">
+        <v>322</v>
+      </c>
+      <c r="C141" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>116</v>
+      </c>
+      <c r="B142" t="s">
+        <v>323</v>
+      </c>
+      <c r="C142" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>117</v>
+      </c>
+      <c r="B143" t="s">
+        <v>324</v>
+      </c>
+      <c r="C143" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>118</v>
+      </c>
+      <c r="B144" t="s">
+        <v>325</v>
+      </c>
+      <c r="C144" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>118</v>
+      </c>
+      <c r="B145" t="s">
+        <v>326</v>
+      </c>
+      <c r="C145" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>119</v>
+      </c>
+      <c r="B146" t="s">
+        <v>327</v>
+      </c>
+      <c r="C146" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>119</v>
+      </c>
+      <c r="B147" t="s">
+        <v>328</v>
+      </c>
+      <c r="C147" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>119</v>
+      </c>
+      <c r="B148" t="s">
+        <v>329</v>
+      </c>
+      <c r="C148" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>120</v>
+      </c>
+      <c r="B149" t="s">
+        <v>330</v>
+      </c>
+      <c r="C149" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>120</v>
+      </c>
+      <c r="B150" t="s">
+        <v>331</v>
+      </c>
+      <c r="C150" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>121</v>
+      </c>
+      <c r="B151" t="s">
+        <v>332</v>
+      </c>
+      <c r="C151" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>122</v>
+      </c>
+      <c r="B152" t="s">
+        <v>333</v>
+      </c>
+      <c r="C152" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>123</v>
+      </c>
+      <c r="B153" t="s">
+        <v>334</v>
+      </c>
+      <c r="C153" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>124</v>
+      </c>
+      <c r="B154" t="s">
+        <v>335</v>
+      </c>
+      <c r="C154" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>125</v>
+      </c>
+      <c r="B155" t="s">
+        <v>336</v>
+      </c>
+      <c r="C155" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>179</v>
+      </c>
+      <c r="B156" t="s">
+        <v>337</v>
+      </c>
+      <c r="C156" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>180</v>
+      </c>
+      <c r="B157" t="s">
+        <v>338</v>
+      </c>
+      <c r="C157" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>181</v>
+      </c>
+      <c r="B158" t="s">
+        <v>339</v>
+      </c>
+      <c r="C158" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>182</v>
+      </c>
+      <c r="B159" t="s">
+        <v>340</v>
+      </c>
+      <c r="C159" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>183</v>
+      </c>
+      <c r="B160" t="s">
+        <v>341</v>
+      </c>
+      <c r="C160" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>184</v>
+      </c>
+      <c r="B161" t="s">
+        <v>342</v>
+      </c>
+      <c r="C161" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C107" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C108" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C109" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C110" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C111" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C112" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C113" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C114" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C115" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C116" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C117" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C118" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C119" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C120" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C121" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C122" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C123" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C124" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" s="2" t="s">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>185</v>
+      </c>
+      <c r="B162" t="s">
+        <v>343</v>
+      </c>
+      <c r="C162" t="s">
         <v>126</v>
       </c>
-      <c r="C125" t="s">
-        <v>127</v>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>186</v>
+      </c>
+      <c r="B163" t="s">
+        <v>344</v>
+      </c>
+      <c r="C163" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>187</v>
+      </c>
+      <c r="B164" t="s">
+        <v>345</v>
+      </c>
+      <c r="C164" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>188</v>
+      </c>
+      <c r="B165" t="s">
+        <v>346</v>
+      </c>
+      <c r="C165" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>188</v>
+      </c>
+      <c r="B166" t="s">
+        <v>347</v>
+      </c>
+      <c r="C166" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>189</v>
+      </c>
+      <c r="B167" t="s">
+        <v>348</v>
+      </c>
+      <c r="C167" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>190</v>
+      </c>
+      <c r="B168" t="s">
+        <v>349</v>
+      </c>
+      <c r="C168" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>191</v>
+      </c>
+      <c r="B169" t="s">
+        <v>350</v>
+      </c>
+      <c r="C169" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>192</v>
+      </c>
+      <c r="B170" t="s">
+        <v>351</v>
+      </c>
+      <c r="C170" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>193</v>
+      </c>
+      <c r="B171" t="s">
+        <v>352</v>
+      </c>
+      <c r="C171" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>194</v>
+      </c>
+      <c r="B172" t="s">
+        <v>353</v>
+      </c>
+      <c r="C172" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>195</v>
+      </c>
+      <c r="B173" t="s">
+        <v>354</v>
+      </c>
+      <c r="C173" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>196</v>
+      </c>
+      <c r="B174" t="s">
+        <v>355</v>
+      </c>
+      <c r="C174" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>197</v>
+      </c>
+      <c r="B175" t="s">
+        <v>356</v>
+      </c>
+      <c r="C175" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>198</v>
+      </c>
+      <c r="B176" t="s">
+        <v>357</v>
+      </c>
+      <c r="C176" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>199</v>
+      </c>
+      <c r="B177" t="s">
+        <v>358</v>
+      </c>
+      <c r="C177" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>200</v>
+      </c>
+      <c r="B178" t="s">
+        <v>359</v>
+      </c>
+      <c r="C178" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>201</v>
+      </c>
+      <c r="B179" t="s">
+        <v>360</v>
+      </c>
+      <c r="C179" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>201</v>
+      </c>
+      <c r="B180" t="s">
+        <v>361</v>
+      </c>
+      <c r="C180" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>202</v>
+      </c>
+      <c r="B181" t="s">
+        <v>362</v>
+      </c>
+      <c r="C181" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>203</v>
+      </c>
+      <c r="B182" t="s">
+        <v>363</v>
+      </c>
+      <c r="C182" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>204</v>
+      </c>
+      <c r="B183" t="s">
+        <v>364</v>
+      </c>
+      <c r="C183" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>204</v>
+      </c>
+      <c r="B184" t="s">
+        <v>365</v>
+      </c>
+      <c r="C184" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>204</v>
+      </c>
+      <c r="B185" t="s">
+        <v>366</v>
+      </c>
+      <c r="C185" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>205</v>
+      </c>
+      <c r="B186" t="s">
+        <v>367</v>
+      </c>
+      <c r="C186" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>205</v>
+      </c>
+      <c r="B187" t="s">
+        <v>368</v>
+      </c>
+      <c r="C187" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>205</v>
+      </c>
+      <c r="B188" t="s">
+        <v>369</v>
+      </c>
+      <c r="C188" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>206</v>
+      </c>
+      <c r="B189" t="s">
+        <v>370</v>
+      </c>
+      <c r="C189" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>206</v>
+      </c>
+      <c r="B190" t="s">
+        <v>371</v>
+      </c>
+      <c r="C190" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>207</v>
+      </c>
+      <c r="B191" t="s">
+        <v>372</v>
+      </c>
+      <c r="C191" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>208</v>
+      </c>
+      <c r="B192" t="s">
+        <v>373</v>
+      </c>
+      <c r="C192" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>208</v>
+      </c>
+      <c r="B193" t="s">
+        <v>374</v>
+      </c>
+      <c r="C193" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>209</v>
+      </c>
+      <c r="B194" t="s">
+        <v>375</v>
+      </c>
+      <c r="C194" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D354F4F3-48A9-4E99-BC49-77B07BED5596}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D43F36-E0C7-4D9C-87C1-FF2D9EE100B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="285">
   <si>
     <t>UTK</t>
   </si>
@@ -297,7 +297,592 @@
     <t>311246117</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>SZ-850</t>
+  </si>
+  <si>
+    <t>SZ-870</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>SZ-854</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-807</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-810</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-802</t>
+  </si>
+  <si>
+    <t>267006592</t>
+  </si>
+  <si>
+    <t>NFD6-04-30-6LDK</t>
+  </si>
+  <si>
+    <t>NFD6-04-30-FQSC/CS</t>
+  </si>
+  <si>
+    <t>NFD6-05-02-FMGP/CSXD</t>
+  </si>
+  <si>
+    <t>NFD6-05-04-RAPA</t>
+  </si>
+  <si>
+    <t>NFD6-05-06-35QK</t>
+  </si>
+  <si>
+    <t>NFD6-05-06-EZSM</t>
+  </si>
+  <si>
+    <t>NFD6-05-06-P65C</t>
+  </si>
+  <si>
+    <t>NFD6-05-06-ST9R</t>
+  </si>
+  <si>
+    <t>NFD6-05-06-VXWC</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-562L</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-5D4J</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-5FVQ</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-94PU</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-CNDU</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-LALH</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-NHDT</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-PMNX</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-T8JE</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-TCRK</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-WK7X</t>
+  </si>
+  <si>
+    <t>NFE6-05-04-YW4V</t>
+  </si>
+  <si>
+    <t>NFE6-05-06-9JPZ</t>
+  </si>
+  <si>
+    <t>NFE6-05-07-CP66</t>
+  </si>
+  <si>
+    <t>NFE6-05-07-G4QV</t>
+  </si>
+  <si>
+    <t>NFE6-05-07-PY6T</t>
+  </si>
+  <si>
+    <t>SA26/H002557</t>
+  </si>
+  <si>
+    <t>SA26/H002598</t>
+  </si>
+  <si>
+    <t>SA26/H002599</t>
+  </si>
+  <si>
+    <t>SZ 2026 142427</t>
+  </si>
+  <si>
+    <t>69fb2e3147d1aed7c38652f5</t>
+  </si>
+  <si>
+    <t>69fc4a688046ce4dbfb8eaab</t>
+  </si>
+  <si>
+    <t>69fb465947d1aed7c3865739</t>
+  </si>
+  <si>
+    <t>69f9e29247d1aed7c3863b0a</t>
+  </si>
+  <si>
+    <t>69fc4fd38046ce4dbfb8eb83</t>
+  </si>
+  <si>
+    <t>69f4edb647d1aed7c385fe89</t>
+  </si>
+  <si>
+    <t>69fb3a8247d1aed7c3865551</t>
+  </si>
+  <si>
+    <t>69fc93618046ce4dbfb8f6a5</t>
+  </si>
+  <si>
+    <t>69fd8cd68046ce4dbfb900fe</t>
+  </si>
+  <si>
+    <t>69f8754847d1aed7c3861c26</t>
+  </si>
+  <si>
+    <t>69f8754847d1aed7c3861c28</t>
+  </si>
+  <si>
+    <t>69fb6be347d1aed7c3865be6</t>
+  </si>
+  <si>
+    <t>69f8a67a47d1aed7c3862476</t>
+  </si>
+  <si>
+    <t>69fda0728046ce4dbfb9052a</t>
+  </si>
+  <si>
+    <t>69fa699f47d1aed7c3864697</t>
+  </si>
+  <si>
+    <t>69fc80aa8046ce4dbfb8f3ad</t>
+  </si>
+  <si>
+    <t>69fb73a147d1aed7c3865c50</t>
+  </si>
+  <si>
+    <t>69fafafa47d1aed7c3864b1f</t>
+  </si>
+  <si>
+    <t>69fafafa47d1aed7c3864b22</t>
+  </si>
+  <si>
+    <t>69fb320b47d1aed7c38653e6</t>
+  </si>
+  <si>
+    <t>69fb5fb347d1aed7c3865ae8</t>
+  </si>
+  <si>
+    <t>69fb6c9d47d1aed7c3865bfc</t>
+  </si>
+  <si>
+    <t>69fc375d8046ce4dbfb8e817</t>
+  </si>
+  <si>
+    <t>69fc3fa28046ce4dbfb8e8f3</t>
+  </si>
+  <si>
+    <t>69fc98988046ce4dbfb8f77d</t>
+  </si>
+  <si>
+    <t>69fca0df8046ce4dbfb8f8e1</t>
+  </si>
+  <si>
+    <t>69fce4c58046ce4dbfb8fed4</t>
+  </si>
+  <si>
+    <t>69fc15a58046ce4dbfb8e714</t>
+  </si>
+  <si>
+    <t>69fc55dc8046ce4dbfb8ec7c</t>
+  </si>
+  <si>
+    <t>69fc7c828046ce4dbfb8f325</t>
+  </si>
+  <si>
+    <t>69fc7a308046ce4dbfb8f2c9</t>
+  </si>
+  <si>
+    <t>69fc84ba8046ce4dbfb8f447</t>
+  </si>
+  <si>
+    <t>69fca2018046ce4dbfb8f8fa</t>
+  </si>
+  <si>
+    <t>69fca2018046ce4dbfb8f8fb</t>
+  </si>
+  <si>
+    <t>69fcb4be8046ce4dbfb8fb70</t>
+  </si>
+  <si>
+    <t>69fcd6b78046ce4dbfb8fe30</t>
+  </si>
+  <si>
+    <t>69fcd6b78046ce4dbfb8fe31</t>
+  </si>
+  <si>
+    <t>69fce5f68046ce4dbfb8fee1</t>
+  </si>
+  <si>
+    <t>69fce5f68046ce4dbfb8fee3</t>
+  </si>
+  <si>
+    <t>69fdac048046ce4dbfb90743</t>
+  </si>
+  <si>
+    <t>69fdc0a88046ce4dbfb90a83</t>
+  </si>
+  <si>
+    <t>FIZZ-1000900867</t>
+  </si>
+  <si>
+    <t>305411701/1</t>
+  </si>
+  <si>
+    <t>308936983/1</t>
+  </si>
+  <si>
+    <t>308936983/2</t>
+  </si>
+  <si>
+    <t>308936983/3</t>
+  </si>
+  <si>
+    <t>309514662/1</t>
+  </si>
+  <si>
+    <t>309514662/2</t>
+  </si>
+  <si>
+    <t>309514662/3</t>
+  </si>
+  <si>
+    <t>309514924/1</t>
+  </si>
+  <si>
+    <t>309514924/2</t>
+  </si>
+  <si>
+    <t>310000877/1</t>
+  </si>
+  <si>
+    <t>310000877/2</t>
+  </si>
+  <si>
+    <t>310354298/1</t>
+  </si>
+  <si>
+    <t>310468638/1</t>
+  </si>
+  <si>
+    <t>310520618/1</t>
+  </si>
+  <si>
+    <t>310520664/1</t>
+  </si>
+  <si>
+    <t>310620478/1</t>
+  </si>
+  <si>
+    <t>310673324/1</t>
+  </si>
+  <si>
+    <t>310673535/1</t>
+  </si>
+  <si>
+    <t>310673648/1</t>
+  </si>
+  <si>
+    <t>310673844/1</t>
+  </si>
+  <si>
+    <t>310673844/2</t>
+  </si>
+  <si>
+    <t>310673850/1</t>
+  </si>
+  <si>
+    <t>310673943/1</t>
+  </si>
+  <si>
+    <t>310715476/1</t>
+  </si>
+  <si>
+    <t>310715476/2</t>
+  </si>
+  <si>
+    <t>310716225/1</t>
+  </si>
+  <si>
+    <t>310716265/1</t>
+  </si>
+  <si>
+    <t>310716288/1</t>
+  </si>
+  <si>
+    <t>310776424/1</t>
+  </si>
+  <si>
+    <t>310776678/1</t>
+  </si>
+  <si>
+    <t>310776859/1</t>
+  </si>
+  <si>
+    <t>310776868/1</t>
+  </si>
+  <si>
+    <t>310776868/2</t>
+  </si>
+  <si>
+    <t>310776868/3</t>
+  </si>
+  <si>
+    <t>310850025/1</t>
+  </si>
+  <si>
+    <t>310850159/1</t>
+  </si>
+  <si>
+    <t>310850226/1</t>
+  </si>
+  <si>
+    <t>310850226/2</t>
+  </si>
+  <si>
+    <t>310850322/1</t>
+  </si>
+  <si>
+    <t>310850322/2</t>
+  </si>
+  <si>
+    <t>310850609/1</t>
+  </si>
+  <si>
+    <t>310850637/1</t>
+  </si>
+  <si>
+    <t>310850637/2</t>
+  </si>
+  <si>
+    <t>310850805/1</t>
+  </si>
+  <si>
+    <t>310904183/1</t>
+  </si>
+  <si>
+    <t>310904637/1</t>
+  </si>
+  <si>
+    <t>310904738/1</t>
+  </si>
+  <si>
+    <t>310904784/1</t>
+  </si>
+  <si>
+    <t>310904890/1</t>
+  </si>
+  <si>
+    <t>310905077/1</t>
+  </si>
+  <si>
+    <t>310968800/1</t>
+  </si>
+  <si>
+    <t>310968892/1</t>
+  </si>
+  <si>
+    <t>310969449/1</t>
+  </si>
+  <si>
+    <t>311102919/1</t>
+  </si>
+  <si>
+    <t>311103043/1</t>
+  </si>
+  <si>
+    <t>311103250/1</t>
+  </si>
+  <si>
+    <t>311103259/1</t>
+  </si>
+  <si>
+    <t>311103464/1</t>
+  </si>
+  <si>
+    <t>311177585/1</t>
+  </si>
+  <si>
+    <t>311245483/1</t>
+  </si>
+  <si>
+    <t>311245948/1</t>
+  </si>
+  <si>
+    <t>311246040/1</t>
+  </si>
+  <si>
+    <t>311246117/1</t>
+  </si>
+  <si>
+    <t>202605082600984901</t>
+  </si>
+  <si>
+    <t>159995579539980748</t>
+  </si>
+  <si>
+    <t>159995579539992017</t>
+  </si>
+  <si>
+    <t>202605082601001501</t>
+  </si>
+  <si>
+    <t>202605072601015901</t>
+  </si>
+  <si>
+    <t>202605072601011301</t>
+  </si>
+  <si>
+    <t>202605072601016501</t>
+  </si>
+  <si>
+    <t>202605072601014601</t>
+  </si>
+  <si>
+    <t>202605072601012001</t>
+  </si>
+  <si>
+    <t>202605082601019901</t>
+  </si>
+  <si>
+    <t>202605082601019801</t>
+  </si>
+  <si>
+    <t>202605082601021701</t>
+  </si>
+  <si>
+    <t>202605082601018901</t>
+  </si>
+  <si>
+    <t>202605082601021001</t>
+  </si>
+  <si>
+    <t>202605082601021801</t>
+  </si>
+  <si>
+    <t>202605082601024601</t>
+  </si>
+  <si>
+    <t>202605082601024602</t>
+  </si>
+  <si>
+    <t>202605082601021101</t>
+  </si>
+  <si>
+    <t>202605082601023101</t>
+  </si>
+  <si>
+    <t>202605082601022401</t>
+  </si>
+  <si>
+    <t>202605082601021501</t>
+  </si>
+  <si>
+    <t>202605082601001201</t>
+  </si>
+  <si>
+    <t>202605082601001202</t>
+  </si>
+  <si>
+    <t>202605082601001203</t>
+  </si>
+  <si>
+    <t>202605072601014301</t>
+  </si>
+  <si>
+    <t>202605072601014302</t>
+  </si>
+  <si>
+    <t>202605072601014303</t>
+  </si>
+  <si>
+    <t>202605082601020401</t>
+  </si>
+  <si>
+    <t>202605082601020402</t>
+  </si>
+  <si>
+    <t>202605082601025201</t>
+  </si>
+  <si>
+    <t>202605082601023201</t>
+  </si>
+  <si>
+    <t>159995579539927842</t>
+  </si>
+  <si>
+    <t>159995579539927859</t>
+  </si>
+  <si>
+    <t>159995579539980700</t>
+  </si>
+  <si>
+    <t>159995579539980717</t>
+  </si>
+  <si>
+    <t>159995579539980724</t>
+  </si>
+  <si>
+    <t>159995579539980809</t>
+  </si>
+  <si>
+    <t>SZ2026142427/1</t>
+  </si>
+  <si>
+    <t>SZ2026142427/2</t>
   </si>
 </sst>
 </file>
@@ -333,10 +918,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -618,12 +1202,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D146"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
@@ -639,691 +1223,1598 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>141</v>
       </c>
       <c r="C2" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
+      <c r="B3" t="s">
+        <v>142</v>
+      </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>143</v>
       </c>
       <c r="C4" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>144</v>
       </c>
       <c r="C5" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
+      <c r="B6" t="s">
+        <v>145</v>
+      </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
+      <c r="B7" t="s">
+        <v>146</v>
+      </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
+      <c r="B8" t="s">
+        <v>147</v>
+      </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>14</v>
       </c>
+      <c r="B9" t="s">
+        <v>148</v>
+      </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
         <v>15</v>
       </c>
+      <c r="B10" t="s">
+        <v>149</v>
+      </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" t="s">
         <v>16</v>
       </c>
+      <c r="B11" t="s">
+        <v>150</v>
+      </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>17</v>
       </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>18</v>
       </c>
-      <c r="C13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>19</v>
       </c>
-      <c r="C14" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="B15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>20</v>
       </c>
-      <c r="C15" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="B16" t="s">
+        <v>155</v>
+      </c>
+      <c r="C16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>21</v>
       </c>
-      <c r="C16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="B17" t="s">
+        <v>156</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>22</v>
       </c>
-      <c r="C17" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="B18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>23</v>
       </c>
-      <c r="C18" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="B19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>24</v>
       </c>
-      <c r="C19" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="B21" t="s">
+        <v>160</v>
+      </c>
+      <c r="C21" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>3</v>
       </c>
-      <c r="C20" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="B22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>25</v>
       </c>
-      <c r="C21" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>27</v>
+      <c r="B23" t="s">
+        <v>162</v>
       </c>
       <c r="C23" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>163</v>
+      </c>
+      <c r="C24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>28</v>
       </c>
-      <c r="C24" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="B26" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>29</v>
       </c>
-      <c r="C25" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="B27" t="s">
+        <v>166</v>
+      </c>
+      <c r="C27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>30</v>
       </c>
-      <c r="C26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="B28" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>31</v>
       </c>
-      <c r="C27" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="B29" t="s">
+        <v>168</v>
+      </c>
+      <c r="C29" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>32</v>
       </c>
-      <c r="C28" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="B30" t="s">
+        <v>169</v>
+      </c>
+      <c r="C30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>33</v>
       </c>
-      <c r="C29" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="B31" t="s">
+        <v>170</v>
+      </c>
+      <c r="C31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>34</v>
       </c>
-      <c r="C30" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="B32" t="s">
+        <v>171</v>
+      </c>
+      <c r="C32" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>35</v>
       </c>
-      <c r="C31" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="B33" t="s">
+        <v>172</v>
+      </c>
+      <c r="C33" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>36</v>
       </c>
-      <c r="C32" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="B34" t="s">
+        <v>173</v>
+      </c>
+      <c r="C34" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s">
+        <v>174</v>
+      </c>
+      <c r="C35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>37</v>
       </c>
-      <c r="C33" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="B36" t="s">
+        <v>175</v>
+      </c>
+      <c r="C36" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>38</v>
       </c>
-      <c r="C34" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="B37" t="s">
+        <v>176</v>
+      </c>
+      <c r="C37" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>177</v>
+      </c>
+      <c r="C38" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>39</v>
       </c>
-      <c r="C35" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+      <c r="B39" t="s">
+        <v>178</v>
+      </c>
+      <c r="C39" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>179</v>
+      </c>
+      <c r="C40" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>40</v>
       </c>
-      <c r="C36" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+      <c r="B41" t="s">
+        <v>180</v>
+      </c>
+      <c r="C41" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>41</v>
       </c>
-      <c r="C37" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="B42" t="s">
+        <v>181</v>
+      </c>
+      <c r="C42" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" t="s">
+        <v>182</v>
+      </c>
+      <c r="C43" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>42</v>
       </c>
-      <c r="C38" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="B44" t="s">
+        <v>183</v>
+      </c>
+      <c r="C44" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>43</v>
       </c>
-      <c r="C39" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="B45" t="s">
+        <v>184</v>
+      </c>
+      <c r="C45" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" t="s">
+        <v>185</v>
+      </c>
+      <c r="C46" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>43</v>
+      </c>
+      <c r="B47" t="s">
+        <v>186</v>
+      </c>
+      <c r="C47" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>44</v>
       </c>
-      <c r="C40" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="B48" t="s">
+        <v>187</v>
+      </c>
+      <c r="C48" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" t="s">
+        <v>188</v>
+      </c>
+      <c r="C49" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" t="s">
+        <v>189</v>
+      </c>
+      <c r="C50" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>45</v>
       </c>
-      <c r="C41" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+      <c r="B51" t="s">
+        <v>190</v>
+      </c>
+      <c r="C51" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" t="s">
+        <v>191</v>
+      </c>
+      <c r="C52" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>46</v>
       </c>
-      <c r="C42" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+      <c r="B53" t="s">
+        <v>192</v>
+      </c>
+      <c r="C53" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>46</v>
+      </c>
+      <c r="B54" t="s">
+        <v>193</v>
+      </c>
+      <c r="C54" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>47</v>
       </c>
-      <c r="C43" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+      <c r="B55" t="s">
+        <v>194</v>
+      </c>
+      <c r="C55" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>48</v>
       </c>
-      <c r="C44" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+      <c r="B56" t="s">
+        <v>195</v>
+      </c>
+      <c r="C56" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>49</v>
       </c>
-      <c r="C45" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+      <c r="B57" t="s">
+        <v>196</v>
+      </c>
+      <c r="C57" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>50</v>
       </c>
-      <c r="C46" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+      <c r="B58" t="s">
+        <v>197</v>
+      </c>
+      <c r="C58" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>51</v>
       </c>
-      <c r="C47" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+      <c r="B59" t="s">
+        <v>198</v>
+      </c>
+      <c r="C59" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>52</v>
       </c>
-      <c r="C48" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+      <c r="B60" t="s">
+        <v>199</v>
+      </c>
+      <c r="C60" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>53</v>
       </c>
-      <c r="C49" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+      <c r="B61" t="s">
+        <v>200</v>
+      </c>
+      <c r="C61" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>54</v>
       </c>
-      <c r="C50" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
+      <c r="B62" t="s">
+        <v>201</v>
+      </c>
+      <c r="C62" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>55</v>
       </c>
-      <c r="C51" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+      <c r="B63" t="s">
+        <v>202</v>
+      </c>
+      <c r="C63" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>55</v>
+      </c>
+      <c r="B64" t="s">
+        <v>203</v>
+      </c>
+      <c r="C64" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>4</v>
       </c>
-      <c r="C52" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
+      <c r="B65" t="s">
+        <v>204</v>
+      </c>
+      <c r="C65" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>5</v>
       </c>
-      <c r="C53" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
+      <c r="B66" t="s">
+        <v>205</v>
+      </c>
+      <c r="C66" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>56</v>
       </c>
-      <c r="C54" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
+      <c r="B67" t="s">
+        <v>206</v>
+      </c>
+      <c r="C67" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>56</v>
+      </c>
+      <c r="B68" t="s">
+        <v>207</v>
+      </c>
+      <c r="C68" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>57</v>
       </c>
-      <c r="C55" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
+      <c r="B69" t="s">
+        <v>208</v>
+      </c>
+      <c r="C69" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>58</v>
       </c>
-      <c r="C56" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
+      <c r="B70" t="s">
+        <v>209</v>
+      </c>
+      <c r="C70" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>59</v>
       </c>
-      <c r="C57" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
+      <c r="B71" t="s">
+        <v>210</v>
+      </c>
+      <c r="C71" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>60</v>
       </c>
-      <c r="C58" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
+      <c r="B72" t="s">
+        <v>211</v>
+      </c>
+      <c r="C72" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>61</v>
       </c>
-      <c r="C59" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+      <c r="B73" t="s">
+        <v>212</v>
+      </c>
+      <c r="C73" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>62</v>
       </c>
-      <c r="C60" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
+      <c r="B74" t="s">
+        <v>213</v>
+      </c>
+      <c r="C74" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>63</v>
       </c>
-      <c r="C61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
+      <c r="B75" t="s">
+        <v>214</v>
+      </c>
+      <c r="C75" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>63</v>
+      </c>
+      <c r="B76" t="s">
+        <v>215</v>
+      </c>
+      <c r="C76" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" t="s">
+        <v>216</v>
+      </c>
+      <c r="C77" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>6</v>
       </c>
-      <c r="C62" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
+      <c r="B78" t="s">
+        <v>217</v>
+      </c>
+      <c r="C78" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>64</v>
       </c>
-      <c r="C63" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
+      <c r="B79" t="s">
+        <v>218</v>
+      </c>
+      <c r="C79" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>65</v>
       </c>
-      <c r="C64" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
+      <c r="B80" t="s">
+        <v>219</v>
+      </c>
+      <c r="C80" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>65</v>
+      </c>
+      <c r="B81" t="s">
+        <v>220</v>
+      </c>
+      <c r="C81" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>66</v>
       </c>
-      <c r="C65" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
+      <c r="B82" t="s">
+        <v>221</v>
+      </c>
+      <c r="C82" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>66</v>
+      </c>
+      <c r="B83" t="s">
+        <v>222</v>
+      </c>
+      <c r="C83" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>67</v>
       </c>
-      <c r="C66" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
+      <c r="B84" t="s">
+        <v>223</v>
+      </c>
+      <c r="C84" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>68</v>
       </c>
-      <c r="C67" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C68" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C69" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C70" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C71" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C72" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C73" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C74" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C75" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C76" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C77" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C78" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C79" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C80" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C81" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C82" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C83" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C84" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>86</v>
+      <c r="B85" t="s">
+        <v>224</v>
       </c>
       <c r="C85" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>87</v>
+      <c r="A86" t="s">
+        <v>68</v>
+      </c>
+      <c r="B86" t="s">
+        <v>225</v>
       </c>
       <c r="C86" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
+      <c r="A87" t="s">
+        <v>69</v>
+      </c>
+      <c r="B87" t="s">
+        <v>226</v>
+      </c>
+      <c r="C87" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>70</v>
+      </c>
+      <c r="B88" t="s">
+        <v>227</v>
+      </c>
+      <c r="C88" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>71</v>
+      </c>
+      <c r="B89" t="s">
+        <v>228</v>
+      </c>
+      <c r="C89" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>72</v>
+      </c>
+      <c r="B90" t="s">
+        <v>229</v>
+      </c>
+      <c r="C90" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>73</v>
+      </c>
+      <c r="B91" t="s">
+        <v>230</v>
+      </c>
+      <c r="C91" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>74</v>
+      </c>
+      <c r="B92" t="s">
+        <v>231</v>
+      </c>
+      <c r="C92" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>75</v>
+      </c>
+      <c r="B93" t="s">
+        <v>232</v>
+      </c>
+      <c r="C93" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>76</v>
+      </c>
+      <c r="B94" t="s">
+        <v>233</v>
+      </c>
+      <c r="C94" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>77</v>
+      </c>
+      <c r="B95" t="s">
+        <v>234</v>
+      </c>
+      <c r="C95" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>78</v>
+      </c>
+      <c r="B96" t="s">
+        <v>235</v>
+      </c>
+      <c r="C96" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>79</v>
+      </c>
+      <c r="B97" t="s">
+        <v>236</v>
+      </c>
+      <c r="C97" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>80</v>
+      </c>
+      <c r="B98" t="s">
+        <v>237</v>
+      </c>
+      <c r="C98" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>81</v>
+      </c>
+      <c r="B99" t="s">
+        <v>238</v>
+      </c>
+      <c r="C99" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>82</v>
+      </c>
+      <c r="B100" t="s">
+        <v>239</v>
+      </c>
+      <c r="C100" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>83</v>
+      </c>
+      <c r="B101" t="s">
+        <v>240</v>
+      </c>
+      <c r="C101" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>84</v>
+      </c>
+      <c r="B102" t="s">
+        <v>241</v>
+      </c>
+      <c r="C102" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>85</v>
+      </c>
+      <c r="B103" t="s">
+        <v>242</v>
+      </c>
+      <c r="C103" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>86</v>
+      </c>
+      <c r="B104" t="s">
+        <v>243</v>
+      </c>
+      <c r="C104" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>87</v>
+      </c>
+      <c r="B105" t="s">
+        <v>244</v>
+      </c>
+      <c r="C105" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
         <v>88</v>
       </c>
-      <c r="C87" t="s">
+      <c r="B106" t="s">
+        <v>245</v>
+      </c>
+      <c r="C106" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>112</v>
+      </c>
+      <c r="B107" t="s">
+        <v>246</v>
+      </c>
+      <c r="C107" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>113</v>
+      </c>
+      <c r="B108" t="s">
+        <v>247</v>
+      </c>
+      <c r="C108" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>114</v>
+      </c>
+      <c r="B109" t="s">
+        <v>248</v>
+      </c>
+      <c r="C109" t="s">
         <v>89</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>115</v>
+      </c>
+      <c r="B110" t="s">
+        <v>249</v>
+      </c>
+      <c r="C110" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>116</v>
+      </c>
+      <c r="B111" t="s">
+        <v>250</v>
+      </c>
+      <c r="C111" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>117</v>
+      </c>
+      <c r="B112" t="s">
+        <v>251</v>
+      </c>
+      <c r="C112" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>118</v>
+      </c>
+      <c r="B113" t="s">
+        <v>252</v>
+      </c>
+      <c r="C113" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>119</v>
+      </c>
+      <c r="B114" t="s">
+        <v>253</v>
+      </c>
+      <c r="C114" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>120</v>
+      </c>
+      <c r="B115" t="s">
+        <v>254</v>
+      </c>
+      <c r="C115" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>121</v>
+      </c>
+      <c r="B116" t="s">
+        <v>255</v>
+      </c>
+      <c r="C116" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>122</v>
+      </c>
+      <c r="B117" t="s">
+        <v>256</v>
+      </c>
+      <c r="C117" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>123</v>
+      </c>
+      <c r="B118" t="s">
+        <v>257</v>
+      </c>
+      <c r="C118" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>124</v>
+      </c>
+      <c r="B119" t="s">
+        <v>258</v>
+      </c>
+      <c r="C119" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>125</v>
+      </c>
+      <c r="B120" t="s">
+        <v>259</v>
+      </c>
+      <c r="C120" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>126</v>
+      </c>
+      <c r="B121" t="s">
+        <v>260</v>
+      </c>
+      <c r="C121" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>127</v>
+      </c>
+      <c r="B122" t="s">
+        <v>261</v>
+      </c>
+      <c r="C122" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>127</v>
+      </c>
+      <c r="B123" t="s">
+        <v>262</v>
+      </c>
+      <c r="C123" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>128</v>
+      </c>
+      <c r="B124" t="s">
+        <v>263</v>
+      </c>
+      <c r="C124" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>129</v>
+      </c>
+      <c r="B125" t="s">
+        <v>264</v>
+      </c>
+      <c r="C125" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>130</v>
+      </c>
+      <c r="B126" t="s">
+        <v>265</v>
+      </c>
+      <c r="C126" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>131</v>
+      </c>
+      <c r="B127" t="s">
+        <v>266</v>
+      </c>
+      <c r="C127" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>132</v>
+      </c>
+      <c r="B128" t="s">
+        <v>267</v>
+      </c>
+      <c r="C128" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>132</v>
+      </c>
+      <c r="B129" t="s">
+        <v>268</v>
+      </c>
+      <c r="C129" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>132</v>
+      </c>
+      <c r="B130" t="s">
+        <v>269</v>
+      </c>
+      <c r="C130" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>133</v>
+      </c>
+      <c r="B131" t="s">
+        <v>270</v>
+      </c>
+      <c r="C131" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>133</v>
+      </c>
+      <c r="B132" t="s">
+        <v>271</v>
+      </c>
+      <c r="C132" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>133</v>
+      </c>
+      <c r="B133" t="s">
+        <v>272</v>
+      </c>
+      <c r="C133" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>134</v>
+      </c>
+      <c r="B134" t="s">
+        <v>273</v>
+      </c>
+      <c r="C134" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>274</v>
+      </c>
+      <c r="C135" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>275</v>
+      </c>
+      <c r="C136" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>276</v>
+      </c>
+      <c r="C137" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>277</v>
+      </c>
+      <c r="C138" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>137</v>
+      </c>
+      <c r="B139" t="s">
+        <v>278</v>
+      </c>
+      <c r="C139" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>138</v>
+      </c>
+      <c r="B140" t="s">
+        <v>279</v>
+      </c>
+      <c r="C140" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>138</v>
+      </c>
+      <c r="B141" t="s">
+        <v>280</v>
+      </c>
+      <c r="C141" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>138</v>
+      </c>
+      <c r="B142" t="s">
+        <v>281</v>
+      </c>
+      <c r="C142" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>139</v>
+      </c>
+      <c r="B143" t="s">
+        <v>282</v>
+      </c>
+      <c r="C143" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>140</v>
+      </c>
+      <c r="B144" t="s">
+        <v>283</v>
+      </c>
+      <c r="C144" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>140</v>
+      </c>
+      <c r="B145" t="s">
+        <v>284</v>
+      </c>
+      <c r="C145" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" s="1">
+        <v>310468298</v>
+      </c>
+      <c r="B146" s="1">
+        <v>310468298</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EF8EBF-3CEB-41AA-B0FA-D86F0E01B24F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C501F1B-BCBF-43E7-AD3A-AD894BBBA1AD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="306">
   <si>
     <t>UTK</t>
   </si>
@@ -126,9 +126,6 @@
     <t>260508-F00012957</t>
   </si>
   <si>
-    <t>260508-F00014034</t>
-  </si>
-  <si>
     <t>260508-W00001873</t>
   </si>
   <si>
@@ -273,7 +270,682 @@
     <t>99002492</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-854</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-870</t>
+  </si>
+  <si>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>SZ-850</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>267006705</t>
+  </si>
+  <si>
+    <t>267006862</t>
+  </si>
+  <si>
+    <t>267006876</t>
+  </si>
+  <si>
+    <t>267006913</t>
+  </si>
+  <si>
+    <t>267006942</t>
+  </si>
+  <si>
+    <t>267006947</t>
+  </si>
+  <si>
+    <t>26MPE0004956</t>
+  </si>
+  <si>
+    <t>NFD6-04-30-8MHX</t>
+  </si>
+  <si>
+    <t>NFD6-05-04-J7MF</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-BETQ</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-EF4S</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-H8HW</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-JFHV</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-JKXT</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-S3SD</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-VA5L</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-W5PA</t>
+  </si>
+  <si>
+    <t>NFD6-05-08-33UB</t>
+  </si>
+  <si>
+    <t>NFD6-05-08-5JLB</t>
+  </si>
+  <si>
+    <t>NFD6-05-08-73HD</t>
+  </si>
+  <si>
+    <t>NFD6-05-08-EKRS</t>
+  </si>
+  <si>
+    <t>NFD6-05-08-LGXG</t>
+  </si>
+  <si>
+    <t>NFD6-05-08-TW67</t>
+  </si>
+  <si>
+    <t>NFD6-05-08-UDGH</t>
+  </si>
+  <si>
+    <t>NFD6-05-08-WEU2</t>
+  </si>
+  <si>
+    <t>NFD6-05-08-WYZU</t>
+  </si>
+  <si>
+    <t>NFD6-05-08-YWW9</t>
+  </si>
+  <si>
+    <t>NFD6-05-09-3AAC</t>
+  </si>
+  <si>
+    <t>NFD6-05-09-6YGP</t>
+  </si>
+  <si>
+    <t>NFD6-05-09-8S8L</t>
+  </si>
+  <si>
+    <t>NFD6-05-09-A9PS</t>
+  </si>
+  <si>
+    <t>NFD6-05-09-E9FT</t>
+  </si>
+  <si>
+    <t>NFD6-05-09-GHM8</t>
+  </si>
+  <si>
+    <t>NFD6-05-09-JN8A</t>
+  </si>
+  <si>
+    <t>NFD6-05-09-MS6J</t>
+  </si>
+  <si>
+    <t>NFD6-05-09-RLTE</t>
+  </si>
+  <si>
+    <t>NFD6-05-09-YWPY</t>
+  </si>
+  <si>
+    <t>NFD6-05-10-5LE5</t>
+  </si>
+  <si>
+    <t>NFD6-05-10-93ZS</t>
+  </si>
+  <si>
+    <t>NFD6-05-10-EH29</t>
+  </si>
+  <si>
+    <t>NFD6-05-10-EQEQ</t>
+  </si>
+  <si>
+    <t>NFD6-05-10-FA2R</t>
+  </si>
+  <si>
+    <t>NFD6-05-10-HAGA</t>
+  </si>
+  <si>
+    <t>NFD6-05-10-MZAA</t>
+  </si>
+  <si>
+    <t>NFD6-05-10-UJ27</t>
+  </si>
+  <si>
+    <t>NFE6-05-08-84P3</t>
+  </si>
+  <si>
+    <t>NFE6-05-10-6GMY</t>
+  </si>
+  <si>
+    <t>NFE6-05-10-DJ6E</t>
+  </si>
+  <si>
+    <t>NFE6-05-10-GEEL</t>
+  </si>
+  <si>
+    <t>R418721</t>
+  </si>
+  <si>
+    <t>SA26/H002489</t>
+  </si>
+  <si>
+    <t>SA26/H002516</t>
+  </si>
+  <si>
+    <t>SA26/H002662</t>
+  </si>
+  <si>
+    <t>SZ 2026 142546</t>
+  </si>
+  <si>
+    <t>SZ 2026 142607</t>
+  </si>
+  <si>
+    <t>VA26/002486/1</t>
+  </si>
+  <si>
+    <t>248745678/1</t>
+  </si>
+  <si>
+    <t>69fdd7fd8046ce4dbfb90e80</t>
+  </si>
+  <si>
+    <t>69fef8e98046ce4dbfb91e3e</t>
+  </si>
+  <si>
+    <t>69f9e29247d1aed7c3863b0a</t>
+  </si>
+  <si>
+    <t>69fd9f508046ce4dbfb904c8</t>
+  </si>
+  <si>
+    <t>69fdd3ed8046ce4dbfb90db0</t>
+  </si>
+  <si>
+    <t>69ff1f1d8046ce4dbfb92230</t>
+  </si>
+  <si>
+    <t>6a01b0e98046ce4dbfb93fd0</t>
+  </si>
+  <si>
+    <t>69fcb4dc8046ce4dbfb8fb77</t>
+  </si>
+  <si>
+    <t>69fe07038046ce4dbfb915ab</t>
+  </si>
+  <si>
+    <t>69fc9a298046ce4dbfb8f7d8</t>
+  </si>
+  <si>
+    <t>69fca24d8046ce4dbfb8f929</t>
+  </si>
+  <si>
+    <t>69fa280647d1aed7c386444a</t>
+  </si>
+  <si>
+    <t>69f9ff0147d1aed7c3863fc0</t>
+  </si>
+  <si>
+    <t>69fdf7868046ce4dbfb913d2</t>
+  </si>
+  <si>
+    <t>69fd814d8046ce4dbfb9002f</t>
+  </si>
+  <si>
+    <t>69fb878e47d1aed7c3865dd1</t>
+  </si>
+  <si>
+    <t>69fb8fc647d1aed7c3865e1c</t>
+  </si>
+  <si>
+    <t>69fc896a8046ce4dbfb8f4f6</t>
+  </si>
+  <si>
+    <t>69fce84d8046ce4dbfb8ff06</t>
+  </si>
+  <si>
+    <t>69fce84d8046ce4dbfb8ff08</t>
+  </si>
+  <si>
+    <t>69fc794d8046ce4dbfb8f295</t>
+  </si>
+  <si>
+    <t>69fc794d8046ce4dbfb8f296</t>
+  </si>
+  <si>
+    <t>69fc9faa8046ce4dbfb8f891</t>
+  </si>
+  <si>
+    <t>69fcb4be8046ce4dbfb8fb6a</t>
+  </si>
+  <si>
+    <t>69fcd5918046ce4dbfb8fe27</t>
+  </si>
+  <si>
+    <t>69fce9738046ce4dbfb8ff0f</t>
+  </si>
+  <si>
+    <t>69fda87b8046ce4dbfb90680</t>
+  </si>
+  <si>
+    <t>69fda87b8046ce4dbfb90681</t>
+  </si>
+  <si>
+    <t>69fdd06f8046ce4dbfb90d20</t>
+  </si>
+  <si>
+    <t>69fedfc58046ce4dbfb91a94</t>
+  </si>
+  <si>
+    <t>69fdfbd18046ce4dbfb91487</t>
+  </si>
+  <si>
+    <t>69fd8c618046ce4dbfb900f1</t>
+  </si>
+  <si>
+    <t>69fd92398046ce4dbfb901c4</t>
+  </si>
+  <si>
+    <t>69fd9cd48046ce4dbfb90426</t>
+  </si>
+  <si>
+    <t>69fdc3708046ce4dbfb90af9</t>
+  </si>
+  <si>
+    <t>69fdc8338046ce4dbfb90bd2</t>
+  </si>
+  <si>
+    <t>69fe47da8046ce4dbfb91946</t>
+  </si>
+  <si>
+    <t>69fefd838046ce4dbfb91ee1</t>
+  </si>
+  <si>
+    <t>69ff55688046ce4dbfb92608</t>
+  </si>
+  <si>
+    <t>69ff55688046ce4dbfb92609</t>
+  </si>
+  <si>
+    <t>69ff4c098046ce4dbfb92570</t>
+  </si>
+  <si>
+    <t>6a00ae388046ce4dbfb9319d</t>
+  </si>
+  <si>
+    <t>6a00b0438046ce4dbfb931c2</t>
+  </si>
+  <si>
+    <t>6a00b0438046ce4dbfb931c3</t>
+  </si>
+  <si>
+    <t>6a00d9438046ce4dbfb9331c</t>
+  </si>
+  <si>
+    <t>6a017fba8046ce4dbfb93571</t>
+  </si>
+  <si>
+    <t>FIZZ-1000902873</t>
+  </si>
+  <si>
+    <t>FIZZ-1000900138</t>
+  </si>
+  <si>
+    <t>FIZZ-1000902380</t>
+  </si>
+  <si>
+    <t>1449-862210</t>
+  </si>
+  <si>
+    <t>1449-858179</t>
+  </si>
+  <si>
+    <t>1449-687201</t>
+  </si>
+  <si>
+    <t>26MPE0004956/1</t>
+  </si>
+  <si>
+    <t>310143712/1</t>
+  </si>
+  <si>
+    <t>310412094/1</t>
+  </si>
+  <si>
+    <t>310412418/1</t>
+  </si>
+  <si>
+    <t>310412418/2</t>
+  </si>
+  <si>
+    <t>310620464/1</t>
+  </si>
+  <si>
+    <t>310776615/1</t>
+  </si>
+  <si>
+    <t>310849925/1</t>
+  </si>
+  <si>
+    <t>310850013/1</t>
+  </si>
+  <si>
+    <t>310904529/1</t>
+  </si>
+  <si>
+    <t>310904596/1</t>
+  </si>
+  <si>
+    <t>310904635/1</t>
+  </si>
+  <si>
+    <t>310904955/1</t>
+  </si>
+  <si>
+    <t>310969526/1</t>
+  </si>
+  <si>
+    <t>310969693/1</t>
+  </si>
+  <si>
+    <t>310969726/1</t>
+  </si>
+  <si>
+    <t>311037917/1</t>
+  </si>
+  <si>
+    <t>311038283/1</t>
+  </si>
+  <si>
+    <t>311102929/1</t>
+  </si>
+  <si>
+    <t>311103741/1</t>
+  </si>
+  <si>
+    <t>311103888/1</t>
+  </si>
+  <si>
+    <t>311103888/2</t>
+  </si>
+  <si>
+    <t>311103888/3</t>
+  </si>
+  <si>
+    <t>311177151/1</t>
+  </si>
+  <si>
+    <t>311177435/1</t>
+  </si>
+  <si>
+    <t>311177648/1</t>
+  </si>
+  <si>
+    <t>311177665/1</t>
+  </si>
+  <si>
+    <t>311177959/1</t>
+  </si>
+  <si>
+    <t>311245342/1</t>
+  </si>
+  <si>
+    <t>311245348/1</t>
+  </si>
+  <si>
+    <t>311245561/1</t>
+  </si>
+  <si>
+    <t>311245636/1</t>
+  </si>
+  <si>
+    <t>311245667/1</t>
+  </si>
+  <si>
+    <t>311245667/2</t>
+  </si>
+  <si>
+    <t>311245809/1</t>
+  </si>
+  <si>
+    <t>311245833/1</t>
+  </si>
+  <si>
+    <t>311245914/1</t>
+  </si>
+  <si>
+    <t>311245950/1</t>
+  </si>
+  <si>
+    <t>311246183/1</t>
+  </si>
+  <si>
+    <t>99002492/1</t>
+  </si>
+  <si>
+    <t>202605082600982801</t>
+  </si>
+  <si>
+    <t>202605082600982802</t>
+  </si>
+  <si>
+    <t>202605082601001001</t>
+  </si>
+  <si>
+    <t>202605082601021601</t>
+  </si>
+  <si>
+    <t>202605082601024501</t>
+  </si>
+  <si>
+    <t>202605082601019701</t>
+  </si>
+  <si>
+    <t>202605082601022501</t>
+  </si>
+  <si>
+    <t>202605082601024201</t>
+  </si>
+  <si>
+    <t>202605082601022201</t>
+  </si>
+  <si>
+    <t>202605082601022301</t>
+  </si>
+  <si>
+    <t>202605082601019601</t>
+  </si>
+  <si>
+    <t>202605112601030701</t>
+  </si>
+  <si>
+    <t>202605112601030101</t>
+  </si>
+  <si>
+    <t>202605112601027701</t>
+  </si>
+  <si>
+    <t>202605112601031401</t>
+  </si>
+  <si>
+    <t>202605112601029701</t>
+  </si>
+  <si>
+    <t>202605112601029101</t>
+  </si>
+  <si>
+    <t>202605112601029901</t>
+  </si>
+  <si>
+    <t>202605112601029902</t>
+  </si>
+  <si>
+    <t>202605112601029801</t>
+  </si>
+  <si>
+    <t>202605112601030301</t>
+  </si>
+  <si>
+    <t>202605112601027301</t>
+  </si>
+  <si>
+    <t>202605112601035301</t>
+  </si>
+  <si>
+    <t>202605112601036301</t>
+  </si>
+  <si>
+    <t>202605112601035801</t>
+  </si>
+  <si>
+    <t>202605112601035802</t>
+  </si>
+  <si>
+    <t>202605112601035701</t>
+  </si>
+  <si>
+    <t>202605112601037601</t>
+  </si>
+  <si>
+    <t>202605112601037701</t>
+  </si>
+  <si>
+    <t>202605112601034001</t>
+  </si>
+  <si>
+    <t>202605112601034002</t>
+  </si>
+  <si>
+    <t>202605112601039701</t>
+  </si>
+  <si>
+    <t>202605112601034701</t>
+  </si>
+  <si>
+    <t>202605112601038501</t>
+  </si>
+  <si>
+    <t>202605112601042401</t>
+  </si>
+  <si>
+    <t>202605112601047201</t>
+  </si>
+  <si>
+    <t>202605112601045701</t>
+  </si>
+  <si>
+    <t>202605112601045401</t>
+  </si>
+  <si>
+    <t>202605112601047601</t>
+  </si>
+  <si>
+    <t>202605112601045901</t>
+  </si>
+  <si>
+    <t>202605112601044701</t>
+  </si>
+  <si>
+    <t>202605112601044702</t>
+  </si>
+  <si>
+    <t>202605112601042901</t>
+  </si>
+  <si>
+    <t>202605112601026601</t>
+  </si>
+  <si>
+    <t>202605112601046101</t>
+  </si>
+  <si>
+    <t>202605112601049201</t>
+  </si>
+  <si>
+    <t>202605112601048501</t>
+  </si>
+  <si>
+    <t>159995579540014715</t>
+  </si>
+  <si>
+    <t>159995579539873675</t>
+  </si>
+  <si>
+    <t>159995579539873682</t>
+  </si>
+  <si>
+    <t>159995579539892348</t>
+  </si>
+  <si>
+    <t>159995579540036281</t>
+  </si>
+  <si>
+    <t>159995579540036298</t>
+  </si>
+  <si>
+    <t>SZ2026142546</t>
+  </si>
+  <si>
+    <t>SZ2026142607</t>
+  </si>
+  <si>
+    <t>159995579540051116</t>
   </si>
 </sst>
 </file>
@@ -309,10 +981,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -594,10 +1265,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="1"/>
@@ -615,627 +1286,1642 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
+      <c r="B2" t="s">
+        <v>157</v>
+      </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>158</v>
       </c>
       <c r="C3" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
+      <c r="B4" t="s">
+        <v>159</v>
+      </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
+      <c r="B5" t="s">
+        <v>160</v>
+      </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
+      <c r="B6" t="s">
+        <v>161</v>
+      </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
+      <c r="B7" t="s">
+        <v>162</v>
+      </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
+      <c r="B8" t="s">
+        <v>163</v>
+      </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
+      <c r="B9" t="s">
+        <v>164</v>
+      </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
         <v>11</v>
       </c>
+      <c r="B10" t="s">
+        <v>165</v>
+      </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" t="s">
         <v>12</v>
       </c>
+      <c r="B11" t="s">
+        <v>166</v>
+      </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" t="s">
         <v>13</v>
       </c>
+      <c r="B12" t="s">
+        <v>167</v>
+      </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" t="s">
         <v>14</v>
       </c>
+      <c r="B13" t="s">
+        <v>168</v>
+      </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" t="s">
         <v>15</v>
       </c>
+      <c r="B14" t="s">
+        <v>169</v>
+      </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" t="s">
         <v>16</v>
       </c>
+      <c r="B15" t="s">
+        <v>170</v>
+      </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" t="s">
         <v>17</v>
       </c>
+      <c r="B16" t="s">
+        <v>171</v>
+      </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" t="s">
         <v>18</v>
       </c>
+      <c r="B17" t="s">
+        <v>172</v>
+      </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" t="s">
         <v>19</v>
       </c>
+      <c r="B18" t="s">
+        <v>173</v>
+      </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" t="s">
         <v>20</v>
       </c>
+      <c r="B19" t="s">
+        <v>174</v>
+      </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" t="s">
         <v>21</v>
       </c>
+      <c r="B20" t="s">
+        <v>175</v>
+      </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="A21" t="s">
         <v>22</v>
       </c>
+      <c r="B21" t="s">
+        <v>176</v>
+      </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>177</v>
+      </c>
+      <c r="C22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="C22" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="B23" t="s">
+        <v>178</v>
+      </c>
+      <c r="C23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>179</v>
+      </c>
+      <c r="C24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="C23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="B25" t="s">
+        <v>180</v>
+      </c>
+      <c r="C25" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="C24" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="B26" t="s">
+        <v>181</v>
+      </c>
+      <c r="C26" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>26</v>
       </c>
-      <c r="C25" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="B27" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>27</v>
       </c>
-      <c r="C26" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="B28" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>28</v>
       </c>
-      <c r="C27" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="B29" t="s">
+        <v>184</v>
+      </c>
+      <c r="C29" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>185</v>
+      </c>
+      <c r="C30" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>29</v>
       </c>
-      <c r="C28" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="B31" t="s">
+        <v>186</v>
+      </c>
+      <c r="C31" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>30</v>
       </c>
-      <c r="C29" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="B32" t="s">
+        <v>187</v>
+      </c>
+      <c r="C32" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>31</v>
       </c>
-      <c r="C30" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="B33" t="s">
+        <v>188</v>
+      </c>
+      <c r="C33" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>32</v>
       </c>
-      <c r="C31" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="B34" t="s">
+        <v>189</v>
+      </c>
+      <c r="C34" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>33</v>
       </c>
-      <c r="C32" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="B35" t="s">
+        <v>190</v>
+      </c>
+      <c r="C35" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>34</v>
       </c>
-      <c r="C33" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="B36" t="s">
+        <v>191</v>
+      </c>
+      <c r="C36" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>35</v>
       </c>
-      <c r="C34" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="B37" t="s">
+        <v>192</v>
+      </c>
+      <c r="C37" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>36</v>
       </c>
-      <c r="C35" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+      <c r="B38" t="s">
+        <v>193</v>
+      </c>
+      <c r="C38" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>37</v>
       </c>
-      <c r="C36" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+      <c r="B39" t="s">
+        <v>194</v>
+      </c>
+      <c r="C39" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>38</v>
       </c>
-      <c r="C37" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="B40" t="s">
+        <v>195</v>
+      </c>
+      <c r="C40" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>39</v>
       </c>
-      <c r="C38" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="B41" t="s">
+        <v>196</v>
+      </c>
+      <c r="C41" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" t="s">
+        <v>197</v>
+      </c>
+      <c r="C42" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>40</v>
       </c>
-      <c r="C39" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="B43" t="s">
+        <v>198</v>
+      </c>
+      <c r="C43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>41</v>
       </c>
-      <c r="C40" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="B44" t="s">
+        <v>199</v>
+      </c>
+      <c r="C44" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>42</v>
       </c>
-      <c r="C41" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+      <c r="B45" t="s">
+        <v>200</v>
+      </c>
+      <c r="C45" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" t="s">
+        <v>201</v>
+      </c>
+      <c r="C46" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>43</v>
       </c>
-      <c r="C42" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+      <c r="B47" t="s">
+        <v>202</v>
+      </c>
+      <c r="C47" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>44</v>
       </c>
-      <c r="C43" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C44" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C46" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>49</v>
+      <c r="B48" t="s">
+        <v>203</v>
       </c>
       <c r="C48" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>50</v>
+      <c r="A49" t="s">
+        <v>101</v>
+      </c>
+      <c r="B49" t="s">
+        <v>204</v>
       </c>
       <c r="C49" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>51</v>
+      <c r="A50" t="s">
+        <v>102</v>
+      </c>
+      <c r="B50" t="s">
+        <v>205</v>
       </c>
       <c r="C50" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>52</v>
+      <c r="A51" t="s">
+        <v>103</v>
+      </c>
+      <c r="B51" t="s">
+        <v>206</v>
       </c>
       <c r="C51" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>53</v>
+      <c r="A52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B52" t="s">
+        <v>207</v>
       </c>
       <c r="C52" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>54</v>
+      <c r="A53" t="s">
+        <v>105</v>
+      </c>
+      <c r="B53" t="s">
+        <v>208</v>
       </c>
       <c r="C53" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>55</v>
+      <c r="A54" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" t="s">
+        <v>209</v>
       </c>
       <c r="C54" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>56</v>
+      <c r="A55" t="s">
+        <v>107</v>
+      </c>
+      <c r="B55" t="s">
+        <v>210</v>
       </c>
       <c r="C55" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>57</v>
+      <c r="A56" t="s">
+        <v>45</v>
+      </c>
+      <c r="B56" t="s">
+        <v>211</v>
       </c>
       <c r="C56" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>58</v>
+      <c r="A57" t="s">
+        <v>46</v>
+      </c>
+      <c r="B57" t="s">
+        <v>212</v>
       </c>
       <c r="C57" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
+      <c r="A58" t="s">
+        <v>47</v>
+      </c>
+      <c r="B58" t="s">
+        <v>213</v>
+      </c>
+      <c r="C58" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>47</v>
+      </c>
+      <c r="B59" t="s">
+        <v>214</v>
+      </c>
+      <c r="C59" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>48</v>
+      </c>
+      <c r="B60" t="s">
+        <v>215</v>
+      </c>
+      <c r="C60" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>49</v>
+      </c>
+      <c r="B61" t="s">
+        <v>216</v>
+      </c>
+      <c r="C61" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>50</v>
+      </c>
+      <c r="B62" t="s">
+        <v>217</v>
+      </c>
+      <c r="C62" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>51</v>
+      </c>
+      <c r="B63" t="s">
+        <v>218</v>
+      </c>
+      <c r="C63" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>52</v>
+      </c>
+      <c r="B64" t="s">
+        <v>219</v>
+      </c>
+      <c r="C64" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>53</v>
+      </c>
+      <c r="B65" t="s">
+        <v>220</v>
+      </c>
+      <c r="C65" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>54</v>
+      </c>
+      <c r="B66" t="s">
+        <v>221</v>
+      </c>
+      <c r="C66" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>55</v>
+      </c>
+      <c r="B67" t="s">
+        <v>222</v>
+      </c>
+      <c r="C67" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>56</v>
+      </c>
+      <c r="B68" t="s">
+        <v>223</v>
+      </c>
+      <c r="C68" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>57</v>
+      </c>
+      <c r="B69" t="s">
+        <v>224</v>
+      </c>
+      <c r="C69" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>58</v>
+      </c>
+      <c r="B70" t="s">
+        <v>225</v>
+      </c>
+      <c r="C70" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>59</v>
       </c>
-      <c r="C58" t="s">
+      <c r="B71" t="s">
+        <v>226</v>
+      </c>
+      <c r="C71" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>60</v>
+      </c>
+      <c r="B72" t="s">
+        <v>227</v>
+      </c>
+      <c r="C72" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>61</v>
+      </c>
+      <c r="B73" t="s">
+        <v>228</v>
+      </c>
+      <c r="C73" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" t="s">
+        <v>229</v>
+      </c>
+      <c r="C74" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75" t="s">
+        <v>230</v>
+      </c>
+      <c r="C75" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>63</v>
+      </c>
+      <c r="B76" t="s">
+        <v>231</v>
+      </c>
+      <c r="C76" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" t="s">
+        <v>232</v>
+      </c>
+      <c r="C77" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B78" t="s">
+        <v>233</v>
+      </c>
+      <c r="C78" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" t="s">
+        <v>234</v>
+      </c>
+      <c r="C79" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>66</v>
+      </c>
+      <c r="B80" t="s">
+        <v>235</v>
+      </c>
+      <c r="C80" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>67</v>
+      </c>
+      <c r="B81" t="s">
+        <v>236</v>
+      </c>
+      <c r="C81" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>68</v>
+      </c>
+      <c r="B82" t="s">
+        <v>237</v>
+      </c>
+      <c r="C82" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>69</v>
+      </c>
+      <c r="B83" t="s">
+        <v>238</v>
+      </c>
+      <c r="C83" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>70</v>
+      </c>
+      <c r="B84" t="s">
+        <v>239</v>
+      </c>
+      <c r="C84" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>71</v>
+      </c>
+      <c r="B85" t="s">
+        <v>240</v>
+      </c>
+      <c r="C85" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>72</v>
+      </c>
+      <c r="B86" t="s">
+        <v>241</v>
+      </c>
+      <c r="C86" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>73</v>
+      </c>
+      <c r="B87" t="s">
+        <v>242</v>
+      </c>
+      <c r="C87" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>73</v>
+      </c>
+      <c r="B88" t="s">
+        <v>243</v>
+      </c>
+      <c r="C88" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>74</v>
+      </c>
+      <c r="B89" t="s">
+        <v>244</v>
+      </c>
+      <c r="C89" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>75</v>
+      </c>
+      <c r="B90" t="s">
+        <v>245</v>
+      </c>
+      <c r="C90" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>76</v>
+      </c>
+      <c r="B91" t="s">
+        <v>246</v>
+      </c>
+      <c r="C91" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>77</v>
+      </c>
+      <c r="B92" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>78</v>
+      </c>
+      <c r="B93" t="s">
+        <v>248</v>
+      </c>
+      <c r="C93" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>79</v>
+      </c>
+      <c r="B94" t="s">
+        <v>249</v>
+      </c>
+      <c r="C94" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>108</v>
+      </c>
+      <c r="B95" t="s">
+        <v>250</v>
+      </c>
+      <c r="C95" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>108</v>
+      </c>
+      <c r="B96" t="s">
+        <v>251</v>
+      </c>
+      <c r="C96" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>109</v>
+      </c>
+      <c r="B97" t="s">
+        <v>252</v>
+      </c>
+      <c r="C97" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>110</v>
+      </c>
+      <c r="B98" t="s">
+        <v>253</v>
+      </c>
+      <c r="C98" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>111</v>
+      </c>
+      <c r="B99" t="s">
+        <v>254</v>
+      </c>
+      <c r="C99" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>112</v>
+      </c>
+      <c r="B100" t="s">
+        <v>255</v>
+      </c>
+      <c r="C100" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>113</v>
+      </c>
+      <c r="B101" t="s">
+        <v>256</v>
+      </c>
+      <c r="C101" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>114</v>
+      </c>
+      <c r="B102" t="s">
+        <v>257</v>
+      </c>
+      <c r="C102" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>115</v>
+      </c>
+      <c r="B103" t="s">
+        <v>258</v>
+      </c>
+      <c r="C103" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>116</v>
+      </c>
+      <c r="B104" t="s">
+        <v>259</v>
+      </c>
+      <c r="C104" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>117</v>
+      </c>
+      <c r="B105" t="s">
+        <v>260</v>
+      </c>
+      <c r="C105" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>118</v>
+      </c>
+      <c r="B106" t="s">
+        <v>261</v>
+      </c>
+      <c r="C106" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>119</v>
+      </c>
+      <c r="B107" t="s">
+        <v>262</v>
+      </c>
+      <c r="C107" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C59" t="s">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>120</v>
+      </c>
+      <c r="B108" t="s">
+        <v>263</v>
+      </c>
+      <c r="C108" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>121</v>
+      </c>
+      <c r="B109" t="s">
+        <v>264</v>
+      </c>
+      <c r="C109" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>122</v>
+      </c>
+      <c r="B110" t="s">
+        <v>265</v>
+      </c>
+      <c r="C110" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>123</v>
+      </c>
+      <c r="B111" t="s">
+        <v>266</v>
+      </c>
+      <c r="C111" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>124</v>
+      </c>
+      <c r="B112" t="s">
+        <v>267</v>
+      </c>
+      <c r="C112" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>124</v>
+      </c>
+      <c r="B113" t="s">
+        <v>268</v>
+      </c>
+      <c r="C113" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>125</v>
+      </c>
+      <c r="B114" t="s">
+        <v>269</v>
+      </c>
+      <c r="C114" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>126</v>
+      </c>
+      <c r="B115" t="s">
+        <v>270</v>
+      </c>
+      <c r="C115" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>127</v>
+      </c>
+      <c r="B116" t="s">
+        <v>271</v>
+      </c>
+      <c r="C116" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>128</v>
+      </c>
+      <c r="B117" t="s">
+        <v>272</v>
+      </c>
+      <c r="C117" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>129</v>
+      </c>
+      <c r="B118" t="s">
+        <v>273</v>
+      </c>
+      <c r="C118" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>130</v>
+      </c>
+      <c r="B119" t="s">
+        <v>274</v>
+      </c>
+      <c r="C119" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>130</v>
+      </c>
+      <c r="B120" t="s">
+        <v>275</v>
+      </c>
+      <c r="C120" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>131</v>
+      </c>
+      <c r="B121" t="s">
+        <v>276</v>
+      </c>
+      <c r="C121" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C61" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C62" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C63" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C64" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C65" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C66" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C67" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C68" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C69" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C70" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C71" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C72" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C73" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C74" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C75" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C76" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C77" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C78" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>132</v>
+      </c>
+      <c r="B122" t="s">
+        <v>277</v>
+      </c>
+      <c r="C122" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>133</v>
+      </c>
+      <c r="B123" t="s">
+        <v>278</v>
+      </c>
+      <c r="C123" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>134</v>
+      </c>
+      <c r="B124" t="s">
+        <v>279</v>
+      </c>
+      <c r="C124" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>134</v>
+      </c>
+      <c r="B125" t="s">
+        <v>280</v>
+      </c>
+      <c r="C125" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>135</v>
+      </c>
+      <c r="B126" t="s">
+        <v>281</v>
+      </c>
+      <c r="C126" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>136</v>
+      </c>
+      <c r="B127" t="s">
+        <v>282</v>
+      </c>
+      <c r="C127" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>137</v>
+      </c>
+      <c r="B128" t="s">
+        <v>283</v>
+      </c>
+      <c r="C128" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>138</v>
+      </c>
+      <c r="B129" t="s">
+        <v>284</v>
+      </c>
+      <c r="C129" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>139</v>
+      </c>
+      <c r="B130" t="s">
+        <v>285</v>
+      </c>
+      <c r="C130" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>140</v>
+      </c>
+      <c r="B131" t="s">
+        <v>286</v>
+      </c>
+      <c r="C131" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>141</v>
+      </c>
+      <c r="B132" t="s">
+        <v>287</v>
+      </c>
+      <c r="C132" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>142</v>
+      </c>
+      <c r="B133" t="s">
+        <v>288</v>
+      </c>
+      <c r="C133" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>143</v>
+      </c>
+      <c r="B134" t="s">
+        <v>289</v>
+      </c>
+      <c r="C134" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>144</v>
+      </c>
+      <c r="B135" t="s">
+        <v>290</v>
+      </c>
+      <c r="C135" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>144</v>
+      </c>
+      <c r="B136" t="s">
+        <v>291</v>
+      </c>
+      <c r="C136" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>145</v>
+      </c>
+      <c r="B137" t="s">
+        <v>292</v>
+      </c>
+      <c r="C137" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>146</v>
+      </c>
+      <c r="B138" t="s">
+        <v>293</v>
+      </c>
+      <c r="C138" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>147</v>
+      </c>
+      <c r="B139" t="s">
+        <v>294</v>
+      </c>
+      <c r="C139" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>148</v>
+      </c>
+      <c r="B140" t="s">
+        <v>295</v>
+      </c>
+      <c r="C140" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>149</v>
+      </c>
+      <c r="B141" t="s">
+        <v>296</v>
+      </c>
+      <c r="C141" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>150</v>
+      </c>
+      <c r="B142" t="s">
+        <v>297</v>
+      </c>
+      <c r="C142" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>151</v>
+      </c>
+      <c r="B143" t="s">
+        <v>298</v>
+      </c>
+      <c r="C143" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>151</v>
+      </c>
+      <c r="B144" t="s">
+        <v>299</v>
+      </c>
+      <c r="C144" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>152</v>
+      </c>
+      <c r="B145" t="s">
+        <v>300</v>
+      </c>
+      <c r="C145" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>153</v>
+      </c>
+      <c r="B146" t="s">
+        <v>301</v>
+      </c>
+      <c r="C146" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>153</v>
+      </c>
+      <c r="B147" t="s">
+        <v>302</v>
+      </c>
+      <c r="C147" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>154</v>
+      </c>
+      <c r="B148" t="s">
+        <v>303</v>
+      </c>
+      <c r="C148" t="s">
         <v>80</v>
       </c>
-      <c r="C79" t="s">
-        <v>81</v>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>155</v>
+      </c>
+      <c r="B149" t="s">
+        <v>304</v>
+      </c>
+      <c r="C149" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>156</v>
+      </c>
+      <c r="B150" t="s">
+        <v>305</v>
+      </c>
+      <c r="C150" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9733E5E-B9DC-4952-8C2A-D99A72132D9C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD0F22B-D26A-48C7-BB39-AC78865E32DE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="430">
   <si>
     <t>UTK</t>
   </si>
@@ -435,7 +435,889 @@
     <t>99002506</t>
   </si>
   <si>
-    <t>sz</t>
+    <t>SZ-854</t>
+  </si>
+  <si>
+    <t>SZ-850</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-870</t>
+  </si>
+  <si>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-802</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>SZ-8101</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-800</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>SZ-860</t>
+  </si>
+  <si>
+    <t>267006799</t>
+  </si>
+  <si>
+    <t>267006894</t>
+  </si>
+  <si>
+    <t>267006919</t>
+  </si>
+  <si>
+    <t>267006938</t>
+  </si>
+  <si>
+    <t>267006940</t>
+  </si>
+  <si>
+    <t>ID5118_XD</t>
+  </si>
+  <si>
+    <t>ID5121_XD</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-XSAQ</t>
+  </si>
+  <si>
+    <t>NFD6-05-08-2CYR</t>
+  </si>
+  <si>
+    <t>NFD6-05-08-JXN2</t>
+  </si>
+  <si>
+    <t>NFD6-05-08-MJ9A</t>
+  </si>
+  <si>
+    <t>NFD6-05-08-Q6JE</t>
+  </si>
+  <si>
+    <t>NFD6-05-09-4Y2E</t>
+  </si>
+  <si>
+    <t>NFD6-05-09-52DR</t>
+  </si>
+  <si>
+    <t>NFD6-05-09-5G6K</t>
+  </si>
+  <si>
+    <t>NFD6-05-09-G7NS</t>
+  </si>
+  <si>
+    <t>NFD6-05-09-RXZD</t>
+  </si>
+  <si>
+    <t>NFD6-05-10-59HT</t>
+  </si>
+  <si>
+    <t>NFD6-05-10-TXLL</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-3ZCZ</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-6R9E</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-7VDZ</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-874A</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-BJAA</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-BP46</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-DKYL</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-GLQ9</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-H4JJ</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-J3LE</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-LSGB</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-SGRY</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-XJJN</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-XMY8</t>
+  </si>
+  <si>
+    <t>NFE6-05-05-QNNL</t>
+  </si>
+  <si>
+    <t>NFE6-05-09-27KK</t>
+  </si>
+  <si>
+    <t>NFE6-05-10-5JPV</t>
+  </si>
+  <si>
+    <t>NFE6-05-10-MY4N</t>
+  </si>
+  <si>
+    <t>NFE6-05-11-5BAK</t>
+  </si>
+  <si>
+    <t>NFE6-05-11-642L</t>
+  </si>
+  <si>
+    <t>NFE6-05-11-NMWK</t>
+  </si>
+  <si>
+    <t>NFE6-05-11-XPQS</t>
+  </si>
+  <si>
+    <t>SA26/H002661</t>
+  </si>
+  <si>
+    <t>SA26/H002700</t>
+  </si>
+  <si>
+    <t>SA26/H002703</t>
+  </si>
+  <si>
+    <t>SA26/H002704</t>
+  </si>
+  <si>
+    <t>SA26/H002712</t>
+  </si>
+  <si>
+    <t>arajanlat</t>
+  </si>
+  <si>
+    <t>69fdd3ed8046ce4dbfb90db0</t>
+  </si>
+  <si>
+    <t>69fe07038046ce4dbfb915ab</t>
+  </si>
+  <si>
+    <t>6a0302968046ce4dbfb95ddb</t>
+  </si>
+  <si>
+    <t>6a01ed968046ce4dbfb94b52</t>
+  </si>
+  <si>
+    <t>69f8c4ec47d1aed7c386283d</t>
+  </si>
+  <si>
+    <t>6a0185c48046ce4dbfb936d5</t>
+  </si>
+  <si>
+    <t>6a01c6068046ce4dbfb9438e</t>
+  </si>
+  <si>
+    <t>69f9eb1447d1aed7c3863c74</t>
+  </si>
+  <si>
+    <t>69fc25c28046ce4dbfb8e757</t>
+  </si>
+  <si>
+    <t>6a02fe638046ce4dbfb95d2b</t>
+  </si>
+  <si>
+    <t>6a01c6588046ce4dbfb943a1</t>
+  </si>
+  <si>
+    <t>6a030dc58046ce4dbfb95fd4</t>
+  </si>
+  <si>
+    <t>6a01ae668046ce4dbfb93f49</t>
+  </si>
+  <si>
+    <t>69fdd06f8046ce4dbfb90d24</t>
+  </si>
+  <si>
+    <t>69fdf3818046ce4dbfb91312</t>
+  </si>
+  <si>
+    <t>69fdf3818046ce4dbfb91315</t>
+  </si>
+  <si>
+    <t>69fde69d8046ce4dbfb91116</t>
+  </si>
+  <si>
+    <t>69fe089b8046ce4dbfb915d8</t>
+  </si>
+  <si>
+    <t>69fe22578046ce4dbfb91826</t>
+  </si>
+  <si>
+    <t>69fe22578046ce4dbfb91827</t>
+  </si>
+  <si>
+    <t>69fee2978046ce4dbfb91aef</t>
+  </si>
+  <si>
+    <t>69fee2978046ce4dbfb91af2</t>
+  </si>
+  <si>
+    <t>69ff4e5e8046ce4dbfb92599</t>
+  </si>
+  <si>
+    <t>69ff4e5e8046ce4dbfb9259a</t>
+  </si>
+  <si>
+    <t>69fee0398046ce4dbfb91aa6</t>
+  </si>
+  <si>
+    <t>69fee3be8046ce4dbfb91b1d</t>
+  </si>
+  <si>
+    <t>69fee3be8046ce4dbfb91b21</t>
+  </si>
+  <si>
+    <t>69fee6188046ce4dbfb91b79</t>
+  </si>
+  <si>
+    <t>69ff187a8046ce4dbfb921ce</t>
+  </si>
+  <si>
+    <t>69ff187a8046ce4dbfb921d0</t>
+  </si>
+  <si>
+    <t>69ff7f978046ce4dbfb927cf</t>
+  </si>
+  <si>
+    <t>6a003d6d8046ce4dbfb929b7</t>
+  </si>
+  <si>
+    <t>6a0052818046ce4dbfb92b50</t>
+  </si>
+  <si>
+    <t>6a02ba048046ce4dbfb952b2</t>
+  </si>
+  <si>
+    <t>6a00666e8046ce4dbfb92cb9</t>
+  </si>
+  <si>
+    <t>6a0084ef8046ce4dbfb92f00</t>
+  </si>
+  <si>
+    <t>6a0091d18046ce4dbfb92fc5</t>
+  </si>
+  <si>
+    <t>6a00a48d8046ce4dbfb930f7</t>
+  </si>
+  <si>
+    <t>6a00a48d8046ce4dbfb930f9</t>
+  </si>
+  <si>
+    <t>6a00a35c8046ce4dbfb930e5</t>
+  </si>
+  <si>
+    <t>6a0032de8046ce4dbfb92944</t>
+  </si>
+  <si>
+    <t>6a0054d98046ce4dbfb92b80</t>
+  </si>
+  <si>
+    <t>6a005f688046ce4dbfb92c2f</t>
+  </si>
+  <si>
+    <t>6a0073578046ce4dbfb92d9c</t>
+  </si>
+  <si>
+    <t>6a0073578046ce4dbfb92d9d</t>
+  </si>
+  <si>
+    <t>6a00acc58046ce4dbfb93179</t>
+  </si>
+  <si>
+    <t>6a00e9b38046ce4dbfb933a4</t>
+  </si>
+  <si>
+    <t>6a00ec0b8046ce4dbfb933b0</t>
+  </si>
+  <si>
+    <t>6a0179d98046ce4dbfb934e7</t>
+  </si>
+  <si>
+    <t>6a01801e8046ce4dbfb93590</t>
+  </si>
+  <si>
+    <t>6a0197268046ce4dbfb93a07</t>
+  </si>
+  <si>
+    <t>6a01b5988046ce4dbfb940a8</t>
+  </si>
+  <si>
+    <t>6a01d79b8046ce4dbfb9470c</t>
+  </si>
+  <si>
+    <t>6a01d79b8046ce4dbfb9470d</t>
+  </si>
+  <si>
+    <t>6a01fd148046ce4dbfb94dba</t>
+  </si>
+  <si>
+    <t>6a01a0838046ce4dbfb93c4c</t>
+  </si>
+  <si>
+    <t>6a01c6278046ce4dbfb9439b</t>
+  </si>
+  <si>
+    <t>6a01cab98046ce4dbfb9446f</t>
+  </si>
+  <si>
+    <t>6a01d0918046ce4dbfb94603</t>
+  </si>
+  <si>
+    <t>6a01f60d8046ce4dbfb94cb6</t>
+  </si>
+  <si>
+    <t>6a020d848046ce4dbfb94f6b</t>
+  </si>
+  <si>
+    <t>6a02ee868046ce4dbfb959c8</t>
+  </si>
+  <si>
+    <t>6a0309788046ce4dbfb95f02</t>
+  </si>
+  <si>
+    <t>6a02b9c48046ce4dbfb952a7</t>
+  </si>
+  <si>
+    <t>6a030cf78046ce4dbfb95f95</t>
+  </si>
+  <si>
+    <t>FIZZ-1000900874</t>
+  </si>
+  <si>
+    <t>1449-439052</t>
+  </si>
+  <si>
+    <t>1449-401182</t>
+  </si>
+  <si>
+    <t>1449-123150</t>
+  </si>
+  <si>
+    <t>1449-813565</t>
+  </si>
+  <si>
+    <t>309779536/1</t>
+  </si>
+  <si>
+    <t>309830270/2/1</t>
+  </si>
+  <si>
+    <t>309830270/2/2</t>
+  </si>
+  <si>
+    <t>309830270/2/3</t>
+  </si>
+  <si>
+    <t>309999996/1</t>
+  </si>
+  <si>
+    <t>310412095/1</t>
+  </si>
+  <si>
+    <t>310412095/2</t>
+  </si>
+  <si>
+    <t>310412095/3</t>
+  </si>
+  <si>
+    <t>310467645/1</t>
+  </si>
+  <si>
+    <t>310467645/2</t>
+  </si>
+  <si>
+    <t>310573223/1</t>
+  </si>
+  <si>
+    <t>310573223/2</t>
+  </si>
+  <si>
+    <t>310573223/3</t>
+  </si>
+  <si>
+    <t>310776273/1</t>
+  </si>
+  <si>
+    <t>310777057/1</t>
+  </si>
+  <si>
+    <t>310904298/1</t>
+  </si>
+  <si>
+    <t>310904530/1</t>
+  </si>
+  <si>
+    <t>310904530/2</t>
+  </si>
+  <si>
+    <t>310904530/3</t>
+  </si>
+  <si>
+    <t>310904565/1</t>
+  </si>
+  <si>
+    <t>310904565/2</t>
+  </si>
+  <si>
+    <t>310904671/1</t>
+  </si>
+  <si>
+    <t>310904671/2</t>
+  </si>
+  <si>
+    <t>310905005/1</t>
+  </si>
+  <si>
+    <t>310969084/1</t>
+  </si>
+  <si>
+    <t>310969174/1</t>
+  </si>
+  <si>
+    <t>310969174/2</t>
+  </si>
+  <si>
+    <t>310969217/1</t>
+  </si>
+  <si>
+    <t>310969250/1</t>
+  </si>
+  <si>
+    <t>310969430/1</t>
+  </si>
+  <si>
+    <t>310969430/2</t>
+  </si>
+  <si>
+    <t>310969501/1</t>
+  </si>
+  <si>
+    <t>310969545/1</t>
+  </si>
+  <si>
+    <t>311037873/1</t>
+  </si>
+  <si>
+    <t>311037873/2</t>
+  </si>
+  <si>
+    <t>311037873/3</t>
+  </si>
+  <si>
+    <t>311038012/1</t>
+  </si>
+  <si>
+    <t>311038109/1</t>
+  </si>
+  <si>
+    <t>311038109/2</t>
+  </si>
+  <si>
+    <t>311038233/1</t>
+  </si>
+  <si>
+    <t>311038623/1</t>
+  </si>
+  <si>
+    <t>311038768/1</t>
+  </si>
+  <si>
+    <t>311103072/1</t>
+  </si>
+  <si>
+    <t>311103154/1</t>
+  </si>
+  <si>
+    <t>311103227/1</t>
+  </si>
+  <si>
+    <t>311103305/1</t>
+  </si>
+  <si>
+    <t>311103542/1</t>
+  </si>
+  <si>
+    <t>311103600/1</t>
+  </si>
+  <si>
+    <t>311103600/2</t>
+  </si>
+  <si>
+    <t>311103805/1</t>
+  </si>
+  <si>
+    <t>311177137/1</t>
+  </si>
+  <si>
+    <t>311177166/1</t>
+  </si>
+  <si>
+    <t>311177570/1</t>
+  </si>
+  <si>
+    <t>311177570/2</t>
+  </si>
+  <si>
+    <t>311177646/1</t>
+  </si>
+  <si>
+    <t>311245302/1</t>
+  </si>
+  <si>
+    <t>311245302/2</t>
+  </si>
+  <si>
+    <t>311245393/1</t>
+  </si>
+  <si>
+    <t>311245587/1</t>
+  </si>
+  <si>
+    <t>311245812/1</t>
+  </si>
+  <si>
+    <t>311245914/1</t>
+  </si>
+  <si>
+    <t>311245993/1</t>
+  </si>
+  <si>
+    <t>311246086/1</t>
+  </si>
+  <si>
+    <t>311246086/2</t>
+  </si>
+  <si>
+    <t>311246161/1</t>
+  </si>
+  <si>
+    <t>311288109/1</t>
+  </si>
+  <si>
+    <t>311288178/1</t>
+  </si>
+  <si>
+    <t>311288178/2</t>
+  </si>
+  <si>
+    <t>311288178/3</t>
+  </si>
+  <si>
+    <t>311288327/1</t>
+  </si>
+  <si>
+    <t>311288343/1</t>
+  </si>
+  <si>
+    <t>311288609/1</t>
+  </si>
+  <si>
+    <t>311288642/1</t>
+  </si>
+  <si>
+    <t>311288658/1</t>
+  </si>
+  <si>
+    <t>311288658/2</t>
+  </si>
+  <si>
+    <t>311288658/3</t>
+  </si>
+  <si>
+    <t>311288795/1</t>
+  </si>
+  <si>
+    <t>311288830/1</t>
+  </si>
+  <si>
+    <t>311288935/1</t>
+  </si>
+  <si>
+    <t>311289053/1</t>
+  </si>
+  <si>
+    <t>311289075/1</t>
+  </si>
+  <si>
+    <t>311345286/1</t>
+  </si>
+  <si>
+    <t>311345508/1</t>
+  </si>
+  <si>
+    <t>311345610/1</t>
+  </si>
+  <si>
+    <t>311345642/1</t>
+  </si>
+  <si>
+    <t>311345780/1</t>
+  </si>
+  <si>
+    <t>311345928/1</t>
+  </si>
+  <si>
+    <t>311345979/1</t>
+  </si>
+  <si>
+    <t>311346001/1</t>
+  </si>
+  <si>
+    <t>311346072/1</t>
+  </si>
+  <si>
+    <t>311346091/1</t>
+  </si>
+  <si>
+    <t>311378946/1</t>
+  </si>
+  <si>
+    <t>311379048/1</t>
+  </si>
+  <si>
+    <t>311379093/1</t>
+  </si>
+  <si>
+    <t>311379275/1</t>
+  </si>
+  <si>
+    <t>311379275/2</t>
+  </si>
+  <si>
+    <t>311379630/1</t>
+  </si>
+  <si>
+    <t>311379706/1</t>
+  </si>
+  <si>
+    <t>311379848/1</t>
+  </si>
+  <si>
+    <t>99002434/1</t>
+  </si>
+  <si>
+    <t>99002506/1</t>
+  </si>
+  <si>
+    <t>159995579540072845</t>
+  </si>
+  <si>
+    <t>159995579540072579</t>
+  </si>
+  <si>
+    <t>202605082601023601</t>
+  </si>
+  <si>
+    <t>202605112601030601</t>
+  </si>
+  <si>
+    <t>202605112601031701</t>
+  </si>
+  <si>
+    <t>202605112601028501</t>
+  </si>
+  <si>
+    <t>202605112601028401</t>
+  </si>
+  <si>
+    <t>202605112601037801</t>
+  </si>
+  <si>
+    <t>202605112601034201</t>
+  </si>
+  <si>
+    <t>202605112601038201</t>
+  </si>
+  <si>
+    <t>202605112601034401</t>
+  </si>
+  <si>
+    <t>202605112601034101</t>
+  </si>
+  <si>
+    <t>202605112601041801</t>
+  </si>
+  <si>
+    <t>202605112601042101</t>
+  </si>
+  <si>
+    <t>202605122601052801</t>
+  </si>
+  <si>
+    <t>202605122601050801</t>
+  </si>
+  <si>
+    <t>202605122601051901</t>
+  </si>
+  <si>
+    <t>202605122601051902</t>
+  </si>
+  <si>
+    <t>202605122601050501</t>
+  </si>
+  <si>
+    <t>202605122601052601</t>
+  </si>
+  <si>
+    <t>202605122601052101</t>
+  </si>
+  <si>
+    <t>202605122601056501</t>
+  </si>
+  <si>
+    <t>202605122601053801</t>
+  </si>
+  <si>
+    <t>202605122601053802</t>
+  </si>
+  <si>
+    <t>202605122601051301</t>
+  </si>
+  <si>
+    <t>202605122601055301</t>
+  </si>
+  <si>
+    <t>202605122601053001</t>
+  </si>
+  <si>
+    <t>202605122601057701</t>
+  </si>
+  <si>
+    <t>202605122601057301</t>
+  </si>
+  <si>
+    <t>202605122601050701</t>
+  </si>
+  <si>
+    <t>202605122601010601</t>
+  </si>
+  <si>
+    <t>202605112601034801</t>
+  </si>
+  <si>
+    <t>202605112601049301</t>
+  </si>
+  <si>
+    <t>202605112601045301</t>
+  </si>
+  <si>
+    <t>202605122601052301</t>
+  </si>
+  <si>
+    <t>202605122601055701</t>
+  </si>
+  <si>
+    <t>202605122601053701</t>
+  </si>
+  <si>
+    <t>202605122601054101</t>
+  </si>
+  <si>
+    <t>202605122601054102</t>
+  </si>
+  <si>
+    <t>202605122601054103</t>
+  </si>
+  <si>
+    <t>202605122601054104</t>
+  </si>
+  <si>
+    <t>159995579540036212</t>
+  </si>
+  <si>
+    <t>159995579540036229</t>
+  </si>
+  <si>
+    <t>159995579540051314</t>
+  </si>
+  <si>
+    <t>159995579540069814</t>
+  </si>
+  <si>
+    <t>159995579540069883</t>
+  </si>
+  <si>
+    <t>159995579540069890</t>
+  </si>
+  <si>
+    <t>159995579540072180</t>
+  </si>
+  <si>
+    <t>159995579540072197</t>
+  </si>
+  <si>
+    <t>159995579540075105</t>
+  </si>
+  <si>
+    <t>159995579540075112</t>
+  </si>
+  <si>
+    <t>159995579540075129</t>
   </si>
 </sst>
 </file>
@@ -471,10 +1353,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -756,12 +1637,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D133"/>
+  <dimension ref="A1:D224"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
@@ -777,1059 +1658,2456 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>207</v>
       </c>
       <c r="C2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
+      <c r="B3" t="s">
+        <v>208</v>
+      </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
+      <c r="B4" t="s">
+        <v>209</v>
+      </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
+      <c r="B5" t="s">
+        <v>210</v>
+      </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
+      <c r="B6" t="s">
+        <v>211</v>
+      </c>
       <c r="C6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
+      <c r="B7" t="s">
+        <v>212</v>
+      </c>
       <c r="C7" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
+      <c r="B8" t="s">
+        <v>213</v>
+      </c>
       <c r="C8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>11</v>
       </c>
+      <c r="B9" t="s">
+        <v>214</v>
+      </c>
       <c r="C9" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
+      <c r="B10" t="s">
+        <v>215</v>
+      </c>
       <c r="C10" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" t="s">
         <v>13</v>
       </c>
+      <c r="B11" t="s">
+        <v>216</v>
+      </c>
       <c r="C11" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" t="s">
         <v>14</v>
       </c>
+      <c r="B12" t="s">
+        <v>217</v>
+      </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" t="s">
         <v>15</v>
       </c>
+      <c r="B13" t="s">
+        <v>218</v>
+      </c>
       <c r="C13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" t="s">
         <v>16</v>
       </c>
+      <c r="B14" t="s">
+        <v>219</v>
+      </c>
       <c r="C14" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" t="s">
         <v>17</v>
       </c>
+      <c r="B15" t="s">
+        <v>220</v>
+      </c>
       <c r="C15" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" t="s">
         <v>18</v>
       </c>
+      <c r="B16" t="s">
+        <v>221</v>
+      </c>
       <c r="C16" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>222</v>
+      </c>
+      <c r="C17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>19</v>
       </c>
-      <c r="C17" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="B18" t="s">
+        <v>223</v>
+      </c>
+      <c r="C18" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>20</v>
       </c>
-      <c r="C18" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="B19" t="s">
+        <v>224</v>
+      </c>
+      <c r="C19" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>21</v>
       </c>
-      <c r="C19" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="B20" t="s">
+        <v>225</v>
+      </c>
+      <c r="C20" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>226</v>
+      </c>
+      <c r="C21" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="C20" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="B22" t="s">
+        <v>227</v>
+      </c>
+      <c r="C22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>228</v>
+      </c>
+      <c r="C23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="C21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="B24" t="s">
+        <v>229</v>
+      </c>
+      <c r="C24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>230</v>
+      </c>
+      <c r="C25" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>24</v>
       </c>
-      <c r="C22" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="B26" t="s">
+        <v>231</v>
+      </c>
+      <c r="C26" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>25</v>
       </c>
-      <c r="C23" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="B27" t="s">
+        <v>232</v>
+      </c>
+      <c r="C27" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>233</v>
+      </c>
+      <c r="C28" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>26</v>
       </c>
-      <c r="C24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="B29" t="s">
+        <v>234</v>
+      </c>
+      <c r="C29" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>27</v>
       </c>
-      <c r="C25" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="B30" t="s">
+        <v>235</v>
+      </c>
+      <c r="C30" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" t="s">
+        <v>236</v>
+      </c>
+      <c r="C31" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>28</v>
       </c>
-      <c r="C26" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="B32" t="s">
+        <v>237</v>
+      </c>
+      <c r="C32" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>29</v>
       </c>
-      <c r="C27" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="B33" t="s">
+        <v>238</v>
+      </c>
+      <c r="C33" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="C28" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="B34" t="s">
+        <v>239</v>
+      </c>
+      <c r="C34" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>31</v>
       </c>
-      <c r="C29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="B35" t="s">
+        <v>240</v>
+      </c>
+      <c r="C35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>32</v>
       </c>
-      <c r="C30" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="B36" t="s">
+        <v>241</v>
+      </c>
+      <c r="C36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>33</v>
       </c>
-      <c r="C31" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="B37" t="s">
+        <v>242</v>
+      </c>
+      <c r="C37" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>34</v>
       </c>
-      <c r="C32" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="B38" t="s">
+        <v>243</v>
+      </c>
+      <c r="C38" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>35</v>
       </c>
-      <c r="C33" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="B39" t="s">
+        <v>244</v>
+      </c>
+      <c r="C39" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" t="s">
+        <v>245</v>
+      </c>
+      <c r="C40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>36</v>
       </c>
-      <c r="C34" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="B41" t="s">
+        <v>246</v>
+      </c>
+      <c r="C41" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>37</v>
       </c>
-      <c r="C35" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+      <c r="B42" t="s">
+        <v>247</v>
+      </c>
+      <c r="C42" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>38</v>
       </c>
-      <c r="C36" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+      <c r="B43" t="s">
+        <v>248</v>
+      </c>
+      <c r="C43" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>39</v>
       </c>
-      <c r="C37" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="B44" t="s">
+        <v>249</v>
+      </c>
+      <c r="C44" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>40</v>
       </c>
-      <c r="C38" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="B45" t="s">
+        <v>250</v>
+      </c>
+      <c r="C45" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" t="s">
+        <v>251</v>
+      </c>
+      <c r="C46" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>41</v>
       </c>
-      <c r="C39" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="B47" t="s">
+        <v>252</v>
+      </c>
+      <c r="C47" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>42</v>
       </c>
-      <c r="C40" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="B48" t="s">
+        <v>253</v>
+      </c>
+      <c r="C48" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>43</v>
       </c>
-      <c r="C41" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+      <c r="B49" t="s">
+        <v>254</v>
+      </c>
+      <c r="C49" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>44</v>
       </c>
-      <c r="C42" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+      <c r="B50" t="s">
+        <v>255</v>
+      </c>
+      <c r="C50" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>45</v>
       </c>
-      <c r="C43" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+      <c r="B51" t="s">
+        <v>256</v>
+      </c>
+      <c r="C51" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>46</v>
       </c>
-      <c r="C44" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+      <c r="B52" t="s">
+        <v>257</v>
+      </c>
+      <c r="C52" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>47</v>
       </c>
-      <c r="C45" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+      <c r="B53" t="s">
+        <v>258</v>
+      </c>
+      <c r="C53" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>48</v>
       </c>
-      <c r="C46" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+      <c r="B54" t="s">
+        <v>259</v>
+      </c>
+      <c r="C54" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>48</v>
+      </c>
+      <c r="B55" t="s">
+        <v>260</v>
+      </c>
+      <c r="C55" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>49</v>
       </c>
-      <c r="C47" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+      <c r="B56" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>50</v>
       </c>
-      <c r="C48" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+      <c r="B57" t="s">
+        <v>262</v>
+      </c>
+      <c r="C57" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>51</v>
       </c>
-      <c r="C49" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+      <c r="B58" t="s">
+        <v>263</v>
+      </c>
+      <c r="C58" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>52</v>
       </c>
-      <c r="C50" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C51" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C52" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C53" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C54" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C55" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C56" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C57" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C58" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>61</v>
+      <c r="B59" t="s">
+        <v>264</v>
       </c>
       <c r="C59" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>62</v>
+      <c r="A60" t="s">
+        <v>53</v>
+      </c>
+      <c r="B60" t="s">
+        <v>265</v>
       </c>
       <c r="C60" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>63</v>
+      <c r="A61" t="s">
+        <v>54</v>
+      </c>
+      <c r="B61" t="s">
+        <v>266</v>
       </c>
       <c r="C61" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>64</v>
+      <c r="A62" t="s">
+        <v>55</v>
+      </c>
+      <c r="B62" t="s">
+        <v>267</v>
       </c>
       <c r="C62" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>65</v>
+      <c r="A63" t="s">
+        <v>56</v>
+      </c>
+      <c r="B63" t="s">
+        <v>268</v>
       </c>
       <c r="C63" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>66</v>
+      <c r="A64" t="s">
+        <v>57</v>
+      </c>
+      <c r="B64" t="s">
+        <v>269</v>
       </c>
       <c r="C64" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>67</v>
+      <c r="A65" t="s">
+        <v>58</v>
+      </c>
+      <c r="B65" t="s">
+        <v>270</v>
       </c>
       <c r="C65" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>68</v>
+      <c r="A66" t="s">
+        <v>59</v>
+      </c>
+      <c r="B66" t="s">
+        <v>271</v>
       </c>
       <c r="C66" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>69</v>
+      <c r="A67" t="s">
+        <v>160</v>
+      </c>
+      <c r="B67" t="s">
+        <v>272</v>
       </c>
       <c r="C67" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>70</v>
+      <c r="A68" t="s">
+        <v>161</v>
+      </c>
+      <c r="B68" t="s">
+        <v>273</v>
       </c>
       <c r="C68" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>71</v>
+      <c r="A69" t="s">
+        <v>162</v>
+      </c>
+      <c r="B69" t="s">
+        <v>274</v>
       </c>
       <c r="C69" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>72</v>
+      <c r="A70" t="s">
+        <v>163</v>
+      </c>
+      <c r="B70" t="s">
+        <v>275</v>
       </c>
       <c r="C70" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>73</v>
+      <c r="A71" t="s">
+        <v>164</v>
+      </c>
+      <c r="B71" t="s">
+        <v>276</v>
       </c>
       <c r="C71" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>74</v>
+      <c r="A72" t="s">
+        <v>60</v>
+      </c>
+      <c r="B72" t="s">
+        <v>277</v>
       </c>
       <c r="C72" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>75</v>
+      <c r="A73" t="s">
+        <v>61</v>
+      </c>
+      <c r="B73" t="s">
+        <v>278</v>
       </c>
       <c r="C73" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>76</v>
+      <c r="A74" t="s">
+        <v>61</v>
+      </c>
+      <c r="B74" t="s">
+        <v>279</v>
       </c>
       <c r="C74" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>77</v>
+      <c r="A75" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75" t="s">
+        <v>280</v>
       </c>
       <c r="C75" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
+      <c r="A76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76" t="s">
+        <v>281</v>
+      </c>
+      <c r="C76" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" t="s">
+        <v>282</v>
+      </c>
+      <c r="C77" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>63</v>
+      </c>
+      <c r="B78" t="s">
+        <v>283</v>
+      </c>
+      <c r="C78" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>63</v>
+      </c>
+      <c r="B79" t="s">
+        <v>284</v>
+      </c>
+      <c r="C79" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>64</v>
+      </c>
+      <c r="B80" t="s">
+        <v>285</v>
+      </c>
+      <c r="C80" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>64</v>
+      </c>
+      <c r="B81" t="s">
+        <v>286</v>
+      </c>
+      <c r="C81" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>65</v>
+      </c>
+      <c r="B82" t="s">
+        <v>287</v>
+      </c>
+      <c r="C82" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>65</v>
+      </c>
+      <c r="B83" t="s">
+        <v>288</v>
+      </c>
+      <c r="C83" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>65</v>
+      </c>
+      <c r="B84" t="s">
+        <v>289</v>
+      </c>
+      <c r="C84" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>66</v>
+      </c>
+      <c r="B85" t="s">
+        <v>290</v>
+      </c>
+      <c r="C85" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>67</v>
+      </c>
+      <c r="B86" t="s">
+        <v>291</v>
+      </c>
+      <c r="C86" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>68</v>
+      </c>
+      <c r="B87" t="s">
+        <v>292</v>
+      </c>
+      <c r="C87" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>69</v>
+      </c>
+      <c r="B88" t="s">
+        <v>293</v>
+      </c>
+      <c r="C88" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>69</v>
+      </c>
+      <c r="B89" t="s">
+        <v>294</v>
+      </c>
+      <c r="C89" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>69</v>
+      </c>
+      <c r="B90" t="s">
+        <v>295</v>
+      </c>
+      <c r="C90" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>70</v>
+      </c>
+      <c r="B91" t="s">
+        <v>296</v>
+      </c>
+      <c r="C91" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>70</v>
+      </c>
+      <c r="B92" t="s">
+        <v>297</v>
+      </c>
+      <c r="C92" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>71</v>
+      </c>
+      <c r="B93" t="s">
+        <v>298</v>
+      </c>
+      <c r="C93" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>71</v>
+      </c>
+      <c r="B94" t="s">
+        <v>299</v>
+      </c>
+      <c r="C94" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>72</v>
+      </c>
+      <c r="B95" t="s">
+        <v>300</v>
+      </c>
+      <c r="C95" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>73</v>
+      </c>
+      <c r="B96" t="s">
+        <v>301</v>
+      </c>
+      <c r="C96" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>74</v>
+      </c>
+      <c r="B97" t="s">
+        <v>302</v>
+      </c>
+      <c r="C97" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>74</v>
+      </c>
+      <c r="B98" t="s">
+        <v>303</v>
+      </c>
+      <c r="C98" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>75</v>
+      </c>
+      <c r="B99" t="s">
+        <v>304</v>
+      </c>
+      <c r="C99" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>76</v>
+      </c>
+      <c r="B100" t="s">
+        <v>305</v>
+      </c>
+      <c r="C100" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>77</v>
+      </c>
+      <c r="B101" t="s">
+        <v>306</v>
+      </c>
+      <c r="C101" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>77</v>
+      </c>
+      <c r="B102" t="s">
+        <v>307</v>
+      </c>
+      <c r="C102" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
         <v>78</v>
       </c>
-      <c r="C76" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
+      <c r="B103" t="s">
+        <v>308</v>
+      </c>
+      <c r="C103" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
         <v>79</v>
       </c>
-      <c r="C77" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
+      <c r="B104" t="s">
+        <v>309</v>
+      </c>
+      <c r="C104" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
         <v>80</v>
       </c>
-      <c r="C78" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
+      <c r="B105" t="s">
+        <v>310</v>
+      </c>
+      <c r="C105" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>80</v>
+      </c>
+      <c r="B106" t="s">
+        <v>311</v>
+      </c>
+      <c r="C106" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>80</v>
+      </c>
+      <c r="B107" t="s">
+        <v>312</v>
+      </c>
+      <c r="C107" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
         <v>81</v>
       </c>
-      <c r="C79" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
+      <c r="B108" t="s">
+        <v>313</v>
+      </c>
+      <c r="C108" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
         <v>82</v>
       </c>
-      <c r="C80" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
+      <c r="B109" t="s">
+        <v>314</v>
+      </c>
+      <c r="C109" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>82</v>
+      </c>
+      <c r="B110" t="s">
+        <v>315</v>
+      </c>
+      <c r="C110" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
         <v>83</v>
       </c>
-      <c r="C81" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
+      <c r="B111" t="s">
+        <v>316</v>
+      </c>
+      <c r="C111" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>84</v>
       </c>
-      <c r="C82" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
+      <c r="B112" t="s">
+        <v>317</v>
+      </c>
+      <c r="C112" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
         <v>85</v>
       </c>
-      <c r="C83" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
+      <c r="B113" t="s">
+        <v>318</v>
+      </c>
+      <c r="C113" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
         <v>86</v>
       </c>
-      <c r="C84" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
+      <c r="B114" t="s">
+        <v>319</v>
+      </c>
+      <c r="C114" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
         <v>87</v>
       </c>
-      <c r="C85" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
+      <c r="B115" t="s">
+        <v>320</v>
+      </c>
+      <c r="C115" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
         <v>88</v>
       </c>
-      <c r="C86" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C87" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C88" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C89" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C90" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C91" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C92" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C93" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C94" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C95" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C96" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C97" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C98" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C99" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C100" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C101" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C102" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C103" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C104" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C105" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C106" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C107" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C108" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C109" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C110" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C111" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C112" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C113" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C114" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C115" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" s="2" t="s">
-        <v>117</v>
+      <c r="B116" t="s">
+        <v>321</v>
       </c>
       <c r="C116" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" s="2" t="s">
+      <c r="A117" t="s">
+        <v>89</v>
+      </c>
+      <c r="B117" t="s">
+        <v>322</v>
+      </c>
+      <c r="C117" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>90</v>
+      </c>
+      <c r="B118" t="s">
+        <v>323</v>
+      </c>
+      <c r="C118" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>91</v>
+      </c>
+      <c r="B119" t="s">
+        <v>324</v>
+      </c>
+      <c r="C119" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>91</v>
+      </c>
+      <c r="B120" t="s">
+        <v>325</v>
+      </c>
+      <c r="C120" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>92</v>
+      </c>
+      <c r="B121" t="s">
+        <v>326</v>
+      </c>
+      <c r="C121" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>93</v>
+      </c>
+      <c r="B122" t="s">
+        <v>327</v>
+      </c>
+      <c r="C122" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>94</v>
+      </c>
+      <c r="B123" t="s">
+        <v>328</v>
+      </c>
+      <c r="C123" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>95</v>
+      </c>
+      <c r="B124" t="s">
+        <v>329</v>
+      </c>
+      <c r="C124" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>95</v>
+      </c>
+      <c r="B125" t="s">
+        <v>330</v>
+      </c>
+      <c r="C125" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>96</v>
+      </c>
+      <c r="B126" t="s">
+        <v>331</v>
+      </c>
+      <c r="C126" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>97</v>
+      </c>
+      <c r="B127" t="s">
+        <v>332</v>
+      </c>
+      <c r="C127" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>97</v>
+      </c>
+      <c r="B128" t="s">
+        <v>333</v>
+      </c>
+      <c r="C128" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>98</v>
+      </c>
+      <c r="B129" t="s">
+        <v>334</v>
+      </c>
+      <c r="C129" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>99</v>
+      </c>
+      <c r="B130" t="s">
+        <v>335</v>
+      </c>
+      <c r="C130" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>100</v>
+      </c>
+      <c r="B131" t="s">
+        <v>336</v>
+      </c>
+      <c r="C131" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>5</v>
+      </c>
+      <c r="B132" t="s">
+        <v>337</v>
+      </c>
+      <c r="C132" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>101</v>
+      </c>
+      <c r="B133" t="s">
+        <v>338</v>
+      </c>
+      <c r="C133" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>102</v>
+      </c>
+      <c r="B134" t="s">
+        <v>339</v>
+      </c>
+      <c r="C134" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>102</v>
+      </c>
+      <c r="B135" t="s">
+        <v>340</v>
+      </c>
+      <c r="C135" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>103</v>
+      </c>
+      <c r="B136" t="s">
+        <v>341</v>
+      </c>
+      <c r="C136" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>104</v>
+      </c>
+      <c r="B137" t="s">
+        <v>342</v>
+      </c>
+      <c r="C137" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>105</v>
+      </c>
+      <c r="B138" t="s">
+        <v>343</v>
+      </c>
+      <c r="C138" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>105</v>
+      </c>
+      <c r="B139" t="s">
+        <v>344</v>
+      </c>
+      <c r="C139" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>105</v>
+      </c>
+      <c r="B140" t="s">
+        <v>345</v>
+      </c>
+      <c r="C140" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>106</v>
+      </c>
+      <c r="B141" t="s">
+        <v>346</v>
+      </c>
+      <c r="C141" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>107</v>
+      </c>
+      <c r="B142" t="s">
+        <v>347</v>
+      </c>
+      <c r="C142" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>108</v>
+      </c>
+      <c r="B143" t="s">
+        <v>348</v>
+      </c>
+      <c r="C143" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>109</v>
+      </c>
+      <c r="B144" t="s">
+        <v>349</v>
+      </c>
+      <c r="C144" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>110</v>
+      </c>
+      <c r="B145" t="s">
+        <v>350</v>
+      </c>
+      <c r="C145" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>110</v>
+      </c>
+      <c r="B146" t="s">
+        <v>351</v>
+      </c>
+      <c r="C146" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>110</v>
+      </c>
+      <c r="B147" t="s">
+        <v>352</v>
+      </c>
+      <c r="C147" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>111</v>
+      </c>
+      <c r="B148" t="s">
+        <v>353</v>
+      </c>
+      <c r="C148" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>112</v>
+      </c>
+      <c r="B149" t="s">
+        <v>354</v>
+      </c>
+      <c r="C149" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>113</v>
+      </c>
+      <c r="B150" t="s">
+        <v>355</v>
+      </c>
+      <c r="C150" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>114</v>
+      </c>
+      <c r="B151" t="s">
+        <v>356</v>
+      </c>
+      <c r="C151" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>115</v>
+      </c>
+      <c r="B152" t="s">
+        <v>357</v>
+      </c>
+      <c r="C152" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>116</v>
+      </c>
+      <c r="B153" t="s">
+        <v>358</v>
+      </c>
+      <c r="C153" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>117</v>
+      </c>
+      <c r="B154" t="s">
+        <v>359</v>
+      </c>
+      <c r="C154" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
         <v>118</v>
       </c>
-      <c r="C117" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
+      <c r="B155" t="s">
+        <v>360</v>
+      </c>
+      <c r="C155" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
         <v>119</v>
       </c>
-      <c r="C118" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
+      <c r="B156" t="s">
+        <v>361</v>
+      </c>
+      <c r="C156" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
         <v>120</v>
       </c>
-      <c r="C119" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" s="2" t="s">
+      <c r="B157" t="s">
+        <v>362</v>
+      </c>
+      <c r="C157" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
         <v>121</v>
       </c>
-      <c r="C120" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" s="2" t="s">
+      <c r="B158" t="s">
+        <v>363</v>
+      </c>
+      <c r="C158" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
         <v>122</v>
       </c>
-      <c r="C121" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" s="2" t="s">
+      <c r="B159" t="s">
+        <v>364</v>
+      </c>
+      <c r="C159" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
         <v>123</v>
       </c>
-      <c r="C122" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" s="2" t="s">
+      <c r="B160" t="s">
+        <v>365</v>
+      </c>
+      <c r="C160" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
         <v>124</v>
       </c>
-      <c r="C123" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" s="2" t="s">
+      <c r="B161" t="s">
+        <v>366</v>
+      </c>
+      <c r="C161" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
         <v>125</v>
       </c>
-      <c r="C124" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" s="2" t="s">
+      <c r="B162" t="s">
+        <v>367</v>
+      </c>
+      <c r="C162" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
         <v>126</v>
       </c>
-      <c r="C125" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" s="2" t="s">
+      <c r="B163" t="s">
+        <v>368</v>
+      </c>
+      <c r="C163" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
         <v>127</v>
       </c>
-      <c r="C126" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" s="2" t="s">
+      <c r="B164" t="s">
+        <v>369</v>
+      </c>
+      <c r="C164" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
         <v>128</v>
       </c>
-      <c r="C127" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128" s="2" t="s">
+      <c r="B165" t="s">
+        <v>370</v>
+      </c>
+      <c r="C165" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
         <v>129</v>
       </c>
-      <c r="C128" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129" s="2" t="s">
+      <c r="B166" t="s">
+        <v>371</v>
+      </c>
+      <c r="C166" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>129</v>
+      </c>
+      <c r="B167" t="s">
+        <v>372</v>
+      </c>
+      <c r="C167" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
         <v>130</v>
       </c>
-      <c r="C129" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130" s="2" t="s">
+      <c r="B168" t="s">
+        <v>373</v>
+      </c>
+      <c r="C168" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
         <v>131</v>
       </c>
-      <c r="C130" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" s="2" t="s">
+      <c r="B169" t="s">
+        <v>374</v>
+      </c>
+      <c r="C169" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
         <v>132</v>
       </c>
-      <c r="C131" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132" s="2" t="s">
+      <c r="B170" t="s">
+        <v>375</v>
+      </c>
+      <c r="C170" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
         <v>133</v>
       </c>
-      <c r="C132" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133" s="2" t="s">
+      <c r="B171" t="s">
+        <v>376</v>
+      </c>
+      <c r="C171" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
         <v>134</v>
       </c>
-      <c r="C133" t="s">
-        <v>135</v>
+      <c r="B172" t="s">
+        <v>377</v>
+      </c>
+      <c r="C172" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>165</v>
+      </c>
+      <c r="B173" t="s">
+        <v>378</v>
+      </c>
+      <c r="C173" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>166</v>
+      </c>
+      <c r="B174" t="s">
+        <v>379</v>
+      </c>
+      <c r="C174" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>167</v>
+      </c>
+      <c r="B175" t="s">
+        <v>380</v>
+      </c>
+      <c r="C175" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>168</v>
+      </c>
+      <c r="B176" t="s">
+        <v>381</v>
+      </c>
+      <c r="C176" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>169</v>
+      </c>
+      <c r="B177" t="s">
+        <v>382</v>
+      </c>
+      <c r="C177" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>170</v>
+      </c>
+      <c r="B178" t="s">
+        <v>383</v>
+      </c>
+      <c r="C178" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>171</v>
+      </c>
+      <c r="B179" t="s">
+        <v>384</v>
+      </c>
+      <c r="C179" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>172</v>
+      </c>
+      <c r="B180" t="s">
+        <v>385</v>
+      </c>
+      <c r="C180" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>173</v>
+      </c>
+      <c r="B181" t="s">
+        <v>386</v>
+      </c>
+      <c r="C181" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>174</v>
+      </c>
+      <c r="B182" t="s">
+        <v>387</v>
+      </c>
+      <c r="C182" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>175</v>
+      </c>
+      <c r="B183" t="s">
+        <v>388</v>
+      </c>
+      <c r="C183" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>176</v>
+      </c>
+      <c r="B184" t="s">
+        <v>389</v>
+      </c>
+      <c r="C184" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>177</v>
+      </c>
+      <c r="B185" t="s">
+        <v>390</v>
+      </c>
+      <c r="C185" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>178</v>
+      </c>
+      <c r="B186" t="s">
+        <v>391</v>
+      </c>
+      <c r="C186" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>179</v>
+      </c>
+      <c r="B187" t="s">
+        <v>392</v>
+      </c>
+      <c r="C187" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>180</v>
+      </c>
+      <c r="B188" t="s">
+        <v>393</v>
+      </c>
+      <c r="C188" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>181</v>
+      </c>
+      <c r="B189" t="s">
+        <v>394</v>
+      </c>
+      <c r="C189" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>181</v>
+      </c>
+      <c r="B190" t="s">
+        <v>395</v>
+      </c>
+      <c r="C190" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>182</v>
+      </c>
+      <c r="B191" t="s">
+        <v>396</v>
+      </c>
+      <c r="C191" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>183</v>
+      </c>
+      <c r="B192" t="s">
+        <v>397</v>
+      </c>
+      <c r="C192" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>184</v>
+      </c>
+      <c r="B193" t="s">
+        <v>398</v>
+      </c>
+      <c r="C193" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>185</v>
+      </c>
+      <c r="B194" t="s">
+        <v>399</v>
+      </c>
+      <c r="C194" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>186</v>
+      </c>
+      <c r="B195" t="s">
+        <v>400</v>
+      </c>
+      <c r="C195" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>186</v>
+      </c>
+      <c r="B196" t="s">
+        <v>401</v>
+      </c>
+      <c r="C196" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>187</v>
+      </c>
+      <c r="B197" t="s">
+        <v>402</v>
+      </c>
+      <c r="C197" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>188</v>
+      </c>
+      <c r="B198" t="s">
+        <v>403</v>
+      </c>
+      <c r="C198" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>189</v>
+      </c>
+      <c r="B199" t="s">
+        <v>404</v>
+      </c>
+      <c r="C199" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>190</v>
+      </c>
+      <c r="B200" t="s">
+        <v>405</v>
+      </c>
+      <c r="C200" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>191</v>
+      </c>
+      <c r="B201" t="s">
+        <v>406</v>
+      </c>
+      <c r="C201" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>192</v>
+      </c>
+      <c r="B202" t="s">
+        <v>407</v>
+      </c>
+      <c r="C202" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>193</v>
+      </c>
+      <c r="B203" t="s">
+        <v>408</v>
+      </c>
+      <c r="C203" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>194</v>
+      </c>
+      <c r="B204" t="s">
+        <v>409</v>
+      </c>
+      <c r="C204" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>195</v>
+      </c>
+      <c r="B205" t="s">
+        <v>410</v>
+      </c>
+      <c r="C205" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>196</v>
+      </c>
+      <c r="B206" t="s">
+        <v>411</v>
+      </c>
+      <c r="C206" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>197</v>
+      </c>
+      <c r="B207" t="s">
+        <v>412</v>
+      </c>
+      <c r="C207" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>198</v>
+      </c>
+      <c r="B208" t="s">
+        <v>413</v>
+      </c>
+      <c r="C208" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>199</v>
+      </c>
+      <c r="B209" t="s">
+        <v>414</v>
+      </c>
+      <c r="C209" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>200</v>
+      </c>
+      <c r="B210" t="s">
+        <v>415</v>
+      </c>
+      <c r="C210" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>200</v>
+      </c>
+      <c r="B211" t="s">
+        <v>416</v>
+      </c>
+      <c r="C211" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>200</v>
+      </c>
+      <c r="B212" t="s">
+        <v>417</v>
+      </c>
+      <c r="C212" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>200</v>
+      </c>
+      <c r="B213" t="s">
+        <v>418</v>
+      </c>
+      <c r="C213" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>201</v>
+      </c>
+      <c r="B214" t="s">
+        <v>419</v>
+      </c>
+      <c r="C214" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>201</v>
+      </c>
+      <c r="B215" t="s">
+        <v>420</v>
+      </c>
+      <c r="C215" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>202</v>
+      </c>
+      <c r="B216" t="s">
+        <v>421</v>
+      </c>
+      <c r="C216" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>203</v>
+      </c>
+      <c r="B217" t="s">
+        <v>422</v>
+      </c>
+      <c r="C217" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>204</v>
+      </c>
+      <c r="B218" t="s">
+        <v>423</v>
+      </c>
+      <c r="C218" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>204</v>
+      </c>
+      <c r="B219" t="s">
+        <v>424</v>
+      </c>
+      <c r="C219" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>205</v>
+      </c>
+      <c r="B220" t="s">
+        <v>425</v>
+      </c>
+      <c r="C220" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>205</v>
+      </c>
+      <c r="B221" t="s">
+        <v>426</v>
+      </c>
+      <c r="C221" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>206</v>
+      </c>
+      <c r="B222" t="s">
+        <v>427</v>
+      </c>
+      <c r="C222" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>206</v>
+      </c>
+      <c r="B223" t="s">
+        <v>428</v>
+      </c>
+      <c r="C223" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>206</v>
+      </c>
+      <c r="B224" t="s">
+        <v>429</v>
+      </c>
+      <c r="C224" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A532CF1F-BE8E-48BC-8C62-8D03B5BE2125}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEE2DF6-0721-4EC6-929A-4C9882BEF7C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="332">
   <si>
     <t>UTK</t>
   </si>
@@ -324,7 +324,706 @@
     <t>99002514</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-850</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>SZ-827</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-854</t>
+  </si>
+  <si>
+    <t>SZ-804</t>
+  </si>
+  <si>
+    <t>SZ-860</t>
+  </si>
+  <si>
+    <t>SA26/H002748</t>
+  </si>
+  <si>
+    <t>1-3939/2026</t>
+  </si>
+  <si>
+    <t>267006949</t>
+  </si>
+  <si>
+    <t>267007054</t>
+  </si>
+  <si>
+    <t>267007056</t>
+  </si>
+  <si>
+    <t>26MPE0005027</t>
+  </si>
+  <si>
+    <t>311725390</t>
+  </si>
+  <si>
+    <t>NFD6-04-29-JMY6</t>
+  </si>
+  <si>
+    <t>NFD6-05-06-6HHQ</t>
+  </si>
+  <si>
+    <t>NFD6-05-06-LT6R</t>
+  </si>
+  <si>
+    <t>NFD6-05-06-Z8D4</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-DKAG</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-KK2Y</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-P58A</t>
+  </si>
+  <si>
+    <t>NFD6-05-08-H2ZY</t>
+  </si>
+  <si>
+    <t>NFD6-05-09-UPJG</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-4KEB</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-74WL</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-7DYH</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-8P5J</t>
+  </si>
+  <si>
+    <t>NFD6-05-12-3D3R</t>
+  </si>
+  <si>
+    <t>NFD6-05-12-8TKM</t>
+  </si>
+  <si>
+    <t>NFD6-05-12-CFXT</t>
+  </si>
+  <si>
+    <t>NFD6-05-12-E9E2</t>
+  </si>
+  <si>
+    <t>NFD6-05-12-FP7Z</t>
+  </si>
+  <si>
+    <t>NFD6-05-12-KXQX</t>
+  </si>
+  <si>
+    <t>NFD6-05-12-VRYV</t>
+  </si>
+  <si>
+    <t>NFE6-04-30-MBAS</t>
+  </si>
+  <si>
+    <t>NFE6-05-06-QJBG</t>
+  </si>
+  <si>
+    <t>NFE6-05-08-UALN</t>
+  </si>
+  <si>
+    <t>NFE6-05-12-AZN3</t>
+  </si>
+  <si>
+    <t>NFE6-05-12-CRME</t>
+  </si>
+  <si>
+    <t>NFE6-05-12-SMDJ</t>
+  </si>
+  <si>
+    <t>NFE6-05-12-TJNS</t>
+  </si>
+  <si>
+    <t>NFE6-05-12-YCWQ</t>
+  </si>
+  <si>
+    <t>SA26/H001568</t>
+  </si>
+  <si>
+    <t>SA26/H002667</t>
+  </si>
+  <si>
+    <t>SA26/H002698</t>
+  </si>
+  <si>
+    <t>SA26/H002699</t>
+  </si>
+  <si>
+    <t>SA26/H002702</t>
+  </si>
+  <si>
+    <t>SA26/H002708</t>
+  </si>
+  <si>
+    <t>K/365</t>
+  </si>
+  <si>
+    <t>159995579540124902</t>
+  </si>
+  <si>
+    <t>248745814/1</t>
+  </si>
+  <si>
+    <t>248745814/2</t>
+  </si>
+  <si>
+    <t>69f989d347d1aed7c3862c9a</t>
+  </si>
+  <si>
+    <t>69faf9d747d1aed7c3864aef</t>
+  </si>
+  <si>
+    <t>6a02fe638046ce4dbfb95d2b</t>
+  </si>
+  <si>
+    <t>6a032e548046ce4dbfb966c3</t>
+  </si>
+  <si>
+    <t>6a032e548046ce4dbfb966c4</t>
+  </si>
+  <si>
+    <t>6a030dc58046ce4dbfb95fd4</t>
+  </si>
+  <si>
+    <t>69fda87b8046ce4dbfb90680</t>
+  </si>
+  <si>
+    <t>69fda87b8046ce4dbfb90681</t>
+  </si>
+  <si>
+    <t>69fdab238046ce4dbfb9072e</t>
+  </si>
+  <si>
+    <t>69fdbc688046ce4dbfb909d9</t>
+  </si>
+  <si>
+    <t>69fdbc688046ce4dbfb909da</t>
+  </si>
+  <si>
+    <t>69fddc0c8046ce4dbfb90f2d</t>
+  </si>
+  <si>
+    <t>6a02fa788046ce4dbfb95c79</t>
+  </si>
+  <si>
+    <t>69fdf5d98046ce4dbfb91385</t>
+  </si>
+  <si>
+    <t>69fe0c1e8046ce4dbfb91658</t>
+  </si>
+  <si>
+    <t>69fef8d48046ce4dbfb91e15</t>
+  </si>
+  <si>
+    <t>69fef8d48046ce4dbfb91e16</t>
+  </si>
+  <si>
+    <t>69ff1acf8046ce4dbfb921f2</t>
+  </si>
+  <si>
+    <t>69ff1acf8046ce4dbfb921f3</t>
+  </si>
+  <si>
+    <t>69ff2fe28046ce4dbfb92390</t>
+  </si>
+  <si>
+    <t>69ff4e5e8046ce4dbfb92599</t>
+  </si>
+  <si>
+    <t>69ff4e5e8046ce4dbfb9259a</t>
+  </si>
+  <si>
+    <t>69ff336b8046ce4dbfb923cf</t>
+  </si>
+  <si>
+    <t>6a006d758046ce4dbfb92d11</t>
+  </si>
+  <si>
+    <t>6a006d758046ce4dbfb92d13</t>
+  </si>
+  <si>
+    <t>6a030e038046ce4dbfb95fd7</t>
+  </si>
+  <si>
+    <t>6a0215b08046ce4dbfb94fff</t>
+  </si>
+  <si>
+    <t>6a01cf698046ce4dbfb945a3</t>
+  </si>
+  <si>
+    <t>6a01cf698046ce4dbfb945a4</t>
+  </si>
+  <si>
+    <t>6a033bef8046ce4dbfb96973</t>
+  </si>
+  <si>
+    <t>6a01cf698046ce4dbfb945a5</t>
+  </si>
+  <si>
+    <t>6a01d66b8046ce4dbfb946c9</t>
+  </si>
+  <si>
+    <t>6a01dc4b8046ce4dbfb947ee</t>
+  </si>
+  <si>
+    <t>6a01e3888046ce4dbfb9493b</t>
+  </si>
+  <si>
+    <t>6a01e80b8046ce4dbfb94a56</t>
+  </si>
+  <si>
+    <t>6a02cd208046ce4dbfb953b5</t>
+  </si>
+  <si>
+    <t>6a02cd208046ce4dbfb953b6</t>
+  </si>
+  <si>
+    <t>6a023c668046ce4dbfb9520c</t>
+  </si>
+  <si>
+    <t>6a0249408046ce4dbfb95230</t>
+  </si>
+  <si>
+    <t>6a0249408046ce4dbfb95231</t>
+  </si>
+  <si>
+    <t>6a02d5eb8046ce4dbfb954ed</t>
+  </si>
+  <si>
+    <t>6a02d5eb8046ce4dbfb954ee</t>
+  </si>
+  <si>
+    <t>6a03027e8046ce4dbfb95dd3</t>
+  </si>
+  <si>
+    <t>6a032b698046ce4dbfb96622</t>
+  </si>
+  <si>
+    <t>6a033e418046ce4dbfb969dd</t>
+  </si>
+  <si>
+    <t>6a02cb4f8046ce4dbfb95384</t>
+  </si>
+  <si>
+    <t>6a0335fc8046ce4dbfb9685d</t>
+  </si>
+  <si>
+    <t>6a0352128046ce4dbfb96c92</t>
+  </si>
+  <si>
+    <t>6a0352128046ce4dbfb96c93</t>
+  </si>
+  <si>
+    <t>6a037a8e8046ce4dbfb9701d</t>
+  </si>
+  <si>
+    <t>6a037e9b8046ce4dbfb9703c</t>
+  </si>
+  <si>
+    <t>6a0445e38046ce4dbfb979cf</t>
+  </si>
+  <si>
+    <t>1449-537887</t>
+  </si>
+  <si>
+    <t>1449-984634</t>
+  </si>
+  <si>
+    <t>1449-792430</t>
+  </si>
+  <si>
+    <t>26MPE0005027/1</t>
+  </si>
+  <si>
+    <t>308467177/1</t>
+  </si>
+  <si>
+    <t>309941263/1</t>
+  </si>
+  <si>
+    <t>309941263/2</t>
+  </si>
+  <si>
+    <t>309941263/3</t>
+  </si>
+  <si>
+    <t>310572499/1</t>
+  </si>
+  <si>
+    <t>310620987/1</t>
+  </si>
+  <si>
+    <t>310673390/1</t>
+  </si>
+  <si>
+    <t>310715759/1</t>
+  </si>
+  <si>
+    <t>310715759/2</t>
+  </si>
+  <si>
+    <t>310715759/3</t>
+  </si>
+  <si>
+    <t>310850167/1</t>
+  </si>
+  <si>
+    <t>310850167/2</t>
+  </si>
+  <si>
+    <t>310850440/1</t>
+  </si>
+  <si>
+    <t>310850440/2</t>
+  </si>
+  <si>
+    <t>310905102/1</t>
+  </si>
+  <si>
+    <t>310968991/1</t>
+  </si>
+  <si>
+    <t>310968991/2</t>
+  </si>
+  <si>
+    <t>310969648/1</t>
+  </si>
+  <si>
+    <t>310969648/2</t>
+  </si>
+  <si>
+    <t>311038062/1</t>
+  </si>
+  <si>
+    <t>311038062/2</t>
+  </si>
+  <si>
+    <t>311038315/1</t>
+  </si>
+  <si>
+    <t>311038402/1</t>
+  </si>
+  <si>
+    <t>311038614/1</t>
+  </si>
+  <si>
+    <t>311038614/2</t>
+  </si>
+  <si>
+    <t>311102914/1</t>
+  </si>
+  <si>
+    <t>311103728/1</t>
+  </si>
+  <si>
+    <t>311177290/1</t>
+  </si>
+  <si>
+    <t>311245243/1</t>
+  </si>
+  <si>
+    <t>311245384/1</t>
+  </si>
+  <si>
+    <t>311245729/1</t>
+  </si>
+  <si>
+    <t>311245874/1</t>
+  </si>
+  <si>
+    <t>311246018/1</t>
+  </si>
+  <si>
+    <t>311246120/1</t>
+  </si>
+  <si>
+    <t>311288331/1</t>
+  </si>
+  <si>
+    <t>311288348/1</t>
+  </si>
+  <si>
+    <t>311288515/1</t>
+  </si>
+  <si>
+    <t>311288814/1</t>
+  </si>
+  <si>
+    <t>311288869/1</t>
+  </si>
+  <si>
+    <t>311288989/1</t>
+  </si>
+  <si>
+    <t>311345247/1</t>
+  </si>
+  <si>
+    <t>311345329/1</t>
+  </si>
+  <si>
+    <t>311345413/1</t>
+  </si>
+  <si>
+    <t>311345437/1</t>
+  </si>
+  <si>
+    <t>311345677/1</t>
+  </si>
+  <si>
+    <t>311345805/1</t>
+  </si>
+  <si>
+    <t>311345861/1</t>
+  </si>
+  <si>
+    <t>311346044/1</t>
+  </si>
+  <si>
+    <t>311346044/2</t>
+  </si>
+  <si>
+    <t>311346127/1</t>
+  </si>
+  <si>
+    <t>311379041/1</t>
+  </si>
+  <si>
+    <t>311379873/1</t>
+  </si>
+  <si>
+    <t>311379873/2</t>
+  </si>
+  <si>
+    <t>311432006/1</t>
+  </si>
+  <si>
+    <t>311432036/1</t>
+  </si>
+  <si>
+    <t>311432044/1</t>
+  </si>
+  <si>
+    <t>311432044/2</t>
+  </si>
+  <si>
+    <t>311481861/1</t>
+  </si>
+  <si>
+    <t>311481927/1</t>
+  </si>
+  <si>
+    <t>311482305/1</t>
+  </si>
+  <si>
+    <t>311482375/1</t>
+  </si>
+  <si>
+    <t>311545539/1</t>
+  </si>
+  <si>
+    <t>311545539/2</t>
+  </si>
+  <si>
+    <t>311545677/1</t>
+  </si>
+  <si>
+    <t>311545677/2</t>
+  </si>
+  <si>
+    <t>311545767/1</t>
+  </si>
+  <si>
+    <t>311545788/1</t>
+  </si>
+  <si>
+    <t>311545990/1</t>
+  </si>
+  <si>
+    <t>311725390/1</t>
+  </si>
+  <si>
+    <t>311725390/2</t>
+  </si>
+  <si>
+    <t>99002514/1</t>
+  </si>
+  <si>
+    <t>202605132600974301</t>
+  </si>
+  <si>
+    <t>202605132601016901</t>
+  </si>
+  <si>
+    <t>202605132601016001</t>
+  </si>
+  <si>
+    <t>202605132601016002</t>
+  </si>
+  <si>
+    <t>202605132601016003</t>
+  </si>
+  <si>
+    <t>202605132601016004</t>
+  </si>
+  <si>
+    <t>202605072601016301</t>
+  </si>
+  <si>
+    <t>202605132601022701</t>
+  </si>
+  <si>
+    <t>202605082601019201</t>
+  </si>
+  <si>
+    <t>202605132601023301</t>
+  </si>
+  <si>
+    <t>202605112601029201</t>
+  </si>
+  <si>
+    <t>202605112601035901</t>
+  </si>
+  <si>
+    <t>202605122601052501</t>
+  </si>
+  <si>
+    <t>202605122601057801</t>
+  </si>
+  <si>
+    <t>202605122601052201</t>
+  </si>
+  <si>
+    <t>202605122601055601</t>
+  </si>
+  <si>
+    <t>202605132601065301</t>
+  </si>
+  <si>
+    <t>202605132601064001</t>
+  </si>
+  <si>
+    <t>202605132601061801</t>
+  </si>
+  <si>
+    <t>202605132601064501</t>
+  </si>
+  <si>
+    <t>202605132601059401</t>
+  </si>
+  <si>
+    <t>202605132601064901</t>
+  </si>
+  <si>
+    <t>202605132601066401</t>
+  </si>
+  <si>
+    <t>202605072600985501</t>
+  </si>
+  <si>
+    <t>202605132601018301</t>
+  </si>
+  <si>
+    <t>202605112601030201</t>
+  </si>
+  <si>
+    <t>202605132601066101</t>
+  </si>
+  <si>
+    <t>202605132601064401</t>
+  </si>
+  <si>
+    <t>202605132601059501</t>
+  </si>
+  <si>
+    <t>202605132601059801</t>
+  </si>
+  <si>
+    <t>202605132601064101</t>
+  </si>
+  <si>
+    <t>159995579540049397</t>
+  </si>
+  <si>
+    <t>159995579540049403</t>
+  </si>
+  <si>
+    <t>159995579540126906</t>
+  </si>
+  <si>
+    <t>159995579540126913</t>
+  </si>
+  <si>
+    <t>159995579540051253</t>
+  </si>
+  <si>
+    <t>159995579540051291</t>
+  </si>
+  <si>
+    <t>159995579540051307</t>
+  </si>
+  <si>
+    <t>159995579540051574</t>
+  </si>
+  <si>
+    <t>159995579540071459</t>
   </si>
 </sst>
 </file>
@@ -360,10 +1059,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -645,12 +1343,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
@@ -666,763 +1364,1895 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
+      <c r="A2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" t="s">
+        <v>162</v>
       </c>
       <c r="C2" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="B6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="B7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="C6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="B9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>4</v>
       </c>
-      <c r="C7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="B11" t="s">
+        <v>170</v>
+      </c>
+      <c r="C11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="C8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="B12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>11</v>
       </c>
-      <c r="C9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B14" t="s">
+        <v>173</v>
+      </c>
+      <c r="C14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>12</v>
       </c>
-      <c r="C10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="B15" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>175</v>
+      </c>
+      <c r="C16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>13</v>
       </c>
-      <c r="C11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="B17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>14</v>
       </c>
-      <c r="C12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B18" t="s">
+        <v>177</v>
+      </c>
+      <c r="C18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>15</v>
       </c>
-      <c r="C13" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B19" t="s">
+        <v>178</v>
+      </c>
+      <c r="C19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>16</v>
       </c>
-      <c r="C14" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>21</v>
+      <c r="B20" t="s">
+        <v>179</v>
       </c>
       <c r="C20" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>180</v>
+      </c>
+      <c r="C21" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
+        <v>181</v>
+      </c>
+      <c r="C22" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>182</v>
+      </c>
+      <c r="C23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>183</v>
+      </c>
+      <c r="C24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>185</v>
+      </c>
+      <c r="C26" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" t="s">
+        <v>186</v>
+      </c>
+      <c r="C27" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" t="s">
+        <v>187</v>
+      </c>
+      <c r="C28" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" t="s">
+        <v>189</v>
+      </c>
+      <c r="C30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>22</v>
       </c>
-      <c r="C21" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="B31" t="s">
+        <v>190</v>
+      </c>
+      <c r="C31" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>23</v>
       </c>
-      <c r="C22" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="B32" t="s">
+        <v>191</v>
+      </c>
+      <c r="C32" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>24</v>
       </c>
-      <c r="C23" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="B33" t="s">
+        <v>192</v>
+      </c>
+      <c r="C33" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" t="s">
+        <v>193</v>
+      </c>
+      <c r="C34" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>25</v>
       </c>
-      <c r="C24" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="B35" t="s">
+        <v>194</v>
+      </c>
+      <c r="C35" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>26</v>
       </c>
-      <c r="C25" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>37</v>
+      <c r="B36" t="s">
+        <v>195</v>
       </c>
       <c r="C36" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>38</v>
+      <c r="A37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" t="s">
+        <v>196</v>
       </c>
       <c r="C37" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>39</v>
+      <c r="A38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" t="s">
+        <v>197</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>40</v>
+      <c r="A39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" t="s">
+        <v>198</v>
       </c>
       <c r="C39" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>41</v>
+      <c r="A40" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" t="s">
+        <v>199</v>
       </c>
       <c r="C40" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>42</v>
+      <c r="A41" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" t="s">
+        <v>200</v>
       </c>
       <c r="C41" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>43</v>
+      <c r="A42" t="s">
+        <v>31</v>
+      </c>
+      <c r="B42" t="s">
+        <v>201</v>
       </c>
       <c r="C42" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>44</v>
+      <c r="A43" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" t="s">
+        <v>202</v>
       </c>
       <c r="C43" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>45</v>
+      <c r="A44" t="s">
+        <v>33</v>
+      </c>
+      <c r="B44" t="s">
+        <v>203</v>
       </c>
       <c r="C44" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>46</v>
+      <c r="A45" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45" t="s">
+        <v>204</v>
       </c>
       <c r="C45" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>47</v>
+      <c r="A46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" t="s">
+        <v>205</v>
       </c>
       <c r="C46" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>48</v>
+      <c r="A47" t="s">
+        <v>34</v>
+      </c>
+      <c r="B47" t="s">
+        <v>206</v>
       </c>
       <c r="C47" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>49</v>
+      <c r="A48" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" t="s">
+        <v>207</v>
       </c>
       <c r="C48" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+      <c r="A49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B49" t="s">
+        <v>208</v>
+      </c>
+      <c r="C49" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" t="s">
+        <v>209</v>
+      </c>
+      <c r="C50" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" t="s">
+        <v>210</v>
+      </c>
+      <c r="C51" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>39</v>
+      </c>
+      <c r="B52" t="s">
+        <v>211</v>
+      </c>
+      <c r="C52" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" t="s">
+        <v>212</v>
+      </c>
+      <c r="C53" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" t="s">
+        <v>213</v>
+      </c>
+      <c r="C54" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" t="s">
+        <v>214</v>
+      </c>
+      <c r="C55" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" t="s">
+        <v>215</v>
+      </c>
+      <c r="C56" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" t="s">
+        <v>216</v>
+      </c>
+      <c r="C57" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>122</v>
+      </c>
+      <c r="B58" t="s">
+        <v>217</v>
+      </c>
+      <c r="C58" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>123</v>
+      </c>
+      <c r="B59" t="s">
+        <v>218</v>
+      </c>
+      <c r="C59" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>124</v>
+      </c>
+      <c r="B60" t="s">
+        <v>219</v>
+      </c>
+      <c r="C60" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>125</v>
+      </c>
+      <c r="B61" t="s">
+        <v>220</v>
+      </c>
+      <c r="C61" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" t="s">
+        <v>221</v>
+      </c>
+      <c r="C62" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" t="s">
+        <v>222</v>
+      </c>
+      <c r="C63" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>45</v>
+      </c>
+      <c r="B64" t="s">
+        <v>223</v>
+      </c>
+      <c r="C64" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>45</v>
+      </c>
+      <c r="B65" t="s">
+        <v>224</v>
+      </c>
+      <c r="C65" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>46</v>
+      </c>
+      <c r="B66" t="s">
+        <v>225</v>
+      </c>
+      <c r="C66" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>47</v>
+      </c>
+      <c r="B67" t="s">
+        <v>226</v>
+      </c>
+      <c r="C67" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>48</v>
+      </c>
+      <c r="B68" t="s">
+        <v>227</v>
+      </c>
+      <c r="C68" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>49</v>
+      </c>
+      <c r="B69" t="s">
+        <v>228</v>
+      </c>
+      <c r="C69" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>49</v>
+      </c>
+      <c r="B70" t="s">
+        <v>229</v>
+      </c>
+      <c r="C70" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>49</v>
+      </c>
+      <c r="B71" t="s">
+        <v>230</v>
+      </c>
+      <c r="C71" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>50</v>
       </c>
-      <c r="C49" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+      <c r="B72" t="s">
+        <v>231</v>
+      </c>
+      <c r="C72" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>50</v>
+      </c>
+      <c r="B73" t="s">
+        <v>232</v>
+      </c>
+      <c r="C73" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>51</v>
       </c>
-      <c r="C50" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
+      <c r="B74" t="s">
+        <v>233</v>
+      </c>
+      <c r="C74" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>51</v>
+      </c>
+      <c r="B75" t="s">
+        <v>234</v>
+      </c>
+      <c r="C75" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>52</v>
       </c>
-      <c r="C51" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+      <c r="B76" t="s">
+        <v>235</v>
+      </c>
+      <c r="C76" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>53</v>
       </c>
-      <c r="C52" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
+      <c r="B77" t="s">
+        <v>236</v>
+      </c>
+      <c r="C77" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>53</v>
+      </c>
+      <c r="B78" t="s">
+        <v>237</v>
+      </c>
+      <c r="C78" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>54</v>
       </c>
-      <c r="C53" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C55" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C58" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C59" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C61" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C62" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C63" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C64" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C65" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C66" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C67" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C68" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C69" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C70" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C71" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C72" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C73" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C74" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C75" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C76" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C77" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C78" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>80</v>
+      <c r="B79" t="s">
+        <v>238</v>
       </c>
       <c r="C79" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>81</v>
+      <c r="A80" t="s">
+        <v>54</v>
+      </c>
+      <c r="B80" t="s">
+        <v>239</v>
       </c>
       <c r="C80" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
+      <c r="A81" t="s">
+        <v>55</v>
+      </c>
+      <c r="B81" t="s">
+        <v>240</v>
+      </c>
+      <c r="C81" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>55</v>
+      </c>
+      <c r="B82" t="s">
+        <v>241</v>
+      </c>
+      <c r="C82" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>56</v>
+      </c>
+      <c r="B83" t="s">
+        <v>242</v>
+      </c>
+      <c r="C83" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>57</v>
+      </c>
+      <c r="B84" t="s">
+        <v>243</v>
+      </c>
+      <c r="C84" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>58</v>
+      </c>
+      <c r="B85" t="s">
+        <v>244</v>
+      </c>
+      <c r="C85" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>58</v>
+      </c>
+      <c r="B86" t="s">
+        <v>245</v>
+      </c>
+      <c r="C86" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>59</v>
+      </c>
+      <c r="B87" t="s">
+        <v>246</v>
+      </c>
+      <c r="C87" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>60</v>
+      </c>
+      <c r="B88" t="s">
+        <v>247</v>
+      </c>
+      <c r="C88" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>61</v>
+      </c>
+      <c r="B89" t="s">
+        <v>248</v>
+      </c>
+      <c r="C89" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>62</v>
+      </c>
+      <c r="B90" t="s">
+        <v>249</v>
+      </c>
+      <c r="C90" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>63</v>
+      </c>
+      <c r="B91" t="s">
+        <v>250</v>
+      </c>
+      <c r="C91" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>64</v>
+      </c>
+      <c r="B92" t="s">
+        <v>251</v>
+      </c>
+      <c r="C92" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>65</v>
+      </c>
+      <c r="B93" t="s">
+        <v>252</v>
+      </c>
+      <c r="C93" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>66</v>
+      </c>
+      <c r="B94" t="s">
+        <v>253</v>
+      </c>
+      <c r="C94" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>67</v>
+      </c>
+      <c r="B95" t="s">
+        <v>254</v>
+      </c>
+      <c r="C95" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>68</v>
+      </c>
+      <c r="B96" t="s">
+        <v>255</v>
+      </c>
+      <c r="C96" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>69</v>
+      </c>
+      <c r="B97" t="s">
+        <v>256</v>
+      </c>
+      <c r="C97" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>70</v>
+      </c>
+      <c r="B98" t="s">
+        <v>257</v>
+      </c>
+      <c r="C98" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>71</v>
+      </c>
+      <c r="B99" t="s">
+        <v>258</v>
+      </c>
+      <c r="C99" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>72</v>
+      </c>
+      <c r="B100" t="s">
+        <v>259</v>
+      </c>
+      <c r="C100" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>73</v>
+      </c>
+      <c r="B101" t="s">
+        <v>260</v>
+      </c>
+      <c r="C101" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>74</v>
+      </c>
+      <c r="B102" t="s">
+        <v>261</v>
+      </c>
+      <c r="C102" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>75</v>
+      </c>
+      <c r="B103" t="s">
+        <v>262</v>
+      </c>
+      <c r="C103" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>76</v>
+      </c>
+      <c r="B104" t="s">
+        <v>263</v>
+      </c>
+      <c r="C104" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>77</v>
+      </c>
+      <c r="B105" t="s">
+        <v>264</v>
+      </c>
+      <c r="C105" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>78</v>
+      </c>
+      <c r="B106" t="s">
+        <v>265</v>
+      </c>
+      <c r="C106" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>79</v>
+      </c>
+      <c r="B107" t="s">
+        <v>266</v>
+      </c>
+      <c r="C107" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>80</v>
+      </c>
+      <c r="B108" t="s">
+        <v>267</v>
+      </c>
+      <c r="C108" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>81</v>
+      </c>
+      <c r="B109" t="s">
+        <v>268</v>
+      </c>
+      <c r="C109" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>81</v>
+      </c>
+      <c r="B110" t="s">
+        <v>269</v>
+      </c>
+      <c r="C110" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
         <v>82</v>
       </c>
-      <c r="C81" t="s">
+      <c r="B111" t="s">
+        <v>270</v>
+      </c>
+      <c r="C111" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>83</v>
+      </c>
+      <c r="B112" t="s">
+        <v>271</v>
+      </c>
+      <c r="C112" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>84</v>
+      </c>
+      <c r="B113" t="s">
+        <v>272</v>
+      </c>
+      <c r="C113" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>84</v>
+      </c>
+      <c r="B114" t="s">
+        <v>273</v>
+      </c>
+      <c r="C114" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>85</v>
+      </c>
+      <c r="B115" t="s">
+        <v>274</v>
+      </c>
+      <c r="C115" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>86</v>
+      </c>
+      <c r="B116" t="s">
+        <v>275</v>
+      </c>
+      <c r="C116" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>87</v>
+      </c>
+      <c r="B117" t="s">
+        <v>276</v>
+      </c>
+      <c r="C117" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>87</v>
+      </c>
+      <c r="B118" t="s">
+        <v>277</v>
+      </c>
+      <c r="C118" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>88</v>
+      </c>
+      <c r="B119" t="s">
+        <v>278</v>
+      </c>
+      <c r="C119" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>89</v>
+      </c>
+      <c r="B120" t="s">
+        <v>279</v>
+      </c>
+      <c r="C120" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>90</v>
+      </c>
+      <c r="B121" t="s">
+        <v>280</v>
+      </c>
+      <c r="C121" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>91</v>
+      </c>
+      <c r="B122" t="s">
+        <v>281</v>
+      </c>
+      <c r="C122" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>92</v>
+      </c>
+      <c r="B123" t="s">
+        <v>282</v>
+      </c>
+      <c r="C123" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>92</v>
+      </c>
+      <c r="B124" t="s">
+        <v>283</v>
+      </c>
+      <c r="C124" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>93</v>
+      </c>
+      <c r="B125" t="s">
+        <v>284</v>
+      </c>
+      <c r="C125" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>93</v>
+      </c>
+      <c r="B126" t="s">
+        <v>285</v>
+      </c>
+      <c r="C126" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>94</v>
+      </c>
+      <c r="B127" t="s">
+        <v>286</v>
+      </c>
+      <c r="C127" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>95</v>
+      </c>
+      <c r="B128" t="s">
+        <v>287</v>
+      </c>
+      <c r="C128" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>96</v>
+      </c>
+      <c r="B129" t="s">
+        <v>288</v>
+      </c>
+      <c r="C129" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>126</v>
+      </c>
+      <c r="B130" t="s">
+        <v>289</v>
+      </c>
+      <c r="C130" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>126</v>
+      </c>
+      <c r="B131" t="s">
+        <v>290</v>
+      </c>
+      <c r="C131" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>97</v>
+      </c>
+      <c r="B132" t="s">
+        <v>291</v>
+      </c>
+      <c r="C132" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>127</v>
+      </c>
+      <c r="B133" t="s">
+        <v>292</v>
+      </c>
+      <c r="C133" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>128</v>
+      </c>
+      <c r="B134" t="s">
+        <v>293</v>
+      </c>
+      <c r="C134" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>129</v>
+      </c>
+      <c r="B135" t="s">
+        <v>294</v>
+      </c>
+      <c r="C135" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>129</v>
+      </c>
+      <c r="B136" t="s">
+        <v>295</v>
+      </c>
+      <c r="C136" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>129</v>
+      </c>
+      <c r="B137" t="s">
+        <v>296</v>
+      </c>
+      <c r="C137" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>129</v>
+      </c>
+      <c r="B138" t="s">
+        <v>297</v>
+      </c>
+      <c r="C138" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>130</v>
+      </c>
+      <c r="B139" t="s">
+        <v>298</v>
+      </c>
+      <c r="C139" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>131</v>
+      </c>
+      <c r="B140" t="s">
+        <v>299</v>
+      </c>
+      <c r="C140" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>132</v>
+      </c>
+      <c r="B141" t="s">
+        <v>300</v>
+      </c>
+      <c r="C141" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C82" t="s">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>133</v>
+      </c>
+      <c r="B142" t="s">
+        <v>301</v>
+      </c>
+      <c r="C142" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>134</v>
+      </c>
+      <c r="B143" t="s">
+        <v>302</v>
+      </c>
+      <c r="C143" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>135</v>
+      </c>
+      <c r="B144" t="s">
+        <v>303</v>
+      </c>
+      <c r="C144" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>136</v>
+      </c>
+      <c r="B145" t="s">
+        <v>304</v>
+      </c>
+      <c r="C145" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>137</v>
+      </c>
+      <c r="B146" t="s">
+        <v>305</v>
+      </c>
+      <c r="C146" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>138</v>
+      </c>
+      <c r="B147" t="s">
+        <v>306</v>
+      </c>
+      <c r="C147" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C83" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C84" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C85" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C86" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C87" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C88" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C89" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C90" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C91" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C92" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C93" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C94" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C95" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C96" t="s">
-        <v>98</v>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>139</v>
+      </c>
+      <c r="B148" t="s">
+        <v>307</v>
+      </c>
+      <c r="C148" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>140</v>
+      </c>
+      <c r="B149" t="s">
+        <v>308</v>
+      </c>
+      <c r="C149" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>141</v>
+      </c>
+      <c r="B150" t="s">
+        <v>309</v>
+      </c>
+      <c r="C150" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>142</v>
+      </c>
+      <c r="B151" t="s">
+        <v>310</v>
+      </c>
+      <c r="C151" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>143</v>
+      </c>
+      <c r="B152" t="s">
+        <v>311</v>
+      </c>
+      <c r="C152" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>144</v>
+      </c>
+      <c r="B153" t="s">
+        <v>312</v>
+      </c>
+      <c r="C153" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>145</v>
+      </c>
+      <c r="B154" t="s">
+        <v>313</v>
+      </c>
+      <c r="C154" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>146</v>
+      </c>
+      <c r="B155" t="s">
+        <v>314</v>
+      </c>
+      <c r="C155" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>147</v>
+      </c>
+      <c r="B156" t="s">
+        <v>315</v>
+      </c>
+      <c r="C156" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>148</v>
+      </c>
+      <c r="B157" t="s">
+        <v>316</v>
+      </c>
+      <c r="C157" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>149</v>
+      </c>
+      <c r="B158" t="s">
+        <v>317</v>
+      </c>
+      <c r="C158" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>150</v>
+      </c>
+      <c r="B159" t="s">
+        <v>318</v>
+      </c>
+      <c r="C159" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>151</v>
+      </c>
+      <c r="B160" t="s">
+        <v>319</v>
+      </c>
+      <c r="C160" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>152</v>
+      </c>
+      <c r="B161" t="s">
+        <v>320</v>
+      </c>
+      <c r="C161" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>153</v>
+      </c>
+      <c r="B162" t="s">
+        <v>321</v>
+      </c>
+      <c r="C162" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>154</v>
+      </c>
+      <c r="B163" t="s">
+        <v>322</v>
+      </c>
+      <c r="C163" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>155</v>
+      </c>
+      <c r="B164" t="s">
+        <v>323</v>
+      </c>
+      <c r="C164" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>155</v>
+      </c>
+      <c r="B165" t="s">
+        <v>324</v>
+      </c>
+      <c r="C165" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>156</v>
+      </c>
+      <c r="B166" t="s">
+        <v>325</v>
+      </c>
+      <c r="C166" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>156</v>
+      </c>
+      <c r="B167" t="s">
+        <v>326</v>
+      </c>
+      <c r="C167" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>157</v>
+      </c>
+      <c r="B168" t="s">
+        <v>327</v>
+      </c>
+      <c r="C168" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>158</v>
+      </c>
+      <c r="B169" t="s">
+        <v>328</v>
+      </c>
+      <c r="C169" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>158</v>
+      </c>
+      <c r="B170" t="s">
+        <v>329</v>
+      </c>
+      <c r="C170" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>159</v>
+      </c>
+      <c r="B171" t="s">
+        <v>330</v>
+      </c>
+      <c r="C171" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>160</v>
+      </c>
+      <c r="B172" t="s">
+        <v>331</v>
+      </c>
+      <c r="C172" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>161</v>
+      </c>
+      <c r="B173" t="s">
+        <v>161</v>
+      </c>
+      <c r="C173" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACB8832-B329-4317-8DF2-CC5649AA89E4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADDEAF71-0A31-4AAA-8D42-1EF9D70F75C2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="825">
   <si>
     <t>UTK</t>
   </si>
@@ -132,9 +132,6 @@
     <t>260514-F00003736</t>
   </si>
   <si>
-    <t>260514-F00004739</t>
-  </si>
-  <si>
     <t>260514-W00003470</t>
   </si>
   <si>
@@ -363,7 +360,2149 @@
     <t>99002504</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>K-941</t>
+  </si>
+  <si>
+    <t>K-951</t>
+  </si>
+  <si>
+    <t>K-961</t>
+  </si>
+  <si>
+    <t>SZ-870</t>
+  </si>
+  <si>
+    <t>K-922</t>
+  </si>
+  <si>
+    <t>K-999</t>
+  </si>
+  <si>
+    <t>K-943</t>
+  </si>
+  <si>
+    <t>K-972</t>
+  </si>
+  <si>
+    <t>K-929</t>
+  </si>
+  <si>
+    <t>K-902</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>K-942</t>
+  </si>
+  <si>
+    <t>K-983</t>
+  </si>
+  <si>
+    <t>K-921</t>
+  </si>
+  <si>
+    <t>K-910</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>K-931</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>K-930</t>
+  </si>
+  <si>
+    <t>K-915</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>K-952</t>
+  </si>
+  <si>
+    <t>K-920</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>K-918</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>K-971</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>K-9111</t>
+  </si>
+  <si>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>K-982</t>
+  </si>
+  <si>
+    <t>SZ-827</t>
+  </si>
+  <si>
+    <t>K-912</t>
+  </si>
+  <si>
+    <t>K-998</t>
+  </si>
+  <si>
+    <t>K-906</t>
+  </si>
+  <si>
+    <t>K-962</t>
+  </si>
+  <si>
+    <t>K-932</t>
+  </si>
+  <si>
+    <t>K-981</t>
+  </si>
+  <si>
+    <t>K-9110</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-860</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-854</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-8101</t>
+  </si>
+  <si>
+    <t>1-4035/2026</t>
+  </si>
+  <si>
+    <t>2026/06243</t>
+  </si>
+  <si>
+    <t>2026/06288</t>
+  </si>
+  <si>
+    <t>260410-F00010165</t>
+  </si>
+  <si>
+    <t>260414-F00007518</t>
+  </si>
+  <si>
+    <t>260415-F00010647</t>
+  </si>
+  <si>
+    <t>260423-F00014796</t>
+  </si>
+  <si>
+    <t>260425-W00003442</t>
+  </si>
+  <si>
+    <t>260428-F00012773</t>
+  </si>
+  <si>
+    <t>260430-F00001938</t>
+  </si>
+  <si>
+    <t>260504-F00009809</t>
+  </si>
+  <si>
+    <t>260505-F00007003</t>
+  </si>
+  <si>
+    <t>260505-F00007281</t>
+  </si>
+  <si>
+    <t>260505-W00012988</t>
+  </si>
+  <si>
+    <t>260506-F00000863</t>
+  </si>
+  <si>
+    <t>260506-F00007454</t>
+  </si>
+  <si>
+    <t>260506-F00009853</t>
+  </si>
+  <si>
+    <t>260506-W00004651</t>
+  </si>
+  <si>
+    <t>260506-W00007529</t>
+  </si>
+  <si>
+    <t>260506-W00007634</t>
+  </si>
+  <si>
+    <t>260507-F00005354</t>
+  </si>
+  <si>
+    <t>260507-F00006122-1</t>
+  </si>
+  <si>
+    <t>260507-F00011398</t>
+  </si>
+  <si>
+    <t>260507-W00004542</t>
+  </si>
+  <si>
+    <t>260507-W00011904</t>
+  </si>
+  <si>
+    <t>260508-F00001222</t>
+  </si>
+  <si>
+    <t>260508-F00006338</t>
+  </si>
+  <si>
+    <t>260508-F00008962</t>
+  </si>
+  <si>
+    <t>260508-F00010454</t>
+  </si>
+  <si>
+    <t>260508-W00003156</t>
+  </si>
+  <si>
+    <t>260508-W00006809</t>
+  </si>
+  <si>
+    <t>260508-W00007433</t>
+  </si>
+  <si>
+    <t>260508-W00007900</t>
+  </si>
+  <si>
+    <t>260509-F00004374</t>
+  </si>
+  <si>
+    <t>260509-W00003182</t>
+  </si>
+  <si>
+    <t>260509-W00005160</t>
+  </si>
+  <si>
+    <t>260510-F00000284</t>
+  </si>
+  <si>
+    <t>260510-W00004707</t>
+  </si>
+  <si>
+    <t>260510-W00008770</t>
+  </si>
+  <si>
+    <t>260511-F00003475</t>
+  </si>
+  <si>
+    <t>260511-F00007279</t>
+  </si>
+  <si>
+    <t>260511-F00008598</t>
+  </si>
+  <si>
+    <t>260511-F00011931-2</t>
+  </si>
+  <si>
+    <t>260511-F00012081</t>
+  </si>
+  <si>
+    <t>260511-F00013109</t>
+  </si>
+  <si>
+    <t>260511-F00014214</t>
+  </si>
+  <si>
+    <t>260511-W00006487</t>
+  </si>
+  <si>
+    <t>260511-W00008068</t>
+  </si>
+  <si>
+    <t>260511-W00008075</t>
+  </si>
+  <si>
+    <t>260511-W00010227</t>
+  </si>
+  <si>
+    <t>260511-W00011505</t>
+  </si>
+  <si>
+    <t>260512-F00002537</t>
+  </si>
+  <si>
+    <t>260512-F00003779</t>
+  </si>
+  <si>
+    <t>260512-F00004405</t>
+  </si>
+  <si>
+    <t>260512-F00006041</t>
+  </si>
+  <si>
+    <t>260512-F00007800</t>
+  </si>
+  <si>
+    <t>260512-F00008981</t>
+  </si>
+  <si>
+    <t>260512-F00010609</t>
+  </si>
+  <si>
+    <t>260512-F00010759</t>
+  </si>
+  <si>
+    <t>260512-F00012176</t>
+  </si>
+  <si>
+    <t>260512-F00013843</t>
+  </si>
+  <si>
+    <t>260512-F00014087</t>
+  </si>
+  <si>
+    <t>260512-F00014388</t>
+  </si>
+  <si>
+    <t>260512-F00014525</t>
+  </si>
+  <si>
+    <t>260512-F00014607</t>
+  </si>
+  <si>
+    <t>260512-F00014833</t>
+  </si>
+  <si>
+    <t>260512-F00014896</t>
+  </si>
+  <si>
+    <t>260512-F00015298</t>
+  </si>
+  <si>
+    <t>260512-F00015541</t>
+  </si>
+  <si>
+    <t>260512-F00015812</t>
+  </si>
+  <si>
+    <t>260512-W00006149</t>
+  </si>
+  <si>
+    <t>260512-W00006681</t>
+  </si>
+  <si>
+    <t>260512-W00007259</t>
+  </si>
+  <si>
+    <t>260512-W00007377</t>
+  </si>
+  <si>
+    <t>260512-W00007573</t>
+  </si>
+  <si>
+    <t>260512-W00007645</t>
+  </si>
+  <si>
+    <t>260512-W00007735</t>
+  </si>
+  <si>
+    <t>260512-W00008581</t>
+  </si>
+  <si>
+    <t>260512-W00008968</t>
+  </si>
+  <si>
+    <t>260512-W00008984</t>
+  </si>
+  <si>
+    <t>260512-W00009224</t>
+  </si>
+  <si>
+    <t>260512-W00009628</t>
+  </si>
+  <si>
+    <t>260512-W00009815</t>
+  </si>
+  <si>
+    <t>260512-W00010278</t>
+  </si>
+  <si>
+    <t>260512-W00010986</t>
+  </si>
+  <si>
+    <t>260512-W00011514</t>
+  </si>
+  <si>
+    <t>260513-F00000763</t>
+  </si>
+  <si>
+    <t>260513-F00001060</t>
+  </si>
+  <si>
+    <t>260513-F00001226</t>
+  </si>
+  <si>
+    <t>260513-F00001640</t>
+  </si>
+  <si>
+    <t>260513-F00002073</t>
+  </si>
+  <si>
+    <t>260513-F00002178</t>
+  </si>
+  <si>
+    <t>260513-F00002461-1</t>
+  </si>
+  <si>
+    <t>260513-F00002758</t>
+  </si>
+  <si>
+    <t>260513-F00002768</t>
+  </si>
+  <si>
+    <t>260513-F00003039</t>
+  </si>
+  <si>
+    <t>260513-F00004103</t>
+  </si>
+  <si>
+    <t>260513-F00004648</t>
+  </si>
+  <si>
+    <t>260513-F00005466</t>
+  </si>
+  <si>
+    <t>260513-F00005812</t>
+  </si>
+  <si>
+    <t>260513-F00005844</t>
+  </si>
+  <si>
+    <t>260513-F00007061</t>
+  </si>
+  <si>
+    <t>260513-F00007088</t>
+  </si>
+  <si>
+    <t>260513-F00008082</t>
+  </si>
+  <si>
+    <t>260513-F00009093</t>
+  </si>
+  <si>
+    <t>260513-F00012088</t>
+  </si>
+  <si>
+    <t>260513-F00012172</t>
+  </si>
+  <si>
+    <t>260513-F00012435</t>
+  </si>
+  <si>
+    <t>260513-F00013206</t>
+  </si>
+  <si>
+    <t>260513-F00013360</t>
+  </si>
+  <si>
+    <t>260513-F00014748</t>
+  </si>
+  <si>
+    <t>260513-F00014821</t>
+  </si>
+  <si>
+    <t>260513-F00015493</t>
+  </si>
+  <si>
+    <t>260513-F00015943</t>
+  </si>
+  <si>
+    <t>260513-W00000006</t>
+  </si>
+  <si>
+    <t>260513-W00000115</t>
+  </si>
+  <si>
+    <t>260513-W00000614</t>
+  </si>
+  <si>
+    <t>260513-W00001235</t>
+  </si>
+  <si>
+    <t>260513-W00001733</t>
+  </si>
+  <si>
+    <t>260513-W00001809</t>
+  </si>
+  <si>
+    <t>260513-W00003136</t>
+  </si>
+  <si>
+    <t>260513-W00003411</t>
+  </si>
+  <si>
+    <t>260513-W00003592</t>
+  </si>
+  <si>
+    <t>260513-W00003861</t>
+  </si>
+  <si>
+    <t>260513-W00004588</t>
+  </si>
+  <si>
+    <t>260513-W00005656</t>
+  </si>
+  <si>
+    <t>260513-W00006856</t>
+  </si>
+  <si>
+    <t>260513-W00007027</t>
+  </si>
+  <si>
+    <t>260513-W00007031</t>
+  </si>
+  <si>
+    <t>260513-W00007203</t>
+  </si>
+  <si>
+    <t>260513-W00007513</t>
+  </si>
+  <si>
+    <t>260513-W00008505</t>
+  </si>
+  <si>
+    <t>260513-W00008535</t>
+  </si>
+  <si>
+    <t>260513-W00009314</t>
+  </si>
+  <si>
+    <t>260513-W00010085</t>
+  </si>
+  <si>
+    <t>260513-W00010748</t>
+  </si>
+  <si>
+    <t>260513-W00012122</t>
+  </si>
+  <si>
+    <t>260513-W00013583</t>
+  </si>
+  <si>
+    <t>260514-F00002198</t>
+  </si>
+  <si>
+    <t>260514-F00002301</t>
+  </si>
+  <si>
+    <t>260514-F00002616</t>
+  </si>
+  <si>
+    <t>260514-F00004737</t>
+  </si>
+  <si>
+    <t>260514-F00004881</t>
+  </si>
+  <si>
+    <t>260514-F00005021</t>
+  </si>
+  <si>
+    <t>260514-F00005299</t>
+  </si>
+  <si>
+    <t>260514-F00005447</t>
+  </si>
+  <si>
+    <t>260514-F00005692</t>
+  </si>
+  <si>
+    <t>260514-F00006912</t>
+  </si>
+  <si>
+    <t>260514-F00007478</t>
+  </si>
+  <si>
+    <t>260514-W00002878</t>
+  </si>
+  <si>
+    <t>260514-W00003251</t>
+  </si>
+  <si>
+    <t>260514-W00003724</t>
+  </si>
+  <si>
+    <t>260514-W00003969</t>
+  </si>
+  <si>
+    <t>260514-W00004312</t>
+  </si>
+  <si>
+    <t>260514-W00004606</t>
+  </si>
+  <si>
+    <t>260514-W00004890</t>
+  </si>
+  <si>
+    <t>260514-W00004892</t>
+  </si>
+  <si>
+    <t>260514-W00005411</t>
+  </si>
+  <si>
+    <t>267007058</t>
+  </si>
+  <si>
+    <t>267007087</t>
+  </si>
+  <si>
+    <t>267007098</t>
+  </si>
+  <si>
+    <t>267007105</t>
+  </si>
+  <si>
+    <t>26MPE0005083</t>
+  </si>
+  <si>
+    <t>26MPE0005127</t>
+  </si>
+  <si>
+    <t>26MPE0005129</t>
+  </si>
+  <si>
+    <t>26MPE0005178</t>
+  </si>
+  <si>
+    <t>308544508</t>
+  </si>
+  <si>
+    <t>309999931</t>
+  </si>
+  <si>
+    <t>310850736</t>
+  </si>
+  <si>
+    <t>311346022</t>
+  </si>
+  <si>
+    <t>311545884</t>
+  </si>
+  <si>
+    <t>311545996</t>
+  </si>
+  <si>
+    <t>311546258</t>
+  </si>
+  <si>
+    <t>311546426</t>
+  </si>
+  <si>
+    <t>311605545</t>
+  </si>
+  <si>
+    <t>311725703</t>
+  </si>
+  <si>
+    <t>311725762</t>
+  </si>
+  <si>
+    <t>311725844</t>
+  </si>
+  <si>
+    <t>311725943</t>
+  </si>
+  <si>
+    <t>311726028</t>
+  </si>
+  <si>
+    <t>311777717</t>
+  </si>
+  <si>
+    <t>311777832</t>
+  </si>
+  <si>
+    <t>311777888</t>
+  </si>
+  <si>
+    <t>311777923</t>
+  </si>
+  <si>
+    <t>311777992</t>
+  </si>
+  <si>
+    <t>311778004</t>
+  </si>
+  <si>
+    <t>311861914</t>
+  </si>
+  <si>
+    <t>311861996</t>
+  </si>
+  <si>
+    <t>311862060</t>
+  </si>
+  <si>
+    <t>NFD6-05-07-P58A</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-FZSS</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-K6E6</t>
+  </si>
+  <si>
+    <t>NFD6-05-11-MZD4</t>
+  </si>
+  <si>
+    <t>NFD6-05-12-29Z3</t>
+  </si>
+  <si>
+    <t>NFD6-05-12-2Y2Q</t>
+  </si>
+  <si>
+    <t>NFD6-05-12-373F</t>
+  </si>
+  <si>
+    <t>NFD6-05-12-73JR</t>
+  </si>
+  <si>
+    <t>NFD6-05-12-D4U6</t>
+  </si>
+  <si>
+    <t>NFD6-05-13-2FTX</t>
+  </si>
+  <si>
+    <t>NFD6-05-13-4SUQ</t>
+  </si>
+  <si>
+    <t>NFD6-05-13-5PN8</t>
+  </si>
+  <si>
+    <t>NFD6-05-13-8LAL</t>
+  </si>
+  <si>
+    <t>NFD6-05-13-AALG</t>
+  </si>
+  <si>
+    <t>NFD6-05-13-ABAN</t>
+  </si>
+  <si>
+    <t>NFD6-05-13-CR3V</t>
+  </si>
+  <si>
+    <t>NFD6-05-13-DSXQ</t>
+  </si>
+  <si>
+    <t>NFD6-05-13-LWXA</t>
+  </si>
+  <si>
+    <t>NFD6-05-13-QB5H</t>
+  </si>
+  <si>
+    <t>NFD6-05-13-U3EG</t>
+  </si>
+  <si>
+    <t>NFD6-05-13-XTPT</t>
+  </si>
+  <si>
+    <t>NFE6-05-01-LH54</t>
+  </si>
+  <si>
+    <t>NFE6-05-06-JEUV</t>
+  </si>
+  <si>
+    <t>NFE6-05-07-JU3R</t>
+  </si>
+  <si>
+    <t>NFE6-05-11-5FTT</t>
+  </si>
+  <si>
+    <t>NFE6-05-12-6FHK</t>
+  </si>
+  <si>
+    <t>NFE6-05-13-24DT</t>
+  </si>
+  <si>
+    <t>NFE6-05-13-2H87</t>
+  </si>
+  <si>
+    <t>NFE6-05-13-33YF</t>
+  </si>
+  <si>
+    <t>NFE6-05-13-3VK5</t>
+  </si>
+  <si>
+    <t>NFE6-05-13-3XPK</t>
+  </si>
+  <si>
+    <t>NFE6-05-13-6PQ6</t>
+  </si>
+  <si>
+    <t>NFE6-05-13-7TXB</t>
+  </si>
+  <si>
+    <t>NFE6-05-13-8UV7</t>
+  </si>
+  <si>
+    <t>NFE6-05-13-DLVG</t>
+  </si>
+  <si>
+    <t>NFE6-05-13-HWGT</t>
+  </si>
+  <si>
+    <t>NFE6-05-13-KECE</t>
+  </si>
+  <si>
+    <t>NFE6-05-13-MVSY</t>
+  </si>
+  <si>
+    <t>NFE6-05-13-NBB7</t>
+  </si>
+  <si>
+    <t>NFE6-05-13-RH4X</t>
+  </si>
+  <si>
+    <t>NFE6-05-13-ULXE</t>
+  </si>
+  <si>
+    <t>NFE6-05-13-WJD4</t>
+  </si>
+  <si>
+    <t>NFE6-05-13-XN9X</t>
+  </si>
+  <si>
+    <t>R417968</t>
+  </si>
+  <si>
+    <t>R420222</t>
+  </si>
+  <si>
+    <t>R420554</t>
+  </si>
+  <si>
+    <t>SA26/H002664</t>
+  </si>
+  <si>
+    <t>SZL00112/2026</t>
+  </si>
+  <si>
+    <t>NFD6-04-22-W7XY</t>
+  </si>
+  <si>
+    <t>159995579540177113</t>
+  </si>
+  <si>
+    <t>159995579540220000</t>
+  </si>
+  <si>
+    <t>248745805/1</t>
+  </si>
+  <si>
+    <t>248745805/2</t>
+  </si>
+  <si>
+    <t>6a05abbe8046ce4dbfb9991b</t>
+  </si>
+  <si>
+    <t>6a04631f8046ce4dbfb97f2f</t>
+  </si>
+  <si>
+    <t>6a04631f8046ce4dbfb97f30</t>
+  </si>
+  <si>
+    <t>69f1f7387d88c5c4ea84cb86</t>
+  </si>
+  <si>
+    <t>6a03357c8046ce4dbfb9682a</t>
+  </si>
+  <si>
+    <t>69ec9c705cef447acaba1011</t>
+  </si>
+  <si>
+    <t>6a0469ac8046ce4dbfb98051</t>
+  </si>
+  <si>
+    <t>6a0584408046ce4dbfb9910d</t>
+  </si>
+  <si>
+    <t>6a0584408046ce4dbfb9910e</t>
+  </si>
+  <si>
+    <t>69f4613047d1aed7c385fba6</t>
+  </si>
+  <si>
+    <t>69ff1f1d8046ce4dbfb92230</t>
+  </si>
+  <si>
+    <t>6a018b0e8046ce4dbfb937b5</t>
+  </si>
+  <si>
+    <t>69fd97388046ce4dbfb902e6</t>
+  </si>
+  <si>
+    <t>6a01c2848046ce4dbfb942d9</t>
+  </si>
+  <si>
+    <t>69fa5bb747d1aed7c3864673</t>
+  </si>
+  <si>
+    <t>6a01cefe8046ce4dbfb9456f</t>
+  </si>
+  <si>
+    <t>69fdc2658046ce4dbfb90ad1</t>
+  </si>
+  <si>
+    <t>69fdd75f8046ce4dbfb90e74</t>
+  </si>
+  <si>
+    <t>69fafafa47d1aed7c3864b1e</t>
+  </si>
+  <si>
+    <t>6a031af48046ce4dbfb962a9</t>
+  </si>
+  <si>
+    <t>6a0418de8046ce4dbfb97158</t>
+  </si>
+  <si>
+    <t>6a02df468046ce4dbfb956b8</t>
+  </si>
+  <si>
+    <t>69fc25c28046ce4dbfb8e757</t>
+  </si>
+  <si>
+    <t>69fdcdbb8046ce4dbfb90c87</t>
+  </si>
+  <si>
+    <t>6a03202f8046ce4dbfb963d1</t>
+  </si>
+  <si>
+    <t>6a042fc58046ce4dbfb9751c</t>
+  </si>
+  <si>
+    <t>69fc6c1a8046ce4dbfb8f078</t>
+  </si>
+  <si>
+    <t>69fc6c1a8046ce4dbfb8f07b</t>
+  </si>
+  <si>
+    <t>6a0324bd8046ce4dbfb9648c</t>
+  </si>
+  <si>
+    <t>69fdd77f8046ce4dbfb90e77</t>
+  </si>
+  <si>
+    <t>6a01ae668046ce4dbfb93f49</t>
+  </si>
+  <si>
+    <t>6a057aee8046ce4dbfb98f37</t>
+  </si>
+  <si>
+    <t>6a04265a8046ce4dbfb972ea</t>
+  </si>
+  <si>
+    <t>69fddfa48046ce4dbfb90ff3</t>
+  </si>
+  <si>
+    <t>69fe0f9b8046ce4dbfb916ae</t>
+  </si>
+  <si>
+    <t>69fe0f9b8046ce4dbfb916af</t>
+  </si>
+  <si>
+    <t>69fda1798046ce4dbfb90543</t>
+  </si>
+  <si>
+    <t>6a031f098046ce4dbfb96386</t>
+  </si>
+  <si>
+    <t>69fde7c78046ce4dbfb91154</t>
+  </si>
+  <si>
+    <t>69fe157b8046ce4dbfb91732</t>
+  </si>
+  <si>
+    <t>6a0459af8046ce4dbfb97d5d</t>
+  </si>
+  <si>
+    <t>69ff24338046ce4dbfb922b3</t>
+  </si>
+  <si>
+    <t>6a033e3c8046ce4dbfb969d9</t>
+  </si>
+  <si>
+    <t>69feff168046ce4dbfb91f24</t>
+  </si>
+  <si>
+    <t>69feff168046ce4dbfb91f25</t>
+  </si>
+  <si>
+    <t>69ff0ab48046ce4dbfb9205f</t>
+  </si>
+  <si>
+    <t>69ff20a48046ce4dbfb9225e</t>
+  </si>
+  <si>
+    <t>69ff43cf8046ce4dbfb924e2</t>
+  </si>
+  <si>
+    <t>69ff43cf8046ce4dbfb924e4</t>
+  </si>
+  <si>
+    <t>6a0021488046ce4dbfb928b6</t>
+  </si>
+  <si>
+    <t>6a007a5b8046ce4dbfb92e10</t>
+  </si>
+  <si>
+    <t>6a00cebf8046ce4dbfb932bc</t>
+  </si>
+  <si>
+    <t>6a00cebf8046ce4dbfb932bd</t>
+  </si>
+  <si>
+    <t>6a0595288046ce4dbfb994d0</t>
+  </si>
+  <si>
+    <t>6a01b5978046ce4dbfb94097</t>
+  </si>
+  <si>
+    <t>6a01b5978046ce4dbfb94099</t>
+  </si>
+  <si>
+    <t>6a01bdd18046ce4dbfb9422b</t>
+  </si>
+  <si>
+    <t>6a0300578046ce4dbfb95d81</t>
+  </si>
+  <si>
+    <t>6a059f9e8046ce4dbfb996cf</t>
+  </si>
+  <si>
+    <t>6a04774a8046ce4dbfb982ad</t>
+  </si>
+  <si>
+    <t>6a0456b18046ce4dbfb97ceb</t>
+  </si>
+  <si>
+    <t>6a0483c38046ce4dbfb9850b</t>
+  </si>
+  <si>
+    <t>6a01c3b48046ce4dbfb9431b</t>
+  </si>
+  <si>
+    <t>6a01c3b48046ce4dbfb9431e</t>
+  </si>
+  <si>
+    <t>6a01cae48046ce4dbfb94483</t>
+  </si>
+  <si>
+    <t>6a057b498046ce4dbfb98f6d</t>
+  </si>
+  <si>
+    <t>6a01f98b8046ce4dbfb94d44</t>
+  </si>
+  <si>
+    <t>6a02041f8046ce4dbfb94e9e</t>
+  </si>
+  <si>
+    <t>6a0219398046ce4dbfb9504b</t>
+  </si>
+  <si>
+    <t>6a0219398046ce4dbfb9504c</t>
+  </si>
+  <si>
+    <t>6a04abed8046ce4dbfb989f2</t>
+  </si>
+  <si>
+    <t>6a02ed558046ce4dbfb95975</t>
+  </si>
+  <si>
+    <t>6a02ed558046ce4dbfb95977</t>
+  </si>
+  <si>
+    <t>6a05ae298046ce4dbfb9998b</t>
+  </si>
+  <si>
+    <t>6a02fb628046ce4dbfb95c8e</t>
+  </si>
+  <si>
+    <t>6a0311a68046ce4dbfb9608c</t>
+  </si>
+  <si>
+    <t>6a0314018046ce4dbfb96137</t>
+  </si>
+  <si>
+    <t>6a031fcd8046ce4dbfb963c6</t>
+  </si>
+  <si>
+    <t>6a031fcd8046ce4dbfb963c7</t>
+  </si>
+  <si>
+    <t>6a031fb58046ce4dbfb963c1</t>
+  </si>
+  <si>
+    <t>6a0327ed8046ce4dbfb9654f</t>
+  </si>
+  <si>
+    <t>6a0330188046ce4dbfb96703</t>
+  </si>
+  <si>
+    <t>6a0330188046ce4dbfb96704</t>
+  </si>
+  <si>
+    <t>6a0332c78046ce4dbfb96780</t>
+  </si>
+  <si>
+    <t>6a0349e68046ce4dbfb96baa</t>
+  </si>
+  <si>
+    <t>6a0349e68046ce4dbfb96bab</t>
+  </si>
+  <si>
+    <t>6a0349e68046ce4dbfb96baf</t>
+  </si>
+  <si>
+    <t>6a033bd98046ce4dbfb96947</t>
+  </si>
+  <si>
+    <t>6a0340888046ce4dbfb96a37</t>
+  </si>
+  <si>
+    <t>6a0341d98046ce4dbfb96a6d</t>
+  </si>
+  <si>
+    <t>6a0345378046ce4dbfb96ae4</t>
+  </si>
+  <si>
+    <t>6a03465e8046ce4dbfb96b16</t>
+  </si>
+  <si>
+    <t>6a034b238046ce4dbfb96bca</t>
+  </si>
+  <si>
+    <t>6a03465d8046ce4dbfb96b07</t>
+  </si>
+  <si>
+    <t>6a034c3d8046ce4dbfb96be7</t>
+  </si>
+  <si>
+    <t>6a034c3d8046ce4dbfb96be8</t>
+  </si>
+  <si>
+    <t>6a03523e8046ce4dbfb96cc3</t>
+  </si>
+  <si>
+    <t>6a0356cc8046ce4dbfb96d4c</t>
+  </si>
+  <si>
+    <t>6a02f2038046ce4dbfb95a9b</t>
+  </si>
+  <si>
+    <t>6a02f2038046ce4dbfb95a9d</t>
+  </si>
+  <si>
+    <t>6a0311b18046ce4dbfb960ab</t>
+  </si>
+  <si>
+    <t>6a0311b18046ce4dbfb960ad</t>
+  </si>
+  <si>
+    <t>6a0313298046ce4dbfb96101</t>
+  </si>
+  <si>
+    <t>6a031a338046ce4dbfb9629f</t>
+  </si>
+  <si>
+    <t>6a031a338046ce4dbfb962a0</t>
+  </si>
+  <si>
+    <t>6a031c368046ce4dbfb96311</t>
+  </si>
+  <si>
+    <t>6a0326ba8046ce4dbfb964d2</t>
+  </si>
+  <si>
+    <t>6a0326ba8046ce4dbfb964d3</t>
+  </si>
+  <si>
+    <t>6a0327ec8046ce4dbfb9652e</t>
+  </si>
+  <si>
+    <t>6a0327ed8046ce4dbfb96543</t>
+  </si>
+  <si>
+    <t>6a0327eb8046ce4dbfb9651d</t>
+  </si>
+  <si>
+    <t>6a0329608046ce4dbfb965bf</t>
+  </si>
+  <si>
+    <t>6a0329608046ce4dbfb965c0</t>
+  </si>
+  <si>
+    <t>6a0335fc8046ce4dbfb96857</t>
+  </si>
+  <si>
+    <t>6a0339858046ce4dbfb96904</t>
+  </si>
+  <si>
+    <t>6a033d018046ce4dbfb969a6</t>
+  </si>
+  <si>
+    <t>6a033f588046ce4dbfb96a15</t>
+  </si>
+  <si>
+    <t>6a0341af8046ce4dbfb96a5b</t>
+  </si>
+  <si>
+    <t>6a034e958046ce4dbfb96c32</t>
+  </si>
+  <si>
+    <t>6a034e958046ce4dbfb96c33</t>
+  </si>
+  <si>
+    <t>6a0348b58046ce4dbfb96b80</t>
+  </si>
+  <si>
+    <t>6a0348b58046ce4dbfb96b81</t>
+  </si>
+  <si>
+    <t>6a034fc88046ce4dbfb96c5c</t>
+  </si>
+  <si>
+    <t>6a035a518046ce4dbfb96ddc</t>
+  </si>
+  <si>
+    <t>6a0361518046ce4dbfb96e97</t>
+  </si>
+  <si>
+    <t>6a0364dd8046ce4dbfb96eef</t>
+  </si>
+  <si>
+    <t>6a0420578046ce4dbfb971ee</t>
+  </si>
+  <si>
+    <t>6a0420578046ce4dbfb971f0</t>
+  </si>
+  <si>
+    <t>6a042c0e8046ce4dbfb9744a</t>
+  </si>
+  <si>
+    <t>6a042c0e8046ce4dbfb97447</t>
+  </si>
+  <si>
+    <t>6a05a5138046ce4dbfb997f0</t>
+  </si>
+  <si>
+    <t>6a042c0d8046ce4dbfb97424</t>
+  </si>
+  <si>
+    <t>6a0434538046ce4dbfb975f1</t>
+  </si>
+  <si>
+    <t>6a042e658046ce4dbfb974a6</t>
+  </si>
+  <si>
+    <t>6a042e658046ce4dbfb974aa</t>
+  </si>
+  <si>
+    <t>6a0436a18046ce4dbfb97678</t>
+  </si>
+  <si>
+    <t>6a0434508046ce4dbfb975c9</t>
+  </si>
+  <si>
+    <t>6a0434508046ce4dbfb975cb</t>
+  </si>
+  <si>
+    <t>6a0435768046ce4dbfb9761e</t>
+  </si>
+  <si>
+    <t>6a05936c8046ce4dbfb9945b</t>
+  </si>
+  <si>
+    <t>6a0433208046ce4dbfb9759f</t>
+  </si>
+  <si>
+    <t>6a0436a18046ce4dbfb97675</t>
+  </si>
+  <si>
+    <t>6a0440018046ce4dbfb97895</t>
+  </si>
+  <si>
+    <t>6a043ffd8046ce4dbfb9788f</t>
+  </si>
+  <si>
+    <t>6a0447028046ce4dbfb979f3</t>
+  </si>
+  <si>
+    <t>6a0579a58046ce4dbfb98ef6</t>
+  </si>
+  <si>
+    <t>6a044ce28046ce4dbfb97b13</t>
+  </si>
+  <si>
+    <t>6a058a8f8046ce4dbfb992bd</t>
+  </si>
+  <si>
+    <t>6a04551e8046ce4dbfb97ca4</t>
+  </si>
+  <si>
+    <t>6a04564b8046ce4dbfb97ce2</t>
+  </si>
+  <si>
+    <t>6a04564b8046ce4dbfb97ce3</t>
+  </si>
+  <si>
+    <t>6a045e838046ce4dbfb97e52</t>
+  </si>
+  <si>
+    <t>6a0467f88046ce4dbfb9801b</t>
+  </si>
+  <si>
+    <t>6a0480718046ce4dbfb9844f</t>
+  </si>
+  <si>
+    <t>6a047f518046ce4dbfb98417</t>
+  </si>
+  <si>
+    <t>6a0587848046ce4dbfb99201</t>
+  </si>
+  <si>
+    <t>6a048b0b8046ce4dbfb98605</t>
+  </si>
+  <si>
+    <t>6a048b0b8046ce4dbfb98607</t>
+  </si>
+  <si>
+    <t>6a048c898046ce4dbfb9863e</t>
+  </si>
+  <si>
+    <t>6a048c948046ce4dbfb9865b</t>
+  </si>
+  <si>
+    <t>6a049b658046ce4dbfb9882b</t>
+  </si>
+  <si>
+    <t>6a049b708046ce4dbfb9884a</t>
+  </si>
+  <si>
+    <t>6a04af618046ce4dbfb98a32</t>
+  </si>
+  <si>
+    <t>6a04b5638046ce4dbfb98a82</t>
+  </si>
+  <si>
+    <t>6a03cbf98046ce4dbfb970a5</t>
+  </si>
+  <si>
+    <t>6a03f9b18046ce4dbfb970be</t>
+  </si>
+  <si>
+    <t>6a0407d38046ce4dbfb970ed</t>
+  </si>
+  <si>
+    <t>6a04263a8046ce4dbfb972d5</t>
+  </si>
+  <si>
+    <t>6a04263a8046ce4dbfb972d6</t>
+  </si>
+  <si>
+    <t>6a04218a8046ce4dbfb9721f</t>
+  </si>
+  <si>
+    <t>6a0421948046ce4dbfb97225</t>
+  </si>
+  <si>
+    <t>6a0421948046ce4dbfb97226</t>
+  </si>
+  <si>
+    <t>6a0437d98046ce4dbfb976ae</t>
+  </si>
+  <si>
+    <t>6a043c808046ce4dbfb977c2</t>
+  </si>
+  <si>
+    <t>6a043ffa8046ce4dbfb97876</t>
+  </si>
+  <si>
+    <t>6a043ffa8046ce4dbfb97879</t>
+  </si>
+  <si>
+    <t>6a0443838046ce4dbfb9792f</t>
+  </si>
+  <si>
+    <t>6a044f398046ce4dbfb97b86</t>
+  </si>
+  <si>
+    <t>6a044f398046ce4dbfb97b88</t>
+  </si>
+  <si>
+    <t>6a048d588046ce4dbfb9866a</t>
+  </si>
+  <si>
+    <t>6a048d588046ce4dbfb9866b</t>
+  </si>
+  <si>
+    <t>6a0471348046ce4dbfb98175</t>
+  </si>
+  <si>
+    <t>6a0471348046ce4dbfb98178</t>
+  </si>
+  <si>
+    <t>6a0472668046ce4dbfb981a8</t>
+  </si>
+  <si>
+    <t>6a0474bb8046ce4dbfb98200</t>
+  </si>
+  <si>
+    <t>6a04784a8046ce4dbfb982c6</t>
+  </si>
+  <si>
+    <t>6a04784a8046ce4dbfb982c7</t>
+  </si>
+  <si>
+    <t>6a047d138046ce4dbfb983d1</t>
+  </si>
+  <si>
+    <t>6a04a4c38046ce4dbfb9895a</t>
+  </si>
+  <si>
+    <t>6a048a118046ce4dbfb985e9</t>
+  </si>
+  <si>
+    <t>6a048a118046ce4dbfb985eb</t>
+  </si>
+  <si>
+    <t>6a04c9158046ce4dbfb98b78</t>
+  </si>
+  <si>
+    <t>6a048e828046ce4dbfb986c8</t>
+  </si>
+  <si>
+    <t>6a048e828046ce4dbfb986c9</t>
+  </si>
+  <si>
+    <t>6a04abc98046ce4dbfb989e3</t>
+  </si>
+  <si>
+    <t>6a04a26f8046ce4dbfb98922</t>
+  </si>
+  <si>
+    <t>6a04a71a8046ce4dbfb9897b</t>
+  </si>
+  <si>
+    <t>6a04b9d78046ce4dbfb98acb</t>
+  </si>
+  <si>
+    <t>6a04d4cb8046ce4dbfb98bec</t>
+  </si>
+  <si>
+    <t>6a04f3478046ce4dbfb98c60</t>
+  </si>
+  <si>
+    <t>6a0585d88046ce4dbfb9918c</t>
+  </si>
+  <si>
+    <t>6a057ee78046ce4dbfb9901d</t>
+  </si>
+  <si>
+    <t>6a057ee78046ce4dbfb9901e</t>
+  </si>
+  <si>
+    <t>6a057ec68046ce4dbfb99016</t>
+  </si>
+  <si>
+    <t>6a057ec68046ce4dbfb99017</t>
+  </si>
+  <si>
+    <t>6a0582478046ce4dbfb99094</t>
+  </si>
+  <si>
+    <t>6a0582478046ce4dbfb99098</t>
+  </si>
+  <si>
+    <t>6a058a788046ce4dbfb99299</t>
+  </si>
+  <si>
+    <t>6a0591878046ce4dbfb99406</t>
+  </si>
+  <si>
+    <t>6a0592b78046ce4dbfb9944d</t>
+  </si>
+  <si>
+    <t>6a0599e08046ce4dbfb995c3</t>
+  </si>
+  <si>
+    <t>6a0599e08046ce4dbfb995c5</t>
+  </si>
+  <si>
+    <t>6a0595048046ce4dbfb994b9</t>
+  </si>
+  <si>
+    <t>6a0597778046ce4dbfb99544</t>
+  </si>
+  <si>
+    <t>6a0597778046ce4dbfb99546</t>
+  </si>
+  <si>
+    <t>6a0597778046ce4dbfb99547</t>
+  </si>
+  <si>
+    <t>6a05a3128046ce4dbfb997a4</t>
+  </si>
+  <si>
+    <t>6a05a7cb8046ce4dbfb99878</t>
+  </si>
+  <si>
+    <t>6a05894e8046ce4dbfb9925c</t>
+  </si>
+  <si>
+    <t>6a058ba58046ce4dbfb992d1</t>
+  </si>
+  <si>
+    <t>6a058f238046ce4dbfb99381</t>
+  </si>
+  <si>
+    <t>6a0592ab8046ce4dbfb99426</t>
+  </si>
+  <si>
+    <t>6a0597708046ce4dbfb994f6</t>
+  </si>
+  <si>
+    <t>6a0598ae8046ce4dbfb99597</t>
+  </si>
+  <si>
+    <t>6a0598ae8046ce4dbfb99598</t>
+  </si>
+  <si>
+    <t>6a059c0a8046ce4dbfb9960f</t>
+  </si>
+  <si>
+    <t>6a05a0bc8046ce4dbfb9972b</t>
+  </si>
+  <si>
+    <t>6a05a6998046ce4dbfb9981b</t>
+  </si>
+  <si>
+    <t>6a05a6998046ce4dbfb99815</t>
+  </si>
+  <si>
+    <t>6a05a6998046ce4dbfb99816</t>
+  </si>
+  <si>
+    <t>6a05a6998046ce4dbfb99817</t>
+  </si>
+  <si>
+    <t>6a05a5688046ce4dbfb99808</t>
+  </si>
+  <si>
+    <t>6a05affe8046ce4dbfb999e9</t>
+  </si>
+  <si>
+    <t>1449-619376</t>
+  </si>
+  <si>
+    <t>1449-632273</t>
+  </si>
+  <si>
+    <t>FIZZ-1000916148</t>
+  </si>
+  <si>
+    <t>FIZZ-1000916567</t>
+  </si>
+  <si>
+    <t>26MPE0005083/1</t>
+  </si>
+  <si>
+    <t>26MPE0005127/1</t>
+  </si>
+  <si>
+    <t>26MPE0005129/1</t>
+  </si>
+  <si>
+    <t>26MPE0005178/1</t>
+  </si>
+  <si>
+    <t>307141470/1</t>
+  </si>
+  <si>
+    <t>307141470/2</t>
+  </si>
+  <si>
+    <t>307141470/3</t>
+  </si>
+  <si>
+    <t>307279504/1</t>
+  </si>
+  <si>
+    <t>308544508/1</t>
+  </si>
+  <si>
+    <t>308544508/2</t>
+  </si>
+  <si>
+    <t>309999931/1</t>
+  </si>
+  <si>
+    <t>310674041/1</t>
+  </si>
+  <si>
+    <t>310850736/1</t>
+  </si>
+  <si>
+    <t>310904465/1</t>
+  </si>
+  <si>
+    <t>310904465/2</t>
+  </si>
+  <si>
+    <t>310969078/1</t>
+  </si>
+  <si>
+    <t>311103072/1</t>
+  </si>
+  <si>
+    <t>311177414/1</t>
+  </si>
+  <si>
+    <t>311177414/2</t>
+  </si>
+  <si>
+    <t>311177414/3</t>
+  </si>
+  <si>
+    <t>311245762/1</t>
+  </si>
+  <si>
+    <t>311245762/2</t>
+  </si>
+  <si>
+    <t>311288553/1</t>
+  </si>
+  <si>
+    <t>311288553/2</t>
+  </si>
+  <si>
+    <t>311345569/1</t>
+  </si>
+  <si>
+    <t>311346022/1</t>
+  </si>
+  <si>
+    <t>311379820/1</t>
+  </si>
+  <si>
+    <t>311431962/1</t>
+  </si>
+  <si>
+    <t>311432110/1</t>
+  </si>
+  <si>
+    <t>311432110/2</t>
+  </si>
+  <si>
+    <t>311432184/1</t>
+  </si>
+  <si>
+    <t>311432184/2</t>
+  </si>
+  <si>
+    <t>311432675/1</t>
+  </si>
+  <si>
+    <t>311432759/1</t>
+  </si>
+  <si>
+    <t>311432859/1</t>
+  </si>
+  <si>
+    <t>311432904/1</t>
+  </si>
+  <si>
+    <t>311432904/2</t>
+  </si>
+  <si>
+    <t>311481475/1</t>
+  </si>
+  <si>
+    <t>311481475/2</t>
+  </si>
+  <si>
+    <t>311481866/1</t>
+  </si>
+  <si>
+    <t>311482056/1</t>
+  </si>
+  <si>
+    <t>311482092/1</t>
+  </si>
+  <si>
+    <t>311482127/1</t>
+  </si>
+  <si>
+    <t>311545617/1</t>
+  </si>
+  <si>
+    <t>311545668/1</t>
+  </si>
+  <si>
+    <t>311545884/1</t>
+  </si>
+  <si>
+    <t>311545957/1</t>
+  </si>
+  <si>
+    <t>311545996/1</t>
+  </si>
+  <si>
+    <t>311546037/1</t>
+  </si>
+  <si>
+    <t>311546128/1</t>
+  </si>
+  <si>
+    <t>311546128/2</t>
+  </si>
+  <si>
+    <t>311546131/1</t>
+  </si>
+  <si>
+    <t>311546131/2</t>
+  </si>
+  <si>
+    <t>311546131/3</t>
+  </si>
+  <si>
+    <t>311546138/1</t>
+  </si>
+  <si>
+    <t>311546169/1</t>
+  </si>
+  <si>
+    <t>311546169/2</t>
+  </si>
+  <si>
+    <t>311546184/1</t>
+  </si>
+  <si>
+    <t>311546184/2</t>
+  </si>
+  <si>
+    <t>311546258/1</t>
+  </si>
+  <si>
+    <t>311546308/1</t>
+  </si>
+  <si>
+    <t>311546360/1</t>
+  </si>
+  <si>
+    <t>311546401/1</t>
+  </si>
+  <si>
+    <t>311546426/1</t>
+  </si>
+  <si>
+    <t>311546479/1</t>
+  </si>
+  <si>
+    <t>311546517/1</t>
+  </si>
+  <si>
+    <t>311605447/1</t>
+  </si>
+  <si>
+    <t>311605545/1</t>
+  </si>
+  <si>
+    <t>311605556/1</t>
+  </si>
+  <si>
+    <t>311605679/1</t>
+  </si>
+  <si>
+    <t>311605679/2</t>
+  </si>
+  <si>
+    <t>311605852/1</t>
+  </si>
+  <si>
+    <t>311605852/2</t>
+  </si>
+  <si>
+    <t>311605949/1</t>
+  </si>
+  <si>
+    <t>311606017/1</t>
+  </si>
+  <si>
+    <t>311606112/1</t>
+  </si>
+  <si>
+    <t>311725045/1</t>
+  </si>
+  <si>
+    <t>311725074/1</t>
+  </si>
+  <si>
+    <t>311725108/1</t>
+  </si>
+  <si>
+    <t>311725121/1</t>
+  </si>
+  <si>
+    <t>311725151/1</t>
+  </si>
+  <si>
+    <t>311725157/1</t>
+  </si>
+  <si>
+    <t>311725325/1</t>
+  </si>
+  <si>
+    <t>311725542/1</t>
+  </si>
+  <si>
+    <t>311725618/1</t>
+  </si>
+  <si>
+    <t>311725618/2</t>
+  </si>
+  <si>
+    <t>311725694/1</t>
+  </si>
+  <si>
+    <t>311725703/1</t>
+  </si>
+  <si>
+    <t>311725722/1</t>
+  </si>
+  <si>
+    <t>311725762/1</t>
+  </si>
+  <si>
+    <t>311725785/1</t>
+  </si>
+  <si>
+    <t>311725813/1</t>
+  </si>
+  <si>
+    <t>311725813/2</t>
+  </si>
+  <si>
+    <t>311725813/3</t>
+  </si>
+  <si>
+    <t>311725843/1</t>
+  </si>
+  <si>
+    <t>311725844/1</t>
+  </si>
+  <si>
+    <t>311725844/2</t>
+  </si>
+  <si>
+    <t>311725943/1</t>
+  </si>
+  <si>
+    <t>311725976/1</t>
+  </si>
+  <si>
+    <t>311725998/1</t>
+  </si>
+  <si>
+    <t>311726024/1</t>
+  </si>
+  <si>
+    <t>311726028/1</t>
+  </si>
+  <si>
+    <t>311777650/1</t>
+  </si>
+  <si>
+    <t>311777679/1</t>
+  </si>
+  <si>
+    <t>311777712/1</t>
+  </si>
+  <si>
+    <t>311777717/1</t>
+  </si>
+  <si>
+    <t>311777780/1</t>
+  </si>
+  <si>
+    <t>311777832/1</t>
+  </si>
+  <si>
+    <t>311777852/1</t>
+  </si>
+  <si>
+    <t>311777866/1</t>
+  </si>
+  <si>
+    <t>311777866/2</t>
+  </si>
+  <si>
+    <t>311777888/1</t>
+  </si>
+  <si>
+    <t>311777906/1</t>
+  </si>
+  <si>
+    <t>311777923/1</t>
+  </si>
+  <si>
+    <t>311777992/1</t>
+  </si>
+  <si>
+    <t>311778004/1</t>
+  </si>
+  <si>
+    <t>311778004/2</t>
+  </si>
+  <si>
+    <t>311778264/1</t>
+  </si>
+  <si>
+    <t>311778518/1</t>
+  </si>
+  <si>
+    <t>311826331/1</t>
+  </si>
+  <si>
+    <t>311861914/1</t>
+  </si>
+  <si>
+    <t>311861996/1</t>
+  </si>
+  <si>
+    <t>311862037/1</t>
+  </si>
+  <si>
+    <t>311862060/1</t>
+  </si>
+  <si>
+    <t>99002504/1</t>
+  </si>
+  <si>
+    <t>202605132601023301</t>
+  </si>
+  <si>
+    <t>202605122601052401</t>
+  </si>
+  <si>
+    <t>202605122601050401</t>
+  </si>
+  <si>
+    <t>202605122601054801</t>
+  </si>
+  <si>
+    <t>202605132601063501</t>
+  </si>
+  <si>
+    <t>202605132601064801</t>
+  </si>
+  <si>
+    <t>202605132601063901</t>
+  </si>
+  <si>
+    <t>202605132601060901</t>
+  </si>
+  <si>
+    <t>202605132601064601</t>
+  </si>
+  <si>
+    <t>202605142601071901</t>
+  </si>
+  <si>
+    <t>202605142601068001</t>
+  </si>
+  <si>
+    <t>202605142601068201</t>
+  </si>
+  <si>
+    <t>202605142601067501</t>
+  </si>
+  <si>
+    <t>202605142601068601</t>
+  </si>
+  <si>
+    <t>202605142601071501</t>
+  </si>
+  <si>
+    <t>202605142601071001</t>
+  </si>
+  <si>
+    <t>202605142601072701</t>
+  </si>
+  <si>
+    <t>202605142601073301</t>
+  </si>
+  <si>
+    <t>202605142601070501</t>
+  </si>
+  <si>
+    <t>202605142601067601</t>
+  </si>
+  <si>
+    <t>202605142601067801</t>
+  </si>
+  <si>
+    <t>202605142600987101</t>
+  </si>
+  <si>
+    <t>202605132601015201</t>
+  </si>
+  <si>
+    <t>202605132601024901</t>
+  </si>
+  <si>
+    <t>202605122601051201</t>
+  </si>
+  <si>
+    <t>202605142601051202</t>
+  </si>
+  <si>
+    <t>202605132601061301</t>
+  </si>
+  <si>
+    <t>202605142601072101</t>
+  </si>
+  <si>
+    <t>202605142601069301</t>
+  </si>
+  <si>
+    <t>202605142601071201</t>
+  </si>
+  <si>
+    <t>202605142601068701</t>
+  </si>
+  <si>
+    <t>202605142601068901</t>
+  </si>
+  <si>
+    <t>202605142601069901</t>
+  </si>
+  <si>
+    <t>202605142601069902</t>
+  </si>
+  <si>
+    <t>202605142601070701</t>
+  </si>
+  <si>
+    <t>202605142601070301</t>
+  </si>
+  <si>
+    <t>202605142601073701</t>
+  </si>
+  <si>
+    <t>202605142601072001</t>
+  </si>
+  <si>
+    <t>202605142601071401</t>
+  </si>
+  <si>
+    <t>202605142601067001</t>
+  </si>
+  <si>
+    <t>202605142601072801</t>
+  </si>
+  <si>
+    <t>202605142601072802</t>
+  </si>
+  <si>
+    <t>202605142601067301</t>
+  </si>
+  <si>
+    <t>202605142601067302</t>
+  </si>
+  <si>
+    <t>202605142601067101</t>
+  </si>
+  <si>
+    <t>202605142601067102</t>
+  </si>
+  <si>
+    <t>202605142601068401</t>
+  </si>
+  <si>
+    <t>202605142601068402</t>
+  </si>
+  <si>
+    <t>202605142601068403</t>
+  </si>
+  <si>
+    <t>202605142601071301</t>
+  </si>
+  <si>
+    <t>202605142601071302</t>
+  </si>
+  <si>
+    <t>202605142601071303</t>
+  </si>
+  <si>
+    <t>159995579540194714</t>
+  </si>
+  <si>
+    <t>159995579540194721</t>
+  </si>
+  <si>
+    <t>159995579540194738</t>
+  </si>
+  <si>
+    <t>159995579540194851</t>
+  </si>
+  <si>
+    <t>159995579540194868</t>
+  </si>
+  <si>
+    <t>159995579540194875</t>
+  </si>
+  <si>
+    <t>159995579540194677</t>
+  </si>
+  <si>
+    <t>159995579540126432</t>
+  </si>
+  <si>
+    <t>159995579540173283</t>
   </si>
 </sst>
 </file>
@@ -399,10 +2538,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -684,12 +2822,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D430"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
@@ -705,867 +2843,4722 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
+      <c r="A2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2" t="s">
+        <v>160</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
+      <c r="A3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" t="s">
+        <v>398</v>
       </c>
       <c r="C3" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>400</v>
+      </c>
+      <c r="C5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>401</v>
+      </c>
+      <c r="C6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" t="s">
+        <v>402</v>
+      </c>
+      <c r="C7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" t="s">
+        <v>404</v>
+      </c>
+      <c r="C9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" t="s">
+        <v>406</v>
+      </c>
+      <c r="C11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B12" t="s">
+        <v>407</v>
+      </c>
+      <c r="C12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B13" t="s">
+        <v>408</v>
+      </c>
+      <c r="C13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>169</v>
+      </c>
+      <c r="B14" t="s">
+        <v>409</v>
+      </c>
+      <c r="C14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B15" t="s">
+        <v>410</v>
+      </c>
+      <c r="C15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>411</v>
+      </c>
+      <c r="C16" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="B17" t="s">
+        <v>412</v>
+      </c>
+      <c r="C17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>170</v>
+      </c>
+      <c r="B18" t="s">
+        <v>413</v>
+      </c>
+      <c r="C18" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>171</v>
+      </c>
+      <c r="B19" t="s">
+        <v>414</v>
+      </c>
+      <c r="C19" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>172</v>
+      </c>
+      <c r="B20" t="s">
+        <v>415</v>
+      </c>
+      <c r="C20" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>173</v>
+      </c>
+      <c r="B21" t="s">
+        <v>416</v>
+      </c>
+      <c r="C21" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" t="s">
+        <v>417</v>
+      </c>
+      <c r="C22" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>175</v>
+      </c>
+      <c r="B23" t="s">
+        <v>418</v>
+      </c>
+      <c r="C23" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>176</v>
+      </c>
+      <c r="B24" t="s">
+        <v>419</v>
+      </c>
+      <c r="C24" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>6</v>
       </c>
-      <c r="C5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B25" t="s">
+        <v>420</v>
+      </c>
+      <c r="C25" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>177</v>
+      </c>
+      <c r="B26" t="s">
+        <v>421</v>
+      </c>
+      <c r="C26" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>178</v>
+      </c>
+      <c r="B27" t="s">
+        <v>422</v>
+      </c>
+      <c r="C27" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>179</v>
+      </c>
+      <c r="B28" t="s">
+        <v>423</v>
+      </c>
+      <c r="C28" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>7</v>
       </c>
-      <c r="C6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="B29" t="s">
+        <v>424</v>
+      </c>
+      <c r="C29" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>180</v>
+      </c>
+      <c r="B30" t="s">
+        <v>425</v>
+      </c>
+      <c r="C30" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>181</v>
+      </c>
+      <c r="B31" t="s">
+        <v>426</v>
+      </c>
+      <c r="C31" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>182</v>
+      </c>
+      <c r="B32" t="s">
+        <v>427</v>
+      </c>
+      <c r="C32" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>183</v>
+      </c>
+      <c r="B33" t="s">
+        <v>428</v>
+      </c>
+      <c r="C33" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>183</v>
+      </c>
+      <c r="B34" t="s">
+        <v>429</v>
+      </c>
+      <c r="C34" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>184</v>
+      </c>
+      <c r="B35" t="s">
+        <v>430</v>
+      </c>
+      <c r="C35" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>185</v>
+      </c>
+      <c r="B36" t="s">
+        <v>431</v>
+      </c>
+      <c r="C36" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>8</v>
       </c>
-      <c r="C7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="B37" t="s">
+        <v>432</v>
+      </c>
+      <c r="C37" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>186</v>
+      </c>
+      <c r="B38" t="s">
+        <v>433</v>
+      </c>
+      <c r="C38" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>187</v>
+      </c>
+      <c r="B39" t="s">
+        <v>434</v>
+      </c>
+      <c r="C39" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>188</v>
+      </c>
+      <c r="B40" t="s">
+        <v>435</v>
+      </c>
+      <c r="C40" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>9</v>
       </c>
-      <c r="C8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>42</v>
+      <c r="B41" t="s">
+        <v>436</v>
       </c>
       <c r="C41" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>43</v>
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" t="s">
+        <v>437</v>
       </c>
       <c r="C42" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>44</v>
+      <c r="A43" t="s">
+        <v>189</v>
+      </c>
+      <c r="B43" t="s">
+        <v>438</v>
       </c>
       <c r="C43" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>45</v>
+      <c r="A44" t="s">
+        <v>190</v>
+      </c>
+      <c r="B44" t="s">
+        <v>439</v>
       </c>
       <c r="C44" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>46</v>
+      <c r="A45" t="s">
+        <v>191</v>
+      </c>
+      <c r="B45" t="s">
+        <v>440</v>
       </c>
       <c r="C45" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>47</v>
+      <c r="A46" t="s">
+        <v>10</v>
+      </c>
+      <c r="B46" t="s">
+        <v>441</v>
       </c>
       <c r="C46" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>48</v>
+      <c r="A47" t="s">
+        <v>192</v>
+      </c>
+      <c r="B47" t="s">
+        <v>442</v>
       </c>
       <c r="C47" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>49</v>
+      <c r="A48" t="s">
+        <v>193</v>
+      </c>
+      <c r="B48" t="s">
+        <v>443</v>
       </c>
       <c r="C48" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>50</v>
+      <c r="A49" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" t="s">
+        <v>444</v>
       </c>
       <c r="C49" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>51</v>
+      <c r="A50" t="s">
+        <v>194</v>
+      </c>
+      <c r="B50" t="s">
+        <v>445</v>
       </c>
       <c r="C50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>52</v>
+      <c r="A51" t="s">
+        <v>194</v>
+      </c>
+      <c r="B51" t="s">
+        <v>446</v>
       </c>
       <c r="C51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>53</v>
+      <c r="A52" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" t="s">
+        <v>447</v>
       </c>
       <c r="C52" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>54</v>
+      <c r="A53" t="s">
+        <v>195</v>
+      </c>
+      <c r="B53" t="s">
+        <v>448</v>
       </c>
       <c r="C53" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>55</v>
+      <c r="A54" t="s">
+        <v>13</v>
+      </c>
+      <c r="B54" t="s">
+        <v>449</v>
       </c>
       <c r="C54" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>56</v>
+      <c r="A55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" t="s">
+        <v>450</v>
       </c>
       <c r="C55" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>57</v>
+      <c r="A56" t="s">
+        <v>196</v>
+      </c>
+      <c r="B56" t="s">
+        <v>451</v>
       </c>
       <c r="C56" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>58</v>
+      <c r="A57" t="s">
+        <v>197</v>
+      </c>
+      <c r="B57" t="s">
+        <v>452</v>
       </c>
       <c r="C57" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>59</v>
+      <c r="A58" t="s">
+        <v>198</v>
+      </c>
+      <c r="B58" t="s">
+        <v>453</v>
       </c>
       <c r="C58" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>60</v>
+      <c r="A59" t="s">
+        <v>198</v>
+      </c>
+      <c r="B59" t="s">
+        <v>454</v>
       </c>
       <c r="C59" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>61</v>
+      <c r="A60" t="s">
+        <v>199</v>
+      </c>
+      <c r="B60" t="s">
+        <v>455</v>
       </c>
       <c r="C60" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>62</v>
+      <c r="A61" t="s">
+        <v>200</v>
+      </c>
+      <c r="B61" t="s">
+        <v>456</v>
       </c>
       <c r="C61" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>63</v>
+      <c r="A62" t="s">
+        <v>200</v>
+      </c>
+      <c r="B62" t="s">
+        <v>457</v>
       </c>
       <c r="C62" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>64</v>
+      <c r="A63" t="s">
+        <v>14</v>
+      </c>
+      <c r="B63" t="s">
+        <v>458</v>
       </c>
       <c r="C63" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>65</v>
+      <c r="A64" t="s">
+        <v>201</v>
+      </c>
+      <c r="B64" t="s">
+        <v>459</v>
       </c>
       <c r="C64" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>66</v>
+      <c r="A65" t="s">
+        <v>202</v>
+      </c>
+      <c r="B65" t="s">
+        <v>460</v>
       </c>
       <c r="C65" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>67</v>
+      <c r="A66" t="s">
+        <v>203</v>
+      </c>
+      <c r="B66" t="s">
+        <v>461</v>
       </c>
       <c r="C66" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>68</v>
+      <c r="A67" t="s">
+        <v>204</v>
+      </c>
+      <c r="B67" t="s">
+        <v>462</v>
       </c>
       <c r="C67" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>69</v>
+      <c r="A68" t="s">
+        <v>205</v>
+      </c>
+      <c r="B68" t="s">
+        <v>463</v>
       </c>
       <c r="C68" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>70</v>
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>464</v>
       </c>
       <c r="C69" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>71</v>
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>465</v>
       </c>
       <c r="C70" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>72</v>
+      <c r="A71" t="s">
+        <v>206</v>
+      </c>
+      <c r="B71" t="s">
+        <v>466</v>
       </c>
       <c r="C71" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>73</v>
+      <c r="A72" t="s">
+        <v>207</v>
+      </c>
+      <c r="B72" t="s">
+        <v>467</v>
       </c>
       <c r="C72" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>74</v>
+      <c r="A73" t="s">
+        <v>208</v>
+      </c>
+      <c r="B73" t="s">
+        <v>468</v>
       </c>
       <c r="C73" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>75</v>
+      <c r="A74" t="s">
+        <v>209</v>
+      </c>
+      <c r="B74" t="s">
+        <v>469</v>
       </c>
       <c r="C74" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>76</v>
+      <c r="A75" t="s">
+        <v>210</v>
+      </c>
+      <c r="B75" t="s">
+        <v>470</v>
       </c>
       <c r="C75" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>77</v>
+      <c r="A76" t="s">
+        <v>210</v>
+      </c>
+      <c r="B76" t="s">
+        <v>471</v>
       </c>
       <c r="C76" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>78</v>
+      <c r="A77" t="s">
+        <v>211</v>
+      </c>
+      <c r="B77" t="s">
+        <v>472</v>
       </c>
       <c r="C77" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>79</v>
+      <c r="A78" t="s">
+        <v>212</v>
+      </c>
+      <c r="B78" t="s">
+        <v>473</v>
       </c>
       <c r="C78" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>80</v>
+      <c r="A79" t="s">
+        <v>212</v>
+      </c>
+      <c r="B79" t="s">
+        <v>474</v>
       </c>
       <c r="C79" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>81</v>
+      <c r="A80" t="s">
+        <v>213</v>
+      </c>
+      <c r="B80" t="s">
+        <v>475</v>
       </c>
       <c r="C80" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>82</v>
+      <c r="A81" t="s">
+        <v>214</v>
+      </c>
+      <c r="B81" t="s">
+        <v>476</v>
       </c>
       <c r="C81" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>83</v>
+      <c r="A82" t="s">
+        <v>215</v>
+      </c>
+      <c r="B82" t="s">
+        <v>477</v>
       </c>
       <c r="C82" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>84</v>
+      <c r="A83" t="s">
+        <v>216</v>
+      </c>
+      <c r="B83" t="s">
+        <v>478</v>
       </c>
       <c r="C83" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>85</v>
+      <c r="A84" t="s">
+        <v>217</v>
+      </c>
+      <c r="B84" t="s">
+        <v>479</v>
       </c>
       <c r="C84" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>86</v>
+      <c r="A85" t="s">
+        <v>217</v>
+      </c>
+      <c r="B85" t="s">
+        <v>480</v>
       </c>
       <c r="C85" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>87</v>
+      <c r="A86" t="s">
+        <v>218</v>
+      </c>
+      <c r="B86" t="s">
+        <v>481</v>
       </c>
       <c r="C86" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>88</v>
+      <c r="A87" t="s">
+        <v>16</v>
+      </c>
+      <c r="B87" t="s">
+        <v>482</v>
       </c>
       <c r="C87" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>89</v>
+      <c r="A88" t="s">
+        <v>219</v>
+      </c>
+      <c r="B88" t="s">
+        <v>483</v>
       </c>
       <c r="C88" t="s">
-        <v>111</v>
+        <v>146</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
-        <v>90</v>
+      <c r="A89" t="s">
+        <v>219</v>
+      </c>
+      <c r="B89" t="s">
+        <v>484</v>
       </c>
       <c r="C89" t="s">
-        <v>111</v>
+        <v>146</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>91</v>
+      <c r="A90" t="s">
+        <v>17</v>
+      </c>
+      <c r="B90" t="s">
+        <v>485</v>
       </c>
       <c r="C90" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>92</v>
+      <c r="A91" t="s">
+        <v>220</v>
+      </c>
+      <c r="B91" t="s">
+        <v>486</v>
       </c>
       <c r="C91" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>93</v>
+      <c r="A92" t="s">
+        <v>220</v>
+      </c>
+      <c r="B92" t="s">
+        <v>487</v>
       </c>
       <c r="C92" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>94</v>
+      <c r="A93" t="s">
+        <v>220</v>
+      </c>
+      <c r="B93" t="s">
+        <v>488</v>
       </c>
       <c r="C93" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
-        <v>95</v>
+      <c r="A94" t="s">
+        <v>221</v>
+      </c>
+      <c r="B94" t="s">
+        <v>489</v>
       </c>
       <c r="C94" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>96</v>
+      <c r="A95" t="s">
+        <v>222</v>
+      </c>
+      <c r="B95" t="s">
+        <v>490</v>
       </c>
       <c r="C95" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>97</v>
+      <c r="A96" t="s">
+        <v>18</v>
+      </c>
+      <c r="B96" t="s">
+        <v>491</v>
       </c>
       <c r="C96" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
-        <v>98</v>
+      <c r="A97" t="s">
+        <v>223</v>
+      </c>
+      <c r="B97" t="s">
+        <v>492</v>
       </c>
       <c r="C97" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>99</v>
+      <c r="A98" t="s">
+        <v>224</v>
+      </c>
+      <c r="B98" t="s">
+        <v>493</v>
       </c>
       <c r="C98" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>100</v>
+      <c r="A99" t="s">
+        <v>225</v>
+      </c>
+      <c r="B99" t="s">
+        <v>494</v>
       </c>
       <c r="C99" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>101</v>
+      <c r="A100" t="s">
+        <v>226</v>
+      </c>
+      <c r="B100" t="s">
+        <v>495</v>
       </c>
       <c r="C100" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>102</v>
+      <c r="A101" t="s">
+        <v>227</v>
+      </c>
+      <c r="B101" t="s">
+        <v>496</v>
       </c>
       <c r="C101" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
-        <v>103</v>
+      <c r="A102" t="s">
+        <v>227</v>
+      </c>
+      <c r="B102" t="s">
+        <v>497</v>
       </c>
       <c r="C102" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
-        <v>104</v>
+      <c r="A103" t="s">
+        <v>228</v>
+      </c>
+      <c r="B103" t="s">
+        <v>498</v>
       </c>
       <c r="C103" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
-        <v>105</v>
+      <c r="A104" t="s">
+        <v>229</v>
+      </c>
+      <c r="B104" t="s">
+        <v>499</v>
       </c>
       <c r="C104" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
+      <c r="A105" t="s">
+        <v>19</v>
+      </c>
+      <c r="B105" t="s">
+        <v>500</v>
+      </c>
+      <c r="C105" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>19</v>
+      </c>
+      <c r="B106" t="s">
+        <v>501</v>
+      </c>
+      <c r="C106" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>230</v>
+      </c>
+      <c r="B107" t="s">
+        <v>502</v>
+      </c>
+      <c r="C107" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>230</v>
+      </c>
+      <c r="B108" t="s">
+        <v>503</v>
+      </c>
+      <c r="C108" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>20</v>
+      </c>
+      <c r="B109" t="s">
+        <v>504</v>
+      </c>
+      <c r="C109" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>231</v>
+      </c>
+      <c r="B110" t="s">
+        <v>505</v>
+      </c>
+      <c r="C110" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>231</v>
+      </c>
+      <c r="B111" t="s">
+        <v>506</v>
+      </c>
+      <c r="C111" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>21</v>
+      </c>
+      <c r="B112" t="s">
+        <v>507</v>
+      </c>
+      <c r="C112" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>232</v>
+      </c>
+      <c r="B113" t="s">
+        <v>508</v>
+      </c>
+      <c r="C113" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>232</v>
+      </c>
+      <c r="B114" t="s">
+        <v>509</v>
+      </c>
+      <c r="C114" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>233</v>
+      </c>
+      <c r="B115" t="s">
+        <v>510</v>
+      </c>
+      <c r="C115" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>234</v>
+      </c>
+      <c r="B116" t="s">
+        <v>511</v>
+      </c>
+      <c r="C116" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>235</v>
+      </c>
+      <c r="B117" t="s">
+        <v>512</v>
+      </c>
+      <c r="C117" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>236</v>
+      </c>
+      <c r="B118" t="s">
+        <v>513</v>
+      </c>
+      <c r="C118" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>236</v>
+      </c>
+      <c r="B119" t="s">
+        <v>514</v>
+      </c>
+      <c r="C119" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>237</v>
+      </c>
+      <c r="B120" t="s">
+        <v>515</v>
+      </c>
+      <c r="C120" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>22</v>
+      </c>
+      <c r="B121" t="s">
+        <v>516</v>
+      </c>
+      <c r="C121" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>238</v>
+      </c>
+      <c r="B122" t="s">
+        <v>517</v>
+      </c>
+      <c r="C122" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>239</v>
+      </c>
+      <c r="B123" t="s">
+        <v>518</v>
+      </c>
+      <c r="C123" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>240</v>
+      </c>
+      <c r="B124" t="s">
+        <v>519</v>
+      </c>
+      <c r="C124" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>241</v>
+      </c>
+      <c r="B125" t="s">
+        <v>520</v>
+      </c>
+      <c r="C125" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>241</v>
+      </c>
+      <c r="B126" t="s">
+        <v>521</v>
+      </c>
+      <c r="C126" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>242</v>
+      </c>
+      <c r="B127" t="s">
+        <v>522</v>
+      </c>
+      <c r="C127" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>242</v>
+      </c>
+      <c r="B128" t="s">
+        <v>523</v>
+      </c>
+      <c r="C128" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>243</v>
+      </c>
+      <c r="B129" t="s">
+        <v>524</v>
+      </c>
+      <c r="C129" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>244</v>
+      </c>
+      <c r="B130" t="s">
+        <v>525</v>
+      </c>
+      <c r="C130" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>245</v>
+      </c>
+      <c r="B131" t="s">
+        <v>526</v>
+      </c>
+      <c r="C131" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>23</v>
+      </c>
+      <c r="B132" t="s">
+        <v>527</v>
+      </c>
+      <c r="C132" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>246</v>
+      </c>
+      <c r="B133" t="s">
+        <v>528</v>
+      </c>
+      <c r="C133" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>246</v>
+      </c>
+      <c r="B134" t="s">
+        <v>529</v>
+      </c>
+      <c r="C134" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>247</v>
+      </c>
+      <c r="B135" t="s">
+        <v>530</v>
+      </c>
+      <c r="C135" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>248</v>
+      </c>
+      <c r="B136" t="s">
+        <v>531</v>
+      </c>
+      <c r="C136" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>249</v>
+      </c>
+      <c r="B137" t="s">
+        <v>532</v>
+      </c>
+      <c r="C137" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>250</v>
+      </c>
+      <c r="B138" t="s">
+        <v>533</v>
+      </c>
+      <c r="C138" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>24</v>
+      </c>
+      <c r="B139" t="s">
+        <v>534</v>
+      </c>
+      <c r="C139" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>25</v>
+      </c>
+      <c r="B140" t="s">
+        <v>535</v>
+      </c>
+      <c r="C140" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>25</v>
+      </c>
+      <c r="B141" t="s">
+        <v>536</v>
+      </c>
+      <c r="C141" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>251</v>
+      </c>
+      <c r="B142" t="s">
+        <v>537</v>
+      </c>
+      <c r="C142" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>252</v>
+      </c>
+      <c r="B143" t="s">
+        <v>538</v>
+      </c>
+      <c r="C143" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>252</v>
+      </c>
+      <c r="B144" t="s">
+        <v>539</v>
+      </c>
+      <c r="C144" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>253</v>
+      </c>
+      <c r="B145" t="s">
+        <v>540</v>
+      </c>
+      <c r="C145" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>254</v>
+      </c>
+      <c r="B146" t="s">
+        <v>541</v>
+      </c>
+      <c r="C146" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>255</v>
+      </c>
+      <c r="B147" t="s">
+        <v>542</v>
+      </c>
+      <c r="C147" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>26</v>
+      </c>
+      <c r="B148" t="s">
+        <v>543</v>
+      </c>
+      <c r="C148" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>256</v>
+      </c>
+      <c r="B149" t="s">
+        <v>544</v>
+      </c>
+      <c r="C149" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>257</v>
+      </c>
+      <c r="B150" t="s">
+        <v>545</v>
+      </c>
+      <c r="C150" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>258</v>
+      </c>
+      <c r="B151" t="s">
+        <v>546</v>
+      </c>
+      <c r="C151" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>259</v>
+      </c>
+      <c r="B152" t="s">
+        <v>547</v>
+      </c>
+      <c r="C152" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>260</v>
+      </c>
+      <c r="B153" t="s">
+        <v>548</v>
+      </c>
+      <c r="C153" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>27</v>
+      </c>
+      <c r="B154" t="s">
+        <v>549</v>
+      </c>
+      <c r="C154" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>261</v>
+      </c>
+      <c r="B155" t="s">
+        <v>550</v>
+      </c>
+      <c r="C155" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>262</v>
+      </c>
+      <c r="B156" t="s">
+        <v>551</v>
+      </c>
+      <c r="C156" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>262</v>
+      </c>
+      <c r="B157" t="s">
+        <v>552</v>
+      </c>
+      <c r="C157" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>263</v>
+      </c>
+      <c r="B158" t="s">
+        <v>553</v>
+      </c>
+      <c r="C158" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>264</v>
+      </c>
+      <c r="B159" t="s">
+        <v>554</v>
+      </c>
+      <c r="C159" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>28</v>
+      </c>
+      <c r="B160" t="s">
+        <v>555</v>
+      </c>
+      <c r="C160" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>265</v>
+      </c>
+      <c r="B161" t="s">
+        <v>556</v>
+      </c>
+      <c r="C161" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>266</v>
+      </c>
+      <c r="B162" t="s">
+        <v>557</v>
+      </c>
+      <c r="C162" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>267</v>
+      </c>
+      <c r="B163" t="s">
+        <v>558</v>
+      </c>
+      <c r="C163" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>267</v>
+      </c>
+      <c r="B164" t="s">
+        <v>559</v>
+      </c>
+      <c r="C164" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>268</v>
+      </c>
+      <c r="B165" t="s">
+        <v>560</v>
+      </c>
+      <c r="C165" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>269</v>
+      </c>
+      <c r="B166" t="s">
+        <v>561</v>
+      </c>
+      <c r="C166" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>270</v>
+      </c>
+      <c r="B167" t="s">
+        <v>562</v>
+      </c>
+      <c r="C167" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>271</v>
+      </c>
+      <c r="B168" t="s">
+        <v>563</v>
+      </c>
+      <c r="C168" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>272</v>
+      </c>
+      <c r="B169" t="s">
+        <v>564</v>
+      </c>
+      <c r="C169" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>273</v>
+      </c>
+      <c r="B170" t="s">
+        <v>565</v>
+      </c>
+      <c r="C170" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>274</v>
+      </c>
+      <c r="B171" t="s">
+        <v>566</v>
+      </c>
+      <c r="C171" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>275</v>
+      </c>
+      <c r="B172" t="s">
+        <v>567</v>
+      </c>
+      <c r="C172" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>276</v>
+      </c>
+      <c r="B173" t="s">
+        <v>568</v>
+      </c>
+      <c r="C173" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>277</v>
+      </c>
+      <c r="B174" t="s">
+        <v>569</v>
+      </c>
+      <c r="C174" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>277</v>
+      </c>
+      <c r="B175" t="s">
+        <v>570</v>
+      </c>
+      <c r="C175" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>278</v>
+      </c>
+      <c r="B176" t="s">
+        <v>571</v>
+      </c>
+      <c r="C176" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>279</v>
+      </c>
+      <c r="B177" t="s">
+        <v>572</v>
+      </c>
+      <c r="C177" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>279</v>
+      </c>
+      <c r="B178" t="s">
+        <v>573</v>
+      </c>
+      <c r="C178" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>280</v>
+      </c>
+      <c r="B179" t="s">
+        <v>574</v>
+      </c>
+      <c r="C179" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>281</v>
+      </c>
+      <c r="B180" t="s">
+        <v>575</v>
+      </c>
+      <c r="C180" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>282</v>
+      </c>
+      <c r="B181" t="s">
+        <v>576</v>
+      </c>
+      <c r="C181" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>282</v>
+      </c>
+      <c r="B182" t="s">
+        <v>577</v>
+      </c>
+      <c r="C182" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>283</v>
+      </c>
+      <c r="B183" t="s">
+        <v>578</v>
+      </c>
+      <c r="C183" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>284</v>
+      </c>
+      <c r="B184" t="s">
+        <v>579</v>
+      </c>
+      <c r="C184" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>284</v>
+      </c>
+      <c r="B185" t="s">
+        <v>580</v>
+      </c>
+      <c r="C185" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>285</v>
+      </c>
+      <c r="B186" t="s">
+        <v>581</v>
+      </c>
+      <c r="C186" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>285</v>
+      </c>
+      <c r="B187" t="s">
+        <v>582</v>
+      </c>
+      <c r="C187" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>29</v>
+      </c>
+      <c r="B188" t="s">
+        <v>583</v>
+      </c>
+      <c r="C188" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>29</v>
+      </c>
+      <c r="B189" t="s">
+        <v>584</v>
+      </c>
+      <c r="C189" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>286</v>
+      </c>
+      <c r="B190" t="s">
+        <v>585</v>
+      </c>
+      <c r="C190" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>287</v>
+      </c>
+      <c r="B191" t="s">
+        <v>586</v>
+      </c>
+      <c r="C191" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>288</v>
+      </c>
+      <c r="B192" t="s">
+        <v>587</v>
+      </c>
+      <c r="C192" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>288</v>
+      </c>
+      <c r="B193" t="s">
+        <v>588</v>
+      </c>
+      <c r="C193" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>289</v>
+      </c>
+      <c r="B194" t="s">
+        <v>589</v>
+      </c>
+      <c r="C194" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>290</v>
+      </c>
+      <c r="B195" t="s">
+        <v>590</v>
+      </c>
+      <c r="C195" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>30</v>
+      </c>
+      <c r="B196" t="s">
+        <v>591</v>
+      </c>
+      <c r="C196" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>30</v>
+      </c>
+      <c r="B197" t="s">
+        <v>592</v>
+      </c>
+      <c r="C197" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>291</v>
+      </c>
+      <c r="B198" t="s">
+        <v>593</v>
+      </c>
+      <c r="C198" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>292</v>
+      </c>
+      <c r="B199" t="s">
+        <v>594</v>
+      </c>
+      <c r="C199" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>292</v>
+      </c>
+      <c r="B200" t="s">
+        <v>595</v>
+      </c>
+      <c r="C200" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>293</v>
+      </c>
+      <c r="B201" t="s">
+        <v>596</v>
+      </c>
+      <c r="C201" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>31</v>
+      </c>
+      <c r="B202" t="s">
+        <v>597</v>
+      </c>
+      <c r="C202" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>294</v>
+      </c>
+      <c r="B203" t="s">
+        <v>598</v>
+      </c>
+      <c r="C203" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>295</v>
+      </c>
+      <c r="B204" t="s">
+        <v>599</v>
+      </c>
+      <c r="C204" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>296</v>
+      </c>
+      <c r="B205" t="s">
+        <v>600</v>
+      </c>
+      <c r="C205" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>297</v>
+      </c>
+      <c r="B206" t="s">
+        <v>601</v>
+      </c>
+      <c r="C206" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>298</v>
+      </c>
+      <c r="B207" t="s">
+        <v>602</v>
+      </c>
+      <c r="C207" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>32</v>
+      </c>
+      <c r="B208" t="s">
+        <v>603</v>
+      </c>
+      <c r="C208" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>32</v>
+      </c>
+      <c r="B209" t="s">
+        <v>604</v>
+      </c>
+      <c r="C209" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>299</v>
+      </c>
+      <c r="B210" t="s">
+        <v>605</v>
+      </c>
+      <c r="C210" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>299</v>
+      </c>
+      <c r="B211" t="s">
+        <v>606</v>
+      </c>
+      <c r="C211" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>300</v>
+      </c>
+      <c r="B212" t="s">
+        <v>607</v>
+      </c>
+      <c r="C212" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>300</v>
+      </c>
+      <c r="B213" t="s">
+        <v>608</v>
+      </c>
+      <c r="C213" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>33</v>
+      </c>
+      <c r="B214" t="s">
+        <v>609</v>
+      </c>
+      <c r="C214" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>301</v>
+      </c>
+      <c r="B215" t="s">
+        <v>610</v>
+      </c>
+      <c r="C215" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>302</v>
+      </c>
+      <c r="B216" t="s">
+        <v>611</v>
+      </c>
+      <c r="C216" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>303</v>
+      </c>
+      <c r="B217" t="s">
+        <v>612</v>
+      </c>
+      <c r="C217" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>303</v>
+      </c>
+      <c r="B218" t="s">
+        <v>613</v>
+      </c>
+      <c r="C218" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>304</v>
+      </c>
+      <c r="B219" t="s">
+        <v>614</v>
+      </c>
+      <c r="C219" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>305</v>
+      </c>
+      <c r="B220" t="s">
+        <v>615</v>
+      </c>
+      <c r="C220" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>305</v>
+      </c>
+      <c r="B221" t="s">
+        <v>616</v>
+      </c>
+      <c r="C221" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>306</v>
+      </c>
+      <c r="B222" t="s">
+        <v>617</v>
+      </c>
+      <c r="C222" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>307</v>
+      </c>
+      <c r="B223" t="s">
+        <v>618</v>
+      </c>
+      <c r="C223" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>308</v>
+      </c>
+      <c r="B224" t="s">
+        <v>619</v>
+      </c>
+      <c r="C224" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>309</v>
+      </c>
+      <c r="B225" t="s">
+        <v>620</v>
+      </c>
+      <c r="C225" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>310</v>
+      </c>
+      <c r="B226" t="s">
+        <v>621</v>
+      </c>
+      <c r="C226" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>34</v>
+      </c>
+      <c r="B227" t="s">
+        <v>622</v>
+      </c>
+      <c r="C227" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>311</v>
+      </c>
+      <c r="B228" t="s">
+        <v>623</v>
+      </c>
+      <c r="C228" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>312</v>
+      </c>
+      <c r="B229" t="s">
+        <v>624</v>
+      </c>
+      <c r="C229" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>35</v>
+      </c>
+      <c r="B230" t="s">
+        <v>625</v>
+      </c>
+      <c r="C230" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>35</v>
+      </c>
+      <c r="B231" t="s">
+        <v>626</v>
+      </c>
+      <c r="C231" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>313</v>
+      </c>
+      <c r="B232" t="s">
+        <v>627</v>
+      </c>
+      <c r="C232" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>314</v>
+      </c>
+      <c r="B233" t="s">
+        <v>628</v>
+      </c>
+      <c r="C233" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>36</v>
+      </c>
+      <c r="B234" t="s">
+        <v>629</v>
+      </c>
+      <c r="C234" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>315</v>
+      </c>
+      <c r="B235" t="s">
+        <v>630</v>
+      </c>
+      <c r="C235" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>315</v>
+      </c>
+      <c r="B236" t="s">
+        <v>631</v>
+      </c>
+      <c r="C236" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>315</v>
+      </c>
+      <c r="B237" t="s">
+        <v>632</v>
+      </c>
+      <c r="C237" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>316</v>
+      </c>
+      <c r="B238" t="s">
+        <v>633</v>
+      </c>
+      <c r="C238" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>317</v>
+      </c>
+      <c r="B239" t="s">
+        <v>634</v>
+      </c>
+      <c r="C239" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>318</v>
+      </c>
+      <c r="B240" t="s">
+        <v>635</v>
+      </c>
+      <c r="C240" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>319</v>
+      </c>
+      <c r="B241" t="s">
+        <v>636</v>
+      </c>
+      <c r="C241" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>320</v>
+      </c>
+      <c r="B242" t="s">
+        <v>637</v>
+      </c>
+      <c r="C242" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>321</v>
+      </c>
+      <c r="B243" t="s">
+        <v>638</v>
+      </c>
+      <c r="C243" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>322</v>
+      </c>
+      <c r="B244" t="s">
+        <v>639</v>
+      </c>
+      <c r="C244" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>323</v>
+      </c>
+      <c r="B245" t="s">
+        <v>640</v>
+      </c>
+      <c r="C245" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>324</v>
+      </c>
+      <c r="B246" t="s">
+        <v>641</v>
+      </c>
+      <c r="C246" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>325</v>
+      </c>
+      <c r="B247" t="s">
+        <v>642</v>
+      </c>
+      <c r="C247" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>37</v>
+      </c>
+      <c r="B248" t="s">
+        <v>643</v>
+      </c>
+      <c r="C248" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>37</v>
+      </c>
+      <c r="B249" t="s">
+        <v>644</v>
+      </c>
+      <c r="C249" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>37</v>
+      </c>
+      <c r="B250" t="s">
+        <v>645</v>
+      </c>
+      <c r="C250" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>38</v>
+      </c>
+      <c r="B251" t="s">
+        <v>646</v>
+      </c>
+      <c r="C251" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>326</v>
+      </c>
+      <c r="B252" t="s">
+        <v>647</v>
+      </c>
+      <c r="C252" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>326</v>
+      </c>
+      <c r="B253" t="s">
+        <v>648</v>
+      </c>
+      <c r="C253" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>327</v>
+      </c>
+      <c r="B254" t="s">
+        <v>649</v>
+      </c>
+      <c r="C254" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>39</v>
+      </c>
+      <c r="B255" t="s">
+        <v>650</v>
+      </c>
+      <c r="C255" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>328</v>
+      </c>
+      <c r="B256" t="s">
+        <v>651</v>
+      </c>
+      <c r="C256" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>40</v>
+      </c>
+      <c r="B257" t="s">
+        <v>652</v>
+      </c>
+      <c r="C257" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>40</v>
+      </c>
+      <c r="B258" t="s">
+        <v>653</v>
+      </c>
+      <c r="C258" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>41</v>
+      </c>
+      <c r="B259" t="s">
+        <v>654</v>
+      </c>
+      <c r="C259" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>42</v>
+      </c>
+      <c r="B260" t="s">
+        <v>655</v>
+      </c>
+      <c r="C260" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>43</v>
+      </c>
+      <c r="B261" t="s">
+        <v>656</v>
+      </c>
+      <c r="C261" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>43</v>
+      </c>
+      <c r="B262" t="s">
+        <v>657</v>
+      </c>
+      <c r="C262" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>43</v>
+      </c>
+      <c r="B263" t="s">
+        <v>658</v>
+      </c>
+      <c r="C263" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>44</v>
+      </c>
+      <c r="B264" t="s">
+        <v>659</v>
+      </c>
+      <c r="C264" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>44</v>
+      </c>
+      <c r="B265" t="s">
+        <v>660</v>
+      </c>
+      <c r="C265" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>45</v>
+      </c>
+      <c r="B266" t="s">
+        <v>661</v>
+      </c>
+      <c r="C266" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>45</v>
+      </c>
+      <c r="B267" t="s">
+        <v>662</v>
+      </c>
+      <c r="C267" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>46</v>
+      </c>
+      <c r="B268" t="s">
+        <v>663</v>
+      </c>
+      <c r="C268" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>329</v>
+      </c>
+      <c r="B269" t="s">
+        <v>664</v>
+      </c>
+      <c r="C269" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>47</v>
+      </c>
+      <c r="B270" t="s">
+        <v>665</v>
+      </c>
+      <c r="C270" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>48</v>
+      </c>
+      <c r="B271" t="s">
+        <v>666</v>
+      </c>
+      <c r="C271" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>49</v>
+      </c>
+      <c r="B272" t="s">
+        <v>667</v>
+      </c>
+      <c r="C272" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>49</v>
+      </c>
+      <c r="B273" t="s">
+        <v>668</v>
+      </c>
+      <c r="C273" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>50</v>
+      </c>
+      <c r="B274" t="s">
+        <v>669</v>
+      </c>
+      <c r="C274" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>50</v>
+      </c>
+      <c r="B275" t="s">
+        <v>670</v>
+      </c>
+      <c r="C275" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>51</v>
+      </c>
+      <c r="B276" t="s">
+        <v>671</v>
+      </c>
+      <c r="C276" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>52</v>
+      </c>
+      <c r="B277" t="s">
+        <v>672</v>
+      </c>
+      <c r="C277" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>53</v>
+      </c>
+      <c r="B278" t="s">
+        <v>673</v>
+      </c>
+      <c r="C278" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>54</v>
+      </c>
+      <c r="B279" t="s">
+        <v>674</v>
+      </c>
+      <c r="C279" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>54</v>
+      </c>
+      <c r="B280" t="s">
+        <v>675</v>
+      </c>
+      <c r="C280" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>55</v>
+      </c>
+      <c r="B281" t="s">
+        <v>676</v>
+      </c>
+      <c r="C281" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>55</v>
+      </c>
+      <c r="B282" t="s">
+        <v>677</v>
+      </c>
+      <c r="C282" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>56</v>
+      </c>
+      <c r="B283" t="s">
+        <v>678</v>
+      </c>
+      <c r="C283" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>57</v>
+      </c>
+      <c r="B284" t="s">
+        <v>679</v>
+      </c>
+      <c r="C284" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>58</v>
+      </c>
+      <c r="B285" t="s">
+        <v>680</v>
+      </c>
+      <c r="C285" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>59</v>
+      </c>
+      <c r="B286" t="s">
+        <v>681</v>
+      </c>
+      <c r="C286" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>60</v>
+      </c>
+      <c r="B287" t="s">
+        <v>682</v>
+      </c>
+      <c r="C287" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>61</v>
+      </c>
+      <c r="B288" t="s">
+        <v>683</v>
+      </c>
+      <c r="C288" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>330</v>
+      </c>
+      <c r="B289" t="s">
+        <v>684</v>
+      </c>
+      <c r="C289" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>62</v>
+      </c>
+      <c r="B290" t="s">
+        <v>685</v>
+      </c>
+      <c r="C290" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>331</v>
+      </c>
+      <c r="B291" t="s">
+        <v>686</v>
+      </c>
+      <c r="C291" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>63</v>
+      </c>
+      <c r="B292" t="s">
+        <v>687</v>
+      </c>
+      <c r="C292" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>64</v>
+      </c>
+      <c r="B293" t="s">
+        <v>688</v>
+      </c>
+      <c r="C293" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>64</v>
+      </c>
+      <c r="B294" t="s">
+        <v>689</v>
+      </c>
+      <c r="C294" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>65</v>
+      </c>
+      <c r="B295" t="s">
+        <v>690</v>
+      </c>
+      <c r="C295" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>65</v>
+      </c>
+      <c r="B296" t="s">
+        <v>691</v>
+      </c>
+      <c r="C296" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>65</v>
+      </c>
+      <c r="B297" t="s">
+        <v>692</v>
+      </c>
+      <c r="C297" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>66</v>
+      </c>
+      <c r="B298" t="s">
+        <v>693</v>
+      </c>
+      <c r="C298" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>67</v>
+      </c>
+      <c r="B299" t="s">
+        <v>694</v>
+      </c>
+      <c r="C299" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>67</v>
+      </c>
+      <c r="B300" t="s">
+        <v>695</v>
+      </c>
+      <c r="C300" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>68</v>
+      </c>
+      <c r="B301" t="s">
+        <v>696</v>
+      </c>
+      <c r="C301" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>68</v>
+      </c>
+      <c r="B302" t="s">
+        <v>697</v>
+      </c>
+      <c r="C302" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>332</v>
+      </c>
+      <c r="B303" t="s">
+        <v>698</v>
+      </c>
+      <c r="C303" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>69</v>
+      </c>
+      <c r="B304" t="s">
+        <v>699</v>
+      </c>
+      <c r="C304" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>70</v>
+      </c>
+      <c r="B305" t="s">
+        <v>700</v>
+      </c>
+      <c r="C305" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>71</v>
+      </c>
+      <c r="B306" t="s">
+        <v>701</v>
+      </c>
+      <c r="C306" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>333</v>
+      </c>
+      <c r="B307" t="s">
+        <v>702</v>
+      </c>
+      <c r="C307" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>72</v>
+      </c>
+      <c r="B308" t="s">
+        <v>703</v>
+      </c>
+      <c r="C308" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>73</v>
+      </c>
+      <c r="B309" t="s">
+        <v>704</v>
+      </c>
+      <c r="C309" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>74</v>
+      </c>
+      <c r="B310" t="s">
+        <v>705</v>
+      </c>
+      <c r="C310" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>334</v>
+      </c>
+      <c r="B311" t="s">
+        <v>706</v>
+      </c>
+      <c r="C311" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>75</v>
+      </c>
+      <c r="B312" t="s">
+        <v>707</v>
+      </c>
+      <c r="C312" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>76</v>
+      </c>
+      <c r="B313" t="s">
+        <v>708</v>
+      </c>
+      <c r="C313" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>76</v>
+      </c>
+      <c r="B314" t="s">
+        <v>709</v>
+      </c>
+      <c r="C314" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>77</v>
+      </c>
+      <c r="B315" t="s">
+        <v>710</v>
+      </c>
+      <c r="C315" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>77</v>
+      </c>
+      <c r="B316" t="s">
+        <v>711</v>
+      </c>
+      <c r="C316" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>78</v>
+      </c>
+      <c r="B317" t="s">
+        <v>712</v>
+      </c>
+      <c r="C317" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>79</v>
+      </c>
+      <c r="B318" t="s">
+        <v>713</v>
+      </c>
+      <c r="C318" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>80</v>
+      </c>
+      <c r="B319" t="s">
+        <v>714</v>
+      </c>
+      <c r="C319" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>81</v>
+      </c>
+      <c r="B320" t="s">
+        <v>715</v>
+      </c>
+      <c r="C320" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>82</v>
+      </c>
+      <c r="B321" t="s">
+        <v>716</v>
+      </c>
+      <c r="C321" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>83</v>
+      </c>
+      <c r="B322" t="s">
+        <v>717</v>
+      </c>
+      <c r="C322" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>84</v>
+      </c>
+      <c r="B323" t="s">
+        <v>718</v>
+      </c>
+      <c r="C323" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>85</v>
+      </c>
+      <c r="B324" t="s">
+        <v>719</v>
+      </c>
+      <c r="C324" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>86</v>
+      </c>
+      <c r="B325" t="s">
+        <v>720</v>
+      </c>
+      <c r="C325" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>87</v>
+      </c>
+      <c r="B326" t="s">
+        <v>721</v>
+      </c>
+      <c r="C326" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A327" t="s">
+        <v>88</v>
+      </c>
+      <c r="B327" t="s">
+        <v>722</v>
+      </c>
+      <c r="C327" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>89</v>
+      </c>
+      <c r="B328" t="s">
+        <v>723</v>
+      </c>
+      <c r="C328" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A329" t="s">
+        <v>89</v>
+      </c>
+      <c r="B329" t="s">
+        <v>724</v>
+      </c>
+      <c r="C329" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A330" t="s">
+        <v>90</v>
+      </c>
+      <c r="B330" t="s">
+        <v>725</v>
+      </c>
+      <c r="C330" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A331" t="s">
+        <v>335</v>
+      </c>
+      <c r="B331" t="s">
+        <v>726</v>
+      </c>
+      <c r="C331" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A332" t="s">
+        <v>91</v>
+      </c>
+      <c r="B332" t="s">
+        <v>727</v>
+      </c>
+      <c r="C332" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A333" t="s">
+        <v>336</v>
+      </c>
+      <c r="B333" t="s">
+        <v>728</v>
+      </c>
+      <c r="C333" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A334" t="s">
+        <v>92</v>
+      </c>
+      <c r="B334" t="s">
+        <v>729</v>
+      </c>
+      <c r="C334" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A335" t="s">
+        <v>93</v>
+      </c>
+      <c r="B335" t="s">
+        <v>730</v>
+      </c>
+      <c r="C335" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A336" t="s">
+        <v>93</v>
+      </c>
+      <c r="B336" t="s">
+        <v>731</v>
+      </c>
+      <c r="C336" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A337" t="s">
+        <v>93</v>
+      </c>
+      <c r="B337" t="s">
+        <v>732</v>
+      </c>
+      <c r="C337" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A338" t="s">
+        <v>94</v>
+      </c>
+      <c r="B338" t="s">
+        <v>733</v>
+      </c>
+      <c r="C338" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A339" t="s">
+        <v>337</v>
+      </c>
+      <c r="B339" t="s">
+        <v>734</v>
+      </c>
+      <c r="C339" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A340" t="s">
+        <v>337</v>
+      </c>
+      <c r="B340" t="s">
+        <v>735</v>
+      </c>
+      <c r="C340" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A341" t="s">
+        <v>338</v>
+      </c>
+      <c r="B341" t="s">
+        <v>736</v>
+      </c>
+      <c r="C341" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A342" t="s">
+        <v>95</v>
+      </c>
+      <c r="B342" t="s">
+        <v>737</v>
+      </c>
+      <c r="C342" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A343" t="s">
+        <v>96</v>
+      </c>
+      <c r="B343" t="s">
+        <v>738</v>
+      </c>
+      <c r="C343" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A344" t="s">
+        <v>97</v>
+      </c>
+      <c r="B344" t="s">
+        <v>739</v>
+      </c>
+      <c r="C344" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A345" t="s">
+        <v>339</v>
+      </c>
+      <c r="B345" t="s">
+        <v>740</v>
+      </c>
+      <c r="C345" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A346" t="s">
+        <v>98</v>
+      </c>
+      <c r="B346" t="s">
+        <v>741</v>
+      </c>
+      <c r="C346" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A347" t="s">
+        <v>99</v>
+      </c>
+      <c r="B347" t="s">
+        <v>742</v>
+      </c>
+      <c r="C347" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A348" t="s">
+        <v>100</v>
+      </c>
+      <c r="B348" t="s">
+        <v>743</v>
+      </c>
+      <c r="C348" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A349" t="s">
+        <v>340</v>
+      </c>
+      <c r="B349" t="s">
+        <v>744</v>
+      </c>
+      <c r="C349" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A350" t="s">
+        <v>101</v>
+      </c>
+      <c r="B350" t="s">
+        <v>745</v>
+      </c>
+      <c r="C350" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A351" t="s">
+        <v>341</v>
+      </c>
+      <c r="B351" t="s">
+        <v>746</v>
+      </c>
+      <c r="C351" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A352" t="s">
+        <v>102</v>
+      </c>
+      <c r="B352" t="s">
+        <v>747</v>
+      </c>
+      <c r="C352" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A353" t="s">
+        <v>103</v>
+      </c>
+      <c r="B353" t="s">
+        <v>748</v>
+      </c>
+      <c r="C353" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A354" t="s">
+        <v>103</v>
+      </c>
+      <c r="B354" t="s">
+        <v>749</v>
+      </c>
+      <c r="C354" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A355" t="s">
+        <v>342</v>
+      </c>
+      <c r="B355" t="s">
+        <v>750</v>
+      </c>
+      <c r="C355" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A356" t="s">
+        <v>104</v>
+      </c>
+      <c r="B356" t="s">
+        <v>751</v>
+      </c>
+      <c r="C356" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A357" t="s">
+        <v>343</v>
+      </c>
+      <c r="B357" t="s">
+        <v>752</v>
+      </c>
+      <c r="C357" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A358" t="s">
+        <v>344</v>
+      </c>
+      <c r="B358" t="s">
+        <v>753</v>
+      </c>
+      <c r="C358" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A359" t="s">
+        <v>345</v>
+      </c>
+      <c r="B359" t="s">
+        <v>754</v>
+      </c>
+      <c r="C359" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A360" t="s">
+        <v>345</v>
+      </c>
+      <c r="B360" t="s">
+        <v>755</v>
+      </c>
+      <c r="C360" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A361" t="s">
+        <v>105</v>
+      </c>
+      <c r="B361" t="s">
+        <v>756</v>
+      </c>
+      <c r="C361" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A362" t="s">
         <v>106</v>
       </c>
-      <c r="C105" t="s">
+      <c r="B362" t="s">
+        <v>757</v>
+      </c>
+      <c r="C362" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A363" t="s">
+        <v>107</v>
+      </c>
+      <c r="B363" t="s">
+        <v>758</v>
+      </c>
+      <c r="C363" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A364" t="s">
+        <v>346</v>
+      </c>
+      <c r="B364" t="s">
+        <v>759</v>
+      </c>
+      <c r="C364" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A365" t="s">
+        <v>347</v>
+      </c>
+      <c r="B365" t="s">
+        <v>760</v>
+      </c>
+      <c r="C365" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A366" t="s">
+        <v>108</v>
+      </c>
+      <c r="B366" t="s">
+        <v>761</v>
+      </c>
+      <c r="C366" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>348</v>
+      </c>
+      <c r="B367" t="s">
+        <v>762</v>
+      </c>
+      <c r="C367" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>109</v>
+      </c>
+      <c r="B368" t="s">
+        <v>763</v>
+      </c>
+      <c r="C368" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A369" t="s">
+        <v>349</v>
+      </c>
+      <c r="B369" t="s">
+        <v>764</v>
+      </c>
+      <c r="C369" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A370" t="s">
+        <v>350</v>
+      </c>
+      <c r="B370" t="s">
+        <v>765</v>
+      </c>
+      <c r="C370" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>351</v>
+      </c>
+      <c r="B371" t="s">
+        <v>766</v>
+      </c>
+      <c r="C371" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>352</v>
+      </c>
+      <c r="B372" t="s">
+        <v>767</v>
+      </c>
+      <c r="C372" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
+        <v>353</v>
+      </c>
+      <c r="B373" t="s">
+        <v>768</v>
+      </c>
+      <c r="C373" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A374" t="s">
+        <v>354</v>
+      </c>
+      <c r="B374" t="s">
+        <v>769</v>
+      </c>
+      <c r="C374" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A375" t="s">
+        <v>355</v>
+      </c>
+      <c r="B375" t="s">
+        <v>770</v>
+      </c>
+      <c r="C375" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A376" t="s">
+        <v>356</v>
+      </c>
+      <c r="B376" t="s">
+        <v>771</v>
+      </c>
+      <c r="C376" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A377" t="s">
+        <v>357</v>
+      </c>
+      <c r="B377" t="s">
+        <v>772</v>
+      </c>
+      <c r="C377" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A378" t="s">
+        <v>358</v>
+      </c>
+      <c r="B378" t="s">
+        <v>773</v>
+      </c>
+      <c r="C378" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A379" t="s">
+        <v>359</v>
+      </c>
+      <c r="B379" t="s">
+        <v>774</v>
+      </c>
+      <c r="C379" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A380" t="s">
+        <v>360</v>
+      </c>
+      <c r="B380" t="s">
+        <v>775</v>
+      </c>
+      <c r="C380" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A381" t="s">
+        <v>361</v>
+      </c>
+      <c r="B381" t="s">
+        <v>776</v>
+      </c>
+      <c r="C381" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A382" t="s">
+        <v>362</v>
+      </c>
+      <c r="B382" t="s">
+        <v>777</v>
+      </c>
+      <c r="C382" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A383" t="s">
+        <v>363</v>
+      </c>
+      <c r="B383" t="s">
+        <v>778</v>
+      </c>
+      <c r="C383" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A384" t="s">
+        <v>364</v>
+      </c>
+      <c r="B384" t="s">
+        <v>779</v>
+      </c>
+      <c r="C384" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A385" t="s">
+        <v>365</v>
+      </c>
+      <c r="B385" t="s">
+        <v>780</v>
+      </c>
+      <c r="C385" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A386" t="s">
+        <v>366</v>
+      </c>
+      <c r="B386" t="s">
+        <v>781</v>
+      </c>
+      <c r="C386" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A387" t="s">
+        <v>367</v>
+      </c>
+      <c r="B387" t="s">
+        <v>782</v>
+      </c>
+      <c r="C387" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A388" t="s">
+        <v>368</v>
+      </c>
+      <c r="B388" t="s">
+        <v>783</v>
+      </c>
+      <c r="C388" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A389" t="s">
+        <v>369</v>
+      </c>
+      <c r="B389" t="s">
+        <v>784</v>
+      </c>
+      <c r="C389" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A390" t="s">
+        <v>370</v>
+      </c>
+      <c r="B390" t="s">
+        <v>785</v>
+      </c>
+      <c r="C390" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A391" t="s">
+        <v>371</v>
+      </c>
+      <c r="B391" t="s">
+        <v>786</v>
+      </c>
+      <c r="C391" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A392" t="s">
+        <v>372</v>
+      </c>
+      <c r="B392" t="s">
+        <v>787</v>
+      </c>
+      <c r="C392" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A393" t="s">
+        <v>373</v>
+      </c>
+      <c r="B393" t="s">
+        <v>788</v>
+      </c>
+      <c r="C393" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A394" t="s">
+        <v>373</v>
+      </c>
+      <c r="B394" t="s">
+        <v>789</v>
+      </c>
+      <c r="C394" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A395" t="s">
+        <v>374</v>
+      </c>
+      <c r="B395" t="s">
+        <v>790</v>
+      </c>
+      <c r="C395" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A396" t="s">
+        <v>375</v>
+      </c>
+      <c r="B396" t="s">
+        <v>791</v>
+      </c>
+      <c r="C396" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A397" t="s">
+        <v>376</v>
+      </c>
+      <c r="B397" t="s">
+        <v>792</v>
+      </c>
+      <c r="C397" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A398" t="s">
+        <v>377</v>
+      </c>
+      <c r="B398" t="s">
+        <v>793</v>
+      </c>
+      <c r="C398" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C106" t="s">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A399" t="s">
+        <v>378</v>
+      </c>
+      <c r="B399" t="s">
+        <v>794</v>
+      </c>
+      <c r="C399" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A400" t="s">
+        <v>379</v>
+      </c>
+      <c r="B400" t="s">
+        <v>795</v>
+      </c>
+      <c r="C400" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A401" t="s">
+        <v>380</v>
+      </c>
+      <c r="B401" t="s">
+        <v>796</v>
+      </c>
+      <c r="C401" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A402" t="s">
+        <v>380</v>
+      </c>
+      <c r="B402" t="s">
+        <v>797</v>
+      </c>
+      <c r="C402" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A403" t="s">
+        <v>381</v>
+      </c>
+      <c r="B403" t="s">
+        <v>798</v>
+      </c>
+      <c r="C403" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A404" t="s">
+        <v>382</v>
+      </c>
+      <c r="B404" t="s">
+        <v>799</v>
+      </c>
+      <c r="C404" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A405" t="s">
+        <v>383</v>
+      </c>
+      <c r="B405" t="s">
+        <v>800</v>
+      </c>
+      <c r="C405" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C107" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C108" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C109" t="s">
-        <v>111</v>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A406" t="s">
+        <v>384</v>
+      </c>
+      <c r="B406" t="s">
+        <v>801</v>
+      </c>
+      <c r="C406" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A407" t="s">
+        <v>385</v>
+      </c>
+      <c r="B407" t="s">
+        <v>802</v>
+      </c>
+      <c r="C407" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A408" t="s">
+        <v>386</v>
+      </c>
+      <c r="B408" t="s">
+        <v>803</v>
+      </c>
+      <c r="C408" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A409" t="s">
+        <v>387</v>
+      </c>
+      <c r="B409" t="s">
+        <v>804</v>
+      </c>
+      <c r="C409" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A410" t="s">
+        <v>387</v>
+      </c>
+      <c r="B410" t="s">
+        <v>805</v>
+      </c>
+      <c r="C410" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A411" t="s">
+        <v>388</v>
+      </c>
+      <c r="B411" t="s">
+        <v>806</v>
+      </c>
+      <c r="C411" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A412" t="s">
+        <v>388</v>
+      </c>
+      <c r="B412" t="s">
+        <v>807</v>
+      </c>
+      <c r="C412" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A413" t="s">
+        <v>389</v>
+      </c>
+      <c r="B413" t="s">
+        <v>808</v>
+      </c>
+      <c r="C413" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A414" t="s">
+        <v>389</v>
+      </c>
+      <c r="B414" t="s">
+        <v>809</v>
+      </c>
+      <c r="C414" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A415" t="s">
+        <v>390</v>
+      </c>
+      <c r="B415" t="s">
+        <v>810</v>
+      </c>
+      <c r="C415" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A416" t="s">
+        <v>390</v>
+      </c>
+      <c r="B416" t="s">
+        <v>811</v>
+      </c>
+      <c r="C416" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A417" t="s">
+        <v>390</v>
+      </c>
+      <c r="B417" t="s">
+        <v>812</v>
+      </c>
+      <c r="C417" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A418" t="s">
+        <v>391</v>
+      </c>
+      <c r="B418" t="s">
+        <v>813</v>
+      </c>
+      <c r="C418" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A419" t="s">
+        <v>391</v>
+      </c>
+      <c r="B419" t="s">
+        <v>814</v>
+      </c>
+      <c r="C419" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A420" t="s">
+        <v>391</v>
+      </c>
+      <c r="B420" t="s">
+        <v>815</v>
+      </c>
+      <c r="C420" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A421" t="s">
+        <v>392</v>
+      </c>
+      <c r="B421" t="s">
+        <v>816</v>
+      </c>
+      <c r="C421" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A422" t="s">
+        <v>392</v>
+      </c>
+      <c r="B422" t="s">
+        <v>817</v>
+      </c>
+      <c r="C422" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A423" t="s">
+        <v>392</v>
+      </c>
+      <c r="B423" t="s">
+        <v>818</v>
+      </c>
+      <c r="C423" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A424" t="s">
+        <v>393</v>
+      </c>
+      <c r="B424" t="s">
+        <v>819</v>
+      </c>
+      <c r="C424" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A425" t="s">
+        <v>393</v>
+      </c>
+      <c r="B425" t="s">
+        <v>820</v>
+      </c>
+      <c r="C425" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A426" t="s">
+        <v>393</v>
+      </c>
+      <c r="B426" t="s">
+        <v>821</v>
+      </c>
+      <c r="C426" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A427" t="s">
+        <v>394</v>
+      </c>
+      <c r="B427" t="s">
+        <v>822</v>
+      </c>
+      <c r="C427" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A428" t="s">
+        <v>395</v>
+      </c>
+      <c r="B428" t="s">
+        <v>823</v>
+      </c>
+      <c r="C428" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A429" t="s">
+        <v>396</v>
+      </c>
+      <c r="B429" t="s">
+        <v>824</v>
+      </c>
+      <c r="C429" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A430" t="s">
+        <v>397</v>
+      </c>
+      <c r="B430" t="s">
+        <v>397</v>
+      </c>
+      <c r="C430" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C396535-040B-4E35-955D-01059EF060B7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DDB4DB8-671E-4D27-BF49-61792ED8D6F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="689">
   <si>
     <t>UTK</t>
   </si>
@@ -2083,6 +2083,18 @@
   </si>
   <si>
     <t>202605222601087701</t>
+  </si>
+  <si>
+    <t>NFD6-05-20-S6X4</t>
+  </si>
+  <si>
+    <t>NFD6-05-20-J5GY/1</t>
+  </si>
+  <si>
+    <t>NFD6-05-20-J5GY/2</t>
+  </si>
+  <si>
+    <t>NFD6-05-20-J5GY</t>
   </si>
 </sst>
 </file>
@@ -2402,7 +2414,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D358"/>
+  <dimension ref="A1:D361"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
@@ -6432,6 +6444,39 @@
         <v>135</v>
       </c>
     </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A359" t="s">
+        <v>685</v>
+      </c>
+      <c r="B359" t="s">
+        <v>685</v>
+      </c>
+      <c r="C359" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A360" t="s">
+        <v>688</v>
+      </c>
+      <c r="B360" t="s">
+        <v>686</v>
+      </c>
+      <c r="C360" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A361" t="s">
+        <v>688</v>
+      </c>
+      <c r="B361" t="s">
+        <v>687</v>
+      </c>
+      <c r="C361" t="s">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="C1" xr:uid="{66E3D377-5F1B-48CD-A9ED-4AF810829D06}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DDB4DB8-671E-4D27-BF49-61792ED8D6F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F6F003-D922-4BAA-90D2-28719E0F2E02}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="664">
   <si>
     <t>UTK</t>
   </si>
@@ -447,9 +447,6 @@
     <t>260424-F00004090</t>
   </si>
   <si>
-    <t>260520-W00004412</t>
-  </si>
-  <si>
     <t>260521-F00004551</t>
   </si>
   <si>
@@ -459,9 +456,6 @@
     <t>NFE6-05-14-TUTU</t>
   </si>
   <si>
-    <t>NFE6-05-21-FX7M</t>
-  </si>
-  <si>
     <t>260518-F00008424</t>
   </si>
   <si>
@@ -504,9 +498,6 @@
     <t>NFD6-05-16-F7JT</t>
   </si>
   <si>
-    <t>260520-F00010455</t>
-  </si>
-  <si>
     <t>312541091</t>
   </si>
   <si>
@@ -540,9 +531,6 @@
     <t>260520-W00004823</t>
   </si>
   <si>
-    <t>260521-W00002914</t>
-  </si>
-  <si>
     <t>312583636</t>
   </si>
   <si>
@@ -639,18 +627,12 @@
     <t>260520-F00012178</t>
   </si>
   <si>
-    <t>260521-W00002846</t>
-  </si>
-  <si>
     <t>312496523</t>
   </si>
   <si>
     <t>R420333</t>
   </si>
   <si>
-    <t>260428-F00010045</t>
-  </si>
-  <si>
     <t>260520-W00009724</t>
   </si>
   <si>
@@ -672,9 +654,6 @@
     <t>260520-W00008856</t>
   </si>
   <si>
-    <t>267007227</t>
-  </si>
-  <si>
     <t>312679763</t>
   </si>
   <si>
@@ -717,15 +696,6 @@
     <t>260521-W00002593</t>
   </si>
   <si>
-    <t>2026/06486</t>
-  </si>
-  <si>
-    <t>2026/06533</t>
-  </si>
-  <si>
-    <t>26MPE0005468</t>
-  </si>
-  <si>
     <t>312540742</t>
   </si>
   <si>
@@ -1020,12 +990,6 @@
     <t>6a0b30af8046ce4dbfb9f74f</t>
   </si>
   <si>
-    <t>6a0d9c798046ce4dbfba24d0</t>
-  </si>
-  <si>
-    <t>6a0d9c798046ce4dbfba24d1</t>
-  </si>
-  <si>
     <t>6a0ecc058046ce4dbfba38fd</t>
   </si>
   <si>
@@ -1041,9 +1005,6 @@
     <t>202605212601076702</t>
   </si>
   <si>
-    <t>202605222601116001</t>
-  </si>
-  <si>
     <t>6a0dd20b8046ce4dbfba2d65</t>
   </si>
   <si>
@@ -1107,9 +1068,6 @@
     <t>202605222601087204</t>
   </si>
   <si>
-    <t>6a0daf828046ce4dbfba27d0</t>
-  </si>
-  <si>
     <t>312541091/1</t>
   </si>
   <si>
@@ -1155,9 +1113,6 @@
     <t>6a0da37b8046ce4dbfba25a6</t>
   </si>
   <si>
-    <t>6a0ecc058046ce4dbfba38f2</t>
-  </si>
-  <si>
     <t>312583636/1</t>
   </si>
   <si>
@@ -1278,9 +1233,6 @@
     <t>6a0dbe7b8046ce4dbfba2a7c</t>
   </si>
   <si>
-    <t>6a0ec87c8046ce4dbfba383f</t>
-  </si>
-  <si>
     <t>312496523/1</t>
   </si>
   <si>
@@ -1293,9 +1245,6 @@
     <t>159995579540510576</t>
   </si>
   <si>
-    <t>6a086c198046ce4dbfb9cb35</t>
-  </si>
-  <si>
     <t>6a0e07208046ce4dbfba3171</t>
   </si>
   <si>
@@ -1335,9 +1284,6 @@
     <t>6a0dec4d8046ce4dbfba3031</t>
   </si>
   <si>
-    <t>FIZZ-1000918997</t>
-  </si>
-  <si>
     <t>312679763/1</t>
   </si>
   <si>
@@ -1378,27 +1324,6 @@
   </si>
   <si>
     <t>6a0ec3ce8046ce4dbfba375b</t>
-  </si>
-  <si>
-    <t>159995579540348605</t>
-  </si>
-  <si>
-    <t>159995579540348612</t>
-  </si>
-  <si>
-    <t>159995579540449449</t>
-  </si>
-  <si>
-    <t>159995579540449456</t>
-  </si>
-  <si>
-    <t>159995579540449463</t>
-  </si>
-  <si>
-    <t>159995579540449470</t>
-  </si>
-  <si>
-    <t>26MPE0005468/1</t>
   </si>
   <si>
     <t>312540742/1</t>
@@ -2414,7 +2339,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D361"/>
+  <dimension ref="A1:D346"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
@@ -2439,7 +2364,7 @@
         <v>138</v>
       </c>
       <c r="B2" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="C2" t="s">
         <v>86</v>
@@ -2451,7 +2376,7 @@
         <v>139</v>
       </c>
       <c r="B3" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C3" t="s">
         <v>86</v>
@@ -2460,10 +2385,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="C4" t="s">
         <v>86</v>
@@ -2475,7 +2400,7 @@
         <v>140</v>
       </c>
       <c r="B5" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="C5" t="s">
         <v>86</v>
@@ -2487,10 +2412,10 @@
         <v>141</v>
       </c>
       <c r="B6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D6"/>
     </row>
@@ -2499,10 +2424,10 @@
         <v>141</v>
       </c>
       <c r="B7" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D7"/>
     </row>
@@ -2511,79 +2436,79 @@
         <v>142</v>
       </c>
       <c r="B8" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D8"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B9" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D9"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D10"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D11"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B12" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D12"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B13" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B14" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="C14" t="s">
         <v>89</v>
@@ -2592,10 +2517,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B15" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="C15" t="s">
         <v>89</v>
@@ -2607,7 +2532,7 @@
         <v>149</v>
       </c>
       <c r="B16" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="C16" t="s">
         <v>89</v>
@@ -2619,7 +2544,7 @@
         <v>150</v>
       </c>
       <c r="B17" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="C17" t="s">
         <v>89</v>
@@ -2631,7 +2556,7 @@
         <v>151</v>
       </c>
       <c r="B18" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="C18" t="s">
         <v>89</v>
@@ -2643,7 +2568,7 @@
         <v>151</v>
       </c>
       <c r="B19" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C19" t="s">
         <v>89</v>
@@ -2652,10 +2577,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B20" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="C20" t="s">
         <v>89</v>
@@ -2664,10 +2589,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B21" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="C21" t="s">
         <v>89</v>
@@ -2676,10 +2601,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B22" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="C22" t="s">
         <v>89</v>
@@ -2691,7 +2616,7 @@
         <v>153</v>
       </c>
       <c r="B23" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C23" t="s">
         <v>89</v>
@@ -2703,7 +2628,7 @@
         <v>154</v>
       </c>
       <c r="B24" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="C24" t="s">
         <v>89</v>
@@ -2712,10 +2637,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="C25" t="s">
         <v>89</v>
@@ -2727,7 +2652,7 @@
         <v>155</v>
       </c>
       <c r="B26" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="C26" t="s">
         <v>89</v>
@@ -2736,10 +2661,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B27" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C27" t="s">
         <v>89</v>
@@ -2748,10 +2673,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B28" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="C28" t="s">
         <v>89</v>
@@ -2760,25 +2685,25 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B29" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D29"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B30" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="C30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D30"/>
     </row>
@@ -2787,34 +2712,34 @@
         <v>157</v>
       </c>
       <c r="B31" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="C31" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D31"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B32" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C32" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D32"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B33" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C33" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D33"/>
     </row>
@@ -2823,10 +2748,10 @@
         <v>159</v>
       </c>
       <c r="B34" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="C34" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D34"/>
     </row>
@@ -2835,7 +2760,7 @@
         <v>160</v>
       </c>
       <c r="B35" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="C35" t="s">
         <v>91</v>
@@ -2844,10 +2769,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B36" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="C36" t="s">
         <v>91</v>
@@ -2856,37 +2781,37 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B37" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C37" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D37"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B38" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C38" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D38"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B39" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D39"/>
     </row>
@@ -2895,43 +2820,43 @@
         <v>164</v>
       </c>
       <c r="B40" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D40"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B41" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C41" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D41"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B42" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C42" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D42"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B43" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C43" t="s">
         <v>93</v>
@@ -2943,7 +2868,7 @@
         <v>167</v>
       </c>
       <c r="B44" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C44" t="s">
         <v>93</v>
@@ -2952,10 +2877,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="C45" t="s">
         <v>93</v>
@@ -2964,49 +2889,49 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D46"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C47" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D47"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B48" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C48" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D48"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B49" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C49" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D49"/>
     </row>
@@ -3015,10 +2940,10 @@
         <v>172</v>
       </c>
       <c r="B50" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="C50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D50"/>
     </row>
@@ -3027,7 +2952,7 @@
         <v>173</v>
       </c>
       <c r="B51" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="C51" t="s">
         <v>94</v>
@@ -3036,10 +2961,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B52" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C52" t="s">
         <v>94</v>
@@ -3048,10 +2973,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B53" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C53" t="s">
         <v>94</v>
@@ -3060,10 +2985,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B54" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="C54" t="s">
         <v>94</v>
@@ -3072,10 +2997,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B55" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C55" t="s">
         <v>94</v>
@@ -3084,13 +3009,13 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B56" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="C56" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D56"/>
     </row>
@@ -3099,22 +3024,22 @@
         <v>177</v>
       </c>
       <c r="B57" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C57" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D57"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B58" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C58" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D58"/>
     </row>
@@ -3123,10 +3048,10 @@
         <v>178</v>
       </c>
       <c r="B59" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C59" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D59"/>
     </row>
@@ -3135,19 +3060,19 @@
         <v>179</v>
       </c>
       <c r="B60" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="C60" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D60"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B61" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="C61" t="s">
         <v>95</v>
@@ -3156,10 +3081,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B62" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C62" t="s">
         <v>95</v>
@@ -3171,7 +3096,7 @@
         <v>181</v>
       </c>
       <c r="B63" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C63" t="s">
         <v>95</v>
@@ -3183,7 +3108,7 @@
         <v>182</v>
       </c>
       <c r="B64" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="C64" t="s">
         <v>95</v>
@@ -3195,7 +3120,7 @@
         <v>183</v>
       </c>
       <c r="B65" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C65" t="s">
         <v>95</v>
@@ -3207,7 +3132,7 @@
         <v>183</v>
       </c>
       <c r="B66" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="C66" t="s">
         <v>95</v>
@@ -3219,7 +3144,7 @@
         <v>184</v>
       </c>
       <c r="B67" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="C67" t="s">
         <v>95</v>
@@ -3228,10 +3153,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B68" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="C68" t="s">
         <v>95</v>
@@ -3240,10 +3165,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B69" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="C69" t="s">
         <v>95</v>
@@ -3252,13 +3177,13 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B70" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="C70" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D70"/>
     </row>
@@ -3267,10 +3192,10 @@
         <v>187</v>
       </c>
       <c r="B71" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C71" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D71"/>
     </row>
@@ -3279,43 +3204,43 @@
         <v>188</v>
       </c>
       <c r="B72" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="C72" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D72"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B73" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C73" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D73"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B74" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="C74" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D74"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B75" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="C75" t="s">
         <v>96</v>
@@ -3324,61 +3249,61 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B76" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C76" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D76"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B77" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C77" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D77"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B78" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C78" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D78"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B79" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="C79" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D79"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B80" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C80" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D80"/>
     </row>
@@ -3387,10 +3312,10 @@
         <v>196</v>
       </c>
       <c r="B81" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C81" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D81"/>
     </row>
@@ -3399,10 +3324,10 @@
         <v>197</v>
       </c>
       <c r="B82" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="C82" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D82"/>
     </row>
@@ -3411,10 +3336,10 @@
         <v>198</v>
       </c>
       <c r="B83" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C83" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D83"/>
     </row>
@@ -3423,22 +3348,22 @@
         <v>199</v>
       </c>
       <c r="B84" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="C84" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D84"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B85" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C85" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -3446,18 +3371,18 @@
         <v>200</v>
       </c>
       <c r="B86" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="C86" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B87" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="C87" t="s">
         <v>99</v>
@@ -3465,76 +3390,76 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B88" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="C88" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B89" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C89" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B90" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="C90" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B91" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C91" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B92" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="C92" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B93" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C93" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B94" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="C94" t="s">
         <v>100</v>
@@ -3542,10 +3467,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B95" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="C95" t="s">
         <v>100</v>
@@ -3553,10 +3478,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B96" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="C96" t="s">
         <v>100</v>
@@ -3564,68 +3489,68 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B97" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="C97" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B98" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="C98" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B99" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="C99" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B100" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="C100" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B101" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="C101" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B102" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C102" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
@@ -3633,10 +3558,10 @@
         <v>210</v>
       </c>
       <c r="B103" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C103" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
@@ -3644,7 +3569,7 @@
         <v>211</v>
       </c>
       <c r="B104" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C104" t="s">
         <v>101</v>
@@ -3655,7 +3580,7 @@
         <v>212</v>
       </c>
       <c r="B105" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="C105" t="s">
         <v>101</v>
@@ -3666,95 +3591,95 @@
         <v>213</v>
       </c>
       <c r="B106" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="C106" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B107" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="C107" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B108" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C108" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B109" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="C109" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B110" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C110" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B111" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="C111" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B112" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="C112" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B113" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C113" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B114" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="C114" t="s">
         <v>102</v>
@@ -3762,13 +3687,13 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B115" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="C115" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
@@ -3776,10 +3701,10 @@
         <v>222</v>
       </c>
       <c r="B116" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="C116" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
@@ -3787,10 +3712,10 @@
         <v>223</v>
       </c>
       <c r="B117" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="C117" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
@@ -3798,10 +3723,10 @@
         <v>224</v>
       </c>
       <c r="B118" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="C118" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
@@ -3809,10 +3734,10 @@
         <v>225</v>
       </c>
       <c r="B119" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="C119" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
@@ -3820,10 +3745,10 @@
         <v>226</v>
       </c>
       <c r="B120" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C120" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
@@ -3831,10 +3756,10 @@
         <v>227</v>
       </c>
       <c r="B121" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="C121" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
@@ -3842,10 +3767,10 @@
         <v>228</v>
       </c>
       <c r="B122" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C122" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
@@ -3853,10 +3778,10 @@
         <v>229</v>
       </c>
       <c r="B123" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C123" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
@@ -3864,10 +3789,10 @@
         <v>229</v>
       </c>
       <c r="B124" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="C124" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
@@ -3875,54 +3800,54 @@
         <v>230</v>
       </c>
       <c r="B125" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C125" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B126" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="C126" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B127" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="C127" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B128" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="C128" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B129" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="C129" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
@@ -3930,32 +3855,32 @@
         <v>232</v>
       </c>
       <c r="B130" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="C130" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B131" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="C131" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B132" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="C132" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
@@ -3963,10 +3888,10 @@
         <v>234</v>
       </c>
       <c r="B133" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C133" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
@@ -3974,10 +3899,10 @@
         <v>235</v>
       </c>
       <c r="B134" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="C134" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
@@ -3985,10 +3910,10 @@
         <v>236</v>
       </c>
       <c r="B135" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="C135" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
@@ -3996,10 +3921,10 @@
         <v>237</v>
       </c>
       <c r="B136" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="C136" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
@@ -4007,10 +3932,10 @@
         <v>238</v>
       </c>
       <c r="B137" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="C137" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
@@ -4018,43 +3943,43 @@
         <v>239</v>
       </c>
       <c r="B138" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="C138" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B139" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C139" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B140" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="C140" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B141" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="C141" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
@@ -4062,549 +3987,549 @@
         <v>242</v>
       </c>
       <c r="B142" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="C142" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B143" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="C143" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B144" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="C144" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B145" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="C145" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B146" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="C146" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B147" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="C147" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B148" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="C148" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B149" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="C149" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B150" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="C150" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B151" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="C151" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B152" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="C152" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B153" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="C153" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B154" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="C154" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B155" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="C155" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B156" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C156" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B157" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="C157" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B158" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="C158" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B159" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C159" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B160" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="C160" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B161" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="C161" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B162" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="C162" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B163" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="C163" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B164" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="C164" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B165" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="C165" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B166" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="C166" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B167" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="C167" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B168" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="C168" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B169" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="C169" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B170" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="C170" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B171" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="C171" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B172" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="C172" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B173" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="C173" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B174" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="C174" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B175" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="C175" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B176" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="C176" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B177" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="C177" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B178" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="C178" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B179" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="C179" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B180" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="C180" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B181" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="C181" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B182" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="C182" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B183" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="C183" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B184" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="C184" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B185" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="C185" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B186" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="C186" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B187" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="C187" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B188" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C188" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B189" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="C189" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B190" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="C190" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B191" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="C191" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
@@ -4612,7 +4537,7 @@
         <v>280</v>
       </c>
       <c r="B192" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="C192" t="s">
         <v>113</v>
@@ -4620,10 +4545,10 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B193" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="C193" t="s">
         <v>113</v>
@@ -4631,1849 +4556,1684 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B194" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="C194" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B195" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="C195" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B196" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="C196" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B197" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="C197" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>286</v>
+        <v>37</v>
       </c>
       <c r="B198" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="C198" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>287</v>
+        <v>52</v>
       </c>
       <c r="B199" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="C199" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>287</v>
+        <v>5</v>
       </c>
       <c r="B200" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="C200" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>288</v>
+        <v>5</v>
       </c>
       <c r="B201" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="C201" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B202" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="C202" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>290</v>
+        <v>8</v>
       </c>
       <c r="B203" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="C203" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>290</v>
+        <v>20</v>
       </c>
       <c r="B204" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="C204" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>290</v>
+        <v>20</v>
       </c>
       <c r="B205" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="C205" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>290</v>
+        <v>26</v>
       </c>
       <c r="B206" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="C206" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B207" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="C207" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>290</v>
+        <v>46</v>
       </c>
       <c r="B208" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="C208" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>291</v>
+        <v>59</v>
       </c>
       <c r="B209" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="C209" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>292</v>
+        <v>59</v>
       </c>
       <c r="B210" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="C210" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>293</v>
+        <v>73</v>
       </c>
       <c r="B211" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="C211" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B212" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="C212" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B213" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="C213" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="B214" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="C214" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B215" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="C215" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B216" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="C216" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>295</v>
+        <v>11</v>
       </c>
       <c r="B217" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="C217" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B218" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="C218" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>20</v>
+        <v>288</v>
       </c>
       <c r="B219" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="C219" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="B220" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="C220" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B221" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="C221" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>296</v>
+        <v>62</v>
       </c>
       <c r="B222" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="C222" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B223" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="C223" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>59</v>
+        <v>290</v>
       </c>
       <c r="B224" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="C224" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>59</v>
+        <v>291</v>
       </c>
       <c r="B225" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="C225" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>73</v>
+        <v>292</v>
       </c>
       <c r="B226" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="C226" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>297</v>
+        <v>3</v>
       </c>
       <c r="B227" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="C227" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="B228" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="C228" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="B229" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="C229" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B230" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="C230" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B231" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="C231" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="B232" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="C232" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>30</v>
+        <v>293</v>
       </c>
       <c r="B233" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="C233" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>298</v>
+        <v>23</v>
       </c>
       <c r="B234" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="C234" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>299</v>
+        <v>23</v>
       </c>
       <c r="B235" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="C235" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>49</v>
+        <v>294</v>
       </c>
       <c r="B236" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="C236" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B237" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="C237" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="B238" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="C238" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>300</v>
+        <v>56</v>
       </c>
       <c r="B239" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="C239" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>301</v>
+        <v>56</v>
       </c>
       <c r="B240" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="C240" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>302</v>
+        <v>80</v>
       </c>
       <c r="B241" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="C241" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>3</v>
+        <v>295</v>
       </c>
       <c r="B242" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="C242" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>60</v>
+        <v>296</v>
       </c>
       <c r="B243" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="C243" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>22</v>
+        <v>296</v>
       </c>
       <c r="B244" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="C244" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>22</v>
+        <v>296</v>
       </c>
       <c r="B245" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="C245" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>29</v>
+        <v>296</v>
       </c>
       <c r="B246" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="C246" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>36</v>
+        <v>297</v>
       </c>
       <c r="B247" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="C247" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B248" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="C248" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B249" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="C249" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="C250" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>304</v>
+        <v>17</v>
       </c>
       <c r="B251" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="C251" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B252" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="C252" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="B253" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="C253" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="B254" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="C254" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B255" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="C255" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="B256" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="C256" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>305</v>
+        <v>77</v>
       </c>
       <c r="B257" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="C257" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>306</v>
+        <v>77</v>
       </c>
       <c r="B258" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="C258" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>306</v>
+        <v>77</v>
       </c>
       <c r="B259" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="C259" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B260" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="C260" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>306</v>
+        <v>51</v>
       </c>
       <c r="B261" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="C261" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>307</v>
+        <v>58</v>
       </c>
       <c r="B262" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="C262" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="B263" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="C263" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>4</v>
+        <v>300</v>
       </c>
       <c r="B264" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="C264" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B265" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="C265" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B266" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="C266" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>25</v>
+        <v>301</v>
       </c>
       <c r="B267" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="C267" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="B268" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="C268" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="B269" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="C269" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B270" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="C270" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>38</v>
+        <v>302</v>
       </c>
       <c r="B271" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="C271" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>77</v>
+        <v>303</v>
       </c>
       <c r="B272" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="C272" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="B273" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="C273" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>77</v>
+        <v>304</v>
       </c>
       <c r="B274" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="C274" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>308</v>
+        <v>61</v>
       </c>
       <c r="B275" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="C275" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B276" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="C276" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="B277" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="C277" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B278" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="C278" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>310</v>
+        <v>45</v>
       </c>
       <c r="B279" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="C279" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B280" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="C280" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B281" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="C281" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>311</v>
+        <v>28</v>
       </c>
       <c r="B282" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="C282" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B283" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="C283" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B284" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="C284" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B285" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="C285" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>312</v>
+        <v>65</v>
       </c>
       <c r="B286" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="C286" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B287" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="C287" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="B288" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="C288" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>314</v>
+        <v>14</v>
       </c>
       <c r="B289" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="C289" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="B290" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="C290" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="B291" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="C291" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B292" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="C292" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>315</v>
+        <v>15</v>
       </c>
       <c r="B293" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="C293" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="B294" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="C294" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>45</v>
+        <v>307</v>
       </c>
       <c r="B295" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="C295" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="B296" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="C296" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="B297" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="C297" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="B298" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="C298" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B299" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="C299" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>54</v>
+        <v>308</v>
       </c>
       <c r="B300" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="C300" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="B301" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="C301" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>316</v>
+        <v>27</v>
       </c>
       <c r="B302" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="C302" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="B303" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="C303" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="B304" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="C304" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B305" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="C305" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="B306" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="C306" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="B307" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="C307" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="B308" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
       <c r="C308" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="B309" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="C309" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>317</v>
+        <v>55</v>
       </c>
       <c r="B310" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="C310" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B311" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="C311" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="B312" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="C312" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="B313" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="C313" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B314" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="C314" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>318</v>
+        <v>74</v>
       </c>
       <c r="B315" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="C315" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="B316" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C316" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>27</v>
+        <v>309</v>
       </c>
       <c r="B317" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="C317" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>43</v>
+        <v>310</v>
       </c>
       <c r="B318" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="C318" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>43</v>
+        <v>311</v>
       </c>
       <c r="B319" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="C319" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B320" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="C320" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B321" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="C321" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="B322" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="C322" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="B323" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="C323" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="B324" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="C324" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B325" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="C325" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="B326" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="C326" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B327" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="C327" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="B328" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="C328" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="B329" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="C329" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B330" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="C330" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="B331" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="C331" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B332" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="C332" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>320</v>
+        <v>18</v>
       </c>
       <c r="B333" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="C333" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B334" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="C334" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B335" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="C335" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B336" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="C336" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B337" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="C337" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B338" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="C338" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B339" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="C339" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>66</v>
+        <v>315</v>
       </c>
       <c r="B340" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="C340" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>66</v>
+        <v>316</v>
       </c>
       <c r="B341" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="C341" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>71</v>
+        <v>317</v>
       </c>
       <c r="B342" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="C342" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>13</v>
+        <v>318</v>
       </c>
       <c r="B343" t="s">
-        <v>670</v>
+        <v>318</v>
       </c>
       <c r="C343" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>39</v>
+        <v>660</v>
       </c>
       <c r="B344" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="C344" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>57</v>
+        <v>663</v>
       </c>
       <c r="B345" t="s">
-        <v>672</v>
+        <v>661</v>
       </c>
       <c r="C345" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>322</v>
+        <v>663</v>
       </c>
       <c r="B346" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="C346" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A347" t="s">
-        <v>323</v>
-      </c>
-      <c r="B347" t="s">
-        <v>674</v>
-      </c>
-      <c r="C347" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A348" t="s">
-        <v>18</v>
-      </c>
-      <c r="B348" t="s">
-        <v>675</v>
-      </c>
-      <c r="C348" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A349" t="s">
-        <v>324</v>
-      </c>
-      <c r="B349" t="s">
-        <v>676</v>
-      </c>
-      <c r="C349" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A350" t="s">
-        <v>40</v>
-      </c>
-      <c r="B350" t="s">
-        <v>677</v>
-      </c>
-      <c r="C350" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A351" t="s">
-        <v>41</v>
-      </c>
-      <c r="B351" t="s">
-        <v>678</v>
-      </c>
-      <c r="C351" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A352" t="s">
-        <v>41</v>
-      </c>
-      <c r="B352" t="s">
-        <v>679</v>
-      </c>
-      <c r="C352" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A353" t="s">
-        <v>63</v>
-      </c>
-      <c r="B353" t="s">
-        <v>680</v>
-      </c>
-      <c r="C353" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A354" t="s">
-        <v>67</v>
-      </c>
-      <c r="B354" t="s">
-        <v>681</v>
-      </c>
-      <c r="C354" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A355" t="s">
-        <v>325</v>
-      </c>
-      <c r="B355" t="s">
-        <v>682</v>
-      </c>
-      <c r="C355" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A356" t="s">
-        <v>326</v>
-      </c>
-      <c r="B356" t="s">
-        <v>683</v>
-      </c>
-      <c r="C356" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A357" t="s">
-        <v>327</v>
-      </c>
-      <c r="B357" t="s">
-        <v>684</v>
-      </c>
-      <c r="C357" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A358" t="s">
-        <v>328</v>
-      </c>
-      <c r="B358" t="s">
-        <v>328</v>
-      </c>
-      <c r="C358" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A359" t="s">
-        <v>685</v>
-      </c>
-      <c r="B359" t="s">
-        <v>685</v>
-      </c>
-      <c r="C359" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A360" t="s">
-        <v>688</v>
-      </c>
-      <c r="B360" t="s">
-        <v>686</v>
-      </c>
-      <c r="C360" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A361" t="s">
-        <v>688</v>
-      </c>
-      <c r="B361" t="s">
-        <v>687</v>
-      </c>
-      <c r="C361" t="s">
         <v>110</v>
       </c>
     </row>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B2CA25-6861-4297-BB65-07A2083ECEEF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6192AE06-7195-4AE2-8A29-6B3768E7B563}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="1038">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="1014">
   <si>
     <t>UTK</t>
   </si>
@@ -636,9 +636,6 @@
     <t>260522-F00007111</t>
   </si>
   <si>
-    <t>260523-W00003011</t>
-  </si>
-  <si>
     <t>260524-F00001190</t>
   </si>
   <si>
@@ -690,9 +687,6 @@
     <t>260522-F00006413</t>
   </si>
   <si>
-    <t>260522-W00005078</t>
-  </si>
-  <si>
     <t>260523-F00000317</t>
   </si>
   <si>
@@ -750,9 +744,6 @@
     <t>260520-F00012103</t>
   </si>
   <si>
-    <t>260522-W00003960</t>
-  </si>
-  <si>
     <t>260523-W00002604</t>
   </si>
   <si>
@@ -876,9 +867,6 @@
     <t>248745844</t>
   </si>
   <si>
-    <t>260519-F00008180</t>
-  </si>
-  <si>
     <t>260520-F00012386</t>
   </si>
   <si>
@@ -906,9 +894,6 @@
     <t>26MPE0005474</t>
   </si>
   <si>
-    <t>26MPE0005584</t>
-  </si>
-  <si>
     <t>312679680</t>
   </si>
   <si>
@@ -1002,9 +987,6 @@
     <t>313181006</t>
   </si>
   <si>
-    <t>313181099</t>
-  </si>
-  <si>
     <t>NFE6-05-22-6FW3</t>
   </si>
   <si>
@@ -1116,12 +1098,6 @@
     <t>260523-F00005224</t>
   </si>
   <si>
-    <t>260524-W00002158</t>
-  </si>
-  <si>
-    <t>260526-F00003721</t>
-  </si>
-  <si>
     <t>312785203</t>
   </si>
   <si>
@@ -1230,9 +1206,6 @@
     <t>260521-F00013171</t>
   </si>
   <si>
-    <t>260521-W00003736</t>
-  </si>
-  <si>
     <t>260521-W00006566</t>
   </si>
   <si>
@@ -1344,9 +1317,6 @@
     <t>260518-F00000808</t>
   </si>
   <si>
-    <t>260521-F00003265</t>
-  </si>
-  <si>
     <t>260522-F00003171</t>
   </si>
   <si>
@@ -1596,9 +1566,6 @@
     <t>6a103bf78046ce4dbfba5576</t>
   </si>
   <si>
-    <t>6a11717c8046ce4dbfba644a</t>
-  </si>
-  <si>
     <t>6a12ee358046ce4dbfba6dcc</t>
   </si>
   <si>
@@ -1650,9 +1617,6 @@
     <t>6a1033c38046ce4dbfba5454</t>
   </si>
   <si>
-    <t>6a1046af8046ce4dbfba56c7</t>
-  </si>
-  <si>
     <t>6a1140198046ce4dbfba6065</t>
   </si>
   <si>
@@ -1713,9 +1677,6 @@
     <t>6a100d2f8046ce4dbfba4e28</t>
   </si>
   <si>
-    <t>6a1030428046ce4dbfba53d4</t>
-  </si>
-  <si>
     <t>6a1169258046ce4dbfba633d</t>
   </si>
   <si>
@@ -1860,9 +1821,6 @@
     <t>248745844/2</t>
   </si>
   <si>
-    <t>6a0f38288046ce4dbfba48b7</t>
-  </si>
-  <si>
     <t>6a1007538046ce4dbfba4d08</t>
   </si>
   <si>
@@ -1893,9 +1851,6 @@
     <t>26MPE0005474/1</t>
   </si>
   <si>
-    <t>26MPE0005584/1</t>
-  </si>
-  <si>
     <t>312679680/1</t>
   </si>
   <si>
@@ -2013,12 +1968,6 @@
     <t>313181006/1</t>
   </si>
   <si>
-    <t>313181099/1</t>
-  </si>
-  <si>
-    <t>313181099/2</t>
-  </si>
-  <si>
     <t>202605262601116401</t>
   </si>
   <si>
@@ -2157,21 +2106,6 @@
     <t>6a11c83d8046ce4dbfba6965</t>
   </si>
   <si>
-    <t>6a12be238046ce4dbfba6c5c</t>
-  </si>
-  <si>
-    <t>6a12be238046ce4dbfba6c5d</t>
-  </si>
-  <si>
-    <t>6a155ed08046ce4dbfba7e3e</t>
-  </si>
-  <si>
-    <t>6a155ed08046ce4dbfba7e41</t>
-  </si>
-  <si>
-    <t>6a155ed08046ce4dbfba7e43</t>
-  </si>
-  <si>
     <t>312785203/1</t>
   </si>
   <si>
@@ -2316,9 +2250,6 @@
     <t>6a0f27688046ce4dbfba475f</t>
   </si>
   <si>
-    <t>6a103d7d8046ce4dbfba55b1</t>
-  </si>
-  <si>
     <t>6a0f15e08046ce4dbfba4526</t>
   </si>
   <si>
@@ -2455,9 +2386,6 @@
   </si>
   <si>
     <t>6a0fde558046ce4dbfba4ad4</t>
-  </si>
-  <si>
-    <t>6a0ec7518046ce4dbfba3812</t>
   </si>
   <si>
     <t>6a10154e8046ce4dbfba4f60</t>
@@ -3461,7 +3389,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D541"/>
+  <dimension ref="A1:D527"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
@@ -3486,7 +3414,7 @@
         <v>198</v>
       </c>
       <c r="B2" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="C2" t="s">
         <v>148</v>
@@ -3498,7 +3426,7 @@
         <v>199</v>
       </c>
       <c r="B3" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="C3" t="s">
         <v>148</v>
@@ -3510,7 +3438,7 @@
         <v>200</v>
       </c>
       <c r="B4" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="C4" t="s">
         <v>148</v>
@@ -3522,7 +3450,7 @@
         <v>201</v>
       </c>
       <c r="B5" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="C5" t="s">
         <v>148</v>
@@ -3534,7 +3462,7 @@
         <v>202</v>
       </c>
       <c r="B6" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="C6" t="s">
         <v>148</v>
@@ -3546,7 +3474,7 @@
         <v>203</v>
       </c>
       <c r="B7" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="C7" t="s">
         <v>148</v>
@@ -3558,7 +3486,7 @@
         <v>204</v>
       </c>
       <c r="B8" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="C8" t="s">
         <v>148</v>
@@ -3570,7 +3498,7 @@
         <v>205</v>
       </c>
       <c r="B9" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="C9" t="s">
         <v>148</v>
@@ -3582,7 +3510,7 @@
         <v>206</v>
       </c>
       <c r="B10" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="C10" t="s">
         <v>148</v>
@@ -3594,10 +3522,10 @@
         <v>207</v>
       </c>
       <c r="B11" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11"/>
     </row>
@@ -3606,7 +3534,7 @@
         <v>208</v>
       </c>
       <c r="B12" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="C12" t="s">
         <v>149</v>
@@ -3618,7 +3546,7 @@
         <v>209</v>
       </c>
       <c r="B13" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="C13" t="s">
         <v>149</v>
@@ -3630,7 +3558,7 @@
         <v>210</v>
       </c>
       <c r="B14" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="C14" t="s">
         <v>149</v>
@@ -3642,10 +3570,10 @@
         <v>211</v>
       </c>
       <c r="B15" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="C15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D15"/>
     </row>
@@ -3654,7 +3582,7 @@
         <v>212</v>
       </c>
       <c r="B16" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="C16" t="s">
         <v>150</v>
@@ -3666,7 +3594,7 @@
         <v>213</v>
       </c>
       <c r="B17" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="C17" t="s">
         <v>150</v>
@@ -3678,7 +3606,7 @@
         <v>214</v>
       </c>
       <c r="B18" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="C18" t="s">
         <v>150</v>
@@ -3690,10 +3618,10 @@
         <v>215</v>
       </c>
       <c r="B19" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="C19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D19"/>
     </row>
@@ -3702,7 +3630,7 @@
         <v>216</v>
       </c>
       <c r="B20" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="C20" t="s">
         <v>151</v>
@@ -3714,7 +3642,7 @@
         <v>217</v>
       </c>
       <c r="B21" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="C21" t="s">
         <v>151</v>
@@ -3726,7 +3654,7 @@
         <v>218</v>
       </c>
       <c r="B22" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="C22" t="s">
         <v>151</v>
@@ -3738,7 +3666,7 @@
         <v>219</v>
       </c>
       <c r="B23" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="C23" t="s">
         <v>151</v>
@@ -3750,7 +3678,7 @@
         <v>220</v>
       </c>
       <c r="B24" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="C24" t="s">
         <v>151</v>
@@ -3762,7 +3690,7 @@
         <v>221</v>
       </c>
       <c r="B25" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="C25" t="s">
         <v>151</v>
@@ -3774,7 +3702,7 @@
         <v>222</v>
       </c>
       <c r="B26" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="C26" t="s">
         <v>151</v>
@@ -3783,10 +3711,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B27" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="C27" t="s">
         <v>151</v>
@@ -3795,10 +3723,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B28" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="C28" t="s">
         <v>151</v>
@@ -3810,7 +3738,7 @@
         <v>224</v>
       </c>
       <c r="B29" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="C29" t="s">
         <v>151</v>
@@ -3822,7 +3750,7 @@
         <v>225</v>
       </c>
       <c r="B30" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="C30" t="s">
         <v>151</v>
@@ -3834,7 +3762,7 @@
         <v>226</v>
       </c>
       <c r="B31" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="C31" t="s">
         <v>151</v>
@@ -3846,7 +3774,7 @@
         <v>227</v>
       </c>
       <c r="B32" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="C32" t="s">
         <v>151</v>
@@ -3858,7 +3786,7 @@
         <v>228</v>
       </c>
       <c r="B33" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="C33" t="s">
         <v>151</v>
@@ -3870,7 +3798,7 @@
         <v>229</v>
       </c>
       <c r="B34" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="C34" t="s">
         <v>151</v>
@@ -3882,7 +3810,7 @@
         <v>230</v>
       </c>
       <c r="B35" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="C35" t="s">
         <v>151</v>
@@ -3894,7 +3822,7 @@
         <v>231</v>
       </c>
       <c r="B36" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="C36" t="s">
         <v>151</v>
@@ -3906,10 +3834,10 @@
         <v>232</v>
       </c>
       <c r="B37" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="C37" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D37"/>
     </row>
@@ -3918,10 +3846,10 @@
         <v>233</v>
       </c>
       <c r="B38" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="C38" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D38"/>
     </row>
@@ -3930,7 +3858,7 @@
         <v>234</v>
       </c>
       <c r="B39" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="C39" t="s">
         <v>152</v>
@@ -3942,7 +3870,7 @@
         <v>235</v>
       </c>
       <c r="B40" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="C40" t="s">
         <v>152</v>
@@ -3954,7 +3882,7 @@
         <v>236</v>
       </c>
       <c r="B41" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="C41" t="s">
         <v>152</v>
@@ -3966,10 +3894,10 @@
         <v>237</v>
       </c>
       <c r="B42" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="C42" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D42"/>
     </row>
@@ -3978,10 +3906,10 @@
         <v>238</v>
       </c>
       <c r="B43" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="C43" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D43"/>
     </row>
@@ -3990,7 +3918,7 @@
         <v>239</v>
       </c>
       <c r="B44" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="C44" t="s">
         <v>153</v>
@@ -4002,7 +3930,7 @@
         <v>240</v>
       </c>
       <c r="B45" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="C45" t="s">
         <v>153</v>
@@ -4014,7 +3942,7 @@
         <v>241</v>
       </c>
       <c r="B46" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="C46" t="s">
         <v>153</v>
@@ -4026,10 +3954,10 @@
         <v>242</v>
       </c>
       <c r="B47" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="C47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D47"/>
     </row>
@@ -4038,10 +3966,10 @@
         <v>243</v>
       </c>
       <c r="B48" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="C48" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D48"/>
     </row>
@@ -4050,10 +3978,10 @@
         <v>244</v>
       </c>
       <c r="B49" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="C49" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D49"/>
     </row>
@@ -4062,7 +3990,7 @@
         <v>245</v>
       </c>
       <c r="B50" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="C50" t="s">
         <v>154</v>
@@ -4074,7 +4002,7 @@
         <v>246</v>
       </c>
       <c r="B51" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="C51" t="s">
         <v>154</v>
@@ -4086,7 +4014,7 @@
         <v>247</v>
       </c>
       <c r="B52" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="C52" t="s">
         <v>154</v>
@@ -4098,7 +4026,7 @@
         <v>248</v>
       </c>
       <c r="B53" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="C53" t="s">
         <v>154</v>
@@ -4110,7 +4038,7 @@
         <v>249</v>
       </c>
       <c r="B54" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="C54" t="s">
         <v>154</v>
@@ -4122,7 +4050,7 @@
         <v>250</v>
       </c>
       <c r="B55" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="C55" t="s">
         <v>154</v>
@@ -4134,7 +4062,7 @@
         <v>251</v>
       </c>
       <c r="B56" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="C56" t="s">
         <v>154</v>
@@ -4146,7 +4074,7 @@
         <v>252</v>
       </c>
       <c r="B57" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="C57" t="s">
         <v>154</v>
@@ -4155,10 +4083,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B58" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="C58" t="s">
         <v>154</v>
@@ -4167,10 +4095,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B59" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="C59" t="s">
         <v>154</v>
@@ -4179,10 +4107,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B60" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="C60" t="s">
         <v>154</v>
@@ -4194,43 +4122,43 @@
         <v>255</v>
       </c>
       <c r="B61" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="C61" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D61"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B62" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="C62" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D62"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B63" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="C63" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D63"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B64" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="C64" t="s">
         <v>155</v>
@@ -4239,10 +4167,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B65" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="C65" t="s">
         <v>155</v>
@@ -4251,10 +4179,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B66" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="C66" t="s">
         <v>155</v>
@@ -4263,10 +4191,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B67" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="C67" t="s">
         <v>155</v>
@@ -4278,7 +4206,7 @@
         <v>259</v>
       </c>
       <c r="B68" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="C68" t="s">
         <v>155</v>
@@ -4290,7 +4218,7 @@
         <v>260</v>
       </c>
       <c r="B69" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="C69" t="s">
         <v>155</v>
@@ -4302,7 +4230,7 @@
         <v>261</v>
       </c>
       <c r="B70" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="C70" t="s">
         <v>155</v>
@@ -4314,7 +4242,7 @@
         <v>262</v>
       </c>
       <c r="B71" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="C71" t="s">
         <v>155</v>
@@ -4323,10 +4251,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B72" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="C72" t="s">
         <v>155</v>
@@ -4335,25 +4263,25 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B73" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="C73" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D73"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B74" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="C74" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D74"/>
     </row>
@@ -4362,10 +4290,10 @@
         <v>265</v>
       </c>
       <c r="B75" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="C75" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D75"/>
     </row>
@@ -4374,7 +4302,7 @@
         <v>266</v>
       </c>
       <c r="B76" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="C76" t="s">
         <v>156</v>
@@ -4383,10 +4311,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B77" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="C77" t="s">
         <v>156</v>
@@ -4395,10 +4323,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B78" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="C78" t="s">
         <v>156</v>
@@ -4407,10 +4335,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B79" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="C79" t="s">
         <v>156</v>
@@ -4422,7 +4350,7 @@
         <v>269</v>
       </c>
       <c r="B80" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="C80" t="s">
         <v>156</v>
@@ -4434,7 +4362,7 @@
         <v>270</v>
       </c>
       <c r="B81" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="C81" t="s">
         <v>156</v>
@@ -4446,7 +4374,7 @@
         <v>271</v>
       </c>
       <c r="B82" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="C82" t="s">
         <v>156</v>
@@ -4458,10 +4386,10 @@
         <v>272</v>
       </c>
       <c r="B83" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="C83" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D83"/>
     </row>
@@ -4470,10 +4398,10 @@
         <v>273</v>
       </c>
       <c r="B84" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="C84" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -4481,10 +4409,10 @@
         <v>274</v>
       </c>
       <c r="B85" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="C85" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -4492,7 +4420,7 @@
         <v>275</v>
       </c>
       <c r="B86" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="C86" t="s">
         <v>157</v>
@@ -4503,7 +4431,7 @@
         <v>276</v>
       </c>
       <c r="B87" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="C87" t="s">
         <v>157</v>
@@ -4514,7 +4442,7 @@
         <v>277</v>
       </c>
       <c r="B88" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="C88" t="s">
         <v>157</v>
@@ -4525,40 +4453,40 @@
         <v>278</v>
       </c>
       <c r="B89" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="C89" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B90" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="C90" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B91" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="C91" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B92" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="C92" t="s">
         <v>158</v>
@@ -4569,18 +4497,18 @@
         <v>281</v>
       </c>
       <c r="B93" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="C93" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B94" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="C94" t="s">
         <v>159</v>
@@ -4588,10 +4516,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B95" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="C95" t="s">
         <v>158</v>
@@ -4599,10 +4527,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B96" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="C96" t="s">
         <v>158</v>
@@ -4610,10 +4538,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B97" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="C97" t="s">
         <v>159</v>
@@ -4624,10 +4552,10 @@
         <v>285</v>
       </c>
       <c r="B98" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="C98" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
@@ -4635,7 +4563,7 @@
         <v>286</v>
       </c>
       <c r="B99" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="C99" t="s">
         <v>158</v>
@@ -4646,10 +4574,10 @@
         <v>287</v>
       </c>
       <c r="B100" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="C100" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
@@ -4657,18 +4585,18 @@
         <v>288</v>
       </c>
       <c r="B101" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="C101" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B102" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="C102" t="s">
         <v>158</v>
@@ -4676,10 +4604,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B103" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="C103" t="s">
         <v>158</v>
@@ -4687,32 +4615,32 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B104" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="C104" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B105" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="C105" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B106" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="C106" t="s">
         <v>158</v>
@@ -4720,10 +4648,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B107" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="C107" t="s">
         <v>158</v>
@@ -4734,7 +4662,7 @@
         <v>293</v>
       </c>
       <c r="B108" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="C108" t="s">
         <v>158</v>
@@ -4745,7 +4673,7 @@
         <v>294</v>
       </c>
       <c r="B109" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="C109" t="s">
         <v>158</v>
@@ -4756,10 +4684,10 @@
         <v>295</v>
       </c>
       <c r="B110" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="C110" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
@@ -4767,10 +4695,10 @@
         <v>296</v>
       </c>
       <c r="B111" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="C111" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
@@ -4778,10 +4706,10 @@
         <v>297</v>
       </c>
       <c r="B112" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="C112" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -4789,51 +4717,51 @@
         <v>298</v>
       </c>
       <c r="B113" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="C113" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B114" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="C114" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B115" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="C115" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B116" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="C116" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B117" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="C117" t="s">
         <v>160</v>
@@ -4841,10 +4769,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B118" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="C118" t="s">
         <v>160</v>
@@ -4852,10 +4780,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B119" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
       <c r="C119" t="s">
         <v>160</v>
@@ -4863,10 +4791,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B120" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="C120" t="s">
         <v>160</v>
@@ -4874,10 +4802,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B121" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="C121" t="s">
         <v>160</v>
@@ -4885,10 +4813,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B122" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="C122" t="s">
         <v>160</v>
@@ -4896,10 +4824,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B123" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="C123" t="s">
         <v>160</v>
@@ -4907,10 +4835,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B124" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="C124" t="s">
         <v>160</v>
@@ -4918,24 +4846,24 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B125" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="C125" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B126" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="C126" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
@@ -4943,10 +4871,10 @@
         <v>308</v>
       </c>
       <c r="B127" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C127" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
@@ -4954,10 +4882,10 @@
         <v>309</v>
       </c>
       <c r="B128" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="C128" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
@@ -4965,10 +4893,10 @@
         <v>310</v>
       </c>
       <c r="B129" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="C129" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
@@ -4976,51 +4904,51 @@
         <v>311</v>
       </c>
       <c r="B130" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="C130" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B131" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="C131" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B132" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="C132" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B133" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="C133" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B134" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="C134" t="s">
         <v>162</v>
@@ -5028,10 +4956,10 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B135" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="C135" t="s">
         <v>162</v>
@@ -5039,10 +4967,10 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B136" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="C136" t="s">
         <v>162</v>
@@ -5050,10 +4978,10 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B137" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="C137" t="s">
         <v>162</v>
@@ -5061,10 +4989,10 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B138" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="C138" t="s">
         <v>162</v>
@@ -5072,10 +5000,10 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B139" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="C139" t="s">
         <v>162</v>
@@ -5083,10 +5011,10 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B140" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="C140" t="s">
         <v>162</v>
@@ -5097,10 +5025,10 @@
         <v>320</v>
       </c>
       <c r="B141" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="C141" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
@@ -5108,10 +5036,10 @@
         <v>321</v>
       </c>
       <c r="B142" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="C142" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
@@ -5119,10 +5047,10 @@
         <v>322</v>
       </c>
       <c r="B143" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="C143" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
@@ -5130,10 +5058,10 @@
         <v>323</v>
       </c>
       <c r="B144" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="C144" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
@@ -5141,40 +5069,40 @@
         <v>324</v>
       </c>
       <c r="B145" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="C145" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B146" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="C146" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B147" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="C147" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B148" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="C148" t="s">
         <v>163</v>
@@ -5182,10 +5110,10 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B149" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="C149" t="s">
         <v>163</v>
@@ -5193,10 +5121,10 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B150" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="C150" t="s">
         <v>163</v>
@@ -5204,13 +5132,13 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B151" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="C151" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
@@ -5218,10 +5146,10 @@
         <v>330</v>
       </c>
       <c r="B152" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="C152" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
@@ -5229,62 +5157,62 @@
         <v>331</v>
       </c>
       <c r="B153" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="C153" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B154" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="C154" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B155" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="C155" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B156" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="C156" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B157" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C157" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B158" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="C158" t="s">
         <v>164</v>
@@ -5292,10 +5220,10 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B159" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="C159" t="s">
         <v>164</v>
@@ -5303,10 +5231,10 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B160" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="C160" t="s">
         <v>164</v>
@@ -5314,10 +5242,10 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B161" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="C161" t="s">
         <v>164</v>
@@ -5325,10 +5253,10 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B162" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="C162" t="s">
         <v>164</v>
@@ -5336,10 +5264,10 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B163" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="C163" t="s">
         <v>164</v>
@@ -5347,10 +5275,10 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B164" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="C164" t="s">
         <v>164</v>
@@ -5361,7 +5289,7 @@
         <v>338</v>
       </c>
       <c r="B165" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="C165" t="s">
         <v>164</v>
@@ -5369,10 +5297,10 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B166" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="C166" t="s">
         <v>164</v>
@@ -5383,7 +5311,7 @@
         <v>339</v>
       </c>
       <c r="B167" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="C167" t="s">
         <v>164</v>
@@ -5394,10 +5322,10 @@
         <v>340</v>
       </c>
       <c r="B168" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="C168" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
@@ -5405,10 +5333,10 @@
         <v>341</v>
       </c>
       <c r="B169" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="C169" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
@@ -5416,10 +5344,10 @@
         <v>342</v>
       </c>
       <c r="B170" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="C170" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
@@ -5427,10 +5355,10 @@
         <v>343</v>
       </c>
       <c r="B171" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="C171" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
@@ -5438,21 +5366,21 @@
         <v>344</v>
       </c>
       <c r="B172" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="C172" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B173" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="C173" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
@@ -5460,10 +5388,10 @@
         <v>345</v>
       </c>
       <c r="B174" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="C174" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
@@ -5471,7 +5399,7 @@
         <v>346</v>
       </c>
       <c r="B175" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="C175" t="s">
         <v>165</v>
@@ -5479,10 +5407,10 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B176" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="C176" t="s">
         <v>165</v>
@@ -5490,10 +5418,10 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B177" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="C177" t="s">
         <v>165</v>
@@ -5501,10 +5429,10 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B178" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="C178" t="s">
         <v>165</v>
@@ -5512,10 +5440,10 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B179" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="C179" t="s">
         <v>165</v>
@@ -5526,7 +5454,7 @@
         <v>350</v>
       </c>
       <c r="B180" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="C180" t="s">
         <v>165</v>
@@ -5537,10 +5465,10 @@
         <v>351</v>
       </c>
       <c r="B181" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="C181" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
@@ -5548,54 +5476,54 @@
         <v>352</v>
       </c>
       <c r="B182" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="C182" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B183" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="C183" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B184" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="C184" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B185" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="C185" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B186" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="C186" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
@@ -5603,18 +5531,18 @@
         <v>356</v>
       </c>
       <c r="B187" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="C187" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B188" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="C188" t="s">
         <v>166</v>
@@ -5622,10 +5550,10 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B189" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="C189" t="s">
         <v>166</v>
@@ -5633,10 +5561,10 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B190" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="C190" t="s">
         <v>166</v>
@@ -5644,10 +5572,10 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B191" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="C191" t="s">
         <v>166</v>
@@ -5655,10 +5583,10 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B192" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="C192" t="s">
         <v>166</v>
@@ -5666,10 +5594,10 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B193" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="C193" t="s">
         <v>166</v>
@@ -5677,35 +5605,35 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B194" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="C194" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B195" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="C195" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B196" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="C196" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
@@ -5713,21 +5641,21 @@
         <v>363</v>
       </c>
       <c r="B197" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="C197" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B198" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="C198" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
@@ -5735,10 +5663,10 @@
         <v>364</v>
       </c>
       <c r="B199" t="s">
-        <v>715</v>
+        <v>705</v>
       </c>
       <c r="C199" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
@@ -5746,21 +5674,21 @@
         <v>364</v>
       </c>
       <c r="B200" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="C200" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B201" t="s">
-        <v>717</v>
+        <v>707</v>
       </c>
       <c r="C201" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
@@ -5768,10 +5696,10 @@
         <v>365</v>
       </c>
       <c r="B202" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
       <c r="C202" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
@@ -5779,10 +5707,10 @@
         <v>366</v>
       </c>
       <c r="B203" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="C203" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
@@ -5790,32 +5718,32 @@
         <v>367</v>
       </c>
       <c r="B204" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="C204" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B205" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="C205" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B206" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
       <c r="C206" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
@@ -5823,10 +5751,10 @@
         <v>369</v>
       </c>
       <c r="B207" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
       <c r="C207" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
@@ -5834,10 +5762,10 @@
         <v>370</v>
       </c>
       <c r="B208" t="s">
-        <v>724</v>
+        <v>714</v>
       </c>
       <c r="C208" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
@@ -5845,131 +5773,131 @@
         <v>371</v>
       </c>
       <c r="B209" t="s">
-        <v>725</v>
+        <v>715</v>
       </c>
       <c r="C209" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B210" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
       <c r="C210" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B211" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
       <c r="C211" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B212" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="C212" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B213" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
       <c r="C213" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B214" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="C214" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B215" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="C215" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B216" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="C216" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B217" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="C217" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B218" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="C218" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B219" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="C219" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B220" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="C220" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
@@ -5977,10 +5905,10 @@
         <v>379</v>
       </c>
       <c r="B221" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="C221" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
@@ -5988,10 +5916,10 @@
         <v>380</v>
       </c>
       <c r="B222" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="C222" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
@@ -5999,10 +5927,10 @@
         <v>381</v>
       </c>
       <c r="B223" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="C223" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
@@ -6010,10 +5938,10 @@
         <v>382</v>
       </c>
       <c r="B224" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="C224" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
@@ -6021,10 +5949,10 @@
         <v>383</v>
       </c>
       <c r="B225" t="s">
-        <v>741</v>
+        <v>731</v>
       </c>
       <c r="C225" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
@@ -6032,7 +5960,7 @@
         <v>384</v>
       </c>
       <c r="B226" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="C226" t="s">
         <v>169</v>
@@ -6043,7 +5971,7 @@
         <v>385</v>
       </c>
       <c r="B227" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
       <c r="C227" t="s">
         <v>169</v>
@@ -6054,7 +5982,7 @@
         <v>386</v>
       </c>
       <c r="B228" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="C228" t="s">
         <v>169</v>
@@ -6062,10 +5990,10 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B229" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="C229" t="s">
         <v>169</v>
@@ -6073,10 +6001,10 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B230" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
       <c r="C230" t="s">
         <v>169</v>
@@ -6084,10 +6012,10 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B231" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
       <c r="C231" t="s">
         <v>169</v>
@@ -6095,142 +6023,142 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B232" t="s">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="C232" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B233" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="C233" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B234" t="s">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="C234" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B235" t="s">
-        <v>751</v>
+        <v>741</v>
       </c>
       <c r="C235" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B236" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="C236" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B237" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
       <c r="C237" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B238" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="C238" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B239" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="C239" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B240" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="C240" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B241" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="C241" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B242" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
       <c r="C242" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B243" t="s">
-        <v>759</v>
+        <v>749</v>
       </c>
       <c r="C243" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B244" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="C244" t="s">
         <v>170</v>
@@ -6241,7 +6169,7 @@
         <v>399</v>
       </c>
       <c r="B245" t="s">
-        <v>761</v>
+        <v>751</v>
       </c>
       <c r="C245" t="s">
         <v>170</v>
@@ -6252,7 +6180,7 @@
         <v>400</v>
       </c>
       <c r="B246" t="s">
-        <v>762</v>
+        <v>752</v>
       </c>
       <c r="C246" t="s">
         <v>170</v>
@@ -6263,7 +6191,7 @@
         <v>401</v>
       </c>
       <c r="B247" t="s">
-        <v>763</v>
+        <v>753</v>
       </c>
       <c r="C247" t="s">
         <v>170</v>
@@ -6274,10 +6202,10 @@
         <v>402</v>
       </c>
       <c r="B248" t="s">
-        <v>764</v>
+        <v>754</v>
       </c>
       <c r="C248" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
@@ -6285,10 +6213,10 @@
         <v>403</v>
       </c>
       <c r="B249" t="s">
-        <v>765</v>
+        <v>755</v>
       </c>
       <c r="C249" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
@@ -6296,43 +6224,43 @@
         <v>404</v>
       </c>
       <c r="B250" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="C250" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B251" t="s">
-        <v>767</v>
+        <v>757</v>
       </c>
       <c r="C251" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B252" t="s">
-        <v>768</v>
+        <v>758</v>
       </c>
       <c r="C252" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B253" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="C253" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
@@ -6340,10 +6268,10 @@
         <v>407</v>
       </c>
       <c r="B254" t="s">
-        <v>770</v>
+        <v>760</v>
       </c>
       <c r="C254" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
@@ -6351,249 +6279,249 @@
         <v>407</v>
       </c>
       <c r="B255" t="s">
-        <v>771</v>
+        <v>761</v>
       </c>
       <c r="C255" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B256" t="s">
-        <v>772</v>
+        <v>762</v>
       </c>
       <c r="C256" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B257" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
       <c r="C257" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B258" t="s">
-        <v>774</v>
+        <v>764</v>
       </c>
       <c r="C258" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B259" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
       <c r="C259" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B260" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
       <c r="C260" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B261" t="s">
-        <v>777</v>
+        <v>767</v>
       </c>
       <c r="C261" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B262" t="s">
-        <v>778</v>
+        <v>768</v>
       </c>
       <c r="C262" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B263" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="C263" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B264" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
       <c r="C264" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B265" t="s">
-        <v>781</v>
+        <v>771</v>
       </c>
       <c r="C265" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B266" t="s">
-        <v>782</v>
+        <v>772</v>
       </c>
       <c r="C266" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B267" t="s">
-        <v>783</v>
+        <v>773</v>
       </c>
       <c r="C267" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B268" t="s">
-        <v>784</v>
+        <v>774</v>
       </c>
       <c r="C268" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B269" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="C269" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B270" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
       <c r="C270" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B271" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="C271" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B272" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
       <c r="C272" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B273" t="s">
-        <v>789</v>
+        <v>779</v>
       </c>
       <c r="C273" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B274" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="C274" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B275" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
       <c r="C275" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B276" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="C276" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B277" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
       <c r="C277" t="s">
         <v>173</v>
@@ -6601,68 +6529,68 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B278" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="C278" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B279" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="C279" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B280" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="C280" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B281" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
       <c r="C281" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B282" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
       <c r="C282" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B283" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
       <c r="C283" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
@@ -6670,293 +6598,293 @@
         <v>431</v>
       </c>
       <c r="B284" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="C284" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B285" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
       <c r="C285" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B286" t="s">
-        <v>802</v>
+        <v>792</v>
       </c>
       <c r="C286" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B287" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
       <c r="C287" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B288" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
       <c r="C288" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B289" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="C289" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B290" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
       <c r="C290" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B291" t="s">
-        <v>807</v>
+        <v>797</v>
       </c>
       <c r="C291" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B292" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
       <c r="C292" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B293" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="C293" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B294" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
       <c r="C294" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B295" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
       <c r="C295" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B296" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
       <c r="C296" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B297" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
       <c r="C297" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B298" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="C298" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B299" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="C299" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B300" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="C300" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B301" t="s">
-        <v>817</v>
+        <v>807</v>
       </c>
       <c r="C301" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B302" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
       <c r="C302" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B303" t="s">
-        <v>819</v>
+        <v>809</v>
       </c>
       <c r="C303" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B304" t="s">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="C304" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B305" t="s">
-        <v>821</v>
+        <v>811</v>
       </c>
       <c r="C305" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B306" t="s">
-        <v>822</v>
+        <v>812</v>
       </c>
       <c r="C306" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B307" t="s">
-        <v>823</v>
+        <v>813</v>
       </c>
       <c r="C307" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B308" t="s">
-        <v>824</v>
+        <v>814</v>
       </c>
       <c r="C308" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B309" t="s">
-        <v>825</v>
+        <v>815</v>
       </c>
       <c r="C309" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B310" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="C310" t="s">
         <v>176</v>
@@ -6964,10 +6892,10 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B311" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="C311" t="s">
         <v>176</v>
@@ -6975,10 +6903,10 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B312" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="C312" t="s">
         <v>176</v>
@@ -6986,10 +6914,10 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B313" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="C313" t="s">
         <v>176</v>
@@ -6997,912 +6925,912 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>457</v>
+        <v>6</v>
       </c>
       <c r="B314" t="s">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="C314" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>458</v>
+        <v>26</v>
       </c>
       <c r="B315" t="s">
-        <v>831</v>
+        <v>821</v>
       </c>
       <c r="C315" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B316" t="s">
-        <v>832</v>
+        <v>4</v>
       </c>
       <c r="C316" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>459</v>
+        <v>49</v>
       </c>
       <c r="B317" t="s">
-        <v>833</v>
+        <v>822</v>
       </c>
       <c r="C317" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>460</v>
+        <v>57</v>
       </c>
       <c r="B318" t="s">
-        <v>834</v>
+        <v>823</v>
       </c>
       <c r="C318" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>461</v>
+        <v>66</v>
       </c>
       <c r="B319" t="s">
-        <v>835</v>
+        <v>824</v>
       </c>
       <c r="C319" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>462</v>
+        <v>66</v>
       </c>
       <c r="B320" t="s">
-        <v>836</v>
+        <v>825</v>
       </c>
       <c r="C320" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>463</v>
+        <v>78</v>
       </c>
       <c r="B321" t="s">
-        <v>837</v>
+        <v>826</v>
       </c>
       <c r="C321" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>464</v>
+        <v>79</v>
       </c>
       <c r="B322" t="s">
-        <v>838</v>
+        <v>827</v>
       </c>
       <c r="C322" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>465</v>
+        <v>99</v>
       </c>
       <c r="B323" t="s">
-        <v>839</v>
+        <v>828</v>
       </c>
       <c r="C323" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>466</v>
+        <v>106</v>
       </c>
       <c r="B324" t="s">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="C324" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>467</v>
+        <v>115</v>
       </c>
       <c r="B325" t="s">
-        <v>841</v>
+        <v>830</v>
       </c>
       <c r="C325" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>467</v>
+        <v>135</v>
       </c>
       <c r="B326" t="s">
-        <v>842</v>
+        <v>831</v>
       </c>
       <c r="C326" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="B327" t="s">
-        <v>843</v>
+        <v>832</v>
       </c>
       <c r="C327" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B328" t="s">
-        <v>844</v>
+        <v>833</v>
       </c>
       <c r="C328" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="B329" t="s">
-        <v>845</v>
+        <v>834</v>
       </c>
       <c r="C329" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>468</v>
+        <v>89</v>
       </c>
       <c r="B330" t="s">
-        <v>4</v>
+        <v>835</v>
       </c>
       <c r="C330" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="B331" t="s">
-        <v>846</v>
+        <v>836</v>
       </c>
       <c r="C331" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="B332" t="s">
-        <v>847</v>
+        <v>837</v>
       </c>
       <c r="C332" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="B333" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="C333" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="B334" t="s">
-        <v>849</v>
+        <v>839</v>
       </c>
       <c r="C334" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>78</v>
+        <v>460</v>
       </c>
       <c r="B335" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="C335" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>79</v>
+        <v>461</v>
       </c>
       <c r="B336" t="s">
-        <v>851</v>
+        <v>841</v>
       </c>
       <c r="C336" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>99</v>
+        <v>462</v>
       </c>
       <c r="B337" t="s">
-        <v>852</v>
+        <v>842</v>
       </c>
       <c r="C337" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>106</v>
+        <v>463</v>
       </c>
       <c r="B338" t="s">
-        <v>853</v>
+        <v>843</v>
       </c>
       <c r="C338" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>115</v>
+        <v>464</v>
       </c>
       <c r="B339" t="s">
-        <v>854</v>
+        <v>844</v>
       </c>
       <c r="C339" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="B340" t="s">
-        <v>855</v>
+        <v>845</v>
       </c>
       <c r="C340" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>469</v>
+        <v>8</v>
       </c>
       <c r="B341" t="s">
-        <v>856</v>
+        <v>846</v>
       </c>
       <c r="C341" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B342" t="s">
-        <v>857</v>
+        <v>847</v>
       </c>
       <c r="C342" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B343" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C343" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B344" t="s">
-        <v>859</v>
+        <v>849</v>
       </c>
       <c r="C344" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="B345" t="s">
-        <v>860</v>
+        <v>850</v>
       </c>
       <c r="C345" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="B346" t="s">
-        <v>861</v>
+        <v>851</v>
       </c>
       <c r="C346" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="B347" t="s">
-        <v>862</v>
+        <v>852</v>
       </c>
       <c r="C347" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B348" t="s">
-        <v>863</v>
+        <v>853</v>
       </c>
       <c r="C348" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>470</v>
+        <v>143</v>
       </c>
       <c r="B349" t="s">
-        <v>864</v>
+        <v>854</v>
       </c>
       <c r="C349" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>471</v>
+        <v>144</v>
       </c>
       <c r="B350" t="s">
-        <v>865</v>
+        <v>855</v>
       </c>
       <c r="C350" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>472</v>
+        <v>60</v>
       </c>
       <c r="B351" t="s">
-        <v>866</v>
+        <v>856</v>
       </c>
       <c r="C351" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>473</v>
+        <v>25</v>
       </c>
       <c r="B352" t="s">
-        <v>867</v>
+        <v>857</v>
       </c>
       <c r="C352" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>474</v>
+        <v>25</v>
       </c>
       <c r="B353" t="s">
-        <v>868</v>
+        <v>858</v>
       </c>
       <c r="C353" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>8</v>
+        <v>465</v>
       </c>
       <c r="B354" t="s">
-        <v>869</v>
+        <v>41</v>
       </c>
       <c r="C354" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="B355" t="s">
-        <v>870</v>
+        <v>859</v>
       </c>
       <c r="C355" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="B356" t="s">
-        <v>871</v>
+        <v>860</v>
       </c>
       <c r="C356" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="B357" t="s">
-        <v>872</v>
+        <v>861</v>
       </c>
       <c r="C357" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="B358" t="s">
-        <v>873</v>
+        <v>862</v>
       </c>
       <c r="C358" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="B359" t="s">
-        <v>874</v>
+        <v>863</v>
       </c>
       <c r="C359" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="B360" t="s">
-        <v>875</v>
+        <v>864</v>
       </c>
       <c r="C360" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>88</v>
+        <v>466</v>
       </c>
       <c r="B361" t="s">
-        <v>876</v>
+        <v>865</v>
       </c>
       <c r="C361" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>130</v>
+        <v>11</v>
       </c>
       <c r="B362" t="s">
-        <v>877</v>
+        <v>866</v>
       </c>
       <c r="C362" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>143</v>
+        <v>54</v>
       </c>
       <c r="B363" t="s">
-        <v>878</v>
+        <v>867</v>
       </c>
       <c r="C363" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="B364" t="s">
-        <v>879</v>
+        <v>868</v>
       </c>
       <c r="C364" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="B365" t="s">
-        <v>880</v>
+        <v>869</v>
       </c>
       <c r="C365" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>25</v>
+        <v>467</v>
       </c>
       <c r="B366" t="s">
-        <v>881</v>
+        <v>870</v>
       </c>
       <c r="C366" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>25</v>
+        <v>468</v>
       </c>
       <c r="B367" t="s">
-        <v>882</v>
+        <v>871</v>
       </c>
       <c r="C367" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B368" t="s">
-        <v>41</v>
+        <v>872</v>
       </c>
       <c r="C368" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="B369" t="s">
-        <v>883</v>
+        <v>873</v>
       </c>
       <c r="C369" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="B370" t="s">
-        <v>884</v>
+        <v>874</v>
       </c>
       <c r="C370" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>117</v>
+        <v>27</v>
       </c>
       <c r="B371" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="C371" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>132</v>
+        <v>470</v>
       </c>
       <c r="B372" t="s">
-        <v>886</v>
+        <v>42</v>
       </c>
       <c r="C372" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="B373" t="s">
-        <v>887</v>
+        <v>876</v>
       </c>
       <c r="C373" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="B374" t="s">
-        <v>888</v>
+        <v>877</v>
       </c>
       <c r="C374" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>476</v>
+        <v>55</v>
       </c>
       <c r="B375" t="s">
-        <v>889</v>
+        <v>878</v>
       </c>
       <c r="C375" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="B376" t="s">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="C376" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="B377" t="s">
-        <v>891</v>
+        <v>880</v>
       </c>
       <c r="C377" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="B378" t="s">
-        <v>892</v>
+        <v>881</v>
       </c>
       <c r="C378" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="B379" t="s">
-        <v>893</v>
+        <v>882</v>
       </c>
       <c r="C379" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>477</v>
+        <v>87</v>
       </c>
       <c r="B380" t="s">
-        <v>894</v>
+        <v>883</v>
       </c>
       <c r="C380" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>478</v>
+        <v>96</v>
       </c>
       <c r="B381" t="s">
-        <v>895</v>
+        <v>884</v>
       </c>
       <c r="C381" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>479</v>
+        <v>12</v>
       </c>
       <c r="B382" t="s">
-        <v>896</v>
+        <v>885</v>
       </c>
       <c r="C382" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B383" t="s">
-        <v>897</v>
+        <v>886</v>
       </c>
       <c r="C383" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B384" t="s">
-        <v>898</v>
+        <v>887</v>
       </c>
       <c r="C384" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B385" t="s">
-        <v>899</v>
+        <v>888</v>
       </c>
       <c r="C385" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>480</v>
+        <v>22</v>
       </c>
       <c r="B386" t="s">
-        <v>42</v>
+        <v>889</v>
       </c>
       <c r="C386" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="B387" t="s">
-        <v>900</v>
+        <v>890</v>
       </c>
       <c r="C387" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="B388" t="s">
-        <v>901</v>
+        <v>891</v>
       </c>
       <c r="C388" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="B389" t="s">
-        <v>902</v>
+        <v>892</v>
       </c>
       <c r="C389" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>72</v>
+        <v>471</v>
       </c>
       <c r="B390" t="s">
-        <v>903</v>
+        <v>36</v>
       </c>
       <c r="C390" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B391" t="s">
-        <v>904</v>
+        <v>893</v>
       </c>
       <c r="C391" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="B392" t="s">
-        <v>905</v>
+        <v>894</v>
       </c>
       <c r="C392" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="B393" t="s">
-        <v>906</v>
+        <v>895</v>
       </c>
       <c r="C393" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="B394" t="s">
-        <v>907</v>
+        <v>896</v>
       </c>
       <c r="C394" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="B395" t="s">
-        <v>908</v>
+        <v>897</v>
       </c>
       <c r="C395" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>12</v>
+        <v>126</v>
       </c>
       <c r="B396" t="s">
-        <v>909</v>
+        <v>898</v>
       </c>
       <c r="C396" t="s">
         <v>184</v>
@@ -7910,439 +7838,439 @@
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="B397" t="s">
-        <v>910</v>
+        <v>899</v>
       </c>
       <c r="C397" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B398" t="s">
-        <v>911</v>
+        <v>900</v>
       </c>
       <c r="C398" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="B399" t="s">
-        <v>912</v>
+        <v>901</v>
       </c>
       <c r="C399" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="B400" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="C400" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>23</v>
+        <v>122</v>
       </c>
       <c r="B401" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="C401" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>23</v>
+        <v>137</v>
       </c>
       <c r="B402" t="s">
-        <v>915</v>
+        <v>904</v>
       </c>
       <c r="C402" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="B403" t="s">
-        <v>916</v>
+        <v>905</v>
       </c>
       <c r="C403" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="B404" t="s">
-        <v>36</v>
+        <v>906</v>
       </c>
       <c r="C404" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>73</v>
+        <v>473</v>
       </c>
       <c r="B405" t="s">
-        <v>917</v>
+        <v>907</v>
       </c>
       <c r="C405" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>103</v>
+        <v>474</v>
       </c>
       <c r="B406" t="s">
-        <v>918</v>
+        <v>34</v>
       </c>
       <c r="C406" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>108</v>
+        <v>475</v>
       </c>
       <c r="B407" t="s">
-        <v>919</v>
+        <v>39</v>
       </c>
       <c r="C407" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="B408" t="s">
-        <v>920</v>
+        <v>908</v>
       </c>
       <c r="C408" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="B409" t="s">
-        <v>921</v>
+        <v>909</v>
       </c>
       <c r="C409" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="B410" t="s">
-        <v>922</v>
+        <v>910</v>
       </c>
       <c r="C410" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="B411" t="s">
-        <v>923</v>
+        <v>911</v>
       </c>
       <c r="C411" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="B412" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
       <c r="C412" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B413" t="s">
-        <v>925</v>
+        <v>913</v>
       </c>
       <c r="C413" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="B414" t="s">
-        <v>926</v>
+        <v>914</v>
       </c>
       <c r="C414" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="B415" t="s">
-        <v>927</v>
+        <v>915</v>
       </c>
       <c r="C415" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>137</v>
+        <v>476</v>
       </c>
       <c r="B416" t="s">
-        <v>928</v>
+        <v>44</v>
       </c>
       <c r="C416" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>145</v>
+        <v>74</v>
       </c>
       <c r="B417" t="s">
-        <v>929</v>
+        <v>916</v>
       </c>
       <c r="C417" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>482</v>
+        <v>74</v>
       </c>
       <c r="B418" t="s">
-        <v>930</v>
+        <v>917</v>
       </c>
       <c r="C418" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B419" t="s">
-        <v>931</v>
+        <v>918</v>
       </c>
       <c r="C419" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B420" t="s">
-        <v>34</v>
+        <v>919</v>
       </c>
       <c r="C420" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="B421" t="s">
-        <v>39</v>
+        <v>920</v>
       </c>
       <c r="C421" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="B422" t="s">
-        <v>932</v>
+        <v>921</v>
       </c>
       <c r="C422" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>75</v>
+        <v>480</v>
       </c>
       <c r="B423" t="s">
-        <v>933</v>
+        <v>43</v>
       </c>
       <c r="C423" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>75</v>
+        <v>481</v>
       </c>
       <c r="B424" t="s">
-        <v>934</v>
+        <v>45</v>
       </c>
       <c r="C424" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B425" t="s">
-        <v>935</v>
+        <v>922</v>
       </c>
       <c r="C425" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B426" t="s">
-        <v>936</v>
+        <v>923</v>
       </c>
       <c r="C426" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B427" t="s">
-        <v>937</v>
+        <v>924</v>
       </c>
       <c r="C427" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B428" t="s">
-        <v>938</v>
+        <v>925</v>
       </c>
       <c r="C428" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>32</v>
+        <v>482</v>
       </c>
       <c r="B429" t="s">
-        <v>939</v>
+        <v>926</v>
       </c>
       <c r="C429" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B430" t="s">
-        <v>44</v>
+        <v>927</v>
       </c>
       <c r="C430" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>74</v>
+        <v>482</v>
       </c>
       <c r="B431" t="s">
-        <v>940</v>
+        <v>928</v>
       </c>
       <c r="C431" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>74</v>
+        <v>482</v>
       </c>
       <c r="B432" t="s">
-        <v>941</v>
+        <v>929</v>
       </c>
       <c r="C432" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B433" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
       <c r="C433" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="B434" t="s">
-        <v>943</v>
+        <v>931</v>
       </c>
       <c r="C434" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="B435" t="s">
-        <v>944</v>
+        <v>932</v>
       </c>
       <c r="C435" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>28</v>
+        <v>483</v>
       </c>
       <c r="B436" t="s">
-        <v>945</v>
+        <v>933</v>
       </c>
       <c r="C436" t="s">
         <v>188</v>
@@ -8350,219 +8278,219 @@
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>490</v>
+        <v>15</v>
       </c>
       <c r="B437" t="s">
-        <v>43</v>
+        <v>934</v>
       </c>
       <c r="C437" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>491</v>
+        <v>15</v>
       </c>
       <c r="B438" t="s">
-        <v>45</v>
+        <v>935</v>
       </c>
       <c r="C438" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>92</v>
+        <v>484</v>
       </c>
       <c r="B439" t="s">
-        <v>946</v>
+        <v>3</v>
       </c>
       <c r="C439" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="B440" t="s">
-        <v>947</v>
+        <v>936</v>
       </c>
       <c r="C440" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B441" t="s">
-        <v>948</v>
+        <v>937</v>
       </c>
       <c r="C441" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>129</v>
+        <v>52</v>
       </c>
       <c r="B442" t="s">
-        <v>949</v>
+        <v>938</v>
       </c>
       <c r="C442" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>492</v>
+        <v>52</v>
       </c>
       <c r="B443" t="s">
-        <v>950</v>
+        <v>939</v>
       </c>
       <c r="C443" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>492</v>
+        <v>52</v>
       </c>
       <c r="B444" t="s">
-        <v>951</v>
+        <v>940</v>
       </c>
       <c r="C444" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>492</v>
+        <v>64</v>
       </c>
       <c r="B445" t="s">
-        <v>952</v>
+        <v>941</v>
       </c>
       <c r="C445" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>492</v>
+        <v>67</v>
       </c>
       <c r="B446" t="s">
-        <v>953</v>
+        <v>942</v>
       </c>
       <c r="C446" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>493</v>
+        <v>69</v>
       </c>
       <c r="B447" t="s">
-        <v>954</v>
+        <v>943</v>
       </c>
       <c r="C447" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>493</v>
+        <v>69</v>
       </c>
       <c r="B448" t="s">
-        <v>955</v>
+        <v>944</v>
       </c>
       <c r="C448" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>493</v>
+        <v>69</v>
       </c>
       <c r="B449" t="s">
-        <v>956</v>
+        <v>945</v>
       </c>
       <c r="C449" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>493</v>
+        <v>70</v>
       </c>
       <c r="B450" t="s">
-        <v>957</v>
+        <v>946</v>
       </c>
       <c r="C450" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="B451" t="s">
-        <v>958</v>
+        <v>947</v>
       </c>
       <c r="C451" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="B452" t="s">
-        <v>959</v>
+        <v>948</v>
       </c>
       <c r="C452" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>494</v>
+        <v>112</v>
       </c>
       <c r="B453" t="s">
-        <v>3</v>
+        <v>949</v>
       </c>
       <c r="C453" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="B454" t="s">
-        <v>960</v>
+        <v>950</v>
       </c>
       <c r="C454" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>80</v>
+        <v>485</v>
       </c>
       <c r="B455" t="s">
-        <v>961</v>
+        <v>951</v>
       </c>
       <c r="C455" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>52</v>
+        <v>486</v>
       </c>
       <c r="B456" t="s">
-        <v>962</v>
+        <v>952</v>
       </c>
       <c r="C456" t="s">
         <v>190</v>
@@ -8570,252 +8498,252 @@
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>52</v>
+        <v>487</v>
       </c>
       <c r="B457" t="s">
-        <v>963</v>
+        <v>35</v>
       </c>
       <c r="C457" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B458" t="s">
-        <v>964</v>
+        <v>953</v>
       </c>
       <c r="C458" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="B459" t="s">
-        <v>965</v>
+        <v>954</v>
       </c>
       <c r="C459" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="B460" t="s">
-        <v>966</v>
+        <v>955</v>
       </c>
       <c r="C460" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="B461" t="s">
-        <v>967</v>
+        <v>956</v>
       </c>
       <c r="C461" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="B462" t="s">
-        <v>968</v>
+        <v>957</v>
       </c>
       <c r="C462" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>69</v>
+        <v>147</v>
       </c>
       <c r="B463" t="s">
-        <v>969</v>
+        <v>958</v>
       </c>
       <c r="C463" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>70</v>
+        <v>488</v>
       </c>
       <c r="B464" t="s">
-        <v>970</v>
+        <v>959</v>
       </c>
       <c r="C464" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="B465" t="s">
-        <v>971</v>
+        <v>960</v>
       </c>
       <c r="C465" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>104</v>
+        <v>9</v>
       </c>
       <c r="B466" t="s">
-        <v>972</v>
+        <v>961</v>
       </c>
       <c r="C466" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>112</v>
+        <v>489</v>
       </c>
       <c r="B467" t="s">
-        <v>973</v>
+        <v>38</v>
       </c>
       <c r="C467" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="B468" t="s">
-        <v>974</v>
+        <v>962</v>
       </c>
       <c r="C468" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>495</v>
+        <v>53</v>
       </c>
       <c r="B469" t="s">
-        <v>975</v>
+        <v>963</v>
       </c>
       <c r="C469" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>496</v>
+        <v>56</v>
       </c>
       <c r="B470" t="s">
-        <v>976</v>
+        <v>964</v>
       </c>
       <c r="C470" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>497</v>
+        <v>56</v>
       </c>
       <c r="B471" t="s">
-        <v>35</v>
+        <v>965</v>
       </c>
       <c r="C471" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B472" t="s">
-        <v>977</v>
+        <v>966</v>
       </c>
       <c r="C472" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="B473" t="s">
-        <v>978</v>
+        <v>967</v>
       </c>
       <c r="C473" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="B474" t="s">
-        <v>979</v>
+        <v>968</v>
       </c>
       <c r="C474" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="B475" t="s">
-        <v>980</v>
+        <v>969</v>
       </c>
       <c r="C475" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>146</v>
+        <v>94</v>
       </c>
       <c r="B476" t="s">
-        <v>981</v>
+        <v>970</v>
       </c>
       <c r="C476" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="B477" t="s">
-        <v>982</v>
+        <v>971</v>
       </c>
       <c r="C477" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>498</v>
+        <v>139</v>
       </c>
       <c r="B478" t="s">
-        <v>983</v>
+        <v>972</v>
       </c>
       <c r="C478" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>7</v>
+        <v>490</v>
       </c>
       <c r="B479" t="s">
-        <v>984</v>
+        <v>973</v>
       </c>
       <c r="C479" t="s">
         <v>192</v>
@@ -8823,10 +8751,10 @@
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>9</v>
+        <v>491</v>
       </c>
       <c r="B480" t="s">
-        <v>985</v>
+        <v>974</v>
       </c>
       <c r="C480" t="s">
         <v>192</v>
@@ -8834,672 +8762,518 @@
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="B481" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C481" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>53</v>
+        <v>493</v>
       </c>
       <c r="B482" t="s">
-        <v>986</v>
+        <v>48</v>
       </c>
       <c r="C482" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B483" t="s">
-        <v>987</v>
+        <v>975</v>
       </c>
       <c r="C483" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B484" t="s">
-        <v>988</v>
+        <v>976</v>
       </c>
       <c r="C484" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B485" t="s">
-        <v>989</v>
+        <v>977</v>
       </c>
       <c r="C485" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="B486" t="s">
-        <v>990</v>
+        <v>978</v>
       </c>
       <c r="C486" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="B487" t="s">
-        <v>991</v>
+        <v>979</v>
       </c>
       <c r="C487" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>71</v>
+        <v>494</v>
       </c>
       <c r="B488" t="s">
-        <v>992</v>
+        <v>980</v>
       </c>
       <c r="C488" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>90</v>
+        <v>495</v>
       </c>
       <c r="B489" t="s">
-        <v>993</v>
+        <v>981</v>
       </c>
       <c r="C489" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="B490" t="s">
-        <v>994</v>
+        <v>982</v>
       </c>
       <c r="C490" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="B491" t="s">
-        <v>995</v>
+        <v>983</v>
       </c>
       <c r="C491" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="B492" t="s">
-        <v>996</v>
+        <v>984</v>
       </c>
       <c r="C492" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B493" t="s">
-        <v>997</v>
+        <v>985</v>
       </c>
       <c r="C493" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>501</v>
+        <v>77</v>
       </c>
       <c r="B494" t="s">
-        <v>998</v>
+        <v>986</v>
       </c>
       <c r="C494" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>502</v>
+        <v>131</v>
       </c>
       <c r="B495" t="s">
-        <v>33</v>
+        <v>987</v>
       </c>
       <c r="C495" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>503</v>
+        <v>138</v>
       </c>
       <c r="B496" t="s">
-        <v>48</v>
+        <v>988</v>
       </c>
       <c r="C496" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="B497" t="s">
-        <v>999</v>
+        <v>989</v>
       </c>
       <c r="C497" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="B498" t="s">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="C498" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>51</v>
+        <v>497</v>
       </c>
       <c r="B499" t="s">
-        <v>1001</v>
+        <v>37</v>
       </c>
       <c r="C499" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>109</v>
+        <v>498</v>
       </c>
       <c r="B500" t="s">
-        <v>1002</v>
+        <v>40</v>
       </c>
       <c r="C500" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="B501" t="s">
-        <v>1003</v>
+        <v>991</v>
       </c>
       <c r="C501" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
-        <v>504</v>
+        <v>107</v>
       </c>
       <c r="B502" t="s">
-        <v>1004</v>
+        <v>992</v>
       </c>
       <c r="C502" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>505</v>
+        <v>128</v>
       </c>
       <c r="B503" t="s">
-        <v>1005</v>
+        <v>993</v>
       </c>
       <c r="C503" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>19</v>
+        <v>136</v>
       </c>
       <c r="B504" t="s">
-        <v>1006</v>
+        <v>994</v>
       </c>
       <c r="C504" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B505" t="s">
-        <v>1007</v>
+        <v>995</v>
       </c>
       <c r="C505" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
-        <v>20</v>
+        <v>499</v>
       </c>
       <c r="B506" t="s">
-        <v>1008</v>
+        <v>46</v>
       </c>
       <c r="C506" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
-        <v>506</v>
+        <v>113</v>
       </c>
       <c r="B507" t="s">
-        <v>1009</v>
+        <v>996</v>
       </c>
       <c r="C507" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="B508" t="s">
-        <v>1010</v>
+        <v>997</v>
       </c>
       <c r="C508" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B509" t="s">
-        <v>1011</v>
+        <v>998</v>
       </c>
       <c r="C509" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B510" t="s">
-        <v>1012</v>
+        <v>999</v>
       </c>
       <c r="C510" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
-        <v>141</v>
+        <v>500</v>
       </c>
       <c r="B511" t="s">
-        <v>1013</v>
+        <v>1000</v>
       </c>
       <c r="C511" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
-        <v>10</v>
+        <v>501</v>
       </c>
       <c r="B512" t="s">
-        <v>1014</v>
+        <v>1001</v>
       </c>
       <c r="C512" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>507</v>
+        <v>5</v>
       </c>
       <c r="B513" t="s">
-        <v>37</v>
+        <v>1002</v>
       </c>
       <c r="C513" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
-        <v>508</v>
+        <v>5</v>
       </c>
       <c r="B514" t="s">
-        <v>40</v>
+        <v>1003</v>
       </c>
       <c r="C514" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="B515" t="s">
-        <v>1015</v>
+        <v>1004</v>
       </c>
       <c r="C515" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
-        <v>107</v>
+        <v>30</v>
       </c>
       <c r="B516" t="s">
-        <v>1016</v>
+        <v>1005</v>
       </c>
       <c r="C516" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
-        <v>128</v>
+        <v>31</v>
       </c>
       <c r="B517" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
       <c r="C517" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
-        <v>136</v>
+        <v>502</v>
       </c>
       <c r="B518" t="s">
-        <v>1018</v>
+        <v>47</v>
       </c>
       <c r="C518" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="B519" t="s">
-        <v>1019</v>
+        <v>1007</v>
       </c>
       <c r="C519" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
-        <v>509</v>
+        <v>102</v>
       </c>
       <c r="B520" t="s">
-        <v>46</v>
+        <v>1008</v>
       </c>
       <c r="C520" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B521" t="s">
-        <v>1020</v>
+        <v>1009</v>
       </c>
       <c r="C521" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
-        <v>119</v>
+        <v>503</v>
       </c>
       <c r="B522" t="s">
-        <v>1021</v>
+        <v>1010</v>
       </c>
       <c r="C522" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
-        <v>125</v>
+        <v>504</v>
       </c>
       <c r="B523" t="s">
-        <v>1022</v>
+        <v>1011</v>
       </c>
       <c r="C523" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
-        <v>142</v>
+        <v>505</v>
       </c>
       <c r="B524" t="s">
-        <v>1023</v>
+        <v>505</v>
       </c>
       <c r="C524" t="s">
-        <v>196</v>
+        <v>157</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B525" t="s">
-        <v>1024</v>
+        <v>1012</v>
       </c>
       <c r="C525" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B526" t="s">
-        <v>1025</v>
+        <v>1013</v>
       </c>
       <c r="C526" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
-        <v>5</v>
+        <v>507</v>
       </c>
       <c r="B527" t="s">
-        <v>1026</v>
+        <v>507</v>
       </c>
       <c r="C527" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A528" t="s">
-        <v>5</v>
-      </c>
-      <c r="B528" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C528" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A529" t="s">
-        <v>30</v>
-      </c>
-      <c r="B529" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C529" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A530" t="s">
-        <v>30</v>
-      </c>
-      <c r="B530" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C530" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A531" t="s">
-        <v>31</v>
-      </c>
-      <c r="B531" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C531" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A532" t="s">
-        <v>512</v>
-      </c>
-      <c r="B532" t="s">
-        <v>47</v>
-      </c>
-      <c r="C532" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A533" t="s">
-        <v>58</v>
-      </c>
-      <c r="B533" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C533" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A534" t="s">
-        <v>102</v>
-      </c>
-      <c r="B534" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C534" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A535" t="s">
-        <v>111</v>
-      </c>
-      <c r="B535" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C535" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A536" t="s">
-        <v>513</v>
-      </c>
-      <c r="B536" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C536" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A537" t="s">
-        <v>514</v>
-      </c>
-      <c r="B537" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C537" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A538" t="s">
-        <v>515</v>
-      </c>
-      <c r="B538" t="s">
-        <v>515</v>
-      </c>
-      <c r="C538" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A539" t="s">
-        <v>516</v>
-      </c>
-      <c r="B539" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C539" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A540" t="s">
-        <v>516</v>
-      </c>
-      <c r="B540" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C540" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A541" t="s">
-        <v>517</v>
-      </c>
-      <c r="B541" t="s">
-        <v>517</v>
-      </c>
-      <c r="C541" t="s">
         <v>196</v>
       </c>
     </row>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0B033A-9974-4035-AA3B-18B0D08F2C89}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D3829D-1E0C-4305-8FA1-FA40B376CED9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="748">
   <si>
     <t>UTK</t>
   </si>
@@ -489,9 +489,6 @@
     <t>260528-F00008049</t>
   </si>
   <si>
-    <t>260529-W00001304</t>
-  </si>
-  <si>
     <t>313705013</t>
   </si>
   <si>
@@ -522,9 +519,6 @@
     <t>NFE6-05-28-FS5A</t>
   </si>
   <si>
-    <t>260513-F00016572</t>
-  </si>
-  <si>
     <t>260523-F00002906</t>
   </si>
   <si>
@@ -594,9 +588,6 @@
     <t>313435748</t>
   </si>
   <si>
-    <t>NFE6-05-28-5VN6</t>
-  </si>
-  <si>
     <t>260519-F00008180</t>
   </si>
   <si>
@@ -726,9 +717,6 @@
     <t>313556927</t>
   </si>
   <si>
-    <t>313631685</t>
-  </si>
-  <si>
     <t>NFE6-05-28-3XCV</t>
   </si>
   <si>
@@ -750,9 +738,6 @@
     <t>260527-W00006108</t>
   </si>
   <si>
-    <t>260527-W00006936</t>
-  </si>
-  <si>
     <t>260527-W00008891</t>
   </si>
   <si>
@@ -774,9 +759,6 @@
     <t>313380775</t>
   </si>
   <si>
-    <t>260521-F00012066</t>
-  </si>
-  <si>
     <t>260522-F00005522</t>
   </si>
   <si>
@@ -834,9 +816,6 @@
     <t>R421928</t>
   </si>
   <si>
-    <t>260522-W00003720</t>
-  </si>
-  <si>
     <t>260527-F00014893</t>
   </si>
   <si>
@@ -858,9 +837,6 @@
     <t>260519-F00008935</t>
   </si>
   <si>
-    <t>260521-W00003289</t>
-  </si>
-  <si>
     <t>260522-F00002340</t>
   </si>
   <si>
@@ -972,9 +948,6 @@
     <t>260528-F00003495</t>
   </si>
   <si>
-    <t>260528-F00009589</t>
-  </si>
-  <si>
     <t>260528-F00010254</t>
   </si>
   <si>
@@ -987,9 +960,6 @@
     <t>NFE6-05-28-MXCW</t>
   </si>
   <si>
-    <t>260520-F00013842</t>
-  </si>
-  <si>
     <t>260527-W00011085</t>
   </si>
   <si>
@@ -1200,9 +1170,6 @@
     <t>6a1829e58046ce4dbfbab9c5</t>
   </si>
   <si>
-    <t>6a1933ac8046ce4dbfbac744</t>
-  </si>
-  <si>
     <t>313705013/1</t>
   </si>
   <si>
@@ -1233,9 +1200,6 @@
     <t>202605292601146901</t>
   </si>
   <si>
-    <t>6a181a968046ce4dbfbab76d</t>
-  </si>
-  <si>
     <t>6a16db0e8046ce4dbfbaa22c</t>
   </si>
   <si>
@@ -1323,9 +1287,6 @@
     <t>313435748/2</t>
   </si>
   <si>
-    <t>202605292601145801</t>
-  </si>
-  <si>
     <t>6a0f38288046ce4dbfba48b7</t>
   </si>
   <si>
@@ -1476,9 +1437,6 @@
     <t>313556927/1</t>
   </si>
   <si>
-    <t>313631685/1</t>
-  </si>
-  <si>
     <t>202605292601147301</t>
   </si>
   <si>
@@ -1509,9 +1467,6 @@
     <t>6a16ee6d8046ce4dbfbaa526</t>
   </si>
   <si>
-    <t>6a16fedd8046ce4dbfbaa7c4</t>
-  </si>
-  <si>
     <t>6a1731308046ce4dbfbaac63</t>
   </si>
   <si>
@@ -1533,9 +1488,6 @@
     <t>313380775/1</t>
   </si>
   <si>
-    <t>6a1800e48046ce4dbfbab353</t>
-  </si>
-  <si>
     <t>6a16f7508046ce4dbfbaa694</t>
   </si>
   <si>
@@ -1620,9 +1572,6 @@
     <t>159995579540611877</t>
   </si>
   <si>
-    <t>6a16e6998046ce4dbfbaa3dd</t>
-  </si>
-  <si>
     <t>6a17406e8046ce4dbfbaad37</t>
   </si>
   <si>
@@ -1644,9 +1593,6 @@
     <t>6a0c4e898046ce4dbfba0a12</t>
   </si>
   <si>
-    <t>6a1072b88046ce4dbfba5cc2</t>
-  </si>
-  <si>
     <t>6a1948628046ce4dbfbac9c3</t>
   </si>
   <si>
@@ -1794,12 +1740,6 @@
     <t>6a1800a88046ce4dbfbab33f</t>
   </si>
   <si>
-    <t>6a183a118046ce4dbfbabc0f</t>
-  </si>
-  <si>
-    <t>6a183a118046ce4dbfbabc10</t>
-  </si>
-  <si>
     <t>6a1841148046ce4dbfbabd45</t>
   </si>
   <si>
@@ -1813,9 +1753,6 @@
   </si>
   <si>
     <t>202605292601146401</t>
-  </si>
-  <si>
-    <t>6a1837358046ce4dbfbabb98</t>
   </si>
   <si>
     <t>6a1762698046ce4dbfbaadc3</t>
@@ -2654,7 +2591,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D403"/>
+  <dimension ref="A1:D392"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
@@ -2679,7 +2616,7 @@
         <v>137</v>
       </c>
       <c r="B2" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C2" t="s">
         <v>88</v>
@@ -2691,7 +2628,7 @@
         <v>137</v>
       </c>
       <c r="B3" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C3" t="s">
         <v>88</v>
@@ -2703,7 +2640,7 @@
         <v>138</v>
       </c>
       <c r="B4" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C4" t="s">
         <v>88</v>
@@ -2715,7 +2652,7 @@
         <v>139</v>
       </c>
       <c r="B5" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C5" t="s">
         <v>88</v>
@@ -2727,7 +2664,7 @@
         <v>140</v>
       </c>
       <c r="B6" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C6" t="s">
         <v>88</v>
@@ -2739,7 +2676,7 @@
         <v>141</v>
       </c>
       <c r="B7" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="C7" t="s">
         <v>88</v>
@@ -2751,7 +2688,7 @@
         <v>142</v>
       </c>
       <c r="B8" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C8" t="s">
         <v>88</v>
@@ -2763,7 +2700,7 @@
         <v>142</v>
       </c>
       <c r="B9" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C9" t="s">
         <v>88</v>
@@ -2775,7 +2712,7 @@
         <v>143</v>
       </c>
       <c r="B10" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C10" t="s">
         <v>89</v>
@@ -2787,7 +2724,7 @@
         <v>143</v>
       </c>
       <c r="B11" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C11" t="s">
         <v>89</v>
@@ -2799,7 +2736,7 @@
         <v>144</v>
       </c>
       <c r="B12" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="C12" t="s">
         <v>89</v>
@@ -2811,7 +2748,7 @@
         <v>144</v>
       </c>
       <c r="B13" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="C13" t="s">
         <v>89</v>
@@ -2823,7 +2760,7 @@
         <v>145</v>
       </c>
       <c r="B14" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C14" t="s">
         <v>89</v>
@@ -2835,7 +2772,7 @@
         <v>146</v>
       </c>
       <c r="B15" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C15" t="s">
         <v>89</v>
@@ -2847,7 +2784,7 @@
         <v>147</v>
       </c>
       <c r="B16" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="C16" t="s">
         <v>89</v>
@@ -2859,7 +2796,7 @@
         <v>148</v>
       </c>
       <c r="B17" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C17" t="s">
         <v>89</v>
@@ -2871,7 +2808,7 @@
         <v>149</v>
       </c>
       <c r="B18" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="C18" t="s">
         <v>89</v>
@@ -2883,7 +2820,7 @@
         <v>150</v>
       </c>
       <c r="B19" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C19" t="s">
         <v>90</v>
@@ -2895,7 +2832,7 @@
         <v>150</v>
       </c>
       <c r="B20" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C20" t="s">
         <v>90</v>
@@ -2907,7 +2844,7 @@
         <v>151</v>
       </c>
       <c r="B21" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C21" t="s">
         <v>90</v>
@@ -2919,7 +2856,7 @@
         <v>151</v>
       </c>
       <c r="B22" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="C22" t="s">
         <v>90</v>
@@ -2931,7 +2868,7 @@
         <v>151</v>
       </c>
       <c r="B23" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="C23" t="s">
         <v>90</v>
@@ -2943,7 +2880,7 @@
         <v>152</v>
       </c>
       <c r="B24" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C24" t="s">
         <v>91</v>
@@ -2955,7 +2892,7 @@
         <v>153</v>
       </c>
       <c r="B25" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C25" t="s">
         <v>91</v>
@@ -2967,7 +2904,7 @@
         <v>154</v>
       </c>
       <c r="B26" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="C26" t="s">
         <v>91</v>
@@ -2979,7 +2916,7 @@
         <v>155</v>
       </c>
       <c r="B27" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C27" t="s">
         <v>91</v>
@@ -2991,10 +2928,10 @@
         <v>156</v>
       </c>
       <c r="B28" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="C28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D28"/>
     </row>
@@ -3003,7 +2940,7 @@
         <v>157</v>
       </c>
       <c r="B29" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="C29" t="s">
         <v>92</v>
@@ -3015,7 +2952,7 @@
         <v>158</v>
       </c>
       <c r="B30" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="C30" t="s">
         <v>92</v>
@@ -3027,7 +2964,7 @@
         <v>159</v>
       </c>
       <c r="B31" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="C31" t="s">
         <v>92</v>
@@ -3039,7 +2976,7 @@
         <v>160</v>
       </c>
       <c r="B32" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="C32" t="s">
         <v>92</v>
@@ -3051,7 +2988,7 @@
         <v>161</v>
       </c>
       <c r="B33" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C33" t="s">
         <v>92</v>
@@ -3063,7 +3000,7 @@
         <v>162</v>
       </c>
       <c r="B34" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="C34" t="s">
         <v>92</v>
@@ -3075,10 +3012,10 @@
         <v>163</v>
       </c>
       <c r="B35" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D35"/>
     </row>
@@ -3087,7 +3024,7 @@
         <v>164</v>
       </c>
       <c r="B36" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="C36" t="s">
         <v>93</v>
@@ -3099,7 +3036,7 @@
         <v>165</v>
       </c>
       <c r="B37" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="C37" t="s">
         <v>93</v>
@@ -3111,7 +3048,7 @@
         <v>166</v>
       </c>
       <c r="B38" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C38" t="s">
         <v>93</v>
@@ -3123,7 +3060,7 @@
         <v>167</v>
       </c>
       <c r="B39" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C39" t="s">
         <v>93</v>
@@ -3132,10 +3069,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B40" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C40" t="s">
         <v>93</v>
@@ -3144,10 +3081,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B41" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="C41" t="s">
         <v>93</v>
@@ -3156,10 +3093,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B42" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C42" t="s">
         <v>93</v>
@@ -3171,10 +3108,10 @@
         <v>169</v>
       </c>
       <c r="B43" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C43" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D43"/>
     </row>
@@ -3183,10 +3120,10 @@
         <v>170</v>
       </c>
       <c r="B44" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="C44" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D44"/>
     </row>
@@ -3195,7 +3132,7 @@
         <v>171</v>
       </c>
       <c r="B45" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C45" t="s">
         <v>94</v>
@@ -3207,7 +3144,7 @@
         <v>172</v>
       </c>
       <c r="B46" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="C46" t="s">
         <v>94</v>
@@ -3219,7 +3156,7 @@
         <v>173</v>
       </c>
       <c r="B47" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C47" t="s">
         <v>94</v>
@@ -3231,7 +3168,7 @@
         <v>174</v>
       </c>
       <c r="B48" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="C48" t="s">
         <v>94</v>
@@ -3240,10 +3177,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B49" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="C49" t="s">
         <v>94</v>
@@ -3252,10 +3189,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B50" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="C50" t="s">
         <v>94</v>
@@ -3267,7 +3204,7 @@
         <v>176</v>
       </c>
       <c r="B51" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C51" t="s">
         <v>94</v>
@@ -3279,7 +3216,7 @@
         <v>177</v>
       </c>
       <c r="B52" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="C52" t="s">
         <v>94</v>
@@ -3291,7 +3228,7 @@
         <v>178</v>
       </c>
       <c r="B53" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C53" t="s">
         <v>94</v>
@@ -3300,10 +3237,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B54" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="C54" t="s">
         <v>94</v>
@@ -3312,10 +3249,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B55" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C55" t="s">
         <v>94</v>
@@ -3327,31 +3264,31 @@
         <v>180</v>
       </c>
       <c r="B56" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="C56" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D56"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B57" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="C57" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D57"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B58" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="C58" t="s">
         <v>95</v>
@@ -3363,7 +3300,7 @@
         <v>182</v>
       </c>
       <c r="B59" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="C59" t="s">
         <v>95</v>
@@ -3375,7 +3312,7 @@
         <v>183</v>
       </c>
       <c r="B60" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="C60" t="s">
         <v>95</v>
@@ -3387,7 +3324,7 @@
         <v>184</v>
       </c>
       <c r="B61" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="C61" t="s">
         <v>95</v>
@@ -3399,7 +3336,7 @@
         <v>185</v>
       </c>
       <c r="B62" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="C62" t="s">
         <v>95</v>
@@ -3408,10 +3345,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B63" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="C63" t="s">
         <v>95</v>
@@ -3420,13 +3357,13 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B64" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C64" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D64"/>
     </row>
@@ -3435,10 +3372,10 @@
         <v>187</v>
       </c>
       <c r="B65" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C65" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D65"/>
     </row>
@@ -3447,10 +3384,10 @@
         <v>188</v>
       </c>
       <c r="B66" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C66" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D66"/>
     </row>
@@ -3459,7 +3396,7 @@
         <v>189</v>
       </c>
       <c r="B67" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="C67" t="s">
         <v>96</v>
@@ -3471,10 +3408,10 @@
         <v>190</v>
       </c>
       <c r="B68" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="C68" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D68"/>
     </row>
@@ -3483,10 +3420,10 @@
         <v>191</v>
       </c>
       <c r="B69" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="C69" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D69"/>
     </row>
@@ -3495,10 +3432,10 @@
         <v>192</v>
       </c>
       <c r="B70" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C70" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D70"/>
     </row>
@@ -3507,7 +3444,7 @@
         <v>193</v>
       </c>
       <c r="B71" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="C71" t="s">
         <v>97</v>
@@ -3519,7 +3456,7 @@
         <v>194</v>
       </c>
       <c r="B72" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C72" t="s">
         <v>97</v>
@@ -3531,7 +3468,7 @@
         <v>195</v>
       </c>
       <c r="B73" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="C73" t="s">
         <v>97</v>
@@ -3543,7 +3480,7 @@
         <v>196</v>
       </c>
       <c r="B74" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="C74" t="s">
         <v>97</v>
@@ -3555,10 +3492,10 @@
         <v>197</v>
       </c>
       <c r="B75" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C75" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D75"/>
     </row>
@@ -3567,30 +3504,30 @@
         <v>198</v>
       </c>
       <c r="B76" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="C76" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D76"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B77" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="C77" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B78" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="C78" t="s">
         <v>98</v>
@@ -3598,10 +3535,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B79" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="C79" t="s">
         <v>98</v>
@@ -3612,7 +3549,7 @@
         <v>201</v>
       </c>
       <c r="B80" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="C80" t="s">
         <v>98</v>
@@ -3623,7 +3560,7 @@
         <v>202</v>
       </c>
       <c r="B81" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="C81" t="s">
         <v>98</v>
@@ -3634,7 +3571,7 @@
         <v>203</v>
       </c>
       <c r="B82" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C82" t="s">
         <v>98</v>
@@ -3642,10 +3579,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B83" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="C83" t="s">
         <v>98</v>
@@ -3653,24 +3590,24 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B84" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C84" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B85" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C85" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
@@ -3678,18 +3615,18 @@
         <v>206</v>
       </c>
       <c r="B86" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="C86" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B87" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C87" t="s">
         <v>99</v>
@@ -3697,10 +3634,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B88" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="C88" t="s">
         <v>99</v>
@@ -3708,10 +3645,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B89" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="C89" t="s">
         <v>99</v>
@@ -3722,7 +3659,7 @@
         <v>209</v>
       </c>
       <c r="B90" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="C90" t="s">
         <v>99</v>
@@ -3733,7 +3670,7 @@
         <v>210</v>
       </c>
       <c r="B91" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="C91" t="s">
         <v>99</v>
@@ -3744,7 +3681,7 @@
         <v>211</v>
       </c>
       <c r="B92" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="C92" t="s">
         <v>99</v>
@@ -3755,10 +3692,10 @@
         <v>212</v>
       </c>
       <c r="B93" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="C93" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -3766,29 +3703,29 @@
         <v>213</v>
       </c>
       <c r="B94" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="C94" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B95" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C95" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B96" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="C96" t="s">
         <v>100</v>
@@ -3796,13 +3733,13 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B97" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="C97" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
@@ -3810,10 +3747,10 @@
         <v>216</v>
       </c>
       <c r="B98" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="C98" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
@@ -3821,18 +3758,18 @@
         <v>217</v>
       </c>
       <c r="B99" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="C99" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B100" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="C100" t="s">
         <v>101</v>
@@ -3840,10 +3777,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B101" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C101" t="s">
         <v>101</v>
@@ -3851,10 +3788,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B102" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="C102" t="s">
         <v>101</v>
@@ -3865,10 +3802,10 @@
         <v>220</v>
       </c>
       <c r="B103" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="C103" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
@@ -3876,29 +3813,29 @@
         <v>221</v>
       </c>
       <c r="B104" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="C104" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B105" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="C105" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B106" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="C106" t="s">
         <v>102</v>
@@ -3906,10 +3843,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B107" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="C107" t="s">
         <v>102</v>
@@ -3920,7 +3857,7 @@
         <v>224</v>
       </c>
       <c r="B108" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="C108" t="s">
         <v>102</v>
@@ -3928,10 +3865,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B109" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="C109" t="s">
         <v>102</v>
@@ -3939,10 +3876,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B110" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="C110" t="s">
         <v>102</v>
@@ -3950,10 +3887,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B111" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="C111" t="s">
         <v>102</v>
@@ -3964,7 +3901,7 @@
         <v>227</v>
       </c>
       <c r="B112" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="C112" t="s">
         <v>102</v>
@@ -3975,7 +3912,7 @@
         <v>228</v>
       </c>
       <c r="B113" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="C113" t="s">
         <v>102</v>
@@ -3986,7 +3923,7 @@
         <v>229</v>
       </c>
       <c r="B114" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="C114" t="s">
         <v>102</v>
@@ -3997,7 +3934,7 @@
         <v>230</v>
       </c>
       <c r="B115" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="C115" t="s">
         <v>102</v>
@@ -4005,10 +3942,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B116" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="C116" t="s">
         <v>102</v>
@@ -4016,10 +3953,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B117" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="C117" t="s">
         <v>102</v>
@@ -4027,54 +3964,54 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B118" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C118" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B119" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="C119" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B120" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="C120" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B121" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C121" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B122" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="C122" t="s">
         <v>103</v>
@@ -4082,10 +4019,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B123" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="C123" t="s">
         <v>103</v>
@@ -4093,10 +4030,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B124" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="C124" t="s">
         <v>103</v>
@@ -4107,7 +4044,7 @@
         <v>237</v>
       </c>
       <c r="B125" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="C125" t="s">
         <v>103</v>
@@ -4118,7 +4055,7 @@
         <v>238</v>
       </c>
       <c r="B126" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="C126" t="s">
         <v>103</v>
@@ -4129,7 +4066,7 @@
         <v>239</v>
       </c>
       <c r="B127" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="C127" t="s">
         <v>103</v>
@@ -4140,7 +4077,7 @@
         <v>240</v>
       </c>
       <c r="B128" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="C128" t="s">
         <v>103</v>
@@ -4151,7 +4088,7 @@
         <v>241</v>
       </c>
       <c r="B129" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="C129" t="s">
         <v>103</v>
@@ -4162,7 +4099,7 @@
         <v>242</v>
       </c>
       <c r="B130" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="C130" t="s">
         <v>103</v>
@@ -4173,10 +4110,10 @@
         <v>243</v>
       </c>
       <c r="B131" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="C131" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
@@ -4184,51 +4121,51 @@
         <v>244</v>
       </c>
       <c r="B132" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="C132" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B133" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="C133" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B134" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="C134" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B135" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="C135" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B136" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="C136" t="s">
         <v>104</v>
@@ -4236,131 +4173,131 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B137" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="C137" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B138" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="C138" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B139" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="C139" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B140" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="C140" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B141" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="C141" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B142" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="C142" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B143" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="C143" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B144" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="C144" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B145" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="C145" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B146" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="C146" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B147" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="C147" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B148" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="C148" t="s">
         <v>106</v>
@@ -4368,10 +4305,10 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B149" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="C149" t="s">
         <v>106</v>
@@ -4379,10 +4316,10 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B150" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C150" t="s">
         <v>106</v>
@@ -4390,10 +4327,10 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B151" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="C151" t="s">
         <v>106</v>
@@ -4401,10 +4338,10 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B152" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="C152" t="s">
         <v>106</v>
@@ -4412,10 +4349,10 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B153" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="C153" t="s">
         <v>106</v>
@@ -4423,10 +4360,10 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B154" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="C154" t="s">
         <v>106</v>
@@ -4434,10 +4371,10 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B155" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="C155" t="s">
         <v>106</v>
@@ -4445,10 +4382,10 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B156" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="C156" t="s">
         <v>106</v>
@@ -4456,10 +4393,10 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B157" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="C157" t="s">
         <v>106</v>
@@ -4467,10 +4404,10 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B158" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="C158" t="s">
         <v>106</v>
@@ -4478,57 +4415,57 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B159" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="C159" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B160" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="C160" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B161" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="C161" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B162" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="C162" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B163" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="C163" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
@@ -4536,10 +4473,10 @@
         <v>267</v>
       </c>
       <c r="B164" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="C164" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
@@ -4547,10 +4484,10 @@
         <v>268</v>
       </c>
       <c r="B165" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="C165" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
@@ -4558,10 +4495,10 @@
         <v>269</v>
       </c>
       <c r="B166" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="C166" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
@@ -4569,10 +4506,10 @@
         <v>270</v>
       </c>
       <c r="B167" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="C167" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
@@ -4580,10 +4517,10 @@
         <v>271</v>
       </c>
       <c r="B168" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="C168" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
@@ -4591,10 +4528,10 @@
         <v>272</v>
       </c>
       <c r="B169" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="C169" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
@@ -4602,10 +4539,10 @@
         <v>273</v>
       </c>
       <c r="B170" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="C170" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
@@ -4613,227 +4550,227 @@
         <v>274</v>
       </c>
       <c r="B171" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="C171" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B172" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="C172" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B173" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="C173" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B174" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="C174" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B175" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="C175" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B176" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="C176" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B177" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="C177" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B178" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="C178" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B179" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="C179" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B180" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="C180" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B181" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="C181" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B182" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="C182" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B183" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="C183" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B184" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="C184" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B185" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="C185" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B186" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="C186" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B187" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="C187" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B188" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="C188" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B189" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="C189" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B190" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="C190" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B191" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="C191" t="s">
         <v>111</v>
@@ -4841,10 +4778,10 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B192" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="C192" t="s">
         <v>111</v>
@@ -4852,186 +4789,186 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B193" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="C193" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B194" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="C194" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B195" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="C195" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B196" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="C196" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B197" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="C197" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B198" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="C198" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B199" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="C199" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B200" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="C200" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B201" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="C201" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B202" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="C202" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B203" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="C203" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B204" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="C204" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B205" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="C205" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B206" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="C206" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B207" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="C207" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B208" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="C208" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B209" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="C209" t="s">
         <v>113</v>
@@ -5039,10 +4976,10 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B210" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="C210" t="s">
         <v>113</v>
@@ -5050,10 +4987,10 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B211" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="C211" t="s">
         <v>113</v>
@@ -5061,10 +4998,10 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B212" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="C212" t="s">
         <v>113</v>
@@ -5072,10 +5009,10 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B213" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="C213" t="s">
         <v>113</v>
@@ -5083,406 +5020,406 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B214" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="C214" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B215" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="C215" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B216" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="C216" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B217" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="C217" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B218" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="C218" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B219" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="C219" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B220" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="C220" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B221" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="C221" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B222" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="C222" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B223" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="C223" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B224" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="C224" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B225" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="C225" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B226" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="C226" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B227" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="C227" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B228" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="C228" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B229" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="C229" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>319</v>
+        <v>20</v>
       </c>
       <c r="B230" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="C230" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>320</v>
+        <v>21</v>
       </c>
       <c r="B231" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="C231" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>321</v>
+        <v>60</v>
       </c>
       <c r="B232" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="C232" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>321</v>
+        <v>78</v>
       </c>
       <c r="B233" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="C233" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>322</v>
+        <v>79</v>
       </c>
       <c r="B234" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="C234" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B235" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="C235" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B236" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="C236" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B237" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="C237" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B238" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="C238" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>325</v>
+        <v>6</v>
       </c>
       <c r="B239" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="C239" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>326</v>
+        <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="C240" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B241" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="C241" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B242" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="C242" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="B243" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="C243" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="B244" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="C244" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="B245" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="C245" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>327</v>
+        <v>64</v>
       </c>
       <c r="B246" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="C246" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>328</v>
+        <v>76</v>
       </c>
       <c r="B247" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="C247" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="B248" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="C248" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B249" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="C249" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>6</v>
+        <v>322</v>
       </c>
       <c r="B250" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="C250" t="s">
         <v>117</v>
@@ -5490,395 +5427,395 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B251" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="C251" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="B252" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="C252" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="B253" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="C253" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="B254" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="C254" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>43</v>
+        <v>323</v>
       </c>
       <c r="B255" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="C255" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>64</v>
+        <v>324</v>
       </c>
       <c r="B256" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="C256" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="B257" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="C257" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="B258" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="C258" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B259" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="C259" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B260" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="C260" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>332</v>
+        <v>13</v>
       </c>
       <c r="B261" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="C261" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="B262" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="C262" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="B263" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="C263" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="B264" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="C264" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B265" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="C265" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B266" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="C266" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B267" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="C267" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B268" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="C268" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="B269" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="C269" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>335</v>
+        <v>54</v>
       </c>
       <c r="B270" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
       <c r="C270" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>335</v>
+        <v>25</v>
       </c>
       <c r="B271" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="C271" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>13</v>
+        <v>328</v>
       </c>
       <c r="B272" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="C272" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>35</v>
+        <v>328</v>
       </c>
       <c r="B273" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="C273" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B274" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="C274" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="B275" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="C275" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="B276" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="C276" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B277" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="C277" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>337</v>
+        <v>46</v>
       </c>
       <c r="B278" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C278" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="B279" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="C279" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>54</v>
+        <v>330</v>
       </c>
       <c r="B280" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="C280" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>54</v>
+        <v>331</v>
       </c>
       <c r="B281" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="C281" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>25</v>
+        <v>332</v>
       </c>
       <c r="B282" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="C282" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B283" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="C283" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B284" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="C284" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>75</v>
+        <v>332</v>
       </c>
       <c r="B285" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="C285" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>32</v>
+        <v>333</v>
       </c>
       <c r="B286" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="C286" t="s">
         <v>124</v>
@@ -5886,131 +5823,131 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B287" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="C287" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>339</v>
+        <v>41</v>
       </c>
       <c r="B288" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="C288" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B289" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="C289" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="B290" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="C290" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>340</v>
+        <v>45</v>
       </c>
       <c r="B291" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="C291" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>341</v>
+        <v>55</v>
       </c>
       <c r="B292" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="C292" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>342</v>
+        <v>61</v>
       </c>
       <c r="B293" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="C293" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>342</v>
+        <v>70</v>
       </c>
       <c r="B294" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="C294" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>342</v>
+        <v>74</v>
       </c>
       <c r="B295" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="C295" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>342</v>
+        <v>77</v>
       </c>
       <c r="B296" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="C296" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="B297" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="C297" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>24</v>
+        <v>334</v>
       </c>
       <c r="B298" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="C298" t="s">
         <v>125</v>
@@ -6018,10 +5955,10 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>41</v>
+        <v>334</v>
       </c>
       <c r="B299" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="C299" t="s">
         <v>125</v>
@@ -6029,10 +5966,10 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>41</v>
+        <v>334</v>
       </c>
       <c r="B300" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="C300" t="s">
         <v>125</v>
@@ -6040,10 +5977,10 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>41</v>
+        <v>335</v>
       </c>
       <c r="B301" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="C301" t="s">
         <v>125</v>
@@ -6051,131 +5988,131 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B302" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="C302" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="B303" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="C303" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="B304" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="C304" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="B305" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="C305" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>74</v>
+        <v>336</v>
       </c>
       <c r="B306" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="C306" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="B307" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="C307" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B308" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C308" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B309" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="C309" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B310" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="C310" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B311" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="C311" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B312" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="C312" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>23</v>
+        <v>339</v>
       </c>
       <c r="B313" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="C313" t="s">
         <v>126</v>
@@ -6183,131 +6120,131 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B314" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="C314" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B315" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="C315" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B316" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="C316" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>346</v>
+        <v>37</v>
       </c>
       <c r="B317" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="C317" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B318" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="C318" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>347</v>
+        <v>3</v>
       </c>
       <c r="B319" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="C319" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="B320" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="C320" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>348</v>
+        <v>86</v>
       </c>
       <c r="B321" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="C321" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B322" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="C322" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="B323" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="C323" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B324" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="C324" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>8</v>
+        <v>343</v>
       </c>
       <c r="B325" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="C325" t="s">
         <v>127</v>
@@ -6315,10 +6252,10 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>18</v>
+        <v>344</v>
       </c>
       <c r="B326" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="C326" t="s">
         <v>127</v>
@@ -6326,131 +6263,131 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B327" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="C327" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B328" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="C328" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B329" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="C329" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>3</v>
+        <v>345</v>
       </c>
       <c r="B330" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="C330" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="B331" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="C331" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B332" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="C332" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>350</v>
+        <v>59</v>
       </c>
       <c r="B333" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="C333" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>351</v>
+        <v>67</v>
       </c>
       <c r="B334" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="C334" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>352</v>
+        <v>85</v>
       </c>
       <c r="B335" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="C335" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>353</v>
+        <v>85</v>
       </c>
       <c r="B336" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="C336" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="B337" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="C337" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>10</v>
+        <v>347</v>
       </c>
       <c r="B338" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="C338" t="s">
         <v>128</v>
@@ -6458,716 +6395,595 @@
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B339" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="C339" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B340" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="C340" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>355</v>
+        <v>52</v>
       </c>
       <c r="B341" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="C341" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B342" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="C342" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B343" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="C343" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B344" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="C344" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B345" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="C345" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="B346" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="C346" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="B347" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="C347" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B348" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="C348" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B349" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="C349" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="B350" t="s">
-        <v>715</v>
+        <v>705</v>
       </c>
       <c r="C350" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="B351" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="C351" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B352" t="s">
-        <v>717</v>
+        <v>707</v>
       </c>
       <c r="C352" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B353" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
       <c r="C353" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B354" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="C354" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>63</v>
+        <v>350</v>
       </c>
       <c r="B355" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="C355" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="B356" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="C356" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="B357" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
       <c r="C357" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B358" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
       <c r="C358" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B359" t="s">
-        <v>724</v>
+        <v>714</v>
       </c>
       <c r="C359" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>359</v>
+        <v>42</v>
       </c>
       <c r="B360" t="s">
-        <v>725</v>
+        <v>715</v>
       </c>
       <c r="C360" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B361" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
       <c r="C361" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B362" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
       <c r="C362" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B363" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="C363" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B364" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
       <c r="C364" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B365" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="C365" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>360</v>
+        <v>11</v>
       </c>
       <c r="B366" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="C366" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B367" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="C367" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="B368" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="C368" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="B369" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="C369" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>361</v>
+        <v>73</v>
       </c>
       <c r="B370" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="C370" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="B371" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="C371" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>42</v>
+        <v>352</v>
       </c>
       <c r="B372" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="C372" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="B373" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="C373" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="B374" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="C374" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="B375" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="C375" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>66</v>
+        <v>353</v>
       </c>
       <c r="B376" t="s">
-        <v>741</v>
+        <v>731</v>
       </c>
       <c r="C376" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>11</v>
+        <v>354</v>
       </c>
       <c r="B377" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="C377" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>11</v>
+        <v>355</v>
       </c>
       <c r="B378" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
       <c r="C378" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="B379" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="C379" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="B380" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="C380" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="B381" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
       <c r="C381" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="B382" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
       <c r="C382" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>362</v>
+        <v>36</v>
       </c>
       <c r="B383" t="s">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="C383" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="B384" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="C384" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>17</v>
+        <v>356</v>
       </c>
       <c r="B385" t="s">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="C385" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B386" t="s">
-        <v>751</v>
+        <v>741</v>
       </c>
       <c r="C386" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>363</v>
+        <v>5</v>
       </c>
       <c r="B387" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="C387" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>364</v>
+        <v>38</v>
       </c>
       <c r="B388" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
       <c r="C388" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>365</v>
+        <v>38</v>
       </c>
       <c r="B389" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="C389" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="B390" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="C390" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="B391" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="C391" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="B392" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="C392" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A393" t="s">
-        <v>36</v>
-      </c>
-      <c r="B393" t="s">
-        <v>758</v>
-      </c>
-      <c r="C393" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A394" t="s">
-        <v>36</v>
-      </c>
-      <c r="B394" t="s">
-        <v>759</v>
-      </c>
-      <c r="C394" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A395" t="s">
-        <v>72</v>
-      </c>
-      <c r="B395" t="s">
-        <v>760</v>
-      </c>
-      <c r="C395" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A396" t="s">
-        <v>366</v>
-      </c>
-      <c r="B396" t="s">
-        <v>761</v>
-      </c>
-      <c r="C396" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A397" t="s">
-        <v>5</v>
-      </c>
-      <c r="B397" t="s">
-        <v>762</v>
-      </c>
-      <c r="C397" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A398" t="s">
-        <v>5</v>
-      </c>
-      <c r="B398" t="s">
-        <v>763</v>
-      </c>
-      <c r="C398" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A399" t="s">
-        <v>38</v>
-      </c>
-      <c r="B399" t="s">
-        <v>764</v>
-      </c>
-      <c r="C399" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A400" t="s">
-        <v>38</v>
-      </c>
-      <c r="B400" t="s">
-        <v>765</v>
-      </c>
-      <c r="C400" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A401" t="s">
-        <v>56</v>
-      </c>
-      <c r="B401" t="s">
-        <v>766</v>
-      </c>
-      <c r="C401" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A402" t="s">
-        <v>57</v>
-      </c>
-      <c r="B402" t="s">
-        <v>767</v>
-      </c>
-      <c r="C402" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A403" t="s">
-        <v>65</v>
-      </c>
-      <c r="B403" t="s">
-        <v>768</v>
-      </c>
-      <c r="C403" t="s">
         <v>136</v>
       </c>
     </row>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1985866C-BDB9-4B41-AE83-8973DA912035}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7B5A1D-C94B-4ADB-9DE7-E7BE68031992}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="973">
   <si>
     <t>UTK</t>
   </si>
@@ -69,9 +69,6 @@
     <t>260523-W00002242</t>
   </si>
   <si>
-    <t>260524-W00002437</t>
-  </si>
-  <si>
     <t>260524-W00007064</t>
   </si>
   <si>
@@ -144,9 +141,6 @@
     <t>260530-W00005155</t>
   </si>
   <si>
-    <t>260530-W00005427</t>
-  </si>
-  <si>
     <t>260530-W00007679</t>
   </si>
   <si>
@@ -384,7 +378,2575 @@
     <t>99002606</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>K-902</t>
+  </si>
+  <si>
+    <t>K-983</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>K-962</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>K-906</t>
+  </si>
+  <si>
+    <t>K-972</t>
+  </si>
+  <si>
+    <t>K-961</t>
+  </si>
+  <si>
+    <t>K-941</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>K-920</t>
+  </si>
+  <si>
+    <t>K-930</t>
+  </si>
+  <si>
+    <t>K-9111</t>
+  </si>
+  <si>
+    <t>SZ-860</t>
+  </si>
+  <si>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>K-942</t>
+  </si>
+  <si>
+    <t>K-973</t>
+  </si>
+  <si>
+    <t>K-943</t>
+  </si>
+  <si>
+    <t>K-951</t>
+  </si>
+  <si>
+    <t>K-921</t>
+  </si>
+  <si>
+    <t>K-981</t>
+  </si>
+  <si>
+    <t>K-9110</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>K-931</t>
+  </si>
+  <si>
+    <t>K-982</t>
+  </si>
+  <si>
+    <t>K-917</t>
+  </si>
+  <si>
+    <t>SZ-870</t>
+  </si>
+  <si>
+    <t>SZ-854</t>
+  </si>
+  <si>
+    <t>K-908</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>K-998</t>
+  </si>
+  <si>
+    <t>K-952</t>
+  </si>
+  <si>
+    <t>K-999</t>
+  </si>
+  <si>
+    <t>SZ-827</t>
+  </si>
+  <si>
+    <t>K-903</t>
+  </si>
+  <si>
+    <t>K-932</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>K-910</t>
+  </si>
+  <si>
+    <t>K-971</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>K-953</t>
+  </si>
+  <si>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>K-912</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>K-915</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>SZ-850</t>
+  </si>
+  <si>
+    <t>SZ-807</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-8101</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>1-4560/2026</t>
+  </si>
+  <si>
+    <t>2026/07166</t>
+  </si>
+  <si>
+    <t>260421-F00013570</t>
+  </si>
+  <si>
+    <t>260504-F00000386</t>
+  </si>
+  <si>
+    <t>260513-F00011256</t>
+  </si>
+  <si>
+    <t>260513-W00004404</t>
+  </si>
+  <si>
+    <t>260515-F00001625</t>
+  </si>
+  <si>
+    <t>260516-F00004835</t>
+  </si>
+  <si>
+    <t>260518-F00007298</t>
+  </si>
+  <si>
+    <t>260518-F00010289</t>
+  </si>
+  <si>
+    <t>260518-W00002668</t>
+  </si>
+  <si>
+    <t>260519-F00007168</t>
+  </si>
+  <si>
+    <t>260519-F00008935</t>
+  </si>
+  <si>
+    <t>260520-F00010660</t>
+  </si>
+  <si>
+    <t>260520-F00014864</t>
+  </si>
+  <si>
+    <t>260521-F00012066</t>
+  </si>
+  <si>
+    <t>260521-F00012401</t>
+  </si>
+  <si>
+    <t>260522-F00003220</t>
+  </si>
+  <si>
+    <t>260522-F00005728</t>
+  </si>
+  <si>
+    <t>260522-F00006849</t>
+  </si>
+  <si>
+    <t>260522-F00012984</t>
+  </si>
+  <si>
+    <t>260522-W00003720</t>
+  </si>
+  <si>
+    <t>260522-W00005207</t>
+  </si>
+  <si>
+    <t>260522-W00006237</t>
+  </si>
+  <si>
+    <t>260523-W00000912</t>
+  </si>
+  <si>
+    <t>260525-W00007575</t>
+  </si>
+  <si>
+    <t>260526-F00002402</t>
+  </si>
+  <si>
+    <t>260526-F00004857</t>
+  </si>
+  <si>
+    <t>260526-F00004895</t>
+  </si>
+  <si>
+    <t>260526-F00007192</t>
+  </si>
+  <si>
+    <t>260526-F00008651</t>
+  </si>
+  <si>
+    <t>260526-F00015516</t>
+  </si>
+  <si>
+    <t>260526-W00003425</t>
+  </si>
+  <si>
+    <t>260526-W00007598</t>
+  </si>
+  <si>
+    <t>260526-W00008595</t>
+  </si>
+  <si>
+    <t>260527-F00007066</t>
+  </si>
+  <si>
+    <t>260527-F00009115</t>
+  </si>
+  <si>
+    <t>260527-F00011026</t>
+  </si>
+  <si>
+    <t>260527-F00012734</t>
+  </si>
+  <si>
+    <t>260527-W00002728</t>
+  </si>
+  <si>
+    <t>260527-W00006037</t>
+  </si>
+  <si>
+    <t>260528-F00006727</t>
+  </si>
+  <si>
+    <t>260528-F00009337</t>
+  </si>
+  <si>
+    <t>260528-F00009589</t>
+  </si>
+  <si>
+    <t>260528-F00012211</t>
+  </si>
+  <si>
+    <t>260528-F00012984</t>
+  </si>
+  <si>
+    <t>260528-F00014792</t>
+  </si>
+  <si>
+    <t>260528-F00015183</t>
+  </si>
+  <si>
+    <t>260528-W00001109</t>
+  </si>
+  <si>
+    <t>260528-W00002550</t>
+  </si>
+  <si>
+    <t>260528-W00002622</t>
+  </si>
+  <si>
+    <t>260528-W00006180</t>
+  </si>
+  <si>
+    <t>260528-W00009343</t>
+  </si>
+  <si>
+    <t>260529-F00006945</t>
+  </si>
+  <si>
+    <t>260529-F00007230-5</t>
+  </si>
+  <si>
+    <t>260529-F00008147</t>
+  </si>
+  <si>
+    <t>260529-F00008779</t>
+  </si>
+  <si>
+    <t>260529-F00008803</t>
+  </si>
+  <si>
+    <t>260529-F00009328</t>
+  </si>
+  <si>
+    <t>260529-F00010393</t>
+  </si>
+  <si>
+    <t>260529-F00010595</t>
+  </si>
+  <si>
+    <t>260529-F00011295</t>
+  </si>
+  <si>
+    <t>260529-F00011569</t>
+  </si>
+  <si>
+    <t>260529-F00012182</t>
+  </si>
+  <si>
+    <t>260529-F00012312</t>
+  </si>
+  <si>
+    <t>260529-F00012569</t>
+  </si>
+  <si>
+    <t>260529-F00012679</t>
+  </si>
+  <si>
+    <t>260529-F00012988</t>
+  </si>
+  <si>
+    <t>260529-F00013968</t>
+  </si>
+  <si>
+    <t>260529-W00002738</t>
+  </si>
+  <si>
+    <t>260529-W00004096</t>
+  </si>
+  <si>
+    <t>260529-W00004966</t>
+  </si>
+  <si>
+    <t>260529-W00005540</t>
+  </si>
+  <si>
+    <t>260529-W00005744</t>
+  </si>
+  <si>
+    <t>260529-W00006000</t>
+  </si>
+  <si>
+    <t>260529-W00006770</t>
+  </si>
+  <si>
+    <t>260529-W00009387</t>
+  </si>
+  <si>
+    <t>260530-F00001408</t>
+  </si>
+  <si>
+    <t>260530-F00001743</t>
+  </si>
+  <si>
+    <t>260530-F00002405</t>
+  </si>
+  <si>
+    <t>260530-F00002407</t>
+  </si>
+  <si>
+    <t>260530-F00002676</t>
+  </si>
+  <si>
+    <t>260530-F00003279</t>
+  </si>
+  <si>
+    <t>260530-F00003621</t>
+  </si>
+  <si>
+    <t>260530-F00003969</t>
+  </si>
+  <si>
+    <t>260530-F00004031</t>
+  </si>
+  <si>
+    <t>260530-F00004503</t>
+  </si>
+  <si>
+    <t>260530-F00004588</t>
+  </si>
+  <si>
+    <t>260530-F00004590</t>
+  </si>
+  <si>
+    <t>260530-F00005295</t>
+  </si>
+  <si>
+    <t>260530-F00005452</t>
+  </si>
+  <si>
+    <t>260530-W00001425</t>
+  </si>
+  <si>
+    <t>260530-W00001502</t>
+  </si>
+  <si>
+    <t>260530-W00001537</t>
+  </si>
+  <si>
+    <t>260530-W00001704</t>
+  </si>
+  <si>
+    <t>260530-W00002411</t>
+  </si>
+  <si>
+    <t>260530-W00002570</t>
+  </si>
+  <si>
+    <t>260530-W00002594</t>
+  </si>
+  <si>
+    <t>260530-W00003832</t>
+  </si>
+  <si>
+    <t>260530-W00004675</t>
+  </si>
+  <si>
+    <t>260530-W00005666</t>
+  </si>
+  <si>
+    <t>260530-W00005898</t>
+  </si>
+  <si>
+    <t>260530-W00006389</t>
+  </si>
+  <si>
+    <t>260530-W00006472</t>
+  </si>
+  <si>
+    <t>260530-W00006507</t>
+  </si>
+  <si>
+    <t>260530-W00007699</t>
+  </si>
+  <si>
+    <t>260531-F00000284</t>
+  </si>
+  <si>
+    <t>260531-F00001235</t>
+  </si>
+  <si>
+    <t>260531-F00002620</t>
+  </si>
+  <si>
+    <t>260531-F00003842</t>
+  </si>
+  <si>
+    <t>260531-F00003954</t>
+  </si>
+  <si>
+    <t>260531-W00000742</t>
+  </si>
+  <si>
+    <t>260531-W00001425</t>
+  </si>
+  <si>
+    <t>260531-W00001427</t>
+  </si>
+  <si>
+    <t>260531-W00002401</t>
+  </si>
+  <si>
+    <t>260531-W00002499</t>
+  </si>
+  <si>
+    <t>260531-W00002786</t>
+  </si>
+  <si>
+    <t>260531-W00002852</t>
+  </si>
+  <si>
+    <t>260531-W00003669</t>
+  </si>
+  <si>
+    <t>260531-W00003819</t>
+  </si>
+  <si>
+    <t>260531-W00003829</t>
+  </si>
+  <si>
+    <t>260531-W00004068</t>
+  </si>
+  <si>
+    <t>260531-W00004632</t>
+  </si>
+  <si>
+    <t>260531-W00004793</t>
+  </si>
+  <si>
+    <t>260531-W00005994</t>
+  </si>
+  <si>
+    <t>260531-W00006395</t>
+  </si>
+  <si>
+    <t>260531-W00008216</t>
+  </si>
+  <si>
+    <t>260531-W00008231</t>
+  </si>
+  <si>
+    <t>260601-F00000855</t>
+  </si>
+  <si>
+    <t>260601-F00001967</t>
+  </si>
+  <si>
+    <t>260601-F00002179</t>
+  </si>
+  <si>
+    <t>260601-F00002207</t>
+  </si>
+  <si>
+    <t>260601-F00002538</t>
+  </si>
+  <si>
+    <t>260601-F00002751</t>
+  </si>
+  <si>
+    <t>260601-F00002955</t>
+  </si>
+  <si>
+    <t>260601-F00003910</t>
+  </si>
+  <si>
+    <t>260601-F00004216-2</t>
+  </si>
+  <si>
+    <t>260601-F00004500</t>
+  </si>
+  <si>
+    <t>260601-F00004553</t>
+  </si>
+  <si>
+    <t>260601-F00006227-2</t>
+  </si>
+  <si>
+    <t>260601-F00007264</t>
+  </si>
+  <si>
+    <t>260601-F00008882</t>
+  </si>
+  <si>
+    <t>260601-F00010255</t>
+  </si>
+  <si>
+    <t>260601-F00011031</t>
+  </si>
+  <si>
+    <t>260601-F00011044</t>
+  </si>
+  <si>
+    <t>260601-F00011098</t>
+  </si>
+  <si>
+    <t>260601-F00011681</t>
+  </si>
+  <si>
+    <t>260601-F00013674-1</t>
+  </si>
+  <si>
+    <t>260601-F00015791</t>
+  </si>
+  <si>
+    <t>260601-W00001607</t>
+  </si>
+  <si>
+    <t>260601-W00001759</t>
+  </si>
+  <si>
+    <t>260601-W00002371</t>
+  </si>
+  <si>
+    <t>260601-W00002423</t>
+  </si>
+  <si>
+    <t>260601-W00003005</t>
+  </si>
+  <si>
+    <t>260601-W00003557</t>
+  </si>
+  <si>
+    <t>260601-W00003811</t>
+  </si>
+  <si>
+    <t>260601-W00005848</t>
+  </si>
+  <si>
+    <t>260601-W00006309</t>
+  </si>
+  <si>
+    <t>260601-W00007364</t>
+  </si>
+  <si>
+    <t>260601-W00008664</t>
+  </si>
+  <si>
+    <t>260601-W00008714</t>
+  </si>
+  <si>
+    <t>260601-W00008781</t>
+  </si>
+  <si>
+    <t>260601-W00009184</t>
+  </si>
+  <si>
+    <t>260601-W00011309</t>
+  </si>
+  <si>
+    <t>260601-W00012220</t>
+  </si>
+  <si>
+    <t>260601-W00013323</t>
+  </si>
+  <si>
+    <t>260602-F00003188</t>
+  </si>
+  <si>
+    <t>260602-F00006891</t>
+  </si>
+  <si>
+    <t>260602-F00006926</t>
+  </si>
+  <si>
+    <t>260602-F00007092</t>
+  </si>
+  <si>
+    <t>260602-F00007907</t>
+  </si>
+  <si>
+    <t>260602-W00001472</t>
+  </si>
+  <si>
+    <t>260602-W00002187</t>
+  </si>
+  <si>
+    <t>260602-W00004100</t>
+  </si>
+  <si>
+    <t>260602-W00004275</t>
+  </si>
+  <si>
+    <t>260602-W00004312</t>
+  </si>
+  <si>
+    <t>260602-W00004624</t>
+  </si>
+  <si>
+    <t>267007227</t>
+  </si>
+  <si>
+    <t>267007802</t>
+  </si>
+  <si>
+    <t>267008060</t>
+  </si>
+  <si>
+    <t>267008061</t>
+  </si>
+  <si>
+    <t>267008067</t>
+  </si>
+  <si>
+    <t>267008073</t>
+  </si>
+  <si>
+    <t>267008087</t>
+  </si>
+  <si>
+    <t>267008100</t>
+  </si>
+  <si>
+    <t>267008103</t>
+  </si>
+  <si>
+    <t>267008104</t>
+  </si>
+  <si>
+    <t>267008105</t>
+  </si>
+  <si>
+    <t>267008108</t>
+  </si>
+  <si>
+    <t>267008123</t>
+  </si>
+  <si>
+    <t>267008139</t>
+  </si>
+  <si>
+    <t>267008159</t>
+  </si>
+  <si>
+    <t>267008188</t>
+  </si>
+  <si>
+    <t>267008189</t>
+  </si>
+  <si>
+    <t>267008190</t>
+  </si>
+  <si>
+    <t>26MPE0005810</t>
+  </si>
+  <si>
+    <t>26MPE0005820</t>
+  </si>
+  <si>
+    <t>26MPE0005823</t>
+  </si>
+  <si>
+    <t>26MPE0005876</t>
+  </si>
+  <si>
+    <t>26MPE0005882</t>
+  </si>
+  <si>
+    <t>26MPE0005921</t>
+  </si>
+  <si>
+    <t>26MPE0005923</t>
+  </si>
+  <si>
+    <t>313333158</t>
+  </si>
+  <si>
+    <t>313333652</t>
+  </si>
+  <si>
+    <t>313435172</t>
+  </si>
+  <si>
+    <t>313490459</t>
+  </si>
+  <si>
+    <t>313491104</t>
+  </si>
+  <si>
+    <t>313491294</t>
+  </si>
+  <si>
+    <t>313556175</t>
+  </si>
+  <si>
+    <t>313557017</t>
+  </si>
+  <si>
+    <t>313631230</t>
+  </si>
+  <si>
+    <t>313631358</t>
+  </si>
+  <si>
+    <t>313631613</t>
+  </si>
+  <si>
+    <t>313631672</t>
+  </si>
+  <si>
+    <t>313704829</t>
+  </si>
+  <si>
+    <t>313705047</t>
+  </si>
+  <si>
+    <t>313705141</t>
+  </si>
+  <si>
+    <t>313705217</t>
+  </si>
+  <si>
+    <t>313705261</t>
+  </si>
+  <si>
+    <t>313705362</t>
+  </si>
+  <si>
+    <t>313756402</t>
+  </si>
+  <si>
+    <t>313756840</t>
+  </si>
+  <si>
+    <t>313824705</t>
+  </si>
+  <si>
+    <t>313824817</t>
+  </si>
+  <si>
+    <t>313825151</t>
+  </si>
+  <si>
+    <t>313878306</t>
+  </si>
+  <si>
+    <t>313878336</t>
+  </si>
+  <si>
+    <t>313878351</t>
+  </si>
+  <si>
+    <t>313878413</t>
+  </si>
+  <si>
+    <t>313991315</t>
+  </si>
+  <si>
+    <t>421609 ,421626</t>
+  </si>
+  <si>
+    <t>NFD6-05-22-D83S</t>
+  </si>
+  <si>
+    <t>NFD6-05-27-7QN7</t>
+  </si>
+  <si>
+    <t>NFD6-05-27-WF8Z</t>
+  </si>
+  <si>
+    <t>NFD6-05-29-2QR7</t>
+  </si>
+  <si>
+    <t>NFD6-05-29-LVUL</t>
+  </si>
+  <si>
+    <t>NFD6-05-29-Q7N8</t>
+  </si>
+  <si>
+    <t>NFD6-05-29-REHP</t>
+  </si>
+  <si>
+    <t>NFD6-05-29-TS6C</t>
+  </si>
+  <si>
+    <t>NFD6-05-29-UWYY</t>
+  </si>
+  <si>
+    <t>NFD6-05-30-6HRG</t>
+  </si>
+  <si>
+    <t>NFD6-05-30-9TXT</t>
+  </si>
+  <si>
+    <t>NFD6-05-30-E58U</t>
+  </si>
+  <si>
+    <t>NFD6-05-30-VPUP</t>
+  </si>
+  <si>
+    <t>NFD6-05-30-WTFU</t>
+  </si>
+  <si>
+    <t>NFD6-05-31-5X4X</t>
+  </si>
+  <si>
+    <t>NFD6-05-31-9XXK</t>
+  </si>
+  <si>
+    <t>NFD6-06-01-45C7</t>
+  </si>
+  <si>
+    <t>NFD6-06-01-BDHV</t>
+  </si>
+  <si>
+    <t>NFD6-06-01-E8JN</t>
+  </si>
+  <si>
+    <t>NFD6-06-01-ECGP</t>
+  </si>
+  <si>
+    <t>NFD6-06-01-EVEN</t>
+  </si>
+  <si>
+    <t>NFD6-06-01-J3TJ</t>
+  </si>
+  <si>
+    <t>NFD6-06-01-JRJQ</t>
+  </si>
+  <si>
+    <t>NFD6-06-01-LMY5</t>
+  </si>
+  <si>
+    <t>NFD6-06-01-RCXQ</t>
+  </si>
+  <si>
+    <t>NFD6-06-01-T3HR</t>
+  </si>
+  <si>
+    <t>NFD6-06-01-UW8S</t>
+  </si>
+  <si>
+    <t>NFD6-06-01-VJ3C</t>
+  </si>
+  <si>
+    <t>NFD6-06-01-XFGC</t>
+  </si>
+  <si>
+    <t>NFD6-06-02-3MWN</t>
+  </si>
+  <si>
+    <t>NFD6-06-02-F6YE</t>
+  </si>
+  <si>
+    <t>NFD6-06-02-N92M</t>
+  </si>
+  <si>
+    <t>NFD6-06-02-TU3F</t>
+  </si>
+  <si>
+    <t>NFE6-05-28-JLD2</t>
+  </si>
+  <si>
+    <t>NFE6-05-28-PAXV</t>
+  </si>
+  <si>
+    <t>NFE6-05-29-25R3</t>
+  </si>
+  <si>
+    <t>NFE6-05-29-7FDB</t>
+  </si>
+  <si>
+    <t>NFE6-05-29-8DFK</t>
+  </si>
+  <si>
+    <t>NFE6-05-29-N2WD</t>
+  </si>
+  <si>
+    <t>NFE6-05-30-3K8K</t>
+  </si>
+  <si>
+    <t>NFE6-05-30-5FVT</t>
+  </si>
+  <si>
+    <t>NFE6-05-30-DK2G</t>
+  </si>
+  <si>
+    <t>NFE6-05-30-L94C</t>
+  </si>
+  <si>
+    <t>NFE6-05-30-RLJ5</t>
+  </si>
+  <si>
+    <t>NFE6-05-30-SV6F</t>
+  </si>
+  <si>
+    <t>NFE6-05-31-3FES</t>
+  </si>
+  <si>
+    <t>NFE6-05-31-8727</t>
+  </si>
+  <si>
+    <t>NFE6-05-31-9E6Z</t>
+  </si>
+  <si>
+    <t>NFE6-05-31-AGUA</t>
+  </si>
+  <si>
+    <t>NFE6-05-31-LABX</t>
+  </si>
+  <si>
+    <t>NFE6-05-31-PT59</t>
+  </si>
+  <si>
+    <t>NFE6-05-31-QPXJ</t>
+  </si>
+  <si>
+    <t>NFE6-05-31-V9UT</t>
+  </si>
+  <si>
+    <t>NFE6-05-31-XNRW</t>
+  </si>
+  <si>
+    <t>NFE6-06-01-65LW</t>
+  </si>
+  <si>
+    <t>NFE6-06-01-7BLT</t>
+  </si>
+  <si>
+    <t>NFE6-06-01-89VD</t>
+  </si>
+  <si>
+    <t>NFE6-06-01-A9AU</t>
+  </si>
+  <si>
+    <t>NFE6-06-01-B5NW</t>
+  </si>
+  <si>
+    <t>NFE6-06-01-NYPC</t>
+  </si>
+  <si>
+    <t>NFE6-06-01-QRBD</t>
+  </si>
+  <si>
+    <t>NFE6-06-01-TDDY</t>
+  </si>
+  <si>
+    <t>NFE6-06-01-VJ36</t>
+  </si>
+  <si>
+    <t>NFE6-06-02-AYDJ</t>
+  </si>
+  <si>
+    <t>NFE6-06-02-JBUW</t>
+  </si>
+  <si>
+    <t>NFE6-06-02-UULQ</t>
+  </si>
+  <si>
+    <t>R422439</t>
+  </si>
+  <si>
+    <t>R422467</t>
+  </si>
+  <si>
+    <t>SA26/H003254</t>
+  </si>
+  <si>
+    <t>SA26/H003335</t>
+  </si>
+  <si>
+    <t>K/424-K/423</t>
+  </si>
+  <si>
+    <t>NFD6-05-29-HJSW</t>
+  </si>
+  <si>
+    <t>NFD6-05-31-DSQS</t>
+  </si>
+  <si>
+    <t>NFD6-05-23-4ZZ7/XD</t>
+  </si>
+  <si>
+    <t>NFD6-06-01-K77S</t>
+  </si>
+  <si>
+    <t>159995579540801803</t>
+  </si>
+  <si>
+    <t>12345678/1</t>
+  </si>
+  <si>
+    <t>12345678/2</t>
+  </si>
+  <si>
+    <t>6a1d3e0b8046ce4dbfbaf5d9</t>
+  </si>
+  <si>
+    <t>6a19ad328046ce4dbfbad879</t>
+  </si>
+  <si>
+    <t>6a1d09eb8046ce4dbfbaf1fe</t>
+  </si>
+  <si>
+    <t>6a16dc628046ce4dbfbaa260</t>
+  </si>
+  <si>
+    <t>6a1ea0058046ce4dbfbb13c4</t>
+  </si>
+  <si>
+    <t>6a1063918046ce4dbfba5ab0</t>
+  </si>
+  <si>
+    <t>6a06d7468046ce4dbfb9ac52</t>
+  </si>
+  <si>
+    <t>6a1eac2f8046ce4dbfbb162d</t>
+  </si>
+  <si>
+    <t>6a16bd2d8046ce4dbfba9dd7</t>
+  </si>
+  <si>
+    <t>6a0aec9c8046ce4dbfb9ea39</t>
+  </si>
+  <si>
+    <t>6a19a9518046ce4dbfbad81f</t>
+  </si>
+  <si>
+    <t>6a1e87608046ce4dbfbb0efd</t>
+  </si>
+  <si>
+    <t>6a0d65188046ce4dbfba1a82</t>
+  </si>
+  <si>
+    <t>6a0c4e898046ce4dbfba0a12</t>
+  </si>
+  <si>
+    <t>6a16a67d8046ce4dbfba98aa</t>
+  </si>
+  <si>
+    <t>6a1999758046ce4dbfbad60c</t>
+  </si>
+  <si>
+    <t>6a197a818046ce4dbfbad195</t>
+  </si>
+  <si>
+    <t>6a197a818046ce4dbfbad196</t>
+  </si>
+  <si>
+    <t>6a197ea68046ce4dbfbad228</t>
+  </si>
+  <si>
+    <t>6a0ecf858046ce4dbfba39cd</t>
+  </si>
+  <si>
+    <t>6a0ecf858046ce4dbfba39cf</t>
+  </si>
+  <si>
+    <t>6a0eef298046ce4dbfba3ee4</t>
+  </si>
+  <si>
+    <t>6a1800e48046ce4dbfbab353</t>
+  </si>
+  <si>
+    <t>6a196d7a8046ce4dbfbacfea</t>
+  </si>
+  <si>
+    <t>6a1d869c8046ce4dbfbb027f</t>
+  </si>
+  <si>
+    <t>6a102de08046ce4dbfba5382</t>
+  </si>
+  <si>
+    <t>6a1b00fb8046ce4dbfbae651</t>
+  </si>
+  <si>
+    <t>6a1d353f8046ce4dbfbaf412</t>
+  </si>
+  <si>
+    <t>6a16e6998046ce4dbfbaa3dd</t>
+  </si>
+  <si>
+    <t>6a1048e08046ce4dbfba571a</t>
+  </si>
+  <si>
+    <t>6a1a964d8046ce4dbfbaddc8</t>
+  </si>
+  <si>
+    <t>6a113b758046ce4dbfba604b</t>
+  </si>
+  <si>
+    <t>6a1162138046ce4dbfba625c</t>
+  </si>
+  <si>
+    <t>6a13486e8046ce4dbfba6fe6</t>
+  </si>
+  <si>
+    <t>6a1492e88046ce4dbfba7605</t>
+  </si>
+  <si>
+    <t>6a1492e88046ce4dbfba7606</t>
+  </si>
+  <si>
+    <t>6a1d94408046ce4dbfbb04da</t>
+  </si>
+  <si>
+    <t>6a1d78908046ce4dbfbaffe1</t>
+  </si>
+  <si>
+    <t>6a1d6b4f8046ce4dbfbafde2</t>
+  </si>
+  <si>
+    <t>6a1e92298046ce4dbfbb10d9</t>
+  </si>
+  <si>
+    <t>6a1588fe8046ce4dbfba8635</t>
+  </si>
+  <si>
+    <t>6a1588fe8046ce4dbfba8638</t>
+  </si>
+  <si>
+    <t>6a1d9c8a8046ce4dbfbb0674</t>
+  </si>
+  <si>
+    <t>6a1ab80d8046ce4dbfbae1f8</t>
+  </si>
+  <si>
+    <t>6a15d4068046ce4dbfba91a4</t>
+  </si>
+  <si>
+    <t>6a19881b8046ce4dbfbad3cf</t>
+  </si>
+  <si>
+    <t>6a15c97a8046ce4dbfba908c</t>
+  </si>
+  <si>
+    <t>6a15f39d8046ce4dbfba9349</t>
+  </si>
+  <si>
+    <t>6a1e83e28046ce4dbfbb0e64</t>
+  </si>
+  <si>
+    <t>6a1d7bd98046ce4dbfbb0093</t>
+  </si>
+  <si>
+    <t>6a16e75b8046ce4dbfbaa3e7</t>
+  </si>
+  <si>
+    <t>6a16f5788046ce4dbfbaa66e</t>
+  </si>
+  <si>
+    <t>6a1d7c2e8046ce4dbfbb00a0</t>
+  </si>
+  <si>
+    <t>6a1d8f358046ce4dbfbb03ed</t>
+  </si>
+  <si>
+    <t>6a1d3bcc8046ce4dbfbaf54f</t>
+  </si>
+  <si>
+    <t>6a1d41328046ce4dbfbaf67b</t>
+  </si>
+  <si>
+    <t>6a16ec188046ce4dbfbaa4d5</t>
+  </si>
+  <si>
+    <t>6a1d42138046ce4dbfbaf6a0</t>
+  </si>
+  <si>
+    <t>6a1eb6f48046ce4dbfbb17c1</t>
+  </si>
+  <si>
+    <t>6a1837b68046ce4dbfbabba7</t>
+  </si>
+  <si>
+    <t>6a183a118046ce4dbfbabc0f</t>
+  </si>
+  <si>
+    <t>6a183a118046ce4dbfbabc10</t>
+  </si>
+  <si>
+    <t>6a1eae618046ce4dbfbb1666</t>
+  </si>
+  <si>
+    <t>6a1eae618046ce4dbfbb1667</t>
+  </si>
+  <si>
+    <t>6a1a9d858046ce4dbfbadebf</t>
+  </si>
+  <si>
+    <t>6a185ae28046ce4dbfbac18a</t>
+  </si>
+  <si>
+    <t>6a1881898046ce4dbfbac47f</t>
+  </si>
+  <si>
+    <t>6a1eb2a68046ce4dbfbb170b</t>
+  </si>
+  <si>
+    <t>6a197a478046ce4dbfbad191</t>
+  </si>
+  <si>
+    <t>6a17fad18046ce4dbfbab200</t>
+  </si>
+  <si>
+    <t>6a1d532d8046ce4dbfbaf964</t>
+  </si>
+  <si>
+    <t>6a183fec8046ce4dbfbabced</t>
+  </si>
+  <si>
+    <t>6a1865648046ce4dbfbac294</t>
+  </si>
+  <si>
+    <t>6a18818a8046ce4dbfbac488</t>
+  </si>
+  <si>
+    <t>6a1d66888046ce4dbfbafd2e</t>
+  </si>
+  <si>
+    <t>6a1975578046ce4dbfbad0de</t>
+  </si>
+  <si>
+    <t>6a1975578046ce4dbfbad0df</t>
+  </si>
+  <si>
+    <t>6a1979f78046ce4dbfbad174</t>
+  </si>
+  <si>
+    <t>6a1979f78046ce4dbfbad175</t>
+  </si>
+  <si>
+    <t>6a1980fe8046ce4dbfbad28c</t>
+  </si>
+  <si>
+    <t>6a1980fe8046ce4dbfbad28d</t>
+  </si>
+  <si>
+    <t>6a19881a8046ce4dbfbad3c9</t>
+  </si>
+  <si>
+    <t>6a1983598046ce4dbfbad2f9</t>
+  </si>
+  <si>
+    <t>6a198b908046ce4dbfbad438</t>
+  </si>
+  <si>
+    <t>6a198a5c8046ce4dbfbad405</t>
+  </si>
+  <si>
+    <t>6a1993c58046ce4dbfbad539</t>
+  </si>
+  <si>
+    <t>6a1994fa8046ce4dbfbad580</t>
+  </si>
+  <si>
+    <t>6a1998858046ce4dbfbad5fc</t>
+  </si>
+  <si>
+    <t>6a199fc38046ce4dbfbad6cb</t>
+  </si>
+  <si>
+    <t>6a199fc38046ce4dbfbad6cf</t>
+  </si>
+  <si>
+    <t>6a19a2fb8046ce4dbfbad72b</t>
+  </si>
+  <si>
+    <t>6a19aa098046ce4dbfbad839</t>
+  </si>
+  <si>
+    <t>6a19ac6c8046ce4dbfbad865</t>
+  </si>
+  <si>
+    <t>6a19ac6c8046ce4dbfbad867</t>
+  </si>
+  <si>
+    <t>6a19afdf8046ce4dbfbad8c7</t>
+  </si>
+  <si>
+    <t>6a19b3688046ce4dbfbad909</t>
+  </si>
+  <si>
+    <t>6a19b6fe8046ce4dbfbad959</t>
+  </si>
+  <si>
+    <t>6a19b93d8046ce4dbfbad971</t>
+  </si>
+  <si>
+    <t>6a19db388046ce4dbfbadb3a</t>
+  </si>
+  <si>
+    <t>6a19521e8046ce4dbfbacb8d</t>
+  </si>
+  <si>
+    <t>6a1d37498046ce4dbfbaf450</t>
+  </si>
+  <si>
+    <t>6a197c4f8046ce4dbfbad1c1</t>
+  </si>
+  <si>
+    <t>6a1989368046ce4dbfbad3ef</t>
+  </si>
+  <si>
+    <t>6a198f168046ce4dbfbad4c2</t>
+  </si>
+  <si>
+    <t>6a198f168046ce4dbfbad4c3</t>
+  </si>
+  <si>
+    <t>6a198b908046ce4dbfbad439</t>
+  </si>
+  <si>
+    <t>6a19903c8046ce4dbfbad4e9</t>
+  </si>
+  <si>
+    <t>6a1997468046ce4dbfbad5c6</t>
+  </si>
+  <si>
+    <t>6a19afdf8046ce4dbfbad8ca</t>
+  </si>
+  <si>
+    <t>6a19b4b38046ce4dbfbad92b</t>
+  </si>
+  <si>
+    <t>6a19d6a08046ce4dbfbadb09</t>
+  </si>
+  <si>
+    <t>6a19d6a08046ce4dbfbadb0a</t>
+  </si>
+  <si>
+    <t>6a19e81e8046ce4dbfbadb80</t>
+  </si>
+  <si>
+    <t>6a1eb0f08046ce4dbfbb16cd</t>
+  </si>
+  <si>
+    <t>6a1aa1498046ce4dbfbadf4c</t>
+  </si>
+  <si>
+    <t>6a1aa1498046ce4dbfbadf4e</t>
+  </si>
+  <si>
+    <t>6a1aad258046ce4dbfbae0c7</t>
+  </si>
+  <si>
+    <t>6a1aaabf8046ce4dbfbae089</t>
+  </si>
+  <si>
+    <t>6a1aaf528046ce4dbfbae0f9</t>
+  </si>
+  <si>
+    <t>6a1ab9f58046ce4dbfbae229</t>
+  </si>
+  <si>
+    <t>6a1ac5a18046ce4dbfbae2f9</t>
+  </si>
+  <si>
+    <t>6a1acbd98046ce4dbfbae349</t>
+  </si>
+  <si>
+    <t>6a1ad85e8046ce4dbfbae406</t>
+  </si>
+  <si>
+    <t>6a1add258046ce4dbfbae466</t>
+  </si>
+  <si>
+    <t>6a1add258046ce4dbfbae469</t>
+  </si>
+  <si>
+    <t>6a1ade338046ce4dbfbae482</t>
+  </si>
+  <si>
+    <t>6a1ae08d8046ce4dbfbae4a6</t>
+  </si>
+  <si>
+    <t>6a1af4a18046ce4dbfbae5c6</t>
+  </si>
+  <si>
+    <t>6a1eb3f48046ce4dbfbb1735</t>
+  </si>
+  <si>
+    <t>6a1afa598046ce4dbfbae615</t>
+  </si>
+  <si>
+    <t>6a1afde18046ce4dbfbae62a</t>
+  </si>
+  <si>
+    <t>6a1b04e88046ce4dbfbae691</t>
+  </si>
+  <si>
+    <t>6a1a8faf8046ce4dbfbadcd1</t>
+  </si>
+  <si>
+    <t>6a1a90e98046ce4dbfbadd12</t>
+  </si>
+  <si>
+    <t>6a1a90e98046ce4dbfbadd13</t>
+  </si>
+  <si>
+    <t>6a1a933a8046ce4dbfbadd46</t>
+  </si>
+  <si>
+    <t>6a1a933a8046ce4dbfbadd4a</t>
+  </si>
+  <si>
+    <t>6a1a95938046ce4dbfbadd9a</t>
+  </si>
+  <si>
+    <t>6a1a95938046ce4dbfbadd9c</t>
+  </si>
+  <si>
+    <t>6a1aa5fa8046ce4dbfbadfe8</t>
+  </si>
+  <si>
+    <t>6a1aa8538046ce4dbfbae020</t>
+  </si>
+  <si>
+    <t>6a1aa86a8046ce4dbfbae033</t>
+  </si>
+  <si>
+    <t>6a1aae2c8046ce4dbfbae0ce</t>
+  </si>
+  <si>
+    <t>6a1aac238046ce4dbfbae0b3</t>
+  </si>
+  <si>
+    <t>6a1aac238046ce4dbfbae0b4</t>
+  </si>
+  <si>
+    <t>6a1ac7f98046ce4dbfbae31c</t>
+  </si>
+  <si>
+    <t>6a1ad3b08046ce4dbfbae3bc</t>
+  </si>
+  <si>
+    <t>6a1ad3b08046ce4dbfbae3bd</t>
+  </si>
+  <si>
+    <t>6a1adf648046ce4dbfbae495</t>
+  </si>
+  <si>
+    <t>6a1aec4f8046ce4dbfbae558</t>
+  </si>
+  <si>
+    <t>6a1ae9f48046ce4dbfbae528</t>
+  </si>
+  <si>
+    <t>6a1af8008046ce4dbfbae5ef</t>
+  </si>
+  <si>
+    <t>6a1af8008046ce4dbfbae5f1</t>
+  </si>
+  <si>
+    <t>6a1b02918046ce4dbfbae66f</t>
+  </si>
+  <si>
+    <t>6a1b02918046ce4dbfbae670</t>
+  </si>
+  <si>
+    <t>6a1b09978046ce4dbfbae6c6</t>
+  </si>
+  <si>
+    <t>6a1b0abd8046ce4dbfbae6d9</t>
+  </si>
+  <si>
+    <t>6a1b0bf98046ce4dbfbae6de</t>
+  </si>
+  <si>
+    <t>6a1b2b918046ce4dbfbae80b</t>
+  </si>
+  <si>
+    <t>6a1b2ba38046ce4dbfbae80e</t>
+  </si>
+  <si>
+    <t>6a1bcaeb8046ce4dbfbae8a6</t>
+  </si>
+  <si>
+    <t>6a1bddb28046ce4dbfbae8fa</t>
+  </si>
+  <si>
+    <t>6a1bfede8046ce4dbfbaeaaf</t>
+  </si>
+  <si>
+    <t>6a1c00d38046ce4dbfbaeae2</t>
+  </si>
+  <si>
+    <t>6a1c00d38046ce4dbfbaeae4</t>
+  </si>
+  <si>
+    <t>6a1c29ee8046ce4dbfbaed4a</t>
+  </si>
+  <si>
+    <t>6a1c55378046ce4dbfbaefaa</t>
+  </si>
+  <si>
+    <t>6a1c5d738046ce4dbfbaf01f</t>
+  </si>
+  <si>
+    <t>6a1bd7d28046ce4dbfbae8d0</t>
+  </si>
+  <si>
+    <t>6a1bded98046ce4dbfbae906</t>
+  </si>
+  <si>
+    <t>6a1bded98046ce4dbfbae907</t>
+  </si>
+  <si>
+    <t>6a1be4b98046ce4dbfbae925</t>
+  </si>
+  <si>
+    <t>6a1bfd5b8046ce4dbfbaea9f</t>
+  </si>
+  <si>
+    <t>6a1c02058046ce4dbfbaeafd</t>
+  </si>
+  <si>
+    <t>6a1c03358046ce4dbfbaeb12</t>
+  </si>
+  <si>
+    <t>6a1c0a3c8046ce4dbfbaeb8a</t>
+  </si>
+  <si>
+    <t>6a1c333e8046ce4dbfbaedd3</t>
+  </si>
+  <si>
+    <t>6a1c19768046ce4dbfbaec42</t>
+  </si>
+  <si>
+    <t>6a1c1afb8046ce4dbfbaec5c</t>
+  </si>
+  <si>
+    <t>6a1c1e2d8046ce4dbfbaeca9</t>
+  </si>
+  <si>
+    <t>6a1c27878046ce4dbfbaed20</t>
+  </si>
+  <si>
+    <t>6a1c2fb48046ce4dbfbaed95</t>
+  </si>
+  <si>
+    <t>6a1c333d8046ce4dbfbaedca</t>
+  </si>
+  <si>
+    <t>6a1c4f668046ce4dbfbaef6d</t>
+  </si>
+  <si>
+    <t>6a1c55378046ce4dbfbaefa7</t>
+  </si>
+  <si>
+    <t>6a1c57d68046ce4dbfbaefd2</t>
+  </si>
+  <si>
+    <t>6a1cbd898046ce4dbfbaf1e1</t>
+  </si>
+  <si>
+    <t>6a1cbd898046ce4dbfbaf1e2</t>
+  </si>
+  <si>
+    <t>6a1c7f6a8046ce4dbfbaf0f1</t>
+  </si>
+  <si>
+    <t>6a1d2e018046ce4dbfbaf2f0</t>
+  </si>
+  <si>
+    <t>6a1d3fa28046ce4dbfbaf626</t>
+  </si>
+  <si>
+    <t>6a1d3fa28046ce4dbfbaf628</t>
+  </si>
+  <si>
+    <t>6a1d3ae78046ce4dbfbaf527</t>
+  </si>
+  <si>
+    <t>6a1d3ae88046ce4dbfbaf535</t>
+  </si>
+  <si>
+    <t>6a1d3d478046ce4dbfbaf5c5</t>
+  </si>
+  <si>
+    <t>6a1d3d478046ce4dbfbaf5c6</t>
+  </si>
+  <si>
+    <t>6a1d40d38046ce4dbfbaf669</t>
+  </si>
+  <si>
+    <t>6a1d47d08046ce4dbfbaf783</t>
+  </si>
+  <si>
+    <t>6a1d47d08046ce4dbfbaf784</t>
+  </si>
+  <si>
+    <t>6a1d40d38046ce4dbfbaf66c</t>
+  </si>
+  <si>
+    <t>6a1d40d38046ce4dbfbaf66d</t>
+  </si>
+  <si>
+    <t>6a1d50078046ce4dbfbaf8f5</t>
+  </si>
+  <si>
+    <t>6a1d4b578046ce4dbfbaf82e</t>
+  </si>
+  <si>
+    <t>6a1d50068046ce4dbfbaf8df</t>
+  </si>
+  <si>
+    <t>6a1d512d8046ce4dbfbaf91e</t>
+  </si>
+  <si>
+    <t>6a1d4ed58046ce4dbfbaf89e</t>
+  </si>
+  <si>
+    <t>6a1d4ed58046ce4dbfbaf8a0</t>
+  </si>
+  <si>
+    <t>6a1d5ce28046ce4dbfbafb14</t>
+  </si>
+  <si>
+    <t>6a1d66558046ce4dbfbafcff</t>
+  </si>
+  <si>
+    <t>6a1d732b8046ce4dbfbaff0c</t>
+  </si>
+  <si>
+    <t>6a1d73278046ce4dbfbafefa</t>
+  </si>
+  <si>
+    <t>6a1d81338046ce4dbfbb0170</t>
+  </si>
+  <si>
+    <t>6a1d896c8046ce4dbfbb031b</t>
+  </si>
+  <si>
+    <t>6a1d897c8046ce4dbfbb032d</t>
+  </si>
+  <si>
+    <t>6a1d897c8046ce4dbfbb0332</t>
+  </si>
+  <si>
+    <t>6a1d88c28046ce4dbfbb02ff</t>
+  </si>
+  <si>
+    <t>6a1d90778046ce4dbfbb042a</t>
+  </si>
+  <si>
+    <t>6a1d8e1c8046ce4dbfbb03d1</t>
+  </si>
+  <si>
+    <t>6a1d96618046ce4dbfbb054a</t>
+  </si>
+  <si>
+    <t>6a1da20c8046ce4dbfbb0737</t>
+  </si>
+  <si>
+    <t>6a1ddc9f8046ce4dbfbb0be3</t>
+  </si>
+  <si>
+    <t>6a1ddc9f8046ce4dbfbb0be4</t>
+  </si>
+  <si>
+    <t>6a1d32ba8046ce4dbfbaf370</t>
+  </si>
+  <si>
+    <t>6a1d32bb8046ce4dbfbaf373</t>
+  </si>
+  <si>
+    <t>6a1d32bb8046ce4dbfbaf374</t>
+  </si>
+  <si>
+    <t>6a1d4a2d8046ce4dbfbaf80d</t>
+  </si>
+  <si>
+    <t>6a1d3c2d8046ce4dbfbaf58a</t>
+  </si>
+  <si>
+    <t>6a1d40d28046ce4dbfbaf65e</t>
+  </si>
+  <si>
+    <t>6a1d47d58046ce4dbfbaf789</t>
+  </si>
+  <si>
+    <t>6a1d4da48046ce4dbfbaf875</t>
+  </si>
+  <si>
+    <t>6a1d512c8046ce4dbfbaf915</t>
+  </si>
+  <si>
+    <t>6a1d53848046ce4dbfbaf96a</t>
+  </si>
+  <si>
+    <t>6a1d745f8046ce4dbfbaff43</t>
+  </si>
+  <si>
+    <t>6a1d745f8046ce4dbfbaff44</t>
+  </si>
+  <si>
+    <t>6a1d7b608046ce4dbfbb006b</t>
+  </si>
+  <si>
+    <t>6a1d7b608046ce4dbfbb006c</t>
+  </si>
+  <si>
+    <t>6a1d8ab58046ce4dbfbb035e</t>
+  </si>
+  <si>
+    <t>6a1d8ab58046ce4dbfbb035f</t>
+  </si>
+  <si>
+    <t>6a1d9c338046ce4dbfbb0667</t>
+  </si>
+  <si>
+    <t>6a1d9c338046ce4dbfbb066a</t>
+  </si>
+  <si>
+    <t>6a1d9d5b8046ce4dbfbb069e</t>
+  </si>
+  <si>
+    <t>6a1d9e8a8046ce4dbfbb06ab</t>
+  </si>
+  <si>
+    <t>6a1d9fb28046ce4dbfbb06f0</t>
+  </si>
+  <si>
+    <t>6a1daa408046ce4dbfbb0839</t>
+  </si>
+  <si>
+    <t>6a1e99598046ce4dbfbb1287</t>
+  </si>
+  <si>
+    <t>6a1db1498046ce4dbfbb0913</t>
+  </si>
+  <si>
+    <t>6a1dd9578046ce4dbfbb0bb1</t>
+  </si>
+  <si>
+    <t>6a1de0278046ce4dbfbb0c03</t>
+  </si>
+  <si>
+    <t>6a1df9e98046ce4dbfbb0c50</t>
+  </si>
+  <si>
+    <t>6a1e94a38046ce4dbfbb115b</t>
+  </si>
+  <si>
+    <t>6a1e94a38046ce4dbfbb115d</t>
+  </si>
+  <si>
+    <t>6a1ea3dc8046ce4dbfbb14a6</t>
+  </si>
+  <si>
+    <t>6a1eb1ec8046ce4dbfbb16fe</t>
+  </si>
+  <si>
+    <t>6a1eb1ea8046ce4dbfbb16ef</t>
+  </si>
+  <si>
+    <t>6a1eb4588046ce4dbfbb1763</t>
+  </si>
+  <si>
+    <t>6a1ebda08046ce4dbfbb18ed</t>
+  </si>
+  <si>
+    <t>6a1e73ca8046ce4dbfbb0d2b</t>
+  </si>
+  <si>
+    <t>6a1e91248046ce4dbfbb10cd</t>
+  </si>
+  <si>
+    <t>6a1ea08d8046ce4dbfbb13f8</t>
+  </si>
+  <si>
+    <t>6a1ea08d8046ce4dbfbb13fd</t>
+  </si>
+  <si>
+    <t>6a1ea6348046ce4dbfbb14fa</t>
+  </si>
+  <si>
+    <t>6a1ea2b58046ce4dbfbb1487</t>
+  </si>
+  <si>
+    <t>6a1ea75d8046ce4dbfbb1548</t>
+  </si>
+  <si>
+    <t>FIZZ-1000918997</t>
+  </si>
+  <si>
+    <t>FIZZ-1000929184</t>
+  </si>
+  <si>
+    <t>1449-529797</t>
+  </si>
+  <si>
+    <t>1449-804489</t>
+  </si>
+  <si>
+    <t>5427-909954</t>
+  </si>
+  <si>
+    <t>1449-454130</t>
+  </si>
+  <si>
+    <t>1449-113373</t>
+  </si>
+  <si>
+    <t>1449-168857</t>
+  </si>
+  <si>
+    <t>1449-914078</t>
+  </si>
+  <si>
+    <t>1449-559919</t>
+  </si>
+  <si>
+    <t>1449-977081</t>
+  </si>
+  <si>
+    <t>1449-526414</t>
+  </si>
+  <si>
+    <t>1449-552219</t>
+  </si>
+  <si>
+    <t>1449-558683</t>
+  </si>
+  <si>
+    <t>1449-307713</t>
+  </si>
+  <si>
+    <t>1449-889095</t>
+  </si>
+  <si>
+    <t>1449-327116</t>
+  </si>
+  <si>
+    <t>1449-967837</t>
+  </si>
+  <si>
+    <t>26MPE0005810/1</t>
+  </si>
+  <si>
+    <t>26MPE0005820/1</t>
+  </si>
+  <si>
+    <t>26MPE0005823/1</t>
+  </si>
+  <si>
+    <t>26MPE0005876/1</t>
+  </si>
+  <si>
+    <t>26MPE0005882/1</t>
+  </si>
+  <si>
+    <t>26MPE0005921/1</t>
+  </si>
+  <si>
+    <t>26MPE0005923/1</t>
+  </si>
+  <si>
+    <t>311288794/2/1</t>
+  </si>
+  <si>
+    <t>312144935/1</t>
+  </si>
+  <si>
+    <t>312633560/1</t>
+  </si>
+  <si>
+    <t>312633560/2</t>
+  </si>
+  <si>
+    <t>312633560/3</t>
+  </si>
+  <si>
+    <t>312679411/1</t>
+  </si>
+  <si>
+    <t>312679411/2</t>
+  </si>
+  <si>
+    <t>312679411/3</t>
+  </si>
+  <si>
+    <t>312679745/1</t>
+  </si>
+  <si>
+    <t>312679745/2</t>
+  </si>
+  <si>
+    <t>313333158/1</t>
+  </si>
+  <si>
+    <t>313333158/2</t>
+  </si>
+  <si>
+    <t>313333442/1</t>
+  </si>
+  <si>
+    <t>313333652/1</t>
+  </si>
+  <si>
+    <t>313380705/1</t>
+  </si>
+  <si>
+    <t>313380842/1</t>
+  </si>
+  <si>
+    <t>313380842/2</t>
+  </si>
+  <si>
+    <t>313380842/3</t>
+  </si>
+  <si>
+    <t>313381035/1</t>
+  </si>
+  <si>
+    <t>313435172/1</t>
+  </si>
+  <si>
+    <t>313435217/1</t>
+  </si>
+  <si>
+    <t>313435217/2</t>
+  </si>
+  <si>
+    <t>313435217/3</t>
+  </si>
+  <si>
+    <t>313435419/1</t>
+  </si>
+  <si>
+    <t>313435530/1</t>
+  </si>
+  <si>
+    <t>313435575/1</t>
+  </si>
+  <si>
+    <t>313435850/1</t>
+  </si>
+  <si>
+    <t>313435850/2</t>
+  </si>
+  <si>
+    <t>313490459/1</t>
+  </si>
+  <si>
+    <t>313490459/2</t>
+  </si>
+  <si>
+    <t>313490471/1</t>
+  </si>
+  <si>
+    <t>313490514/1</t>
+  </si>
+  <si>
+    <t>313490514/2</t>
+  </si>
+  <si>
+    <t>313490514/3</t>
+  </si>
+  <si>
+    <t>313490708/1</t>
+  </si>
+  <si>
+    <t>313490892/1</t>
+  </si>
+  <si>
+    <t>313491104/1</t>
+  </si>
+  <si>
+    <t>313491104/2</t>
+  </si>
+  <si>
+    <t>313491195/1</t>
+  </si>
+  <si>
+    <t>313491294/1</t>
+  </si>
+  <si>
+    <t>313491333/1</t>
+  </si>
+  <si>
+    <t>313556159/1</t>
+  </si>
+  <si>
+    <t>313556175/1</t>
+  </si>
+  <si>
+    <t>313556477/1</t>
+  </si>
+  <si>
+    <t>313556717/1</t>
+  </si>
+  <si>
+    <t>313557017/1</t>
+  </si>
+  <si>
+    <t>313631159/1</t>
+  </si>
+  <si>
+    <t>313631228/1</t>
+  </si>
+  <si>
+    <t>313631230/1</t>
+  </si>
+  <si>
+    <t>313631230/2</t>
+  </si>
+  <si>
+    <t>313631230/3</t>
+  </si>
+  <si>
+    <t>313631254/1</t>
+  </si>
+  <si>
+    <t>313631358/1</t>
+  </si>
+  <si>
+    <t>313631613/1</t>
+  </si>
+  <si>
+    <t>313631672/1</t>
+  </si>
+  <si>
+    <t>313631672/2</t>
+  </si>
+  <si>
+    <t>313631699/1</t>
+  </si>
+  <si>
+    <t>313631747/1</t>
+  </si>
+  <si>
+    <t>313631763/1</t>
+  </si>
+  <si>
+    <t>313631792/1</t>
+  </si>
+  <si>
+    <t>313631827/1</t>
+  </si>
+  <si>
+    <t>313631916/1</t>
+  </si>
+  <si>
+    <t>313631923/1</t>
+  </si>
+  <si>
+    <t>313631923/2</t>
+  </si>
+  <si>
+    <t>313704659/1</t>
+  </si>
+  <si>
+    <t>313704802/1</t>
+  </si>
+  <si>
+    <t>313704805/1</t>
+  </si>
+  <si>
+    <t>313704805/2</t>
+  </si>
+  <si>
+    <t>313704829/1</t>
+  </si>
+  <si>
+    <t>313705047/1</t>
+  </si>
+  <si>
+    <t>313705141/1</t>
+  </si>
+  <si>
+    <t>313705141/2</t>
+  </si>
+  <si>
+    <t>313705141/3</t>
+  </si>
+  <si>
+    <t>313705217/1</t>
+  </si>
+  <si>
+    <t>313705217/2</t>
+  </si>
+  <si>
+    <t>313705261/1</t>
+  </si>
+  <si>
+    <t>313705320/1</t>
+  </si>
+  <si>
+    <t>313705362/1</t>
+  </si>
+  <si>
+    <t>313705362/2</t>
+  </si>
+  <si>
+    <t>313705364/1</t>
+  </si>
+  <si>
+    <t>313705372/1</t>
+  </si>
+  <si>
+    <t>313756331/1</t>
+  </si>
+  <si>
+    <t>313756402/1</t>
+  </si>
+  <si>
+    <t>313756413/1</t>
+  </si>
+  <si>
+    <t>313756494/1</t>
+  </si>
+  <si>
+    <t>313756559/1</t>
+  </si>
+  <si>
+    <t>313756702/1</t>
+  </si>
+  <si>
+    <t>313756724/1</t>
+  </si>
+  <si>
+    <t>313756806/1</t>
+  </si>
+  <si>
+    <t>313756840/1</t>
+  </si>
+  <si>
+    <t>313756976/1</t>
+  </si>
+  <si>
+    <t>313757044/1</t>
+  </si>
+  <si>
+    <t>313757059/1</t>
+  </si>
+  <si>
+    <t>313757113/1</t>
+  </si>
+  <si>
+    <t>313824643/1</t>
+  </si>
+  <si>
+    <t>313824705/1</t>
+  </si>
+  <si>
+    <t>313824705/2</t>
+  </si>
+  <si>
+    <t>313824705/3</t>
+  </si>
+  <si>
+    <t>313824765/1</t>
+  </si>
+  <si>
+    <t>313824765/2</t>
+  </si>
+  <si>
+    <t>313824765/3</t>
+  </si>
+  <si>
+    <t>313824817/1</t>
+  </si>
+  <si>
+    <t>313824817/2</t>
+  </si>
+  <si>
+    <t>313824825/1</t>
+  </si>
+  <si>
+    <t>313824995/1</t>
+  </si>
+  <si>
+    <t>313825131/1</t>
+  </si>
+  <si>
+    <t>313825151/1</t>
+  </si>
+  <si>
+    <t>313825254/1</t>
+  </si>
+  <si>
+    <t>313878306/1</t>
+  </si>
+  <si>
+    <t>313878336/1</t>
+  </si>
+  <si>
+    <t>313878351/1</t>
+  </si>
+  <si>
+    <t>313878413/1</t>
+  </si>
+  <si>
+    <t>313879033/1</t>
+  </si>
+  <si>
+    <t>313879261/1</t>
+  </si>
+  <si>
+    <t>313944424/1</t>
+  </si>
+  <si>
+    <t>313944600/1</t>
+  </si>
+  <si>
+    <t>313944620/1</t>
+  </si>
+  <si>
+    <t>313945091/1</t>
+  </si>
+  <si>
+    <t>313945105/1</t>
+  </si>
+  <si>
+    <t>313991315/1</t>
+  </si>
+  <si>
+    <t>313991315/2</t>
+  </si>
+  <si>
+    <t>159995579540800318</t>
+  </si>
+  <si>
+    <t>159995579540800325</t>
+  </si>
+  <si>
+    <t>159995579540800332</t>
+  </si>
+  <si>
+    <t>159995579540800349</t>
+  </si>
+  <si>
+    <t>99002606/1</t>
+  </si>
+  <si>
+    <t>202606012601116801</t>
+  </si>
+  <si>
+    <t>202605282601138201</t>
+  </si>
+  <si>
+    <t>202606032601144101</t>
+  </si>
+  <si>
+    <t>202606012601151701</t>
+  </si>
+  <si>
+    <t>202606012601155901</t>
+  </si>
+  <si>
+    <t>202606012601153601</t>
+  </si>
+  <si>
+    <t>202606012601152101</t>
+  </si>
+  <si>
+    <t>202606012601153901</t>
+  </si>
+  <si>
+    <t>202606012601152801</t>
+  </si>
+  <si>
+    <t>202606012601162001</t>
+  </si>
+  <si>
+    <t>202606012601162002</t>
+  </si>
+  <si>
+    <t>202606012601160701</t>
+  </si>
+  <si>
+    <t>202606012601160901</t>
+  </si>
+  <si>
+    <t>202606012601163201</t>
+  </si>
+  <si>
+    <t>202606012601158101</t>
+  </si>
+  <si>
+    <t>202606012601158102</t>
+  </si>
+  <si>
+    <t>202606012601168701</t>
+  </si>
+  <si>
+    <t>202606012601166101</t>
+  </si>
+  <si>
+    <t>202606022601174601</t>
+  </si>
+  <si>
+    <t>202606022601175101</t>
+  </si>
+  <si>
+    <t>202606022601172901</t>
+  </si>
+  <si>
+    <t>202606022601172101</t>
+  </si>
+  <si>
+    <t>202606022601172701</t>
+  </si>
+  <si>
+    <t>202606022601174201</t>
+  </si>
+  <si>
+    <t>202606022601176501</t>
+  </si>
+  <si>
+    <t>202606022601173401</t>
+  </si>
+  <si>
+    <t>202606022601172001</t>
+  </si>
+  <si>
+    <t>202606022601171701</t>
+  </si>
+  <si>
+    <t>202606022601172601</t>
+  </si>
+  <si>
+    <t>202606022601171801</t>
+  </si>
+  <si>
+    <t>202606022601176401</t>
+  </si>
+  <si>
+    <t>202606032601183201</t>
+  </si>
+  <si>
+    <t>NFD6-06-02-F6YE/1</t>
+  </si>
+  <si>
+    <t>202606032601181101</t>
+  </si>
+  <si>
+    <t>202606032601182401</t>
+  </si>
+  <si>
+    <t>202605292601150401</t>
+  </si>
+  <si>
+    <t>202605292601151101</t>
+  </si>
+  <si>
+    <t>202606012601154501</t>
+  </si>
+  <si>
+    <t>202606012601156801</t>
+  </si>
+  <si>
+    <t>202606012601154601</t>
+  </si>
+  <si>
+    <t>202606012601155001</t>
+  </si>
+  <si>
+    <t>202606012601159401</t>
+  </si>
+  <si>
+    <t>202606012601162801</t>
+  </si>
+  <si>
+    <t>202606012601162802</t>
+  </si>
+  <si>
+    <t>202606012601162803</t>
+  </si>
+  <si>
+    <t>202606012601160401</t>
+  </si>
+  <si>
+    <t>202606012601162601</t>
+  </si>
+  <si>
+    <t>202606012601162602</t>
+  </si>
+  <si>
+    <t>202606012601162101</t>
+  </si>
+  <si>
+    <t>202606012601161901</t>
+  </si>
+  <si>
+    <t>202606012601171001</t>
+  </si>
+  <si>
+    <t>202606012601169501</t>
+  </si>
+  <si>
+    <t>202606012601168301</t>
+  </si>
+  <si>
+    <t>202606012601168101</t>
+  </si>
+  <si>
+    <t>202606012601165801</t>
+  </si>
+  <si>
+    <t>202606012601167501</t>
+  </si>
+  <si>
+    <t>202606012601167502</t>
+  </si>
+  <si>
+    <t>202606012601170201</t>
+  </si>
+  <si>
+    <t>202606012601170101</t>
+  </si>
+  <si>
+    <t>202606012601166901</t>
+  </si>
+  <si>
+    <t>202606022601175701</t>
+  </si>
+  <si>
+    <t>202606022601172401</t>
+  </si>
+  <si>
+    <t>202606022601177001</t>
+  </si>
+  <si>
+    <t>202606022601175301</t>
+  </si>
+  <si>
+    <t>202606022601175302</t>
+  </si>
+  <si>
+    <t>202606022601175303</t>
+  </si>
+  <si>
+    <t>202606022601175601</t>
+  </si>
+  <si>
+    <t>202606022601173001</t>
+  </si>
+  <si>
+    <t>202606022601177201</t>
+  </si>
+  <si>
+    <t>202606022601171301</t>
+  </si>
+  <si>
+    <t>202606022601174501</t>
+  </si>
+  <si>
+    <t>202606032601181201</t>
+  </si>
+  <si>
+    <t>202606032601179301</t>
+  </si>
+  <si>
+    <t>202606032601184101</t>
+  </si>
+  <si>
+    <t>159995579540800363</t>
+  </si>
+  <si>
+    <t>159995579540800462</t>
+  </si>
+  <si>
+    <t>159995579540785431</t>
+  </si>
+  <si>
+    <t>159995579540785448</t>
+  </si>
+  <si>
+    <t>159995579540832302</t>
+  </si>
+  <si>
+    <t>159995579540832319</t>
   </si>
 </sst>
 </file>
@@ -420,10 +2982,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -705,7 +3266,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D116"/>
+  <dimension ref="A1:D503"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
@@ -726,35 +3287,47 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
+      <c r="A2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B2" t="s">
+        <v>476</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
+      <c r="A3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" t="s">
+        <v>477</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D3"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
+      <c r="A4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" t="s">
+        <v>478</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D4"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
+      <c r="A5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" t="s">
+        <v>479</v>
       </c>
       <c r="C5" t="s">
         <v>118</v>
@@ -762,80 +3335,107 @@
       <c r="D5"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>9</v>
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>480</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D6"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>10</v>
+      <c r="A7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" t="s">
+        <v>481</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D7"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>11</v>
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>482</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D8"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
+      <c r="A9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" t="s">
+        <v>483</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D9"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>13</v>
+      <c r="A10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B10" t="s">
+        <v>484</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D10"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>14</v>
+      <c r="A11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B11" t="s">
+        <v>485</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D11"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>15</v>
+      <c r="A12" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" t="s">
+        <v>486</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D12"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>16</v>
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>487</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D13"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>17</v>
+      <c r="A14" t="s">
+        <v>178</v>
+      </c>
+      <c r="B14" t="s">
+        <v>488</v>
       </c>
       <c r="C14" t="s">
         <v>118</v>
@@ -843,134 +3443,179 @@
       <c r="D14"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>18</v>
+      <c r="A15" t="s">
+        <v>179</v>
+      </c>
+      <c r="B15" t="s">
+        <v>489</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D15"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>3</v>
+      <c r="A16" t="s">
+        <v>180</v>
+      </c>
+      <c r="B16" t="s">
+        <v>490</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="D16"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>19</v>
+      <c r="A17" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" t="s">
+        <v>491</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D17"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>20</v>
+      <c r="A18" t="s">
+        <v>182</v>
+      </c>
+      <c r="B18" t="s">
+        <v>492</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D18"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>21</v>
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>493</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D19"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>22</v>
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>494</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="D20"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>23</v>
+      <c r="A21" t="s">
+        <v>183</v>
+      </c>
+      <c r="B21" t="s">
+        <v>495</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="D21"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>24</v>
+      <c r="A22" t="s">
+        <v>183</v>
+      </c>
+      <c r="B22" t="s">
+        <v>496</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="D22"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>25</v>
+      <c r="A23" t="s">
+        <v>184</v>
+      </c>
+      <c r="B23" t="s">
+        <v>497</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D23"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>26</v>
+      <c r="A24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" t="s">
+        <v>498</v>
       </c>
       <c r="C24" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D24"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>27</v>
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>499</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D25"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>28</v>
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" t="s">
+        <v>500</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D26"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>29</v>
+      <c r="A27" t="s">
+        <v>185</v>
+      </c>
+      <c r="B27" t="s">
+        <v>501</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="D27"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>30</v>
+      <c r="A28" t="s">
+        <v>186</v>
+      </c>
+      <c r="B28" t="s">
+        <v>502</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="D28"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>31</v>
+      <c r="A29" t="s">
+        <v>187</v>
+      </c>
+      <c r="B29" t="s">
+        <v>503</v>
       </c>
       <c r="C29" t="s">
         <v>118</v>
@@ -978,53 +3623,71 @@
       <c r="D29"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>32</v>
+      <c r="A30" t="s">
+        <v>188</v>
+      </c>
+      <c r="B30" t="s">
+        <v>504</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="D30"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>33</v>
+      <c r="A31" t="s">
+        <v>189</v>
+      </c>
+      <c r="B31" t="s">
+        <v>505</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="D31"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>34</v>
+      <c r="A32" t="s">
+        <v>190</v>
+      </c>
+      <c r="B32" t="s">
+        <v>506</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D32"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>35</v>
+      <c r="A33" t="s">
+        <v>191</v>
+      </c>
+      <c r="B33" t="s">
+        <v>507</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="D33"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>36</v>
+      <c r="A34" t="s">
+        <v>192</v>
+      </c>
+      <c r="B34" t="s">
+        <v>508</v>
       </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D34"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>37</v>
+      <c r="A35" t="s">
+        <v>193</v>
+      </c>
+      <c r="B35" t="s">
+        <v>509</v>
       </c>
       <c r="C35" t="s">
         <v>118</v>
@@ -1032,80 +3695,107 @@
       <c r="D35"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>38</v>
+      <c r="A36" t="s">
+        <v>194</v>
+      </c>
+      <c r="B36" t="s">
+        <v>510</v>
       </c>
       <c r="C36" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D36"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>39</v>
+      <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" t="s">
+        <v>511</v>
       </c>
       <c r="C37" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="D37"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>40</v>
+      <c r="A38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" t="s">
+        <v>512</v>
       </c>
       <c r="C38" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="D38"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>41</v>
+      <c r="A39" t="s">
+        <v>195</v>
+      </c>
+      <c r="B39" t="s">
+        <v>513</v>
       </c>
       <c r="C39" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="D39"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>42</v>
+      <c r="A40" t="s">
+        <v>195</v>
+      </c>
+      <c r="B40" t="s">
+        <v>514</v>
       </c>
       <c r="C40" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="D40"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>43</v>
+      <c r="A41" t="s">
+        <v>196</v>
+      </c>
+      <c r="B41" t="s">
+        <v>515</v>
       </c>
       <c r="C41" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="D41"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>44</v>
+      <c r="A42" t="s">
+        <v>197</v>
+      </c>
+      <c r="B42" t="s">
+        <v>516</v>
       </c>
       <c r="C42" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D42"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>45</v>
+      <c r="A43" t="s">
+        <v>198</v>
+      </c>
+      <c r="B43" t="s">
+        <v>517</v>
       </c>
       <c r="C43" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="D43"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>46</v>
+      <c r="A44" t="s">
+        <v>199</v>
+      </c>
+      <c r="B44" t="s">
+        <v>518</v>
       </c>
       <c r="C44" t="s">
         <v>118</v>
@@ -1113,188 +3803,251 @@
       <c r="D44"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>47</v>
+      <c r="A45" t="s">
+        <v>200</v>
+      </c>
+      <c r="B45" t="s">
+        <v>519</v>
       </c>
       <c r="C45" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="D45"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>48</v>
+      <c r="A46" t="s">
+        <v>200</v>
+      </c>
+      <c r="B46" t="s">
+        <v>520</v>
       </c>
       <c r="C46" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="D46"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>49</v>
+      <c r="A47" t="s">
+        <v>201</v>
+      </c>
+      <c r="B47" t="s">
+        <v>521</v>
       </c>
       <c r="C47" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D47"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>50</v>
+      <c r="A48" t="s">
+        <v>202</v>
+      </c>
+      <c r="B48" t="s">
+        <v>522</v>
       </c>
       <c r="C48" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="D48"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>51</v>
+      <c r="A49" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" t="s">
+        <v>523</v>
       </c>
       <c r="C49" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D49"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>52</v>
+      <c r="A50" t="s">
+        <v>203</v>
+      </c>
+      <c r="B50" t="s">
+        <v>524</v>
       </c>
       <c r="C50" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="D50"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>53</v>
+      <c r="A51" t="s">
+        <v>204</v>
+      </c>
+      <c r="B51" t="s">
+        <v>525</v>
       </c>
       <c r="C51" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D51"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>54</v>
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>526</v>
       </c>
       <c r="C52" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="D52"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>55</v>
+      <c r="A53" t="s">
+        <v>205</v>
+      </c>
+      <c r="B53" t="s">
+        <v>527</v>
       </c>
       <c r="C53" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D53"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>56</v>
+      <c r="A54" t="s">
+        <v>16</v>
+      </c>
+      <c r="B54" t="s">
+        <v>528</v>
       </c>
       <c r="C54" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="D54"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>57</v>
+      <c r="A55" t="s">
+        <v>206</v>
+      </c>
+      <c r="B55" t="s">
+        <v>529</v>
       </c>
       <c r="C55" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="D55"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>58</v>
+      <c r="A56" t="s">
+        <v>207</v>
+      </c>
+      <c r="B56" t="s">
+        <v>530</v>
       </c>
       <c r="C56" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D56"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>59</v>
+      <c r="A57" t="s">
+        <v>208</v>
+      </c>
+      <c r="B57" t="s">
+        <v>531</v>
       </c>
       <c r="C57" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D57"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>60</v>
+      <c r="A58" t="s">
+        <v>17</v>
+      </c>
+      <c r="B58" t="s">
+        <v>532</v>
       </c>
       <c r="C58" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="D58"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>61</v>
+      <c r="A59" t="s">
+        <v>209</v>
+      </c>
+      <c r="B59" t="s">
+        <v>533</v>
       </c>
       <c r="C59" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="D59"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>62</v>
+      <c r="A60" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" t="s">
+        <v>534</v>
       </c>
       <c r="C60" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D60"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>63</v>
+      <c r="A61" t="s">
+        <v>210</v>
+      </c>
+      <c r="B61" t="s">
+        <v>535</v>
       </c>
       <c r="C61" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="D61"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>64</v>
+      <c r="A62" t="s">
+        <v>18</v>
+      </c>
+      <c r="B62" t="s">
+        <v>536</v>
       </c>
       <c r="C62" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="D62"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>65</v>
+      <c r="A63" t="s">
+        <v>211</v>
+      </c>
+      <c r="B63" t="s">
+        <v>537</v>
       </c>
       <c r="C63" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="D63"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>66</v>
+      <c r="A64" t="s">
+        <v>212</v>
+      </c>
+      <c r="B64" t="s">
+        <v>538</v>
       </c>
       <c r="C64" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D64"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>67</v>
+      <c r="A65" t="s">
+        <v>213</v>
+      </c>
+      <c r="B65" t="s">
+        <v>539</v>
       </c>
       <c r="C65" t="s">
         <v>118</v>
@@ -1302,8 +4055,11 @@
       <c r="D65"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>68</v>
+      <c r="A66" t="s">
+        <v>213</v>
+      </c>
+      <c r="B66" t="s">
+        <v>540</v>
       </c>
       <c r="C66" t="s">
         <v>118</v>
@@ -1311,413 +4067,4820 @@
       <c r="D66"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>69</v>
+      <c r="A67" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" t="s">
+        <v>541</v>
       </c>
       <c r="C67" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="D67"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>70</v>
+      <c r="A68" t="s">
+        <v>19</v>
+      </c>
+      <c r="B68" t="s">
+        <v>542</v>
       </c>
       <c r="C68" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="D68"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>71</v>
+      <c r="A69" t="s">
+        <v>214</v>
+      </c>
+      <c r="B69" t="s">
+        <v>543</v>
       </c>
       <c r="C69" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="D69"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>72</v>
+      <c r="A70" t="s">
+        <v>215</v>
+      </c>
+      <c r="B70" t="s">
+        <v>544</v>
       </c>
       <c r="C70" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="D70"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>73</v>
+      <c r="A71" t="s">
+        <v>216</v>
+      </c>
+      <c r="B71" t="s">
+        <v>545</v>
       </c>
       <c r="C71" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="D71"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>74</v>
+      <c r="A72" t="s">
+        <v>217</v>
+      </c>
+      <c r="B72" t="s">
+        <v>546</v>
       </c>
       <c r="C72" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="D72"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>75</v>
+      <c r="A73" t="s">
+        <v>218</v>
+      </c>
+      <c r="B73" t="s">
+        <v>547</v>
       </c>
       <c r="C73" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="D73"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>76</v>
+      <c r="A74" t="s">
+        <v>219</v>
+      </c>
+      <c r="B74" t="s">
+        <v>548</v>
       </c>
       <c r="C74" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="D74"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>77</v>
+      <c r="A75" t="s">
+        <v>220</v>
+      </c>
+      <c r="B75" t="s">
+        <v>549</v>
       </c>
       <c r="C75" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="D75"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>78</v>
+      <c r="A76" t="s">
+        <v>221</v>
+      </c>
+      <c r="B76" t="s">
+        <v>550</v>
       </c>
       <c r="C76" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="D76"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>4</v>
+      <c r="A77" t="s">
+        <v>20</v>
+      </c>
+      <c r="B77" t="s">
+        <v>551</v>
       </c>
       <c r="C77" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>79</v>
+      <c r="A78" t="s">
+        <v>222</v>
+      </c>
+      <c r="B78" t="s">
+        <v>552</v>
       </c>
       <c r="C78" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>80</v>
+      <c r="A79" t="s">
+        <v>21</v>
+      </c>
+      <c r="B79" t="s">
+        <v>553</v>
       </c>
       <c r="C79" t="s">
-        <v>118</v>
+        <v>151</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>81</v>
+      <c r="A80" t="s">
+        <v>223</v>
+      </c>
+      <c r="B80" t="s">
+        <v>554</v>
       </c>
       <c r="C80" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>82</v>
+      <c r="A81" t="s">
+        <v>223</v>
+      </c>
+      <c r="B81" t="s">
+        <v>555</v>
       </c>
       <c r="C81" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>83</v>
+      <c r="A82" t="s">
+        <v>224</v>
+      </c>
+      <c r="B82" t="s">
+        <v>556</v>
       </c>
       <c r="C82" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>84</v>
+      <c r="A83" t="s">
+        <v>224</v>
+      </c>
+      <c r="B83" t="s">
+        <v>557</v>
       </c>
       <c r="C83" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>85</v>
+      <c r="A84" t="s">
+        <v>225</v>
+      </c>
+      <c r="B84" t="s">
+        <v>558</v>
       </c>
       <c r="C84" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>86</v>
+      <c r="A85" t="s">
+        <v>225</v>
+      </c>
+      <c r="B85" t="s">
+        <v>559</v>
       </c>
       <c r="C85" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>87</v>
+      <c r="A86" t="s">
+        <v>226</v>
+      </c>
+      <c r="B86" t="s">
+        <v>560</v>
       </c>
       <c r="C86" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>88</v>
+      <c r="A87" t="s">
+        <v>227</v>
+      </c>
+      <c r="B87" t="s">
+        <v>561</v>
       </c>
       <c r="C87" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>89</v>
+      <c r="A88" t="s">
+        <v>22</v>
+      </c>
+      <c r="B88" t="s">
+        <v>562</v>
       </c>
       <c r="C88" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
-        <v>90</v>
+      <c r="A89" t="s">
+        <v>228</v>
+      </c>
+      <c r="B89" t="s">
+        <v>563</v>
       </c>
       <c r="C89" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>91</v>
+      <c r="A90" t="s">
+        <v>229</v>
+      </c>
+      <c r="B90" t="s">
+        <v>564</v>
       </c>
       <c r="C90" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>92</v>
+      <c r="A91" t="s">
+        <v>23</v>
+      </c>
+      <c r="B91" t="s">
+        <v>565</v>
       </c>
       <c r="C91" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>93</v>
+      <c r="A92" t="s">
+        <v>230</v>
+      </c>
+      <c r="B92" t="s">
+        <v>566</v>
       </c>
       <c r="C92" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>94</v>
+      <c r="A93" t="s">
+        <v>231</v>
+      </c>
+      <c r="B93" t="s">
+        <v>567</v>
       </c>
       <c r="C93" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
-        <v>95</v>
+      <c r="A94" t="s">
+        <v>231</v>
+      </c>
+      <c r="B94" t="s">
+        <v>568</v>
       </c>
       <c r="C94" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>96</v>
+      <c r="A95" t="s">
+        <v>232</v>
+      </c>
+      <c r="B95" t="s">
+        <v>569</v>
       </c>
       <c r="C95" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>97</v>
+      <c r="A96" t="s">
+        <v>233</v>
+      </c>
+      <c r="B96" t="s">
+        <v>570</v>
       </c>
       <c r="C96" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
-        <v>98</v>
+      <c r="A97" t="s">
+        <v>234</v>
+      </c>
+      <c r="B97" t="s">
+        <v>571</v>
       </c>
       <c r="C97" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>99</v>
+      <c r="A98" t="s">
+        <v>234</v>
+      </c>
+      <c r="B98" t="s">
+        <v>572</v>
       </c>
       <c r="C98" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>100</v>
+      <c r="A99" t="s">
+        <v>235</v>
+      </c>
+      <c r="B99" t="s">
+        <v>573</v>
       </c>
       <c r="C99" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>101</v>
+      <c r="A100" t="s">
+        <v>236</v>
+      </c>
+      <c r="B100" t="s">
+        <v>574</v>
       </c>
       <c r="C100" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>102</v>
+      <c r="A101" t="s">
+        <v>24</v>
+      </c>
+      <c r="B101" t="s">
+        <v>575</v>
       </c>
       <c r="C101" t="s">
-        <v>118</v>
+        <v>154</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
-        <v>103</v>
+      <c r="A102" t="s">
+        <v>237</v>
+      </c>
+      <c r="B102" t="s">
+        <v>576</v>
       </c>
       <c r="C102" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
-        <v>104</v>
+      <c r="A103" t="s">
+        <v>238</v>
+      </c>
+      <c r="B103" t="s">
+        <v>577</v>
       </c>
       <c r="C103" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
-        <v>105</v>
+      <c r="A104" t="s">
+        <v>239</v>
+      </c>
+      <c r="B104" t="s">
+        <v>578</v>
       </c>
       <c r="C104" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
-        <v>106</v>
+      <c r="A105" t="s">
+        <v>240</v>
+      </c>
+      <c r="B105" t="s">
+        <v>579</v>
       </c>
       <c r="C105" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
+      <c r="A106" t="s">
+        <v>241</v>
+      </c>
+      <c r="B106" t="s">
+        <v>580</v>
+      </c>
+      <c r="C106" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>242</v>
+      </c>
+      <c r="B107" t="s">
+        <v>581</v>
+      </c>
+      <c r="C107" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>25</v>
+      </c>
+      <c r="B108" t="s">
+        <v>582</v>
+      </c>
+      <c r="C108" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>25</v>
+      </c>
+      <c r="B109" t="s">
+        <v>583</v>
+      </c>
+      <c r="C109" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>243</v>
+      </c>
+      <c r="B110" t="s">
+        <v>584</v>
+      </c>
+      <c r="C110" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>244</v>
+      </c>
+      <c r="B111" t="s">
+        <v>585</v>
+      </c>
+      <c r="C111" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>26</v>
+      </c>
+      <c r="B112" t="s">
+        <v>586</v>
+      </c>
+      <c r="C112" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>245</v>
+      </c>
+      <c r="B113" t="s">
+        <v>587</v>
+      </c>
+      <c r="C113" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>27</v>
+      </c>
+      <c r="B114" t="s">
+        <v>588</v>
+      </c>
+      <c r="C114" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>28</v>
+      </c>
+      <c r="B115" t="s">
+        <v>589</v>
+      </c>
+      <c r="C115" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>28</v>
+      </c>
+      <c r="B116" t="s">
+        <v>590</v>
+      </c>
+      <c r="C116" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>246</v>
+      </c>
+      <c r="B117" t="s">
+        <v>591</v>
+      </c>
+      <c r="C117" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>247</v>
+      </c>
+      <c r="B118" t="s">
+        <v>592</v>
+      </c>
+      <c r="C118" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>248</v>
+      </c>
+      <c r="B119" t="s">
+        <v>593</v>
+      </c>
+      <c r="C119" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>248</v>
+      </c>
+      <c r="B120" t="s">
+        <v>594</v>
+      </c>
+      <c r="C120" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>249</v>
+      </c>
+      <c r="B121" t="s">
+        <v>595</v>
+      </c>
+      <c r="C121" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>250</v>
+      </c>
+      <c r="B122" t="s">
+        <v>596</v>
+      </c>
+      <c r="C122" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>251</v>
+      </c>
+      <c r="B123" t="s">
+        <v>597</v>
+      </c>
+      <c r="C123" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>252</v>
+      </c>
+      <c r="B124" t="s">
+        <v>598</v>
+      </c>
+      <c r="C124" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>253</v>
+      </c>
+      <c r="B125" t="s">
+        <v>599</v>
+      </c>
+      <c r="C125" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>254</v>
+      </c>
+      <c r="B126" t="s">
+        <v>600</v>
+      </c>
+      <c r="C126" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>255</v>
+      </c>
+      <c r="B127" t="s">
+        <v>601</v>
+      </c>
+      <c r="C127" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>256</v>
+      </c>
+      <c r="B128" t="s">
+        <v>602</v>
+      </c>
+      <c r="C128" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>256</v>
+      </c>
+      <c r="B129" t="s">
+        <v>603</v>
+      </c>
+      <c r="C129" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>257</v>
+      </c>
+      <c r="B130" t="s">
+        <v>604</v>
+      </c>
+      <c r="C130" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>258</v>
+      </c>
+      <c r="B131" t="s">
+        <v>605</v>
+      </c>
+      <c r="C131" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>259</v>
+      </c>
+      <c r="B132" t="s">
+        <v>606</v>
+      </c>
+      <c r="C132" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>29</v>
+      </c>
+      <c r="B133" t="s">
+        <v>607</v>
+      </c>
+      <c r="C133" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>260</v>
+      </c>
+      <c r="B134" t="s">
+        <v>608</v>
+      </c>
+      <c r="C134" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>30</v>
+      </c>
+      <c r="B135" t="s">
+        <v>609</v>
+      </c>
+      <c r="C135" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>31</v>
+      </c>
+      <c r="B136" t="s">
+        <v>610</v>
+      </c>
+      <c r="C136" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>261</v>
+      </c>
+      <c r="B137" t="s">
+        <v>611</v>
+      </c>
+      <c r="C137" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>262</v>
+      </c>
+      <c r="B138" t="s">
+        <v>612</v>
+      </c>
+      <c r="C138" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>262</v>
+      </c>
+      <c r="B139" t="s">
+        <v>613</v>
+      </c>
+      <c r="C139" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>263</v>
+      </c>
+      <c r="B140" t="s">
+        <v>614</v>
+      </c>
+      <c r="C140" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>263</v>
+      </c>
+      <c r="B141" t="s">
+        <v>615</v>
+      </c>
+      <c r="C141" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>264</v>
+      </c>
+      <c r="B142" t="s">
+        <v>616</v>
+      </c>
+      <c r="C142" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>264</v>
+      </c>
+      <c r="B143" t="s">
+        <v>617</v>
+      </c>
+      <c r="C143" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>265</v>
+      </c>
+      <c r="B144" t="s">
+        <v>618</v>
+      </c>
+      <c r="C144" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>32</v>
+      </c>
+      <c r="B145" t="s">
+        <v>619</v>
+      </c>
+      <c r="C145" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>266</v>
+      </c>
+      <c r="B146" t="s">
+        <v>620</v>
+      </c>
+      <c r="C146" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>267</v>
+      </c>
+      <c r="B147" t="s">
+        <v>621</v>
+      </c>
+      <c r="C147" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>33</v>
+      </c>
+      <c r="B148" t="s">
+        <v>622</v>
+      </c>
+      <c r="C148" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>33</v>
+      </c>
+      <c r="B149" t="s">
+        <v>623</v>
+      </c>
+      <c r="C149" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>268</v>
+      </c>
+      <c r="B150" t="s">
+        <v>624</v>
+      </c>
+      <c r="C150" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>34</v>
+      </c>
+      <c r="B151" t="s">
+        <v>625</v>
+      </c>
+      <c r="C151" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>34</v>
+      </c>
+      <c r="B152" t="s">
+        <v>626</v>
+      </c>
+      <c r="C152" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>269</v>
+      </c>
+      <c r="B153" t="s">
+        <v>627</v>
+      </c>
+      <c r="C153" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>35</v>
+      </c>
+      <c r="B154" t="s">
+        <v>628</v>
+      </c>
+      <c r="C154" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>36</v>
+      </c>
+      <c r="B155" t="s">
+        <v>629</v>
+      </c>
+      <c r="C155" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>270</v>
+      </c>
+      <c r="B156" t="s">
+        <v>630</v>
+      </c>
+      <c r="C156" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>270</v>
+      </c>
+      <c r="B157" t="s">
+        <v>631</v>
+      </c>
+      <c r="C157" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>271</v>
+      </c>
+      <c r="B158" t="s">
+        <v>632</v>
+      </c>
+      <c r="C158" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>271</v>
+      </c>
+      <c r="B159" t="s">
+        <v>633</v>
+      </c>
+      <c r="C159" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>272</v>
+      </c>
+      <c r="B160" t="s">
+        <v>634</v>
+      </c>
+      <c r="C160" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>273</v>
+      </c>
+      <c r="B161" t="s">
+        <v>635</v>
+      </c>
+      <c r="C161" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>274</v>
+      </c>
+      <c r="B162" t="s">
+        <v>636</v>
+      </c>
+      <c r="C162" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>37</v>
+      </c>
+      <c r="B163" t="s">
+        <v>637</v>
+      </c>
+      <c r="C163" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>275</v>
+      </c>
+      <c r="B164" t="s">
+        <v>638</v>
+      </c>
+      <c r="C164" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>276</v>
+      </c>
+      <c r="B165" t="s">
+        <v>639</v>
+      </c>
+      <c r="C165" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>38</v>
+      </c>
+      <c r="B166" t="s">
+        <v>640</v>
+      </c>
+      <c r="C166" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>277</v>
+      </c>
+      <c r="B167" t="s">
+        <v>641</v>
+      </c>
+      <c r="C167" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>39</v>
+      </c>
+      <c r="B168" t="s">
+        <v>642</v>
+      </c>
+      <c r="C168" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>39</v>
+      </c>
+      <c r="B169" t="s">
+        <v>643</v>
+      </c>
+      <c r="C169" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>278</v>
+      </c>
+      <c r="B170" t="s">
+        <v>644</v>
+      </c>
+      <c r="C170" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>279</v>
+      </c>
+      <c r="B171" t="s">
+        <v>645</v>
+      </c>
+      <c r="C171" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>280</v>
+      </c>
+      <c r="B172" t="s">
+        <v>646</v>
+      </c>
+      <c r="C172" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>281</v>
+      </c>
+      <c r="B173" t="s">
+        <v>647</v>
+      </c>
+      <c r="C173" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>282</v>
+      </c>
+      <c r="B174" t="s">
+        <v>648</v>
+      </c>
+      <c r="C174" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>282</v>
+      </c>
+      <c r="B175" t="s">
+        <v>649</v>
+      </c>
+      <c r="C175" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>283</v>
+      </c>
+      <c r="B176" t="s">
+        <v>650</v>
+      </c>
+      <c r="C176" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>284</v>
+      </c>
+      <c r="B177" t="s">
+        <v>651</v>
+      </c>
+      <c r="C177" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>285</v>
+      </c>
+      <c r="B178" t="s">
+        <v>652</v>
+      </c>
+      <c r="C178" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>286</v>
+      </c>
+      <c r="B179" t="s">
+        <v>653</v>
+      </c>
+      <c r="C179" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>287</v>
+      </c>
+      <c r="B180" t="s">
+        <v>654</v>
+      </c>
+      <c r="C180" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>288</v>
+      </c>
+      <c r="B181" t="s">
+        <v>655</v>
+      </c>
+      <c r="C181" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>289</v>
+      </c>
+      <c r="B182" t="s">
+        <v>656</v>
+      </c>
+      <c r="C182" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>290</v>
+      </c>
+      <c r="B183" t="s">
+        <v>657</v>
+      </c>
+      <c r="C183" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>40</v>
+      </c>
+      <c r="B184" t="s">
+        <v>658</v>
+      </c>
+      <c r="C184" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>291</v>
+      </c>
+      <c r="B185" t="s">
+        <v>659</v>
+      </c>
+      <c r="C185" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>292</v>
+      </c>
+      <c r="B186" t="s">
+        <v>660</v>
+      </c>
+      <c r="C186" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>293</v>
+      </c>
+      <c r="B187" t="s">
+        <v>661</v>
+      </c>
+      <c r="C187" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>41</v>
+      </c>
+      <c r="B188" t="s">
+        <v>662</v>
+      </c>
+      <c r="C188" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>294</v>
+      </c>
+      <c r="B189" t="s">
+        <v>663</v>
+      </c>
+      <c r="C189" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>295</v>
+      </c>
+      <c r="B190" t="s">
+        <v>664</v>
+      </c>
+      <c r="C190" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>296</v>
+      </c>
+      <c r="B191" t="s">
+        <v>665</v>
+      </c>
+      <c r="C191" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>296</v>
+      </c>
+      <c r="B192" t="s">
+        <v>666</v>
+      </c>
+      <c r="C192" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>297</v>
+      </c>
+      <c r="B193" t="s">
+        <v>667</v>
+      </c>
+      <c r="C193" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>298</v>
+      </c>
+      <c r="B194" t="s">
+        <v>668</v>
+      </c>
+      <c r="C194" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>299</v>
+      </c>
+      <c r="B195" t="s">
+        <v>669</v>
+      </c>
+      <c r="C195" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>299</v>
+      </c>
+      <c r="B196" t="s">
+        <v>670</v>
+      </c>
+      <c r="C196" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>42</v>
+      </c>
+      <c r="B197" t="s">
+        <v>671</v>
+      </c>
+      <c r="C197" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>300</v>
+      </c>
+      <c r="B198" t="s">
+        <v>672</v>
+      </c>
+      <c r="C198" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>301</v>
+      </c>
+      <c r="B199" t="s">
+        <v>673</v>
+      </c>
+      <c r="C199" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>301</v>
+      </c>
+      <c r="B200" t="s">
+        <v>674</v>
+      </c>
+      <c r="C200" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>302</v>
+      </c>
+      <c r="B201" t="s">
+        <v>675</v>
+      </c>
+      <c r="C201" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>303</v>
+      </c>
+      <c r="B202" t="s">
+        <v>676</v>
+      </c>
+      <c r="C202" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>303</v>
+      </c>
+      <c r="B203" t="s">
+        <v>677</v>
+      </c>
+      <c r="C203" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>304</v>
+      </c>
+      <c r="B204" t="s">
+        <v>678</v>
+      </c>
+      <c r="C204" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>304</v>
+      </c>
+      <c r="B205" t="s">
+        <v>679</v>
+      </c>
+      <c r="C205" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>305</v>
+      </c>
+      <c r="B206" t="s">
+        <v>680</v>
+      </c>
+      <c r="C206" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>306</v>
+      </c>
+      <c r="B207" t="s">
+        <v>681</v>
+      </c>
+      <c r="C207" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>307</v>
+      </c>
+      <c r="B208" t="s">
+        <v>682</v>
+      </c>
+      <c r="C208" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>308</v>
+      </c>
+      <c r="B209" t="s">
+        <v>683</v>
+      </c>
+      <c r="C209" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>43</v>
+      </c>
+      <c r="B210" t="s">
+        <v>684</v>
+      </c>
+      <c r="C210" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>43</v>
+      </c>
+      <c r="B211" t="s">
+        <v>685</v>
+      </c>
+      <c r="C211" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>309</v>
+      </c>
+      <c r="B212" t="s">
+        <v>686</v>
+      </c>
+      <c r="C212" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>310</v>
+      </c>
+      <c r="B213" t="s">
+        <v>687</v>
+      </c>
+      <c r="C213" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>44</v>
+      </c>
+      <c r="B214" t="s">
+        <v>688</v>
+      </c>
+      <c r="C214" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>311</v>
+      </c>
+      <c r="B215" t="s">
+        <v>689</v>
+      </c>
+      <c r="C215" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>312</v>
+      </c>
+      <c r="B216" t="s">
+        <v>690</v>
+      </c>
+      <c r="C216" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>45</v>
+      </c>
+      <c r="B217" t="s">
+        <v>691</v>
+      </c>
+      <c r="C217" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>313</v>
+      </c>
+      <c r="B218" t="s">
+        <v>692</v>
+      </c>
+      <c r="C218" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>313</v>
+      </c>
+      <c r="B219" t="s">
+        <v>693</v>
+      </c>
+      <c r="C219" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>314</v>
+      </c>
+      <c r="B220" t="s">
+        <v>694</v>
+      </c>
+      <c r="C220" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>315</v>
+      </c>
+      <c r="B221" t="s">
+        <v>695</v>
+      </c>
+      <c r="C221" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>316</v>
+      </c>
+      <c r="B222" t="s">
+        <v>696</v>
+      </c>
+      <c r="C222" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>46</v>
+      </c>
+      <c r="B223" t="s">
+        <v>697</v>
+      </c>
+      <c r="C223" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>317</v>
+      </c>
+      <c r="B224" t="s">
+        <v>698</v>
+      </c>
+      <c r="C224" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>318</v>
+      </c>
+      <c r="B225" t="s">
+        <v>699</v>
+      </c>
+      <c r="C225" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>318</v>
+      </c>
+      <c r="B226" t="s">
+        <v>700</v>
+      </c>
+      <c r="C226" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>319</v>
+      </c>
+      <c r="B227" t="s">
+        <v>701</v>
+      </c>
+      <c r="C227" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>320</v>
+      </c>
+      <c r="B228" t="s">
+        <v>702</v>
+      </c>
+      <c r="C228" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>320</v>
+      </c>
+      <c r="B229" t="s">
+        <v>703</v>
+      </c>
+      <c r="C229" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>47</v>
+      </c>
+      <c r="B230" t="s">
+        <v>704</v>
+      </c>
+      <c r="C230" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>321</v>
+      </c>
+      <c r="B231" t="s">
+        <v>705</v>
+      </c>
+      <c r="C231" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>322</v>
+      </c>
+      <c r="B232" t="s">
+        <v>706</v>
+      </c>
+      <c r="C232" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>323</v>
+      </c>
+      <c r="B233" t="s">
+        <v>707</v>
+      </c>
+      <c r="C233" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>48</v>
+      </c>
+      <c r="B234" t="s">
+        <v>708</v>
+      </c>
+      <c r="C234" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>324</v>
+      </c>
+      <c r="B235" t="s">
+        <v>709</v>
+      </c>
+      <c r="C235" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>325</v>
+      </c>
+      <c r="B236" t="s">
+        <v>710</v>
+      </c>
+      <c r="C236" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>326</v>
+      </c>
+      <c r="B237" t="s">
+        <v>711</v>
+      </c>
+      <c r="C237" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>326</v>
+      </c>
+      <c r="B238" t="s">
+        <v>712</v>
+      </c>
+      <c r="C238" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>327</v>
+      </c>
+      <c r="B239" t="s">
+        <v>713</v>
+      </c>
+      <c r="C239" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>327</v>
+      </c>
+      <c r="B240" t="s">
+        <v>714</v>
+      </c>
+      <c r="C240" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>328</v>
+      </c>
+      <c r="B241" t="s">
+        <v>715</v>
+      </c>
+      <c r="C241" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>328</v>
+      </c>
+      <c r="B242" t="s">
+        <v>716</v>
+      </c>
+      <c r="C242" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>49</v>
+      </c>
+      <c r="B243" t="s">
+        <v>717</v>
+      </c>
+      <c r="C243" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>49</v>
+      </c>
+      <c r="B244" t="s">
+        <v>718</v>
+      </c>
+      <c r="C244" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>329</v>
+      </c>
+      <c r="B245" t="s">
+        <v>719</v>
+      </c>
+      <c r="C245" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>330</v>
+      </c>
+      <c r="B246" t="s">
+        <v>720</v>
+      </c>
+      <c r="C246" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>331</v>
+      </c>
+      <c r="B247" t="s">
+        <v>721</v>
+      </c>
+      <c r="C247" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>332</v>
+      </c>
+      <c r="B248" t="s">
+        <v>722</v>
+      </c>
+      <c r="C248" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>50</v>
+      </c>
+      <c r="B249" t="s">
+        <v>723</v>
+      </c>
+      <c r="C249" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>51</v>
+      </c>
+      <c r="B250" t="s">
+        <v>724</v>
+      </c>
+      <c r="C250" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>333</v>
+      </c>
+      <c r="B251" t="s">
+        <v>725</v>
+      </c>
+      <c r="C251" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>334</v>
+      </c>
+      <c r="B252" t="s">
+        <v>726</v>
+      </c>
+      <c r="C252" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>335</v>
+      </c>
+      <c r="B253" t="s">
+        <v>727</v>
+      </c>
+      <c r="C253" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>336</v>
+      </c>
+      <c r="B254" t="s">
+        <v>728</v>
+      </c>
+      <c r="C254" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>336</v>
+      </c>
+      <c r="B255" t="s">
+        <v>729</v>
+      </c>
+      <c r="C255" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>52</v>
+      </c>
+      <c r="B256" t="s">
+        <v>730</v>
+      </c>
+      <c r="C256" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>337</v>
+      </c>
+      <c r="B257" t="s">
+        <v>731</v>
+      </c>
+      <c r="C257" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>338</v>
+      </c>
+      <c r="B258" t="s">
+        <v>732</v>
+      </c>
+      <c r="C258" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>339</v>
+      </c>
+      <c r="B259" t="s">
+        <v>733</v>
+      </c>
+      <c r="C259" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>340</v>
+      </c>
+      <c r="B260" t="s">
+        <v>734</v>
+      </c>
+      <c r="C260" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>341</v>
+      </c>
+      <c r="B261" t="s">
+        <v>735</v>
+      </c>
+      <c r="C261" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>342</v>
+      </c>
+      <c r="B262" t="s">
+        <v>736</v>
+      </c>
+      <c r="C262" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>343</v>
+      </c>
+      <c r="B263" t="s">
+        <v>737</v>
+      </c>
+      <c r="C263" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>343</v>
+      </c>
+      <c r="B264" t="s">
+        <v>738</v>
+      </c>
+      <c r="C264" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>344</v>
+      </c>
+      <c r="B265" t="s">
+        <v>739</v>
+      </c>
+      <c r="C265" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>345</v>
+      </c>
+      <c r="B266" t="s">
+        <v>740</v>
+      </c>
+      <c r="C266" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>346</v>
+      </c>
+      <c r="B267" t="s">
+        <v>741</v>
+      </c>
+      <c r="C267" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>347</v>
+      </c>
+      <c r="B268" t="s">
+        <v>742</v>
+      </c>
+      <c r="C268" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>348</v>
+      </c>
+      <c r="B269" t="s">
+        <v>743</v>
+      </c>
+      <c r="C269" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>349</v>
+      </c>
+      <c r="B270" t="s">
+        <v>744</v>
+      </c>
+      <c r="C270" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>350</v>
+      </c>
+      <c r="B271" t="s">
+        <v>745</v>
+      </c>
+      <c r="C271" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>351</v>
+      </c>
+      <c r="B272" t="s">
+        <v>746</v>
+      </c>
+      <c r="C272" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>352</v>
+      </c>
+      <c r="B273" t="s">
+        <v>747</v>
+      </c>
+      <c r="C273" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>353</v>
+      </c>
+      <c r="B274" t="s">
+        <v>748</v>
+      </c>
+      <c r="C274" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>354</v>
+      </c>
+      <c r="B275" t="s">
+        <v>749</v>
+      </c>
+      <c r="C275" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>355</v>
+      </c>
+      <c r="B276" t="s">
+        <v>750</v>
+      </c>
+      <c r="C276" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>356</v>
+      </c>
+      <c r="B277" t="s">
+        <v>751</v>
+      </c>
+      <c r="C277" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>357</v>
+      </c>
+      <c r="B278" t="s">
+        <v>752</v>
+      </c>
+      <c r="C278" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>358</v>
+      </c>
+      <c r="B279" t="s">
+        <v>753</v>
+      </c>
+      <c r="C279" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>359</v>
+      </c>
+      <c r="B280" t="s">
+        <v>754</v>
+      </c>
+      <c r="C280" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>360</v>
+      </c>
+      <c r="B281" t="s">
+        <v>755</v>
+      </c>
+      <c r="C281" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>361</v>
+      </c>
+      <c r="B282" t="s">
+        <v>756</v>
+      </c>
+      <c r="C282" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>362</v>
+      </c>
+      <c r="B283" t="s">
+        <v>757</v>
+      </c>
+      <c r="C283" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>363</v>
+      </c>
+      <c r="B284" t="s">
+        <v>758</v>
+      </c>
+      <c r="C284" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>364</v>
+      </c>
+      <c r="B285" t="s">
+        <v>759</v>
+      </c>
+      <c r="C285" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>365</v>
+      </c>
+      <c r="B286" t="s">
+        <v>760</v>
+      </c>
+      <c r="C286" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>366</v>
+      </c>
+      <c r="B287" t="s">
+        <v>761</v>
+      </c>
+      <c r="C287" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>367</v>
+      </c>
+      <c r="B288" t="s">
+        <v>762</v>
+      </c>
+      <c r="C288" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>368</v>
+      </c>
+      <c r="B289" t="s">
+        <v>763</v>
+      </c>
+      <c r="C289" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>369</v>
+      </c>
+      <c r="B290" t="s">
+        <v>764</v>
+      </c>
+      <c r="C290" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>370</v>
+      </c>
+      <c r="B291" t="s">
+        <v>765</v>
+      </c>
+      <c r="C291" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>371</v>
+      </c>
+      <c r="B292" t="s">
+        <v>766</v>
+      </c>
+      <c r="C292" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>53</v>
+      </c>
+      <c r="B293" t="s">
+        <v>767</v>
+      </c>
+      <c r="C293" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>54</v>
+      </c>
+      <c r="B294" t="s">
+        <v>768</v>
+      </c>
+      <c r="C294" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>55</v>
+      </c>
+      <c r="B295" t="s">
+        <v>769</v>
+      </c>
+      <c r="C295" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>55</v>
+      </c>
+      <c r="B296" t="s">
+        <v>770</v>
+      </c>
+      <c r="C296" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>55</v>
+      </c>
+      <c r="B297" t="s">
+        <v>771</v>
+      </c>
+      <c r="C297" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>56</v>
+      </c>
+      <c r="B298" t="s">
+        <v>772</v>
+      </c>
+      <c r="C298" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>56</v>
+      </c>
+      <c r="B299" t="s">
+        <v>773</v>
+      </c>
+      <c r="C299" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>56</v>
+      </c>
+      <c r="B300" t="s">
+        <v>774</v>
+      </c>
+      <c r="C300" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>57</v>
+      </c>
+      <c r="B301" t="s">
+        <v>775</v>
+      </c>
+      <c r="C301" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>57</v>
+      </c>
+      <c r="B302" t="s">
+        <v>776</v>
+      </c>
+      <c r="C302" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>372</v>
+      </c>
+      <c r="B303" t="s">
+        <v>777</v>
+      </c>
+      <c r="C303" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>372</v>
+      </c>
+      <c r="B304" t="s">
+        <v>778</v>
+      </c>
+      <c r="C304" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>58</v>
+      </c>
+      <c r="B305" t="s">
+        <v>779</v>
+      </c>
+      <c r="C305" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>373</v>
+      </c>
+      <c r="B306" t="s">
+        <v>780</v>
+      </c>
+      <c r="C306" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>59</v>
+      </c>
+      <c r="B307" t="s">
+        <v>781</v>
+      </c>
+      <c r="C307" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>60</v>
+      </c>
+      <c r="B308" t="s">
+        <v>782</v>
+      </c>
+      <c r="C308" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>60</v>
+      </c>
+      <c r="B309" t="s">
+        <v>783</v>
+      </c>
+      <c r="C309" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>60</v>
+      </c>
+      <c r="B310" t="s">
+        <v>784</v>
+      </c>
+      <c r="C310" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>61</v>
+      </c>
+      <c r="B311" t="s">
+        <v>785</v>
+      </c>
+      <c r="C311" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>374</v>
+      </c>
+      <c r="B312" t="s">
+        <v>786</v>
+      </c>
+      <c r="C312" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>62</v>
+      </c>
+      <c r="B313" t="s">
+        <v>787</v>
+      </c>
+      <c r="C313" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>62</v>
+      </c>
+      <c r="B314" t="s">
+        <v>788</v>
+      </c>
+      <c r="C314" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>62</v>
+      </c>
+      <c r="B315" t="s">
+        <v>789</v>
+      </c>
+      <c r="C315" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>63</v>
+      </c>
+      <c r="B316" t="s">
+        <v>790</v>
+      </c>
+      <c r="C316" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>64</v>
+      </c>
+      <c r="B317" t="s">
+        <v>791</v>
+      </c>
+      <c r="C317" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>65</v>
+      </c>
+      <c r="B318" t="s">
+        <v>792</v>
+      </c>
+      <c r="C318" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>66</v>
+      </c>
+      <c r="B319" t="s">
+        <v>793</v>
+      </c>
+      <c r="C319" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>66</v>
+      </c>
+      <c r="B320" t="s">
+        <v>794</v>
+      </c>
+      <c r="C320" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>375</v>
+      </c>
+      <c r="B321" t="s">
+        <v>795</v>
+      </c>
+      <c r="C321" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>375</v>
+      </c>
+      <c r="B322" t="s">
+        <v>796</v>
+      </c>
+      <c r="C322" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>67</v>
+      </c>
+      <c r="B323" t="s">
+        <v>797</v>
+      </c>
+      <c r="C323" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>68</v>
+      </c>
+      <c r="B324" t="s">
+        <v>798</v>
+      </c>
+      <c r="C324" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>68</v>
+      </c>
+      <c r="B325" t="s">
+        <v>799</v>
+      </c>
+      <c r="C325" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>68</v>
+      </c>
+      <c r="B326" t="s">
+        <v>800</v>
+      </c>
+      <c r="C326" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A327" t="s">
+        <v>69</v>
+      </c>
+      <c r="B327" t="s">
+        <v>801</v>
+      </c>
+      <c r="C327" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>70</v>
+      </c>
+      <c r="B328" t="s">
+        <v>802</v>
+      </c>
+      <c r="C328" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A329" t="s">
+        <v>376</v>
+      </c>
+      <c r="B329" t="s">
+        <v>803</v>
+      </c>
+      <c r="C329" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A330" t="s">
+        <v>376</v>
+      </c>
+      <c r="B330" t="s">
+        <v>804</v>
+      </c>
+      <c r="C330" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A331" t="s">
+        <v>71</v>
+      </c>
+      <c r="B331" t="s">
+        <v>805</v>
+      </c>
+      <c r="C331" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A332" t="s">
+        <v>377</v>
+      </c>
+      <c r="B332" t="s">
+        <v>806</v>
+      </c>
+      <c r="C332" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A333" t="s">
+        <v>72</v>
+      </c>
+      <c r="B333" t="s">
+        <v>807</v>
+      </c>
+      <c r="C333" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A334" t="s">
+        <v>73</v>
+      </c>
+      <c r="B334" t="s">
+        <v>808</v>
+      </c>
+      <c r="C334" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A335" t="s">
+        <v>378</v>
+      </c>
+      <c r="B335" t="s">
+        <v>809</v>
+      </c>
+      <c r="C335" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A336" t="s">
+        <v>74</v>
+      </c>
+      <c r="B336" t="s">
+        <v>810</v>
+      </c>
+      <c r="C336" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A337" t="s">
+        <v>75</v>
+      </c>
+      <c r="B337" t="s">
+        <v>811</v>
+      </c>
+      <c r="C337" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A338" t="s">
+        <v>379</v>
+      </c>
+      <c r="B338" t="s">
+        <v>812</v>
+      </c>
+      <c r="C338" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A339" t="s">
+        <v>76</v>
+      </c>
+      <c r="B339" t="s">
+        <v>813</v>
+      </c>
+      <c r="C339" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A340" t="s">
+        <v>4</v>
+      </c>
+      <c r="B340" t="s">
+        <v>814</v>
+      </c>
+      <c r="C340" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A341" t="s">
+        <v>380</v>
+      </c>
+      <c r="B341" t="s">
+        <v>815</v>
+      </c>
+      <c r="C341" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A342" t="s">
+        <v>380</v>
+      </c>
+      <c r="B342" t="s">
+        <v>816</v>
+      </c>
+      <c r="C342" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A343" t="s">
+        <v>380</v>
+      </c>
+      <c r="B343" t="s">
+        <v>817</v>
+      </c>
+      <c r="C343" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A344" t="s">
+        <v>77</v>
+      </c>
+      <c r="B344" t="s">
+        <v>818</v>
+      </c>
+      <c r="C344" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A345" t="s">
+        <v>381</v>
+      </c>
+      <c r="B345" t="s">
+        <v>819</v>
+      </c>
+      <c r="C345" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A346" t="s">
+        <v>382</v>
+      </c>
+      <c r="B346" t="s">
+        <v>820</v>
+      </c>
+      <c r="C346" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A347" t="s">
+        <v>383</v>
+      </c>
+      <c r="B347" t="s">
+        <v>821</v>
+      </c>
+      <c r="C347" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A348" t="s">
+        <v>383</v>
+      </c>
+      <c r="B348" t="s">
+        <v>822</v>
+      </c>
+      <c r="C348" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A349" t="s">
+        <v>78</v>
+      </c>
+      <c r="B349" t="s">
+        <v>823</v>
+      </c>
+      <c r="C349" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A350" t="s">
+        <v>79</v>
+      </c>
+      <c r="B350" t="s">
+        <v>824</v>
+      </c>
+      <c r="C350" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A351" t="s">
+        <v>80</v>
+      </c>
+      <c r="B351" t="s">
+        <v>825</v>
+      </c>
+      <c r="C351" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A352" t="s">
+        <v>81</v>
+      </c>
+      <c r="B352" t="s">
+        <v>826</v>
+      </c>
+      <c r="C352" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A353" t="s">
+        <v>82</v>
+      </c>
+      <c r="B353" t="s">
+        <v>827</v>
+      </c>
+      <c r="C353" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A354" t="s">
+        <v>83</v>
+      </c>
+      <c r="B354" t="s">
+        <v>828</v>
+      </c>
+      <c r="C354" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A355" t="s">
+        <v>84</v>
+      </c>
+      <c r="B355" t="s">
+        <v>829</v>
+      </c>
+      <c r="C355" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A356" t="s">
+        <v>84</v>
+      </c>
+      <c r="B356" t="s">
+        <v>830</v>
+      </c>
+      <c r="C356" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A357" t="s">
+        <v>85</v>
+      </c>
+      <c r="B357" t="s">
+        <v>831</v>
+      </c>
+      <c r="C357" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A358" t="s">
+        <v>86</v>
+      </c>
+      <c r="B358" t="s">
+        <v>832</v>
+      </c>
+      <c r="C358" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A359" t="s">
+        <v>87</v>
+      </c>
+      <c r="B359" t="s">
+        <v>833</v>
+      </c>
+      <c r="C359" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A360" t="s">
+        <v>87</v>
+      </c>
+      <c r="B360" t="s">
+        <v>834</v>
+      </c>
+      <c r="C360" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A361" t="s">
+        <v>384</v>
+      </c>
+      <c r="B361" t="s">
+        <v>835</v>
+      </c>
+      <c r="C361" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A362" t="s">
+        <v>385</v>
+      </c>
+      <c r="B362" t="s">
+        <v>836</v>
+      </c>
+      <c r="C362" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A363" t="s">
+        <v>386</v>
+      </c>
+      <c r="B363" t="s">
+        <v>837</v>
+      </c>
+      <c r="C363" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A364" t="s">
+        <v>386</v>
+      </c>
+      <c r="B364" t="s">
+        <v>838</v>
+      </c>
+      <c r="C364" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A365" t="s">
+        <v>386</v>
+      </c>
+      <c r="B365" t="s">
+        <v>839</v>
+      </c>
+      <c r="C365" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A366" t="s">
+        <v>387</v>
+      </c>
+      <c r="B366" t="s">
+        <v>840</v>
+      </c>
+      <c r="C366" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>387</v>
+      </c>
+      <c r="B367" t="s">
+        <v>841</v>
+      </c>
+      <c r="C367" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>388</v>
+      </c>
+      <c r="B368" t="s">
+        <v>842</v>
+      </c>
+      <c r="C368" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A369" t="s">
+        <v>88</v>
+      </c>
+      <c r="B369" t="s">
+        <v>843</v>
+      </c>
+      <c r="C369" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A370" t="s">
+        <v>389</v>
+      </c>
+      <c r="B370" t="s">
+        <v>844</v>
+      </c>
+      <c r="C370" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>389</v>
+      </c>
+      <c r="B371" t="s">
+        <v>845</v>
+      </c>
+      <c r="C371" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>89</v>
+      </c>
+      <c r="B372" t="s">
+        <v>846</v>
+      </c>
+      <c r="C372" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
+        <v>90</v>
+      </c>
+      <c r="B373" t="s">
+        <v>847</v>
+      </c>
+      <c r="C373" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A374" t="s">
+        <v>91</v>
+      </c>
+      <c r="B374" t="s">
+        <v>848</v>
+      </c>
+      <c r="C374" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A375" t="s">
+        <v>390</v>
+      </c>
+      <c r="B375" t="s">
+        <v>849</v>
+      </c>
+      <c r="C375" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A376" t="s">
+        <v>92</v>
+      </c>
+      <c r="B376" t="s">
+        <v>850</v>
+      </c>
+      <c r="C376" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A377" t="s">
+        <v>93</v>
+      </c>
+      <c r="B377" t="s">
+        <v>851</v>
+      </c>
+      <c r="C377" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A378" t="s">
+        <v>94</v>
+      </c>
+      <c r="B378" t="s">
+        <v>852</v>
+      </c>
+      <c r="C378" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A379" t="s">
+        <v>95</v>
+      </c>
+      <c r="B379" t="s">
+        <v>853</v>
+      </c>
+      <c r="C379" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A380" t="s">
+        <v>96</v>
+      </c>
+      <c r="B380" t="s">
+        <v>854</v>
+      </c>
+      <c r="C380" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A381" t="s">
+        <v>97</v>
+      </c>
+      <c r="B381" t="s">
+        <v>855</v>
+      </c>
+      <c r="C381" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A382" t="s">
+        <v>391</v>
+      </c>
+      <c r="B382" t="s">
+        <v>856</v>
+      </c>
+      <c r="C382" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A383" t="s">
+        <v>98</v>
+      </c>
+      <c r="B383" t="s">
+        <v>857</v>
+      </c>
+      <c r="C383" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A384" t="s">
+        <v>99</v>
+      </c>
+      <c r="B384" t="s">
+        <v>858</v>
+      </c>
+      <c r="C384" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A385" t="s">
+        <v>100</v>
+      </c>
+      <c r="B385" t="s">
+        <v>859</v>
+      </c>
+      <c r="C385" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A386" t="s">
+        <v>101</v>
+      </c>
+      <c r="B386" t="s">
+        <v>860</v>
+      </c>
+      <c r="C386" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A387" t="s">
+        <v>102</v>
+      </c>
+      <c r="B387" t="s">
+        <v>861</v>
+      </c>
+      <c r="C387" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A388" t="s">
+        <v>392</v>
+      </c>
+      <c r="B388" t="s">
+        <v>862</v>
+      </c>
+      <c r="C388" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A389" t="s">
+        <v>392</v>
+      </c>
+      <c r="B389" t="s">
+        <v>863</v>
+      </c>
+      <c r="C389" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A390" t="s">
+        <v>392</v>
+      </c>
+      <c r="B390" t="s">
+        <v>864</v>
+      </c>
+      <c r="C390" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A391" t="s">
+        <v>103</v>
+      </c>
+      <c r="B391" t="s">
+        <v>865</v>
+      </c>
+      <c r="C391" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A392" t="s">
+        <v>103</v>
+      </c>
+      <c r="B392" t="s">
+        <v>866</v>
+      </c>
+      <c r="C392" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A393" t="s">
+        <v>103</v>
+      </c>
+      <c r="B393" t="s">
+        <v>867</v>
+      </c>
+      <c r="C393" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A394" t="s">
+        <v>393</v>
+      </c>
+      <c r="B394" t="s">
+        <v>868</v>
+      </c>
+      <c r="C394" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A395" t="s">
+        <v>393</v>
+      </c>
+      <c r="B395" t="s">
+        <v>869</v>
+      </c>
+      <c r="C395" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A396" t="s">
+        <v>104</v>
+      </c>
+      <c r="B396" t="s">
+        <v>870</v>
+      </c>
+      <c r="C396" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A397" t="s">
+        <v>105</v>
+      </c>
+      <c r="B397" t="s">
+        <v>871</v>
+      </c>
+      <c r="C397" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A398" t="s">
+        <v>106</v>
+      </c>
+      <c r="B398" t="s">
+        <v>872</v>
+      </c>
+      <c r="C398" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A399" t="s">
+        <v>394</v>
+      </c>
+      <c r="B399" t="s">
+        <v>873</v>
+      </c>
+      <c r="C399" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A400" t="s">
         <v>107</v>
       </c>
-      <c r="C106" t="s">
+      <c r="B400" t="s">
+        <v>874</v>
+      </c>
+      <c r="C400" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A401" t="s">
+        <v>395</v>
+      </c>
+      <c r="B401" t="s">
+        <v>875</v>
+      </c>
+      <c r="C401" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A402" t="s">
+        <v>396</v>
+      </c>
+      <c r="B402" t="s">
+        <v>876</v>
+      </c>
+      <c r="C402" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A403" t="s">
+        <v>397</v>
+      </c>
+      <c r="B403" t="s">
+        <v>877</v>
+      </c>
+      <c r="C403" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A404" t="s">
+        <v>398</v>
+      </c>
+      <c r="B404" t="s">
+        <v>878</v>
+      </c>
+      <c r="C404" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A405" t="s">
         <v>108</v>
       </c>
-      <c r="C107" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
+      <c r="B405" t="s">
+        <v>879</v>
+      </c>
+      <c r="C405" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A406" t="s">
         <v>109</v>
       </c>
-      <c r="C108" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
+      <c r="B406" t="s">
+        <v>880</v>
+      </c>
+      <c r="C406" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A407" t="s">
         <v>110</v>
       </c>
-      <c r="C109" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" s="2" t="s">
+      <c r="B407" t="s">
+        <v>881</v>
+      </c>
+      <c r="C407" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A408" t="s">
         <v>111</v>
       </c>
-      <c r="C110" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
+      <c r="B408" t="s">
+        <v>882</v>
+      </c>
+      <c r="C408" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A409" t="s">
         <v>112</v>
       </c>
-      <c r="C111" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" s="2" t="s">
+      <c r="B409" t="s">
+        <v>883</v>
+      </c>
+      <c r="C409" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A410" t="s">
         <v>113</v>
       </c>
-      <c r="C112" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" s="2" t="s">
+      <c r="B410" t="s">
+        <v>884</v>
+      </c>
+      <c r="C410" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A411" t="s">
         <v>114</v>
       </c>
-      <c r="C113" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114" s="2" t="s">
+      <c r="B411" t="s">
+        <v>885</v>
+      </c>
+      <c r="C411" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A412" t="s">
+        <v>399</v>
+      </c>
+      <c r="B412" t="s">
+        <v>886</v>
+      </c>
+      <c r="C412" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A413" t="s">
+        <v>399</v>
+      </c>
+      <c r="B413" t="s">
+        <v>887</v>
+      </c>
+      <c r="C413" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A414" t="s">
+        <v>400</v>
+      </c>
+      <c r="B414" t="s">
+        <v>888</v>
+      </c>
+      <c r="C414" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A415" t="s">
+        <v>400</v>
+      </c>
+      <c r="B415" t="s">
+        <v>889</v>
+      </c>
+      <c r="C415" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A416" t="s">
+        <v>400</v>
+      </c>
+      <c r="B416" t="s">
+        <v>890</v>
+      </c>
+      <c r="C416" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A417" t="s">
+        <v>400</v>
+      </c>
+      <c r="B417" t="s">
+        <v>891</v>
+      </c>
+      <c r="C417" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A418" t="s">
         <v>115</v>
       </c>
-      <c r="C114" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
+      <c r="B418" t="s">
+        <v>892</v>
+      </c>
+      <c r="C418" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A419" t="s">
+        <v>401</v>
+      </c>
+      <c r="B419" t="s">
+        <v>893</v>
+      </c>
+      <c r="C419" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A420" t="s">
+        <v>402</v>
+      </c>
+      <c r="B420" t="s">
+        <v>894</v>
+      </c>
+      <c r="C420" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A421" t="s">
+        <v>403</v>
+      </c>
+      <c r="B421" t="s">
+        <v>895</v>
+      </c>
+      <c r="C421" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A422" t="s">
+        <v>404</v>
+      </c>
+      <c r="B422" t="s">
+        <v>896</v>
+      </c>
+      <c r="C422" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A423" t="s">
+        <v>405</v>
+      </c>
+      <c r="B423" t="s">
+        <v>897</v>
+      </c>
+      <c r="C423" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A424" t="s">
+        <v>406</v>
+      </c>
+      <c r="B424" t="s">
+        <v>898</v>
+      </c>
+      <c r="C424" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A425" t="s">
+        <v>407</v>
+      </c>
+      <c r="B425" t="s">
+        <v>899</v>
+      </c>
+      <c r="C425" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A426" t="s">
+        <v>408</v>
+      </c>
+      <c r="B426" t="s">
+        <v>900</v>
+      </c>
+      <c r="C426" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A427" t="s">
+        <v>409</v>
+      </c>
+      <c r="B427" t="s">
+        <v>901</v>
+      </c>
+      <c r="C427" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A428" t="s">
+        <v>410</v>
+      </c>
+      <c r="B428" t="s">
+        <v>902</v>
+      </c>
+      <c r="C428" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A429" t="s">
+        <v>410</v>
+      </c>
+      <c r="B429" t="s">
+        <v>903</v>
+      </c>
+      <c r="C429" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A430" t="s">
+        <v>411</v>
+      </c>
+      <c r="B430" t="s">
+        <v>904</v>
+      </c>
+      <c r="C430" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A431" t="s">
+        <v>412</v>
+      </c>
+      <c r="B431" t="s">
+        <v>905</v>
+      </c>
+      <c r="C431" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A432" t="s">
+        <v>413</v>
+      </c>
+      <c r="B432" t="s">
+        <v>906</v>
+      </c>
+      <c r="C432" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A433" t="s">
+        <v>414</v>
+      </c>
+      <c r="B433" t="s">
+        <v>907</v>
+      </c>
+      <c r="C433" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A434" t="s">
+        <v>414</v>
+      </c>
+      <c r="B434" t="s">
+        <v>908</v>
+      </c>
+      <c r="C434" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A435" t="s">
+        <v>415</v>
+      </c>
+      <c r="B435" t="s">
+        <v>909</v>
+      </c>
+      <c r="C435" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A436" t="s">
+        <v>416</v>
+      </c>
+      <c r="B436" t="s">
+        <v>910</v>
+      </c>
+      <c r="C436" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A437" t="s">
+        <v>417</v>
+      </c>
+      <c r="B437" t="s">
+        <v>911</v>
+      </c>
+      <c r="C437" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A438" t="s">
+        <v>418</v>
+      </c>
+      <c r="B438" t="s">
+        <v>912</v>
+      </c>
+      <c r="C438" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A439" t="s">
+        <v>419</v>
+      </c>
+      <c r="B439" t="s">
+        <v>913</v>
+      </c>
+      <c r="C439" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A440" t="s">
+        <v>420</v>
+      </c>
+      <c r="B440" t="s">
+        <v>914</v>
+      </c>
+      <c r="C440" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A441" t="s">
+        <v>421</v>
+      </c>
+      <c r="B441" t="s">
+        <v>915</v>
+      </c>
+      <c r="C441" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A442" t="s">
+        <v>422</v>
+      </c>
+      <c r="B442" t="s">
+        <v>916</v>
+      </c>
+      <c r="C442" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A443" t="s">
+        <v>423</v>
+      </c>
+      <c r="B443" t="s">
+        <v>917</v>
+      </c>
+      <c r="C443" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A444" t="s">
+        <v>424</v>
+      </c>
+      <c r="B444" t="s">
+        <v>918</v>
+      </c>
+      <c r="C444" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A445" t="s">
+        <v>425</v>
+      </c>
+      <c r="B445" t="s">
+        <v>919</v>
+      </c>
+      <c r="C445" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A446" t="s">
+        <v>426</v>
+      </c>
+      <c r="B446" t="s">
+        <v>920</v>
+      </c>
+      <c r="C446" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A447" t="s">
+        <v>427</v>
+      </c>
+      <c r="B447" t="s">
+        <v>921</v>
+      </c>
+      <c r="C447" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A448" t="s">
+        <v>428</v>
+      </c>
+      <c r="B448" t="s">
+        <v>922</v>
+      </c>
+      <c r="C448" t="s">
         <v>116</v>
       </c>
-      <c r="C115" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C116" t="s">
-        <v>118</v>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A449" t="s">
+        <v>429</v>
+      </c>
+      <c r="B449" t="s">
+        <v>923</v>
+      </c>
+      <c r="C449" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A450" t="s">
+        <v>430</v>
+      </c>
+      <c r="B450" t="s">
+        <v>924</v>
+      </c>
+      <c r="C450" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A451" t="s">
+        <v>431</v>
+      </c>
+      <c r="B451" t="s">
+        <v>925</v>
+      </c>
+      <c r="C451" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A452" t="s">
+        <v>432</v>
+      </c>
+      <c r="B452" t="s">
+        <v>926</v>
+      </c>
+      <c r="C452" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A453" t="s">
+        <v>433</v>
+      </c>
+      <c r="B453" t="s">
+        <v>927</v>
+      </c>
+      <c r="C453" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A454" t="s">
+        <v>434</v>
+      </c>
+      <c r="B454" t="s">
+        <v>928</v>
+      </c>
+      <c r="C454" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A455" t="s">
+        <v>435</v>
+      </c>
+      <c r="B455" t="s">
+        <v>929</v>
+      </c>
+      <c r="C455" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A456" t="s">
+        <v>436</v>
+      </c>
+      <c r="B456" t="s">
+        <v>930</v>
+      </c>
+      <c r="C456" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A457" t="s">
+        <v>437</v>
+      </c>
+      <c r="B457" t="s">
+        <v>931</v>
+      </c>
+      <c r="C457" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A458" t="s">
+        <v>438</v>
+      </c>
+      <c r="B458" t="s">
+        <v>932</v>
+      </c>
+      <c r="C458" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A459" t="s">
+        <v>439</v>
+      </c>
+      <c r="B459" t="s">
+        <v>933</v>
+      </c>
+      <c r="C459" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A460" t="s">
+        <v>440</v>
+      </c>
+      <c r="B460" t="s">
+        <v>934</v>
+      </c>
+      <c r="C460" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A461" t="s">
+        <v>441</v>
+      </c>
+      <c r="B461" t="s">
+        <v>935</v>
+      </c>
+      <c r="C461" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A462" t="s">
+        <v>441</v>
+      </c>
+      <c r="B462" t="s">
+        <v>936</v>
+      </c>
+      <c r="C462" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A463" t="s">
+        <v>441</v>
+      </c>
+      <c r="B463" t="s">
+        <v>937</v>
+      </c>
+      <c r="C463" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A464" t="s">
+        <v>442</v>
+      </c>
+      <c r="B464" t="s">
+        <v>938</v>
+      </c>
+      <c r="C464" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A465" t="s">
+        <v>443</v>
+      </c>
+      <c r="B465" t="s">
+        <v>939</v>
+      </c>
+      <c r="C465" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A466" t="s">
+        <v>443</v>
+      </c>
+      <c r="B466" t="s">
+        <v>940</v>
+      </c>
+      <c r="C466" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A467" t="s">
+        <v>444</v>
+      </c>
+      <c r="B467" t="s">
+        <v>941</v>
+      </c>
+      <c r="C467" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A468" t="s">
+        <v>445</v>
+      </c>
+      <c r="B468" t="s">
+        <v>942</v>
+      </c>
+      <c r="C468" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A469" t="s">
+        <v>446</v>
+      </c>
+      <c r="B469" t="s">
+        <v>943</v>
+      </c>
+      <c r="C469" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A470" t="s">
+        <v>447</v>
+      </c>
+      <c r="B470" t="s">
+        <v>944</v>
+      </c>
+      <c r="C470" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A471" t="s">
+        <v>448</v>
+      </c>
+      <c r="B471" t="s">
+        <v>945</v>
+      </c>
+      <c r="C471" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A472" t="s">
+        <v>449</v>
+      </c>
+      <c r="B472" t="s">
+        <v>946</v>
+      </c>
+      <c r="C472" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A473" t="s">
+        <v>450</v>
+      </c>
+      <c r="B473" t="s">
+        <v>947</v>
+      </c>
+      <c r="C473" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A474" t="s">
+        <v>451</v>
+      </c>
+      <c r="B474" t="s">
+        <v>948</v>
+      </c>
+      <c r="C474" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A475" t="s">
+        <v>451</v>
+      </c>
+      <c r="B475" t="s">
+        <v>949</v>
+      </c>
+      <c r="C475" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A476" t="s">
+        <v>452</v>
+      </c>
+      <c r="B476" t="s">
+        <v>950</v>
+      </c>
+      <c r="C476" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A477" t="s">
+        <v>453</v>
+      </c>
+      <c r="B477" t="s">
+        <v>951</v>
+      </c>
+      <c r="C477" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A478" t="s">
+        <v>454</v>
+      </c>
+      <c r="B478" t="s">
+        <v>952</v>
+      </c>
+      <c r="C478" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A479" t="s">
+        <v>455</v>
+      </c>
+      <c r="B479" t="s">
+        <v>953</v>
+      </c>
+      <c r="C479" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A480" t="s">
+        <v>456</v>
+      </c>
+      <c r="B480" t="s">
+        <v>954</v>
+      </c>
+      <c r="C480" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A481" t="s">
+        <v>457</v>
+      </c>
+      <c r="B481" t="s">
+        <v>955</v>
+      </c>
+      <c r="C481" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A482" t="s">
+        <v>458</v>
+      </c>
+      <c r="B482" t="s">
+        <v>956</v>
+      </c>
+      <c r="C482" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A483" t="s">
+        <v>458</v>
+      </c>
+      <c r="B483" t="s">
+        <v>957</v>
+      </c>
+      <c r="C483" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A484" t="s">
+        <v>458</v>
+      </c>
+      <c r="B484" t="s">
+        <v>958</v>
+      </c>
+      <c r="C484" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A485" t="s">
+        <v>459</v>
+      </c>
+      <c r="B485" t="s">
+        <v>959</v>
+      </c>
+      <c r="C485" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A486" t="s">
+        <v>460</v>
+      </c>
+      <c r="B486" t="s">
+        <v>960</v>
+      </c>
+      <c r="C486" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A487" t="s">
+        <v>461</v>
+      </c>
+      <c r="B487" t="s">
+        <v>961</v>
+      </c>
+      <c r="C487" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A488" t="s">
+        <v>462</v>
+      </c>
+      <c r="B488" t="s">
+        <v>962</v>
+      </c>
+      <c r="C488" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A489" t="s">
+        <v>463</v>
+      </c>
+      <c r="B489" t="s">
+        <v>963</v>
+      </c>
+      <c r="C489" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A490" t="s">
+        <v>464</v>
+      </c>
+      <c r="B490" t="s">
+        <v>964</v>
+      </c>
+      <c r="C490" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A491" t="s">
+        <v>465</v>
+      </c>
+      <c r="B491" t="s">
+        <v>965</v>
+      </c>
+      <c r="C491" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A492" t="s">
+        <v>466</v>
+      </c>
+      <c r="B492" t="s">
+        <v>966</v>
+      </c>
+      <c r="C492" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A493" t="s">
+        <v>467</v>
+      </c>
+      <c r="B493" t="s">
+        <v>967</v>
+      </c>
+      <c r="C493" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A494" t="s">
+        <v>468</v>
+      </c>
+      <c r="B494" t="s">
+        <v>968</v>
+      </c>
+      <c r="C494" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A495" t="s">
+        <v>469</v>
+      </c>
+      <c r="B495" t="s">
+        <v>969</v>
+      </c>
+      <c r="C495" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A496" t="s">
+        <v>469</v>
+      </c>
+      <c r="B496" t="s">
+        <v>970</v>
+      </c>
+      <c r="C496" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A497" t="s">
+        <v>470</v>
+      </c>
+      <c r="B497" t="s">
+        <v>971</v>
+      </c>
+      <c r="C497" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A498" t="s">
+        <v>470</v>
+      </c>
+      <c r="B498" t="s">
+        <v>972</v>
+      </c>
+      <c r="C498" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A499" t="s">
+        <v>471</v>
+      </c>
+      <c r="B499" t="s">
+        <v>471</v>
+      </c>
+      <c r="C499" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A500" t="s">
+        <v>472</v>
+      </c>
+      <c r="B500" t="s">
+        <v>472</v>
+      </c>
+      <c r="C500" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A501" t="s">
+        <v>473</v>
+      </c>
+      <c r="B501" t="s">
+        <v>473</v>
+      </c>
+      <c r="C501" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A502" t="s">
+        <v>474</v>
+      </c>
+      <c r="B502" t="s">
+        <v>474</v>
+      </c>
+      <c r="C502" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A503" t="s">
+        <v>475</v>
+      </c>
+      <c r="B503" t="s">
+        <v>475</v>
+      </c>
+      <c r="C503" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E541BB-710E-46CD-9442-B70FDDCDDEEA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8BD413-A013-44E7-A080-10D51D466602}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="946">
   <si>
     <t>UTK</t>
   </si>
@@ -1311,9 +1311,6 @@
     <t>R423021</t>
   </si>
   <si>
-    <t>NFD6-06-09-JCC4</t>
-  </si>
-  <si>
     <t>NFD6-05-30-98WH</t>
   </si>
   <si>
@@ -2439,9 +2436,6 @@
     <t>314508296/1</t>
   </si>
   <si>
-    <t>NFD6-06-09-JCC4/1</t>
-  </si>
-  <si>
     <t>6a22c60c6410baf6763cdfda</t>
   </si>
   <si>
@@ -2851,6 +2845,27 @@
   </si>
   <si>
     <t>202606082601203101</t>
+  </si>
+  <si>
+    <t>K-917</t>
+  </si>
+  <si>
+    <t>NFD6-06-05-ZB4F</t>
+  </si>
+  <si>
+    <t>NFD6-06-07-N9V9</t>
+  </si>
+  <si>
+    <t>NFD6-06-05-ZB4F/1</t>
+  </si>
+  <si>
+    <t>NFD6-06-07-N9V9/1</t>
+  </si>
+  <si>
+    <t>NFD6-06-07-N9V9/2</t>
+  </si>
+  <si>
+    <t>NFD6-06-07-N9V9/3</t>
   </si>
 </sst>
 </file>
@@ -3170,7 +3185,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D485"/>
+  <dimension ref="A1:D488"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
@@ -3195,7 +3210,7 @@
         <v>189</v>
       </c>
       <c r="B2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C2" t="s">
         <v>140</v>
@@ -3207,7 +3222,7 @@
         <v>190</v>
       </c>
       <c r="B3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C3" t="s">
         <v>141</v>
@@ -3219,7 +3234,7 @@
         <v>190</v>
       </c>
       <c r="B4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C4" t="s">
         <v>141</v>
@@ -3231,7 +3246,7 @@
         <v>191</v>
       </c>
       <c r="B5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C5" t="s">
         <v>141</v>
@@ -3243,7 +3258,7 @@
         <v>192</v>
       </c>
       <c r="B6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C6" t="s">
         <v>141</v>
@@ -3255,7 +3270,7 @@
         <v>193</v>
       </c>
       <c r="B7" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C7" t="s">
         <v>141</v>
@@ -3267,7 +3282,7 @@
         <v>194</v>
       </c>
       <c r="B8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C8" t="s">
         <v>142</v>
@@ -3279,7 +3294,7 @@
         <v>195</v>
       </c>
       <c r="B9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C9" t="s">
         <v>142</v>
@@ -3291,7 +3306,7 @@
         <v>195</v>
       </c>
       <c r="B10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C10" t="s">
         <v>142</v>
@@ -3303,7 +3318,7 @@
         <v>196</v>
       </c>
       <c r="B11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C11" t="s">
         <v>142</v>
@@ -3315,7 +3330,7 @@
         <v>197</v>
       </c>
       <c r="B12" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C12" t="s">
         <v>142</v>
@@ -3327,7 +3342,7 @@
         <v>198</v>
       </c>
       <c r="B13" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C13" t="s">
         <v>142</v>
@@ -3339,7 +3354,7 @@
         <v>199</v>
       </c>
       <c r="B14" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C14" t="s">
         <v>142</v>
@@ -3351,7 +3366,7 @@
         <v>200</v>
       </c>
       <c r="B15" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C15" t="s">
         <v>142</v>
@@ -3363,7 +3378,7 @@
         <v>200</v>
       </c>
       <c r="B16" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C16" t="s">
         <v>142</v>
@@ -3375,7 +3390,7 @@
         <v>201</v>
       </c>
       <c r="B17" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C17" t="s">
         <v>142</v>
@@ -3387,7 +3402,7 @@
         <v>202</v>
       </c>
       <c r="B18" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C18" t="s">
         <v>142</v>
@@ -3399,7 +3414,7 @@
         <v>203</v>
       </c>
       <c r="B19" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C19" t="s">
         <v>143</v>
@@ -3411,7 +3426,7 @@
         <v>204</v>
       </c>
       <c r="B20" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C20" t="s">
         <v>143</v>
@@ -3423,7 +3438,7 @@
         <v>205</v>
       </c>
       <c r="B21" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C21" t="s">
         <v>143</v>
@@ -3435,7 +3450,7 @@
         <v>206</v>
       </c>
       <c r="B22" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C22" t="s">
         <v>143</v>
@@ -3447,7 +3462,7 @@
         <v>206</v>
       </c>
       <c r="B23" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C23" t="s">
         <v>143</v>
@@ -3459,7 +3474,7 @@
         <v>207</v>
       </c>
       <c r="B24" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C24" t="s">
         <v>143</v>
@@ -3471,7 +3486,7 @@
         <v>208</v>
       </c>
       <c r="B25" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C25" t="s">
         <v>143</v>
@@ -3483,7 +3498,7 @@
         <v>209</v>
       </c>
       <c r="B26" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C26" t="s">
         <v>143</v>
@@ -3495,7 +3510,7 @@
         <v>210</v>
       </c>
       <c r="B27" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C27" t="s">
         <v>144</v>
@@ -3507,7 +3522,7 @@
         <v>210</v>
       </c>
       <c r="B28" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C28" t="s">
         <v>144</v>
@@ -3519,7 +3534,7 @@
         <v>211</v>
       </c>
       <c r="B29" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C29" t="s">
         <v>144</v>
@@ -3531,7 +3546,7 @@
         <v>212</v>
       </c>
       <c r="B30" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C30" t="s">
         <v>144</v>
@@ -3543,7 +3558,7 @@
         <v>213</v>
   